--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="1154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="1182">
   <si>
     <t>##var</t>
   </si>
@@ -3502,6 +3502,90 @@
   </si>
   <si>
     <t>Reklam Yüklenemedi</t>
+  </si>
+  <si>
+    <t>瓶子已满啦</t>
+  </si>
+  <si>
+    <t>Bottle full</t>
+  </si>
+  <si>
+    <t>Flasche voll</t>
+  </si>
+  <si>
+    <t>ボトル満杯</t>
+  </si>
+  <si>
+    <t>Frasco cheio</t>
+  </si>
+  <si>
+    <t>Bouteille pleine</t>
+  </si>
+  <si>
+    <t>Botella llena</t>
+  </si>
+  <si>
+    <t>병 가득함</t>
+  </si>
+  <si>
+    <t>Botol penuh</t>
+  </si>
+  <si>
+    <t>Бутылка полна</t>
+  </si>
+  <si>
+    <t>बोतल भरी</t>
+  </si>
+  <si>
+    <t>ขวดเต็ม</t>
+  </si>
+  <si>
+    <t>Şişe dolu</t>
+  </si>
+  <si>
+    <t>最上面一层颜色相同才可以倒入</t>
+  </si>
+  <si>
+    <t>Top color must match to pour</t>
+  </si>
+  <si>
+    <t>Nur bei gleicher Farbe oben</t>
+  </si>
+  <si>
+    <t>上と同じ色のみ注げる</t>
+  </si>
+  <si>
+    <t>Só se cor do topo for igual</t>
+  </si>
+  <si>
+    <t>Couche supérieure identique requise</t>
+  </si>
+  <si>
+    <t>Solo si el color superior coincide</t>
+  </si>
+  <si>
+    <t>맨 윗층 색깔이 같아야 부움</t>
+  </si>
+  <si>
+    <t>Hanya jika warna atas sama</t>
+  </si>
+  <si>
+    <t>Только если верхний слой одного цвета</t>
+  </si>
+  <si>
+    <t>ऊपरी रंग समान हो तभी डालें</t>
+  </si>
+  <si>
+    <t>เทได้ต่อเมื่อสีชั้นบนสุดเหมือนกัน</t>
+  </si>
+  <si>
+    <t>Sadece üst renk aynıysa dök</t>
+  </si>
+  <si>
+    <t>选择要打乱的瓶子</t>
+  </si>
+  <si>
+    <t>Select the bottle to be Shuffled</t>
   </si>
 </sst>
 </file>
@@ -8999,6 +9083,105 @@
         <v>1153</v>
       </c>
     </row>
+    <row r="96" customHeight="1" spans="2:15">
+      <c r="B96" s="9">
+        <v>10091</v>
+      </c>
+      <c r="C96" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E96" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F96" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G96" t="s">
+        <v>1158</v>
+      </c>
+      <c r="H96" t="s">
+        <v>1159</v>
+      </c>
+      <c r="I96" t="s">
+        <v>1160</v>
+      </c>
+      <c r="J96" t="s">
+        <v>1161</v>
+      </c>
+      <c r="K96" t="s">
+        <v>1162</v>
+      </c>
+      <c r="L96" t="s">
+        <v>1163</v>
+      </c>
+      <c r="M96" t="s">
+        <v>1164</v>
+      </c>
+      <c r="N96" t="s">
+        <v>1165</v>
+      </c>
+      <c r="O96" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="2:16">
+      <c r="B97" s="9">
+        <v>10092</v>
+      </c>
+      <c r="C97" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E97" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F97" t="s">
+        <v>1170</v>
+      </c>
+      <c r="G97" t="s">
+        <v>1171</v>
+      </c>
+      <c r="H97" t="s">
+        <v>1172</v>
+      </c>
+      <c r="I97" t="s">
+        <v>1173</v>
+      </c>
+      <c r="J97" t="s">
+        <v>1174</v>
+      </c>
+      <c r="K97" t="s">
+        <v>1175</v>
+      </c>
+      <c r="L97" t="s">
+        <v>1176</v>
+      </c>
+      <c r="M97" t="s">
+        <v>1177</v>
+      </c>
+      <c r="N97" t="s">
+        <v>1178</v>
+      </c>
+      <c r="O97" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="2:16">
+      <c r="B98" s="2">
+        <v>10093</v>
+      </c>
+      <c r="C98" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>1181</v>
+      </c>
+    </row>
     <row r="101" customHeight="1" spans="2:16">
       <c r="G101" s="12"/>
       <c r="K101" s="12"/>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="1182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="1184">
   <si>
     <t>##var</t>
   </si>
@@ -3585,7 +3585,13 @@
     <t>选择要打乱的瓶子</t>
   </si>
   <si>
-    <t>Select the bottle to be Shuffled</t>
+    <t>Select a bottle to be Shuffled</t>
+  </si>
+  <si>
+    <t>打乱成功</t>
+  </si>
+  <si>
+    <t>Shuffle success</t>
   </si>
 </sst>
 </file>
@@ -9182,6 +9188,17 @@
         <v>1181</v>
       </c>
     </row>
+    <row r="99" customHeight="1" spans="2:16">
+      <c r="B99" s="2">
+        <v>10094</v>
+      </c>
+      <c r="C99" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>1183</v>
+      </c>
+    </row>
     <row r="101" customHeight="1" spans="2:16">
       <c r="G101" s="12"/>
       <c r="K101" s="12"/>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="1184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="1186">
   <si>
     <t>##var</t>
   </si>
@@ -3592,6 +3592,12 @@
   </si>
   <si>
     <t>Shuffle success</t>
+  </si>
+  <si>
+    <t>玩家</t>
+  </si>
+  <si>
+    <t>Player</t>
   </si>
 </sst>
 </file>
@@ -9199,6 +9205,17 @@
         <v>1183</v>
       </c>
     </row>
+    <row r="100" customHeight="1" spans="2:16">
+      <c r="B100" s="2">
+        <v>10095</v>
+      </c>
+      <c r="C100" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>1185</v>
+      </c>
+    </row>
     <row r="101" customHeight="1" spans="2:16">
       <c r="G101" s="12"/>
       <c r="K101" s="12"/>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="1186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="1188">
   <si>
     <t>##var</t>
   </si>
@@ -3598,6 +3598,12 @@
   </si>
   <si>
     <t>Player</t>
+  </si>
+  <si>
+    <t>该瓶子无法打乱</t>
+  </si>
+  <si>
+    <t>This bottle cannot be Shuffled</t>
   </si>
 </sst>
 </file>
@@ -9217,6 +9223,15 @@
       </c>
     </row>
     <row r="101" customHeight="1" spans="2:16">
+      <c r="B101" s="2">
+        <v>10096</v>
+      </c>
+      <c r="C101" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>1187</v>
+      </c>
       <c r="G101" s="12"/>
       <c r="K101" s="12"/>
     </row>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="1188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="1190">
   <si>
     <t>##var</t>
   </si>
@@ -3604,6 +3604,12 @@
   </si>
   <si>
     <t>This bottle cannot be Shuffled</t>
+  </si>
+  <si>
+    <t>没有更多的袋子需解锁</t>
+  </si>
+  <si>
+    <t>No more pockets need to be unlocked</t>
   </si>
 </sst>
 </file>
@@ -9236,6 +9242,15 @@
       <c r="K101" s="12"/>
     </row>
     <row r="102" customHeight="1" spans="2:16">
+      <c r="B102" s="2">
+        <v>10097</v>
+      </c>
+      <c r="C102" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>1189</v>
+      </c>
       <c r="G102" s="12"/>
       <c r="K102" s="12"/>
     </row>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="1190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="1217">
   <si>
     <t>##var</t>
   </si>
@@ -3610,6 +3610,226 @@
   </si>
   <si>
     <t>No more pockets need to be unlocked</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>余额达到{0}方可提现</t>
+  </si>
+  <si>
+    <t>Balance reaches {0} withdraw</t>
+  </si>
+  <si>
+    <t>Guthaben erreicht {0} – Abheben möglich</t>
+  </si>
+  <si>
+    <t>残高が{0}に達すると出金できます</t>
+  </si>
+  <si>
+    <t>Saldo atinge {0} para sacar</t>
+  </si>
+  <si>
+    <t>Le solde atteint {0} pour retirer</t>
+  </si>
+  <si>
+    <t>El saldo alcanza {0} para retirar</t>
+  </si>
+  <si>
+    <t>잔액이 {0}에 도달하면 출금 가능</t>
+  </si>
+  <si>
+    <t>Saldo mencapai {0} untuk menarik</t>
+  </si>
+  <si>
+    <t>Баланс достигает {0} — можно вывести</t>
+  </si>
+  <si>
+    <t>शेष {0} पर पहुँचने पर निकाल सकते हैं</t>
+  </si>
+  <si>
+    <t>ยอดถึง {0} จึงถอนได้</t>
+  </si>
+  <si>
+    <t>Bakiye {0}'a ulaşınca çekilebilir</t>
+  </si>
+  <si>
+    <t>签到{0}日方可提现</t>
+  </si>
+  <si>
+    <t>Check-in {0} days to be credited</t>
+  </si>
+  <si>
+    <t>Sie können erst abheben, wenn Sie {0} Tage lang eingecheckt haben</t>
+  </si>
+  <si>
+    <t>{0}日間サインインしたら出金可能です</t>
+  </si>
+  <si>
+    <t>Você só pode sacar após fazer check-in por {0} dias</t>
+  </si>
+  <si>
+    <t>Vous ne pouvez retirer qu'après avoir fait le check-in pendant {0} jours</t>
+  </si>
+  <si>
+    <t>Solo puedes retirar después de hacer check-in durante {0} días</t>
+  </si>
+  <si>
+    <r>
+      <t>{0}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>동안</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>출석</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>체크해야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>출금</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>가능하며</t>
+    </r>
+  </si>
+  <si>
+    <t>Anda hanya dapat menarik setelah check-in selama {0} hari</t>
+  </si>
+  <si>
+    <t>Вы можете вывести деньги только после {0} дней регистрации</t>
+  </si>
+  <si>
+    <t>आप तभी निकासी कर सकते हैं जब आप {0} दिनों तक चेक-इन करें</t>
+  </si>
+  <si>
+    <t>คุณสามารถถอนเงินได้เมื่อเช็คอินครบ {0} วัน</t>
+  </si>
+  <si>
+    <r>
+      <t>{0} gün check-in yapt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ığı</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ı</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>zda çekebilirsiniz</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3622,7 +3842,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3641,6 +3861,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3779,6 +4005,18 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="MS Gothic"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -4122,16 +4360,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4140,125 +4375,129 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4288,8 +4527,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -4831,7 +5070,7 @@
   <sheetFormatPr defaultColWidth="9.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.875" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="3" customWidth="1"/>
     <col min="3" max="3" width="31.625" customWidth="1"/>
     <col min="4" max="4" width="54.25" style="1" customWidth="1"/>
     <col min="5" max="6" width="28.125" customWidth="1"/>
@@ -4841,49 +5080,49 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:16">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="7" t="s">
         <v>14</v>
       </c>
       <c r="P1" t="s">
@@ -4891,68 +5130,68 @@
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:16">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
     </row>
     <row r="3" customHeight="1" spans="1:16">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="6" t="s">
         <v>17</v>
       </c>
       <c r="P3" t="s">
@@ -4960,49 +5199,49 @@
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:16">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="M4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="N4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="O4" s="9" t="s">
         <v>19</v>
       </c>
       <c r="P4" t="s">
@@ -5010,49 +5249,49 @@
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:16">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="M5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="N5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="O5" s="6" t="s">
         <v>33</v>
       </c>
       <c r="P5" t="s">
@@ -5060,1059 +5299,1059 @@
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="13.5" spans="1:16">
-      <c r="B6" s="9">
+      <c r="B6" s="10">
         <v>10001</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="K6" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="L6" s="10" t="s">
+      <c r="L6" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="M6" s="10" t="s">
+      <c r="M6" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="N6" s="10" t="s">
+      <c r="N6" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="O6" s="10" t="s">
+      <c r="O6" s="11" t="s">
         <v>47</v>
       </c>
       <c r="P6"/>
     </row>
     <row r="7" customFormat="1" customHeight="1" spans="1:16">
-      <c r="B7" s="9">
+      <c r="B7" s="10">
         <v>10002</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="K7" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="10" t="s">
+      <c r="L7" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="M7" s="10" t="s">
+      <c r="M7" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="N7" s="10" t="s">
+      <c r="N7" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="O7" s="10" t="s">
+      <c r="O7" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:16">
-      <c r="B8" s="9">
+      <c r="B8" s="10">
         <v>10003</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="J8" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="K8" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="L8" s="10" t="s">
+      <c r="L8" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="M8" s="10" t="s">
+      <c r="M8" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="N8" s="10" t="s">
+      <c r="N8" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="O8" s="10" t="s">
+      <c r="O8" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:16">
-      <c r="B9" s="9">
+      <c r="B9" s="10">
         <v>10004</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="J9" s="10" t="s">
+      <c r="J9" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="K9" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="L9" s="10" t="s">
+      <c r="L9" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="M9" s="10" t="s">
+      <c r="M9" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="N9" s="10" t="s">
+      <c r="N9" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="O9" s="10" t="s">
+      <c r="O9" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:16">
-      <c r="B10" s="9">
+      <c r="B10" s="10">
         <v>10005</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="J10" s="10" t="s">
+      <c r="J10" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="K10" s="10" t="s">
+      <c r="K10" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="L10" s="10" t="s">
+      <c r="L10" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="M10" s="10" t="s">
+      <c r="M10" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="N10" s="10" t="s">
+      <c r="N10" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="O10" s="10" t="s">
+      <c r="O10" s="11" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:16">
-      <c r="B11" s="9">
+      <c r="B11" s="10">
         <v>10006</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="J11" s="10" t="s">
+      <c r="J11" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="L11" s="10" t="s">
+      <c r="L11" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="M11" s="10" t="s">
+      <c r="M11" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="N11" s="10" t="s">
+      <c r="N11" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="O11" s="10" t="s">
+      <c r="O11" s="11" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="B12" s="9">
+      <c r="B12" s="10">
         <v>10007</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="J12" s="10" t="s">
+      <c r="J12" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="K12" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="L12" s="10" t="s">
+      <c r="L12" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="M12" s="10" t="s">
+      <c r="M12" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="N12" s="10" t="s">
+      <c r="N12" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="O12" s="10" t="s">
+      <c r="O12" s="11" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="B13" s="9">
+      <c r="B13" s="10">
         <v>10008</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I13" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="J13" s="10" t="s">
+      <c r="J13" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="K13" s="10" t="s">
+      <c r="K13" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="L13" s="10" t="s">
+      <c r="L13" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="M13" s="10" t="s">
+      <c r="M13" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="N13" s="10" t="s">
+      <c r="N13" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="O13" s="10" t="s">
+      <c r="O13" s="11" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:16">
-      <c r="B14" s="9">
+      <c r="B14" s="10">
         <v>10009</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G14" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="I14" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="J14" s="10" t="s">
+      <c r="J14" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="K14" s="10" t="s">
+      <c r="K14" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="L14" s="10" t="s">
+      <c r="L14" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="M14" s="10" t="s">
+      <c r="M14" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="N14" s="10" t="s">
+      <c r="N14" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="O14" s="10" t="s">
+      <c r="O14" s="11" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:16">
-      <c r="B15" s="9">
+      <c r="B15" s="10">
         <v>10010</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="G15" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="I15" s="10" t="s">
+      <c r="I15" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="J15" s="10" t="s">
+      <c r="J15" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="K15" s="10" t="s">
+      <c r="K15" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="L15" s="10" t="s">
+      <c r="L15" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="M15" s="10" t="s">
+      <c r="M15" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="N15" s="10" t="s">
+      <c r="N15" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="O15" s="10" t="s">
+      <c r="O15" s="11" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:16">
-      <c r="B16" s="9">
+      <c r="B16" s="10">
         <v>10011</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="H16" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="I16" s="10" t="s">
+      <c r="I16" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="J16" s="10" t="s">
+      <c r="J16" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="K16" s="10" t="s">
+      <c r="K16" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="L16" s="10" t="s">
+      <c r="L16" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="M16" s="10" t="s">
+      <c r="M16" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="N16" s="10" t="s">
+      <c r="N16" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="O16" s="10" t="s">
+      <c r="O16" s="11" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:23">
-      <c r="B17" s="9">
+      <c r="B17" s="10">
         <v>10012</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="I17" s="10" t="s">
+      <c r="I17" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="J17" s="10" t="s">
+      <c r="J17" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="K17" s="10" t="s">
+      <c r="K17" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="L17" s="10" t="s">
+      <c r="L17" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="M17" s="10" t="s">
+      <c r="M17" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="N17" s="10" t="s">
+      <c r="N17" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="O17" s="10" t="s">
+      <c r="O17" s="11" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:23">
-      <c r="B18" s="9">
+      <c r="B18" s="10">
         <v>10013</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="H18" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="I18" s="10" t="s">
+      <c r="I18" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="J18" s="10" t="s">
+      <c r="J18" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="K18" s="10" t="s">
+      <c r="K18" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="L18" s="10" t="s">
+      <c r="L18" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="M18" s="10" t="s">
+      <c r="M18" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="N18" s="10" t="s">
+      <c r="N18" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="O18" s="10" t="s">
+      <c r="O18" s="11" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:23">
-      <c r="B19" s="9">
+      <c r="B19" s="10">
         <v>10014</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="I19" s="10" t="s">
+      <c r="I19" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="J19" s="10" t="s">
+      <c r="J19" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="K19" s="10" t="s">
+      <c r="K19" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="L19" s="10" t="s">
+      <c r="L19" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="M19" s="10" t="s">
+      <c r="M19" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="N19" s="10" t="s">
+      <c r="N19" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="O19" s="10" t="s">
+      <c r="O19" s="11" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:23">
-      <c r="B20" s="9">
+      <c r="B20" s="10">
         <v>10015</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="G20" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H20" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="I20" s="10" t="s">
+      <c r="I20" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="J20" s="10" t="s">
+      <c r="J20" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="K20" s="10" t="s">
+      <c r="K20" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="L20" s="10" t="s">
+      <c r="L20" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="M20" s="10" t="s">
+      <c r="M20" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="N20" s="10" t="s">
+      <c r="N20" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="O20" s="10" t="s">
+      <c r="O20" s="11" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:23">
-      <c r="B21" s="9">
+      <c r="B21" s="10">
         <v>10016</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="G21" s="10" t="s">
+      <c r="G21" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="H21" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="I21" s="10" t="s">
+      <c r="I21" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="J21" s="10" t="s">
+      <c r="J21" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="K21" s="10" t="s">
+      <c r="K21" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="L21" s="10" t="s">
+      <c r="L21" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="M21" s="10" t="s">
+      <c r="M21" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="N21" s="10" t="s">
+      <c r="N21" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="O21" s="10" t="s">
+      <c r="O21" s="11" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:23">
-      <c r="B22" s="9">
+      <c r="B22" s="10">
         <v>10017</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="G22" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="H22" s="10" t="s">
+      <c r="H22" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="I22" s="10" t="s">
+      <c r="I22" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="J22" s="10" t="s">
+      <c r="J22" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="K22" s="10" t="s">
+      <c r="K22" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="L22" s="10" t="s">
+      <c r="L22" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="M22" s="10" t="s">
+      <c r="M22" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="N22" s="10" t="s">
+      <c r="N22" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="O22" s="10" t="s">
+      <c r="O22" s="11" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:23">
-      <c r="B23" s="9">
+      <c r="B23" s="10">
         <v>10018</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="G23" s="10" t="s">
+      <c r="G23" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="H23" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="I23" s="10" t="s">
+      <c r="I23" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="J23" s="10" t="s">
+      <c r="J23" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="K23" s="10" t="s">
+      <c r="K23" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="L23" s="10" t="s">
+      <c r="L23" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="M23" s="10" t="s">
+      <c r="M23" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="N23" s="10" t="s">
+      <c r="N23" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="O23" s="10" t="s">
+      <c r="O23" s="11" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="2:23">
-      <c r="B24" s="9">
+      <c r="B24" s="10">
         <v>10019</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="G24" s="10" t="s">
+      <c r="G24" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="H24" s="10" t="s">
+      <c r="H24" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="I24" s="10" t="s">
+      <c r="I24" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="J24" s="10" t="s">
+      <c r="J24" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="K24" s="10" t="s">
+      <c r="K24" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="L24" s="10" t="s">
+      <c r="L24" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="M24" s="10" t="s">
+      <c r="M24" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="N24" s="10" t="s">
+      <c r="N24" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="O24" s="10" t="s">
+      <c r="O24" s="11" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="2:23">
-      <c r="B25" s="9">
+      <c r="B25" s="10">
         <v>10020</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E25" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="F25" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="G25" s="10" t="s">
+      <c r="G25" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="H25" s="10" t="s">
+      <c r="H25" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="I25" s="10" t="s">
+      <c r="I25" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="J25" s="10" t="s">
+      <c r="J25" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="K25" s="10" t="s">
+      <c r="K25" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="L25" s="10" t="s">
+      <c r="L25" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="M25" s="10" t="s">
+      <c r="M25" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="N25" s="10" t="s">
+      <c r="N25" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="O25" s="10" t="s">
+      <c r="O25" s="11" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:23">
-      <c r="B26" s="9">
+      <c r="B26" s="10">
         <v>10021</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="11" t="s">
         <v>289</v>
       </c>
-      <c r="F26" s="10" t="s">
+      <c r="F26" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="G26" s="10" t="s">
+      <c r="G26" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="H26" s="10" t="s">
+      <c r="H26" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="I26" s="10" t="s">
+      <c r="I26" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="J26" s="10" t="s">
+      <c r="J26" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="K26" s="10" t="s">
+      <c r="K26" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="L26" s="10" t="s">
+      <c r="L26" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="M26" s="10" t="s">
+      <c r="M26" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="N26" s="10" t="s">
+      <c r="N26" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="O26" s="10" t="s">
+      <c r="O26" s="11" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:23">
-      <c r="B27" s="9">
+      <c r="B27" s="10">
         <v>10022</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="11" t="s">
         <v>302</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="G27" s="10" t="s">
+      <c r="G27" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="H27" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="I27" s="10" t="s">
+      <c r="I27" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="J27" s="10" t="s">
+      <c r="J27" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="K27" s="10" t="s">
+      <c r="K27" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="L27" s="10" t="s">
+      <c r="L27" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="M27" s="10" t="s">
+      <c r="M27" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="N27" s="10" t="s">
+      <c r="N27" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="O27" s="10" t="s">
+      <c r="O27" s="11" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="28" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B28" s="9">
+      <c r="B28" s="10">
         <v>10023</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="G28" s="10" t="s">
+      <c r="G28" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="H28" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="I28" s="10" t="s">
+      <c r="I28" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="J28" s="10" t="s">
+      <c r="J28" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="K28" s="10" t="s">
+      <c r="K28" s="11" t="s">
         <v>320</v>
       </c>
-      <c r="L28" s="10" t="s">
+      <c r="L28" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="M28" s="10" t="s">
+      <c r="M28" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="N28" s="10" t="s">
+      <c r="N28" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="O28" s="10" t="s">
+      <c r="O28" s="11" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="29" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B29" s="9">
+      <c r="B29" s="10">
         <v>10024</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="D29" s="12" t="s">
         <v>326</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="F29" s="10" t="s">
+      <c r="F29" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="G29" s="10" t="s">
+      <c r="G29" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="H29" s="10" t="s">
+      <c r="H29" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="I29" s="10" t="s">
+      <c r="I29" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="J29" s="10" t="s">
+      <c r="J29" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="K29" s="10" t="s">
+      <c r="K29" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="L29" s="10" t="s">
+      <c r="L29" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="M29" s="10" t="s">
+      <c r="M29" s="11" t="s">
         <v>335</v>
       </c>
-      <c r="N29" s="10" t="s">
+      <c r="N29" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="O29" s="10" t="s">
+      <c r="O29" s="11" t="s">
         <v>337</v>
       </c>
       <c r="Q29" s="1"/>
@@ -6124,46 +6363,46 @@
       <c r="W29" s="1"/>
     </row>
     <row r="30" customHeight="1" spans="2:23">
-      <c r="B30" s="9">
+      <c r="B30" s="10">
         <v>10025</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" s="12" t="s">
         <v>338</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="F30" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="G30" s="10" t="s">
+      <c r="G30" s="11" t="s">
         <v>341</v>
       </c>
-      <c r="H30" s="10" t="s">
+      <c r="H30" s="11" t="s">
         <v>342</v>
       </c>
-      <c r="I30" s="10" t="s">
+      <c r="I30" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="J30" s="10" t="s">
+      <c r="J30" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="K30" s="10" t="s">
+      <c r="K30" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="L30" s="10" t="s">
+      <c r="L30" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="M30" s="10" t="s">
+      <c r="M30" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="N30" s="10" t="s">
+      <c r="N30" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="O30" s="10" t="s">
+      <c r="O30" s="11" t="s">
         <v>349</v>
       </c>
       <c r="P30" s="1"/>
@@ -6176,46 +6415,46 @@
       <c r="W30" s="1"/>
     </row>
     <row r="31" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B31" s="9">
+      <c r="B31" s="10">
         <v>10026</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="12" t="s">
         <v>351</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="E31" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="F31" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="G31" s="10" t="s">
+      <c r="G31" s="11" t="s">
         <v>354</v>
       </c>
-      <c r="H31" s="10" t="s">
+      <c r="H31" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="I31" s="10" t="s">
+      <c r="I31" s="11" t="s">
         <v>354</v>
       </c>
-      <c r="J31" s="10" t="s">
+      <c r="J31" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="K31" s="10" t="s">
+      <c r="K31" s="11" t="s">
         <v>357</v>
       </c>
-      <c r="L31" s="10" t="s">
+      <c r="L31" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="M31" s="10" t="s">
+      <c r="M31" s="11" t="s">
         <v>359</v>
       </c>
-      <c r="N31" s="10" t="s">
+      <c r="N31" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="O31" s="10" t="s">
+      <c r="O31" s="11" t="s">
         <v>361</v>
       </c>
       <c r="P31"/>
@@ -6228,135 +6467,135 @@
       <c r="W31" s="1"/>
     </row>
     <row r="32" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B32" s="9">
+      <c r="B32" s="10">
         <v>10027</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="11" t="s">
         <v>362</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="11" t="s">
         <v>363</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E32" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="F32" s="10" t="s">
+      <c r="F32" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="G32" s="10" t="s">
+      <c r="G32" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="H32" s="10" t="s">
+      <c r="H32" s="11" t="s">
         <v>366</v>
       </c>
-      <c r="I32" s="10" t="s">
+      <c r="I32" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="J32" s="10" t="s">
+      <c r="J32" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="K32" s="10" t="s">
+      <c r="K32" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="L32" s="10" t="s">
+      <c r="L32" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="M32" s="10" t="s">
+      <c r="M32" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="N32" s="10" t="s">
+      <c r="N32" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="O32" s="10" t="s">
+      <c r="O32" s="11" t="s">
         <v>372</v>
       </c>
       <c r="P32"/>
     </row>
     <row r="33" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B33" s="9">
+      <c r="B33" s="10">
         <v>10028</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="12" t="s">
         <v>373</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="E33" s="11" t="s">
         <v>375</v>
       </c>
-      <c r="F33" s="10" t="s">
+      <c r="F33" s="11" t="s">
         <v>376</v>
       </c>
-      <c r="G33" s="10" t="s">
+      <c r="G33" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="H33" s="10" t="s">
+      <c r="H33" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="I33" s="10" t="s">
+      <c r="I33" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="J33" s="10" t="s">
+      <c r="J33" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="K33" s="10" t="s">
+      <c r="K33" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="L33" s="10" t="s">
+      <c r="L33" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="M33" s="10" t="s">
+      <c r="M33" s="11" t="s">
         <v>383</v>
       </c>
-      <c r="N33" s="10" t="s">
+      <c r="N33" s="11" t="s">
         <v>384</v>
       </c>
-      <c r="O33" s="10" t="s">
+      <c r="O33" s="11" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B34" s="9">
+      <c r="B34" s="10">
         <v>10029</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="11" t="s">
         <v>386</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="E34" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="F34" s="10" t="s">
+      <c r="F34" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="G34" s="10" t="s">
+      <c r="G34" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="H34" s="10" t="s">
+      <c r="H34" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="I34" s="10" t="s">
+      <c r="I34" s="11" t="s">
         <v>391</v>
       </c>
-      <c r="J34" s="10" t="s">
+      <c r="J34" s="11" t="s">
         <v>392</v>
       </c>
-      <c r="K34" s="10" t="s">
+      <c r="K34" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="L34" s="10" t="s">
+      <c r="L34" s="11" t="s">
         <v>393</v>
       </c>
-      <c r="M34" s="10" t="s">
+      <c r="M34" s="11" t="s">
         <v>394</v>
       </c>
-      <c r="N34" s="10" t="s">
+      <c r="N34" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="O34" s="10" t="s">
+      <c r="O34" s="11" t="s">
         <v>396</v>
       </c>
       <c r="Q34"/>
@@ -6368,46 +6607,46 @@
       <c r="W34"/>
     </row>
     <row r="35" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B35" s="9">
+      <c r="B35" s="10">
         <v>10030</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C35" s="12" t="s">
         <v>397</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="11" t="s">
         <v>398</v>
       </c>
-      <c r="E35" s="10" t="s">
+      <c r="E35" s="11" t="s">
         <v>399</v>
       </c>
-      <c r="F35" s="10" t="s">
+      <c r="F35" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="G35" s="10" t="s">
+      <c r="G35" s="11" t="s">
         <v>401</v>
       </c>
-      <c r="H35" s="10" t="s">
+      <c r="H35" s="11" t="s">
         <v>402</v>
       </c>
-      <c r="I35" s="10" t="s">
+      <c r="I35" s="11" t="s">
         <v>403</v>
       </c>
-      <c r="J35" s="10" t="s">
+      <c r="J35" s="11" t="s">
         <v>404</v>
       </c>
-      <c r="K35" s="10" t="s">
+      <c r="K35" s="11" t="s">
         <v>405</v>
       </c>
-      <c r="L35" s="10" t="s">
+      <c r="L35" s="11" t="s">
         <v>406</v>
       </c>
-      <c r="M35" s="10" t="s">
+      <c r="M35" s="11" t="s">
         <v>407</v>
       </c>
-      <c r="N35" s="10" t="s">
+      <c r="N35" s="11" t="s">
         <v>408</v>
       </c>
-      <c r="O35" s="10" t="s">
+      <c r="O35" s="11" t="s">
         <v>409</v>
       </c>
       <c r="P35"/>
@@ -6420,46 +6659,46 @@
       <c r="W35"/>
     </row>
     <row r="36" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B36" s="9">
+      <c r="B36" s="10">
         <v>10031</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C36" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="D36" s="11" t="s">
         <v>411</v>
       </c>
-      <c r="E36" s="10" t="s">
+      <c r="E36" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="F36" s="10" t="s">
+      <c r="F36" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="G36" s="10" t="s">
+      <c r="G36" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="H36" s="10" t="s">
+      <c r="H36" s="11" t="s">
         <v>414</v>
       </c>
-      <c r="I36" s="10" t="s">
+      <c r="I36" s="11" t="s">
         <v>415</v>
       </c>
-      <c r="J36" s="10" t="s">
+      <c r="J36" s="11" t="s">
         <v>416</v>
       </c>
-      <c r="K36" s="10" t="s">
+      <c r="K36" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="L36" s="10" t="s">
+      <c r="L36" s="11" t="s">
         <v>417</v>
       </c>
-      <c r="M36" s="10" t="s">
+      <c r="M36" s="11" t="s">
         <v>418</v>
       </c>
-      <c r="N36" s="10" t="s">
+      <c r="N36" s="11" t="s">
         <v>419</v>
       </c>
-      <c r="O36" s="10" t="s">
+      <c r="O36" s="11" t="s">
         <v>420</v>
       </c>
       <c r="P36"/>
@@ -6472,46 +6711,46 @@
       <c r="W36"/>
     </row>
     <row r="37" customHeight="1" spans="2:23">
-      <c r="B37" s="9">
+      <c r="B37" s="10">
         <v>10032</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C37" s="12" t="s">
         <v>421</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="D37" s="11" t="s">
         <v>422</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="11" t="s">
         <v>423</v>
       </c>
-      <c r="F37" s="10" t="s">
+      <c r="F37" s="11" t="s">
         <v>424</v>
       </c>
-      <c r="G37" s="10" t="s">
+      <c r="G37" s="11" t="s">
         <v>425</v>
       </c>
-      <c r="H37" s="10" t="s">
+      <c r="H37" s="11" t="s">
         <v>426</v>
       </c>
-      <c r="I37" s="10" t="s">
+      <c r="I37" s="11" t="s">
         <v>427</v>
       </c>
-      <c r="J37" s="10" t="s">
+      <c r="J37" s="11" t="s">
         <v>428</v>
       </c>
-      <c r="K37" s="10" t="s">
+      <c r="K37" s="11" t="s">
         <v>429</v>
       </c>
-      <c r="L37" s="10" t="s">
+      <c r="L37" s="11" t="s">
         <v>430</v>
       </c>
-      <c r="M37" s="10" t="s">
+      <c r="M37" s="11" t="s">
         <v>431</v>
       </c>
-      <c r="N37" s="10" t="s">
+      <c r="N37" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="O37" s="10" t="s">
+      <c r="O37" s="11" t="s">
         <v>433</v>
       </c>
       <c r="Q37" s="1"/>
@@ -6523,46 +6762,46 @@
       <c r="W37" s="1"/>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B38" s="9">
+      <c r="B38" s="10">
         <v>10033</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="C38" s="11" t="s">
         <v>434</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" s="11" t="s">
         <v>435</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="E38" s="11" t="s">
         <v>436</v>
       </c>
-      <c r="F38" s="10" t="s">
+      <c r="F38" s="11" t="s">
         <v>437</v>
       </c>
-      <c r="G38" s="10" t="s">
+      <c r="G38" s="11" t="s">
         <v>438</v>
       </c>
-      <c r="H38" s="10" t="s">
+      <c r="H38" s="11" t="s">
         <v>439</v>
       </c>
-      <c r="I38" s="10" t="s">
+      <c r="I38" s="11" t="s">
         <v>440</v>
       </c>
-      <c r="J38" s="10" t="s">
+      <c r="J38" s="11" t="s">
         <v>441</v>
       </c>
-      <c r="K38" s="10" t="s">
+      <c r="K38" s="11" t="s">
         <v>442</v>
       </c>
-      <c r="L38" s="10" t="s">
+      <c r="L38" s="11" t="s">
         <v>443</v>
       </c>
-      <c r="M38" s="10" t="s">
+      <c r="M38" s="11" t="s">
         <v>444</v>
       </c>
-      <c r="N38" s="10" t="s">
+      <c r="N38" s="11" t="s">
         <v>445</v>
       </c>
-      <c r="O38" s="10" t="s">
+      <c r="O38" s="11" t="s">
         <v>446</v>
       </c>
       <c r="P38" s="1"/>
@@ -6575,90 +6814,90 @@
       <c r="W38" s="1"/>
     </row>
     <row r="39" customHeight="1" spans="2:23">
-      <c r="B39" s="9">
+      <c r="B39" s="10">
         <v>10034</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C39" s="11" t="s">
         <v>447</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="11" t="s">
         <v>448</v>
       </c>
-      <c r="E39" s="10" t="s">
+      <c r="E39" s="11" t="s">
         <v>449</v>
       </c>
-      <c r="F39" s="10" t="s">
+      <c r="F39" s="11" t="s">
         <v>450</v>
       </c>
-      <c r="G39" s="10" t="s">
+      <c r="G39" s="11" t="s">
         <v>451</v>
       </c>
-      <c r="H39" s="10" t="s">
+      <c r="H39" s="11" t="s">
         <v>452</v>
       </c>
-      <c r="I39" s="10" t="s">
+      <c r="I39" s="11" t="s">
         <v>453</v>
       </c>
-      <c r="J39" s="10" t="s">
+      <c r="J39" s="11" t="s">
         <v>454</v>
       </c>
-      <c r="K39" s="10" t="s">
+      <c r="K39" s="11" t="s">
         <v>455</v>
       </c>
-      <c r="L39" s="10" t="s">
+      <c r="L39" s="11" t="s">
         <v>456</v>
       </c>
-      <c r="M39" s="10" t="s">
+      <c r="M39" s="11" t="s">
         <v>457</v>
       </c>
-      <c r="N39" s="10" t="s">
+      <c r="N39" s="11" t="s">
         <v>458</v>
       </c>
-      <c r="O39" s="10" t="s">
+      <c r="O39" s="11" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" ht="20" customHeight="1" spans="2:23">
-      <c r="B40" s="9">
+      <c r="B40" s="10">
         <v>10035</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C40" s="11" t="s">
         <v>460</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="D40" s="11" t="s">
         <v>461</v>
       </c>
-      <c r="E40" s="10" t="s">
+      <c r="E40" s="11" t="s">
         <v>462</v>
       </c>
-      <c r="F40" s="10" t="s">
+      <c r="F40" s="11" t="s">
         <v>463</v>
       </c>
-      <c r="G40" s="10" t="s">
+      <c r="G40" s="11" t="s">
         <v>464</v>
       </c>
-      <c r="H40" s="10" t="s">
+      <c r="H40" s="11" t="s">
         <v>465</v>
       </c>
-      <c r="I40" s="10" t="s">
+      <c r="I40" s="11" t="s">
         <v>466</v>
       </c>
-      <c r="J40" s="10" t="s">
+      <c r="J40" s="11" t="s">
         <v>467</v>
       </c>
-      <c r="K40" s="10" t="s">
+      <c r="K40" s="11" t="s">
         <v>468</v>
       </c>
-      <c r="L40" s="10" t="s">
+      <c r="L40" s="11" t="s">
         <v>469</v>
       </c>
-      <c r="M40" s="10" t="s">
+      <c r="M40" s="11" t="s">
         <v>470</v>
       </c>
-      <c r="N40" s="10" t="s">
+      <c r="N40" s="11" t="s">
         <v>471</v>
       </c>
-      <c r="O40" s="10" t="s">
+      <c r="O40" s="11" t="s">
         <v>472</v>
       </c>
       <c r="P40"/>
@@ -6671,46 +6910,46 @@
       <c r="W40"/>
     </row>
     <row r="41" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B41" s="9">
+      <c r="B41" s="10">
         <v>10036</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="C41" s="12" t="s">
         <v>473</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" s="11" t="s">
         <v>474</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="E41" s="11" t="s">
         <v>475</v>
       </c>
-      <c r="F41" s="10" t="s">
+      <c r="F41" s="11" t="s">
         <v>476</v>
       </c>
-      <c r="G41" s="10" t="s">
+      <c r="G41" s="11" t="s">
         <v>477</v>
       </c>
-      <c r="H41" s="10" t="s">
+      <c r="H41" s="11" t="s">
         <v>478</v>
       </c>
-      <c r="I41" s="10" t="s">
+      <c r="I41" s="11" t="s">
         <v>477</v>
       </c>
-      <c r="J41" s="10" t="s">
+      <c r="J41" s="11" t="s">
         <v>479</v>
       </c>
-      <c r="K41" s="10" t="s">
+      <c r="K41" s="11" t="s">
         <v>480</v>
       </c>
-      <c r="L41" s="10" t="s">
+      <c r="L41" s="11" t="s">
         <v>481</v>
       </c>
-      <c r="M41" s="10" t="s">
+      <c r="M41" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="N41" s="10" t="s">
+      <c r="N41" s="11" t="s">
         <v>483</v>
       </c>
-      <c r="O41" s="10" t="s">
+      <c r="O41" s="11" t="s">
         <v>484</v>
       </c>
       <c r="P41"/>
@@ -6723,226 +6962,226 @@
       <c r="W41"/>
     </row>
     <row r="42" customHeight="1" spans="2:23">
-      <c r="B42" s="9">
+      <c r="B42" s="10">
         <v>10037</v>
       </c>
-      <c r="C42" s="11" t="s">
+      <c r="C42" s="12" t="s">
         <v>485</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="D42" s="11" t="s">
         <v>486</v>
       </c>
-      <c r="E42" s="10" t="s">
+      <c r="E42" s="11" t="s">
         <v>487</v>
       </c>
-      <c r="F42" s="10" t="s">
+      <c r="F42" s="11" t="s">
         <v>488</v>
       </c>
-      <c r="G42" s="10" t="s">
+      <c r="G42" s="11" t="s">
         <v>489</v>
       </c>
-      <c r="H42" s="10" t="s">
+      <c r="H42" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="I42" s="10" t="s">
+      <c r="I42" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="J42" s="10" t="s">
+      <c r="J42" s="11" t="s">
         <v>492</v>
       </c>
-      <c r="K42" s="10" t="s">
+      <c r="K42" s="11" t="s">
         <v>493</v>
       </c>
-      <c r="L42" s="10" t="s">
+      <c r="L42" s="11" t="s">
         <v>494</v>
       </c>
-      <c r="M42" s="10" t="s">
+      <c r="M42" s="11" t="s">
         <v>495</v>
       </c>
-      <c r="N42" s="10" t="s">
+      <c r="N42" s="11" t="s">
         <v>496</v>
       </c>
-      <c r="O42" s="10" t="s">
+      <c r="O42" s="11" t="s">
         <v>497</v>
       </c>
       <c r="P42" s="1"/>
     </row>
     <row r="43" customHeight="1" spans="2:23">
-      <c r="B43" s="9">
+      <c r="B43" s="10">
         <v>10038</v>
       </c>
-      <c r="C43" s="10" t="s">
+      <c r="C43" s="11" t="s">
         <v>498</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D43" s="11" t="s">
         <v>499</v>
       </c>
-      <c r="E43" s="10" t="s">
+      <c r="E43" s="11" t="s">
         <v>500</v>
       </c>
-      <c r="F43" s="10" t="s">
+      <c r="F43" s="11" t="s">
         <v>501</v>
       </c>
-      <c r="G43" s="10" t="s">
+      <c r="G43" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="H43" s="10" t="s">
+      <c r="H43" s="11" t="s">
         <v>503</v>
       </c>
-      <c r="I43" s="10" t="s">
+      <c r="I43" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="J43" s="10" t="s">
+      <c r="J43" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="K43" s="10" t="s">
+      <c r="K43" s="11" t="s">
         <v>506</v>
       </c>
-      <c r="L43" s="10" t="s">
+      <c r="L43" s="11" t="s">
         <v>507</v>
       </c>
-      <c r="M43" s="10" t="s">
+      <c r="M43" s="11" t="s">
         <v>508</v>
       </c>
-      <c r="N43" s="10" t="s">
+      <c r="N43" s="11" t="s">
         <v>509</v>
       </c>
-      <c r="O43" s="10" t="s">
+      <c r="O43" s="11" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:23">
-      <c r="B44" s="9">
+      <c r="B44" s="10">
         <v>10039</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C44" s="11" t="s">
         <v>511</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" s="11" t="s">
         <v>512</v>
       </c>
-      <c r="E44" s="10" t="s">
+      <c r="E44" s="11" t="s">
         <v>512</v>
       </c>
-      <c r="F44" s="10" t="s">
+      <c r="F44" s="11" t="s">
         <v>513</v>
       </c>
-      <c r="G44" s="10" t="s">
+      <c r="G44" s="11" t="s">
         <v>514</v>
       </c>
-      <c r="H44" s="10" t="s">
+      <c r="H44" s="11" t="s">
         <v>512</v>
       </c>
-      <c r="I44" s="10" t="s">
+      <c r="I44" s="11" t="s">
         <v>515</v>
       </c>
-      <c r="J44" s="10" t="s">
+      <c r="J44" s="11" t="s">
         <v>516</v>
       </c>
-      <c r="K44" s="10" t="s">
+      <c r="K44" s="11" t="s">
         <v>517</v>
       </c>
-      <c r="L44" s="10" t="s">
+      <c r="L44" s="11" t="s">
         <v>518</v>
       </c>
-      <c r="M44" s="10" t="s">
+      <c r="M44" s="11" t="s">
         <v>519</v>
       </c>
-      <c r="N44" s="10" t="s">
+      <c r="N44" s="11" t="s">
         <v>520</v>
       </c>
-      <c r="O44" s="10" t="s">
+      <c r="O44" s="11" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:23">
-      <c r="B45" s="9">
+      <c r="B45" s="10">
         <v>10040</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="D45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="E45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="F45" s="10" t="s">
+      <c r="F45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="G45" s="10" t="s">
+      <c r="G45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="H45" s="10" t="s">
+      <c r="H45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="I45" s="10" t="s">
+      <c r="I45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="J45" s="10" t="s">
+      <c r="J45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="K45" s="10" t="s">
+      <c r="K45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="L45" s="10" t="s">
+      <c r="L45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="M45" s="10" t="s">
+      <c r="M45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="N45" s="10" t="s">
+      <c r="N45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="O45" s="10" t="s">
+      <c r="O45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="P45" s="12" t="s">
+      <c r="P45" s="13" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:23">
-      <c r="B46" s="9">
+      <c r="B46" s="10">
         <v>10041</v>
       </c>
-      <c r="C46" s="10" t="s">
+      <c r="C46" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="D46" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="E46" s="10" t="s">
+      <c r="E46" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="F46" s="10" t="s">
+      <c r="F46" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="G46" s="10" t="s">
+      <c r="G46" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="H46" s="10" t="s">
+      <c r="H46" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="I46" s="10" t="s">
+      <c r="I46" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="J46" s="10" t="s">
+      <c r="J46" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="K46" s="10" t="s">
+      <c r="K46" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="L46" s="10" t="s">
+      <c r="L46" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="M46" s="10" t="s">
+      <c r="M46" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="N46" s="10" t="s">
+      <c r="N46" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="O46" s="10" t="s">
+      <c r="O46" s="11" t="s">
         <v>523</v>
       </c>
       <c r="P46" t="s">
@@ -6950,2165 +7189,2165 @@
       </c>
     </row>
     <row r="47" customHeight="1" spans="2:23">
-      <c r="B47" s="9">
+      <c r="B47" s="10">
         <v>10042</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="C47" s="11" t="s">
         <v>524</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D47" s="12" t="s">
         <v>525</v>
       </c>
-      <c r="E47" s="10" t="s">
+      <c r="E47" s="11" t="s">
         <v>526</v>
       </c>
-      <c r="F47" s="10" t="s">
+      <c r="F47" s="11" t="s">
         <v>527</v>
       </c>
-      <c r="G47" s="10" t="s">
+      <c r="G47" s="11" t="s">
         <v>528</v>
       </c>
-      <c r="H47" s="10" t="s">
+      <c r="H47" s="11" t="s">
         <v>529</v>
       </c>
-      <c r="I47" s="10" t="s">
+      <c r="I47" s="11" t="s">
         <v>530</v>
       </c>
-      <c r="J47" s="10" t="s">
+      <c r="J47" s="11" t="s">
         <v>531</v>
       </c>
-      <c r="K47" s="10" t="s">
+      <c r="K47" s="11" t="s">
         <v>532</v>
       </c>
-      <c r="L47" s="10" t="s">
+      <c r="L47" s="11" t="s">
         <v>533</v>
       </c>
-      <c r="M47" s="10" t="s">
+      <c r="M47" s="11" t="s">
         <v>534</v>
       </c>
-      <c r="N47" s="10" t="s">
+      <c r="N47" s="11" t="s">
         <v>535</v>
       </c>
-      <c r="O47" s="10" t="s">
+      <c r="O47" s="11" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="2:23">
-      <c r="B48" s="9">
+      <c r="B48" s="10">
         <v>10043</v>
       </c>
-      <c r="C48" s="10" t="s">
+      <c r="C48" s="11" t="s">
         <v>537</v>
       </c>
-      <c r="D48" s="11" t="s">
+      <c r="D48" s="12" t="s">
         <v>538</v>
       </c>
-      <c r="E48" s="10" t="s">
+      <c r="E48" s="11" t="s">
         <v>539</v>
       </c>
-      <c r="F48" s="10" t="s">
+      <c r="F48" s="11" t="s">
         <v>540</v>
       </c>
-      <c r="G48" s="10" t="s">
+      <c r="G48" s="11" t="s">
         <v>541</v>
       </c>
-      <c r="H48" s="10" t="s">
+      <c r="H48" s="11" t="s">
         <v>542</v>
       </c>
-      <c r="I48" s="10" t="s">
+      <c r="I48" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="J48" s="10" t="s">
+      <c r="J48" s="11" t="s">
         <v>544</v>
       </c>
-      <c r="K48" s="10" t="s">
+      <c r="K48" s="11" t="s">
         <v>545</v>
       </c>
-      <c r="L48" s="10" t="s">
+      <c r="L48" s="11" t="s">
         <v>546</v>
       </c>
-      <c r="M48" s="10" t="s">
+      <c r="M48" s="11" t="s">
         <v>547</v>
       </c>
-      <c r="N48" s="10" t="s">
+      <c r="N48" s="11" t="s">
         <v>548</v>
       </c>
-      <c r="O48" s="10" t="s">
+      <c r="O48" s="11" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="2:16">
-      <c r="B49" s="9">
+      <c r="B49" s="10">
         <v>10044</v>
       </c>
-      <c r="C49" s="10" t="s">
+      <c r="C49" s="11" t="s">
         <v>550</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D49" s="12" t="s">
         <v>551</v>
       </c>
-      <c r="E49" s="10" t="s">
+      <c r="E49" s="11" t="s">
         <v>552</v>
       </c>
-      <c r="F49" s="10" t="s">
+      <c r="F49" s="11" t="s">
         <v>553</v>
       </c>
-      <c r="G49" s="10" t="s">
+      <c r="G49" s="11" t="s">
         <v>554</v>
       </c>
-      <c r="H49" s="10" t="s">
+      <c r="H49" s="11" t="s">
         <v>555</v>
       </c>
-      <c r="I49" s="10" t="s">
+      <c r="I49" s="11" t="s">
         <v>556</v>
       </c>
-      <c r="J49" s="10" t="s">
+      <c r="J49" s="11" t="s">
         <v>557</v>
       </c>
-      <c r="K49" s="10" t="s">
+      <c r="K49" s="11" t="s">
         <v>558</v>
       </c>
-      <c r="L49" s="10" t="s">
+      <c r="L49" s="11" t="s">
         <v>559</v>
       </c>
-      <c r="M49" s="10" t="s">
+      <c r="M49" s="11" t="s">
         <v>560</v>
       </c>
-      <c r="N49" s="10" t="s">
+      <c r="N49" s="11" t="s">
         <v>561</v>
       </c>
-      <c r="O49" s="10" t="s">
+      <c r="O49" s="11" t="s">
         <v>562</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="2:16">
-      <c r="B50" s="9">
+      <c r="B50" s="10">
         <v>10045</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="C50" s="11" t="s">
         <v>563</v>
       </c>
-      <c r="D50" s="11" t="s">
+      <c r="D50" s="12" t="s">
         <v>564</v>
       </c>
-      <c r="E50" s="10" t="s">
+      <c r="E50" s="11" t="s">
         <v>565</v>
       </c>
-      <c r="F50" s="10" t="s">
+      <c r="F50" s="11" t="s">
         <v>566</v>
       </c>
-      <c r="G50" s="10" t="s">
+      <c r="G50" s="11" t="s">
         <v>567</v>
       </c>
-      <c r="H50" s="10" t="s">
+      <c r="H50" s="11" t="s">
         <v>568</v>
       </c>
-      <c r="I50" s="10" t="s">
+      <c r="I50" s="11" t="s">
         <v>569</v>
       </c>
-      <c r="J50" s="10" t="s">
+      <c r="J50" s="11" t="s">
         <v>570</v>
       </c>
-      <c r="K50" s="10" t="s">
+      <c r="K50" s="11" t="s">
         <v>571</v>
       </c>
-      <c r="L50" s="10" t="s">
+      <c r="L50" s="11" t="s">
         <v>572</v>
       </c>
-      <c r="M50" s="10" t="s">
+      <c r="M50" s="11" t="s">
         <v>573</v>
       </c>
-      <c r="N50" s="10" t="s">
+      <c r="N50" s="11" t="s">
         <v>574</v>
       </c>
-      <c r="O50" s="10" t="s">
+      <c r="O50" s="11" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="2:16">
-      <c r="B51" s="9">
+      <c r="B51" s="10">
         <v>10046</v>
       </c>
-      <c r="C51" s="10" t="s">
+      <c r="C51" s="11" t="s">
         <v>576</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="D51" s="12" t="s">
         <v>577</v>
       </c>
-      <c r="E51" s="10" t="s">
+      <c r="E51" s="11" t="s">
         <v>578</v>
       </c>
-      <c r="F51" s="10" t="s">
+      <c r="F51" s="11" t="s">
         <v>579</v>
       </c>
-      <c r="G51" s="10" t="s">
+      <c r="G51" s="11" t="s">
         <v>580</v>
       </c>
-      <c r="H51" s="10" t="s">
+      <c r="H51" s="11" t="s">
         <v>581</v>
       </c>
-      <c r="I51" s="10" t="s">
+      <c r="I51" s="11" t="s">
         <v>582</v>
       </c>
-      <c r="J51" s="10" t="s">
+      <c r="J51" s="11" t="s">
         <v>583</v>
       </c>
-      <c r="K51" s="10" t="s">
+      <c r="K51" s="11" t="s">
         <v>584</v>
       </c>
-      <c r="L51" s="10" t="s">
+      <c r="L51" s="11" t="s">
         <v>585</v>
       </c>
-      <c r="M51" s="10" t="s">
+      <c r="M51" s="11" t="s">
         <v>586</v>
       </c>
-      <c r="N51" s="10" t="s">
+      <c r="N51" s="11" t="s">
         <v>587</v>
       </c>
-      <c r="O51" s="10" t="s">
+      <c r="O51" s="11" t="s">
         <v>588</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="2:16">
-      <c r="B52" s="9">
+      <c r="B52" s="10">
         <v>10047</v>
       </c>
-      <c r="C52" s="10" t="s">
+      <c r="C52" s="11" t="s">
         <v>589</v>
       </c>
-      <c r="D52" s="10" t="s">
+      <c r="D52" s="11" t="s">
         <v>590</v>
       </c>
-      <c r="E52" s="10" t="s">
+      <c r="E52" s="11" t="s">
         <v>591</v>
       </c>
-      <c r="F52" s="10" t="s">
+      <c r="F52" s="11" t="s">
         <v>592</v>
       </c>
-      <c r="G52" s="10" t="s">
+      <c r="G52" s="11" t="s">
         <v>593</v>
       </c>
-      <c r="H52" s="10" t="s">
+      <c r="H52" s="11" t="s">
         <v>594</v>
       </c>
-      <c r="I52" s="10" t="s">
+      <c r="I52" s="11" t="s">
         <v>595</v>
       </c>
-      <c r="J52" s="10" t="s">
+      <c r="J52" s="11" t="s">
         <v>596</v>
       </c>
-      <c r="K52" s="10" t="s">
+      <c r="K52" s="11" t="s">
         <v>597</v>
       </c>
-      <c r="L52" s="10" t="s">
+      <c r="L52" s="11" t="s">
         <v>598</v>
       </c>
-      <c r="M52" s="10" t="s">
+      <c r="M52" s="11" t="s">
         <v>599</v>
       </c>
-      <c r="N52" s="10" t="s">
+      <c r="N52" s="11" t="s">
         <v>600</v>
       </c>
-      <c r="O52" s="10" t="s">
+      <c r="O52" s="11" t="s">
         <v>601</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="2:16">
-      <c r="B53" s="9">
+      <c r="B53" s="10">
         <v>10048</v>
       </c>
-      <c r="C53" s="10" t="s">
+      <c r="C53" s="11" t="s">
         <v>602</v>
       </c>
-      <c r="D53" s="10" t="s">
+      <c r="D53" s="11" t="s">
         <v>603</v>
       </c>
-      <c r="E53" s="10" t="s">
+      <c r="E53" s="11" t="s">
         <v>604</v>
       </c>
-      <c r="F53" s="10" t="s">
+      <c r="F53" s="11" t="s">
         <v>605</v>
       </c>
-      <c r="G53" s="10" t="s">
+      <c r="G53" s="11" t="s">
         <v>606</v>
       </c>
-      <c r="H53" s="10" t="s">
+      <c r="H53" s="11" t="s">
         <v>607</v>
       </c>
-      <c r="I53" s="10" t="s">
+      <c r="I53" s="11" t="s">
         <v>608</v>
       </c>
-      <c r="J53" s="10" t="s">
+      <c r="J53" s="11" t="s">
         <v>609</v>
       </c>
-      <c r="K53" s="10" t="s">
+      <c r="K53" s="11" t="s">
         <v>610</v>
       </c>
-      <c r="L53" s="10" t="s">
+      <c r="L53" s="11" t="s">
         <v>611</v>
       </c>
-      <c r="M53" s="10" t="s">
+      <c r="M53" s="11" t="s">
         <v>612</v>
       </c>
-      <c r="N53" s="10" t="s">
+      <c r="N53" s="11" t="s">
         <v>613</v>
       </c>
-      <c r="O53" s="10" t="s">
+      <c r="O53" s="11" t="s">
         <v>614</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="2:16">
-      <c r="B54" s="9">
+      <c r="B54" s="10">
         <v>10049</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="C54" s="11" t="s">
         <v>615</v>
       </c>
-      <c r="D54" s="10" t="s">
+      <c r="D54" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="E54" s="10" t="s">
+      <c r="E54" s="11" t="s">
         <v>617</v>
       </c>
-      <c r="F54" s="10" t="s">
+      <c r="F54" s="11" t="s">
         <v>618</v>
       </c>
-      <c r="G54" s="10" t="s">
+      <c r="G54" s="11" t="s">
         <v>619</v>
       </c>
-      <c r="H54" s="10" t="s">
+      <c r="H54" s="11" t="s">
         <v>620</v>
       </c>
-      <c r="I54" s="10" t="s">
+      <c r="I54" s="11" t="s">
         <v>621</v>
       </c>
-      <c r="J54" s="10" t="s">
+      <c r="J54" s="11" t="s">
         <v>622</v>
       </c>
-      <c r="K54" s="10" t="s">
+      <c r="K54" s="11" t="s">
         <v>623</v>
       </c>
-      <c r="L54" s="10" t="s">
+      <c r="L54" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="M54" s="10" t="s">
+      <c r="M54" s="11" t="s">
         <v>625</v>
       </c>
-      <c r="N54" s="10" t="s">
+      <c r="N54" s="11" t="s">
         <v>626</v>
       </c>
-      <c r="O54" s="10" t="s">
+      <c r="O54" s="11" t="s">
         <v>627</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="2:16">
-      <c r="B55" s="9">
+      <c r="B55" s="10">
         <v>10050</v>
       </c>
-      <c r="C55" s="10" t="s">
+      <c r="C55" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="D55" s="10" t="s">
+      <c r="D55" s="11" t="s">
         <v>629</v>
       </c>
-      <c r="E55" s="10" t="s">
+      <c r="E55" s="11" t="s">
         <v>630</v>
       </c>
-      <c r="F55" s="10" t="s">
+      <c r="F55" s="11" t="s">
         <v>631</v>
       </c>
-      <c r="G55" s="10" t="s">
+      <c r="G55" s="11" t="s">
         <v>632</v>
       </c>
-      <c r="H55" s="10" t="s">
+      <c r="H55" s="11" t="s">
         <v>633</v>
       </c>
-      <c r="I55" s="10" t="s">
+      <c r="I55" s="11" t="s">
         <v>634</v>
       </c>
-      <c r="J55" s="10" t="s">
+      <c r="J55" s="11" t="s">
         <v>635</v>
       </c>
-      <c r="K55" s="10" t="s">
+      <c r="K55" s="11" t="s">
         <v>636</v>
       </c>
-      <c r="L55" s="10" t="s">
+      <c r="L55" s="11" t="s">
         <v>637</v>
       </c>
-      <c r="M55" s="10" t="s">
+      <c r="M55" s="11" t="s">
         <v>638</v>
       </c>
-      <c r="N55" s="10" t="s">
+      <c r="N55" s="11" t="s">
         <v>639</v>
       </c>
-      <c r="O55" s="10" t="s">
+      <c r="O55" s="11" t="s">
         <v>640</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" ht="19" customHeight="1" spans="2:16">
-      <c r="B56" s="9">
+      <c r="B56" s="10">
         <v>10051</v>
       </c>
-      <c r="C56" s="10" t="s">
+      <c r="C56" s="11" t="s">
         <v>641</v>
       </c>
-      <c r="D56" s="10" t="s">
+      <c r="D56" s="11" t="s">
         <v>642</v>
       </c>
-      <c r="E56" s="10" t="s">
+      <c r="E56" s="11" t="s">
         <v>643</v>
       </c>
-      <c r="F56" s="10" t="s">
+      <c r="F56" s="11" t="s">
         <v>644</v>
       </c>
-      <c r="G56" s="10" t="s">
+      <c r="G56" s="11" t="s">
         <v>645</v>
       </c>
-      <c r="H56" s="10" t="s">
+      <c r="H56" s="11" t="s">
         <v>646</v>
       </c>
-      <c r="I56" s="10" t="s">
+      <c r="I56" s="11" t="s">
         <v>647</v>
       </c>
-      <c r="J56" s="10" t="s">
+      <c r="J56" s="11" t="s">
         <v>648</v>
       </c>
-      <c r="K56" s="10" t="s">
+      <c r="K56" s="11" t="s">
         <v>649</v>
       </c>
-      <c r="L56" s="10" t="s">
+      <c r="L56" s="11" t="s">
         <v>650</v>
       </c>
-      <c r="M56" s="10" t="s">
+      <c r="M56" s="11" t="s">
         <v>651</v>
       </c>
-      <c r="N56" s="10" t="s">
+      <c r="N56" s="11" t="s">
         <v>652</v>
       </c>
-      <c r="O56" s="10" t="s">
+      <c r="O56" s="11" t="s">
         <v>653</v>
       </c>
       <c r="P56"/>
     </row>
     <row r="57" customHeight="1" spans="2:16">
-      <c r="B57" s="9">
+      <c r="B57" s="10">
         <v>10052</v>
       </c>
-      <c r="C57" s="10" t="s">
+      <c r="C57" s="11" t="s">
         <v>654</v>
       </c>
-      <c r="D57" s="11" t="s">
+      <c r="D57" s="12" t="s">
         <v>655</v>
       </c>
-      <c r="E57" s="10" t="s">
+      <c r="E57" s="11" t="s">
         <v>656</v>
       </c>
-      <c r="F57" s="10" t="s">
+      <c r="F57" s="11" t="s">
         <v>657</v>
       </c>
-      <c r="G57" s="10" t="s">
+      <c r="G57" s="11" t="s">
         <v>658</v>
       </c>
-      <c r="H57" s="10" t="s">
+      <c r="H57" s="11" t="s">
         <v>659</v>
       </c>
-      <c r="I57" s="10" t="s">
+      <c r="I57" s="11" t="s">
         <v>660</v>
       </c>
-      <c r="J57" s="10" t="s">
+      <c r="J57" s="11" t="s">
         <v>661</v>
       </c>
-      <c r="K57" s="10" t="s">
+      <c r="K57" s="11" t="s">
         <v>662</v>
       </c>
-      <c r="L57" s="10" t="s">
+      <c r="L57" s="11" t="s">
         <v>663</v>
       </c>
-      <c r="M57" s="10" t="s">
+      <c r="M57" s="11" t="s">
         <v>664</v>
       </c>
-      <c r="N57" s="10" t="s">
+      <c r="N57" s="11" t="s">
         <v>665</v>
       </c>
-      <c r="O57" s="10" t="s">
+      <c r="O57" s="11" t="s">
         <v>666</v>
       </c>
       <c r="P57" s="1"/>
     </row>
     <row r="58" customHeight="1" spans="2:16">
-      <c r="B58" s="9">
+      <c r="B58" s="10">
         <v>10053</v>
       </c>
-      <c r="C58" s="10" t="s">
+      <c r="C58" s="11" t="s">
         <v>667</v>
       </c>
-      <c r="D58" s="11" t="s">
+      <c r="D58" s="12" t="s">
         <v>668</v>
       </c>
-      <c r="E58" s="10" t="s">
+      <c r="E58" s="11" t="s">
         <v>669</v>
       </c>
-      <c r="F58" s="10" t="s">
+      <c r="F58" s="11" t="s">
         <v>670</v>
       </c>
-      <c r="G58" s="10" t="s">
+      <c r="G58" s="11" t="s">
         <v>671</v>
       </c>
-      <c r="H58" s="10" t="s">
+      <c r="H58" s="11" t="s">
         <v>672</v>
       </c>
-      <c r="I58" s="10" t="s">
+      <c r="I58" s="11" t="s">
         <v>673</v>
       </c>
-      <c r="J58" s="10" t="s">
+      <c r="J58" s="11" t="s">
         <v>674</v>
       </c>
-      <c r="K58" s="10" t="s">
+      <c r="K58" s="11" t="s">
         <v>675</v>
       </c>
-      <c r="L58" s="10" t="s">
+      <c r="L58" s="11" t="s">
         <v>676</v>
       </c>
-      <c r="M58" s="10" t="s">
+      <c r="M58" s="11" t="s">
         <v>677</v>
       </c>
-      <c r="N58" s="10" t="s">
+      <c r="N58" s="11" t="s">
         <v>678</v>
       </c>
-      <c r="O58" s="10" t="s">
+      <c r="O58" s="11" t="s">
         <v>679</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:16">
-      <c r="B59" s="9">
+      <c r="B59" s="10">
         <v>10054</v>
       </c>
-      <c r="C59" s="10" t="s">
+      <c r="C59" s="11" t="s">
         <v>680</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="D59" s="12" t="s">
         <v>681</v>
       </c>
-      <c r="E59" s="10" t="s">
+      <c r="E59" s="11" t="s">
         <v>682</v>
       </c>
-      <c r="F59" s="10" t="s">
+      <c r="F59" s="11" t="s">
         <v>683</v>
       </c>
-      <c r="G59" s="10" t="s">
+      <c r="G59" s="11" t="s">
         <v>684</v>
       </c>
-      <c r="H59" s="10" t="s">
+      <c r="H59" s="11" t="s">
         <v>685</v>
       </c>
-      <c r="I59" s="10" t="s">
+      <c r="I59" s="11" t="s">
         <v>686</v>
       </c>
-      <c r="J59" s="10" t="s">
+      <c r="J59" s="11" t="s">
         <v>687</v>
       </c>
-      <c r="K59" s="10" t="s">
+      <c r="K59" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="L59" s="10" t="s">
+      <c r="L59" s="11" t="s">
         <v>689</v>
       </c>
-      <c r="M59" s="10" t="s">
+      <c r="M59" s="11" t="s">
         <v>690</v>
       </c>
-      <c r="N59" s="10" t="s">
+      <c r="N59" s="11" t="s">
         <v>691</v>
       </c>
-      <c r="O59" s="10" t="s">
+      <c r="O59" s="11" t="s">
         <v>692</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:16">
-      <c r="B60" s="9">
+      <c r="B60" s="10">
         <v>10055</v>
       </c>
-      <c r="C60" s="11" t="s">
+      <c r="C60" s="12" t="s">
         <v>693</v>
       </c>
-      <c r="D60" s="10" t="s">
+      <c r="D60" s="11" t="s">
         <v>694</v>
       </c>
-      <c r="E60" s="10" t="s">
+      <c r="E60" s="11" t="s">
         <v>695</v>
       </c>
-      <c r="F60" s="10" t="s">
+      <c r="F60" s="11" t="s">
         <v>696</v>
       </c>
-      <c r="G60" s="10" t="s">
+      <c r="G60" s="11" t="s">
         <v>697</v>
       </c>
-      <c r="H60" s="10" t="s">
+      <c r="H60" s="11" t="s">
         <v>698</v>
       </c>
-      <c r="I60" s="10" t="s">
+      <c r="I60" s="11" t="s">
         <v>699</v>
       </c>
-      <c r="J60" s="10" t="s">
+      <c r="J60" s="11" t="s">
         <v>700</v>
       </c>
-      <c r="K60" s="10" t="s">
+      <c r="K60" s="11" t="s">
         <v>701</v>
       </c>
-      <c r="L60" s="10" t="s">
+      <c r="L60" s="11" t="s">
         <v>702</v>
       </c>
-      <c r="M60" s="10" t="s">
+      <c r="M60" s="11" t="s">
         <v>703</v>
       </c>
-      <c r="N60" s="10" t="s">
+      <c r="N60" s="11" t="s">
         <v>704</v>
       </c>
-      <c r="O60" s="10" t="s">
+      <c r="O60" s="11" t="s">
         <v>705</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:16">
-      <c r="B61" s="9">
+      <c r="B61" s="10">
         <v>10056</v>
       </c>
-      <c r="C61" s="10" t="s">
+      <c r="C61" s="11" t="s">
         <v>706</v>
       </c>
-      <c r="D61" s="11" t="s">
+      <c r="D61" s="12" t="s">
         <v>707</v>
       </c>
-      <c r="E61" s="10" t="s">
+      <c r="E61" s="11" t="s">
         <v>708</v>
       </c>
-      <c r="F61" s="10" t="s">
+      <c r="F61" s="11" t="s">
         <v>709</v>
       </c>
-      <c r="G61" s="10" t="s">
+      <c r="G61" s="11" t="s">
         <v>710</v>
       </c>
-      <c r="H61" s="10" t="s">
+      <c r="H61" s="11" t="s">
         <v>711</v>
       </c>
-      <c r="I61" s="10" t="s">
+      <c r="I61" s="11" t="s">
         <v>712</v>
       </c>
-      <c r="J61" s="10" t="s">
+      <c r="J61" s="11" t="s">
         <v>713</v>
       </c>
-      <c r="K61" s="10" t="s">
+      <c r="K61" s="11" t="s">
         <v>714</v>
       </c>
-      <c r="L61" s="10" t="s">
+      <c r="L61" s="11" t="s">
         <v>715</v>
       </c>
-      <c r="M61" s="10" t="s">
+      <c r="M61" s="11" t="s">
         <v>716</v>
       </c>
-      <c r="N61" s="10" t="s">
+      <c r="N61" s="11" t="s">
         <v>717</v>
       </c>
-      <c r="O61" s="10" t="s">
+      <c r="O61" s="11" t="s">
         <v>718</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:16">
-      <c r="B62" s="9">
+      <c r="B62" s="10">
         <v>10057</v>
       </c>
-      <c r="C62" s="10" t="s">
+      <c r="C62" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="D62" s="10" t="s">
+      <c r="D62" s="11" t="s">
         <v>720</v>
       </c>
-      <c r="E62" s="10" t="s">
+      <c r="E62" s="11" t="s">
         <v>721</v>
       </c>
-      <c r="F62" s="10" t="s">
+      <c r="F62" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="G62" s="10" t="s">
+      <c r="G62" s="11" t="s">
         <v>723</v>
       </c>
-      <c r="H62" s="10" t="s">
+      <c r="H62" s="11" t="s">
         <v>724</v>
       </c>
-      <c r="I62" s="10" t="s">
+      <c r="I62" s="11" t="s">
         <v>725</v>
       </c>
-      <c r="J62" s="10" t="s">
+      <c r="J62" s="11" t="s">
         <v>726</v>
       </c>
-      <c r="K62" s="10" t="s">
+      <c r="K62" s="11" t="s">
         <v>727</v>
       </c>
-      <c r="L62" s="10" t="s">
+      <c r="L62" s="11" t="s">
         <v>728</v>
       </c>
-      <c r="M62" s="10" t="s">
+      <c r="M62" s="11" t="s">
         <v>729</v>
       </c>
-      <c r="N62" s="10" t="s">
+      <c r="N62" s="11" t="s">
         <v>730</v>
       </c>
-      <c r="O62" s="10" t="s">
+      <c r="O62" s="11" t="s">
         <v>731</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:16">
-      <c r="B63" s="9">
+      <c r="B63" s="10">
         <v>10058</v>
       </c>
-      <c r="C63" s="10" t="s">
+      <c r="C63" s="11" t="s">
         <v>732</v>
       </c>
-      <c r="D63" s="10" t="s">
+      <c r="D63" s="11" t="s">
         <v>733</v>
       </c>
-      <c r="E63" s="10" t="s">
+      <c r="E63" s="11" t="s">
         <v>734</v>
       </c>
-      <c r="F63" s="10" t="s">
+      <c r="F63" s="11" t="s">
         <v>735</v>
       </c>
-      <c r="G63" s="10" t="s">
+      <c r="G63" s="11" t="s">
         <v>736</v>
       </c>
-      <c r="H63" s="10" t="s">
+      <c r="H63" s="11" t="s">
         <v>737</v>
       </c>
-      <c r="I63" s="10" t="s">
+      <c r="I63" s="11" t="s">
         <v>738</v>
       </c>
-      <c r="J63" s="10" t="s">
+      <c r="J63" s="11" t="s">
         <v>739</v>
       </c>
-      <c r="K63" s="10" t="s">
+      <c r="K63" s="11" t="s">
         <v>740</v>
       </c>
-      <c r="L63" s="10" t="s">
+      <c r="L63" s="11" t="s">
         <v>741</v>
       </c>
-      <c r="M63" s="10" t="s">
+      <c r="M63" s="11" t="s">
         <v>742</v>
       </c>
-      <c r="N63" s="10" t="s">
+      <c r="N63" s="11" t="s">
         <v>743</v>
       </c>
-      <c r="O63" s="10" t="s">
+      <c r="O63" s="11" t="s">
         <v>744</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:16">
-      <c r="B64" s="9">
+      <c r="B64" s="10">
         <v>10059</v>
       </c>
-      <c r="C64" s="10" t="s">
+      <c r="C64" s="11" t="s">
         <v>745</v>
       </c>
-      <c r="D64" s="10" t="s">
+      <c r="D64" s="11" t="s">
         <v>746</v>
       </c>
-      <c r="E64" s="10" t="s">
+      <c r="E64" s="11" t="s">
         <v>747</v>
       </c>
-      <c r="F64" s="10" t="s">
+      <c r="F64" s="11" t="s">
         <v>748</v>
       </c>
-      <c r="G64" s="10" t="s">
+      <c r="G64" s="11" t="s">
         <v>749</v>
       </c>
-      <c r="H64" s="10" t="s">
+      <c r="H64" s="11" t="s">
         <v>750</v>
       </c>
-      <c r="I64" s="10" t="s">
+      <c r="I64" s="11" t="s">
         <v>751</v>
       </c>
-      <c r="J64" s="10" t="s">
+      <c r="J64" s="11" t="s">
         <v>752</v>
       </c>
-      <c r="K64" s="10" t="s">
+      <c r="K64" s="11" t="s">
         <v>753</v>
       </c>
-      <c r="L64" s="10" t="s">
+      <c r="L64" s="11" t="s">
         <v>754</v>
       </c>
-      <c r="M64" s="10" t="s">
+      <c r="M64" s="11" t="s">
         <v>755</v>
       </c>
-      <c r="N64" s="10" t="s">
+      <c r="N64" s="11" t="s">
         <v>756</v>
       </c>
-      <c r="O64" s="10" t="s">
+      <c r="O64" s="11" t="s">
         <v>757</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="2:15">
-      <c r="B65" s="9">
+      <c r="B65" s="10">
         <v>10060</v>
       </c>
-      <c r="C65" s="10" t="s">
+      <c r="C65" s="11" t="s">
         <v>758</v>
       </c>
-      <c r="D65" s="10" t="s">
+      <c r="D65" s="11" t="s">
         <v>759</v>
       </c>
-      <c r="E65" s="10" t="s">
+      <c r="E65" s="11" t="s">
         <v>760</v>
       </c>
-      <c r="F65" s="10" t="s">
+      <c r="F65" s="11" t="s">
         <v>761</v>
       </c>
-      <c r="G65" s="10" t="s">
+      <c r="G65" s="11" t="s">
         <v>762</v>
       </c>
-      <c r="H65" s="10" t="s">
+      <c r="H65" s="11" t="s">
         <v>763</v>
       </c>
-      <c r="I65" s="10" t="s">
+      <c r="I65" s="11" t="s">
         <v>764</v>
       </c>
-      <c r="J65" s="10" t="s">
+      <c r="J65" s="11" t="s">
         <v>765</v>
       </c>
-      <c r="K65" s="10" t="s">
+      <c r="K65" s="11" t="s">
         <v>766</v>
       </c>
-      <c r="L65" s="10" t="s">
+      <c r="L65" s="11" t="s">
         <v>767</v>
       </c>
-      <c r="M65" s="10" t="s">
+      <c r="M65" s="11" t="s">
         <v>768</v>
       </c>
-      <c r="N65" s="10" t="s">
+      <c r="N65" s="11" t="s">
         <v>769</v>
       </c>
-      <c r="O65" s="10" t="s">
+      <c r="O65" s="11" t="s">
         <v>770</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="2:15">
-      <c r="B66" s="9">
+      <c r="B66" s="10">
         <v>10061</v>
       </c>
-      <c r="C66" s="10" t="s">
+      <c r="C66" s="11" t="s">
         <v>771</v>
       </c>
-      <c r="D66" s="10" t="s">
+      <c r="D66" s="11" t="s">
         <v>772</v>
       </c>
-      <c r="E66" s="10" t="s">
+      <c r="E66" s="11" t="s">
         <v>773</v>
       </c>
-      <c r="F66" s="10" t="s">
+      <c r="F66" s="11" t="s">
         <v>774</v>
       </c>
-      <c r="G66" s="10" t="s">
+      <c r="G66" s="11" t="s">
         <v>775</v>
       </c>
-      <c r="H66" s="10" t="s">
+      <c r="H66" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="I66" s="10" t="s">
+      <c r="I66" s="11" t="s">
         <v>777</v>
       </c>
-      <c r="J66" s="10" t="s">
+      <c r="J66" s="11" t="s">
         <v>778</v>
       </c>
-      <c r="K66" s="10" t="s">
+      <c r="K66" s="11" t="s">
         <v>779</v>
       </c>
-      <c r="L66" s="10" t="s">
+      <c r="L66" s="11" t="s">
         <v>780</v>
       </c>
-      <c r="M66" s="10" t="s">
+      <c r="M66" s="11" t="s">
         <v>781</v>
       </c>
-      <c r="N66" s="10" t="s">
+      <c r="N66" s="11" t="s">
         <v>782</v>
       </c>
-      <c r="O66" s="10" t="s">
+      <c r="O66" s="11" t="s">
         <v>783</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="2:15">
-      <c r="B67" s="9">
+      <c r="B67" s="10">
         <v>10062</v>
       </c>
-      <c r="C67" s="10" t="s">
+      <c r="C67" s="11" t="s">
         <v>784</v>
       </c>
-      <c r="D67" s="10" t="s">
+      <c r="D67" s="11" t="s">
         <v>785</v>
       </c>
-      <c r="E67" s="10" t="s">
+      <c r="E67" s="11" t="s">
         <v>786</v>
       </c>
-      <c r="F67" s="10" t="s">
+      <c r="F67" s="11" t="s">
         <v>787</v>
       </c>
-      <c r="G67" s="10" t="s">
+      <c r="G67" s="11" t="s">
         <v>788</v>
       </c>
-      <c r="H67" s="10" t="s">
+      <c r="H67" s="11" t="s">
         <v>789</v>
       </c>
-      <c r="I67" s="10" t="s">
+      <c r="I67" s="11" t="s">
         <v>790</v>
       </c>
-      <c r="J67" s="10" t="s">
+      <c r="J67" s="11" t="s">
         <v>791</v>
       </c>
-      <c r="K67" s="10" t="s">
+      <c r="K67" s="11" t="s">
         <v>792</v>
       </c>
-      <c r="L67" s="10" t="s">
+      <c r="L67" s="11" t="s">
         <v>793</v>
       </c>
-      <c r="M67" s="10" t="s">
+      <c r="M67" s="11" t="s">
         <v>794</v>
       </c>
-      <c r="N67" s="10" t="s">
+      <c r="N67" s="11" t="s">
         <v>795</v>
       </c>
-      <c r="O67" s="10" t="s">
+      <c r="O67" s="11" t="s">
         <v>796</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="2:15">
-      <c r="B68" s="9">
+      <c r="B68" s="10">
         <v>10063</v>
       </c>
-      <c r="C68" s="10" t="s">
+      <c r="C68" s="11" t="s">
         <v>797</v>
       </c>
-      <c r="D68" s="11" t="s">
+      <c r="D68" s="12" t="s">
         <v>798</v>
       </c>
-      <c r="E68" s="10" t="s">
+      <c r="E68" s="11" t="s">
         <v>798</v>
       </c>
-      <c r="F68" s="10" t="s">
+      <c r="F68" s="11" t="s">
         <v>799</v>
       </c>
-      <c r="G68" s="10" t="s">
+      <c r="G68" s="11" t="s">
         <v>798</v>
       </c>
-      <c r="H68" s="10" t="s">
+      <c r="H68" s="11" t="s">
         <v>800</v>
       </c>
-      <c r="I68" s="10" t="s">
+      <c r="I68" s="11" t="s">
         <v>801</v>
       </c>
-      <c r="J68" s="10" t="s">
+      <c r="J68" s="11" t="s">
         <v>802</v>
       </c>
-      <c r="K68" s="10" t="s">
+      <c r="K68" s="11" t="s">
         <v>803</v>
       </c>
-      <c r="L68" s="10" t="s">
+      <c r="L68" s="11" t="s">
         <v>804</v>
       </c>
-      <c r="M68" s="10" t="s">
+      <c r="M68" s="11" t="s">
         <v>805</v>
       </c>
-      <c r="N68" s="10" t="s">
+      <c r="N68" s="11" t="s">
         <v>806</v>
       </c>
-      <c r="O68" s="10" t="s">
+      <c r="O68" s="11" t="s">
         <v>807</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="2:15">
-      <c r="B69" s="9">
+      <c r="B69" s="10">
         <v>10064</v>
       </c>
-      <c r="C69" s="10" t="s">
+      <c r="C69" s="11" t="s">
         <v>808</v>
       </c>
-      <c r="D69" s="10" t="s">
+      <c r="D69" s="11" t="s">
         <v>809</v>
       </c>
-      <c r="E69" s="10" t="s">
+      <c r="E69" s="11" t="s">
         <v>810</v>
       </c>
-      <c r="F69" s="10" t="s">
+      <c r="F69" s="11" t="s">
         <v>811</v>
       </c>
-      <c r="G69" s="10" t="s">
+      <c r="G69" s="11" t="s">
         <v>812</v>
       </c>
-      <c r="H69" s="10" t="s">
+      <c r="H69" s="11" t="s">
         <v>813</v>
       </c>
-      <c r="I69" s="10" t="s">
+      <c r="I69" s="11" t="s">
         <v>814</v>
       </c>
-      <c r="J69" s="10" t="s">
+      <c r="J69" s="11" t="s">
         <v>815</v>
       </c>
-      <c r="K69" s="10" t="s">
+      <c r="K69" s="11" t="s">
         <v>816</v>
       </c>
-      <c r="L69" s="10" t="s">
+      <c r="L69" s="11" t="s">
         <v>817</v>
       </c>
-      <c r="M69" s="10" t="s">
+      <c r="M69" s="11" t="s">
         <v>818</v>
       </c>
-      <c r="N69" s="10" t="s">
+      <c r="N69" s="11" t="s">
         <v>819</v>
       </c>
-      <c r="O69" s="10" t="s">
+      <c r="O69" s="11" t="s">
         <v>820</v>
       </c>
     </row>
     <row r="70" ht="19" customHeight="1" spans="2:15">
-      <c r="B70" s="9">
+      <c r="B70" s="10">
         <v>10065</v>
       </c>
-      <c r="C70" s="10" t="s">
+      <c r="C70" s="11" t="s">
         <v>821</v>
       </c>
-      <c r="D70" s="10" t="s">
+      <c r="D70" s="11" t="s">
         <v>822</v>
       </c>
-      <c r="E70" s="10" t="s">
+      <c r="E70" s="11" t="s">
         <v>823</v>
       </c>
-      <c r="F70" s="10" t="s">
+      <c r="F70" s="11" t="s">
         <v>824</v>
       </c>
-      <c r="G70" s="10" t="s">
+      <c r="G70" s="11" t="s">
         <v>825</v>
       </c>
-      <c r="H70" s="10" t="s">
+      <c r="H70" s="11" t="s">
         <v>826</v>
       </c>
-      <c r="I70" s="10" t="s">
+      <c r="I70" s="11" t="s">
         <v>825</v>
       </c>
-      <c r="J70" s="10" t="s">
+      <c r="J70" s="11" t="s">
         <v>827</v>
       </c>
-      <c r="K70" s="10" t="s">
+      <c r="K70" s="11" t="s">
         <v>828</v>
       </c>
-      <c r="L70" s="10" t="s">
+      <c r="L70" s="11" t="s">
         <v>829</v>
       </c>
-      <c r="M70" s="10" t="s">
+      <c r="M70" s="11" t="s">
         <v>830</v>
       </c>
-      <c r="N70" s="10" t="s">
+      <c r="N70" s="11" t="s">
         <v>831</v>
       </c>
-      <c r="O70" s="10" t="s">
+      <c r="O70" s="11" t="s">
         <v>832</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="2:15">
-      <c r="B71" s="9">
+      <c r="B71" s="10">
         <v>10066</v>
       </c>
-      <c r="C71" s="10" t="s">
+      <c r="C71" s="11" t="s">
         <v>833</v>
       </c>
-      <c r="D71" s="11" t="s">
+      <c r="D71" s="12" t="s">
         <v>834</v>
       </c>
-      <c r="E71" s="10" t="s">
+      <c r="E71" s="11" t="s">
         <v>835</v>
       </c>
-      <c r="F71" s="10" t="s">
+      <c r="F71" s="11" t="s">
         <v>836</v>
       </c>
-      <c r="G71" s="10" t="s">
+      <c r="G71" s="11" t="s">
         <v>837</v>
       </c>
-      <c r="H71" s="10" t="s">
+      <c r="H71" s="11" t="s">
         <v>838</v>
       </c>
-      <c r="I71" s="10" t="s">
+      <c r="I71" s="11" t="s">
         <v>837</v>
       </c>
-      <c r="J71" s="10" t="s">
+      <c r="J71" s="11" t="s">
         <v>839</v>
       </c>
-      <c r="K71" s="10" t="s">
+      <c r="K71" s="11" t="s">
         <v>840</v>
       </c>
-      <c r="L71" s="10" t="s">
+      <c r="L71" s="11" t="s">
         <v>841</v>
       </c>
-      <c r="M71" s="10" t="s">
+      <c r="M71" s="11" t="s">
         <v>842</v>
       </c>
-      <c r="N71" s="10" t="s">
+      <c r="N71" s="11" t="s">
         <v>843</v>
       </c>
-      <c r="O71" s="10" t="s">
+      <c r="O71" s="11" t="s">
         <v>844</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="2:15">
-      <c r="B72" s="9">
+      <c r="B72" s="10">
         <v>10067</v>
       </c>
-      <c r="C72" s="10" t="s">
+      <c r="C72" s="11" t="s">
         <v>845</v>
       </c>
-      <c r="D72" s="11" t="s">
+      <c r="D72" s="12" t="s">
         <v>846</v>
       </c>
-      <c r="E72" s="10" t="s">
+      <c r="E72" s="11" t="s">
         <v>847</v>
       </c>
-      <c r="F72" s="10" t="s">
+      <c r="F72" s="11" t="s">
         <v>848</v>
       </c>
-      <c r="G72" s="10" t="s">
+      <c r="G72" s="11" t="s">
         <v>849</v>
       </c>
-      <c r="H72" s="10" t="s">
+      <c r="H72" s="11" t="s">
         <v>850</v>
       </c>
-      <c r="I72" s="10" t="s">
+      <c r="I72" s="11" t="s">
         <v>849</v>
       </c>
-      <c r="J72" s="10" t="s">
+      <c r="J72" s="11" t="s">
         <v>851</v>
       </c>
-      <c r="K72" s="10" t="s">
+      <c r="K72" s="11" t="s">
         <v>849</v>
       </c>
-      <c r="L72" s="10" t="s">
+      <c r="L72" s="11" t="s">
         <v>852</v>
       </c>
-      <c r="M72" s="10" t="s">
+      <c r="M72" s="11" t="s">
         <v>853</v>
       </c>
-      <c r="N72" s="10" t="s">
+      <c r="N72" s="11" t="s">
         <v>854</v>
       </c>
-      <c r="O72" s="10" t="s">
+      <c r="O72" s="11" t="s">
         <v>855</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="2:15">
-      <c r="B73" s="9">
+      <c r="B73" s="10">
         <v>10068</v>
       </c>
-      <c r="C73" s="10" t="s">
+      <c r="C73" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="D73" s="11" t="s">
+      <c r="D73" s="12" t="s">
         <v>857</v>
       </c>
-      <c r="E73" s="10" t="s">
+      <c r="E73" s="11" t="s">
         <v>858</v>
       </c>
-      <c r="F73" s="10" t="s">
+      <c r="F73" s="11" t="s">
         <v>859</v>
       </c>
-      <c r="G73" s="10" t="s">
+      <c r="G73" s="11" t="s">
         <v>860</v>
       </c>
-      <c r="H73" s="10" t="s">
+      <c r="H73" s="11" t="s">
         <v>861</v>
       </c>
-      <c r="I73" s="10" t="s">
+      <c r="I73" s="11" t="s">
         <v>862</v>
       </c>
-      <c r="J73" s="10" t="s">
+      <c r="J73" s="11" t="s">
         <v>863</v>
       </c>
-      <c r="K73" s="10" t="s">
+      <c r="K73" s="11" t="s">
         <v>864</v>
       </c>
-      <c r="L73" s="10" t="s">
+      <c r="L73" s="11" t="s">
         <v>865</v>
       </c>
-      <c r="M73" s="10" t="s">
+      <c r="M73" s="11" t="s">
         <v>866</v>
       </c>
-      <c r="N73" s="10" t="s">
+      <c r="N73" s="11" t="s">
         <v>867</v>
       </c>
-      <c r="O73" s="10" t="s">
+      <c r="O73" s="11" t="s">
         <v>868</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="2:15">
-      <c r="B74" s="9">
+      <c r="B74" s="10">
         <v>10069</v>
       </c>
-      <c r="C74" s="10" t="s">
+      <c r="C74" s="11" t="s">
         <v>869</v>
       </c>
-      <c r="D74" s="11" t="s">
+      <c r="D74" s="12" t="s">
         <v>870</v>
       </c>
-      <c r="E74" s="10" t="s">
+      <c r="E74" s="11" t="s">
         <v>871</v>
       </c>
-      <c r="F74" s="10" t="s">
+      <c r="F74" s="11" t="s">
         <v>872</v>
       </c>
-      <c r="G74" s="10" t="s">
+      <c r="G74" s="11" t="s">
         <v>873</v>
       </c>
-      <c r="H74" s="10" t="s">
+      <c r="H74" s="11" t="s">
         <v>874</v>
       </c>
-      <c r="I74" s="10" t="s">
+      <c r="I74" s="11" t="s">
         <v>875</v>
       </c>
-      <c r="J74" s="10" t="s">
+      <c r="J74" s="11" t="s">
         <v>876</v>
       </c>
-      <c r="K74" s="10" t="s">
+      <c r="K74" s="11" t="s">
         <v>877</v>
       </c>
-      <c r="L74" s="10" t="s">
+      <c r="L74" s="11" t="s">
         <v>878</v>
       </c>
-      <c r="M74" s="10" t="s">
+      <c r="M74" s="11" t="s">
         <v>879</v>
       </c>
-      <c r="N74" s="10" t="s">
+      <c r="N74" s="11" t="s">
         <v>880</v>
       </c>
-      <c r="O74" s="10" t="s">
+      <c r="O74" s="11" t="s">
         <v>881</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="2:15">
-      <c r="B75" s="9">
+      <c r="B75" s="10">
         <v>10070</v>
       </c>
-      <c r="C75" s="10" t="s">
+      <c r="C75" s="11" t="s">
         <v>882</v>
       </c>
-      <c r="D75" s="10" t="s">
+      <c r="D75" s="11" t="s">
         <v>883</v>
       </c>
-      <c r="E75" s="10" t="s">
+      <c r="E75" s="11" t="s">
         <v>884</v>
       </c>
-      <c r="F75" s="10" t="s">
+      <c r="F75" s="11" t="s">
         <v>885</v>
       </c>
-      <c r="G75" s="10" t="s">
+      <c r="G75" s="11" t="s">
         <v>886</v>
       </c>
-      <c r="H75" s="10" t="s">
+      <c r="H75" s="11" t="s">
         <v>887</v>
       </c>
-      <c r="I75" s="10" t="s">
+      <c r="I75" s="11" t="s">
         <v>888</v>
       </c>
-      <c r="J75" s="10" t="s">
+      <c r="J75" s="11" t="s">
         <v>889</v>
       </c>
-      <c r="K75" s="10" t="s">
+      <c r="K75" s="11" t="s">
         <v>890</v>
       </c>
-      <c r="L75" s="10" t="s">
+      <c r="L75" s="11" t="s">
         <v>891</v>
       </c>
-      <c r="M75" s="10" t="s">
+      <c r="M75" s="11" t="s">
         <v>892</v>
       </c>
-      <c r="N75" s="10" t="s">
+      <c r="N75" s="11" t="s">
         <v>893</v>
       </c>
-      <c r="O75" s="10" t="s">
+      <c r="O75" s="11" t="s">
         <v>894</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="2:15">
-      <c r="B76" s="9">
+      <c r="B76" s="10">
         <v>10071</v>
       </c>
-      <c r="C76" s="10" t="s">
+      <c r="C76" s="11" t="s">
         <v>895</v>
       </c>
-      <c r="D76" s="10" t="s">
+      <c r="D76" s="11" t="s">
         <v>896</v>
       </c>
-      <c r="E76" s="10" t="s">
+      <c r="E76" s="11" t="s">
         <v>897</v>
       </c>
-      <c r="F76" s="10" t="s">
+      <c r="F76" s="11" t="s">
         <v>898</v>
       </c>
-      <c r="G76" s="10" t="s">
+      <c r="G76" s="11" t="s">
         <v>899</v>
       </c>
-      <c r="H76" s="10" t="s">
+      <c r="H76" s="11" t="s">
         <v>900</v>
       </c>
-      <c r="I76" s="10" t="s">
+      <c r="I76" s="11" t="s">
         <v>901</v>
       </c>
-      <c r="J76" s="10" t="s">
+      <c r="J76" s="11" t="s">
         <v>902</v>
       </c>
-      <c r="K76" s="10" t="s">
+      <c r="K76" s="11" t="s">
         <v>903</v>
       </c>
-      <c r="L76" s="10" t="s">
+      <c r="L76" s="11" t="s">
         <v>904</v>
       </c>
-      <c r="M76" s="10" t="s">
+      <c r="M76" s="11" t="s">
         <v>905</v>
       </c>
-      <c r="N76" s="10" t="s">
+      <c r="N76" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="O76" s="10" t="s">
+      <c r="O76" s="11" t="s">
         <v>907</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="2:15">
-      <c r="B77" s="9">
+      <c r="B77" s="10">
         <v>10072</v>
       </c>
-      <c r="C77" s="10" t="s">
+      <c r="C77" s="11" t="s">
         <v>908</v>
       </c>
-      <c r="D77" s="10" t="s">
+      <c r="D77" s="11" t="s">
         <v>909</v>
       </c>
-      <c r="E77" s="10" t="s">
+      <c r="E77" s="11" t="s">
         <v>910</v>
       </c>
-      <c r="F77" s="10" t="s">
+      <c r="F77" s="11" t="s">
         <v>911</v>
       </c>
-      <c r="G77" s="10" t="s">
+      <c r="G77" s="11" t="s">
         <v>912</v>
       </c>
-      <c r="H77" s="10" t="s">
+      <c r="H77" s="11" t="s">
         <v>913</v>
       </c>
-      <c r="I77" s="10" t="s">
+      <c r="I77" s="11" t="s">
         <v>914</v>
       </c>
-      <c r="J77" s="10" t="s">
+      <c r="J77" s="11" t="s">
         <v>915</v>
       </c>
-      <c r="K77" s="10" t="s">
+      <c r="K77" s="11" t="s">
         <v>916</v>
       </c>
-      <c r="L77" s="10" t="s">
+      <c r="L77" s="11" t="s">
         <v>917</v>
       </c>
-      <c r="M77" s="10" t="s">
+      <c r="M77" s="11" t="s">
         <v>918</v>
       </c>
-      <c r="N77" s="10" t="s">
+      <c r="N77" s="11" t="s">
         <v>919</v>
       </c>
-      <c r="O77" s="10" t="s">
+      <c r="O77" s="11" t="s">
         <v>920</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="2:15">
-      <c r="B78" s="9">
+      <c r="B78" s="10">
         <v>10073</v>
       </c>
-      <c r="C78" s="10" t="s">
+      <c r="C78" s="11" t="s">
         <v>921</v>
       </c>
-      <c r="D78" s="11" t="s">
+      <c r="D78" s="12" t="s">
         <v>922</v>
       </c>
-      <c r="E78" s="10" t="s">
+      <c r="E78" s="11" t="s">
         <v>923</v>
       </c>
-      <c r="F78" s="10" t="s">
+      <c r="F78" s="11" t="s">
         <v>924</v>
       </c>
-      <c r="G78" s="10" t="s">
+      <c r="G78" s="11" t="s">
         <v>925</v>
       </c>
-      <c r="H78" s="10" t="s">
+      <c r="H78" s="11" t="s">
         <v>926</v>
       </c>
-      <c r="I78" s="10" t="s">
+      <c r="I78" s="11" t="s">
         <v>927</v>
       </c>
-      <c r="J78" s="10" t="s">
+      <c r="J78" s="11" t="s">
         <v>928</v>
       </c>
-      <c r="K78" s="10" t="s">
+      <c r="K78" s="11" t="s">
         <v>929</v>
       </c>
-      <c r="L78" s="10" t="s">
+      <c r="L78" s="11" t="s">
         <v>930</v>
       </c>
-      <c r="M78" s="10" t="s">
+      <c r="M78" s="11" t="s">
         <v>931</v>
       </c>
-      <c r="N78" s="10" t="s">
+      <c r="N78" s="11" t="s">
         <v>932</v>
       </c>
-      <c r="O78" s="10" t="s">
+      <c r="O78" s="11" t="s">
         <v>933</v>
       </c>
     </row>
     <row r="79" ht="19" customHeight="1" spans="2:15">
-      <c r="B79" s="9">
+      <c r="B79" s="10">
         <v>10074</v>
       </c>
-      <c r="C79" s="11" t="s">
+      <c r="C79" s="12" t="s">
         <v>934</v>
       </c>
-      <c r="D79" s="11" t="s">
+      <c r="D79" s="12" t="s">
         <v>935</v>
       </c>
-      <c r="E79" s="10" t="s">
+      <c r="E79" s="11" t="s">
         <v>936</v>
       </c>
-      <c r="F79" s="10" t="s">
+      <c r="F79" s="11" t="s">
         <v>937</v>
       </c>
-      <c r="G79" s="10" t="s">
+      <c r="G79" s="11" t="s">
         <v>938</v>
       </c>
-      <c r="H79" s="10" t="s">
+      <c r="H79" s="11" t="s">
         <v>939</v>
       </c>
-      <c r="I79" s="10" t="s">
+      <c r="I79" s="11" t="s">
         <v>940</v>
       </c>
-      <c r="J79" s="10" t="s">
+      <c r="J79" s="11" t="s">
         <v>941</v>
       </c>
-      <c r="K79" s="10" t="s">
+      <c r="K79" s="11" t="s">
         <v>942</v>
       </c>
-      <c r="L79" s="10" t="s">
+      <c r="L79" s="11" t="s">
         <v>943</v>
       </c>
-      <c r="M79" s="10" t="s">
+      <c r="M79" s="11" t="s">
         <v>944</v>
       </c>
-      <c r="N79" s="10" t="s">
+      <c r="N79" s="11" t="s">
         <v>945</v>
       </c>
-      <c r="O79" s="10" t="s">
+      <c r="O79" s="11" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="2:15">
-      <c r="B80" s="9">
+      <c r="B80" s="10">
         <v>10075</v>
       </c>
-      <c r="C80" s="10" t="s">
+      <c r="C80" s="11" t="s">
         <v>947</v>
       </c>
-      <c r="D80" s="11" t="s">
+      <c r="D80" s="12" t="s">
         <v>948</v>
       </c>
-      <c r="E80" s="10" t="s">
+      <c r="E80" s="11" t="s">
         <v>949</v>
       </c>
-      <c r="F80" s="10" t="s">
+      <c r="F80" s="11" t="s">
         <v>950</v>
       </c>
-      <c r="G80" s="10" t="s">
+      <c r="G80" s="11" t="s">
         <v>951</v>
       </c>
-      <c r="H80" s="10" t="s">
+      <c r="H80" s="11" t="s">
         <v>952</v>
       </c>
-      <c r="I80" s="10" t="s">
+      <c r="I80" s="11" t="s">
         <v>953</v>
       </c>
-      <c r="J80" s="10" t="s">
+      <c r="J80" s="11" t="s">
         <v>954</v>
       </c>
-      <c r="K80" s="10" t="s">
+      <c r="K80" s="11" t="s">
         <v>955</v>
       </c>
-      <c r="L80" s="10" t="s">
+      <c r="L80" s="11" t="s">
         <v>956</v>
       </c>
-      <c r="M80" s="10" t="s">
+      <c r="M80" s="11" t="s">
         <v>957</v>
       </c>
-      <c r="N80" s="10" t="s">
+      <c r="N80" s="11" t="s">
         <v>958</v>
       </c>
-      <c r="O80" s="10" t="s">
+      <c r="O80" s="11" t="s">
         <v>959</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="2:15">
-      <c r="B81" s="9">
+      <c r="B81" s="10">
         <v>10076</v>
       </c>
-      <c r="C81" s="10" t="s">
+      <c r="C81" s="11" t="s">
         <v>960</v>
       </c>
-      <c r="D81" s="11" t="s">
+      <c r="D81" s="12" t="s">
         <v>961</v>
       </c>
-      <c r="E81" s="10" t="s">
+      <c r="E81" s="11" t="s">
         <v>962</v>
       </c>
-      <c r="F81" s="10" t="s">
+      <c r="F81" s="11" t="s">
         <v>963</v>
       </c>
-      <c r="G81" s="10" t="s">
+      <c r="G81" s="11" t="s">
         <v>964</v>
       </c>
-      <c r="H81" s="10" t="s">
+      <c r="H81" s="11" t="s">
         <v>965</v>
       </c>
-      <c r="I81" s="10" t="s">
+      <c r="I81" s="11" t="s">
         <v>966</v>
       </c>
-      <c r="J81" s="10" t="s">
+      <c r="J81" s="11" t="s">
         <v>967</v>
       </c>
-      <c r="K81" s="10" t="s">
+      <c r="K81" s="11" t="s">
         <v>968</v>
       </c>
-      <c r="L81" s="10" t="s">
+      <c r="L81" s="11" t="s">
         <v>969</v>
       </c>
-      <c r="M81" s="10" t="s">
+      <c r="M81" s="11" t="s">
         <v>970</v>
       </c>
-      <c r="N81" s="10" t="s">
+      <c r="N81" s="11" t="s">
         <v>971</v>
       </c>
-      <c r="O81" s="10" t="s">
+      <c r="O81" s="11" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="2:15">
-      <c r="B82" s="9">
+      <c r="B82" s="10">
         <v>10077</v>
       </c>
-      <c r="C82" s="10" t="s">
+      <c r="C82" s="11" t="s">
         <v>973</v>
       </c>
-      <c r="D82" s="11" t="s">
+      <c r="D82" s="12" t="s">
         <v>974</v>
       </c>
-      <c r="E82" s="10" t="s">
+      <c r="E82" s="11" t="s">
         <v>975</v>
       </c>
-      <c r="F82" s="10" t="s">
+      <c r="F82" s="11" t="s">
         <v>976</v>
       </c>
-      <c r="G82" s="10" t="s">
+      <c r="G82" s="11" t="s">
         <v>977</v>
       </c>
-      <c r="H82" s="10" t="s">
+      <c r="H82" s="11" t="s">
         <v>978</v>
       </c>
-      <c r="I82" s="10" t="s">
+      <c r="I82" s="11" t="s">
         <v>979</v>
       </c>
-      <c r="J82" s="10" t="s">
+      <c r="J82" s="11" t="s">
         <v>980</v>
       </c>
-      <c r="K82" s="10" t="s">
+      <c r="K82" s="11" t="s">
         <v>981</v>
       </c>
-      <c r="L82" s="10" t="s">
+      <c r="L82" s="11" t="s">
         <v>982</v>
       </c>
-      <c r="M82" s="10" t="s">
+      <c r="M82" s="11" t="s">
         <v>983</v>
       </c>
-      <c r="N82" s="10" t="s">
+      <c r="N82" s="11" t="s">
         <v>984</v>
       </c>
-      <c r="O82" s="10" t="s">
+      <c r="O82" s="11" t="s">
         <v>985</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="2:15">
-      <c r="B83" s="9">
+      <c r="B83" s="10">
         <v>10078</v>
       </c>
-      <c r="C83" s="10" t="s">
+      <c r="C83" s="11" t="s">
         <v>986</v>
       </c>
-      <c r="D83" s="11" t="s">
+      <c r="D83" s="12" t="s">
         <v>987</v>
       </c>
-      <c r="E83" s="10" t="s">
+      <c r="E83" s="11" t="s">
         <v>988</v>
       </c>
-      <c r="F83" s="10" t="s">
+      <c r="F83" s="11" t="s">
         <v>989</v>
       </c>
-      <c r="G83" s="10" t="s">
+      <c r="G83" s="11" t="s">
         <v>990</v>
       </c>
-      <c r="H83" s="10" t="s">
+      <c r="H83" s="11" t="s">
         <v>991</v>
       </c>
-      <c r="I83" s="10" t="s">
+      <c r="I83" s="11" t="s">
         <v>992</v>
       </c>
-      <c r="J83" s="10" t="s">
+      <c r="J83" s="11" t="s">
         <v>993</v>
       </c>
-      <c r="K83" s="10" t="s">
+      <c r="K83" s="11" t="s">
         <v>994</v>
       </c>
-      <c r="L83" s="10" t="s">
+      <c r="L83" s="11" t="s">
         <v>995</v>
       </c>
-      <c r="M83" s="10" t="s">
+      <c r="M83" s="11" t="s">
         <v>996</v>
       </c>
-      <c r="N83" s="10" t="s">
+      <c r="N83" s="11" t="s">
         <v>997</v>
       </c>
-      <c r="O83" s="10" t="s">
+      <c r="O83" s="11" t="s">
         <v>998</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="2:15">
-      <c r="B84" s="9">
+      <c r="B84" s="10">
         <v>10079</v>
       </c>
-      <c r="C84" s="10" t="s">
+      <c r="C84" s="11" t="s">
         <v>999</v>
       </c>
-      <c r="D84" s="11" t="s">
+      <c r="D84" s="12" t="s">
         <v>1000</v>
       </c>
-      <c r="E84" s="10" t="s">
+      <c r="E84" s="11" t="s">
         <v>1001</v>
       </c>
-      <c r="F84" s="10" t="s">
+      <c r="F84" s="11" t="s">
         <v>1002</v>
       </c>
-      <c r="G84" s="10" t="s">
+      <c r="G84" s="11" t="s">
         <v>1003</v>
       </c>
-      <c r="H84" s="10" t="s">
+      <c r="H84" s="11" t="s">
         <v>1004</v>
       </c>
-      <c r="I84" s="10" t="s">
+      <c r="I84" s="11" t="s">
         <v>1005</v>
       </c>
-      <c r="J84" s="10" t="s">
+      <c r="J84" s="11" t="s">
         <v>1006</v>
       </c>
-      <c r="K84" s="10" t="s">
+      <c r="K84" s="11" t="s">
         <v>1007</v>
       </c>
-      <c r="L84" s="10" t="s">
+      <c r="L84" s="11" t="s">
         <v>1008</v>
       </c>
-      <c r="M84" s="10" t="s">
+      <c r="M84" s="11" t="s">
         <v>1009</v>
       </c>
-      <c r="N84" s="10" t="s">
+      <c r="N84" s="11" t="s">
         <v>1010</v>
       </c>
-      <c r="O84" s="10" t="s">
+      <c r="O84" s="11" t="s">
         <v>1011</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="2:15">
-      <c r="B85" s="9">
+      <c r="B85" s="10">
         <v>10080</v>
       </c>
-      <c r="C85" s="10" t="s">
+      <c r="C85" s="11" t="s">
         <v>1012</v>
       </c>
-      <c r="D85" s="11" t="s">
+      <c r="D85" s="12" t="s">
         <v>1013</v>
       </c>
-      <c r="E85" s="10" t="s">
+      <c r="E85" s="11" t="s">
         <v>1014</v>
       </c>
-      <c r="F85" s="10" t="s">
+      <c r="F85" s="11" t="s">
         <v>1015</v>
       </c>
-      <c r="G85" s="10" t="s">
+      <c r="G85" s="11" t="s">
         <v>1016</v>
       </c>
-      <c r="H85" s="10" t="s">
+      <c r="H85" s="11" t="s">
         <v>1017</v>
       </c>
-      <c r="I85" s="10" t="s">
+      <c r="I85" s="11" t="s">
         <v>1018</v>
       </c>
-      <c r="J85" s="10" t="s">
+      <c r="J85" s="11" t="s">
         <v>1019</v>
       </c>
-      <c r="K85" s="10" t="s">
+      <c r="K85" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L85" s="10" t="s">
+      <c r="L85" s="11" t="s">
         <v>1021</v>
       </c>
-      <c r="M85" s="10" t="s">
+      <c r="M85" s="11" t="s">
         <v>1022</v>
       </c>
-      <c r="N85" s="10" t="s">
+      <c r="N85" s="11" t="s">
         <v>1023</v>
       </c>
-      <c r="O85" s="10" t="s">
+      <c r="O85" s="11" t="s">
         <v>1024</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="2:15">
-      <c r="B86" s="9">
+      <c r="B86" s="10">
         <v>10081</v>
       </c>
-      <c r="C86" s="10" t="s">
+      <c r="C86" s="11" t="s">
         <v>1025</v>
       </c>
-      <c r="D86" s="11" t="s">
+      <c r="D86" s="12" t="s">
         <v>1026</v>
       </c>
-      <c r="E86" s="10" t="s">
+      <c r="E86" s="11" t="s">
         <v>1027</v>
       </c>
-      <c r="F86" s="10" t="s">
+      <c r="F86" s="11" t="s">
         <v>1028</v>
       </c>
-      <c r="G86" s="10" t="s">
+      <c r="G86" s="11" t="s">
         <v>1029</v>
       </c>
-      <c r="H86" s="10" t="s">
+      <c r="H86" s="11" t="s">
         <v>1030</v>
       </c>
-      <c r="I86" s="10" t="s">
+      <c r="I86" s="11" t="s">
         <v>1031</v>
       </c>
-      <c r="J86" s="10" t="s">
+      <c r="J86" s="11" t="s">
         <v>1032</v>
       </c>
-      <c r="K86" s="10" t="s">
+      <c r="K86" s="11" t="s">
         <v>1033</v>
       </c>
-      <c r="L86" s="10" t="s">
+      <c r="L86" s="11" t="s">
         <v>1034</v>
       </c>
-      <c r="M86" s="10" t="s">
+      <c r="M86" s="11" t="s">
         <v>1035</v>
       </c>
-      <c r="N86" s="10" t="s">
+      <c r="N86" s="11" t="s">
         <v>1036</v>
       </c>
-      <c r="O86" s="10" t="s">
+      <c r="O86" s="11" t="s">
         <v>1037</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="2:15">
-      <c r="B87" s="9">
+      <c r="B87" s="10">
         <v>10082</v>
       </c>
-      <c r="C87" s="10" t="s">
+      <c r="C87" s="11" t="s">
         <v>1038</v>
       </c>
-      <c r="D87" s="11" t="s">
+      <c r="D87" s="12" t="s">
         <v>1039</v>
       </c>
-      <c r="E87" s="10" t="s">
+      <c r="E87" s="11" t="s">
         <v>1040</v>
       </c>
-      <c r="F87" s="10" t="s">
+      <c r="F87" s="11" t="s">
         <v>1041</v>
       </c>
-      <c r="G87" s="10" t="s">
+      <c r="G87" s="11" t="s">
         <v>1042</v>
       </c>
-      <c r="H87" s="10" t="s">
+      <c r="H87" s="11" t="s">
         <v>1043</v>
       </c>
-      <c r="I87" s="10" t="s">
+      <c r="I87" s="11" t="s">
         <v>1044</v>
       </c>
-      <c r="J87" s="10" t="s">
+      <c r="J87" s="11" t="s">
         <v>1045</v>
       </c>
-      <c r="K87" s="10" t="s">
+      <c r="K87" s="11" t="s">
         <v>1046</v>
       </c>
-      <c r="L87" s="10" t="s">
+      <c r="L87" s="11" t="s">
         <v>1047</v>
       </c>
-      <c r="M87" s="10" t="s">
+      <c r="M87" s="11" t="s">
         <v>1048</v>
       </c>
-      <c r="N87" s="10" t="s">
+      <c r="N87" s="11" t="s">
         <v>1049</v>
       </c>
-      <c r="O87" s="10" t="s">
+      <c r="O87" s="11" t="s">
         <v>1050</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="2:15">
-      <c r="B88" s="9">
+      <c r="B88" s="10">
         <v>10083</v>
       </c>
-      <c r="C88" s="10" t="s">
+      <c r="C88" s="11" t="s">
         <v>1051</v>
       </c>
-      <c r="D88" s="11" t="s">
+      <c r="D88" s="12" t="s">
         <v>1052</v>
       </c>
-      <c r="E88" s="10" t="s">
+      <c r="E88" s="11" t="s">
         <v>1053</v>
       </c>
-      <c r="F88" s="10" t="s">
+      <c r="F88" s="11" t="s">
         <v>1054</v>
       </c>
-      <c r="G88" s="10" t="s">
+      <c r="G88" s="11" t="s">
         <v>1055</v>
       </c>
-      <c r="H88" s="10" t="s">
+      <c r="H88" s="11" t="s">
         <v>1056</v>
       </c>
-      <c r="I88" s="10" t="s">
+      <c r="I88" s="11" t="s">
         <v>1057</v>
       </c>
-      <c r="J88" s="10" t="s">
+      <c r="J88" s="11" t="s">
         <v>1058</v>
       </c>
-      <c r="K88" s="10" t="s">
+      <c r="K88" s="11" t="s">
         <v>1059</v>
       </c>
-      <c r="L88" s="10" t="s">
+      <c r="L88" s="11" t="s">
         <v>1060</v>
       </c>
-      <c r="M88" s="10" t="s">
+      <c r="M88" s="11" t="s">
         <v>1061</v>
       </c>
-      <c r="N88" s="10" t="s">
+      <c r="N88" s="11" t="s">
         <v>1062</v>
       </c>
-      <c r="O88" s="10" t="s">
+      <c r="O88" s="11" t="s">
         <v>1063</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="2:15">
-      <c r="B89" s="9">
+      <c r="B89" s="10">
         <v>10084</v>
       </c>
-      <c r="C89" s="10" t="s">
+      <c r="C89" s="11" t="s">
         <v>1064</v>
       </c>
-      <c r="D89" s="11" t="s">
+      <c r="D89" s="12" t="s">
         <v>1065</v>
       </c>
-      <c r="E89" s="10" t="s">
+      <c r="E89" s="11" t="s">
         <v>1066</v>
       </c>
-      <c r="F89" s="10" t="s">
+      <c r="F89" s="11" t="s">
         <v>1067</v>
       </c>
-      <c r="G89" s="10" t="s">
+      <c r="G89" s="11" t="s">
         <v>1068</v>
       </c>
-      <c r="H89" s="10" t="s">
+      <c r="H89" s="11" t="s">
         <v>1069</v>
       </c>
-      <c r="I89" s="10" t="s">
+      <c r="I89" s="11" t="s">
         <v>1068</v>
       </c>
-      <c r="J89" s="10" t="s">
+      <c r="J89" s="11" t="s">
         <v>1070</v>
       </c>
-      <c r="K89" s="10" t="s">
+      <c r="K89" s="11" t="s">
         <v>1071</v>
       </c>
-      <c r="L89" s="10" t="s">
+      <c r="L89" s="11" t="s">
         <v>1072</v>
       </c>
-      <c r="M89" s="10" t="s">
+      <c r="M89" s="11" t="s">
         <v>1073</v>
       </c>
-      <c r="N89" s="10" t="s">
+      <c r="N89" s="11" t="s">
         <v>1074</v>
       </c>
-      <c r="O89" s="10" t="s">
+      <c r="O89" s="11" t="s">
         <v>1075</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="2:15">
-      <c r="B90" s="9">
+      <c r="B90" s="10">
         <v>10085</v>
       </c>
-      <c r="C90" s="10" t="s">
+      <c r="C90" s="11" t="s">
         <v>1076</v>
       </c>
-      <c r="D90" s="11" t="s">
+      <c r="D90" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="E90" s="10" t="s">
+      <c r="E90" s="11" t="s">
         <v>1078</v>
       </c>
-      <c r="F90" s="10" t="s">
+      <c r="F90" s="11" t="s">
         <v>1079</v>
       </c>
-      <c r="G90" s="10" t="s">
+      <c r="G90" s="11" t="s">
         <v>1080</v>
       </c>
-      <c r="H90" s="10" t="s">
+      <c r="H90" s="11" t="s">
         <v>1081</v>
       </c>
-      <c r="I90" s="10" t="s">
+      <c r="I90" s="11" t="s">
         <v>1082</v>
       </c>
-      <c r="J90" s="10" t="s">
+      <c r="J90" s="11" t="s">
         <v>1083</v>
       </c>
-      <c r="K90" s="10" t="s">
+      <c r="K90" s="11" t="s">
         <v>1084</v>
       </c>
-      <c r="L90" s="10" t="s">
+      <c r="L90" s="11" t="s">
         <v>1085</v>
       </c>
-      <c r="M90" s="10" t="s">
+      <c r="M90" s="11" t="s">
         <v>1086</v>
       </c>
-      <c r="N90" s="10" t="s">
+      <c r="N90" s="11" t="s">
         <v>1087</v>
       </c>
-      <c r="O90" s="10" t="s">
+      <c r="O90" s="11" t="s">
         <v>1088</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="2:15">
-      <c r="B91" s="9">
+      <c r="B91" s="10">
         <v>10086</v>
       </c>
-      <c r="C91" s="10" t="s">
+      <c r="C91" s="11" t="s">
         <v>1089</v>
       </c>
-      <c r="D91" s="11" t="s">
+      <c r="D91" s="12" t="s">
         <v>1090</v>
       </c>
-      <c r="E91" s="10" t="s">
+      <c r="E91" s="11" t="s">
         <v>1091</v>
       </c>
-      <c r="F91" s="10" t="s">
+      <c r="F91" s="11" t="s">
         <v>1092</v>
       </c>
-      <c r="G91" s="10" t="s">
+      <c r="G91" s="11" t="s">
         <v>1093</v>
       </c>
-      <c r="H91" s="10" t="s">
+      <c r="H91" s="11" t="s">
         <v>1094</v>
       </c>
-      <c r="I91" s="10" t="s">
+      <c r="I91" s="11" t="s">
         <v>1095</v>
       </c>
-      <c r="J91" s="10" t="s">
+      <c r="J91" s="11" t="s">
         <v>1096</v>
       </c>
-      <c r="K91" s="10" t="s">
+      <c r="K91" s="11" t="s">
         <v>1097</v>
       </c>
-      <c r="L91" s="10" t="s">
+      <c r="L91" s="11" t="s">
         <v>1098</v>
       </c>
-      <c r="M91" s="10" t="s">
+      <c r="M91" s="11" t="s">
         <v>1099</v>
       </c>
-      <c r="N91" s="10" t="s">
+      <c r="N91" s="11" t="s">
         <v>1100</v>
       </c>
-      <c r="O91" s="10" t="s">
+      <c r="O91" s="11" t="s">
         <v>1101</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="2:15">
-      <c r="B92" s="9">
+      <c r="B92" s="10">
         <v>10087</v>
       </c>
-      <c r="C92" s="10" t="s">
+      <c r="C92" s="11" t="s">
         <v>1102</v>
       </c>
-      <c r="D92" s="10" t="s">
+      <c r="D92" s="11" t="s">
         <v>1103</v>
       </c>
-      <c r="E92" s="10" t="s">
+      <c r="E92" s="11" t="s">
         <v>1104</v>
       </c>
-      <c r="F92" s="10" t="s">
+      <c r="F92" s="11" t="s">
         <v>1105</v>
       </c>
-      <c r="G92" s="10" t="s">
+      <c r="G92" s="11" t="s">
         <v>1106</v>
       </c>
-      <c r="H92" s="10" t="s">
+      <c r="H92" s="11" t="s">
         <v>1107</v>
       </c>
-      <c r="I92" s="10" t="s">
+      <c r="I92" s="11" t="s">
         <v>1108</v>
       </c>
-      <c r="J92" s="10" t="s">
+      <c r="J92" s="11" t="s">
         <v>1109</v>
       </c>
-      <c r="K92" s="10" t="s">
+      <c r="K92" s="11" t="s">
         <v>1110</v>
       </c>
-      <c r="L92" s="10" t="s">
+      <c r="L92" s="11" t="s">
         <v>1111</v>
       </c>
-      <c r="M92" s="10" t="s">
+      <c r="M92" s="11" t="s">
         <v>1112</v>
       </c>
-      <c r="N92" s="10" t="s">
+      <c r="N92" s="11" t="s">
         <v>1113</v>
       </c>
-      <c r="O92" s="10" t="s">
+      <c r="O92" s="11" t="s">
         <v>1114</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="2:15">
-      <c r="B93" s="9">
+      <c r="B93" s="10">
         <v>10088</v>
       </c>
-      <c r="C93" s="10" t="s">
+      <c r="C93" s="11" t="s">
         <v>1115</v>
       </c>
-      <c r="D93" s="10" t="s">
+      <c r="D93" s="11" t="s">
         <v>1116</v>
       </c>
-      <c r="E93" s="10" t="s">
+      <c r="E93" s="11" t="s">
         <v>1117</v>
       </c>
-      <c r="F93" s="10" t="s">
+      <c r="F93" s="11" t="s">
         <v>1118</v>
       </c>
-      <c r="G93" s="10" t="s">
+      <c r="G93" s="11" t="s">
         <v>1119</v>
       </c>
-      <c r="H93" s="10" t="s">
+      <c r="H93" s="11" t="s">
         <v>1120</v>
       </c>
-      <c r="I93" s="10" t="s">
+      <c r="I93" s="11" t="s">
         <v>1121</v>
       </c>
-      <c r="J93" s="10" t="s">
+      <c r="J93" s="11" t="s">
         <v>1122</v>
       </c>
-      <c r="K93" s="10" t="s">
+      <c r="K93" s="11" t="s">
         <v>1123</v>
       </c>
-      <c r="L93" s="10" t="s">
+      <c r="L93" s="11" t="s">
         <v>1124</v>
       </c>
-      <c r="M93" s="10" t="s">
+      <c r="M93" s="11" t="s">
         <v>1125</v>
       </c>
-      <c r="N93" s="10" t="s">
+      <c r="N93" s="11" t="s">
         <v>1126</v>
       </c>
-      <c r="O93" s="10" t="s">
+      <c r="O93" s="11" t="s">
         <v>1127</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="2:15">
-      <c r="B94" s="9">
+      <c r="B94" s="10">
         <v>10089</v>
       </c>
-      <c r="C94" s="10" t="s">
+      <c r="C94" s="11" t="s">
         <v>1128</v>
       </c>
-      <c r="D94" s="10" t="s">
+      <c r="D94" s="11" t="s">
         <v>1129</v>
       </c>
-      <c r="E94" s="10" t="s">
+      <c r="E94" s="11" t="s">
         <v>1130</v>
       </c>
-      <c r="F94" s="10" t="s">
+      <c r="F94" s="11" t="s">
         <v>1131</v>
       </c>
-      <c r="G94" s="10" t="s">
+      <c r="G94" s="11" t="s">
         <v>1132</v>
       </c>
-      <c r="H94" s="10" t="s">
+      <c r="H94" s="11" t="s">
         <v>1133</v>
       </c>
-      <c r="I94" s="10" t="s">
+      <c r="I94" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="J94" s="10" t="s">
+      <c r="J94" s="11" t="s">
         <v>1135</v>
       </c>
-      <c r="K94" s="10" t="s">
+      <c r="K94" s="11" t="s">
         <v>1136</v>
       </c>
-      <c r="L94" s="10" t="s">
+      <c r="L94" s="11" t="s">
         <v>1137</v>
       </c>
-      <c r="M94" s="10" t="s">
+      <c r="M94" s="11" t="s">
         <v>1138</v>
       </c>
-      <c r="N94" s="10" t="s">
+      <c r="N94" s="11" t="s">
         <v>1139</v>
       </c>
-      <c r="O94" s="10" t="s">
+      <c r="O94" s="11" t="s">
         <v>1140</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="2:15">
-      <c r="B95" s="9">
+      <c r="B95" s="10">
         <v>10090</v>
       </c>
-      <c r="C95" s="10" t="s">
+      <c r="C95" s="11" t="s">
         <v>1141</v>
       </c>
-      <c r="D95" s="11" t="s">
+      <c r="D95" s="12" t="s">
         <v>1142</v>
       </c>
-      <c r="E95" s="10" t="s">
+      <c r="E95" s="11" t="s">
         <v>1143</v>
       </c>
-      <c r="F95" s="10" t="s">
+      <c r="F95" s="11" t="s">
         <v>1144</v>
       </c>
-      <c r="G95" s="10" t="s">
+      <c r="G95" s="11" t="s">
         <v>1145</v>
       </c>
-      <c r="H95" s="10" t="s">
+      <c r="H95" s="11" t="s">
         <v>1146</v>
       </c>
-      <c r="I95" s="10" t="s">
+      <c r="I95" s="11" t="s">
         <v>1147</v>
       </c>
-      <c r="J95" s="10" t="s">
+      <c r="J95" s="11" t="s">
         <v>1148</v>
       </c>
-      <c r="K95" s="10" t="s">
+      <c r="K95" s="11" t="s">
         <v>1149</v>
       </c>
-      <c r="L95" s="10" t="s">
+      <c r="L95" s="11" t="s">
         <v>1150</v>
       </c>
-      <c r="M95" s="10" t="s">
+      <c r="M95" s="11" t="s">
         <v>1151</v>
       </c>
-      <c r="N95" s="10" t="s">
+      <c r="N95" s="11" t="s">
         <v>1152</v>
       </c>
-      <c r="O95" s="10" t="s">
+      <c r="O95" s="11" t="s">
         <v>1153</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="2:15">
-      <c r="B96" s="9">
+      <c r="B96" s="10">
         <v>10091</v>
       </c>
       <c r="C96" t="s">
@@ -9151,8 +9390,8 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="97" customHeight="1" spans="2:16">
-      <c r="B97" s="9">
+    <row r="97" customHeight="1" spans="1:16">
+      <c r="B97" s="10">
         <v>10092</v>
       </c>
       <c r="C97" t="s">
@@ -9195,8 +9434,8 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="98" customHeight="1" spans="2:16">
-      <c r="B98" s="2">
+    <row r="98" customHeight="1" spans="1:16">
+      <c r="B98" s="3">
         <v>10093</v>
       </c>
       <c r="C98" t="s">
@@ -9206,8 +9445,8 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="99" customHeight="1" spans="2:16">
-      <c r="B99" s="2">
+    <row r="99" customHeight="1" spans="1:16">
+      <c r="B99" s="3">
         <v>10094</v>
       </c>
       <c r="C99" t="s">
@@ -9217,8 +9456,8 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="100" customHeight="1" spans="2:16">
-      <c r="B100" s="2">
+    <row r="100" customHeight="1" spans="1:16">
+      <c r="B100" s="3">
         <v>10095</v>
       </c>
       <c r="C100" t="s">
@@ -9228,8 +9467,8 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="101" customHeight="1" spans="2:16">
-      <c r="B101" s="2">
+    <row r="101" customHeight="1" spans="1:16">
+      <c r="B101" s="3">
         <v>10096</v>
       </c>
       <c r="C101" t="s">
@@ -9238,11 +9477,11 @@
       <c r="D101" s="1" t="s">
         <v>1187</v>
       </c>
-      <c r="G101" s="12"/>
-      <c r="K101" s="12"/>
-    </row>
-    <row r="102" customHeight="1" spans="2:16">
-      <c r="B102" s="2">
+      <c r="G101" s="13"/>
+      <c r="K101" s="13"/>
+    </row>
+    <row r="102" customHeight="1" spans="1:16">
+      <c r="B102" s="3">
         <v>10097</v>
       </c>
       <c r="C102" t="s">
@@ -9251,66 +9490,150 @@
       <c r="D102" s="1" t="s">
         <v>1189</v>
       </c>
-      <c r="G102" s="12"/>
-      <c r="K102" s="12"/>
-    </row>
-    <row r="103" customHeight="1" spans="2:16">
-      <c r="G103" s="12"/>
-      <c r="K103" s="12"/>
-    </row>
-    <row r="104" customHeight="1" spans="2:16">
-      <c r="C104" s="1"/>
-      <c r="D104" s="13"/>
-      <c r="G104" s="13"/>
-      <c r="K104" s="13"/>
-    </row>
-    <row r="105" s="1" customFormat="1" ht="19" customHeight="1" spans="2:16">
-      <c r="B105" s="2"/>
+      <c r="G102" s="13"/>
+      <c r="K102" s="13"/>
+    </row>
+    <row r="103" s="2" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A103" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B103" s="3">
+        <v>10098</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="J103" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="K103" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="L103" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="M103" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="N103" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="O103" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="P103" s="2" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="104" customFormat="1" customHeight="1" spans="1:16">
+      <c r="B104" s="3">
+        <v>10099</v>
+      </c>
+      <c r="C104" s="11" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D104" s="12" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E104" s="11" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F104" s="11" t="s">
+        <v>1207</v>
+      </c>
+      <c r="G104" s="11" t="s">
+        <v>1208</v>
+      </c>
+      <c r="H104" s="11" t="s">
+        <v>1209</v>
+      </c>
+      <c r="I104" s="11" t="s">
+        <v>1210</v>
+      </c>
+      <c r="J104" s="11" t="s">
+        <v>1211</v>
+      </c>
+      <c r="K104" s="11" t="s">
+        <v>1212</v>
+      </c>
+      <c r="L104" s="11" t="s">
+        <v>1213</v>
+      </c>
+      <c r="M104" s="11" t="s">
+        <v>1214</v>
+      </c>
+      <c r="N104" s="14" t="s">
+        <v>1215</v>
+      </c>
+      <c r="O104" s="11" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="105" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
+      <c r="B105" s="3"/>
       <c r="C105"/>
-      <c r="D105" s="12"/>
+      <c r="D105" s="13"/>
       <c r="E105"/>
       <c r="F105"/>
-      <c r="G105" s="12"/>
+      <c r="G105" s="13"/>
       <c r="H105"/>
       <c r="I105"/>
       <c r="J105"/>
-      <c r="K105" s="12"/>
+      <c r="K105" s="13"/>
       <c r="L105"/>
       <c r="M105"/>
       <c r="N105"/>
       <c r="O105"/>
       <c r="P105"/>
     </row>
-    <row r="106" customHeight="1" spans="2:16">
-      <c r="D106" s="12"/>
-      <c r="G106" s="12"/>
-      <c r="K106" s="12"/>
-    </row>
-    <row r="107" customHeight="1" spans="2:16">
-      <c r="D107" s="12"/>
-      <c r="G107" s="12"/>
-      <c r="K107" s="12"/>
-    </row>
-    <row r="108" customHeight="1" spans="2:16">
-      <c r="D108" s="12"/>
-      <c r="G108" s="12"/>
-      <c r="K108" s="12"/>
-    </row>
-    <row r="109" customHeight="1" spans="2:16">
-      <c r="D109" s="12"/>
-      <c r="G109" s="12"/>
-      <c r="K109" s="12"/>
-    </row>
-    <row r="110" customHeight="1" spans="2:16">
-      <c r="D110" s="12"/>
-      <c r="G110" s="12"/>
-      <c r="K110" s="12"/>
-    </row>
-    <row r="111" customHeight="1" spans="2:16">
-      <c r="C111" s="14"/>
-      <c r="D111" s="12"/>
-      <c r="G111" s="12"/>
-      <c r="K111" s="12"/>
+    <row r="106" customHeight="1" spans="1:16">
+      <c r="D106" s="13"/>
+      <c r="G106" s="13"/>
+      <c r="K106" s="13"/>
+    </row>
+    <row r="107" customHeight="1" spans="1:16">
+      <c r="D107" s="13"/>
+      <c r="G107" s="13"/>
+      <c r="K107" s="13"/>
+    </row>
+    <row r="108" customHeight="1" spans="1:16">
+      <c r="D108" s="13"/>
+      <c r="G108" s="13"/>
+      <c r="K108" s="13"/>
+    </row>
+    <row r="109" customHeight="1" spans="1:16">
+      <c r="D109" s="13"/>
+      <c r="G109" s="13"/>
+      <c r="K109" s="13"/>
+    </row>
+    <row r="110" customHeight="1" spans="1:16">
+      <c r="D110" s="13"/>
+      <c r="G110" s="13"/>
+      <c r="K110" s="13"/>
+    </row>
+    <row r="111" customHeight="1" spans="1:16">
+      <c r="C111" s="15"/>
+      <c r="D111" s="13"/>
+      <c r="G111" s="13"/>
+      <c r="K111" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="1217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1303" uniqueCount="1218">
   <si>
     <t>##var</t>
   </si>
@@ -3830,6 +3830,9 @@
       </rPr>
       <t>zda çekebilirsiniz</t>
     </r>
+  </si>
+  <si>
+    <t>现金</t>
   </si>
 </sst>
 </file>
@@ -9588,9 +9591,15 @@
       </c>
     </row>
     <row r="105" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="B105" s="3"/>
-      <c r="C105"/>
-      <c r="D105" s="13"/>
+      <c r="B105" s="3">
+        <v>10100</v>
+      </c>
+      <c r="C105" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D105" s="13" t="s">
+        <v>153</v>
+      </c>
       <c r="E105"/>
       <c r="F105"/>
       <c r="G105" s="13"/>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1303" uniqueCount="1218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="1231">
   <si>
     <t>##var</t>
   </si>
@@ -3676,6 +3676,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>{0}</t>
     </r>
     <r>
@@ -3792,6 +3798,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>{0} gün check-in yapt</t>
     </r>
     <r>
@@ -3833,6 +3845,45 @@
   </si>
   <si>
     <t>现金</t>
+  </si>
+  <si>
+    <t>处理中，请等待审查</t>
+  </si>
+  <si>
+    <t>Processing. please wait for review</t>
+  </si>
+  <si>
+    <t>Wird bearbeitet. Bitte warte auf die Prüfung</t>
+  </si>
+  <si>
+    <t>処理中です。審査をお待ちください</t>
+  </si>
+  <si>
+    <t>Processando. Aguarde a revisão</t>
+  </si>
+  <si>
+    <t>Traitement en cours. Veuillez attendre l'examen</t>
+  </si>
+  <si>
+    <t>Procesando. Espera la revisión</t>
+  </si>
+  <si>
+    <t>처리 중입니다. 심사를 기다려 주세요</t>
+  </si>
+  <si>
+    <t>Memproses. Harap tunggu tinjauan</t>
+  </si>
+  <si>
+    <t>Обработка. Дождитесь проверки</t>
+  </si>
+  <si>
+    <t>प्रसंस्करण। समीक्षा की प्रतीक्षा करें</t>
+  </si>
+  <si>
+    <t>กำลังดำเนินการ กรุณารอการตรวจสอบ</t>
+  </si>
+  <si>
+    <t>İşleniyor. Lütfen incelemeyi bekleyin</t>
   </si>
 </sst>
 </file>
@@ -4012,13 +4063,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="MS Gothic"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
+      <name val="MS Gothic"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -4493,7 +4544,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4533,6 +4584,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -9614,9 +9666,48 @@
       <c r="P105"/>
     </row>
     <row r="106" customHeight="1" spans="1:16">
-      <c r="D106" s="13"/>
-      <c r="G106" s="13"/>
-      <c r="K106" s="13"/>
+      <c r="B106" s="3">
+        <v>10101</v>
+      </c>
+      <c r="C106" s="15" t="s">
+        <v>1218</v>
+      </c>
+      <c r="D106" s="15" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E106" s="15" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F106" s="15" t="s">
+        <v>1221</v>
+      </c>
+      <c r="G106" s="15" t="s">
+        <v>1222</v>
+      </c>
+      <c r="H106" s="15" t="s">
+        <v>1223</v>
+      </c>
+      <c r="I106" s="15" t="s">
+        <v>1224</v>
+      </c>
+      <c r="J106" s="15" t="s">
+        <v>1225</v>
+      </c>
+      <c r="K106" s="15" t="s">
+        <v>1226</v>
+      </c>
+      <c r="L106" s="15" t="s">
+        <v>1227</v>
+      </c>
+      <c r="M106" s="15" t="s">
+        <v>1228</v>
+      </c>
+      <c r="N106" s="15" t="s">
+        <v>1229</v>
+      </c>
+      <c r="O106" s="15" t="s">
+        <v>1230</v>
+      </c>
     </row>
     <row r="107" customHeight="1" spans="1:16">
       <c r="D107" s="13"/>
@@ -9639,7 +9730,7 @@
       <c r="K110" s="13"/>
     </row>
     <row r="111" customHeight="1" spans="1:16">
-      <c r="C111" s="15"/>
+      <c r="C111" s="16"/>
       <c r="D111" s="13"/>
       <c r="G111" s="13"/>
       <c r="K111" s="13"/>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="1231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="1233">
   <si>
     <t>##var</t>
   </si>
@@ -3884,6 +3884,12 @@
   </si>
   <si>
     <t>İşleniyor. Lütfen incelemeyi bekleyin</t>
+  </si>
+  <si>
+    <t>兑现条件未满足</t>
+  </si>
+  <si>
+    <t>Withdrawal conditions not met</t>
   </si>
 </sst>
 </file>
@@ -9710,7 +9716,15 @@
       </c>
     </row>
     <row r="107" customHeight="1" spans="1:16">
-      <c r="D107" s="13"/>
+      <c r="B107" s="3">
+        <v>10102</v>
+      </c>
+      <c r="C107" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D107" s="13" t="s">
+        <v>1232</v>
+      </c>
       <c r="G107" s="13"/>
       <c r="K107" s="13"/>
     </row>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="1233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="1243">
   <si>
     <t>##var</t>
   </si>
@@ -3890,6 +3890,36 @@
   </si>
   <si>
     <t>Withdrawal conditions not met</t>
+  </si>
+  <si>
+    <t>点击瓶子</t>
+  </si>
+  <si>
+    <t>Tap the bottle</t>
+  </si>
+  <si>
+    <t>点击倒水</t>
+  </si>
+  <si>
+    <t>Tap to pour water</t>
+  </si>
+  <si>
+    <t>装满的瓶子会收集到对应的饮料杯中</t>
+  </si>
+  <si>
+    <t>A filled bottle will be collected into the corresponding beverage cup</t>
+  </si>
+  <si>
+    <t>只有相同颜色的水可以导入融合</t>
+  </si>
+  <si>
+    <t>Only water of the same color can be poured and combined</t>
+  </si>
+  <si>
+    <t>所有的饮料制作完成即可通关</t>
+  </si>
+  <si>
+    <t>The level is cleared once all beverages are made</t>
   </si>
 </sst>
 </file>
@@ -4069,13 +4099,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
+      <name val="MS Gothic"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="MS Gothic"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -4550,7 +4580,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4590,7 +4620,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -5127,7 +5156,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W111"/>
+  <dimension ref="A1:W112"/>
   <sheetFormatPr defaultColWidth="9.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.875" customWidth="1"/>
@@ -9675,43 +9704,43 @@
       <c r="B106" s="3">
         <v>10101</v>
       </c>
-      <c r="C106" s="15" t="s">
+      <c r="C106" s="2" t="s">
         <v>1218</v>
       </c>
-      <c r="D106" s="15" t="s">
+      <c r="D106" s="2" t="s">
         <v>1219</v>
       </c>
-      <c r="E106" s="15" t="s">
+      <c r="E106" s="2" t="s">
         <v>1220</v>
       </c>
-      <c r="F106" s="15" t="s">
+      <c r="F106" s="2" t="s">
         <v>1221</v>
       </c>
-      <c r="G106" s="15" t="s">
+      <c r="G106" s="2" t="s">
         <v>1222</v>
       </c>
-      <c r="H106" s="15" t="s">
+      <c r="H106" s="2" t="s">
         <v>1223</v>
       </c>
-      <c r="I106" s="15" t="s">
+      <c r="I106" s="2" t="s">
         <v>1224</v>
       </c>
-      <c r="J106" s="15" t="s">
+      <c r="J106" s="2" t="s">
         <v>1225</v>
       </c>
-      <c r="K106" s="15" t="s">
+      <c r="K106" s="2" t="s">
         <v>1226</v>
       </c>
-      <c r="L106" s="15" t="s">
+      <c r="L106" s="2" t="s">
         <v>1227</v>
       </c>
-      <c r="M106" s="15" t="s">
+      <c r="M106" s="2" t="s">
         <v>1228</v>
       </c>
-      <c r="N106" s="15" t="s">
+      <c r="N106" s="2" t="s">
         <v>1229</v>
       </c>
-      <c r="O106" s="15" t="s">
+      <c r="O106" s="2" t="s">
         <v>1230</v>
       </c>
     </row>
@@ -9729,25 +9758,67 @@
       <c r="K107" s="13"/>
     </row>
     <row r="108" customHeight="1" spans="1:16">
-      <c r="D108" s="13"/>
+      <c r="B108" s="3">
+        <v>10103</v>
+      </c>
+      <c r="C108" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D108" s="13" t="s">
+        <v>1234</v>
+      </c>
       <c r="G108" s="13"/>
       <c r="K108" s="13"/>
     </row>
     <row r="109" customHeight="1" spans="1:16">
-      <c r="D109" s="13"/>
+      <c r="B109" s="3">
+        <v>10104</v>
+      </c>
+      <c r="C109" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D109" s="13" t="s">
+        <v>1236</v>
+      </c>
       <c r="G109" s="13"/>
       <c r="K109" s="13"/>
     </row>
     <row r="110" customHeight="1" spans="1:16">
-      <c r="D110" s="13"/>
+      <c r="B110" s="3">
+        <v>10105</v>
+      </c>
+      <c r="C110" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>1238</v>
+      </c>
       <c r="G110" s="13"/>
       <c r="K110" s="13"/>
     </row>
     <row r="111" customHeight="1" spans="1:16">
-      <c r="C111" s="16"/>
-      <c r="D111" s="13"/>
+      <c r="B111" s="3">
+        <v>10106</v>
+      </c>
+      <c r="C111" s="15" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D111" s="13" t="s">
+        <v>1240</v>
+      </c>
       <c r="G111" s="13"/>
       <c r="K111" s="13"/>
+    </row>
+    <row r="112" customHeight="1" spans="1:16">
+      <c r="B112" s="3">
+        <v>10107</v>
+      </c>
+      <c r="C112" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>1242</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="1243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="1539">
   <si>
     <t>##var</t>
   </si>
@@ -3588,28 +3588,193 @@
     <t>Select a bottle to be Shuffled</t>
   </si>
   <si>
+    <t>Wähle eine Flasche zum Mischen</t>
+  </si>
+  <si>
+    <t>シャッフルする瓶を選んでください</t>
+  </si>
+  <si>
+    <t>Selecione uma garrafa para embaralhar</t>
+  </si>
+  <si>
+    <t>Sélectionnez une bouteille à mélanger</t>
+  </si>
+  <si>
+    <t>Selecciona una botella para mezclar</t>
+  </si>
+  <si>
+    <t>섞을 병을 선택하세요</t>
+  </si>
+  <si>
+    <t>Pilih botol untuk dikocok</t>
+  </si>
+  <si>
+    <t>Выберите бутылку для перемешивания</t>
+  </si>
+  <si>
+    <t>मिलाने के लिए बोतल चुनें</t>
+  </si>
+  <si>
+    <t>เลือกขวดที่จะสับเปลี่ยน</t>
+  </si>
+  <si>
+    <t>Karıştırmak için bir şişe seçin</t>
+  </si>
+  <si>
     <t>打乱成功</t>
   </si>
   <si>
     <t>Shuffle success</t>
   </si>
   <si>
+    <t>Mischen erfolgreich</t>
+  </si>
+  <si>
+    <t>シャッフル成功</t>
+  </si>
+  <si>
+    <t>Embaralhamento bem-sucedido</t>
+  </si>
+  <si>
+    <t>Mélange réussi</t>
+  </si>
+  <si>
+    <t>Mezcla exitosa</t>
+  </si>
+  <si>
+    <t>섞기 성공</t>
+  </si>
+  <si>
+    <t>Pengocokan berhasil</t>
+  </si>
+  <si>
+    <t>Перемешивание успешно</t>
+  </si>
+  <si>
+    <t>मिलाना सफल</t>
+  </si>
+  <si>
+    <t>สับเปลี่ยนสำเร็จ</t>
+  </si>
+  <si>
+    <t>Karıştırma başarılı</t>
+  </si>
+  <si>
     <t>玩家</t>
   </si>
   <si>
     <t>Player</t>
   </si>
   <si>
+    <t>Spieler</t>
+  </si>
+  <si>
+    <t>プレイヤー</t>
+  </si>
+  <si>
+    <t>Jogador</t>
+  </si>
+  <si>
+    <t>Joueur</t>
+  </si>
+  <si>
+    <t>Jugador</t>
+  </si>
+  <si>
+    <t>플레이어</t>
+  </si>
+  <si>
+    <t>Pemain</t>
+  </si>
+  <si>
+    <t>Игрок</t>
+  </si>
+  <si>
+    <t>खिलाड़ी</t>
+  </si>
+  <si>
+    <t>ผู้เล่น</t>
+  </si>
+  <si>
+    <t>Oyuncu</t>
+  </si>
+  <si>
     <t>该瓶子无法打乱</t>
   </si>
   <si>
     <t>This bottle cannot be Shuffled</t>
   </si>
   <si>
+    <t>Diese Flasche kann nicht gemischt werden</t>
+  </si>
+  <si>
+    <t>この瓶はシャッフルできません</t>
+  </si>
+  <si>
+    <t>Esta garrafa não pode ser embaralhada</t>
+  </si>
+  <si>
+    <t>Cette bouteille ne peut pas être mélangée</t>
+  </si>
+  <si>
+    <t>Esta botella no se puede mezclar</t>
+  </si>
+  <si>
+    <t>이 병은 섞을 수 없습니다</t>
+  </si>
+  <si>
+    <t>Botol ini tidak dapat dikocok</t>
+  </si>
+  <si>
+    <t>Эту бутылку нельзя перемешивать</t>
+  </si>
+  <si>
+    <t>यह बोतल मिलाई नहीं जा सकती</t>
+  </si>
+  <si>
+    <t>ขวดนี้ไม่สามารถสับเปลี่ยนได้</t>
+  </si>
+  <si>
+    <t>Bu şişe karıştırılamaz</t>
+  </si>
+  <si>
     <t>没有更多的袋子需解锁</t>
   </si>
   <si>
     <t>No more pockets need to be unlocked</t>
+  </si>
+  <si>
+    <t>Keine weiteren Taschen zum Freischalten</t>
+  </si>
+  <si>
+    <t>これ以上ロック解除するポケットはありません</t>
+  </si>
+  <si>
+    <t>Não há mais bolsos para desbloquear</t>
+  </si>
+  <si>
+    <t>Plus de poches à débloquer</t>
+  </si>
+  <si>
+    <t>No hay más bolsillos para desbloquear</t>
+  </si>
+  <si>
+    <t>잠금 해제할 주머니가 더 이상 없습니다</t>
+  </si>
+  <si>
+    <t>Tidak ada kantong lagi yang perlu dibuka kuncinya</t>
+  </si>
+  <si>
+    <t>Больше нет карманов для разблокировки</t>
+  </si>
+  <si>
+    <t>अनलॉक करने के लिए और कोई पॉकेट नहीं</t>
+  </si>
+  <si>
+    <t>ไม่มีกระเป๋าให้ปลดล็อคเพิ่ม</t>
+  </si>
+  <si>
+    <t>Açılacak başka cep yok</t>
   </si>
   <si>
     <t/>
@@ -3847,6 +4012,39 @@
     <t>现金</t>
   </si>
   <si>
+    <t>Bargeld</t>
+  </si>
+  <si>
+    <t>現金</t>
+  </si>
+  <si>
+    <t>Dinheiro</t>
+  </si>
+  <si>
+    <t>Espèces</t>
+  </si>
+  <si>
+    <t>Efectivo</t>
+  </si>
+  <si>
+    <t>현금</t>
+  </si>
+  <si>
+    <t>Uang tunai</t>
+  </si>
+  <si>
+    <t>Наличные</t>
+  </si>
+  <si>
+    <t>नकद</t>
+  </si>
+  <si>
+    <t>เงินสด</t>
+  </si>
+  <si>
+    <t>Nakit</t>
+  </si>
+  <si>
     <t>处理中，请等待审查</t>
   </si>
   <si>
@@ -3892,34 +4090,748 @@
     <t>Withdrawal conditions not met</t>
   </si>
   <si>
+    <t>Abhebebedingungen nicht erfüllt</t>
+  </si>
+  <si>
+    <t>出金条件未達成</t>
+  </si>
+  <si>
+    <t>Condições de saque não atendidas</t>
+  </si>
+  <si>
+    <t>Conditions de retrait non remplies</t>
+  </si>
+  <si>
+    <t>Condiciones de retiro no cumplidas</t>
+  </si>
+  <si>
+    <t>출금 조건 미충족</t>
+  </si>
+  <si>
+    <t>Syarat penarikan tidak terpenuhi</t>
+  </si>
+  <si>
+    <t>Условия вывода не выполнены</t>
+  </si>
+  <si>
+    <t>निकासी शर्तें पूरी नहीं</t>
+  </si>
+  <si>
+    <t>เงื่อนไขการถอนไม่สำเร็จ</t>
+  </si>
+  <si>
+    <t>Çekim koşulları karşılanmadı</t>
+  </si>
+  <si>
     <t>点击瓶子</t>
   </si>
   <si>
     <t>Tap the bottle</t>
   </si>
   <si>
+    <t>Tippe auf die Flasche</t>
+  </si>
+  <si>
+    <t>ボトルをタップ</t>
+  </si>
+  <si>
+    <t>Toque na garrafa</t>
+  </si>
+  <si>
+    <t>Tapotez la bouteille</t>
+  </si>
+  <si>
+    <t>Toca la botella</t>
+  </si>
+  <si>
+    <t>병을 탭하세요</t>
+  </si>
+  <si>
+    <t>Ketuk botol</t>
+  </si>
+  <si>
+    <t>Нажмите на бутылку</t>
+  </si>
+  <si>
+    <t>बोतल टैप करें</t>
+  </si>
+  <si>
+    <t>แตะขวด</t>
+  </si>
+  <si>
+    <t>Şişeye dokun</t>
+  </si>
+  <si>
     <t>点击倒水</t>
   </si>
   <si>
     <t>Tap to pour water</t>
   </si>
   <si>
+    <t>Tippen, um Wasser zu gießen</t>
+  </si>
+  <si>
+    <t>タップで注ぐ</t>
+  </si>
+  <si>
+    <t>Toque para derramar</t>
+  </si>
+  <si>
+    <t>Tapotez pour verser</t>
+  </si>
+  <si>
+    <t>Toca para verter</t>
+  </si>
+  <si>
+    <t>탭하여 물 따르기</t>
+  </si>
+  <si>
+    <t>Ketuk untuk menuang</t>
+  </si>
+  <si>
+    <t>Нажмите, чтобы налить</t>
+  </si>
+  <si>
+    <t>डालने के लिए टैप करें</t>
+  </si>
+  <si>
+    <t>แตะเพื่อเทน้ำ</t>
+  </si>
+  <si>
+    <t>Dökmek için dokun</t>
+  </si>
+  <si>
     <t>装满的瓶子会收集到对应的饮料杯中</t>
   </si>
   <si>
     <t>A filled bottle will be collected into the corresponding beverage cup</t>
   </si>
   <si>
+    <t>Gefüllte Flasche wird in den Becher gesammelt</t>
+  </si>
+  <si>
+    <t>満杯のボトルは対応する飲料カップに集められます</t>
+  </si>
+  <si>
+    <t>Garrafa cheia será coletada no copo correspondente</t>
+  </si>
+  <si>
+    <t>La bouteille pleine est récupérée dans le verre approprié</t>
+  </si>
+  <si>
+    <t>Botella llena se recolecta en el vaso correspondiente</t>
+  </si>
+  <si>
+    <t>가득 찬 병은 해당 음료 컵에 수집됩니다</t>
+  </si>
+  <si>
+    <t>Botol yang terisi akan dikumpulkan ke gelas minum yang sesuai</t>
+  </si>
+  <si>
+    <t>Полная бутылка собирается в соответствующий стакан</t>
+  </si>
+  <si>
+    <t>भरी बोतल संबंधित पेय कप में एकत्र की जाएगी</t>
+  </si>
+  <si>
+    <t>ขวดที่เต็มจะถูกเก็บในแก้วเครื่องดื่มที่เกี่ยวข้อง</t>
+  </si>
+  <si>
+    <t>Dolu şişe ilgili içecek bardağında toplanır</t>
+  </si>
+  <si>
     <t>只有相同颜色的水可以导入融合</t>
   </si>
   <si>
     <t>Only water of the same color can be poured and combined</t>
   </si>
   <si>
+    <t>Nur gleiche Farben können gemischt werden</t>
+  </si>
+  <si>
+    <t>同じ色の水だけ注いで混ぜられます</t>
+  </si>
+  <si>
+    <t>Apenas água da mesma cor pode ser derramada e misturada</t>
+  </si>
+  <si>
+    <t>Seule l'eau de la même couleur peut être versée et mélangée</t>
+  </si>
+  <si>
+    <t>Solo se puede verter y mezclar agua del mismo color</t>
+  </si>
+  <si>
+    <t>같은 색깔의 물만 부어 섞을 수 있습니다</t>
+  </si>
+  <si>
+    <t>Hanya air dengan warna yang sama yang dapat dituang dan dicampur</t>
+  </si>
+  <si>
+    <t>Можно наливать и смешивать только воду одного цвета</t>
+  </si>
+  <si>
+    <t>केवल एक ही रंग का पानी डाला और मिलाया जा सकता है</t>
+  </si>
+  <si>
+    <t>เทและผสมได้เฉพาะน้ำสีเดียวกันเท่านั้น</t>
+  </si>
+  <si>
+    <t>Sadece aynı renkteki su dökülüp karıştırılabilir</t>
+  </si>
+  <si>
     <t>所有的饮料制作完成即可通关</t>
   </si>
   <si>
     <t>The level is cleared once all beverages are made</t>
+  </si>
+  <si>
+    <t>Alle Getränke hergestellt = Level geschafft</t>
+  </si>
+  <si>
+    <t>すべてのドリンクが完成するとレベルクリア</t>
+  </si>
+  <si>
+    <t>Todos os drinks feitos = fase concluída</t>
+  </si>
+  <si>
+    <t>Toutes les boissons préparées = niveau réussi</t>
+  </si>
+  <si>
+    <t>Todas las bebidas hechas = nivel completado</t>
+  </si>
+  <si>
+    <t>모든 음료 제작 시 레벨 클리어</t>
+  </si>
+  <si>
+    <t>Semua minuman selesai = level selesai</t>
+  </si>
+  <si>
+    <t>Все напитки готовы = уровень пройден</t>
+  </si>
+  <si>
+    <t>सभी पेय बन गए = लेवल पूरा</t>
+  </si>
+  <si>
+    <t>เครื่องดื่มทั้งหมดทำเสร็จ = ผ่านด่าน</t>
+  </si>
+  <si>
+    <t>Tüm içecekler yapıldı = seviye geçildi</t>
+  </si>
+  <si>
+    <t>提款</t>
+  </si>
+  <si>
+    <t>Withdrawal</t>
+  </si>
+  <si>
+    <t>Auszahlung</t>
+  </si>
+  <si>
+    <t>Saque</t>
+  </si>
+  <si>
+    <t>Retrait</t>
+  </si>
+  <si>
+    <t>Retiro</t>
+  </si>
+  <si>
+    <t>Penarikan</t>
+  </si>
+  <si>
+    <t>Вывод</t>
+  </si>
+  <si>
+    <t>निकासी</t>
+  </si>
+  <si>
+    <t>การถอน</t>
+  </si>
+  <si>
+    <t>Çekim</t>
+  </si>
+  <si>
+    <t>完成2次自动提款验证后，高价值提款官将直接为您提取{0}。</t>
+  </si>
+  <si>
+    <t>After completing 2 automatic withdrawalverifications, a high-value withdrawal officer willdirectly withdraw {0} for you.</t>
+  </si>
+  <si>
+    <t>Nach 2 automatischen Auszahlungsprüfungen wird ein Premium-Auszahlungsbeauftragter {0} direkt für dich abheben.</t>
+  </si>
+  <si>
+    <t>自動出金認証を2回完了すると、高額出金担当者が{0}を直接お引き出しします。</t>
+  </si>
+  <si>
+    <t>Após concluir 2 verificações automáticas de saque, um agente de saque premium sacará {0} diretamente para você.</t>
+  </si>
+  <si>
+    <t>Après 2 vérifications automatiques de retrait, un agent premium retirera directement {0} pour vous.</t>
+  </si>
+  <si>
+    <t>Tras completar 2 verificaciones automáticas de retiro, un agente premium retirará {0} directamente por ti.</t>
+  </si>
+  <si>
+    <t>자동 출금 인증 2회 완료 후, 고액 출금 담당자가 {0}을(를) 직접 출금해 드립니다.</t>
+  </si>
+  <si>
+    <t>Setelah menyelesaikan 2 verifikasi penarikan otomatis, petugas penarikan premium akan menarik {0} langsung untuk Anda.</t>
+  </si>
+  <si>
+    <t>После 2 автоматических проверок вывода премиум-агент выведет {0} за вас напрямую.</t>
+  </si>
+  <si>
+    <t>2 स्वचालित निकासी सत्यापन पूरे करने के बाद, प्रीमियम अधिकारी सीधे आपके लिए {0} निकालेगा।</t>
+  </si>
+  <si>
+    <t>หลังยืนยันการถอนอัตโนมัติ 2 ครั้ง เจ้าหน้าที่ถอนพรีเมียมจะถอน {0} ให้คุณโดยตรง</t>
+  </si>
+  <si>
+    <t>2 otomatik çekim doğrulamasından sonra premium çekim görevlisi sizin için doğrudan {0} çekecektir.</t>
+  </si>
+  <si>
+    <t>兑现完成</t>
+  </si>
+  <si>
+    <t>Withdrawal completed</t>
+  </si>
+  <si>
+    <t>Auszahlung abgeschlossen</t>
+  </si>
+  <si>
+    <t>出金完了</t>
+  </si>
+  <si>
+    <t>Saque concluído</t>
+  </si>
+  <si>
+    <t>Retrait terminé</t>
+  </si>
+  <si>
+    <t>Retiro completado</t>
+  </si>
+  <si>
+    <t>출금 완료</t>
+  </si>
+  <si>
+    <t>Penarikan selesai</t>
+  </si>
+  <si>
+    <t>Вывод завершён</t>
+  </si>
+  <si>
+    <t>निकासी पूर्ण</t>
+  </si>
+  <si>
+    <t>ถอนเสร็จสิ้น</t>
+  </si>
+  <si>
+    <t>Çekim tamamlandı</t>
+  </si>
+  <si>
+    <t>通过关卡{0}后兑现</t>
+  </si>
+  <si>
+    <t>Withdrawal after clearing Level {0}</t>
+  </si>
+  <si>
+    <t>Auszahlung nach Abschluss von Level {0}</t>
+  </si>
+  <si>
+    <t>レベル{0}クリア後に出金</t>
+  </si>
+  <si>
+    <t>Saque após concluir o nível {0}</t>
+  </si>
+  <si>
+    <t>Retrait après avoir terminé le niveau {0}</t>
+  </si>
+  <si>
+    <t>Retiro tras completar el nivel {0}</t>
+  </si>
+  <si>
+    <t>레벨 {0} 클리어 후 출금</t>
+  </si>
+  <si>
+    <t>Penarikan setelah menyelesaikan Level {0}</t>
+  </si>
+  <si>
+    <t>Вывод после прохождения уровня {0}</t>
+  </si>
+  <si>
+    <t>स्तर {0} पूरा करने के बाद निकासी</t>
+  </si>
+  <si>
+    <t>ถอนหลังผ่านด่าน {0}</t>
+  </si>
+  <si>
+    <t>Seviye {0} tamamlandıktan sonra çekim</t>
+  </si>
+  <si>
+    <t>官方认证，真真正正的现金兑现</t>
+  </si>
+  <si>
+    <t>officially verified, real cash withdrawals</t>
+  </si>
+  <si>
+    <t>Offiziell verifiziert – echte Bargeldauszahlungen</t>
+  </si>
+  <si>
+    <t>公式認証、本物の現金出金</t>
+  </si>
+  <si>
+    <t>Verificado oficialmente, saques em dinheiro real</t>
+  </si>
+  <si>
+    <t>Vérifié officiellement, retraits en argent réel</t>
+  </si>
+  <si>
+    <t>Verificado oficialmente, retiros en efectivo real</t>
+  </si>
+  <si>
+    <t>공식 인증, 실제 현금 출금</t>
+  </si>
+  <si>
+    <t>Terverifikasi resmi, penarikan uang tunai asli</t>
+  </si>
+  <si>
+    <t>Официально проверено — реальный вывод наличных</t>
+  </si>
+  <si>
+    <t>आधिकारिक रूप से सत्यापित, वास्तविक नकद निकासी</t>
+  </si>
+  <si>
+    <t>ยืนยันอย่างเป็นทางการ ถอนเงินสดจริง</t>
+  </si>
+  <si>
+    <t>Resmi olarak doğrulandı, gerçek nakit çekimler</t>
+  </si>
+  <si>
+    <t>您的提款请求已提交。由于需求量大，资金将在批准后10天内入账。</t>
+  </si>
+  <si>
+    <t>Your withdrawal request has been submitted. Due to high demand, funds will be credited within 10 days of approval.</t>
+  </si>
+  <si>
+    <t>Deine Auszahlungsanfrage wurde eingereicht. Aufgrund der hohen Nachfrage wird das Geld innerhalb von 10 Tagen nach Genehmigung gutgeschrieben.</t>
+  </si>
+  <si>
+    <t>出金リクエストを送信しました。需要が多いため、承認後10日以内に入金されます。</t>
+  </si>
+  <si>
+    <t>Sua solicitação de saque foi enviada. Devido à alta demanda, os fundos serão creditados em até 10 dias após a aprovação.</t>
+  </si>
+  <si>
+    <t>Votre demande de retrait a été soumise. En raison de la forte demande, les fonds seront crédités dans les 10 jours suivant l'approbation.</t>
+  </si>
+  <si>
+    <t>Tu solicitud de retiro ha sido enviada. Debido a la alta demanda, los fondos se acreditarán en un plazo de 10 días tras la aprobación.</t>
+  </si>
+  <si>
+    <t>출금 요청이 제출되었습니다. 수요가 많아 승인 후 10일 이내에 입금됩니다.</t>
+  </si>
+  <si>
+    <t>Permintaan penarikan Anda telah dikirim. Karena permintaan tinggi, dana akan dikreditkan dalam 10 hari setelah disetujui.</t>
+  </si>
+  <si>
+    <t>Заявка на вывод отправлена. Из-за высокого спроса средства поступят в течение 10 дней после одобрения.</t>
+  </si>
+  <si>
+    <t>आपका निकासी अनुरोध जमा हो गया है। अधिक माँग के कारण, स्वीकृति के 10 दिनों के भीतर राशि जमा होगी।</t>
+  </si>
+  <si>
+    <t>ส่งคำขอถอนแล้ว เนื่องจากมีผู้ขอมาก เงินจะโอนภายใน 10 วันหลังอนุมัติ</t>
+  </si>
+  <si>
+    <t>Çekim talebiniz gönderildi. Yoğun talep nedeniyle, onaydan sonra 10 gün içinde para yatırılacaktır.</t>
+  </si>
+  <si>
+    <t>继续攒钱</t>
+  </si>
+  <si>
+    <t>Keep Earning</t>
+  </si>
+  <si>
+    <t>Weiter verdienen</t>
+  </si>
+  <si>
+    <t>稼ぎ続ける</t>
+  </si>
+  <si>
+    <t>Continue ganhando</t>
+  </si>
+  <si>
+    <t>Continuez à gagner</t>
+  </si>
+  <si>
+    <t>Sigue ganando</t>
+  </si>
+  <si>
+    <t>계속 벌기</t>
+  </si>
+  <si>
+    <t>Terus dapatkan</t>
+  </si>
+  <si>
+    <t>Продолжайте зарабатывать</t>
+  </si>
+  <si>
+    <t>कमाते रहें</t>
+  </si>
+  <si>
+    <t>หาเงินต่อ</t>
+  </si>
+  <si>
+    <t>Kazanmaya devam et</t>
+  </si>
+  <si>
+    <t>关卡{0}小关{1}</t>
+  </si>
+  <si>
+    <t>level {0} round {1}</t>
+  </si>
+  <si>
+    <t>Level {0} Runde {1}</t>
+  </si>
+  <si>
+    <t>レベル{0} ラウンド{1}</t>
+  </si>
+  <si>
+    <t>nível {0} rodada {1}</t>
+  </si>
+  <si>
+    <t>niveau {0} manche {1}</t>
+  </si>
+  <si>
+    <t>nivel {0} ronda {1}</t>
+  </si>
+  <si>
+    <t>레벨 {0} 라운드 {1}</t>
+  </si>
+  <si>
+    <t>level {0} putaran {1}</t>
+  </si>
+  <si>
+    <t>уровень {0} раунд {1}</t>
+  </si>
+  <si>
+    <t>स्तर {0} राउंड {1}</t>
+  </si>
+  <si>
+    <t>ด่าน {0} รอบ {1}</t>
+  </si>
+  <si>
+    <t>seviye {0} tur {1}</t>
+  </si>
+  <si>
+    <t>现金
+提取</t>
+  </si>
+  <si>
+    <t>CASH
+WITHDRAW</t>
+  </si>
+  <si>
+    <t>BARGELD
+ABHEBEN</t>
+  </si>
+  <si>
+    <t>現金
+出金</t>
+  </si>
+  <si>
+    <t>DINHEIRO
+SACAR</t>
+  </si>
+  <si>
+    <t>ARGENT
+RETIRER</t>
+  </si>
+  <si>
+    <t>EFECTIVO
+RETIRAR</t>
+  </si>
+  <si>
+    <t>현금
+출금</t>
+  </si>
+  <si>
+    <t>UANG TUNAI
+TARIK</t>
+  </si>
+  <si>
+    <t>НАЛИЧНЫЕ
+ВЫВЕСТИ</t>
+  </si>
+  <si>
+    <t>नकद
+निकालें</t>
+  </si>
+  <si>
+    <t>เงินสด
+ถอน</t>
+  </si>
+  <si>
+    <t>NAKİT
+ÇEK</t>
+  </si>
+  <si>
+    <t>奖励 {0}</t>
+  </si>
+  <si>
+    <t>Reward {0}</t>
+  </si>
+  <si>
+    <t>Belohnung {0}</t>
+  </si>
+  <si>
+    <t>報酬 {0}</t>
+  </si>
+  <si>
+    <t>Recompensa {0}</t>
+  </si>
+  <si>
+    <t>Récompense {0}</t>
+  </si>
+  <si>
+    <t>보상 {0}</t>
+  </si>
+  <si>
+    <t>Hadiah {0}</t>
+  </si>
+  <si>
+    <t>Награда {0}</t>
+  </si>
+  <si>
+    <t>इनाम {0}</t>
+  </si>
+  <si>
+    <t>รางวัล {0}</t>
+  </si>
+  <si>
+    <t>Ödül {0}</t>
+  </si>
+  <si>
+    <t>通过关卡以提取所有现金，每个玩家都可以提取&lt;color=#F47823&gt;｛0｝&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Clear levels to withdraw all cash, each player can withdraw &lt;color=#F47823&gt;{0}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Schließe Level ab, um alles Bargeld abzuheben – jeder Spieler kann &lt;color=#F47823&gt;{0}&lt;/color&gt; abheben</t>
+  </si>
+  <si>
+    <t>レベルをクリアして全額出金。各プレイヤーは&lt;color=#F47823&gt;{0}&lt;/color&gt;を出金できます</t>
+  </si>
+  <si>
+    <t>Conclua níveis para sacar todo o dinheiro; cada jogador pode sacar &lt;color=#F47823&gt;{0}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Terminez les niveaux pour tout retirer ; chaque joueur peut retirer &lt;color=#F47823&gt;{0}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Completa niveles para retirar todo el efectivo; cada jugador puede retirar &lt;color=#F47823&gt;{0}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>레벨을 클리어해 전액 출금. 각 플레이어는 &lt;color=#F47823&gt;{0}&lt;/color&gt; 출금 가능</t>
+  </si>
+  <si>
+    <t>Selesaikan level untuk menarik semua uang tunai; setiap pemain dapat menarik &lt;color=#F47823&gt;{0}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Проходите уровни, чтобы вывести весь баланс; каждый игрок может вывести &lt;color=#F47823&gt;{0}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>सभी नकद निकालने के लिए स्तर पूरे करें; प्रत्येक खिलाड़ी &lt;color=#F47823&gt;{0}&lt;/color&gt; निकाल सकता है</t>
+  </si>
+  <si>
+    <t>ผ่านด่านเพื่อถอนเงินสดทั้งหมด ผู้เล่นแต่ละคนถอนได้ &lt;color=#F47823&gt;{0}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Tüm nakiti çekmek için seviyeleri tamamla; her oyuncu &lt;color=#F47823&gt;{0}&lt;/color&gt; çekebilir</t>
+  </si>
+  <si>
+    <t>完成关卡{0}提取所有现金</t>
+  </si>
+  <si>
+    <t>Clear Level {0} withdraw all cash</t>
+  </si>
+  <si>
+    <t>Level {0} abschließen – gesamtes Bargeld abheben</t>
+  </si>
+  <si>
+    <t>レベル{0}をクリアして全額出金</t>
+  </si>
+  <si>
+    <t>Conclua o nível {0} e saque todo o dinheiro</t>
+  </si>
+  <si>
+    <t>Terminez le niveau {0} et retirez tout l'argent</t>
+  </si>
+  <si>
+    <t>Completa el nivel {0} y retira todo el efectivo</t>
+  </si>
+  <si>
+    <t>레벨 {0} 클리어 후 전액 출금</t>
+  </si>
+  <si>
+    <t>Selesaikan Level {0} dan tarik semua uang tunai</t>
+  </si>
+  <si>
+    <t>Пройдите уровень {0} и выведите весь баланс</t>
+  </si>
+  <si>
+    <t>स्तर {0} पूरा करें और सारी नकद निकालें</t>
+  </si>
+  <si>
+    <t>ผ่านด่าน {0} แล้วถอนเงินสดทั้งหมด</t>
+  </si>
+  <si>
+    <t>Seviye {0}'yi tamamla ve tüm nakiti çek</t>
+  </si>
+  <si>
+    <t>关卡
+{0}</t>
+  </si>
+  <si>
+    <t>Level
+{0}</t>
+  </si>
+  <si>
+    <t>レベル
+{0}</t>
+  </si>
+  <si>
+    <t>Nível
+{0}</t>
+  </si>
+  <si>
+    <t>Niveau
+{0}</t>
+  </si>
+  <si>
+    <t>Nivel
+{0}</t>
+  </si>
+  <si>
+    <t>레벨
+{0}</t>
+  </si>
+  <si>
+    <t>Уровень
+{0}</t>
+  </si>
+  <si>
+    <t>स्तर
+{0}</t>
+  </si>
+  <si>
+    <t>ด่าน
+{0}</t>
+  </si>
+  <si>
+    <t>Seviye
+{0}</t>
   </si>
 </sst>
 </file>
@@ -3932,7 +4844,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3951,6 +4863,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11.25"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -4109,7 +5027,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4131,6 +5049,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4450,16 +5374,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4468,40 +5389,40 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4513,80 +5434,84 @@
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4617,11 +5542,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -5156,11 +6090,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W112"/>
+  <dimension ref="A1:W125"/>
   <sheetFormatPr defaultColWidth="9.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.875" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="4" customWidth="1"/>
     <col min="3" max="3" width="31.625" customWidth="1"/>
     <col min="4" max="4" width="54.25" style="1" customWidth="1"/>
     <col min="5" max="6" width="28.125" customWidth="1"/>
@@ -5170,49 +6104,49 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:16">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="8" t="s">
         <v>14</v>
       </c>
       <c r="P1" t="s">
@@ -5220,68 +6154,68 @@
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:16">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
     </row>
     <row r="3" customHeight="1" spans="1:16">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P3" t="s">
@@ -5289,49 +6223,49 @@
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:16">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="M4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="N4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="9" t="s">
+      <c r="O4" s="10" t="s">
         <v>19</v>
       </c>
       <c r="P4" t="s">
@@ -5339,49 +6273,49 @@
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:16">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="O5" s="7" t="s">
         <v>33</v>
       </c>
       <c r="P5" t="s">
@@ -5389,1059 +6323,1059 @@
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="13.5" spans="1:16">
-      <c r="B6" s="10">
+      <c r="B6" s="11">
         <v>10001</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="N6" s="11" t="s">
+      <c r="N6" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="O6" s="11" t="s">
+      <c r="O6" s="12" t="s">
         <v>47</v>
       </c>
       <c r="P6"/>
     </row>
     <row r="7" customFormat="1" customHeight="1" spans="1:16">
-      <c r="B7" s="10">
+      <c r="B7" s="11">
         <v>10002</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="L7" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="M7" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="N7" s="11" t="s">
+      <c r="N7" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="O7" s="11" t="s">
+      <c r="O7" s="12" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:16">
-      <c r="B8" s="10">
+      <c r="B8" s="11">
         <v>10003</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="J8" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="L8" s="11" t="s">
+      <c r="L8" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="M8" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="N8" s="11" t="s">
+      <c r="N8" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="O8" s="11" t="s">
+      <c r="O8" s="12" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:16">
-      <c r="B9" s="10">
+      <c r="B9" s="11">
         <v>10004</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="J9" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="L9" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="M9" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="N9" s="11" t="s">
+      <c r="N9" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="O9" s="11" t="s">
+      <c r="O9" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:16">
-      <c r="B10" s="10">
+      <c r="B10" s="11">
         <v>10005</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J10" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="L10" s="11" t="s">
+      <c r="L10" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="M10" s="11" t="s">
+      <c r="M10" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="N10" s="11" t="s">
+      <c r="N10" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="O10" s="11" t="s">
+      <c r="O10" s="12" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:16">
-      <c r="B11" s="10">
+      <c r="B11" s="11">
         <v>10006</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="J11" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="L11" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="M11" s="11" t="s">
+      <c r="M11" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="N11" s="11" t="s">
+      <c r="N11" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="O11" s="11" t="s">
+      <c r="O11" s="12" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="B12" s="10">
+      <c r="B12" s="11">
         <v>10007</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="J12" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K12" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="L12" s="11" t="s">
+      <c r="L12" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="M12" s="11" t="s">
+      <c r="M12" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="N12" s="11" t="s">
+      <c r="N12" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="O12" s="11" t="s">
+      <c r="O12" s="12" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="B13" s="10">
+      <c r="B13" s="11">
         <v>10008</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="J13" s="11" t="s">
+      <c r="J13" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K13" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="L13" s="11" t="s">
+      <c r="L13" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="M13" s="11" t="s">
+      <c r="M13" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="N13" s="11" t="s">
+      <c r="N13" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="O13" s="11" t="s">
+      <c r="O13" s="12" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:16">
-      <c r="B14" s="10">
+      <c r="B14" s="11">
         <v>10009</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K14" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="L14" s="11" t="s">
+      <c r="L14" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="M14" s="11" t="s">
+      <c r="M14" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="N14" s="11" t="s">
+      <c r="N14" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="O14" s="11" t="s">
+      <c r="O14" s="12" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:16">
-      <c r="B15" s="10">
+      <c r="B15" s="11">
         <v>10010</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J15" s="11" t="s">
+      <c r="J15" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="K15" s="11" t="s">
+      <c r="K15" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="L15" s="11" t="s">
+      <c r="L15" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="M15" s="11" t="s">
+      <c r="M15" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="N15" s="11" t="s">
+      <c r="N15" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="O15" s="11" t="s">
+      <c r="O15" s="12" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:16">
-      <c r="B16" s="10">
+      <c r="B16" s="11">
         <v>10011</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="H16" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="I16" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="J16" s="11" t="s">
+      <c r="J16" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="K16" s="11" t="s">
+      <c r="K16" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="L16" s="11" t="s">
+      <c r="L16" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="M16" s="11" t="s">
+      <c r="M16" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="N16" s="11" t="s">
+      <c r="N16" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="O16" s="11" t="s">
+      <c r="O16" s="12" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:23">
-      <c r="B17" s="10">
+      <c r="B17" s="11">
         <v>10012</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="H17" s="11" t="s">
+      <c r="H17" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="I17" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="J17" s="11" t="s">
+      <c r="J17" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="K17" s="11" t="s">
+      <c r="K17" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="L17" s="11" t="s">
+      <c r="L17" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="M17" s="11" t="s">
+      <c r="M17" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="N17" s="11" t="s">
+      <c r="N17" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="O17" s="11" t="s">
+      <c r="O17" s="12" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:23">
-      <c r="B18" s="10">
+      <c r="B18" s="11">
         <v>10013</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="H18" s="11" t="s">
+      <c r="H18" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="I18" s="11" t="s">
+      <c r="I18" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="J18" s="11" t="s">
+      <c r="J18" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="K18" s="11" t="s">
+      <c r="K18" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="L18" s="11" t="s">
+      <c r="L18" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="M18" s="11" t="s">
+      <c r="M18" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="N18" s="11" t="s">
+      <c r="N18" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="O18" s="11" t="s">
+      <c r="O18" s="12" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:23">
-      <c r="B19" s="10">
+      <c r="B19" s="11">
         <v>10014</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="H19" s="11" t="s">
+      <c r="H19" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="I19" s="11" t="s">
+      <c r="I19" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="J19" s="11" t="s">
+      <c r="J19" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="K19" s="11" t="s">
+      <c r="K19" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="L19" s="11" t="s">
+      <c r="L19" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="M19" s="11" t="s">
+      <c r="M19" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="N19" s="11" t="s">
+      <c r="N19" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="O19" s="11" t="s">
+      <c r="O19" s="12" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:23">
-      <c r="B20" s="10">
+      <c r="B20" s="11">
         <v>10015</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="G20" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="H20" s="11" t="s">
+      <c r="H20" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="I20" s="11" t="s">
+      <c r="I20" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="J20" s="11" t="s">
+      <c r="J20" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="K20" s="11" t="s">
+      <c r="K20" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="L20" s="11" t="s">
+      <c r="L20" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="M20" s="11" t="s">
+      <c r="M20" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="N20" s="11" t="s">
+      <c r="N20" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="O20" s="11" t="s">
+      <c r="O20" s="12" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:23">
-      <c r="B21" s="10">
+      <c r="B21" s="11">
         <v>10016</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="G21" s="11" t="s">
+      <c r="G21" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="H21" s="11" t="s">
+      <c r="H21" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="I21" s="11" t="s">
+      <c r="I21" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="J21" s="11" t="s">
+      <c r="J21" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="K21" s="11" t="s">
+      <c r="K21" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="L21" s="11" t="s">
+      <c r="L21" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="M21" s="11" t="s">
+      <c r="M21" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="N21" s="11" t="s">
+      <c r="N21" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="O21" s="11" t="s">
+      <c r="O21" s="12" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:23">
-      <c r="B22" s="10">
+      <c r="B22" s="11">
         <v>10017</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G22" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="H22" s="11" t="s">
+      <c r="H22" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="I22" s="11" t="s">
+      <c r="I22" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="J22" s="11" t="s">
+      <c r="J22" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="K22" s="11" t="s">
+      <c r="K22" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="L22" s="11" t="s">
+      <c r="L22" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="M22" s="11" t="s">
+      <c r="M22" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="N22" s="11" t="s">
+      <c r="N22" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="O22" s="11" t="s">
+      <c r="O22" s="12" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:23">
-      <c r="B23" s="10">
+      <c r="B23" s="11">
         <v>10018</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="G23" s="11" t="s">
+      <c r="G23" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="H23" s="11" t="s">
+      <c r="H23" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="I23" s="11" t="s">
+      <c r="I23" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="J23" s="11" t="s">
+      <c r="J23" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="K23" s="11" t="s">
+      <c r="K23" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="L23" s="11" t="s">
+      <c r="L23" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="M23" s="11" t="s">
+      <c r="M23" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="N23" s="11" t="s">
+      <c r="N23" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="O23" s="11" t="s">
+      <c r="O23" s="12" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="2:23">
-      <c r="B24" s="10">
+      <c r="B24" s="11">
         <v>10019</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="I24" s="11" t="s">
+      <c r="I24" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="J24" s="11" t="s">
+      <c r="J24" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="K24" s="11" t="s">
+      <c r="K24" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="L24" s="11" t="s">
+      <c r="L24" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="M24" s="11" t="s">
+      <c r="M24" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="N24" s="11" t="s">
+      <c r="N24" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="O24" s="11" t="s">
+      <c r="O24" s="12" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="2:23">
-      <c r="B25" s="10">
+      <c r="B25" s="11">
         <v>10020</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="G25" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="H25" s="11" t="s">
+      <c r="H25" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="I25" s="11" t="s">
+      <c r="I25" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="J25" s="11" t="s">
+      <c r="J25" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="K25" s="11" t="s">
+      <c r="K25" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="L25" s="11" t="s">
+      <c r="L25" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="M25" s="11" t="s">
+      <c r="M25" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="N25" s="11" t="s">
+      <c r="N25" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="O25" s="11" t="s">
+      <c r="O25" s="12" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:23">
-      <c r="B26" s="10">
+      <c r="B26" s="11">
         <v>10021</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="G26" s="11" t="s">
+      <c r="G26" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="H26" s="11" t="s">
+      <c r="H26" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="I26" s="11" t="s">
+      <c r="I26" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="J26" s="11" t="s">
+      <c r="J26" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="K26" s="11" t="s">
+      <c r="K26" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="L26" s="11" t="s">
+      <c r="L26" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="M26" s="11" t="s">
+      <c r="M26" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="N26" s="11" t="s">
+      <c r="N26" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="O26" s="11" t="s">
+      <c r="O26" s="12" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:23">
-      <c r="B27" s="10">
+      <c r="B27" s="11">
         <v>10022</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="G27" s="11" t="s">
+      <c r="G27" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="H27" s="11" t="s">
+      <c r="H27" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="I27" s="11" t="s">
+      <c r="I27" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="J27" s="11" t="s">
+      <c r="J27" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="K27" s="11" t="s">
+      <c r="K27" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="L27" s="11" t="s">
+      <c r="L27" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="M27" s="11" t="s">
+      <c r="M27" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="N27" s="11" t="s">
+      <c r="N27" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="O27" s="11" t="s">
+      <c r="O27" s="12" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="28" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B28" s="10">
+      <c r="B28" s="11">
         <v>10023</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="12" t="s">
         <v>312</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E28" s="12" t="s">
         <v>314</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="G28" s="11" t="s">
+      <c r="G28" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="H28" s="11" t="s">
+      <c r="H28" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="I28" s="11" t="s">
+      <c r="I28" s="12" t="s">
         <v>318</v>
       </c>
-      <c r="J28" s="11" t="s">
+      <c r="J28" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="K28" s="11" t="s">
+      <c r="K28" s="12" t="s">
         <v>320</v>
       </c>
-      <c r="L28" s="11" t="s">
+      <c r="L28" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="M28" s="11" t="s">
+      <c r="M28" s="12" t="s">
         <v>322</v>
       </c>
-      <c r="N28" s="11" t="s">
+      <c r="N28" s="12" t="s">
         <v>323</v>
       </c>
-      <c r="O28" s="11" t="s">
+      <c r="O28" s="12" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="29" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B29" s="10">
+      <c r="B29" s="11">
         <v>10024</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="12" t="s">
         <v>328</v>
       </c>
-      <c r="G29" s="11" t="s">
+      <c r="G29" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="H29" s="11" t="s">
+      <c r="H29" s="12" t="s">
         <v>330</v>
       </c>
-      <c r="I29" s="11" t="s">
+      <c r="I29" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="J29" s="11" t="s">
+      <c r="J29" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="K29" s="11" t="s">
+      <c r="K29" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="L29" s="11" t="s">
+      <c r="L29" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="M29" s="11" t="s">
+      <c r="M29" s="12" t="s">
         <v>335</v>
       </c>
-      <c r="N29" s="11" t="s">
+      <c r="N29" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="O29" s="11" t="s">
+      <c r="O29" s="12" t="s">
         <v>337</v>
       </c>
       <c r="Q29" s="1"/>
@@ -6453,46 +7387,46 @@
       <c r="W29" s="1"/>
     </row>
     <row r="30" customHeight="1" spans="2:23">
-      <c r="B30" s="10">
+      <c r="B30" s="11">
         <v>10025</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="13" t="s">
         <v>338</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="12" t="s">
         <v>340</v>
       </c>
-      <c r="G30" s="11" t="s">
+      <c r="G30" s="12" t="s">
         <v>341</v>
       </c>
-      <c r="H30" s="11" t="s">
+      <c r="H30" s="12" t="s">
         <v>342</v>
       </c>
-      <c r="I30" s="11" t="s">
+      <c r="I30" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="J30" s="11" t="s">
+      <c r="J30" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="K30" s="11" t="s">
+      <c r="K30" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="L30" s="11" t="s">
+      <c r="L30" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="M30" s="11" t="s">
+      <c r="M30" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="N30" s="11" t="s">
+      <c r="N30" s="12" t="s">
         <v>348</v>
       </c>
-      <c r="O30" s="11" t="s">
+      <c r="O30" s="12" t="s">
         <v>349</v>
       </c>
       <c r="P30" s="1"/>
@@ -6505,46 +7439,46 @@
       <c r="W30" s="1"/>
     </row>
     <row r="31" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B31" s="10">
+      <c r="B31" s="11">
         <v>10026</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="12" t="s">
         <v>353</v>
       </c>
-      <c r="G31" s="11" t="s">
+      <c r="G31" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="H31" s="11" t="s">
+      <c r="H31" s="12" t="s">
         <v>355</v>
       </c>
-      <c r="I31" s="11" t="s">
+      <c r="I31" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="J31" s="11" t="s">
+      <c r="J31" s="12" t="s">
         <v>356</v>
       </c>
-      <c r="K31" s="11" t="s">
+      <c r="K31" s="12" t="s">
         <v>357</v>
       </c>
-      <c r="L31" s="11" t="s">
+      <c r="L31" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="M31" s="11" t="s">
+      <c r="M31" s="12" t="s">
         <v>359</v>
       </c>
-      <c r="N31" s="11" t="s">
+      <c r="N31" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="O31" s="11" t="s">
+      <c r="O31" s="12" t="s">
         <v>361</v>
       </c>
       <c r="P31"/>
@@ -6557,135 +7491,135 @@
       <c r="W31" s="1"/>
     </row>
     <row r="32" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B32" s="10">
+      <c r="B32" s="11">
         <v>10027</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="12" t="s">
         <v>362</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E32" s="12" t="s">
         <v>364</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="12" t="s">
         <v>365</v>
       </c>
-      <c r="G32" s="11" t="s">
+      <c r="G32" s="12" t="s">
         <v>364</v>
       </c>
-      <c r="H32" s="11" t="s">
+      <c r="H32" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="I32" s="11" t="s">
+      <c r="I32" s="12" t="s">
         <v>367</v>
       </c>
-      <c r="J32" s="11" t="s">
+      <c r="J32" s="12" t="s">
         <v>368</v>
       </c>
-      <c r="K32" s="11" t="s">
+      <c r="K32" s="12" t="s">
         <v>364</v>
       </c>
-      <c r="L32" s="11" t="s">
+      <c r="L32" s="12" t="s">
         <v>369</v>
       </c>
-      <c r="M32" s="11" t="s">
+      <c r="M32" s="12" t="s">
         <v>370</v>
       </c>
-      <c r="N32" s="11" t="s">
+      <c r="N32" s="12" t="s">
         <v>371</v>
       </c>
-      <c r="O32" s="11" t="s">
+      <c r="O32" s="12" t="s">
         <v>372</v>
       </c>
       <c r="P32"/>
     </row>
     <row r="33" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B33" s="10">
+      <c r="B33" s="11">
         <v>10028</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" s="12" t="s">
         <v>374</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="E33" s="12" t="s">
         <v>375</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="F33" s="12" t="s">
         <v>376</v>
       </c>
-      <c r="G33" s="11" t="s">
+      <c r="G33" s="12" t="s">
         <v>377</v>
       </c>
-      <c r="H33" s="11" t="s">
+      <c r="H33" s="12" t="s">
         <v>378</v>
       </c>
-      <c r="I33" s="11" t="s">
+      <c r="I33" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="J33" s="11" t="s">
+      <c r="J33" s="12" t="s">
         <v>380</v>
       </c>
-      <c r="K33" s="11" t="s">
+      <c r="K33" s="12" t="s">
         <v>381</v>
       </c>
-      <c r="L33" s="11" t="s">
+      <c r="L33" s="12" t="s">
         <v>382</v>
       </c>
-      <c r="M33" s="11" t="s">
+      <c r="M33" s="12" t="s">
         <v>383</v>
       </c>
-      <c r="N33" s="11" t="s">
+      <c r="N33" s="12" t="s">
         <v>384</v>
       </c>
-      <c r="O33" s="11" t="s">
+      <c r="O33" s="12" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B34" s="10">
+      <c r="B34" s="11">
         <v>10029</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="12" t="s">
         <v>386</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="12" t="s">
         <v>387</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="E34" s="12" t="s">
         <v>388</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="G34" s="11" t="s">
+      <c r="G34" s="12" t="s">
         <v>388</v>
       </c>
-      <c r="H34" s="11" t="s">
+      <c r="H34" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="I34" s="11" t="s">
+      <c r="I34" s="12" t="s">
         <v>391</v>
       </c>
-      <c r="J34" s="11" t="s">
+      <c r="J34" s="12" t="s">
         <v>392</v>
       </c>
-      <c r="K34" s="11" t="s">
+      <c r="K34" s="12" t="s">
         <v>388</v>
       </c>
-      <c r="L34" s="11" t="s">
+      <c r="L34" s="12" t="s">
         <v>393</v>
       </c>
-      <c r="M34" s="11" t="s">
+      <c r="M34" s="12" t="s">
         <v>394</v>
       </c>
-      <c r="N34" s="11" t="s">
+      <c r="N34" s="12" t="s">
         <v>395</v>
       </c>
-      <c r="O34" s="11" t="s">
+      <c r="O34" s="12" t="s">
         <v>396</v>
       </c>
       <c r="Q34"/>
@@ -6697,46 +7631,46 @@
       <c r="W34"/>
     </row>
     <row r="35" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B35" s="10">
+      <c r="B35" s="11">
         <v>10030</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D35" s="12" t="s">
         <v>398</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="E35" s="12" t="s">
         <v>399</v>
       </c>
-      <c r="F35" s="11" t="s">
+      <c r="F35" s="12" t="s">
         <v>400</v>
       </c>
-      <c r="G35" s="11" t="s">
+      <c r="G35" s="12" t="s">
         <v>401</v>
       </c>
-      <c r="H35" s="11" t="s">
+      <c r="H35" s="12" t="s">
         <v>402</v>
       </c>
-      <c r="I35" s="11" t="s">
+      <c r="I35" s="12" t="s">
         <v>403</v>
       </c>
-      <c r="J35" s="11" t="s">
+      <c r="J35" s="12" t="s">
         <v>404</v>
       </c>
-      <c r="K35" s="11" t="s">
+      <c r="K35" s="12" t="s">
         <v>405</v>
       </c>
-      <c r="L35" s="11" t="s">
+      <c r="L35" s="12" t="s">
         <v>406</v>
       </c>
-      <c r="M35" s="11" t="s">
+      <c r="M35" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="N35" s="11" t="s">
+      <c r="N35" s="12" t="s">
         <v>408</v>
       </c>
-      <c r="O35" s="11" t="s">
+      <c r="O35" s="12" t="s">
         <v>409</v>
       </c>
       <c r="P35"/>
@@ -6749,46 +7683,46 @@
       <c r="W35"/>
     </row>
     <row r="36" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B36" s="10">
+      <c r="B36" s="11">
         <v>10031</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C36" s="12" t="s">
         <v>410</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="D36" s="12" t="s">
         <v>411</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E36" s="12" t="s">
         <v>412</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="F36" s="12" t="s">
         <v>413</v>
       </c>
-      <c r="G36" s="11" t="s">
+      <c r="G36" s="12" t="s">
         <v>412</v>
       </c>
-      <c r="H36" s="11" t="s">
+      <c r="H36" s="12" t="s">
         <v>414</v>
       </c>
-      <c r="I36" s="11" t="s">
+      <c r="I36" s="12" t="s">
         <v>415</v>
       </c>
-      <c r="J36" s="11" t="s">
+      <c r="J36" s="12" t="s">
         <v>416</v>
       </c>
-      <c r="K36" s="11" t="s">
+      <c r="K36" s="12" t="s">
         <v>412</v>
       </c>
-      <c r="L36" s="11" t="s">
+      <c r="L36" s="12" t="s">
         <v>417</v>
       </c>
-      <c r="M36" s="11" t="s">
+      <c r="M36" s="12" t="s">
         <v>418</v>
       </c>
-      <c r="N36" s="11" t="s">
+      <c r="N36" s="12" t="s">
         <v>419</v>
       </c>
-      <c r="O36" s="11" t="s">
+      <c r="O36" s="12" t="s">
         <v>420</v>
       </c>
       <c r="P36"/>
@@ -6801,46 +7735,46 @@
       <c r="W36"/>
     </row>
     <row r="37" customHeight="1" spans="2:23">
-      <c r="B37" s="10">
+      <c r="B37" s="11">
         <v>10032</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="13" t="s">
         <v>421</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" s="12" t="s">
         <v>422</v>
       </c>
-      <c r="E37" s="11" t="s">
+      <c r="E37" s="12" t="s">
         <v>423</v>
       </c>
-      <c r="F37" s="11" t="s">
+      <c r="F37" s="12" t="s">
         <v>424</v>
       </c>
-      <c r="G37" s="11" t="s">
+      <c r="G37" s="12" t="s">
         <v>425</v>
       </c>
-      <c r="H37" s="11" t="s">
+      <c r="H37" s="12" t="s">
         <v>426</v>
       </c>
-      <c r="I37" s="11" t="s">
+      <c r="I37" s="12" t="s">
         <v>427</v>
       </c>
-      <c r="J37" s="11" t="s">
+      <c r="J37" s="12" t="s">
         <v>428</v>
       </c>
-      <c r="K37" s="11" t="s">
+      <c r="K37" s="12" t="s">
         <v>429</v>
       </c>
-      <c r="L37" s="11" t="s">
+      <c r="L37" s="12" t="s">
         <v>430</v>
       </c>
-      <c r="M37" s="11" t="s">
+      <c r="M37" s="12" t="s">
         <v>431</v>
       </c>
-      <c r="N37" s="11" t="s">
+      <c r="N37" s="12" t="s">
         <v>432</v>
       </c>
-      <c r="O37" s="11" t="s">
+      <c r="O37" s="12" t="s">
         <v>433</v>
       </c>
       <c r="Q37" s="1"/>
@@ -6852,46 +7786,46 @@
       <c r="W37" s="1"/>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B38" s="10">
+      <c r="B38" s="11">
         <v>10033</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="12" t="s">
         <v>434</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="D38" s="12" t="s">
         <v>435</v>
       </c>
-      <c r="E38" s="11" t="s">
+      <c r="E38" s="12" t="s">
         <v>436</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="F38" s="12" t="s">
         <v>437</v>
       </c>
-      <c r="G38" s="11" t="s">
+      <c r="G38" s="12" t="s">
         <v>438</v>
       </c>
-      <c r="H38" s="11" t="s">
+      <c r="H38" s="12" t="s">
         <v>439</v>
       </c>
-      <c r="I38" s="11" t="s">
+      <c r="I38" s="12" t="s">
         <v>440</v>
       </c>
-      <c r="J38" s="11" t="s">
+      <c r="J38" s="12" t="s">
         <v>441</v>
       </c>
-      <c r="K38" s="11" t="s">
+      <c r="K38" s="12" t="s">
         <v>442</v>
       </c>
-      <c r="L38" s="11" t="s">
+      <c r="L38" s="12" t="s">
         <v>443</v>
       </c>
-      <c r="M38" s="11" t="s">
+      <c r="M38" s="12" t="s">
         <v>444</v>
       </c>
-      <c r="N38" s="11" t="s">
+      <c r="N38" s="12" t="s">
         <v>445</v>
       </c>
-      <c r="O38" s="11" t="s">
+      <c r="O38" s="12" t="s">
         <v>446</v>
       </c>
       <c r="P38" s="1"/>
@@ -6904,90 +7838,90 @@
       <c r="W38" s="1"/>
     </row>
     <row r="39" customHeight="1" spans="2:23">
-      <c r="B39" s="10">
+      <c r="B39" s="11">
         <v>10034</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="12" t="s">
         <v>447</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="D39" s="12" t="s">
         <v>448</v>
       </c>
-      <c r="E39" s="11" t="s">
+      <c r="E39" s="12" t="s">
         <v>449</v>
       </c>
-      <c r="F39" s="11" t="s">
+      <c r="F39" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="G39" s="11" t="s">
+      <c r="G39" s="12" t="s">
         <v>451</v>
       </c>
-      <c r="H39" s="11" t="s">
+      <c r="H39" s="12" t="s">
         <v>452</v>
       </c>
-      <c r="I39" s="11" t="s">
+      <c r="I39" s="12" t="s">
         <v>453</v>
       </c>
-      <c r="J39" s="11" t="s">
+      <c r="J39" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="K39" s="11" t="s">
+      <c r="K39" s="12" t="s">
         <v>455</v>
       </c>
-      <c r="L39" s="11" t="s">
+      <c r="L39" s="12" t="s">
         <v>456</v>
       </c>
-      <c r="M39" s="11" t="s">
+      <c r="M39" s="12" t="s">
         <v>457</v>
       </c>
-      <c r="N39" s="11" t="s">
+      <c r="N39" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="O39" s="11" t="s">
+      <c r="O39" s="12" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" ht="20" customHeight="1" spans="2:23">
-      <c r="B40" s="10">
+      <c r="B40" s="11">
         <v>10035</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C40" s="12" t="s">
         <v>460</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="D40" s="12" t="s">
         <v>461</v>
       </c>
-      <c r="E40" s="11" t="s">
+      <c r="E40" s="12" t="s">
         <v>462</v>
       </c>
-      <c r="F40" s="11" t="s">
+      <c r="F40" s="12" t="s">
         <v>463</v>
       </c>
-      <c r="G40" s="11" t="s">
+      <c r="G40" s="12" t="s">
         <v>464</v>
       </c>
-      <c r="H40" s="11" t="s">
+      <c r="H40" s="12" t="s">
         <v>465</v>
       </c>
-      <c r="I40" s="11" t="s">
+      <c r="I40" s="12" t="s">
         <v>466</v>
       </c>
-      <c r="J40" s="11" t="s">
+      <c r="J40" s="12" t="s">
         <v>467</v>
       </c>
-      <c r="K40" s="11" t="s">
+      <c r="K40" s="12" t="s">
         <v>468</v>
       </c>
-      <c r="L40" s="11" t="s">
+      <c r="L40" s="12" t="s">
         <v>469</v>
       </c>
-      <c r="M40" s="11" t="s">
+      <c r="M40" s="12" t="s">
         <v>470</v>
       </c>
-      <c r="N40" s="11" t="s">
+      <c r="N40" s="12" t="s">
         <v>471</v>
       </c>
-      <c r="O40" s="11" t="s">
+      <c r="O40" s="12" t="s">
         <v>472</v>
       </c>
       <c r="P40"/>
@@ -7000,46 +7934,46 @@
       <c r="W40"/>
     </row>
     <row r="41" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B41" s="10">
+      <c r="B41" s="11">
         <v>10036</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="13" t="s">
         <v>473</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D41" s="12" t="s">
         <v>474</v>
       </c>
-      <c r="E41" s="11" t="s">
+      <c r="E41" s="12" t="s">
         <v>475</v>
       </c>
-      <c r="F41" s="11" t="s">
+      <c r="F41" s="12" t="s">
         <v>476</v>
       </c>
-      <c r="G41" s="11" t="s">
+      <c r="G41" s="12" t="s">
         <v>477</v>
       </c>
-      <c r="H41" s="11" t="s">
+      <c r="H41" s="12" t="s">
         <v>478</v>
       </c>
-      <c r="I41" s="11" t="s">
+      <c r="I41" s="12" t="s">
         <v>477</v>
       </c>
-      <c r="J41" s="11" t="s">
+      <c r="J41" s="12" t="s">
         <v>479</v>
       </c>
-      <c r="K41" s="11" t="s">
+      <c r="K41" s="12" t="s">
         <v>480</v>
       </c>
-      <c r="L41" s="11" t="s">
+      <c r="L41" s="12" t="s">
         <v>481</v>
       </c>
-      <c r="M41" s="11" t="s">
+      <c r="M41" s="12" t="s">
         <v>482</v>
       </c>
-      <c r="N41" s="11" t="s">
+      <c r="N41" s="12" t="s">
         <v>483</v>
       </c>
-      <c r="O41" s="11" t="s">
+      <c r="O41" s="12" t="s">
         <v>484</v>
       </c>
       <c r="P41"/>
@@ -7052,226 +7986,226 @@
       <c r="W41"/>
     </row>
     <row r="42" customHeight="1" spans="2:23">
-      <c r="B42" s="10">
+      <c r="B42" s="11">
         <v>10037</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="13" t="s">
         <v>485</v>
       </c>
-      <c r="D42" s="11" t="s">
+      <c r="D42" s="12" t="s">
         <v>486</v>
       </c>
-      <c r="E42" s="11" t="s">
+      <c r="E42" s="12" t="s">
         <v>487</v>
       </c>
-      <c r="F42" s="11" t="s">
+      <c r="F42" s="12" t="s">
         <v>488</v>
       </c>
-      <c r="G42" s="11" t="s">
+      <c r="G42" s="12" t="s">
         <v>489</v>
       </c>
-      <c r="H42" s="11" t="s">
+      <c r="H42" s="12" t="s">
         <v>490</v>
       </c>
-      <c r="I42" s="11" t="s">
+      <c r="I42" s="12" t="s">
         <v>491</v>
       </c>
-      <c r="J42" s="11" t="s">
+      <c r="J42" s="12" t="s">
         <v>492</v>
       </c>
-      <c r="K42" s="11" t="s">
+      <c r="K42" s="12" t="s">
         <v>493</v>
       </c>
-      <c r="L42" s="11" t="s">
+      <c r="L42" s="12" t="s">
         <v>494</v>
       </c>
-      <c r="M42" s="11" t="s">
+      <c r="M42" s="12" t="s">
         <v>495</v>
       </c>
-      <c r="N42" s="11" t="s">
+      <c r="N42" s="12" t="s">
         <v>496</v>
       </c>
-      <c r="O42" s="11" t="s">
+      <c r="O42" s="12" t="s">
         <v>497</v>
       </c>
       <c r="P42" s="1"/>
     </row>
     <row r="43" customHeight="1" spans="2:23">
-      <c r="B43" s="10">
+      <c r="B43" s="11">
         <v>10038</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C43" s="12" t="s">
         <v>498</v>
       </c>
-      <c r="D43" s="11" t="s">
+      <c r="D43" s="12" t="s">
         <v>499</v>
       </c>
-      <c r="E43" s="11" t="s">
+      <c r="E43" s="12" t="s">
         <v>500</v>
       </c>
-      <c r="F43" s="11" t="s">
+      <c r="F43" s="12" t="s">
         <v>501</v>
       </c>
-      <c r="G43" s="11" t="s">
+      <c r="G43" s="12" t="s">
         <v>502</v>
       </c>
-      <c r="H43" s="11" t="s">
+      <c r="H43" s="12" t="s">
         <v>503</v>
       </c>
-      <c r="I43" s="11" t="s">
+      <c r="I43" s="12" t="s">
         <v>504</v>
       </c>
-      <c r="J43" s="11" t="s">
+      <c r="J43" s="12" t="s">
         <v>505</v>
       </c>
-      <c r="K43" s="11" t="s">
+      <c r="K43" s="12" t="s">
         <v>506</v>
       </c>
-      <c r="L43" s="11" t="s">
+      <c r="L43" s="12" t="s">
         <v>507</v>
       </c>
-      <c r="M43" s="11" t="s">
+      <c r="M43" s="12" t="s">
         <v>508</v>
       </c>
-      <c r="N43" s="11" t="s">
+      <c r="N43" s="12" t="s">
         <v>509</v>
       </c>
-      <c r="O43" s="11" t="s">
+      <c r="O43" s="12" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:23">
-      <c r="B44" s="10">
+      <c r="B44" s="11">
         <v>10039</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C44" s="12" t="s">
         <v>511</v>
       </c>
-      <c r="D44" s="11" t="s">
+      <c r="D44" s="12" t="s">
         <v>512</v>
       </c>
-      <c r="E44" s="11" t="s">
+      <c r="E44" s="12" t="s">
         <v>512</v>
       </c>
-      <c r="F44" s="11" t="s">
+      <c r="F44" s="12" t="s">
         <v>513</v>
       </c>
-      <c r="G44" s="11" t="s">
+      <c r="G44" s="12" t="s">
         <v>514</v>
       </c>
-      <c r="H44" s="11" t="s">
+      <c r="H44" s="12" t="s">
         <v>512</v>
       </c>
-      <c r="I44" s="11" t="s">
+      <c r="I44" s="12" t="s">
         <v>515</v>
       </c>
-      <c r="J44" s="11" t="s">
+      <c r="J44" s="12" t="s">
         <v>516</v>
       </c>
-      <c r="K44" s="11" t="s">
+      <c r="K44" s="12" t="s">
         <v>517</v>
       </c>
-      <c r="L44" s="11" t="s">
+      <c r="L44" s="12" t="s">
         <v>518</v>
       </c>
-      <c r="M44" s="11" t="s">
+      <c r="M44" s="12" t="s">
         <v>519</v>
       </c>
-      <c r="N44" s="11" t="s">
+      <c r="N44" s="12" t="s">
         <v>520</v>
       </c>
-      <c r="O44" s="11" t="s">
+      <c r="O44" s="12" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:23">
-      <c r="B45" s="10">
+      <c r="B45" s="11">
         <v>10040</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C45" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="D45" s="11" t="s">
+      <c r="D45" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="E45" s="11" t="s">
+      <c r="E45" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="F45" s="11" t="s">
+      <c r="F45" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="G45" s="11" t="s">
+      <c r="G45" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="H45" s="11" t="s">
+      <c r="H45" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="I45" s="11" t="s">
+      <c r="I45" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="J45" s="11" t="s">
+      <c r="J45" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="K45" s="11" t="s">
+      <c r="K45" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="L45" s="11" t="s">
+      <c r="L45" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="M45" s="11" t="s">
+      <c r="M45" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="N45" s="11" t="s">
+      <c r="N45" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="O45" s="11" t="s">
+      <c r="O45" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="P45" s="13" t="s">
+      <c r="P45" s="14" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:23">
-      <c r="B46" s="10">
+      <c r="B46" s="11">
         <v>10041</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C46" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="D46" s="11" t="s">
+      <c r="D46" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E46" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="F46" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="G46" s="11" t="s">
+      <c r="G46" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="H46" s="11" t="s">
+      <c r="H46" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="I46" s="11" t="s">
+      <c r="I46" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="J46" s="11" t="s">
+      <c r="J46" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="K46" s="11" t="s">
+      <c r="K46" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="L46" s="11" t="s">
+      <c r="L46" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="M46" s="11" t="s">
+      <c r="M46" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="N46" s="11" t="s">
+      <c r="N46" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="O46" s="11" t="s">
+      <c r="O46" s="12" t="s">
         <v>523</v>
       </c>
       <c r="P46" t="s">
@@ -7279,2165 +8213,2165 @@
       </c>
     </row>
     <row r="47" customHeight="1" spans="2:23">
-      <c r="B47" s="10">
+      <c r="B47" s="11">
         <v>10042</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="12" t="s">
         <v>524</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D47" s="13" t="s">
         <v>525</v>
       </c>
-      <c r="E47" s="11" t="s">
+      <c r="E47" s="12" t="s">
         <v>526</v>
       </c>
-      <c r="F47" s="11" t="s">
+      <c r="F47" s="12" t="s">
         <v>527</v>
       </c>
-      <c r="G47" s="11" t="s">
+      <c r="G47" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="H47" s="11" t="s">
+      <c r="H47" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="I47" s="11" t="s">
+      <c r="I47" s="12" t="s">
         <v>530</v>
       </c>
-      <c r="J47" s="11" t="s">
+      <c r="J47" s="12" t="s">
         <v>531</v>
       </c>
-      <c r="K47" s="11" t="s">
+      <c r="K47" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="L47" s="11" t="s">
+      <c r="L47" s="12" t="s">
         <v>533</v>
       </c>
-      <c r="M47" s="11" t="s">
+      <c r="M47" s="12" t="s">
         <v>534</v>
       </c>
-      <c r="N47" s="11" t="s">
+      <c r="N47" s="12" t="s">
         <v>535</v>
       </c>
-      <c r="O47" s="11" t="s">
+      <c r="O47" s="12" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="2:23">
-      <c r="B48" s="10">
+      <c r="B48" s="11">
         <v>10043</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C48" s="12" t="s">
         <v>537</v>
       </c>
-      <c r="D48" s="12" t="s">
+      <c r="D48" s="13" t="s">
         <v>538</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E48" s="12" t="s">
         <v>539</v>
       </c>
-      <c r="F48" s="11" t="s">
+      <c r="F48" s="12" t="s">
         <v>540</v>
       </c>
-      <c r="G48" s="11" t="s">
+      <c r="G48" s="12" t="s">
         <v>541</v>
       </c>
-      <c r="H48" s="11" t="s">
+      <c r="H48" s="12" t="s">
         <v>542</v>
       </c>
-      <c r="I48" s="11" t="s">
+      <c r="I48" s="12" t="s">
         <v>543</v>
       </c>
-      <c r="J48" s="11" t="s">
+      <c r="J48" s="12" t="s">
         <v>544</v>
       </c>
-      <c r="K48" s="11" t="s">
+      <c r="K48" s="12" t="s">
         <v>545</v>
       </c>
-      <c r="L48" s="11" t="s">
+      <c r="L48" s="12" t="s">
         <v>546</v>
       </c>
-      <c r="M48" s="11" t="s">
+      <c r="M48" s="12" t="s">
         <v>547</v>
       </c>
-      <c r="N48" s="11" t="s">
+      <c r="N48" s="12" t="s">
         <v>548</v>
       </c>
-      <c r="O48" s="11" t="s">
+      <c r="O48" s="12" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="2:16">
-      <c r="B49" s="10">
+      <c r="B49" s="11">
         <v>10044</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C49" s="12" t="s">
         <v>550</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="D49" s="13" t="s">
         <v>551</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="E49" s="12" t="s">
         <v>552</v>
       </c>
-      <c r="F49" s="11" t="s">
+      <c r="F49" s="12" t="s">
         <v>553</v>
       </c>
-      <c r="G49" s="11" t="s">
+      <c r="G49" s="12" t="s">
         <v>554</v>
       </c>
-      <c r="H49" s="11" t="s">
+      <c r="H49" s="12" t="s">
         <v>555</v>
       </c>
-      <c r="I49" s="11" t="s">
+      <c r="I49" s="12" t="s">
         <v>556</v>
       </c>
-      <c r="J49" s="11" t="s">
+      <c r="J49" s="12" t="s">
         <v>557</v>
       </c>
-      <c r="K49" s="11" t="s">
+      <c r="K49" s="12" t="s">
         <v>558</v>
       </c>
-      <c r="L49" s="11" t="s">
+      <c r="L49" s="12" t="s">
         <v>559</v>
       </c>
-      <c r="M49" s="11" t="s">
+      <c r="M49" s="12" t="s">
         <v>560</v>
       </c>
-      <c r="N49" s="11" t="s">
+      <c r="N49" s="12" t="s">
         <v>561</v>
       </c>
-      <c r="O49" s="11" t="s">
+      <c r="O49" s="12" t="s">
         <v>562</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="2:16">
-      <c r="B50" s="10">
+      <c r="B50" s="11">
         <v>10045</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C50" s="12" t="s">
         <v>563</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="13" t="s">
         <v>564</v>
       </c>
-      <c r="E50" s="11" t="s">
+      <c r="E50" s="12" t="s">
         <v>565</v>
       </c>
-      <c r="F50" s="11" t="s">
+      <c r="F50" s="12" t="s">
         <v>566</v>
       </c>
-      <c r="G50" s="11" t="s">
+      <c r="G50" s="12" t="s">
         <v>567</v>
       </c>
-      <c r="H50" s="11" t="s">
+      <c r="H50" s="12" t="s">
         <v>568</v>
       </c>
-      <c r="I50" s="11" t="s">
+      <c r="I50" s="12" t="s">
         <v>569</v>
       </c>
-      <c r="J50" s="11" t="s">
+      <c r="J50" s="12" t="s">
         <v>570</v>
       </c>
-      <c r="K50" s="11" t="s">
+      <c r="K50" s="12" t="s">
         <v>571</v>
       </c>
-      <c r="L50" s="11" t="s">
+      <c r="L50" s="12" t="s">
         <v>572</v>
       </c>
-      <c r="M50" s="11" t="s">
+      <c r="M50" s="12" t="s">
         <v>573</v>
       </c>
-      <c r="N50" s="11" t="s">
+      <c r="N50" s="12" t="s">
         <v>574</v>
       </c>
-      <c r="O50" s="11" t="s">
+      <c r="O50" s="12" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="2:16">
-      <c r="B51" s="10">
+      <c r="B51" s="11">
         <v>10046</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="12" t="s">
         <v>576</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="13" t="s">
         <v>577</v>
       </c>
-      <c r="E51" s="11" t="s">
+      <c r="E51" s="12" t="s">
         <v>578</v>
       </c>
-      <c r="F51" s="11" t="s">
+      <c r="F51" s="12" t="s">
         <v>579</v>
       </c>
-      <c r="G51" s="11" t="s">
+      <c r="G51" s="12" t="s">
         <v>580</v>
       </c>
-      <c r="H51" s="11" t="s">
+      <c r="H51" s="12" t="s">
         <v>581</v>
       </c>
-      <c r="I51" s="11" t="s">
+      <c r="I51" s="12" t="s">
         <v>582</v>
       </c>
-      <c r="J51" s="11" t="s">
+      <c r="J51" s="12" t="s">
         <v>583</v>
       </c>
-      <c r="K51" s="11" t="s">
+      <c r="K51" s="12" t="s">
         <v>584</v>
       </c>
-      <c r="L51" s="11" t="s">
+      <c r="L51" s="12" t="s">
         <v>585</v>
       </c>
-      <c r="M51" s="11" t="s">
+      <c r="M51" s="12" t="s">
         <v>586</v>
       </c>
-      <c r="N51" s="11" t="s">
+      <c r="N51" s="12" t="s">
         <v>587</v>
       </c>
-      <c r="O51" s="11" t="s">
+      <c r="O51" s="12" t="s">
         <v>588</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="2:16">
-      <c r="B52" s="10">
+      <c r="B52" s="11">
         <v>10047</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="C52" s="12" t="s">
         <v>589</v>
       </c>
-      <c r="D52" s="11" t="s">
+      <c r="D52" s="12" t="s">
         <v>590</v>
       </c>
-      <c r="E52" s="11" t="s">
+      <c r="E52" s="12" t="s">
         <v>591</v>
       </c>
-      <c r="F52" s="11" t="s">
+      <c r="F52" s="12" t="s">
         <v>592</v>
       </c>
-      <c r="G52" s="11" t="s">
+      <c r="G52" s="12" t="s">
         <v>593</v>
       </c>
-      <c r="H52" s="11" t="s">
+      <c r="H52" s="12" t="s">
         <v>594</v>
       </c>
-      <c r="I52" s="11" t="s">
+      <c r="I52" s="12" t="s">
         <v>595</v>
       </c>
-      <c r="J52" s="11" t="s">
+      <c r="J52" s="12" t="s">
         <v>596</v>
       </c>
-      <c r="K52" s="11" t="s">
+      <c r="K52" s="12" t="s">
         <v>597</v>
       </c>
-      <c r="L52" s="11" t="s">
+      <c r="L52" s="12" t="s">
         <v>598</v>
       </c>
-      <c r="M52" s="11" t="s">
+      <c r="M52" s="12" t="s">
         <v>599</v>
       </c>
-      <c r="N52" s="11" t="s">
+      <c r="N52" s="12" t="s">
         <v>600</v>
       </c>
-      <c r="O52" s="11" t="s">
+      <c r="O52" s="12" t="s">
         <v>601</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="2:16">
-      <c r="B53" s="10">
+      <c r="B53" s="11">
         <v>10048</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="C53" s="12" t="s">
         <v>602</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D53" s="12" t="s">
         <v>603</v>
       </c>
-      <c r="E53" s="11" t="s">
+      <c r="E53" s="12" t="s">
         <v>604</v>
       </c>
-      <c r="F53" s="11" t="s">
+      <c r="F53" s="12" t="s">
         <v>605</v>
       </c>
-      <c r="G53" s="11" t="s">
+      <c r="G53" s="12" t="s">
         <v>606</v>
       </c>
-      <c r="H53" s="11" t="s">
+      <c r="H53" s="12" t="s">
         <v>607</v>
       </c>
-      <c r="I53" s="11" t="s">
+      <c r="I53" s="12" t="s">
         <v>608</v>
       </c>
-      <c r="J53" s="11" t="s">
+      <c r="J53" s="12" t="s">
         <v>609</v>
       </c>
-      <c r="K53" s="11" t="s">
+      <c r="K53" s="12" t="s">
         <v>610</v>
       </c>
-      <c r="L53" s="11" t="s">
+      <c r="L53" s="12" t="s">
         <v>611</v>
       </c>
-      <c r="M53" s="11" t="s">
+      <c r="M53" s="12" t="s">
         <v>612</v>
       </c>
-      <c r="N53" s="11" t="s">
+      <c r="N53" s="12" t="s">
         <v>613</v>
       </c>
-      <c r="O53" s="11" t="s">
+      <c r="O53" s="12" t="s">
         <v>614</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="2:16">
-      <c r="B54" s="10">
+      <c r="B54" s="11">
         <v>10049</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="C54" s="12" t="s">
         <v>615</v>
       </c>
-      <c r="D54" s="11" t="s">
+      <c r="D54" s="12" t="s">
         <v>616</v>
       </c>
-      <c r="E54" s="11" t="s">
+      <c r="E54" s="12" t="s">
         <v>617</v>
       </c>
-      <c r="F54" s="11" t="s">
+      <c r="F54" s="12" t="s">
         <v>618</v>
       </c>
-      <c r="G54" s="11" t="s">
+      <c r="G54" s="12" t="s">
         <v>619</v>
       </c>
-      <c r="H54" s="11" t="s">
+      <c r="H54" s="12" t="s">
         <v>620</v>
       </c>
-      <c r="I54" s="11" t="s">
+      <c r="I54" s="12" t="s">
         <v>621</v>
       </c>
-      <c r="J54" s="11" t="s">
+      <c r="J54" s="12" t="s">
         <v>622</v>
       </c>
-      <c r="K54" s="11" t="s">
+      <c r="K54" s="12" t="s">
         <v>623</v>
       </c>
-      <c r="L54" s="11" t="s">
+      <c r="L54" s="12" t="s">
         <v>624</v>
       </c>
-      <c r="M54" s="11" t="s">
+      <c r="M54" s="12" t="s">
         <v>625</v>
       </c>
-      <c r="N54" s="11" t="s">
+      <c r="N54" s="12" t="s">
         <v>626</v>
       </c>
-      <c r="O54" s="11" t="s">
+      <c r="O54" s="12" t="s">
         <v>627</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="2:16">
-      <c r="B55" s="10">
+      <c r="B55" s="11">
         <v>10050</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C55" s="12" t="s">
         <v>628</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D55" s="12" t="s">
         <v>629</v>
       </c>
-      <c r="E55" s="11" t="s">
+      <c r="E55" s="12" t="s">
         <v>630</v>
       </c>
-      <c r="F55" s="11" t="s">
+      <c r="F55" s="12" t="s">
         <v>631</v>
       </c>
-      <c r="G55" s="11" t="s">
+      <c r="G55" s="12" t="s">
         <v>632</v>
       </c>
-      <c r="H55" s="11" t="s">
+      <c r="H55" s="12" t="s">
         <v>633</v>
       </c>
-      <c r="I55" s="11" t="s">
+      <c r="I55" s="12" t="s">
         <v>634</v>
       </c>
-      <c r="J55" s="11" t="s">
+      <c r="J55" s="12" t="s">
         <v>635</v>
       </c>
-      <c r="K55" s="11" t="s">
+      <c r="K55" s="12" t="s">
         <v>636</v>
       </c>
-      <c r="L55" s="11" t="s">
+      <c r="L55" s="12" t="s">
         <v>637</v>
       </c>
-      <c r="M55" s="11" t="s">
+      <c r="M55" s="12" t="s">
         <v>638</v>
       </c>
-      <c r="N55" s="11" t="s">
+      <c r="N55" s="12" t="s">
         <v>639</v>
       </c>
-      <c r="O55" s="11" t="s">
+      <c r="O55" s="12" t="s">
         <v>640</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" ht="19" customHeight="1" spans="2:16">
-      <c r="B56" s="10">
+      <c r="B56" s="11">
         <v>10051</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C56" s="12" t="s">
         <v>641</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D56" s="12" t="s">
         <v>642</v>
       </c>
-      <c r="E56" s="11" t="s">
+      <c r="E56" s="12" t="s">
         <v>643</v>
       </c>
-      <c r="F56" s="11" t="s">
+      <c r="F56" s="12" t="s">
         <v>644</v>
       </c>
-      <c r="G56" s="11" t="s">
+      <c r="G56" s="12" t="s">
         <v>645</v>
       </c>
-      <c r="H56" s="11" t="s">
+      <c r="H56" s="12" t="s">
         <v>646</v>
       </c>
-      <c r="I56" s="11" t="s">
+      <c r="I56" s="12" t="s">
         <v>647</v>
       </c>
-      <c r="J56" s="11" t="s">
+      <c r="J56" s="12" t="s">
         <v>648</v>
       </c>
-      <c r="K56" s="11" t="s">
+      <c r="K56" s="12" t="s">
         <v>649</v>
       </c>
-      <c r="L56" s="11" t="s">
+      <c r="L56" s="12" t="s">
         <v>650</v>
       </c>
-      <c r="M56" s="11" t="s">
+      <c r="M56" s="12" t="s">
         <v>651</v>
       </c>
-      <c r="N56" s="11" t="s">
+      <c r="N56" s="12" t="s">
         <v>652</v>
       </c>
-      <c r="O56" s="11" t="s">
+      <c r="O56" s="12" t="s">
         <v>653</v>
       </c>
       <c r="P56"/>
     </row>
     <row r="57" customHeight="1" spans="2:16">
-      <c r="B57" s="10">
+      <c r="B57" s="11">
         <v>10052</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C57" s="12" t="s">
         <v>654</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="D57" s="13" t="s">
         <v>655</v>
       </c>
-      <c r="E57" s="11" t="s">
+      <c r="E57" s="12" t="s">
         <v>656</v>
       </c>
-      <c r="F57" s="11" t="s">
+      <c r="F57" s="12" t="s">
         <v>657</v>
       </c>
-      <c r="G57" s="11" t="s">
+      <c r="G57" s="12" t="s">
         <v>658</v>
       </c>
-      <c r="H57" s="11" t="s">
+      <c r="H57" s="12" t="s">
         <v>659</v>
       </c>
-      <c r="I57" s="11" t="s">
+      <c r="I57" s="12" t="s">
         <v>660</v>
       </c>
-      <c r="J57" s="11" t="s">
+      <c r="J57" s="12" t="s">
         <v>661</v>
       </c>
-      <c r="K57" s="11" t="s">
+      <c r="K57" s="12" t="s">
         <v>662</v>
       </c>
-      <c r="L57" s="11" t="s">
+      <c r="L57" s="12" t="s">
         <v>663</v>
       </c>
-      <c r="M57" s="11" t="s">
+      <c r="M57" s="12" t="s">
         <v>664</v>
       </c>
-      <c r="N57" s="11" t="s">
+      <c r="N57" s="12" t="s">
         <v>665</v>
       </c>
-      <c r="O57" s="11" t="s">
+      <c r="O57" s="12" t="s">
         <v>666</v>
       </c>
       <c r="P57" s="1"/>
     </row>
     <row r="58" customHeight="1" spans="2:16">
-      <c r="B58" s="10">
+      <c r="B58" s="11">
         <v>10053</v>
       </c>
-      <c r="C58" s="11" t="s">
+      <c r="C58" s="12" t="s">
         <v>667</v>
       </c>
-      <c r="D58" s="12" t="s">
+      <c r="D58" s="13" t="s">
         <v>668</v>
       </c>
-      <c r="E58" s="11" t="s">
+      <c r="E58" s="12" t="s">
         <v>669</v>
       </c>
-      <c r="F58" s="11" t="s">
+      <c r="F58" s="12" t="s">
         <v>670</v>
       </c>
-      <c r="G58" s="11" t="s">
+      <c r="G58" s="12" t="s">
         <v>671</v>
       </c>
-      <c r="H58" s="11" t="s">
+      <c r="H58" s="12" t="s">
         <v>672</v>
       </c>
-      <c r="I58" s="11" t="s">
+      <c r="I58" s="12" t="s">
         <v>673</v>
       </c>
-      <c r="J58" s="11" t="s">
+      <c r="J58" s="12" t="s">
         <v>674</v>
       </c>
-      <c r="K58" s="11" t="s">
+      <c r="K58" s="12" t="s">
         <v>675</v>
       </c>
-      <c r="L58" s="11" t="s">
+      <c r="L58" s="12" t="s">
         <v>676</v>
       </c>
-      <c r="M58" s="11" t="s">
+      <c r="M58" s="12" t="s">
         <v>677</v>
       </c>
-      <c r="N58" s="11" t="s">
+      <c r="N58" s="12" t="s">
         <v>678</v>
       </c>
-      <c r="O58" s="11" t="s">
+      <c r="O58" s="12" t="s">
         <v>679</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:16">
-      <c r="B59" s="10">
+      <c r="B59" s="11">
         <v>10054</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C59" s="12" t="s">
         <v>680</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="D59" s="13" t="s">
         <v>681</v>
       </c>
-      <c r="E59" s="11" t="s">
+      <c r="E59" s="12" t="s">
         <v>682</v>
       </c>
-      <c r="F59" s="11" t="s">
+      <c r="F59" s="12" t="s">
         <v>683</v>
       </c>
-      <c r="G59" s="11" t="s">
+      <c r="G59" s="12" t="s">
         <v>684</v>
       </c>
-      <c r="H59" s="11" t="s">
+      <c r="H59" s="12" t="s">
         <v>685</v>
       </c>
-      <c r="I59" s="11" t="s">
+      <c r="I59" s="12" t="s">
         <v>686</v>
       </c>
-      <c r="J59" s="11" t="s">
+      <c r="J59" s="12" t="s">
         <v>687</v>
       </c>
-      <c r="K59" s="11" t="s">
+      <c r="K59" s="12" t="s">
         <v>688</v>
       </c>
-      <c r="L59" s="11" t="s">
+      <c r="L59" s="12" t="s">
         <v>689</v>
       </c>
-      <c r="M59" s="11" t="s">
+      <c r="M59" s="12" t="s">
         <v>690</v>
       </c>
-      <c r="N59" s="11" t="s">
+      <c r="N59" s="12" t="s">
         <v>691</v>
       </c>
-      <c r="O59" s="11" t="s">
+      <c r="O59" s="12" t="s">
         <v>692</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:16">
-      <c r="B60" s="10">
+      <c r="B60" s="11">
         <v>10055</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="C60" s="13" t="s">
         <v>693</v>
       </c>
-      <c r="D60" s="11" t="s">
+      <c r="D60" s="12" t="s">
         <v>694</v>
       </c>
-      <c r="E60" s="11" t="s">
+      <c r="E60" s="12" t="s">
         <v>695</v>
       </c>
-      <c r="F60" s="11" t="s">
+      <c r="F60" s="12" t="s">
         <v>696</v>
       </c>
-      <c r="G60" s="11" t="s">
+      <c r="G60" s="12" t="s">
         <v>697</v>
       </c>
-      <c r="H60" s="11" t="s">
+      <c r="H60" s="12" t="s">
         <v>698</v>
       </c>
-      <c r="I60" s="11" t="s">
+      <c r="I60" s="12" t="s">
         <v>699</v>
       </c>
-      <c r="J60" s="11" t="s">
+      <c r="J60" s="12" t="s">
         <v>700</v>
       </c>
-      <c r="K60" s="11" t="s">
+      <c r="K60" s="12" t="s">
         <v>701</v>
       </c>
-      <c r="L60" s="11" t="s">
+      <c r="L60" s="12" t="s">
         <v>702</v>
       </c>
-      <c r="M60" s="11" t="s">
+      <c r="M60" s="12" t="s">
         <v>703</v>
       </c>
-      <c r="N60" s="11" t="s">
+      <c r="N60" s="12" t="s">
         <v>704</v>
       </c>
-      <c r="O60" s="11" t="s">
+      <c r="O60" s="12" t="s">
         <v>705</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:16">
-      <c r="B61" s="10">
+      <c r="B61" s="11">
         <v>10056</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C61" s="12" t="s">
         <v>706</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="D61" s="13" t="s">
         <v>707</v>
       </c>
-      <c r="E61" s="11" t="s">
+      <c r="E61" s="12" t="s">
         <v>708</v>
       </c>
-      <c r="F61" s="11" t="s">
+      <c r="F61" s="12" t="s">
         <v>709</v>
       </c>
-      <c r="G61" s="11" t="s">
+      <c r="G61" s="12" t="s">
         <v>710</v>
       </c>
-      <c r="H61" s="11" t="s">
+      <c r="H61" s="12" t="s">
         <v>711</v>
       </c>
-      <c r="I61" s="11" t="s">
+      <c r="I61" s="12" t="s">
         <v>712</v>
       </c>
-      <c r="J61" s="11" t="s">
+      <c r="J61" s="12" t="s">
         <v>713</v>
       </c>
-      <c r="K61" s="11" t="s">
+      <c r="K61" s="12" t="s">
         <v>714</v>
       </c>
-      <c r="L61" s="11" t="s">
+      <c r="L61" s="12" t="s">
         <v>715</v>
       </c>
-      <c r="M61" s="11" t="s">
+      <c r="M61" s="12" t="s">
         <v>716</v>
       </c>
-      <c r="N61" s="11" t="s">
+      <c r="N61" s="12" t="s">
         <v>717</v>
       </c>
-      <c r="O61" s="11" t="s">
+      <c r="O61" s="12" t="s">
         <v>718</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:16">
-      <c r="B62" s="10">
+      <c r="B62" s="11">
         <v>10057</v>
       </c>
-      <c r="C62" s="11" t="s">
+      <c r="C62" s="12" t="s">
         <v>719</v>
       </c>
-      <c r="D62" s="11" t="s">
+      <c r="D62" s="12" t="s">
         <v>720</v>
       </c>
-      <c r="E62" s="11" t="s">
+      <c r="E62" s="12" t="s">
         <v>721</v>
       </c>
-      <c r="F62" s="11" t="s">
+      <c r="F62" s="12" t="s">
         <v>722</v>
       </c>
-      <c r="G62" s="11" t="s">
+      <c r="G62" s="12" t="s">
         <v>723</v>
       </c>
-      <c r="H62" s="11" t="s">
+      <c r="H62" s="12" t="s">
         <v>724</v>
       </c>
-      <c r="I62" s="11" t="s">
+      <c r="I62" s="12" t="s">
         <v>725</v>
       </c>
-      <c r="J62" s="11" t="s">
+      <c r="J62" s="12" t="s">
         <v>726</v>
       </c>
-      <c r="K62" s="11" t="s">
+      <c r="K62" s="12" t="s">
         <v>727</v>
       </c>
-      <c r="L62" s="11" t="s">
+      <c r="L62" s="12" t="s">
         <v>728</v>
       </c>
-      <c r="M62" s="11" t="s">
+      <c r="M62" s="12" t="s">
         <v>729</v>
       </c>
-      <c r="N62" s="11" t="s">
+      <c r="N62" s="12" t="s">
         <v>730</v>
       </c>
-      <c r="O62" s="11" t="s">
+      <c r="O62" s="12" t="s">
         <v>731</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:16">
-      <c r="B63" s="10">
+      <c r="B63" s="11">
         <v>10058</v>
       </c>
-      <c r="C63" s="11" t="s">
+      <c r="C63" s="12" t="s">
         <v>732</v>
       </c>
-      <c r="D63" s="11" t="s">
+      <c r="D63" s="12" t="s">
         <v>733</v>
       </c>
-      <c r="E63" s="11" t="s">
+      <c r="E63" s="12" t="s">
         <v>734</v>
       </c>
-      <c r="F63" s="11" t="s">
+      <c r="F63" s="12" t="s">
         <v>735</v>
       </c>
-      <c r="G63" s="11" t="s">
+      <c r="G63" s="12" t="s">
         <v>736</v>
       </c>
-      <c r="H63" s="11" t="s">
+      <c r="H63" s="12" t="s">
         <v>737</v>
       </c>
-      <c r="I63" s="11" t="s">
+      <c r="I63" s="12" t="s">
         <v>738</v>
       </c>
-      <c r="J63" s="11" t="s">
+      <c r="J63" s="12" t="s">
         <v>739</v>
       </c>
-      <c r="K63" s="11" t="s">
+      <c r="K63" s="12" t="s">
         <v>740</v>
       </c>
-      <c r="L63" s="11" t="s">
+      <c r="L63" s="12" t="s">
         <v>741</v>
       </c>
-      <c r="M63" s="11" t="s">
+      <c r="M63" s="12" t="s">
         <v>742</v>
       </c>
-      <c r="N63" s="11" t="s">
+      <c r="N63" s="12" t="s">
         <v>743</v>
       </c>
-      <c r="O63" s="11" t="s">
+      <c r="O63" s="12" t="s">
         <v>744</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:16">
-      <c r="B64" s="10">
+      <c r="B64" s="11">
         <v>10059</v>
       </c>
-      <c r="C64" s="11" t="s">
+      <c r="C64" s="12" t="s">
         <v>745</v>
       </c>
-      <c r="D64" s="11" t="s">
+      <c r="D64" s="12" t="s">
         <v>746</v>
       </c>
-      <c r="E64" s="11" t="s">
+      <c r="E64" s="12" t="s">
         <v>747</v>
       </c>
-      <c r="F64" s="11" t="s">
+      <c r="F64" s="12" t="s">
         <v>748</v>
       </c>
-      <c r="G64" s="11" t="s">
+      <c r="G64" s="12" t="s">
         <v>749</v>
       </c>
-      <c r="H64" s="11" t="s">
+      <c r="H64" s="12" t="s">
         <v>750</v>
       </c>
-      <c r="I64" s="11" t="s">
+      <c r="I64" s="12" t="s">
         <v>751</v>
       </c>
-      <c r="J64" s="11" t="s">
+      <c r="J64" s="12" t="s">
         <v>752</v>
       </c>
-      <c r="K64" s="11" t="s">
+      <c r="K64" s="12" t="s">
         <v>753</v>
       </c>
-      <c r="L64" s="11" t="s">
+      <c r="L64" s="12" t="s">
         <v>754</v>
       </c>
-      <c r="M64" s="11" t="s">
+      <c r="M64" s="12" t="s">
         <v>755</v>
       </c>
-      <c r="N64" s="11" t="s">
+      <c r="N64" s="12" t="s">
         <v>756</v>
       </c>
-      <c r="O64" s="11" t="s">
+      <c r="O64" s="12" t="s">
         <v>757</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="2:15">
-      <c r="B65" s="10">
+      <c r="B65" s="11">
         <v>10060</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="C65" s="12" t="s">
         <v>758</v>
       </c>
-      <c r="D65" s="11" t="s">
+      <c r="D65" s="12" t="s">
         <v>759</v>
       </c>
-      <c r="E65" s="11" t="s">
+      <c r="E65" s="12" t="s">
         <v>760</v>
       </c>
-      <c r="F65" s="11" t="s">
+      <c r="F65" s="12" t="s">
         <v>761</v>
       </c>
-      <c r="G65" s="11" t="s">
+      <c r="G65" s="12" t="s">
         <v>762</v>
       </c>
-      <c r="H65" s="11" t="s">
+      <c r="H65" s="12" t="s">
         <v>763</v>
       </c>
-      <c r="I65" s="11" t="s">
+      <c r="I65" s="12" t="s">
         <v>764</v>
       </c>
-      <c r="J65" s="11" t="s">
+      <c r="J65" s="12" t="s">
         <v>765</v>
       </c>
-      <c r="K65" s="11" t="s">
+      <c r="K65" s="12" t="s">
         <v>766</v>
       </c>
-      <c r="L65" s="11" t="s">
+      <c r="L65" s="12" t="s">
         <v>767</v>
       </c>
-      <c r="M65" s="11" t="s">
+      <c r="M65" s="12" t="s">
         <v>768</v>
       </c>
-      <c r="N65" s="11" t="s">
+      <c r="N65" s="12" t="s">
         <v>769</v>
       </c>
-      <c r="O65" s="11" t="s">
+      <c r="O65" s="12" t="s">
         <v>770</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="2:15">
-      <c r="B66" s="10">
+      <c r="B66" s="11">
         <v>10061</v>
       </c>
-      <c r="C66" s="11" t="s">
+      <c r="C66" s="12" t="s">
         <v>771</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="D66" s="12" t="s">
         <v>772</v>
       </c>
-      <c r="E66" s="11" t="s">
+      <c r="E66" s="12" t="s">
         <v>773</v>
       </c>
-      <c r="F66" s="11" t="s">
+      <c r="F66" s="12" t="s">
         <v>774</v>
       </c>
-      <c r="G66" s="11" t="s">
+      <c r="G66" s="12" t="s">
         <v>775</v>
       </c>
-      <c r="H66" s="11" t="s">
+      <c r="H66" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="I66" s="11" t="s">
+      <c r="I66" s="12" t="s">
         <v>777</v>
       </c>
-      <c r="J66" s="11" t="s">
+      <c r="J66" s="12" t="s">
         <v>778</v>
       </c>
-      <c r="K66" s="11" t="s">
+      <c r="K66" s="12" t="s">
         <v>779</v>
       </c>
-      <c r="L66" s="11" t="s">
+      <c r="L66" s="12" t="s">
         <v>780</v>
       </c>
-      <c r="M66" s="11" t="s">
+      <c r="M66" s="12" t="s">
         <v>781</v>
       </c>
-      <c r="N66" s="11" t="s">
+      <c r="N66" s="12" t="s">
         <v>782</v>
       </c>
-      <c r="O66" s="11" t="s">
+      <c r="O66" s="12" t="s">
         <v>783</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="2:15">
-      <c r="B67" s="10">
+      <c r="B67" s="11">
         <v>10062</v>
       </c>
-      <c r="C67" s="11" t="s">
+      <c r="C67" s="12" t="s">
         <v>784</v>
       </c>
-      <c r="D67" s="11" t="s">
+      <c r="D67" s="12" t="s">
         <v>785</v>
       </c>
-      <c r="E67" s="11" t="s">
+      <c r="E67" s="12" t="s">
         <v>786</v>
       </c>
-      <c r="F67" s="11" t="s">
+      <c r="F67" s="12" t="s">
         <v>787</v>
       </c>
-      <c r="G67" s="11" t="s">
+      <c r="G67" s="12" t="s">
         <v>788</v>
       </c>
-      <c r="H67" s="11" t="s">
+      <c r="H67" s="12" t="s">
         <v>789</v>
       </c>
-      <c r="I67" s="11" t="s">
+      <c r="I67" s="12" t="s">
         <v>790</v>
       </c>
-      <c r="J67" s="11" t="s">
+      <c r="J67" s="12" t="s">
         <v>791</v>
       </c>
-      <c r="K67" s="11" t="s">
+      <c r="K67" s="12" t="s">
         <v>792</v>
       </c>
-      <c r="L67" s="11" t="s">
+      <c r="L67" s="12" t="s">
         <v>793</v>
       </c>
-      <c r="M67" s="11" t="s">
+      <c r="M67" s="12" t="s">
         <v>794</v>
       </c>
-      <c r="N67" s="11" t="s">
+      <c r="N67" s="12" t="s">
         <v>795</v>
       </c>
-      <c r="O67" s="11" t="s">
+      <c r="O67" s="12" t="s">
         <v>796</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="2:15">
-      <c r="B68" s="10">
+      <c r="B68" s="11">
         <v>10063</v>
       </c>
-      <c r="C68" s="11" t="s">
+      <c r="C68" s="12" t="s">
         <v>797</v>
       </c>
-      <c r="D68" s="12" t="s">
+      <c r="D68" s="13" t="s">
         <v>798</v>
       </c>
-      <c r="E68" s="11" t="s">
+      <c r="E68" s="12" t="s">
         <v>798</v>
       </c>
-      <c r="F68" s="11" t="s">
+      <c r="F68" s="12" t="s">
         <v>799</v>
       </c>
-      <c r="G68" s="11" t="s">
+      <c r="G68" s="12" t="s">
         <v>798</v>
       </c>
-      <c r="H68" s="11" t="s">
+      <c r="H68" s="12" t="s">
         <v>800</v>
       </c>
-      <c r="I68" s="11" t="s">
+      <c r="I68" s="12" t="s">
         <v>801</v>
       </c>
-      <c r="J68" s="11" t="s">
+      <c r="J68" s="12" t="s">
         <v>802</v>
       </c>
-      <c r="K68" s="11" t="s">
+      <c r="K68" s="12" t="s">
         <v>803</v>
       </c>
-      <c r="L68" s="11" t="s">
+      <c r="L68" s="12" t="s">
         <v>804</v>
       </c>
-      <c r="M68" s="11" t="s">
+      <c r="M68" s="12" t="s">
         <v>805</v>
       </c>
-      <c r="N68" s="11" t="s">
+      <c r="N68" s="12" t="s">
         <v>806</v>
       </c>
-      <c r="O68" s="11" t="s">
+      <c r="O68" s="12" t="s">
         <v>807</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="2:15">
-      <c r="B69" s="10">
+      <c r="B69" s="11">
         <v>10064</v>
       </c>
-      <c r="C69" s="11" t="s">
+      <c r="C69" s="12" t="s">
         <v>808</v>
       </c>
-      <c r="D69" s="11" t="s">
+      <c r="D69" s="12" t="s">
         <v>809</v>
       </c>
-      <c r="E69" s="11" t="s">
+      <c r="E69" s="12" t="s">
         <v>810</v>
       </c>
-      <c r="F69" s="11" t="s">
+      <c r="F69" s="12" t="s">
         <v>811</v>
       </c>
-      <c r="G69" s="11" t="s">
+      <c r="G69" s="12" t="s">
         <v>812</v>
       </c>
-      <c r="H69" s="11" t="s">
+      <c r="H69" s="12" t="s">
         <v>813</v>
       </c>
-      <c r="I69" s="11" t="s">
+      <c r="I69" s="12" t="s">
         <v>814</v>
       </c>
-      <c r="J69" s="11" t="s">
+      <c r="J69" s="12" t="s">
         <v>815</v>
       </c>
-      <c r="K69" s="11" t="s">
+      <c r="K69" s="12" t="s">
         <v>816</v>
       </c>
-      <c r="L69" s="11" t="s">
+      <c r="L69" s="12" t="s">
         <v>817</v>
       </c>
-      <c r="M69" s="11" t="s">
+      <c r="M69" s="12" t="s">
         <v>818</v>
       </c>
-      <c r="N69" s="11" t="s">
+      <c r="N69" s="12" t="s">
         <v>819</v>
       </c>
-      <c r="O69" s="11" t="s">
+      <c r="O69" s="12" t="s">
         <v>820</v>
       </c>
     </row>
     <row r="70" ht="19" customHeight="1" spans="2:15">
-      <c r="B70" s="10">
+      <c r="B70" s="11">
         <v>10065</v>
       </c>
-      <c r="C70" s="11" t="s">
+      <c r="C70" s="12" t="s">
         <v>821</v>
       </c>
-      <c r="D70" s="11" t="s">
+      <c r="D70" s="12" t="s">
         <v>822</v>
       </c>
-      <c r="E70" s="11" t="s">
+      <c r="E70" s="12" t="s">
         <v>823</v>
       </c>
-      <c r="F70" s="11" t="s">
+      <c r="F70" s="12" t="s">
         <v>824</v>
       </c>
-      <c r="G70" s="11" t="s">
+      <c r="G70" s="12" t="s">
         <v>825</v>
       </c>
-      <c r="H70" s="11" t="s">
+      <c r="H70" s="12" t="s">
         <v>826</v>
       </c>
-      <c r="I70" s="11" t="s">
+      <c r="I70" s="12" t="s">
         <v>825</v>
       </c>
-      <c r="J70" s="11" t="s">
+      <c r="J70" s="12" t="s">
         <v>827</v>
       </c>
-      <c r="K70" s="11" t="s">
+      <c r="K70" s="12" t="s">
         <v>828</v>
       </c>
-      <c r="L70" s="11" t="s">
+      <c r="L70" s="12" t="s">
         <v>829</v>
       </c>
-      <c r="M70" s="11" t="s">
+      <c r="M70" s="12" t="s">
         <v>830</v>
       </c>
-      <c r="N70" s="11" t="s">
+      <c r="N70" s="12" t="s">
         <v>831</v>
       </c>
-      <c r="O70" s="11" t="s">
+      <c r="O70" s="12" t="s">
         <v>832</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="2:15">
-      <c r="B71" s="10">
+      <c r="B71" s="11">
         <v>10066</v>
       </c>
-      <c r="C71" s="11" t="s">
+      <c r="C71" s="12" t="s">
         <v>833</v>
       </c>
-      <c r="D71" s="12" t="s">
+      <c r="D71" s="13" t="s">
         <v>834</v>
       </c>
-      <c r="E71" s="11" t="s">
+      <c r="E71" s="12" t="s">
         <v>835</v>
       </c>
-      <c r="F71" s="11" t="s">
+      <c r="F71" s="12" t="s">
         <v>836</v>
       </c>
-      <c r="G71" s="11" t="s">
+      <c r="G71" s="12" t="s">
         <v>837</v>
       </c>
-      <c r="H71" s="11" t="s">
+      <c r="H71" s="12" t="s">
         <v>838</v>
       </c>
-      <c r="I71" s="11" t="s">
+      <c r="I71" s="12" t="s">
         <v>837</v>
       </c>
-      <c r="J71" s="11" t="s">
+      <c r="J71" s="12" t="s">
         <v>839</v>
       </c>
-      <c r="K71" s="11" t="s">
+      <c r="K71" s="12" t="s">
         <v>840</v>
       </c>
-      <c r="L71" s="11" t="s">
+      <c r="L71" s="12" t="s">
         <v>841</v>
       </c>
-      <c r="M71" s="11" t="s">
+      <c r="M71" s="12" t="s">
         <v>842</v>
       </c>
-      <c r="N71" s="11" t="s">
+      <c r="N71" s="12" t="s">
         <v>843</v>
       </c>
-      <c r="O71" s="11" t="s">
+      <c r="O71" s="12" t="s">
         <v>844</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="2:15">
-      <c r="B72" s="10">
+      <c r="B72" s="11">
         <v>10067</v>
       </c>
-      <c r="C72" s="11" t="s">
+      <c r="C72" s="12" t="s">
         <v>845</v>
       </c>
-      <c r="D72" s="12" t="s">
+      <c r="D72" s="13" t="s">
         <v>846</v>
       </c>
-      <c r="E72" s="11" t="s">
+      <c r="E72" s="12" t="s">
         <v>847</v>
       </c>
-      <c r="F72" s="11" t="s">
+      <c r="F72" s="12" t="s">
         <v>848</v>
       </c>
-      <c r="G72" s="11" t="s">
+      <c r="G72" s="12" t="s">
         <v>849</v>
       </c>
-      <c r="H72" s="11" t="s">
+      <c r="H72" s="12" t="s">
         <v>850</v>
       </c>
-      <c r="I72" s="11" t="s">
+      <c r="I72" s="12" t="s">
         <v>849</v>
       </c>
-      <c r="J72" s="11" t="s">
+      <c r="J72" s="12" t="s">
         <v>851</v>
       </c>
-      <c r="K72" s="11" t="s">
+      <c r="K72" s="12" t="s">
         <v>849</v>
       </c>
-      <c r="L72" s="11" t="s">
+      <c r="L72" s="12" t="s">
         <v>852</v>
       </c>
-      <c r="M72" s="11" t="s">
+      <c r="M72" s="12" t="s">
         <v>853</v>
       </c>
-      <c r="N72" s="11" t="s">
+      <c r="N72" s="12" t="s">
         <v>854</v>
       </c>
-      <c r="O72" s="11" t="s">
+      <c r="O72" s="12" t="s">
         <v>855</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="2:15">
-      <c r="B73" s="10">
+      <c r="B73" s="11">
         <v>10068</v>
       </c>
-      <c r="C73" s="11" t="s">
+      <c r="C73" s="12" t="s">
         <v>856</v>
       </c>
-      <c r="D73" s="12" t="s">
+      <c r="D73" s="13" t="s">
         <v>857</v>
       </c>
-      <c r="E73" s="11" t="s">
+      <c r="E73" s="12" t="s">
         <v>858</v>
       </c>
-      <c r="F73" s="11" t="s">
+      <c r="F73" s="12" t="s">
         <v>859</v>
       </c>
-      <c r="G73" s="11" t="s">
+      <c r="G73" s="12" t="s">
         <v>860</v>
       </c>
-      <c r="H73" s="11" t="s">
+      <c r="H73" s="12" t="s">
         <v>861</v>
       </c>
-      <c r="I73" s="11" t="s">
+      <c r="I73" s="12" t="s">
         <v>862</v>
       </c>
-      <c r="J73" s="11" t="s">
+      <c r="J73" s="12" t="s">
         <v>863</v>
       </c>
-      <c r="K73" s="11" t="s">
+      <c r="K73" s="12" t="s">
         <v>864</v>
       </c>
-      <c r="L73" s="11" t="s">
+      <c r="L73" s="12" t="s">
         <v>865</v>
       </c>
-      <c r="M73" s="11" t="s">
+      <c r="M73" s="12" t="s">
         <v>866</v>
       </c>
-      <c r="N73" s="11" t="s">
+      <c r="N73" s="12" t="s">
         <v>867</v>
       </c>
-      <c r="O73" s="11" t="s">
+      <c r="O73" s="12" t="s">
         <v>868</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="2:15">
-      <c r="B74" s="10">
+      <c r="B74" s="11">
         <v>10069</v>
       </c>
-      <c r="C74" s="11" t="s">
+      <c r="C74" s="12" t="s">
         <v>869</v>
       </c>
-      <c r="D74" s="12" t="s">
+      <c r="D74" s="13" t="s">
         <v>870</v>
       </c>
-      <c r="E74" s="11" t="s">
+      <c r="E74" s="12" t="s">
         <v>871</v>
       </c>
-      <c r="F74" s="11" t="s">
+      <c r="F74" s="12" t="s">
         <v>872</v>
       </c>
-      <c r="G74" s="11" t="s">
+      <c r="G74" s="12" t="s">
         <v>873</v>
       </c>
-      <c r="H74" s="11" t="s">
+      <c r="H74" s="12" t="s">
         <v>874</v>
       </c>
-      <c r="I74" s="11" t="s">
+      <c r="I74" s="12" t="s">
         <v>875</v>
       </c>
-      <c r="J74" s="11" t="s">
+      <c r="J74" s="12" t="s">
         <v>876</v>
       </c>
-      <c r="K74" s="11" t="s">
+      <c r="K74" s="12" t="s">
         <v>877</v>
       </c>
-      <c r="L74" s="11" t="s">
+      <c r="L74" s="12" t="s">
         <v>878</v>
       </c>
-      <c r="M74" s="11" t="s">
+      <c r="M74" s="12" t="s">
         <v>879</v>
       </c>
-      <c r="N74" s="11" t="s">
+      <c r="N74" s="12" t="s">
         <v>880</v>
       </c>
-      <c r="O74" s="11" t="s">
+      <c r="O74" s="12" t="s">
         <v>881</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="2:15">
-      <c r="B75" s="10">
+      <c r="B75" s="11">
         <v>10070</v>
       </c>
-      <c r="C75" s="11" t="s">
+      <c r="C75" s="12" t="s">
         <v>882</v>
       </c>
-      <c r="D75" s="11" t="s">
+      <c r="D75" s="12" t="s">
         <v>883</v>
       </c>
-      <c r="E75" s="11" t="s">
+      <c r="E75" s="12" t="s">
         <v>884</v>
       </c>
-      <c r="F75" s="11" t="s">
+      <c r="F75" s="12" t="s">
         <v>885</v>
       </c>
-      <c r="G75" s="11" t="s">
+      <c r="G75" s="12" t="s">
         <v>886</v>
       </c>
-      <c r="H75" s="11" t="s">
+      <c r="H75" s="12" t="s">
         <v>887</v>
       </c>
-      <c r="I75" s="11" t="s">
+      <c r="I75" s="12" t="s">
         <v>888</v>
       </c>
-      <c r="J75" s="11" t="s">
+      <c r="J75" s="12" t="s">
         <v>889</v>
       </c>
-      <c r="K75" s="11" t="s">
+      <c r="K75" s="12" t="s">
         <v>890</v>
       </c>
-      <c r="L75" s="11" t="s">
+      <c r="L75" s="12" t="s">
         <v>891</v>
       </c>
-      <c r="M75" s="11" t="s">
+      <c r="M75" s="12" t="s">
         <v>892</v>
       </c>
-      <c r="N75" s="11" t="s">
+      <c r="N75" s="12" t="s">
         <v>893</v>
       </c>
-      <c r="O75" s="11" t="s">
+      <c r="O75" s="12" t="s">
         <v>894</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="2:15">
-      <c r="B76" s="10">
+      <c r="B76" s="11">
         <v>10071</v>
       </c>
-      <c r="C76" s="11" t="s">
+      <c r="C76" s="12" t="s">
         <v>895</v>
       </c>
-      <c r="D76" s="11" t="s">
+      <c r="D76" s="12" t="s">
         <v>896</v>
       </c>
-      <c r="E76" s="11" t="s">
+      <c r="E76" s="12" t="s">
         <v>897</v>
       </c>
-      <c r="F76" s="11" t="s">
+      <c r="F76" s="12" t="s">
         <v>898</v>
       </c>
-      <c r="G76" s="11" t="s">
+      <c r="G76" s="12" t="s">
         <v>899</v>
       </c>
-      <c r="H76" s="11" t="s">
+      <c r="H76" s="12" t="s">
         <v>900</v>
       </c>
-      <c r="I76" s="11" t="s">
+      <c r="I76" s="12" t="s">
         <v>901</v>
       </c>
-      <c r="J76" s="11" t="s">
+      <c r="J76" s="12" t="s">
         <v>902</v>
       </c>
-      <c r="K76" s="11" t="s">
+      <c r="K76" s="12" t="s">
         <v>903</v>
       </c>
-      <c r="L76" s="11" t="s">
+      <c r="L76" s="12" t="s">
         <v>904</v>
       </c>
-      <c r="M76" s="11" t="s">
+      <c r="M76" s="12" t="s">
         <v>905</v>
       </c>
-      <c r="N76" s="11" t="s">
+      <c r="N76" s="12" t="s">
         <v>906</v>
       </c>
-      <c r="O76" s="11" t="s">
+      <c r="O76" s="12" t="s">
         <v>907</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="2:15">
-      <c r="B77" s="10">
+      <c r="B77" s="11">
         <v>10072</v>
       </c>
-      <c r="C77" s="11" t="s">
+      <c r="C77" s="12" t="s">
         <v>908</v>
       </c>
-      <c r="D77" s="11" t="s">
+      <c r="D77" s="12" t="s">
         <v>909</v>
       </c>
-      <c r="E77" s="11" t="s">
+      <c r="E77" s="12" t="s">
         <v>910</v>
       </c>
-      <c r="F77" s="11" t="s">
+      <c r="F77" s="12" t="s">
         <v>911</v>
       </c>
-      <c r="G77" s="11" t="s">
+      <c r="G77" s="12" t="s">
         <v>912</v>
       </c>
-      <c r="H77" s="11" t="s">
+      <c r="H77" s="12" t="s">
         <v>913</v>
       </c>
-      <c r="I77" s="11" t="s">
+      <c r="I77" s="12" t="s">
         <v>914</v>
       </c>
-      <c r="J77" s="11" t="s">
+      <c r="J77" s="12" t="s">
         <v>915</v>
       </c>
-      <c r="K77" s="11" t="s">
+      <c r="K77" s="12" t="s">
         <v>916</v>
       </c>
-      <c r="L77" s="11" t="s">
+      <c r="L77" s="12" t="s">
         <v>917</v>
       </c>
-      <c r="M77" s="11" t="s">
+      <c r="M77" s="12" t="s">
         <v>918</v>
       </c>
-      <c r="N77" s="11" t="s">
+      <c r="N77" s="12" t="s">
         <v>919</v>
       </c>
-      <c r="O77" s="11" t="s">
+      <c r="O77" s="12" t="s">
         <v>920</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="2:15">
-      <c r="B78" s="10">
+      <c r="B78" s="11">
         <v>10073</v>
       </c>
-      <c r="C78" s="11" t="s">
+      <c r="C78" s="12" t="s">
         <v>921</v>
       </c>
-      <c r="D78" s="12" t="s">
+      <c r="D78" s="13" t="s">
         <v>922</v>
       </c>
-      <c r="E78" s="11" t="s">
+      <c r="E78" s="12" t="s">
         <v>923</v>
       </c>
-      <c r="F78" s="11" t="s">
+      <c r="F78" s="12" t="s">
         <v>924</v>
       </c>
-      <c r="G78" s="11" t="s">
+      <c r="G78" s="12" t="s">
         <v>925</v>
       </c>
-      <c r="H78" s="11" t="s">
+      <c r="H78" s="12" t="s">
         <v>926</v>
       </c>
-      <c r="I78" s="11" t="s">
+      <c r="I78" s="12" t="s">
         <v>927</v>
       </c>
-      <c r="J78" s="11" t="s">
+      <c r="J78" s="12" t="s">
         <v>928</v>
       </c>
-      <c r="K78" s="11" t="s">
+      <c r="K78" s="12" t="s">
         <v>929</v>
       </c>
-      <c r="L78" s="11" t="s">
+      <c r="L78" s="12" t="s">
         <v>930</v>
       </c>
-      <c r="M78" s="11" t="s">
+      <c r="M78" s="12" t="s">
         <v>931</v>
       </c>
-      <c r="N78" s="11" t="s">
+      <c r="N78" s="12" t="s">
         <v>932</v>
       </c>
-      <c r="O78" s="11" t="s">
+      <c r="O78" s="12" t="s">
         <v>933</v>
       </c>
     </row>
     <row r="79" ht="19" customHeight="1" spans="2:15">
-      <c r="B79" s="10">
+      <c r="B79" s="11">
         <v>10074</v>
       </c>
-      <c r="C79" s="12" t="s">
+      <c r="C79" s="13" t="s">
         <v>934</v>
       </c>
-      <c r="D79" s="12" t="s">
+      <c r="D79" s="13" t="s">
         <v>935</v>
       </c>
-      <c r="E79" s="11" t="s">
+      <c r="E79" s="12" t="s">
         <v>936</v>
       </c>
-      <c r="F79" s="11" t="s">
+      <c r="F79" s="12" t="s">
         <v>937</v>
       </c>
-      <c r="G79" s="11" t="s">
+      <c r="G79" s="12" t="s">
         <v>938</v>
       </c>
-      <c r="H79" s="11" t="s">
+      <c r="H79" s="12" t="s">
         <v>939</v>
       </c>
-      <c r="I79" s="11" t="s">
+      <c r="I79" s="12" t="s">
         <v>940</v>
       </c>
-      <c r="J79" s="11" t="s">
+      <c r="J79" s="12" t="s">
         <v>941</v>
       </c>
-      <c r="K79" s="11" t="s">
+      <c r="K79" s="12" t="s">
         <v>942</v>
       </c>
-      <c r="L79" s="11" t="s">
+      <c r="L79" s="12" t="s">
         <v>943</v>
       </c>
-      <c r="M79" s="11" t="s">
+      <c r="M79" s="12" t="s">
         <v>944</v>
       </c>
-      <c r="N79" s="11" t="s">
+      <c r="N79" s="12" t="s">
         <v>945</v>
       </c>
-      <c r="O79" s="11" t="s">
+      <c r="O79" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="2:15">
-      <c r="B80" s="10">
+      <c r="B80" s="11">
         <v>10075</v>
       </c>
-      <c r="C80" s="11" t="s">
+      <c r="C80" s="12" t="s">
         <v>947</v>
       </c>
-      <c r="D80" s="12" t="s">
+      <c r="D80" s="13" t="s">
         <v>948</v>
       </c>
-      <c r="E80" s="11" t="s">
+      <c r="E80" s="12" t="s">
         <v>949</v>
       </c>
-      <c r="F80" s="11" t="s">
+      <c r="F80" s="12" t="s">
         <v>950</v>
       </c>
-      <c r="G80" s="11" t="s">
+      <c r="G80" s="12" t="s">
         <v>951</v>
       </c>
-      <c r="H80" s="11" t="s">
+      <c r="H80" s="12" t="s">
         <v>952</v>
       </c>
-      <c r="I80" s="11" t="s">
+      <c r="I80" s="12" t="s">
         <v>953</v>
       </c>
-      <c r="J80" s="11" t="s">
+      <c r="J80" s="12" t="s">
         <v>954</v>
       </c>
-      <c r="K80" s="11" t="s">
+      <c r="K80" s="12" t="s">
         <v>955</v>
       </c>
-      <c r="L80" s="11" t="s">
+      <c r="L80" s="12" t="s">
         <v>956</v>
       </c>
-      <c r="M80" s="11" t="s">
+      <c r="M80" s="12" t="s">
         <v>957</v>
       </c>
-      <c r="N80" s="11" t="s">
+      <c r="N80" s="12" t="s">
         <v>958</v>
       </c>
-      <c r="O80" s="11" t="s">
+      <c r="O80" s="12" t="s">
         <v>959</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="2:15">
-      <c r="B81" s="10">
+      <c r="B81" s="11">
         <v>10076</v>
       </c>
-      <c r="C81" s="11" t="s">
+      <c r="C81" s="12" t="s">
         <v>960</v>
       </c>
-      <c r="D81" s="12" t="s">
+      <c r="D81" s="13" t="s">
         <v>961</v>
       </c>
-      <c r="E81" s="11" t="s">
+      <c r="E81" s="12" t="s">
         <v>962</v>
       </c>
-      <c r="F81" s="11" t="s">
+      <c r="F81" s="12" t="s">
         <v>963</v>
       </c>
-      <c r="G81" s="11" t="s">
+      <c r="G81" s="12" t="s">
         <v>964</v>
       </c>
-      <c r="H81" s="11" t="s">
+      <c r="H81" s="12" t="s">
         <v>965</v>
       </c>
-      <c r="I81" s="11" t="s">
+      <c r="I81" s="12" t="s">
         <v>966</v>
       </c>
-      <c r="J81" s="11" t="s">
+      <c r="J81" s="12" t="s">
         <v>967</v>
       </c>
-      <c r="K81" s="11" t="s">
+      <c r="K81" s="12" t="s">
         <v>968</v>
       </c>
-      <c r="L81" s="11" t="s">
+      <c r="L81" s="12" t="s">
         <v>969</v>
       </c>
-      <c r="M81" s="11" t="s">
+      <c r="M81" s="12" t="s">
         <v>970</v>
       </c>
-      <c r="N81" s="11" t="s">
+      <c r="N81" s="12" t="s">
         <v>971</v>
       </c>
-      <c r="O81" s="11" t="s">
+      <c r="O81" s="12" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="2:15">
-      <c r="B82" s="10">
+      <c r="B82" s="11">
         <v>10077</v>
       </c>
-      <c r="C82" s="11" t="s">
+      <c r="C82" s="12" t="s">
         <v>973</v>
       </c>
-      <c r="D82" s="12" t="s">
+      <c r="D82" s="13" t="s">
         <v>974</v>
       </c>
-      <c r="E82" s="11" t="s">
+      <c r="E82" s="12" t="s">
         <v>975</v>
       </c>
-      <c r="F82" s="11" t="s">
+      <c r="F82" s="12" t="s">
         <v>976</v>
       </c>
-      <c r="G82" s="11" t="s">
+      <c r="G82" s="12" t="s">
         <v>977</v>
       </c>
-      <c r="H82" s="11" t="s">
+      <c r="H82" s="12" t="s">
         <v>978</v>
       </c>
-      <c r="I82" s="11" t="s">
+      <c r="I82" s="12" t="s">
         <v>979</v>
       </c>
-      <c r="J82" s="11" t="s">
+      <c r="J82" s="12" t="s">
         <v>980</v>
       </c>
-      <c r="K82" s="11" t="s">
+      <c r="K82" s="12" t="s">
         <v>981</v>
       </c>
-      <c r="L82" s="11" t="s">
+      <c r="L82" s="12" t="s">
         <v>982</v>
       </c>
-      <c r="M82" s="11" t="s">
+      <c r="M82" s="12" t="s">
         <v>983</v>
       </c>
-      <c r="N82" s="11" t="s">
+      <c r="N82" s="12" t="s">
         <v>984</v>
       </c>
-      <c r="O82" s="11" t="s">
+      <c r="O82" s="12" t="s">
         <v>985</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="2:15">
-      <c r="B83" s="10">
+      <c r="B83" s="11">
         <v>10078</v>
       </c>
-      <c r="C83" s="11" t="s">
+      <c r="C83" s="12" t="s">
         <v>986</v>
       </c>
-      <c r="D83" s="12" t="s">
+      <c r="D83" s="13" t="s">
         <v>987</v>
       </c>
-      <c r="E83" s="11" t="s">
+      <c r="E83" s="12" t="s">
         <v>988</v>
       </c>
-      <c r="F83" s="11" t="s">
+      <c r="F83" s="12" t="s">
         <v>989</v>
       </c>
-      <c r="G83" s="11" t="s">
+      <c r="G83" s="12" t="s">
         <v>990</v>
       </c>
-      <c r="H83" s="11" t="s">
+      <c r="H83" s="12" t="s">
         <v>991</v>
       </c>
-      <c r="I83" s="11" t="s">
+      <c r="I83" s="12" t="s">
         <v>992</v>
       </c>
-      <c r="J83" s="11" t="s">
+      <c r="J83" s="12" t="s">
         <v>993</v>
       </c>
-      <c r="K83" s="11" t="s">
+      <c r="K83" s="12" t="s">
         <v>994</v>
       </c>
-      <c r="L83" s="11" t="s">
+      <c r="L83" s="12" t="s">
         <v>995</v>
       </c>
-      <c r="M83" s="11" t="s">
+      <c r="M83" s="12" t="s">
         <v>996</v>
       </c>
-      <c r="N83" s="11" t="s">
+      <c r="N83" s="12" t="s">
         <v>997</v>
       </c>
-      <c r="O83" s="11" t="s">
+      <c r="O83" s="12" t="s">
         <v>998</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="2:15">
-      <c r="B84" s="10">
+      <c r="B84" s="11">
         <v>10079</v>
       </c>
-      <c r="C84" s="11" t="s">
+      <c r="C84" s="12" t="s">
         <v>999</v>
       </c>
-      <c r="D84" s="12" t="s">
+      <c r="D84" s="13" t="s">
         <v>1000</v>
       </c>
-      <c r="E84" s="11" t="s">
+      <c r="E84" s="12" t="s">
         <v>1001</v>
       </c>
-      <c r="F84" s="11" t="s">
+      <c r="F84" s="12" t="s">
         <v>1002</v>
       </c>
-      <c r="G84" s="11" t="s">
+      <c r="G84" s="12" t="s">
         <v>1003</v>
       </c>
-      <c r="H84" s="11" t="s">
+      <c r="H84" s="12" t="s">
         <v>1004</v>
       </c>
-      <c r="I84" s="11" t="s">
+      <c r="I84" s="12" t="s">
         <v>1005</v>
       </c>
-      <c r="J84" s="11" t="s">
+      <c r="J84" s="12" t="s">
         <v>1006</v>
       </c>
-      <c r="K84" s="11" t="s">
+      <c r="K84" s="12" t="s">
         <v>1007</v>
       </c>
-      <c r="L84" s="11" t="s">
+      <c r="L84" s="12" t="s">
         <v>1008</v>
       </c>
-      <c r="M84" s="11" t="s">
+      <c r="M84" s="12" t="s">
         <v>1009</v>
       </c>
-      <c r="N84" s="11" t="s">
+      <c r="N84" s="12" t="s">
         <v>1010</v>
       </c>
-      <c r="O84" s="11" t="s">
+      <c r="O84" s="12" t="s">
         <v>1011</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="2:15">
-      <c r="B85" s="10">
+      <c r="B85" s="11">
         <v>10080</v>
       </c>
-      <c r="C85" s="11" t="s">
+      <c r="C85" s="12" t="s">
         <v>1012</v>
       </c>
-      <c r="D85" s="12" t="s">
+      <c r="D85" s="13" t="s">
         <v>1013</v>
       </c>
-      <c r="E85" s="11" t="s">
+      <c r="E85" s="12" t="s">
         <v>1014</v>
       </c>
-      <c r="F85" s="11" t="s">
+      <c r="F85" s="12" t="s">
         <v>1015</v>
       </c>
-      <c r="G85" s="11" t="s">
+      <c r="G85" s="12" t="s">
         <v>1016</v>
       </c>
-      <c r="H85" s="11" t="s">
+      <c r="H85" s="12" t="s">
         <v>1017</v>
       </c>
-      <c r="I85" s="11" t="s">
+      <c r="I85" s="12" t="s">
         <v>1018</v>
       </c>
-      <c r="J85" s="11" t="s">
+      <c r="J85" s="12" t="s">
         <v>1019</v>
       </c>
-      <c r="K85" s="11" t="s">
+      <c r="K85" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L85" s="11" t="s">
+      <c r="L85" s="12" t="s">
         <v>1021</v>
       </c>
-      <c r="M85" s="11" t="s">
+      <c r="M85" s="12" t="s">
         <v>1022</v>
       </c>
-      <c r="N85" s="11" t="s">
+      <c r="N85" s="12" t="s">
         <v>1023</v>
       </c>
-      <c r="O85" s="11" t="s">
+      <c r="O85" s="12" t="s">
         <v>1024</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="2:15">
-      <c r="B86" s="10">
+      <c r="B86" s="11">
         <v>10081</v>
       </c>
-      <c r="C86" s="11" t="s">
+      <c r="C86" s="12" t="s">
         <v>1025</v>
       </c>
-      <c r="D86" s="12" t="s">
+      <c r="D86" s="13" t="s">
         <v>1026</v>
       </c>
-      <c r="E86" s="11" t="s">
+      <c r="E86" s="12" t="s">
         <v>1027</v>
       </c>
-      <c r="F86" s="11" t="s">
+      <c r="F86" s="12" t="s">
         <v>1028</v>
       </c>
-      <c r="G86" s="11" t="s">
+      <c r="G86" s="12" t="s">
         <v>1029</v>
       </c>
-      <c r="H86" s="11" t="s">
+      <c r="H86" s="12" t="s">
         <v>1030</v>
       </c>
-      <c r="I86" s="11" t="s">
+      <c r="I86" s="12" t="s">
         <v>1031</v>
       </c>
-      <c r="J86" s="11" t="s">
+      <c r="J86" s="12" t="s">
         <v>1032</v>
       </c>
-      <c r="K86" s="11" t="s">
+      <c r="K86" s="12" t="s">
         <v>1033</v>
       </c>
-      <c r="L86" s="11" t="s">
+      <c r="L86" s="12" t="s">
         <v>1034</v>
       </c>
-      <c r="M86" s="11" t="s">
+      <c r="M86" s="12" t="s">
         <v>1035</v>
       </c>
-      <c r="N86" s="11" t="s">
+      <c r="N86" s="12" t="s">
         <v>1036</v>
       </c>
-      <c r="O86" s="11" t="s">
+      <c r="O86" s="12" t="s">
         <v>1037</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="2:15">
-      <c r="B87" s="10">
+      <c r="B87" s="11">
         <v>10082</v>
       </c>
-      <c r="C87" s="11" t="s">
+      <c r="C87" s="12" t="s">
         <v>1038</v>
       </c>
-      <c r="D87" s="12" t="s">
+      <c r="D87" s="13" t="s">
         <v>1039</v>
       </c>
-      <c r="E87" s="11" t="s">
+      <c r="E87" s="12" t="s">
         <v>1040</v>
       </c>
-      <c r="F87" s="11" t="s">
+      <c r="F87" s="12" t="s">
         <v>1041</v>
       </c>
-      <c r="G87" s="11" t="s">
+      <c r="G87" s="12" t="s">
         <v>1042</v>
       </c>
-      <c r="H87" s="11" t="s">
+      <c r="H87" s="12" t="s">
         <v>1043</v>
       </c>
-      <c r="I87" s="11" t="s">
+      <c r="I87" s="12" t="s">
         <v>1044</v>
       </c>
-      <c r="J87" s="11" t="s">
+      <c r="J87" s="12" t="s">
         <v>1045</v>
       </c>
-      <c r="K87" s="11" t="s">
+      <c r="K87" s="12" t="s">
         <v>1046</v>
       </c>
-      <c r="L87" s="11" t="s">
+      <c r="L87" s="12" t="s">
         <v>1047</v>
       </c>
-      <c r="M87" s="11" t="s">
+      <c r="M87" s="12" t="s">
         <v>1048</v>
       </c>
-      <c r="N87" s="11" t="s">
+      <c r="N87" s="12" t="s">
         <v>1049</v>
       </c>
-      <c r="O87" s="11" t="s">
+      <c r="O87" s="12" t="s">
         <v>1050</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="2:15">
-      <c r="B88" s="10">
+      <c r="B88" s="11">
         <v>10083</v>
       </c>
-      <c r="C88" s="11" t="s">
+      <c r="C88" s="12" t="s">
         <v>1051</v>
       </c>
-      <c r="D88" s="12" t="s">
+      <c r="D88" s="13" t="s">
         <v>1052</v>
       </c>
-      <c r="E88" s="11" t="s">
+      <c r="E88" s="12" t="s">
         <v>1053</v>
       </c>
-      <c r="F88" s="11" t="s">
+      <c r="F88" s="12" t="s">
         <v>1054</v>
       </c>
-      <c r="G88" s="11" t="s">
+      <c r="G88" s="12" t="s">
         <v>1055</v>
       </c>
-      <c r="H88" s="11" t="s">
+      <c r="H88" s="12" t="s">
         <v>1056</v>
       </c>
-      <c r="I88" s="11" t="s">
+      <c r="I88" s="12" t="s">
         <v>1057</v>
       </c>
-      <c r="J88" s="11" t="s">
+      <c r="J88" s="12" t="s">
         <v>1058</v>
       </c>
-      <c r="K88" s="11" t="s">
+      <c r="K88" s="12" t="s">
         <v>1059</v>
       </c>
-      <c r="L88" s="11" t="s">
+      <c r="L88" s="12" t="s">
         <v>1060</v>
       </c>
-      <c r="M88" s="11" t="s">
+      <c r="M88" s="12" t="s">
         <v>1061</v>
       </c>
-      <c r="N88" s="11" t="s">
+      <c r="N88" s="12" t="s">
         <v>1062</v>
       </c>
-      <c r="O88" s="11" t="s">
+      <c r="O88" s="12" t="s">
         <v>1063</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="2:15">
-      <c r="B89" s="10">
+      <c r="B89" s="11">
         <v>10084</v>
       </c>
-      <c r="C89" s="11" t="s">
+      <c r="C89" s="12" t="s">
         <v>1064</v>
       </c>
-      <c r="D89" s="12" t="s">
+      <c r="D89" s="13" t="s">
         <v>1065</v>
       </c>
-      <c r="E89" s="11" t="s">
+      <c r="E89" s="12" t="s">
         <v>1066</v>
       </c>
-      <c r="F89" s="11" t="s">
+      <c r="F89" s="12" t="s">
         <v>1067</v>
       </c>
-      <c r="G89" s="11" t="s">
+      <c r="G89" s="12" t="s">
         <v>1068</v>
       </c>
-      <c r="H89" s="11" t="s">
+      <c r="H89" s="12" t="s">
         <v>1069</v>
       </c>
-      <c r="I89" s="11" t="s">
+      <c r="I89" s="12" t="s">
         <v>1068</v>
       </c>
-      <c r="J89" s="11" t="s">
+      <c r="J89" s="12" t="s">
         <v>1070</v>
       </c>
-      <c r="K89" s="11" t="s">
+      <c r="K89" s="12" t="s">
         <v>1071</v>
       </c>
-      <c r="L89" s="11" t="s">
+      <c r="L89" s="12" t="s">
         <v>1072</v>
       </c>
-      <c r="M89" s="11" t="s">
+      <c r="M89" s="12" t="s">
         <v>1073</v>
       </c>
-      <c r="N89" s="11" t="s">
+      <c r="N89" s="12" t="s">
         <v>1074</v>
       </c>
-      <c r="O89" s="11" t="s">
+      <c r="O89" s="12" t="s">
         <v>1075</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="2:15">
-      <c r="B90" s="10">
+      <c r="B90" s="11">
         <v>10085</v>
       </c>
-      <c r="C90" s="11" t="s">
+      <c r="C90" s="12" t="s">
         <v>1076</v>
       </c>
-      <c r="D90" s="12" t="s">
+      <c r="D90" s="13" t="s">
         <v>1077</v>
       </c>
-      <c r="E90" s="11" t="s">
+      <c r="E90" s="12" t="s">
         <v>1078</v>
       </c>
-      <c r="F90" s="11" t="s">
+      <c r="F90" s="12" t="s">
         <v>1079</v>
       </c>
-      <c r="G90" s="11" t="s">
+      <c r="G90" s="12" t="s">
         <v>1080</v>
       </c>
-      <c r="H90" s="11" t="s">
+      <c r="H90" s="12" t="s">
         <v>1081</v>
       </c>
-      <c r="I90" s="11" t="s">
+      <c r="I90" s="12" t="s">
         <v>1082</v>
       </c>
-      <c r="J90" s="11" t="s">
+      <c r="J90" s="12" t="s">
         <v>1083</v>
       </c>
-      <c r="K90" s="11" t="s">
+      <c r="K90" s="12" t="s">
         <v>1084</v>
       </c>
-      <c r="L90" s="11" t="s">
+      <c r="L90" s="12" t="s">
         <v>1085</v>
       </c>
-      <c r="M90" s="11" t="s">
+      <c r="M90" s="12" t="s">
         <v>1086</v>
       </c>
-      <c r="N90" s="11" t="s">
+      <c r="N90" s="12" t="s">
         <v>1087</v>
       </c>
-      <c r="O90" s="11" t="s">
+      <c r="O90" s="12" t="s">
         <v>1088</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="2:15">
-      <c r="B91" s="10">
+      <c r="B91" s="11">
         <v>10086</v>
       </c>
-      <c r="C91" s="11" t="s">
+      <c r="C91" s="12" t="s">
         <v>1089</v>
       </c>
-      <c r="D91" s="12" t="s">
+      <c r="D91" s="13" t="s">
         <v>1090</v>
       </c>
-      <c r="E91" s="11" t="s">
+      <c r="E91" s="12" t="s">
         <v>1091</v>
       </c>
-      <c r="F91" s="11" t="s">
+      <c r="F91" s="12" t="s">
         <v>1092</v>
       </c>
-      <c r="G91" s="11" t="s">
+      <c r="G91" s="12" t="s">
         <v>1093</v>
       </c>
-      <c r="H91" s="11" t="s">
+      <c r="H91" s="12" t="s">
         <v>1094</v>
       </c>
-      <c r="I91" s="11" t="s">
+      <c r="I91" s="12" t="s">
         <v>1095</v>
       </c>
-      <c r="J91" s="11" t="s">
+      <c r="J91" s="12" t="s">
         <v>1096</v>
       </c>
-      <c r="K91" s="11" t="s">
+      <c r="K91" s="12" t="s">
         <v>1097</v>
       </c>
-      <c r="L91" s="11" t="s">
+      <c r="L91" s="12" t="s">
         <v>1098</v>
       </c>
-      <c r="M91" s="11" t="s">
+      <c r="M91" s="12" t="s">
         <v>1099</v>
       </c>
-      <c r="N91" s="11" t="s">
+      <c r="N91" s="12" t="s">
         <v>1100</v>
       </c>
-      <c r="O91" s="11" t="s">
+      <c r="O91" s="12" t="s">
         <v>1101</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="2:15">
-      <c r="B92" s="10">
+      <c r="B92" s="11">
         <v>10087</v>
       </c>
-      <c r="C92" s="11" t="s">
+      <c r="C92" s="12" t="s">
         <v>1102</v>
       </c>
-      <c r="D92" s="11" t="s">
+      <c r="D92" s="12" t="s">
         <v>1103</v>
       </c>
-      <c r="E92" s="11" t="s">
+      <c r="E92" s="12" t="s">
         <v>1104</v>
       </c>
-      <c r="F92" s="11" t="s">
+      <c r="F92" s="12" t="s">
         <v>1105</v>
       </c>
-      <c r="G92" s="11" t="s">
+      <c r="G92" s="12" t="s">
         <v>1106</v>
       </c>
-      <c r="H92" s="11" t="s">
+      <c r="H92" s="12" t="s">
         <v>1107</v>
       </c>
-      <c r="I92" s="11" t="s">
+      <c r="I92" s="12" t="s">
         <v>1108</v>
       </c>
-      <c r="J92" s="11" t="s">
+      <c r="J92" s="12" t="s">
         <v>1109</v>
       </c>
-      <c r="K92" s="11" t="s">
+      <c r="K92" s="12" t="s">
         <v>1110</v>
       </c>
-      <c r="L92" s="11" t="s">
+      <c r="L92" s="12" t="s">
         <v>1111</v>
       </c>
-      <c r="M92" s="11" t="s">
+      <c r="M92" s="12" t="s">
         <v>1112</v>
       </c>
-      <c r="N92" s="11" t="s">
+      <c r="N92" s="12" t="s">
         <v>1113</v>
       </c>
-      <c r="O92" s="11" t="s">
+      <c r="O92" s="12" t="s">
         <v>1114</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="2:15">
-      <c r="B93" s="10">
+      <c r="B93" s="11">
         <v>10088</v>
       </c>
-      <c r="C93" s="11" t="s">
+      <c r="C93" s="12" t="s">
         <v>1115</v>
       </c>
-      <c r="D93" s="11" t="s">
+      <c r="D93" s="12" t="s">
         <v>1116</v>
       </c>
-      <c r="E93" s="11" t="s">
+      <c r="E93" s="12" t="s">
         <v>1117</v>
       </c>
-      <c r="F93" s="11" t="s">
+      <c r="F93" s="12" t="s">
         <v>1118</v>
       </c>
-      <c r="G93" s="11" t="s">
+      <c r="G93" s="12" t="s">
         <v>1119</v>
       </c>
-      <c r="H93" s="11" t="s">
+      <c r="H93" s="12" t="s">
         <v>1120</v>
       </c>
-      <c r="I93" s="11" t="s">
+      <c r="I93" s="12" t="s">
         <v>1121</v>
       </c>
-      <c r="J93" s="11" t="s">
+      <c r="J93" s="12" t="s">
         <v>1122</v>
       </c>
-      <c r="K93" s="11" t="s">
+      <c r="K93" s="12" t="s">
         <v>1123</v>
       </c>
-      <c r="L93" s="11" t="s">
+      <c r="L93" s="12" t="s">
         <v>1124</v>
       </c>
-      <c r="M93" s="11" t="s">
+      <c r="M93" s="12" t="s">
         <v>1125</v>
       </c>
-      <c r="N93" s="11" t="s">
+      <c r="N93" s="12" t="s">
         <v>1126</v>
       </c>
-      <c r="O93" s="11" t="s">
+      <c r="O93" s="12" t="s">
         <v>1127</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="2:15">
-      <c r="B94" s="10">
+      <c r="B94" s="11">
         <v>10089</v>
       </c>
-      <c r="C94" s="11" t="s">
+      <c r="C94" s="12" t="s">
         <v>1128</v>
       </c>
-      <c r="D94" s="11" t="s">
+      <c r="D94" s="12" t="s">
         <v>1129</v>
       </c>
-      <c r="E94" s="11" t="s">
+      <c r="E94" s="12" t="s">
         <v>1130</v>
       </c>
-      <c r="F94" s="11" t="s">
+      <c r="F94" s="12" t="s">
         <v>1131</v>
       </c>
-      <c r="G94" s="11" t="s">
+      <c r="G94" s="12" t="s">
         <v>1132</v>
       </c>
-      <c r="H94" s="11" t="s">
+      <c r="H94" s="12" t="s">
         <v>1133</v>
       </c>
-      <c r="I94" s="11" t="s">
+      <c r="I94" s="12" t="s">
         <v>1134</v>
       </c>
-      <c r="J94" s="11" t="s">
+      <c r="J94" s="12" t="s">
         <v>1135</v>
       </c>
-      <c r="K94" s="11" t="s">
+      <c r="K94" s="12" t="s">
         <v>1136</v>
       </c>
-      <c r="L94" s="11" t="s">
+      <c r="L94" s="12" t="s">
         <v>1137</v>
       </c>
-      <c r="M94" s="11" t="s">
+      <c r="M94" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="N94" s="11" t="s">
+      <c r="N94" s="12" t="s">
         <v>1139</v>
       </c>
-      <c r="O94" s="11" t="s">
+      <c r="O94" s="12" t="s">
         <v>1140</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="2:15">
-      <c r="B95" s="10">
+      <c r="B95" s="11">
         <v>10090</v>
       </c>
-      <c r="C95" s="11" t="s">
+      <c r="C95" s="12" t="s">
         <v>1141</v>
       </c>
-      <c r="D95" s="12" t="s">
+      <c r="D95" s="13" t="s">
         <v>1142</v>
       </c>
-      <c r="E95" s="11" t="s">
+      <c r="E95" s="12" t="s">
         <v>1143</v>
       </c>
-      <c r="F95" s="11" t="s">
+      <c r="F95" s="12" t="s">
         <v>1144</v>
       </c>
-      <c r="G95" s="11" t="s">
+      <c r="G95" s="12" t="s">
         <v>1145</v>
       </c>
-      <c r="H95" s="11" t="s">
+      <c r="H95" s="12" t="s">
         <v>1146</v>
       </c>
-      <c r="I95" s="11" t="s">
+      <c r="I95" s="12" t="s">
         <v>1147</v>
       </c>
-      <c r="J95" s="11" t="s">
+      <c r="J95" s="12" t="s">
         <v>1148</v>
       </c>
-      <c r="K95" s="11" t="s">
+      <c r="K95" s="12" t="s">
         <v>1149</v>
       </c>
-      <c r="L95" s="11" t="s">
+      <c r="L95" s="12" t="s">
         <v>1150</v>
       </c>
-      <c r="M95" s="11" t="s">
+      <c r="M95" s="12" t="s">
         <v>1151</v>
       </c>
-      <c r="N95" s="11" t="s">
+      <c r="N95" s="12" t="s">
         <v>1152</v>
       </c>
-      <c r="O95" s="11" t="s">
+      <c r="O95" s="12" t="s">
         <v>1153</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="2:15">
-      <c r="B96" s="10">
+      <c r="B96" s="11">
         <v>10091</v>
       </c>
       <c r="C96" t="s">
@@ -9481,7 +10415,7 @@
       </c>
     </row>
     <row r="97" customHeight="1" spans="1:16">
-      <c r="B97" s="10">
+      <c r="B97" s="11">
         <v>10092</v>
       </c>
       <c r="C97" t="s">
@@ -9525,7 +10459,7 @@
       </c>
     </row>
     <row r="98" customHeight="1" spans="1:16">
-      <c r="B98" s="3">
+      <c r="B98" s="4">
         <v>10093</v>
       </c>
       <c r="C98" t="s">
@@ -9534,290 +10468,1311 @@
       <c r="D98" s="1" t="s">
         <v>1181</v>
       </c>
+      <c r="E98" t="s">
+        <v>1182</v>
+      </c>
+      <c r="F98" s="15" t="s">
+        <v>1183</v>
+      </c>
+      <c r="G98" s="15" t="s">
+        <v>1184</v>
+      </c>
+      <c r="H98" t="s">
+        <v>1185</v>
+      </c>
+      <c r="I98" s="15" t="s">
+        <v>1186</v>
+      </c>
+      <c r="J98" s="15" t="s">
+        <v>1187</v>
+      </c>
+      <c r="K98" s="15" t="s">
+        <v>1188</v>
+      </c>
+      <c r="L98" t="s">
+        <v>1189</v>
+      </c>
+      <c r="M98" s="15" t="s">
+        <v>1190</v>
+      </c>
+      <c r="N98" t="s">
+        <v>1191</v>
+      </c>
+      <c r="O98" t="s">
+        <v>1192</v>
+      </c>
     </row>
     <row r="99" customHeight="1" spans="1:16">
-      <c r="B99" s="3">
+      <c r="B99" s="4">
         <v>10094</v>
       </c>
       <c r="C99" t="s">
-        <v>1182</v>
+        <v>1193</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>1183</v>
+        <v>1194</v>
+      </c>
+      <c r="E99" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F99" t="s">
+        <v>1196</v>
+      </c>
+      <c r="G99" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H99" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I99" s="15" t="s">
+        <v>1199</v>
+      </c>
+      <c r="J99" s="15" t="s">
+        <v>1200</v>
+      </c>
+      <c r="K99" t="s">
+        <v>1201</v>
+      </c>
+      <c r="L99" t="s">
+        <v>1202</v>
+      </c>
+      <c r="M99" s="15" t="s">
+        <v>1203</v>
+      </c>
+      <c r="N99" s="15" t="s">
+        <v>1204</v>
+      </c>
+      <c r="O99" s="15" t="s">
+        <v>1205</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="1:16">
-      <c r="B100" s="3">
+      <c r="B100" s="4">
         <v>10095</v>
       </c>
       <c r="C100" t="s">
-        <v>1184</v>
+        <v>1206</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>1185</v>
+        <v>1207</v>
+      </c>
+      <c r="E100" t="s">
+        <v>1208</v>
+      </c>
+      <c r="F100" t="s">
+        <v>1209</v>
+      </c>
+      <c r="G100" t="s">
+        <v>1210</v>
+      </c>
+      <c r="H100" t="s">
+        <v>1211</v>
+      </c>
+      <c r="I100" t="s">
+        <v>1212</v>
+      </c>
+      <c r="J100" t="s">
+        <v>1213</v>
+      </c>
+      <c r="K100" t="s">
+        <v>1214</v>
+      </c>
+      <c r="L100" t="s">
+        <v>1215</v>
+      </c>
+      <c r="M100" s="15" t="s">
+        <v>1216</v>
+      </c>
+      <c r="N100" s="15" t="s">
+        <v>1217</v>
+      </c>
+      <c r="O100" s="15" t="s">
+        <v>1218</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="1:16">
-      <c r="B101" s="3">
+      <c r="B101" s="4">
         <v>10096</v>
       </c>
       <c r="C101" t="s">
-        <v>1186</v>
+        <v>1219</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>1187</v>
-      </c>
-      <c r="G101" s="13"/>
-      <c r="K101" s="13"/>
+        <v>1220</v>
+      </c>
+      <c r="E101" t="s">
+        <v>1221</v>
+      </c>
+      <c r="F101" s="15" t="s">
+        <v>1222</v>
+      </c>
+      <c r="G101" s="15" t="s">
+        <v>1223</v>
+      </c>
+      <c r="H101" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I101" s="15" t="s">
+        <v>1225</v>
+      </c>
+      <c r="J101" s="15" t="s">
+        <v>1226</v>
+      </c>
+      <c r="K101" s="15" t="s">
+        <v>1227</v>
+      </c>
+      <c r="L101" s="15" t="s">
+        <v>1228</v>
+      </c>
+      <c r="M101" s="15" t="s">
+        <v>1229</v>
+      </c>
+      <c r="N101" s="15" t="s">
+        <v>1230</v>
+      </c>
+      <c r="O101" t="s">
+        <v>1231</v>
+      </c>
     </row>
     <row r="102" customHeight="1" spans="1:16">
-      <c r="B102" s="3">
+      <c r="B102" s="4">
         <v>10097</v>
       </c>
       <c r="C102" t="s">
-        <v>1188</v>
+        <v>1232</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>1189</v>
-      </c>
-      <c r="G102" s="13"/>
-      <c r="K102" s="13"/>
+        <v>1233</v>
+      </c>
+      <c r="E102" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F102" s="16" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G102" s="16" t="s">
+        <v>1236</v>
+      </c>
+      <c r="H102" t="s">
+        <v>1237</v>
+      </c>
+      <c r="I102" s="15" t="s">
+        <v>1238</v>
+      </c>
+      <c r="J102" s="15" t="s">
+        <v>1239</v>
+      </c>
+      <c r="K102" s="15" t="s">
+        <v>1240</v>
+      </c>
+      <c r="L102" t="s">
+        <v>1241</v>
+      </c>
+      <c r="M102" s="15" t="s">
+        <v>1242</v>
+      </c>
+      <c r="N102" t="s">
+        <v>1243</v>
+      </c>
+      <c r="O102" t="s">
+        <v>1244</v>
+      </c>
     </row>
     <row r="103" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A103" s="2" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B103" s="3">
+        <v>1245</v>
+      </c>
+      <c r="B103" s="4">
         <v>10098</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>1191</v>
+        <v>1246</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>1192</v>
+        <v>1247</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>1193</v>
+        <v>1248</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>1194</v>
+        <v>1249</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>1195</v>
+        <v>1250</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>1196</v>
+        <v>1251</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>1197</v>
+        <v>1252</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>1198</v>
+        <v>1253</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>1199</v>
+        <v>1254</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>1200</v>
+        <v>1255</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>1201</v>
+        <v>1256</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>1202</v>
+        <v>1257</v>
       </c>
       <c r="O103" s="2" t="s">
-        <v>1203</v>
+        <v>1258</v>
       </c>
       <c r="P103" s="2" t="s">
-        <v>1190</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="104" customFormat="1" customHeight="1" spans="1:16">
-      <c r="B104" s="3">
+      <c r="B104" s="4">
         <v>10099</v>
       </c>
-      <c r="C104" s="11" t="s">
-        <v>1204</v>
-      </c>
-      <c r="D104" s="12" t="s">
-        <v>1205</v>
-      </c>
-      <c r="E104" s="11" t="s">
-        <v>1206</v>
-      </c>
-      <c r="F104" s="11" t="s">
-        <v>1207</v>
-      </c>
-      <c r="G104" s="11" t="s">
-        <v>1208</v>
-      </c>
-      <c r="H104" s="11" t="s">
-        <v>1209</v>
-      </c>
-      <c r="I104" s="11" t="s">
-        <v>1210</v>
-      </c>
-      <c r="J104" s="11" t="s">
-        <v>1211</v>
-      </c>
-      <c r="K104" s="11" t="s">
-        <v>1212</v>
-      </c>
-      <c r="L104" s="11" t="s">
-        <v>1213</v>
-      </c>
-      <c r="M104" s="11" t="s">
-        <v>1214</v>
-      </c>
-      <c r="N104" s="14" t="s">
-        <v>1215</v>
-      </c>
-      <c r="O104" s="11" t="s">
-        <v>1216</v>
+      <c r="C104" s="12" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D104" s="13" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E104" s="12" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F104" s="12" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G104" s="12" t="s">
+        <v>1263</v>
+      </c>
+      <c r="H104" s="12" t="s">
+        <v>1264</v>
+      </c>
+      <c r="I104" s="12" t="s">
+        <v>1265</v>
+      </c>
+      <c r="J104" s="12" t="s">
+        <v>1266</v>
+      </c>
+      <c r="K104" s="12" t="s">
+        <v>1267</v>
+      </c>
+      <c r="L104" s="12" t="s">
+        <v>1268</v>
+      </c>
+      <c r="M104" s="12" t="s">
+        <v>1269</v>
+      </c>
+      <c r="N104" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="O104" s="12" t="s">
+        <v>1271</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="B105" s="3">
+      <c r="B105" s="4">
         <v>10100</v>
       </c>
       <c r="C105" t="s">
-        <v>1217</v>
-      </c>
-      <c r="D105" s="13" t="s">
+        <v>1272</v>
+      </c>
+      <c r="D105" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="E105"/>
-      <c r="F105"/>
-      <c r="G105" s="13"/>
-      <c r="H105"/>
-      <c r="I105"/>
-      <c r="J105"/>
-      <c r="K105" s="13"/>
-      <c r="L105"/>
-      <c r="M105"/>
-      <c r="N105"/>
-      <c r="O105"/>
+      <c r="E105" t="s">
+        <v>1273</v>
+      </c>
+      <c r="F105" t="s">
+        <v>1274</v>
+      </c>
+      <c r="G105" s="14" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H105" t="s">
+        <v>1276</v>
+      </c>
+      <c r="I105" t="s">
+        <v>1277</v>
+      </c>
+      <c r="J105" t="s">
+        <v>1278</v>
+      </c>
+      <c r="K105" s="14" t="s">
+        <v>1279</v>
+      </c>
+      <c r="L105" t="s">
+        <v>1280</v>
+      </c>
+      <c r="M105" s="15" t="s">
+        <v>1281</v>
+      </c>
+      <c r="N105" s="16" t="s">
+        <v>1282</v>
+      </c>
+      <c r="O105" s="15" t="s">
+        <v>1283</v>
+      </c>
       <c r="P105"/>
     </row>
     <row r="106" customHeight="1" spans="1:16">
-      <c r="B106" s="3">
+      <c r="B106" s="4">
         <v>10101</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>1218</v>
+        <v>1284</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>1219</v>
+        <v>1285</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>1220</v>
+        <v>1286</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>1221</v>
+        <v>1287</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>1222</v>
+        <v>1288</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>1223</v>
+        <v>1289</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>1224</v>
+        <v>1290</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>1225</v>
+        <v>1291</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>1226</v>
+        <v>1292</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>1227</v>
+        <v>1293</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>1228</v>
+        <v>1294</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>1229</v>
+        <v>1295</v>
       </c>
       <c r="O106" s="2" t="s">
-        <v>1230</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="1:16">
-      <c r="B107" s="3">
+      <c r="B107" s="4">
         <v>10102</v>
       </c>
       <c r="C107" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D107" s="13" t="s">
-        <v>1232</v>
-      </c>
-      <c r="G107" s="13"/>
-      <c r="K107" s="13"/>
+        <v>1297</v>
+      </c>
+      <c r="D107" s="14" t="s">
+        <v>1298</v>
+      </c>
+      <c r="E107" t="s">
+        <v>1299</v>
+      </c>
+      <c r="F107" s="15" t="s">
+        <v>1300</v>
+      </c>
+      <c r="G107" s="15" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H107" s="15" t="s">
+        <v>1302</v>
+      </c>
+      <c r="I107" s="15" t="s">
+        <v>1303</v>
+      </c>
+      <c r="J107" s="15" t="s">
+        <v>1304</v>
+      </c>
+      <c r="K107" s="15" t="s">
+        <v>1305</v>
+      </c>
+      <c r="L107" s="15" t="s">
+        <v>1306</v>
+      </c>
+      <c r="M107" s="15" t="s">
+        <v>1307</v>
+      </c>
+      <c r="N107" s="15" t="s">
+        <v>1308</v>
+      </c>
+      <c r="O107" t="s">
+        <v>1309</v>
+      </c>
     </row>
     <row r="108" customHeight="1" spans="1:16">
-      <c r="B108" s="3">
+      <c r="B108" s="4">
         <v>10103</v>
       </c>
       <c r="C108" t="s">
-        <v>1233</v>
-      </c>
-      <c r="D108" s="13" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G108" s="13"/>
-      <c r="K108" s="13"/>
+        <v>1310</v>
+      </c>
+      <c r="D108" s="14" t="s">
+        <v>1311</v>
+      </c>
+      <c r="E108" t="s">
+        <v>1312</v>
+      </c>
+      <c r="F108" t="s">
+        <v>1313</v>
+      </c>
+      <c r="G108" s="14" t="s">
+        <v>1314</v>
+      </c>
+      <c r="H108" t="s">
+        <v>1315</v>
+      </c>
+      <c r="I108" t="s">
+        <v>1316</v>
+      </c>
+      <c r="J108" t="s">
+        <v>1317</v>
+      </c>
+      <c r="K108" s="15" t="s">
+        <v>1318</v>
+      </c>
+      <c r="L108" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="M108" s="15" t="s">
+        <v>1320</v>
+      </c>
+      <c r="N108" t="s">
+        <v>1321</v>
+      </c>
+      <c r="O108" t="s">
+        <v>1322</v>
+      </c>
     </row>
     <row r="109" customHeight="1" spans="1:16">
-      <c r="B109" s="3">
+      <c r="B109" s="4">
         <v>10104</v>
       </c>
       <c r="C109" t="s">
-        <v>1235</v>
-      </c>
-      <c r="D109" s="13" t="s">
-        <v>1236</v>
-      </c>
-      <c r="G109" s="13"/>
-      <c r="K109" s="13"/>
+        <v>1323</v>
+      </c>
+      <c r="D109" s="14" t="s">
+        <v>1324</v>
+      </c>
+      <c r="E109" t="s">
+        <v>1325</v>
+      </c>
+      <c r="F109" t="s">
+        <v>1326</v>
+      </c>
+      <c r="G109" s="14" t="s">
+        <v>1327</v>
+      </c>
+      <c r="H109" t="s">
+        <v>1328</v>
+      </c>
+      <c r="I109" t="s">
+        <v>1329</v>
+      </c>
+      <c r="J109" t="s">
+        <v>1330</v>
+      </c>
+      <c r="K109" s="15" t="s">
+        <v>1331</v>
+      </c>
+      <c r="L109" s="15" t="s">
+        <v>1332</v>
+      </c>
+      <c r="M109" s="15" t="s">
+        <v>1333</v>
+      </c>
+      <c r="N109" s="15" t="s">
+        <v>1334</v>
+      </c>
+      <c r="O109" s="15" t="s">
+        <v>1335</v>
+      </c>
     </row>
     <row r="110" customHeight="1" spans="1:16">
-      <c r="B110" s="3">
+      <c r="B110" s="4">
         <v>10105</v>
       </c>
       <c r="C110" t="s">
-        <v>1237</v>
+        <v>1336</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>1238</v>
-      </c>
-      <c r="G110" s="13"/>
-      <c r="K110" s="13"/>
+        <v>1337</v>
+      </c>
+      <c r="E110" t="s">
+        <v>1338</v>
+      </c>
+      <c r="F110" s="15" t="s">
+        <v>1339</v>
+      </c>
+      <c r="G110" s="15" t="s">
+        <v>1340</v>
+      </c>
+      <c r="H110" s="15" t="s">
+        <v>1341</v>
+      </c>
+      <c r="I110" s="15" t="s">
+        <v>1342</v>
+      </c>
+      <c r="J110" s="15" t="s">
+        <v>1343</v>
+      </c>
+      <c r="K110" s="15" t="s">
+        <v>1344</v>
+      </c>
+      <c r="L110" t="s">
+        <v>1345</v>
+      </c>
+      <c r="M110" s="16" t="s">
+        <v>1346</v>
+      </c>
+      <c r="N110" s="16" t="s">
+        <v>1347</v>
+      </c>
+      <c r="O110" s="16" t="s">
+        <v>1348</v>
+      </c>
     </row>
     <row r="111" customHeight="1" spans="1:16">
-      <c r="B111" s="3">
+      <c r="B111" s="4">
         <v>10106</v>
       </c>
-      <c r="C111" s="15" t="s">
-        <v>1239</v>
-      </c>
-      <c r="D111" s="13" t="s">
-        <v>1240</v>
-      </c>
-      <c r="G111" s="13"/>
-      <c r="K111" s="13"/>
+      <c r="C111" s="18" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D111" s="14" t="s">
+        <v>1350</v>
+      </c>
+      <c r="E111" t="s">
+        <v>1351</v>
+      </c>
+      <c r="F111" s="15" t="s">
+        <v>1352</v>
+      </c>
+      <c r="G111" s="14" t="s">
+        <v>1353</v>
+      </c>
+      <c r="H111" s="15" t="s">
+        <v>1354</v>
+      </c>
+      <c r="I111" s="15" t="s">
+        <v>1355</v>
+      </c>
+      <c r="J111" s="15" t="s">
+        <v>1356</v>
+      </c>
+      <c r="K111" s="15" t="s">
+        <v>1357</v>
+      </c>
+      <c r="L111" t="s">
+        <v>1358</v>
+      </c>
+      <c r="M111" s="15" t="s">
+        <v>1359</v>
+      </c>
+      <c r="N111" s="15" t="s">
+        <v>1360</v>
+      </c>
+      <c r="O111" t="s">
+        <v>1361</v>
+      </c>
     </row>
     <row r="112" customHeight="1" spans="1:16">
-      <c r="B112" s="3">
+      <c r="B112" s="4">
         <v>10107</v>
       </c>
       <c r="C112" t="s">
-        <v>1241</v>
+        <v>1362</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>1242</v>
+        <v>1363</v>
+      </c>
+      <c r="E112" t="s">
+        <v>1364</v>
+      </c>
+      <c r="F112" s="15" t="s">
+        <v>1365</v>
+      </c>
+      <c r="G112" t="s">
+        <v>1366</v>
+      </c>
+      <c r="H112" t="s">
+        <v>1367</v>
+      </c>
+      <c r="I112" s="15" t="s">
+        <v>1368</v>
+      </c>
+      <c r="J112" s="15" t="s">
+        <v>1369</v>
+      </c>
+      <c r="K112" s="15" t="s">
+        <v>1370</v>
+      </c>
+      <c r="L112" t="s">
+        <v>1371</v>
+      </c>
+      <c r="M112" s="15" t="s">
+        <v>1372</v>
+      </c>
+      <c r="N112" t="s">
+        <v>1373</v>
+      </c>
+      <c r="O112" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="113" s="3" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A113" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B113" s="4">
+        <v>10108</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>1376</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>1377</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>1378</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>1379</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>1380</v>
+      </c>
+      <c r="J113" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="K113" s="3" t="s">
+        <v>1381</v>
+      </c>
+      <c r="L113" s="3" t="s">
+        <v>1382</v>
+      </c>
+      <c r="M113" s="3" t="s">
+        <v>1383</v>
+      </c>
+      <c r="N113" s="3" t="s">
+        <v>1384</v>
+      </c>
+      <c r="O113" s="3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="P113" s="3" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="114" s="3" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A114" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B114" s="4">
+        <v>10109</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>1387</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>1388</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>1389</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>1390</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>1391</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="J114" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="K114" s="3" t="s">
+        <v>1394</v>
+      </c>
+      <c r="L114" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="M114" s="3" t="s">
+        <v>1396</v>
+      </c>
+      <c r="N114" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="O114" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="P114" s="3" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="115" s="3" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A115" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B115" s="4">
+        <v>10110</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J115" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="K115" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="L115" s="3" t="s">
+        <v>1408</v>
+      </c>
+      <c r="M115" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="N115" s="3" t="s">
+        <v>1410</v>
+      </c>
+      <c r="O115" s="3" t="s">
+        <v>1411</v>
+      </c>
+      <c r="P115" s="3" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="116" s="3" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A116" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B116" s="4">
+        <v>10111</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>1414</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>1415</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>1416</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>1417</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J116" s="3" t="s">
+        <v>1419</v>
+      </c>
+      <c r="K116" s="3" t="s">
+        <v>1420</v>
+      </c>
+      <c r="L116" s="3" t="s">
+        <v>1421</v>
+      </c>
+      <c r="M116" s="3" t="s">
+        <v>1422</v>
+      </c>
+      <c r="N116" s="3" t="s">
+        <v>1423</v>
+      </c>
+      <c r="O116" s="3" t="s">
+        <v>1424</v>
+      </c>
+      <c r="P116" s="3" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="117" s="3" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A117" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B117" s="4">
+        <v>10112</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>1425</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>1426</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>1427</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>1428</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>1429</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>1430</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J117" s="3" t="s">
+        <v>1432</v>
+      </c>
+      <c r="K117" s="3" t="s">
+        <v>1433</v>
+      </c>
+      <c r="L117" s="3" t="s">
+        <v>1434</v>
+      </c>
+      <c r="M117" s="3" t="s">
+        <v>1435</v>
+      </c>
+      <c r="N117" s="3" t="s">
+        <v>1436</v>
+      </c>
+      <c r="O117" s="3" t="s">
+        <v>1437</v>
+      </c>
+      <c r="P117" s="3" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="118" s="3" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A118" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B118" s="4">
+        <v>10113</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>1439</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>1440</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>1441</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>1442</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>1443</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>1444</v>
+      </c>
+      <c r="J118" s="3" t="s">
+        <v>1445</v>
+      </c>
+      <c r="K118" s="3" t="s">
+        <v>1446</v>
+      </c>
+      <c r="L118" s="3" t="s">
+        <v>1447</v>
+      </c>
+      <c r="M118" s="3" t="s">
+        <v>1448</v>
+      </c>
+      <c r="N118" s="3" t="s">
+        <v>1449</v>
+      </c>
+      <c r="O118" s="3" t="s">
+        <v>1450</v>
+      </c>
+      <c r="P118" s="3" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="119" s="3" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A119" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B119" s="4">
+        <v>10114</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>1454</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>1455</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>1457</v>
+      </c>
+      <c r="J119" s="3" t="s">
+        <v>1458</v>
+      </c>
+      <c r="K119" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="L119" s="3" t="s">
+        <v>1460</v>
+      </c>
+      <c r="M119" s="3" t="s">
+        <v>1461</v>
+      </c>
+      <c r="N119" s="3" t="s">
+        <v>1462</v>
+      </c>
+      <c r="O119" s="3" t="s">
+        <v>1463</v>
+      </c>
+      <c r="P119" s="3" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="120" s="3" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A120" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B120" s="4">
+        <v>10115</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>1464</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>1466</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>1467</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>1468</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>1469</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>1470</v>
+      </c>
+      <c r="J120" s="3" t="s">
+        <v>1471</v>
+      </c>
+      <c r="K120" s="3" t="s">
+        <v>1472</v>
+      </c>
+      <c r="L120" s="3" t="s">
+        <v>1473</v>
+      </c>
+      <c r="M120" s="3" t="s">
+        <v>1474</v>
+      </c>
+      <c r="N120" s="3" t="s">
+        <v>1475</v>
+      </c>
+      <c r="O120" s="3" t="s">
+        <v>1476</v>
+      </c>
+      <c r="P120" s="3" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="121" s="3" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A121" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B121" s="4">
+        <v>10116</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>1478</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>1480</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>1481</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>1483</v>
+      </c>
+      <c r="J121" s="3" t="s">
+        <v>1484</v>
+      </c>
+      <c r="K121" s="3" t="s">
+        <v>1485</v>
+      </c>
+      <c r="L121" s="3" t="s">
+        <v>1486</v>
+      </c>
+      <c r="M121" s="3" t="s">
+        <v>1487</v>
+      </c>
+      <c r="N121" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="O121" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="P121" s="3" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="122" s="3" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A122" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B122" s="4">
+        <v>10117</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>1490</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>1493</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>1494</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>1494</v>
+      </c>
+      <c r="J122" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="K122" s="3" t="s">
+        <v>1497</v>
+      </c>
+      <c r="L122" s="3" t="s">
+        <v>1498</v>
+      </c>
+      <c r="M122" s="3" t="s">
+        <v>1499</v>
+      </c>
+      <c r="N122" s="3" t="s">
+        <v>1500</v>
+      </c>
+      <c r="O122" s="3" t="s">
+        <v>1501</v>
+      </c>
+      <c r="P122" s="3" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="123" s="3" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A123" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B123" s="4">
+        <v>10118</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>1504</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>1505</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>1506</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>1508</v>
+      </c>
+      <c r="J123" s="3" t="s">
+        <v>1509</v>
+      </c>
+      <c r="K123" s="3" t="s">
+        <v>1510</v>
+      </c>
+      <c r="L123" s="3" t="s">
+        <v>1511</v>
+      </c>
+      <c r="M123" s="3" t="s">
+        <v>1512</v>
+      </c>
+      <c r="N123" s="3" t="s">
+        <v>1513</v>
+      </c>
+      <c r="O123" s="3" t="s">
+        <v>1514</v>
+      </c>
+      <c r="P123" s="3" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="124" s="3" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A124" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B124" s="4">
+        <v>10119</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>1516</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>1517</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>1518</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>1519</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>1520</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>1521</v>
+      </c>
+      <c r="J124" s="3" t="s">
+        <v>1522</v>
+      </c>
+      <c r="K124" s="3" t="s">
+        <v>1523</v>
+      </c>
+      <c r="L124" s="3" t="s">
+        <v>1524</v>
+      </c>
+      <c r="M124" s="3" t="s">
+        <v>1525</v>
+      </c>
+      <c r="N124" s="3" t="s">
+        <v>1526</v>
+      </c>
+      <c r="O124" s="3" t="s">
+        <v>1527</v>
+      </c>
+      <c r="P124" s="3" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="125" s="3" customFormat="1" ht="27" spans="1:16">
+      <c r="A125" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B125" s="4">
+        <v>10120</v>
+      </c>
+      <c r="C125" s="19" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>1529</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>1529</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>1530</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>1531</v>
+      </c>
+      <c r="H125" s="3" t="s">
+        <v>1532</v>
+      </c>
+      <c r="I125" s="3" t="s">
+        <v>1533</v>
+      </c>
+      <c r="J125" s="3" t="s">
+        <v>1534</v>
+      </c>
+      <c r="K125" s="3" t="s">
+        <v>1529</v>
+      </c>
+      <c r="L125" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="M125" s="3" t="s">
+        <v>1536</v>
+      </c>
+      <c r="N125" s="3" t="s">
+        <v>1537</v>
+      </c>
+      <c r="O125" s="3" t="s">
+        <v>1538</v>
+      </c>
+      <c r="P125" s="3" t="s">
+        <v>1245</v>
       </c>
     </row>
   </sheetData>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="1539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="1604">
   <si>
     <t>##var</t>
   </si>
@@ -4833,6 +4833,201 @@
     <t>Seviye
 {0}</t>
   </si>
+  <si>
+    <t>新玩法</t>
+  </si>
+  <si>
+    <t>New Gameplay</t>
+  </si>
+  <si>
+    <t>Neues Gameplay</t>
+  </si>
+  <si>
+    <t>新しいゲームプレイ</t>
+  </si>
+  <si>
+    <t>Nova Jogabilidade</t>
+  </si>
+  <si>
+    <t>Nouveau Gameplay</t>
+  </si>
+  <si>
+    <t>Nueva Jugabilidad</t>
+  </si>
+  <si>
+    <t>새로운 게임플레이</t>
+  </si>
+  <si>
+    <t>Gameplay Baru</t>
+  </si>
+  <si>
+    <t>Новый Геймплей</t>
+  </si>
+  <si>
+    <t>नया गेमप्ले</t>
+  </si>
+  <si>
+    <t>เกมเพลย์ใหม่</t>
+  </si>
+  <si>
+    <t>Yeni Oynanış</t>
+  </si>
+  <si>
+    <t>当任意一瓶瓶子颜色装满时，它将解锁为一个瓶子</t>
+  </si>
+  <si>
+    <t>Fill 1 bottle with any single color to turn the milk tea into a botle</t>
+  </si>
+  <si>
+    <t>Fülle 1 Flasche mit einer Farbe zum Freischalten</t>
+  </si>
+  <si>
+    <t>単色でボトルを満たすとアンロック</t>
+  </si>
+  <si>
+    <t>Encha 1 garrafa com uma cor para desbloquear</t>
+  </si>
+  <si>
+    <t>Remplissez 1 bouteille d'une couleur pour la déverrouiller</t>
+  </si>
+  <si>
+    <t>Llena 1 botella con un color para desbloquearla</t>
+  </si>
+  <si>
+    <t>단색으로 병 채우면 잠금 해제</t>
+  </si>
+  <si>
+    <t>Isi 1 botol dengan satu warna untuk membuka</t>
+  </si>
+  <si>
+    <t>Заполните бутылку одним цветом для разблокировки</t>
+  </si>
+  <si>
+    <t>1 बोतल को एक रंग से भरें ताकि अनलॉक हो</t>
+  </si>
+  <si>
+    <t>เติมขวดด้วยสีเดียวเพื่อปลดล็อก</t>
+  </si>
+  <si>
+    <t>1 şişeyi tek renkle doldurarak kilidini aç</t>
+  </si>
+  <si>
+    <t>倒出顶层，露出未知的颜色</t>
+  </si>
+  <si>
+    <t>Pour out the top layer to reveal the unknown color</t>
+  </si>
+  <si>
+    <t>Obere Schicht ausgießen, unbekannte Farbe enthüllen</t>
+  </si>
+  <si>
+    <t>上の層を注ぎ、未知の色を表示</t>
+  </si>
+  <si>
+    <t>Despeje a camada superior para revelar a cor desconhecida</t>
+  </si>
+  <si>
+    <t>Versez la couche supérieure pour révéler la couleur inconnue</t>
+  </si>
+  <si>
+    <t>Vierte la capa superior para revelar el color desconocido</t>
+  </si>
+  <si>
+    <t>윗층을 따라내 미지의 색 공개</t>
+  </si>
+  <si>
+    <t>Tuang lapisan atas untuk ungkap warna tidak dikenal</t>
+  </si>
+  <si>
+    <t>Вылейте верхний слой, чтобы открыть неизвестный цвет</t>
+  </si>
+  <si>
+    <t>ऊपरी परत डालें, अज्ञात रंग प्रकट करें</t>
+  </si>
+  <si>
+    <t>เทชั้นบนเพื่อเปิดเผยสีที่ไม่รู้จัก</t>
+  </si>
+  <si>
+    <t>Üst katmanı dök, bilinmeyen rengi ortaya çıkar</t>
+  </si>
+  <si>
+    <t>数据展示</t>
+  </si>
+  <si>
+    <t>DATA SHOW</t>
+  </si>
+  <si>
+    <t>DATENANZEIGE</t>
+  </si>
+  <si>
+    <t>データ表示</t>
+  </si>
+  <si>
+    <t>EXIBIÇÃO DE DADOS</t>
+  </si>
+  <si>
+    <t>AFFICHAGE DES DONNÉES</t>
+  </si>
+  <si>
+    <t>MUESTRA DE DATOS</t>
+  </si>
+  <si>
+    <t>데이터 표시</t>
+  </si>
+  <si>
+    <t>TAMPILAN DATA</t>
+  </si>
+  <si>
+    <t>ОТОБРАЖЕНИЕ ДАННЫХ</t>
+  </si>
+  <si>
+    <t>डेटा प्रदर्शन</t>
+  </si>
+  <si>
+    <t>แสดงข้อมูล</t>
+  </si>
+  <si>
+    <t>VERİ GÖSTERİMİ</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFED74&gt;{0}&lt;/color&gt;的玩家在&lt;color=#FFED74&gt;{1} 分钟&lt;/color&gt;内达到了目标, 提现了所有 &lt;color=#FFED74&gt;{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFED74&gt;{0}&lt;/color&gt; of player reached the goal within &lt;color=#FFED74&gt;{1} minutes&lt;/color&gt;, withdrawn all &lt;color=#FFED74&gt;{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFED74&gt;{0}&lt;/color&gt; Spieler erreichten Ziel in &lt;color=#FFED74&gt;{1} Min.&lt;/color&gt;, hoben alle &lt;color=#FFED74&gt;{2}&lt;/color&gt; ab</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFED74&gt;{0}&lt;/color&gt;のプレイヤーが&lt;color=#FFED74&gt;{1}分&lt;/color&gt;以内に目標達成、&lt;color=#FFED74&gt;{2}&lt;/color&gt;を全額出金</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFED74&gt;{0}&lt;/color&gt; dos jogadores atingiram o objetivo em &lt;color=#FFED74&gt;{1} min.&lt;/color&gt;, sacaram todo o &lt;color=#FFED74&gt;{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFED74&gt;{0}&lt;/color&gt; des joueurs ont atteint l'objectif en &lt;color=#FFED74&gt;{1} min.&lt;/color&gt;, ont retiré tout le &lt;color=#FFED74&gt;{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFED74&gt;{0}&lt;/color&gt; de los jugadores alcanzaron el objetivo en &lt;color=#FFED74&gt;{1} min.&lt;/color&gt;, retiraron todo el &lt;color=#FFED74&gt;{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFED74&gt;{0}&lt;/color&gt; 플레이어 &lt;color=#FFED74&gt;{1}분&lt;/color&gt; 내 목표 달성, &lt;color=#FFED74&gt;{2}&lt;/color&gt; 전액 출금</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFED74&gt;{0}&lt;/color&gt; pemain capai tujuan dalam &lt;color=#FFED74&gt;{1} menit&lt;/color&gt;, tarik semua &lt;color=#FFED74&gt;{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFED74&gt;{0}&lt;/color&gt; игроков достигли цели за &lt;color=#FFED74&gt;{1} мин.&lt;/color&gt;, вывели все &lt;color=#FFED74&gt;{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFED74&gt;{0}&lt;/color&gt; खिलाड़ियों ने &lt;color=#FFED74&gt;{1} मिनट&lt;/color&gt; में लक्ष्य हासिल, सभी &lt;color=#FFED74&gt;{2}&lt;/color&gt; निकाल लिया</t>
+  </si>
+  <si>
+    <t>ผู้เล่น &lt;color=#FFED74&gt;{0}&lt;/color&gt; ครบเป้าหมายภายใน &lt;color=#FFED74&gt;{1} นาที&lt;/color&gt; ถอน &lt;color=#FFED74&gt;{2}&lt;/color&gt; ทั้งหมด</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFED74&gt;{0}&lt;/color&gt; oyuncu &lt;color=#FFED74&gt;{1} dakika&lt;/color&gt; içinde hedefe ulaştı, tüm &lt;color=#FFED74&gt;{2}&lt;/color&gt; çekti</t>
+  </si>
 </sst>
 </file>
 
@@ -4844,7 +5039,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4875,6 +5070,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -5017,13 +5218,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="MS Gothic"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
+      <name val="MS Gothic"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -5374,16 +5575,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5392,126 +5590,128 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -5556,6 +5756,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -6090,11 +6296,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W125"/>
+  <dimension ref="A1:W130"/>
   <sheetFormatPr defaultColWidth="9.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.875" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="3" customWidth="1"/>
     <col min="3" max="3" width="31.625" customWidth="1"/>
     <col min="4" max="4" width="54.25" style="1" customWidth="1"/>
     <col min="5" max="6" width="28.125" customWidth="1"/>
@@ -6104,49 +6310,49 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:16">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="7" t="s">
         <v>14</v>
       </c>
       <c r="P1" t="s">
@@ -6154,68 +6360,68 @@
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:16">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
     </row>
     <row r="3" customHeight="1" spans="1:16">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="6" t="s">
         <v>17</v>
       </c>
       <c r="P3" t="s">
@@ -6223,49 +6429,49 @@
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:16">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="10" t="s">
+      <c r="N4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="10" t="s">
+      <c r="O4" s="9" t="s">
         <v>19</v>
       </c>
       <c r="P4" t="s">
@@ -6273,49 +6479,49 @@
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:16">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="M5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="N5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="O5" s="6" t="s">
         <v>33</v>
       </c>
       <c r="P5" t="s">
@@ -6323,1059 +6529,1059 @@
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="13.5" spans="1:16">
-      <c r="B6" s="11">
+      <c r="B6" s="10">
         <v>10001</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K6" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="L6" s="12" t="s">
+      <c r="L6" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="M6" s="12" t="s">
+      <c r="M6" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="N6" s="12" t="s">
+      <c r="N6" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="O6" s="12" t="s">
+      <c r="O6" s="11" t="s">
         <v>47</v>
       </c>
       <c r="P6"/>
     </row>
     <row r="7" customFormat="1" customHeight="1" spans="1:16">
-      <c r="B7" s="11">
+      <c r="B7" s="10">
         <v>10002</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="J7" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="K7" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="L7" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="M7" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="N7" s="12" t="s">
+      <c r="N7" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="O7" s="12" t="s">
+      <c r="O7" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:16">
-      <c r="B8" s="11">
+      <c r="B8" s="10">
         <v>10003</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="J8" s="12" t="s">
+      <c r="J8" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="K8" s="12" t="s">
+      <c r="K8" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="L8" s="12" t="s">
+      <c r="L8" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="M8" s="12" t="s">
+      <c r="M8" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="N8" s="12" t="s">
+      <c r="N8" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="O8" s="12" t="s">
+      <c r="O8" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:16">
-      <c r="B9" s="11">
+      <c r="B9" s="10">
         <v>10004</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="J9" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="K9" s="12" t="s">
+      <c r="K9" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="L9" s="12" t="s">
+      <c r="L9" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="M9" s="12" t="s">
+      <c r="M9" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="N9" s="12" t="s">
+      <c r="N9" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="O9" s="12" t="s">
+      <c r="O9" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:16">
-      <c r="B10" s="11">
+      <c r="B10" s="10">
         <v>10005</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="J10" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="K10" s="12" t="s">
+      <c r="K10" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="L10" s="12" t="s">
+      <c r="L10" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="M10" s="12" t="s">
+      <c r="M10" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="N10" s="12" t="s">
+      <c r="N10" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="O10" s="12" t="s">
+      <c r="O10" s="11" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:16">
-      <c r="B11" s="11">
+      <c r="B11" s="10">
         <v>10006</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="J11" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="K11" s="12" t="s">
+      <c r="K11" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="L11" s="12" t="s">
+      <c r="L11" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="M11" s="12" t="s">
+      <c r="M11" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="N11" s="12" t="s">
+      <c r="N11" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="O11" s="12" t="s">
+      <c r="O11" s="11" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="B12" s="11">
+      <c r="B12" s="10">
         <v>10007</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="I12" s="12" t="s">
+      <c r="I12" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="J12" s="12" t="s">
+      <c r="J12" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="K12" s="12" t="s">
+      <c r="K12" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="L12" s="12" t="s">
+      <c r="L12" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="M12" s="12" t="s">
+      <c r="M12" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="N12" s="12" t="s">
+      <c r="N12" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="O12" s="12" t="s">
+      <c r="O12" s="11" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="B13" s="11">
+      <c r="B13" s="10">
         <v>10008</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="G13" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="I13" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="J13" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="K13" s="12" t="s">
+      <c r="K13" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="L13" s="12" t="s">
+      <c r="L13" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="M13" s="12" t="s">
+      <c r="M13" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="N13" s="12" t="s">
+      <c r="N13" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="O13" s="12" t="s">
+      <c r="O13" s="11" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:16">
-      <c r="B14" s="11">
+      <c r="B14" s="10">
         <v>10009</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="H14" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="J14" s="12" t="s">
+      <c r="J14" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="K14" s="12" t="s">
+      <c r="K14" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="L14" s="12" t="s">
+      <c r="L14" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="M14" s="12" t="s">
+      <c r="M14" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="N14" s="12" t="s">
+      <c r="N14" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="O14" s="12" t="s">
+      <c r="O14" s="11" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:16">
-      <c r="B15" s="11">
+      <c r="B15" s="10">
         <v>10010</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="G15" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="I15" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="J15" s="12" t="s">
+      <c r="J15" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="K15" s="12" t="s">
+      <c r="K15" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="L15" s="12" t="s">
+      <c r="L15" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="M15" s="12" t="s">
+      <c r="M15" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="N15" s="12" t="s">
+      <c r="N15" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="O15" s="12" t="s">
+      <c r="O15" s="11" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:16">
-      <c r="B16" s="11">
+      <c r="B16" s="10">
         <v>10011</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="I16" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="J16" s="12" t="s">
+      <c r="J16" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="K16" s="12" t="s">
+      <c r="K16" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="L16" s="12" t="s">
+      <c r="L16" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="M16" s="12" t="s">
+      <c r="M16" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="N16" s="12" t="s">
+      <c r="N16" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="O16" s="12" t="s">
+      <c r="O16" s="11" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:23">
-      <c r="B17" s="11">
+      <c r="B17" s="10">
         <v>10012</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="G17" s="12" t="s">
+      <c r="G17" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="H17" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="I17" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="J17" s="12" t="s">
+      <c r="J17" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="K17" s="12" t="s">
+      <c r="K17" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="L17" s="12" t="s">
+      <c r="L17" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="M17" s="12" t="s">
+      <c r="M17" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="N17" s="12" t="s">
+      <c r="N17" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="O17" s="12" t="s">
+      <c r="O17" s="11" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:23">
-      <c r="B18" s="11">
+      <c r="B18" s="10">
         <v>10013</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="I18" s="12" t="s">
+      <c r="I18" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="J18" s="12" t="s">
+      <c r="J18" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="K18" s="12" t="s">
+      <c r="K18" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="L18" s="12" t="s">
+      <c r="L18" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="M18" s="12" t="s">
+      <c r="M18" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="N18" s="12" t="s">
+      <c r="N18" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="O18" s="12" t="s">
+      <c r="O18" s="11" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:23">
-      <c r="B19" s="11">
+      <c r="B19" s="10">
         <v>10014</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="G19" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="H19" s="12" t="s">
+      <c r="H19" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="I19" s="12" t="s">
+      <c r="I19" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="J19" s="12" t="s">
+      <c r="J19" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="K19" s="12" t="s">
+      <c r="K19" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="L19" s="12" t="s">
+      <c r="L19" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="M19" s="12" t="s">
+      <c r="M19" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="N19" s="12" t="s">
+      <c r="N19" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="O19" s="12" t="s">
+      <c r="O19" s="11" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:23">
-      <c r="B20" s="11">
+      <c r="B20" s="10">
         <v>10015</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="G20" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="H20" s="12" t="s">
+      <c r="H20" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="I20" s="12" t="s">
+      <c r="I20" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="J20" s="12" t="s">
+      <c r="J20" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="K20" s="12" t="s">
+      <c r="K20" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="L20" s="12" t="s">
+      <c r="L20" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="M20" s="12" t="s">
+      <c r="M20" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="N20" s="12" t="s">
+      <c r="N20" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="O20" s="12" t="s">
+      <c r="O20" s="11" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:23">
-      <c r="B21" s="11">
+      <c r="B21" s="10">
         <v>10016</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="F21" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="G21" s="12" t="s">
+      <c r="G21" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="H21" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="I21" s="12" t="s">
+      <c r="I21" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="J21" s="12" t="s">
+      <c r="J21" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="K21" s="12" t="s">
+      <c r="K21" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="L21" s="12" t="s">
+      <c r="L21" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="M21" s="12" t="s">
+      <c r="M21" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="N21" s="12" t="s">
+      <c r="N21" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="O21" s="12" t="s">
+      <c r="O21" s="11" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:23">
-      <c r="B22" s="11">
+      <c r="B22" s="10">
         <v>10017</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="F22" s="12" t="s">
+      <c r="F22" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="G22" s="12" t="s">
+      <c r="G22" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="H22" s="12" t="s">
+      <c r="H22" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="I22" s="12" t="s">
+      <c r="I22" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="J22" s="12" t="s">
+      <c r="J22" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="K22" s="12" t="s">
+      <c r="K22" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="L22" s="12" t="s">
+      <c r="L22" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="M22" s="12" t="s">
+      <c r="M22" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="N22" s="12" t="s">
+      <c r="N22" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="O22" s="12" t="s">
+      <c r="O22" s="11" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:23">
-      <c r="B23" s="11">
+      <c r="B23" s="10">
         <v>10018</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="F23" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="G23" s="12" t="s">
+      <c r="G23" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="H23" s="12" t="s">
+      <c r="H23" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="I23" s="12" t="s">
+      <c r="I23" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="J23" s="12" t="s">
+      <c r="J23" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="K23" s="12" t="s">
+      <c r="K23" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="L23" s="12" t="s">
+      <c r="L23" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="M23" s="12" t="s">
+      <c r="M23" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="N23" s="12" t="s">
+      <c r="N23" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="O23" s="12" t="s">
+      <c r="O23" s="11" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="2:23">
-      <c r="B24" s="11">
+      <c r="B24" s="10">
         <v>10019</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="F24" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="G24" s="12" t="s">
+      <c r="G24" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="H24" s="12" t="s">
+      <c r="H24" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="I24" s="12" t="s">
+      <c r="I24" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="J24" s="12" t="s">
+      <c r="J24" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="K24" s="12" t="s">
+      <c r="K24" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="L24" s="12" t="s">
+      <c r="L24" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="M24" s="12" t="s">
+      <c r="M24" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="N24" s="12" t="s">
+      <c r="N24" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="O24" s="12" t="s">
+      <c r="O24" s="11" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="2:23">
-      <c r="B25" s="11">
+      <c r="B25" s="10">
         <v>10020</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="F25" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="G25" s="12" t="s">
+      <c r="G25" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="H25" s="12" t="s">
+      <c r="H25" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="I25" s="12" t="s">
+      <c r="I25" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="J25" s="12" t="s">
+      <c r="J25" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="K25" s="12" t="s">
+      <c r="K25" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="L25" s="12" t="s">
+      <c r="L25" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="M25" s="12" t="s">
+      <c r="M25" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="N25" s="12" t="s">
+      <c r="N25" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="O25" s="12" t="s">
+      <c r="O25" s="11" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:23">
-      <c r="B26" s="11">
+      <c r="B26" s="10">
         <v>10021</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="11" t="s">
         <v>289</v>
       </c>
-      <c r="F26" s="12" t="s">
+      <c r="F26" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="G26" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="H26" s="12" t="s">
+      <c r="H26" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="I26" s="12" t="s">
+      <c r="I26" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="J26" s="12" t="s">
+      <c r="J26" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="K26" s="12" t="s">
+      <c r="K26" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="L26" s="12" t="s">
+      <c r="L26" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="M26" s="12" t="s">
+      <c r="M26" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="N26" s="12" t="s">
+      <c r="N26" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="O26" s="12" t="s">
+      <c r="O26" s="11" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:23">
-      <c r="B27" s="11">
+      <c r="B27" s="10">
         <v>10022</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="E27" s="11" t="s">
         <v>302</v>
       </c>
-      <c r="F27" s="12" t="s">
+      <c r="F27" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="G27" s="12" t="s">
+      <c r="G27" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="H27" s="12" t="s">
+      <c r="H27" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="I27" s="12" t="s">
+      <c r="I27" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="J27" s="12" t="s">
+      <c r="J27" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="K27" s="12" t="s">
+      <c r="K27" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="L27" s="12" t="s">
+      <c r="L27" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="M27" s="12" t="s">
+      <c r="M27" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="N27" s="12" t="s">
+      <c r="N27" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="O27" s="12" t="s">
+      <c r="O27" s="11" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="28" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B28" s="11">
+      <c r="B28" s="10">
         <v>10023</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="F28" s="12" t="s">
+      <c r="F28" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="G28" s="12" t="s">
+      <c r="G28" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="H28" s="12" t="s">
+      <c r="H28" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="I28" s="12" t="s">
+      <c r="I28" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="J28" s="12" t="s">
+      <c r="J28" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="K28" s="12" t="s">
+      <c r="K28" s="11" t="s">
         <v>320</v>
       </c>
-      <c r="L28" s="12" t="s">
+      <c r="L28" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="M28" s="12" t="s">
+      <c r="M28" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="N28" s="12" t="s">
+      <c r="N28" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="O28" s="12" t="s">
+      <c r="O28" s="11" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="29" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B29" s="11">
+      <c r="B29" s="10">
         <v>10024</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="12" t="s">
         <v>326</v>
       </c>
-      <c r="E29" s="12" t="s">
+      <c r="E29" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="F29" s="12" t="s">
+      <c r="F29" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="G29" s="12" t="s">
+      <c r="G29" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="H29" s="12" t="s">
+      <c r="H29" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="I29" s="12" t="s">
+      <c r="I29" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="J29" s="12" t="s">
+      <c r="J29" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="K29" s="12" t="s">
+      <c r="K29" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="L29" s="12" t="s">
+      <c r="L29" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="M29" s="12" t="s">
+      <c r="M29" s="11" t="s">
         <v>335</v>
       </c>
-      <c r="N29" s="12" t="s">
+      <c r="N29" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="O29" s="12" t="s">
+      <c r="O29" s="11" t="s">
         <v>337</v>
       </c>
       <c r="Q29" s="1"/>
@@ -7387,46 +7593,46 @@
       <c r="W29" s="1"/>
     </row>
     <row r="30" customHeight="1" spans="2:23">
-      <c r="B30" s="11">
+      <c r="B30" s="10">
         <v>10025</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="D30" s="13" t="s">
+      <c r="D30" s="12" t="s">
         <v>338</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="E30" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="F30" s="12" t="s">
+      <c r="F30" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="G30" s="12" t="s">
+      <c r="G30" s="11" t="s">
         <v>341</v>
       </c>
-      <c r="H30" s="12" t="s">
+      <c r="H30" s="11" t="s">
         <v>342</v>
       </c>
-      <c r="I30" s="12" t="s">
+      <c r="I30" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="J30" s="12" t="s">
+      <c r="J30" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="K30" s="12" t="s">
+      <c r="K30" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="L30" s="12" t="s">
+      <c r="L30" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="M30" s="12" t="s">
+      <c r="M30" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="N30" s="12" t="s">
+      <c r="N30" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="O30" s="12" t="s">
+      <c r="O30" s="11" t="s">
         <v>349</v>
       </c>
       <c r="P30" s="1"/>
@@ -7439,46 +7645,46 @@
       <c r="W30" s="1"/>
     </row>
     <row r="31" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B31" s="11">
+      <c r="B31" s="10">
         <v>10026</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="12" t="s">
         <v>351</v>
       </c>
-      <c r="E31" s="12" t="s">
+      <c r="E31" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="F31" s="12" t="s">
+      <c r="F31" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="G31" s="12" t="s">
+      <c r="G31" s="11" t="s">
         <v>354</v>
       </c>
-      <c r="H31" s="12" t="s">
+      <c r="H31" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="I31" s="12" t="s">
+      <c r="I31" s="11" t="s">
         <v>354</v>
       </c>
-      <c r="J31" s="12" t="s">
+      <c r="J31" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="K31" s="12" t="s">
+      <c r="K31" s="11" t="s">
         <v>357</v>
       </c>
-      <c r="L31" s="12" t="s">
+      <c r="L31" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="M31" s="12" t="s">
+      <c r="M31" s="11" t="s">
         <v>359</v>
       </c>
-      <c r="N31" s="12" t="s">
+      <c r="N31" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="O31" s="12" t="s">
+      <c r="O31" s="11" t="s">
         <v>361</v>
       </c>
       <c r="P31"/>
@@ -7491,135 +7697,135 @@
       <c r="W31" s="1"/>
     </row>
     <row r="32" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B32" s="11">
+      <c r="B32" s="10">
         <v>10027</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="11" t="s">
         <v>362</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="11" t="s">
         <v>363</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="E32" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="F32" s="12" t="s">
+      <c r="F32" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="G32" s="12" t="s">
+      <c r="G32" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="H32" s="12" t="s">
+      <c r="H32" s="11" t="s">
         <v>366</v>
       </c>
-      <c r="I32" s="12" t="s">
+      <c r="I32" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="J32" s="12" t="s">
+      <c r="J32" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="K32" s="12" t="s">
+      <c r="K32" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="L32" s="12" t="s">
+      <c r="L32" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="M32" s="12" t="s">
+      <c r="M32" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="N32" s="12" t="s">
+      <c r="N32" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="O32" s="12" t="s">
+      <c r="O32" s="11" t="s">
         <v>372</v>
       </c>
       <c r="P32"/>
     </row>
     <row r="33" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B33" s="11">
+      <c r="B33" s="10">
         <v>10028</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="12" t="s">
         <v>373</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="E33" s="12" t="s">
+      <c r="E33" s="11" t="s">
         <v>375</v>
       </c>
-      <c r="F33" s="12" t="s">
+      <c r="F33" s="11" t="s">
         <v>376</v>
       </c>
-      <c r="G33" s="12" t="s">
+      <c r="G33" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="H33" s="12" t="s">
+      <c r="H33" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="I33" s="12" t="s">
+      <c r="I33" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="J33" s="12" t="s">
+      <c r="J33" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="K33" s="12" t="s">
+      <c r="K33" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="L33" s="12" t="s">
+      <c r="L33" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="M33" s="12" t="s">
+      <c r="M33" s="11" t="s">
         <v>383</v>
       </c>
-      <c r="N33" s="12" t="s">
+      <c r="N33" s="11" t="s">
         <v>384</v>
       </c>
-      <c r="O33" s="12" t="s">
+      <c r="O33" s="11" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B34" s="11">
+      <c r="B34" s="10">
         <v>10029</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="11" t="s">
         <v>386</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="E34" s="12" t="s">
+      <c r="E34" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="F34" s="12" t="s">
+      <c r="F34" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="G34" s="12" t="s">
+      <c r="G34" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="H34" s="12" t="s">
+      <c r="H34" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="I34" s="12" t="s">
+      <c r="I34" s="11" t="s">
         <v>391</v>
       </c>
-      <c r="J34" s="12" t="s">
+      <c r="J34" s="11" t="s">
         <v>392</v>
       </c>
-      <c r="K34" s="12" t="s">
+      <c r="K34" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="L34" s="12" t="s">
+      <c r="L34" s="11" t="s">
         <v>393</v>
       </c>
-      <c r="M34" s="12" t="s">
+      <c r="M34" s="11" t="s">
         <v>394</v>
       </c>
-      <c r="N34" s="12" t="s">
+      <c r="N34" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="O34" s="12" t="s">
+      <c r="O34" s="11" t="s">
         <v>396</v>
       </c>
       <c r="Q34"/>
@@ -7631,46 +7837,46 @@
       <c r="W34"/>
     </row>
     <row r="35" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B35" s="11">
+      <c r="B35" s="10">
         <v>10030</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="12" t="s">
         <v>397</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="11" t="s">
         <v>398</v>
       </c>
-      <c r="E35" s="12" t="s">
+      <c r="E35" s="11" t="s">
         <v>399</v>
       </c>
-      <c r="F35" s="12" t="s">
+      <c r="F35" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="G35" s="12" t="s">
+      <c r="G35" s="11" t="s">
         <v>401</v>
       </c>
-      <c r="H35" s="12" t="s">
+      <c r="H35" s="11" t="s">
         <v>402</v>
       </c>
-      <c r="I35" s="12" t="s">
+      <c r="I35" s="11" t="s">
         <v>403</v>
       </c>
-      <c r="J35" s="12" t="s">
+      <c r="J35" s="11" t="s">
         <v>404</v>
       </c>
-      <c r="K35" s="12" t="s">
+      <c r="K35" s="11" t="s">
         <v>405</v>
       </c>
-      <c r="L35" s="12" t="s">
+      <c r="L35" s="11" t="s">
         <v>406</v>
       </c>
-      <c r="M35" s="12" t="s">
+      <c r="M35" s="11" t="s">
         <v>407</v>
       </c>
-      <c r="N35" s="12" t="s">
+      <c r="N35" s="11" t="s">
         <v>408</v>
       </c>
-      <c r="O35" s="12" t="s">
+      <c r="O35" s="11" t="s">
         <v>409</v>
       </c>
       <c r="P35"/>
@@ -7683,46 +7889,46 @@
       <c r="W35"/>
     </row>
     <row r="36" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B36" s="11">
+      <c r="B36" s="10">
         <v>10031</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="11" t="s">
         <v>411</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E36" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="F36" s="12" t="s">
+      <c r="F36" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="G36" s="12" t="s">
+      <c r="G36" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="H36" s="12" t="s">
+      <c r="H36" s="11" t="s">
         <v>414</v>
       </c>
-      <c r="I36" s="12" t="s">
+      <c r="I36" s="11" t="s">
         <v>415</v>
       </c>
-      <c r="J36" s="12" t="s">
+      <c r="J36" s="11" t="s">
         <v>416</v>
       </c>
-      <c r="K36" s="12" t="s">
+      <c r="K36" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="L36" s="12" t="s">
+      <c r="L36" s="11" t="s">
         <v>417</v>
       </c>
-      <c r="M36" s="12" t="s">
+      <c r="M36" s="11" t="s">
         <v>418</v>
       </c>
-      <c r="N36" s="12" t="s">
+      <c r="N36" s="11" t="s">
         <v>419</v>
       </c>
-      <c r="O36" s="12" t="s">
+      <c r="O36" s="11" t="s">
         <v>420</v>
       </c>
       <c r="P36"/>
@@ -7735,46 +7941,46 @@
       <c r="W36"/>
     </row>
     <row r="37" customHeight="1" spans="2:23">
-      <c r="B37" s="11">
+      <c r="B37" s="10">
         <v>10032</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="12" t="s">
         <v>421</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="11" t="s">
         <v>422</v>
       </c>
-      <c r="E37" s="12" t="s">
+      <c r="E37" s="11" t="s">
         <v>423</v>
       </c>
-      <c r="F37" s="12" t="s">
+      <c r="F37" s="11" t="s">
         <v>424</v>
       </c>
-      <c r="G37" s="12" t="s">
+      <c r="G37" s="11" t="s">
         <v>425</v>
       </c>
-      <c r="H37" s="12" t="s">
+      <c r="H37" s="11" t="s">
         <v>426</v>
       </c>
-      <c r="I37" s="12" t="s">
+      <c r="I37" s="11" t="s">
         <v>427</v>
       </c>
-      <c r="J37" s="12" t="s">
+      <c r="J37" s="11" t="s">
         <v>428</v>
       </c>
-      <c r="K37" s="12" t="s">
+      <c r="K37" s="11" t="s">
         <v>429</v>
       </c>
-      <c r="L37" s="12" t="s">
+      <c r="L37" s="11" t="s">
         <v>430</v>
       </c>
-      <c r="M37" s="12" t="s">
+      <c r="M37" s="11" t="s">
         <v>431</v>
       </c>
-      <c r="N37" s="12" t="s">
+      <c r="N37" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="O37" s="12" t="s">
+      <c r="O37" s="11" t="s">
         <v>433</v>
       </c>
       <c r="Q37" s="1"/>
@@ -7786,46 +7992,46 @@
       <c r="W37" s="1"/>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B38" s="11">
+      <c r="B38" s="10">
         <v>10033</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="11" t="s">
         <v>434</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="11" t="s">
         <v>435</v>
       </c>
-      <c r="E38" s="12" t="s">
+      <c r="E38" s="11" t="s">
         <v>436</v>
       </c>
-      <c r="F38" s="12" t="s">
+      <c r="F38" s="11" t="s">
         <v>437</v>
       </c>
-      <c r="G38" s="12" t="s">
+      <c r="G38" s="11" t="s">
         <v>438</v>
       </c>
-      <c r="H38" s="12" t="s">
+      <c r="H38" s="11" t="s">
         <v>439</v>
       </c>
-      <c r="I38" s="12" t="s">
+      <c r="I38" s="11" t="s">
         <v>440</v>
       </c>
-      <c r="J38" s="12" t="s">
+      <c r="J38" s="11" t="s">
         <v>441</v>
       </c>
-      <c r="K38" s="12" t="s">
+      <c r="K38" s="11" t="s">
         <v>442</v>
       </c>
-      <c r="L38" s="12" t="s">
+      <c r="L38" s="11" t="s">
         <v>443</v>
       </c>
-      <c r="M38" s="12" t="s">
+      <c r="M38" s="11" t="s">
         <v>444</v>
       </c>
-      <c r="N38" s="12" t="s">
+      <c r="N38" s="11" t="s">
         <v>445</v>
       </c>
-      <c r="O38" s="12" t="s">
+      <c r="O38" s="11" t="s">
         <v>446</v>
       </c>
       <c r="P38" s="1"/>
@@ -7838,90 +8044,90 @@
       <c r="W38" s="1"/>
     </row>
     <row r="39" customHeight="1" spans="2:23">
-      <c r="B39" s="11">
+      <c r="B39" s="10">
         <v>10034</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="11" t="s">
         <v>447</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="11" t="s">
         <v>448</v>
       </c>
-      <c r="E39" s="12" t="s">
+      <c r="E39" s="11" t="s">
         <v>449</v>
       </c>
-      <c r="F39" s="12" t="s">
+      <c r="F39" s="11" t="s">
         <v>450</v>
       </c>
-      <c r="G39" s="12" t="s">
+      <c r="G39" s="11" t="s">
         <v>451</v>
       </c>
-      <c r="H39" s="12" t="s">
+      <c r="H39" s="11" t="s">
         <v>452</v>
       </c>
-      <c r="I39" s="12" t="s">
+      <c r="I39" s="11" t="s">
         <v>453</v>
       </c>
-      <c r="J39" s="12" t="s">
+      <c r="J39" s="11" t="s">
         <v>454</v>
       </c>
-      <c r="K39" s="12" t="s">
+      <c r="K39" s="11" t="s">
         <v>455</v>
       </c>
-      <c r="L39" s="12" t="s">
+      <c r="L39" s="11" t="s">
         <v>456</v>
       </c>
-      <c r="M39" s="12" t="s">
+      <c r="M39" s="11" t="s">
         <v>457</v>
       </c>
-      <c r="N39" s="12" t="s">
+      <c r="N39" s="11" t="s">
         <v>458</v>
       </c>
-      <c r="O39" s="12" t="s">
+      <c r="O39" s="11" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" ht="20" customHeight="1" spans="2:23">
-      <c r="B40" s="11">
+      <c r="B40" s="10">
         <v>10035</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="11" t="s">
         <v>460</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D40" s="11" t="s">
         <v>461</v>
       </c>
-      <c r="E40" s="12" t="s">
+      <c r="E40" s="11" t="s">
         <v>462</v>
       </c>
-      <c r="F40" s="12" t="s">
+      <c r="F40" s="11" t="s">
         <v>463</v>
       </c>
-      <c r="G40" s="12" t="s">
+      <c r="G40" s="11" t="s">
         <v>464</v>
       </c>
-      <c r="H40" s="12" t="s">
+      <c r="H40" s="11" t="s">
         <v>465</v>
       </c>
-      <c r="I40" s="12" t="s">
+      <c r="I40" s="11" t="s">
         <v>466</v>
       </c>
-      <c r="J40" s="12" t="s">
+      <c r="J40" s="11" t="s">
         <v>467</v>
       </c>
-      <c r="K40" s="12" t="s">
+      <c r="K40" s="11" t="s">
         <v>468</v>
       </c>
-      <c r="L40" s="12" t="s">
+      <c r="L40" s="11" t="s">
         <v>469</v>
       </c>
-      <c r="M40" s="12" t="s">
+      <c r="M40" s="11" t="s">
         <v>470</v>
       </c>
-      <c r="N40" s="12" t="s">
+      <c r="N40" s="11" t="s">
         <v>471</v>
       </c>
-      <c r="O40" s="12" t="s">
+      <c r="O40" s="11" t="s">
         <v>472</v>
       </c>
       <c r="P40"/>
@@ -7934,46 +8140,46 @@
       <c r="W40"/>
     </row>
     <row r="41" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B41" s="11">
+      <c r="B41" s="10">
         <v>10036</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="12" t="s">
         <v>473</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="11" t="s">
         <v>474</v>
       </c>
-      <c r="E41" s="12" t="s">
+      <c r="E41" s="11" t="s">
         <v>475</v>
       </c>
-      <c r="F41" s="12" t="s">
+      <c r="F41" s="11" t="s">
         <v>476</v>
       </c>
-      <c r="G41" s="12" t="s">
+      <c r="G41" s="11" t="s">
         <v>477</v>
       </c>
-      <c r="H41" s="12" t="s">
+      <c r="H41" s="11" t="s">
         <v>478</v>
       </c>
-      <c r="I41" s="12" t="s">
+      <c r="I41" s="11" t="s">
         <v>477</v>
       </c>
-      <c r="J41" s="12" t="s">
+      <c r="J41" s="11" t="s">
         <v>479</v>
       </c>
-      <c r="K41" s="12" t="s">
+      <c r="K41" s="11" t="s">
         <v>480</v>
       </c>
-      <c r="L41" s="12" t="s">
+      <c r="L41" s="11" t="s">
         <v>481</v>
       </c>
-      <c r="M41" s="12" t="s">
+      <c r="M41" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="N41" s="12" t="s">
+      <c r="N41" s="11" t="s">
         <v>483</v>
       </c>
-      <c r="O41" s="12" t="s">
+      <c r="O41" s="11" t="s">
         <v>484</v>
       </c>
       <c r="P41"/>
@@ -7986,226 +8192,226 @@
       <c r="W41"/>
     </row>
     <row r="42" customHeight="1" spans="2:23">
-      <c r="B42" s="11">
+      <c r="B42" s="10">
         <v>10037</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" s="12" t="s">
         <v>485</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D42" s="11" t="s">
         <v>486</v>
       </c>
-      <c r="E42" s="12" t="s">
+      <c r="E42" s="11" t="s">
         <v>487</v>
       </c>
-      <c r="F42" s="12" t="s">
+      <c r="F42" s="11" t="s">
         <v>488</v>
       </c>
-      <c r="G42" s="12" t="s">
+      <c r="G42" s="11" t="s">
         <v>489</v>
       </c>
-      <c r="H42" s="12" t="s">
+      <c r="H42" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="I42" s="12" t="s">
+      <c r="I42" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="J42" s="12" t="s">
+      <c r="J42" s="11" t="s">
         <v>492</v>
       </c>
-      <c r="K42" s="12" t="s">
+      <c r="K42" s="11" t="s">
         <v>493</v>
       </c>
-      <c r="L42" s="12" t="s">
+      <c r="L42" s="11" t="s">
         <v>494</v>
       </c>
-      <c r="M42" s="12" t="s">
+      <c r="M42" s="11" t="s">
         <v>495</v>
       </c>
-      <c r="N42" s="12" t="s">
+      <c r="N42" s="11" t="s">
         <v>496</v>
       </c>
-      <c r="O42" s="12" t="s">
+      <c r="O42" s="11" t="s">
         <v>497</v>
       </c>
       <c r="P42" s="1"/>
     </row>
     <row r="43" customHeight="1" spans="2:23">
-      <c r="B43" s="11">
+      <c r="B43" s="10">
         <v>10038</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="C43" s="11" t="s">
         <v>498</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="D43" s="11" t="s">
         <v>499</v>
       </c>
-      <c r="E43" s="12" t="s">
+      <c r="E43" s="11" t="s">
         <v>500</v>
       </c>
-      <c r="F43" s="12" t="s">
+      <c r="F43" s="11" t="s">
         <v>501</v>
       </c>
-      <c r="G43" s="12" t="s">
+      <c r="G43" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="H43" s="12" t="s">
+      <c r="H43" s="11" t="s">
         <v>503</v>
       </c>
-      <c r="I43" s="12" t="s">
+      <c r="I43" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="J43" s="12" t="s">
+      <c r="J43" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="K43" s="12" t="s">
+      <c r="K43" s="11" t="s">
         <v>506</v>
       </c>
-      <c r="L43" s="12" t="s">
+      <c r="L43" s="11" t="s">
         <v>507</v>
       </c>
-      <c r="M43" s="12" t="s">
+      <c r="M43" s="11" t="s">
         <v>508</v>
       </c>
-      <c r="N43" s="12" t="s">
+      <c r="N43" s="11" t="s">
         <v>509</v>
       </c>
-      <c r="O43" s="12" t="s">
+      <c r="O43" s="11" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:23">
-      <c r="B44" s="11">
+      <c r="B44" s="10">
         <v>10039</v>
       </c>
-      <c r="C44" s="12" t="s">
+      <c r="C44" s="11" t="s">
         <v>511</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="D44" s="11" t="s">
         <v>512</v>
       </c>
-      <c r="E44" s="12" t="s">
+      <c r="E44" s="11" t="s">
         <v>512</v>
       </c>
-      <c r="F44" s="12" t="s">
+      <c r="F44" s="11" t="s">
         <v>513</v>
       </c>
-      <c r="G44" s="12" t="s">
+      <c r="G44" s="11" t="s">
         <v>514</v>
       </c>
-      <c r="H44" s="12" t="s">
+      <c r="H44" s="11" t="s">
         <v>512</v>
       </c>
-      <c r="I44" s="12" t="s">
+      <c r="I44" s="11" t="s">
         <v>515</v>
       </c>
-      <c r="J44" s="12" t="s">
+      <c r="J44" s="11" t="s">
         <v>516</v>
       </c>
-      <c r="K44" s="12" t="s">
+      <c r="K44" s="11" t="s">
         <v>517</v>
       </c>
-      <c r="L44" s="12" t="s">
+      <c r="L44" s="11" t="s">
         <v>518</v>
       </c>
-      <c r="M44" s="12" t="s">
+      <c r="M44" s="11" t="s">
         <v>519</v>
       </c>
-      <c r="N44" s="12" t="s">
+      <c r="N44" s="11" t="s">
         <v>520</v>
       </c>
-      <c r="O44" s="12" t="s">
+      <c r="O44" s="11" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:23">
-      <c r="B45" s="11">
+      <c r="B45" s="10">
         <v>10040</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="C45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="D45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="E45" s="12" t="s">
+      <c r="E45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="F45" s="12" t="s">
+      <c r="F45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="G45" s="12" t="s">
+      <c r="G45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="H45" s="12" t="s">
+      <c r="H45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="I45" s="12" t="s">
+      <c r="I45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="J45" s="12" t="s">
+      <c r="J45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="K45" s="12" t="s">
+      <c r="K45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="L45" s="12" t="s">
+      <c r="L45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="M45" s="12" t="s">
+      <c r="M45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="N45" s="12" t="s">
+      <c r="N45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="O45" s="12" t="s">
+      <c r="O45" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="P45" s="14" t="s">
+      <c r="P45" s="13" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:23">
-      <c r="B46" s="11">
+      <c r="B46" s="10">
         <v>10041</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="E46" s="12" t="s">
+      <c r="E46" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="F46" s="12" t="s">
+      <c r="F46" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="G46" s="12" t="s">
+      <c r="G46" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="H46" s="12" t="s">
+      <c r="H46" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="I46" s="12" t="s">
+      <c r="I46" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="J46" s="12" t="s">
+      <c r="J46" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="K46" s="12" t="s">
+      <c r="K46" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="L46" s="12" t="s">
+      <c r="L46" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="M46" s="12" t="s">
+      <c r="M46" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="N46" s="12" t="s">
+      <c r="N46" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="O46" s="12" t="s">
+      <c r="O46" s="11" t="s">
         <v>523</v>
       </c>
       <c r="P46" t="s">
@@ -8213,2165 +8419,2165 @@
       </c>
     </row>
     <row r="47" customHeight="1" spans="2:23">
-      <c r="B47" s="11">
+      <c r="B47" s="10">
         <v>10042</v>
       </c>
-      <c r="C47" s="12" t="s">
+      <c r="C47" s="11" t="s">
         <v>524</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="12" t="s">
         <v>525</v>
       </c>
-      <c r="E47" s="12" t="s">
+      <c r="E47" s="11" t="s">
         <v>526</v>
       </c>
-      <c r="F47" s="12" t="s">
+      <c r="F47" s="11" t="s">
         <v>527</v>
       </c>
-      <c r="G47" s="12" t="s">
+      <c r="G47" s="11" t="s">
         <v>528</v>
       </c>
-      <c r="H47" s="12" t="s">
+      <c r="H47" s="11" t="s">
         <v>529</v>
       </c>
-      <c r="I47" s="12" t="s">
+      <c r="I47" s="11" t="s">
         <v>530</v>
       </c>
-      <c r="J47" s="12" t="s">
+      <c r="J47" s="11" t="s">
         <v>531</v>
       </c>
-      <c r="K47" s="12" t="s">
+      <c r="K47" s="11" t="s">
         <v>532</v>
       </c>
-      <c r="L47" s="12" t="s">
+      <c r="L47" s="11" t="s">
         <v>533</v>
       </c>
-      <c r="M47" s="12" t="s">
+      <c r="M47" s="11" t="s">
         <v>534</v>
       </c>
-      <c r="N47" s="12" t="s">
+      <c r="N47" s="11" t="s">
         <v>535</v>
       </c>
-      <c r="O47" s="12" t="s">
+      <c r="O47" s="11" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="2:23">
-      <c r="B48" s="11">
+      <c r="B48" s="10">
         <v>10043</v>
       </c>
-      <c r="C48" s="12" t="s">
+      <c r="C48" s="11" t="s">
         <v>537</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="D48" s="12" t="s">
         <v>538</v>
       </c>
-      <c r="E48" s="12" t="s">
+      <c r="E48" s="11" t="s">
         <v>539</v>
       </c>
-      <c r="F48" s="12" t="s">
+      <c r="F48" s="11" t="s">
         <v>540</v>
       </c>
-      <c r="G48" s="12" t="s">
+      <c r="G48" s="11" t="s">
         <v>541</v>
       </c>
-      <c r="H48" s="12" t="s">
+      <c r="H48" s="11" t="s">
         <v>542</v>
       </c>
-      <c r="I48" s="12" t="s">
+      <c r="I48" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="J48" s="12" t="s">
+      <c r="J48" s="11" t="s">
         <v>544</v>
       </c>
-      <c r="K48" s="12" t="s">
+      <c r="K48" s="11" t="s">
         <v>545</v>
       </c>
-      <c r="L48" s="12" t="s">
+      <c r="L48" s="11" t="s">
         <v>546</v>
       </c>
-      <c r="M48" s="12" t="s">
+      <c r="M48" s="11" t="s">
         <v>547</v>
       </c>
-      <c r="N48" s="12" t="s">
+      <c r="N48" s="11" t="s">
         <v>548</v>
       </c>
-      <c r="O48" s="12" t="s">
+      <c r="O48" s="11" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="2:16">
-      <c r="B49" s="11">
+      <c r="B49" s="10">
         <v>10044</v>
       </c>
-      <c r="C49" s="12" t="s">
+      <c r="C49" s="11" t="s">
         <v>550</v>
       </c>
-      <c r="D49" s="13" t="s">
+      <c r="D49" s="12" t="s">
         <v>551</v>
       </c>
-      <c r="E49" s="12" t="s">
+      <c r="E49" s="11" t="s">
         <v>552</v>
       </c>
-      <c r="F49" s="12" t="s">
+      <c r="F49" s="11" t="s">
         <v>553</v>
       </c>
-      <c r="G49" s="12" t="s">
+      <c r="G49" s="11" t="s">
         <v>554</v>
       </c>
-      <c r="H49" s="12" t="s">
+      <c r="H49" s="11" t="s">
         <v>555</v>
       </c>
-      <c r="I49" s="12" t="s">
+      <c r="I49" s="11" t="s">
         <v>556</v>
       </c>
-      <c r="J49" s="12" t="s">
+      <c r="J49" s="11" t="s">
         <v>557</v>
       </c>
-      <c r="K49" s="12" t="s">
+      <c r="K49" s="11" t="s">
         <v>558</v>
       </c>
-      <c r="L49" s="12" t="s">
+      <c r="L49" s="11" t="s">
         <v>559</v>
       </c>
-      <c r="M49" s="12" t="s">
+      <c r="M49" s="11" t="s">
         <v>560</v>
       </c>
-      <c r="N49" s="12" t="s">
+      <c r="N49" s="11" t="s">
         <v>561</v>
       </c>
-      <c r="O49" s="12" t="s">
+      <c r="O49" s="11" t="s">
         <v>562</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="2:16">
-      <c r="B50" s="11">
+      <c r="B50" s="10">
         <v>10045</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="11" t="s">
         <v>563</v>
       </c>
-      <c r="D50" s="13" t="s">
+      <c r="D50" s="12" t="s">
         <v>564</v>
       </c>
-      <c r="E50" s="12" t="s">
+      <c r="E50" s="11" t="s">
         <v>565</v>
       </c>
-      <c r="F50" s="12" t="s">
+      <c r="F50" s="11" t="s">
         <v>566</v>
       </c>
-      <c r="G50" s="12" t="s">
+      <c r="G50" s="11" t="s">
         <v>567</v>
       </c>
-      <c r="H50" s="12" t="s">
+      <c r="H50" s="11" t="s">
         <v>568</v>
       </c>
-      <c r="I50" s="12" t="s">
+      <c r="I50" s="11" t="s">
         <v>569</v>
       </c>
-      <c r="J50" s="12" t="s">
+      <c r="J50" s="11" t="s">
         <v>570</v>
       </c>
-      <c r="K50" s="12" t="s">
+      <c r="K50" s="11" t="s">
         <v>571</v>
       </c>
-      <c r="L50" s="12" t="s">
+      <c r="L50" s="11" t="s">
         <v>572</v>
       </c>
-      <c r="M50" s="12" t="s">
+      <c r="M50" s="11" t="s">
         <v>573</v>
       </c>
-      <c r="N50" s="12" t="s">
+      <c r="N50" s="11" t="s">
         <v>574</v>
       </c>
-      <c r="O50" s="12" t="s">
+      <c r="O50" s="11" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="2:16">
-      <c r="B51" s="11">
+      <c r="B51" s="10">
         <v>10046</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="C51" s="11" t="s">
         <v>576</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D51" s="12" t="s">
         <v>577</v>
       </c>
-      <c r="E51" s="12" t="s">
+      <c r="E51" s="11" t="s">
         <v>578</v>
       </c>
-      <c r="F51" s="12" t="s">
+      <c r="F51" s="11" t="s">
         <v>579</v>
       </c>
-      <c r="G51" s="12" t="s">
+      <c r="G51" s="11" t="s">
         <v>580</v>
       </c>
-      <c r="H51" s="12" t="s">
+      <c r="H51" s="11" t="s">
         <v>581</v>
       </c>
-      <c r="I51" s="12" t="s">
+      <c r="I51" s="11" t="s">
         <v>582</v>
       </c>
-      <c r="J51" s="12" t="s">
+      <c r="J51" s="11" t="s">
         <v>583</v>
       </c>
-      <c r="K51" s="12" t="s">
+      <c r="K51" s="11" t="s">
         <v>584</v>
       </c>
-      <c r="L51" s="12" t="s">
+      <c r="L51" s="11" t="s">
         <v>585</v>
       </c>
-      <c r="M51" s="12" t="s">
+      <c r="M51" s="11" t="s">
         <v>586</v>
       </c>
-      <c r="N51" s="12" t="s">
+      <c r="N51" s="11" t="s">
         <v>587</v>
       </c>
-      <c r="O51" s="12" t="s">
+      <c r="O51" s="11" t="s">
         <v>588</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="2:16">
-      <c r="B52" s="11">
+      <c r="B52" s="10">
         <v>10047</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="11" t="s">
         <v>589</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="D52" s="11" t="s">
         <v>590</v>
       </c>
-      <c r="E52" s="12" t="s">
+      <c r="E52" s="11" t="s">
         <v>591</v>
       </c>
-      <c r="F52" s="12" t="s">
+      <c r="F52" s="11" t="s">
         <v>592</v>
       </c>
-      <c r="G52" s="12" t="s">
+      <c r="G52" s="11" t="s">
         <v>593</v>
       </c>
-      <c r="H52" s="12" t="s">
+      <c r="H52" s="11" t="s">
         <v>594</v>
       </c>
-      <c r="I52" s="12" t="s">
+      <c r="I52" s="11" t="s">
         <v>595</v>
       </c>
-      <c r="J52" s="12" t="s">
+      <c r="J52" s="11" t="s">
         <v>596</v>
       </c>
-      <c r="K52" s="12" t="s">
+      <c r="K52" s="11" t="s">
         <v>597</v>
       </c>
-      <c r="L52" s="12" t="s">
+      <c r="L52" s="11" t="s">
         <v>598</v>
       </c>
-      <c r="M52" s="12" t="s">
+      <c r="M52" s="11" t="s">
         <v>599</v>
       </c>
-      <c r="N52" s="12" t="s">
+      <c r="N52" s="11" t="s">
         <v>600</v>
       </c>
-      <c r="O52" s="12" t="s">
+      <c r="O52" s="11" t="s">
         <v>601</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="2:16">
-      <c r="B53" s="11">
+      <c r="B53" s="10">
         <v>10048</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="11" t="s">
         <v>602</v>
       </c>
-      <c r="D53" s="12" t="s">
+      <c r="D53" s="11" t="s">
         <v>603</v>
       </c>
-      <c r="E53" s="12" t="s">
+      <c r="E53" s="11" t="s">
         <v>604</v>
       </c>
-      <c r="F53" s="12" t="s">
+      <c r="F53" s="11" t="s">
         <v>605</v>
       </c>
-      <c r="G53" s="12" t="s">
+      <c r="G53" s="11" t="s">
         <v>606</v>
       </c>
-      <c r="H53" s="12" t="s">
+      <c r="H53" s="11" t="s">
         <v>607</v>
       </c>
-      <c r="I53" s="12" t="s">
+      <c r="I53" s="11" t="s">
         <v>608</v>
       </c>
-      <c r="J53" s="12" t="s">
+      <c r="J53" s="11" t="s">
         <v>609</v>
       </c>
-      <c r="K53" s="12" t="s">
+      <c r="K53" s="11" t="s">
         <v>610</v>
       </c>
-      <c r="L53" s="12" t="s">
+      <c r="L53" s="11" t="s">
         <v>611</v>
       </c>
-      <c r="M53" s="12" t="s">
+      <c r="M53" s="11" t="s">
         <v>612</v>
       </c>
-      <c r="N53" s="12" t="s">
+      <c r="N53" s="11" t="s">
         <v>613</v>
       </c>
-      <c r="O53" s="12" t="s">
+      <c r="O53" s="11" t="s">
         <v>614</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="2:16">
-      <c r="B54" s="11">
+      <c r="B54" s="10">
         <v>10049</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="11" t="s">
         <v>615</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="D54" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="E54" s="12" t="s">
+      <c r="E54" s="11" t="s">
         <v>617</v>
       </c>
-      <c r="F54" s="12" t="s">
+      <c r="F54" s="11" t="s">
         <v>618</v>
       </c>
-      <c r="G54" s="12" t="s">
+      <c r="G54" s="11" t="s">
         <v>619</v>
       </c>
-      <c r="H54" s="12" t="s">
+      <c r="H54" s="11" t="s">
         <v>620</v>
       </c>
-      <c r="I54" s="12" t="s">
+      <c r="I54" s="11" t="s">
         <v>621</v>
       </c>
-      <c r="J54" s="12" t="s">
+      <c r="J54" s="11" t="s">
         <v>622</v>
       </c>
-      <c r="K54" s="12" t="s">
+      <c r="K54" s="11" t="s">
         <v>623</v>
       </c>
-      <c r="L54" s="12" t="s">
+      <c r="L54" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="M54" s="12" t="s">
+      <c r="M54" s="11" t="s">
         <v>625</v>
       </c>
-      <c r="N54" s="12" t="s">
+      <c r="N54" s="11" t="s">
         <v>626</v>
       </c>
-      <c r="O54" s="12" t="s">
+      <c r="O54" s="11" t="s">
         <v>627</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="2:16">
-      <c r="B55" s="11">
+      <c r="B55" s="10">
         <v>10050</v>
       </c>
-      <c r="C55" s="12" t="s">
+      <c r="C55" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="D55" s="12" t="s">
+      <c r="D55" s="11" t="s">
         <v>629</v>
       </c>
-      <c r="E55" s="12" t="s">
+      <c r="E55" s="11" t="s">
         <v>630</v>
       </c>
-      <c r="F55" s="12" t="s">
+      <c r="F55" s="11" t="s">
         <v>631</v>
       </c>
-      <c r="G55" s="12" t="s">
+      <c r="G55" s="11" t="s">
         <v>632</v>
       </c>
-      <c r="H55" s="12" t="s">
+      <c r="H55" s="11" t="s">
         <v>633</v>
       </c>
-      <c r="I55" s="12" t="s">
+      <c r="I55" s="11" t="s">
         <v>634</v>
       </c>
-      <c r="J55" s="12" t="s">
+      <c r="J55" s="11" t="s">
         <v>635</v>
       </c>
-      <c r="K55" s="12" t="s">
+      <c r="K55" s="11" t="s">
         <v>636</v>
       </c>
-      <c r="L55" s="12" t="s">
+      <c r="L55" s="11" t="s">
         <v>637</v>
       </c>
-      <c r="M55" s="12" t="s">
+      <c r="M55" s="11" t="s">
         <v>638</v>
       </c>
-      <c r="N55" s="12" t="s">
+      <c r="N55" s="11" t="s">
         <v>639</v>
       </c>
-      <c r="O55" s="12" t="s">
+      <c r="O55" s="11" t="s">
         <v>640</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" ht="19" customHeight="1" spans="2:16">
-      <c r="B56" s="11">
+      <c r="B56" s="10">
         <v>10051</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="11" t="s">
         <v>641</v>
       </c>
-      <c r="D56" s="12" t="s">
+      <c r="D56" s="11" t="s">
         <v>642</v>
       </c>
-      <c r="E56" s="12" t="s">
+      <c r="E56" s="11" t="s">
         <v>643</v>
       </c>
-      <c r="F56" s="12" t="s">
+      <c r="F56" s="11" t="s">
         <v>644</v>
       </c>
-      <c r="G56" s="12" t="s">
+      <c r="G56" s="11" t="s">
         <v>645</v>
       </c>
-      <c r="H56" s="12" t="s">
+      <c r="H56" s="11" t="s">
         <v>646</v>
       </c>
-      <c r="I56" s="12" t="s">
+      <c r="I56" s="11" t="s">
         <v>647</v>
       </c>
-      <c r="J56" s="12" t="s">
+      <c r="J56" s="11" t="s">
         <v>648</v>
       </c>
-      <c r="K56" s="12" t="s">
+      <c r="K56" s="11" t="s">
         <v>649</v>
       </c>
-      <c r="L56" s="12" t="s">
+      <c r="L56" s="11" t="s">
         <v>650</v>
       </c>
-      <c r="M56" s="12" t="s">
+      <c r="M56" s="11" t="s">
         <v>651</v>
       </c>
-      <c r="N56" s="12" t="s">
+      <c r="N56" s="11" t="s">
         <v>652</v>
       </c>
-      <c r="O56" s="12" t="s">
+      <c r="O56" s="11" t="s">
         <v>653</v>
       </c>
       <c r="P56"/>
     </row>
     <row r="57" customHeight="1" spans="2:16">
-      <c r="B57" s="11">
+      <c r="B57" s="10">
         <v>10052</v>
       </c>
-      <c r="C57" s="12" t="s">
+      <c r="C57" s="11" t="s">
         <v>654</v>
       </c>
-      <c r="D57" s="13" t="s">
+      <c r="D57" s="12" t="s">
         <v>655</v>
       </c>
-      <c r="E57" s="12" t="s">
+      <c r="E57" s="11" t="s">
         <v>656</v>
       </c>
-      <c r="F57" s="12" t="s">
+      <c r="F57" s="11" t="s">
         <v>657</v>
       </c>
-      <c r="G57" s="12" t="s">
+      <c r="G57" s="11" t="s">
         <v>658</v>
       </c>
-      <c r="H57" s="12" t="s">
+      <c r="H57" s="11" t="s">
         <v>659</v>
       </c>
-      <c r="I57" s="12" t="s">
+      <c r="I57" s="11" t="s">
         <v>660</v>
       </c>
-      <c r="J57" s="12" t="s">
+      <c r="J57" s="11" t="s">
         <v>661</v>
       </c>
-      <c r="K57" s="12" t="s">
+      <c r="K57" s="11" t="s">
         <v>662</v>
       </c>
-      <c r="L57" s="12" t="s">
+      <c r="L57" s="11" t="s">
         <v>663</v>
       </c>
-      <c r="M57" s="12" t="s">
+      <c r="M57" s="11" t="s">
         <v>664</v>
       </c>
-      <c r="N57" s="12" t="s">
+      <c r="N57" s="11" t="s">
         <v>665</v>
       </c>
-      <c r="O57" s="12" t="s">
+      <c r="O57" s="11" t="s">
         <v>666</v>
       </c>
       <c r="P57" s="1"/>
     </row>
     <row r="58" customHeight="1" spans="2:16">
-      <c r="B58" s="11">
+      <c r="B58" s="10">
         <v>10053</v>
       </c>
-      <c r="C58" s="12" t="s">
+      <c r="C58" s="11" t="s">
         <v>667</v>
       </c>
-      <c r="D58" s="13" t="s">
+      <c r="D58" s="12" t="s">
         <v>668</v>
       </c>
-      <c r="E58" s="12" t="s">
+      <c r="E58" s="11" t="s">
         <v>669</v>
       </c>
-      <c r="F58" s="12" t="s">
+      <c r="F58" s="11" t="s">
         <v>670</v>
       </c>
-      <c r="G58" s="12" t="s">
+      <c r="G58" s="11" t="s">
         <v>671</v>
       </c>
-      <c r="H58" s="12" t="s">
+      <c r="H58" s="11" t="s">
         <v>672</v>
       </c>
-      <c r="I58" s="12" t="s">
+      <c r="I58" s="11" t="s">
         <v>673</v>
       </c>
-      <c r="J58" s="12" t="s">
+      <c r="J58" s="11" t="s">
         <v>674</v>
       </c>
-      <c r="K58" s="12" t="s">
+      <c r="K58" s="11" t="s">
         <v>675</v>
       </c>
-      <c r="L58" s="12" t="s">
+      <c r="L58" s="11" t="s">
         <v>676</v>
       </c>
-      <c r="M58" s="12" t="s">
+      <c r="M58" s="11" t="s">
         <v>677</v>
       </c>
-      <c r="N58" s="12" t="s">
+      <c r="N58" s="11" t="s">
         <v>678</v>
       </c>
-      <c r="O58" s="12" t="s">
+      <c r="O58" s="11" t="s">
         <v>679</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:16">
-      <c r="B59" s="11">
+      <c r="B59" s="10">
         <v>10054</v>
       </c>
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="11" t="s">
         <v>680</v>
       </c>
-      <c r="D59" s="13" t="s">
+      <c r="D59" s="12" t="s">
         <v>681</v>
       </c>
-      <c r="E59" s="12" t="s">
+      <c r="E59" s="11" t="s">
         <v>682</v>
       </c>
-      <c r="F59" s="12" t="s">
+      <c r="F59" s="11" t="s">
         <v>683</v>
       </c>
-      <c r="G59" s="12" t="s">
+      <c r="G59" s="11" t="s">
         <v>684</v>
       </c>
-      <c r="H59" s="12" t="s">
+      <c r="H59" s="11" t="s">
         <v>685</v>
       </c>
-      <c r="I59" s="12" t="s">
+      <c r="I59" s="11" t="s">
         <v>686</v>
       </c>
-      <c r="J59" s="12" t="s">
+      <c r="J59" s="11" t="s">
         <v>687</v>
       </c>
-      <c r="K59" s="12" t="s">
+      <c r="K59" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="L59" s="12" t="s">
+      <c r="L59" s="11" t="s">
         <v>689</v>
       </c>
-      <c r="M59" s="12" t="s">
+      <c r="M59" s="11" t="s">
         <v>690</v>
       </c>
-      <c r="N59" s="12" t="s">
+      <c r="N59" s="11" t="s">
         <v>691</v>
       </c>
-      <c r="O59" s="12" t="s">
+      <c r="O59" s="11" t="s">
         <v>692</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:16">
-      <c r="B60" s="11">
+      <c r="B60" s="10">
         <v>10055</v>
       </c>
-      <c r="C60" s="13" t="s">
+      <c r="C60" s="12" t="s">
         <v>693</v>
       </c>
-      <c r="D60" s="12" t="s">
+      <c r="D60" s="11" t="s">
         <v>694</v>
       </c>
-      <c r="E60" s="12" t="s">
+      <c r="E60" s="11" t="s">
         <v>695</v>
       </c>
-      <c r="F60" s="12" t="s">
+      <c r="F60" s="11" t="s">
         <v>696</v>
       </c>
-      <c r="G60" s="12" t="s">
+      <c r="G60" s="11" t="s">
         <v>697</v>
       </c>
-      <c r="H60" s="12" t="s">
+      <c r="H60" s="11" t="s">
         <v>698</v>
       </c>
-      <c r="I60" s="12" t="s">
+      <c r="I60" s="11" t="s">
         <v>699</v>
       </c>
-      <c r="J60" s="12" t="s">
+      <c r="J60" s="11" t="s">
         <v>700</v>
       </c>
-      <c r="K60" s="12" t="s">
+      <c r="K60" s="11" t="s">
         <v>701</v>
       </c>
-      <c r="L60" s="12" t="s">
+      <c r="L60" s="11" t="s">
         <v>702</v>
       </c>
-      <c r="M60" s="12" t="s">
+      <c r="M60" s="11" t="s">
         <v>703</v>
       </c>
-      <c r="N60" s="12" t="s">
+      <c r="N60" s="11" t="s">
         <v>704</v>
       </c>
-      <c r="O60" s="12" t="s">
+      <c r="O60" s="11" t="s">
         <v>705</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:16">
-      <c r="B61" s="11">
+      <c r="B61" s="10">
         <v>10056</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="C61" s="11" t="s">
         <v>706</v>
       </c>
-      <c r="D61" s="13" t="s">
+      <c r="D61" s="12" t="s">
         <v>707</v>
       </c>
-      <c r="E61" s="12" t="s">
+      <c r="E61" s="11" t="s">
         <v>708</v>
       </c>
-      <c r="F61" s="12" t="s">
+      <c r="F61" s="11" t="s">
         <v>709</v>
       </c>
-      <c r="G61" s="12" t="s">
+      <c r="G61" s="11" t="s">
         <v>710</v>
       </c>
-      <c r="H61" s="12" t="s">
+      <c r="H61" s="11" t="s">
         <v>711</v>
       </c>
-      <c r="I61" s="12" t="s">
+      <c r="I61" s="11" t="s">
         <v>712</v>
       </c>
-      <c r="J61" s="12" t="s">
+      <c r="J61" s="11" t="s">
         <v>713</v>
       </c>
-      <c r="K61" s="12" t="s">
+      <c r="K61" s="11" t="s">
         <v>714</v>
       </c>
-      <c r="L61" s="12" t="s">
+      <c r="L61" s="11" t="s">
         <v>715</v>
       </c>
-      <c r="M61" s="12" t="s">
+      <c r="M61" s="11" t="s">
         <v>716</v>
       </c>
-      <c r="N61" s="12" t="s">
+      <c r="N61" s="11" t="s">
         <v>717</v>
       </c>
-      <c r="O61" s="12" t="s">
+      <c r="O61" s="11" t="s">
         <v>718</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:16">
-      <c r="B62" s="11">
+      <c r="B62" s="10">
         <v>10057</v>
       </c>
-      <c r="C62" s="12" t="s">
+      <c r="C62" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="D62" s="12" t="s">
+      <c r="D62" s="11" t="s">
         <v>720</v>
       </c>
-      <c r="E62" s="12" t="s">
+      <c r="E62" s="11" t="s">
         <v>721</v>
       </c>
-      <c r="F62" s="12" t="s">
+      <c r="F62" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="G62" s="12" t="s">
+      <c r="G62" s="11" t="s">
         <v>723</v>
       </c>
-      <c r="H62" s="12" t="s">
+      <c r="H62" s="11" t="s">
         <v>724</v>
       </c>
-      <c r="I62" s="12" t="s">
+      <c r="I62" s="11" t="s">
         <v>725</v>
       </c>
-      <c r="J62" s="12" t="s">
+      <c r="J62" s="11" t="s">
         <v>726</v>
       </c>
-      <c r="K62" s="12" t="s">
+      <c r="K62" s="11" t="s">
         <v>727</v>
       </c>
-      <c r="L62" s="12" t="s">
+      <c r="L62" s="11" t="s">
         <v>728</v>
       </c>
-      <c r="M62" s="12" t="s">
+      <c r="M62" s="11" t="s">
         <v>729</v>
       </c>
-      <c r="N62" s="12" t="s">
+      <c r="N62" s="11" t="s">
         <v>730</v>
       </c>
-      <c r="O62" s="12" t="s">
+      <c r="O62" s="11" t="s">
         <v>731</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:16">
-      <c r="B63" s="11">
+      <c r="B63" s="10">
         <v>10058</v>
       </c>
-      <c r="C63" s="12" t="s">
+      <c r="C63" s="11" t="s">
         <v>732</v>
       </c>
-      <c r="D63" s="12" t="s">
+      <c r="D63" s="11" t="s">
         <v>733</v>
       </c>
-      <c r="E63" s="12" t="s">
+      <c r="E63" s="11" t="s">
         <v>734</v>
       </c>
-      <c r="F63" s="12" t="s">
+      <c r="F63" s="11" t="s">
         <v>735</v>
       </c>
-      <c r="G63" s="12" t="s">
+      <c r="G63" s="11" t="s">
         <v>736</v>
       </c>
-      <c r="H63" s="12" t="s">
+      <c r="H63" s="11" t="s">
         <v>737</v>
       </c>
-      <c r="I63" s="12" t="s">
+      <c r="I63" s="11" t="s">
         <v>738</v>
       </c>
-      <c r="J63" s="12" t="s">
+      <c r="J63" s="11" t="s">
         <v>739</v>
       </c>
-      <c r="K63" s="12" t="s">
+      <c r="K63" s="11" t="s">
         <v>740</v>
       </c>
-      <c r="L63" s="12" t="s">
+      <c r="L63" s="11" t="s">
         <v>741</v>
       </c>
-      <c r="M63" s="12" t="s">
+      <c r="M63" s="11" t="s">
         <v>742</v>
       </c>
-      <c r="N63" s="12" t="s">
+      <c r="N63" s="11" t="s">
         <v>743</v>
       </c>
-      <c r="O63" s="12" t="s">
+      <c r="O63" s="11" t="s">
         <v>744</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:16">
-      <c r="B64" s="11">
+      <c r="B64" s="10">
         <v>10059</v>
       </c>
-      <c r="C64" s="12" t="s">
+      <c r="C64" s="11" t="s">
         <v>745</v>
       </c>
-      <c r="D64" s="12" t="s">
+      <c r="D64" s="11" t="s">
         <v>746</v>
       </c>
-      <c r="E64" s="12" t="s">
+      <c r="E64" s="11" t="s">
         <v>747</v>
       </c>
-      <c r="F64" s="12" t="s">
+      <c r="F64" s="11" t="s">
         <v>748</v>
       </c>
-      <c r="G64" s="12" t="s">
+      <c r="G64" s="11" t="s">
         <v>749</v>
       </c>
-      <c r="H64" s="12" t="s">
+      <c r="H64" s="11" t="s">
         <v>750</v>
       </c>
-      <c r="I64" s="12" t="s">
+      <c r="I64" s="11" t="s">
         <v>751</v>
       </c>
-      <c r="J64" s="12" t="s">
+      <c r="J64" s="11" t="s">
         <v>752</v>
       </c>
-      <c r="K64" s="12" t="s">
+      <c r="K64" s="11" t="s">
         <v>753</v>
       </c>
-      <c r="L64" s="12" t="s">
+      <c r="L64" s="11" t="s">
         <v>754</v>
       </c>
-      <c r="M64" s="12" t="s">
+      <c r="M64" s="11" t="s">
         <v>755</v>
       </c>
-      <c r="N64" s="12" t="s">
+      <c r="N64" s="11" t="s">
         <v>756</v>
       </c>
-      <c r="O64" s="12" t="s">
+      <c r="O64" s="11" t="s">
         <v>757</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="2:15">
-      <c r="B65" s="11">
+      <c r="B65" s="10">
         <v>10060</v>
       </c>
-      <c r="C65" s="12" t="s">
+      <c r="C65" s="11" t="s">
         <v>758</v>
       </c>
-      <c r="D65" s="12" t="s">
+      <c r="D65" s="11" t="s">
         <v>759</v>
       </c>
-      <c r="E65" s="12" t="s">
+      <c r="E65" s="11" t="s">
         <v>760</v>
       </c>
-      <c r="F65" s="12" t="s">
+      <c r="F65" s="11" t="s">
         <v>761</v>
       </c>
-      <c r="G65" s="12" t="s">
+      <c r="G65" s="11" t="s">
         <v>762</v>
       </c>
-      <c r="H65" s="12" t="s">
+      <c r="H65" s="11" t="s">
         <v>763</v>
       </c>
-      <c r="I65" s="12" t="s">
+      <c r="I65" s="11" t="s">
         <v>764</v>
       </c>
-      <c r="J65" s="12" t="s">
+      <c r="J65" s="11" t="s">
         <v>765</v>
       </c>
-      <c r="K65" s="12" t="s">
+      <c r="K65" s="11" t="s">
         <v>766</v>
       </c>
-      <c r="L65" s="12" t="s">
+      <c r="L65" s="11" t="s">
         <v>767</v>
       </c>
-      <c r="M65" s="12" t="s">
+      <c r="M65" s="11" t="s">
         <v>768</v>
       </c>
-      <c r="N65" s="12" t="s">
+      <c r="N65" s="11" t="s">
         <v>769</v>
       </c>
-      <c r="O65" s="12" t="s">
+      <c r="O65" s="11" t="s">
         <v>770</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="2:15">
-      <c r="B66" s="11">
+      <c r="B66" s="10">
         <v>10061</v>
       </c>
-      <c r="C66" s="12" t="s">
+      <c r="C66" s="11" t="s">
         <v>771</v>
       </c>
-      <c r="D66" s="12" t="s">
+      <c r="D66" s="11" t="s">
         <v>772</v>
       </c>
-      <c r="E66" s="12" t="s">
+      <c r="E66" s="11" t="s">
         <v>773</v>
       </c>
-      <c r="F66" s="12" t="s">
+      <c r="F66" s="11" t="s">
         <v>774</v>
       </c>
-      <c r="G66" s="12" t="s">
+      <c r="G66" s="11" t="s">
         <v>775</v>
       </c>
-      <c r="H66" s="12" t="s">
+      <c r="H66" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="I66" s="12" t="s">
+      <c r="I66" s="11" t="s">
         <v>777</v>
       </c>
-      <c r="J66" s="12" t="s">
+      <c r="J66" s="11" t="s">
         <v>778</v>
       </c>
-      <c r="K66" s="12" t="s">
+      <c r="K66" s="11" t="s">
         <v>779</v>
       </c>
-      <c r="L66" s="12" t="s">
+      <c r="L66" s="11" t="s">
         <v>780</v>
       </c>
-      <c r="M66" s="12" t="s">
+      <c r="M66" s="11" t="s">
         <v>781</v>
       </c>
-      <c r="N66" s="12" t="s">
+      <c r="N66" s="11" t="s">
         <v>782</v>
       </c>
-      <c r="O66" s="12" t="s">
+      <c r="O66" s="11" t="s">
         <v>783</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="2:15">
-      <c r="B67" s="11">
+      <c r="B67" s="10">
         <v>10062</v>
       </c>
-      <c r="C67" s="12" t="s">
+      <c r="C67" s="11" t="s">
         <v>784</v>
       </c>
-      <c r="D67" s="12" t="s">
+      <c r="D67" s="11" t="s">
         <v>785</v>
       </c>
-      <c r="E67" s="12" t="s">
+      <c r="E67" s="11" t="s">
         <v>786</v>
       </c>
-      <c r="F67" s="12" t="s">
+      <c r="F67" s="11" t="s">
         <v>787</v>
       </c>
-      <c r="G67" s="12" t="s">
+      <c r="G67" s="11" t="s">
         <v>788</v>
       </c>
-      <c r="H67" s="12" t="s">
+      <c r="H67" s="11" t="s">
         <v>789</v>
       </c>
-      <c r="I67" s="12" t="s">
+      <c r="I67" s="11" t="s">
         <v>790</v>
       </c>
-      <c r="J67" s="12" t="s">
+      <c r="J67" s="11" t="s">
         <v>791</v>
       </c>
-      <c r="K67" s="12" t="s">
+      <c r="K67" s="11" t="s">
         <v>792</v>
       </c>
-      <c r="L67" s="12" t="s">
+      <c r="L67" s="11" t="s">
         <v>793</v>
       </c>
-      <c r="M67" s="12" t="s">
+      <c r="M67" s="11" t="s">
         <v>794</v>
       </c>
-      <c r="N67" s="12" t="s">
+      <c r="N67" s="11" t="s">
         <v>795</v>
       </c>
-      <c r="O67" s="12" t="s">
+      <c r="O67" s="11" t="s">
         <v>796</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="2:15">
-      <c r="B68" s="11">
+      <c r="B68" s="10">
         <v>10063</v>
       </c>
-      <c r="C68" s="12" t="s">
+      <c r="C68" s="11" t="s">
         <v>797</v>
       </c>
-      <c r="D68" s="13" t="s">
+      <c r="D68" s="12" t="s">
         <v>798</v>
       </c>
-      <c r="E68" s="12" t="s">
+      <c r="E68" s="11" t="s">
         <v>798</v>
       </c>
-      <c r="F68" s="12" t="s">
+      <c r="F68" s="11" t="s">
         <v>799</v>
       </c>
-      <c r="G68" s="12" t="s">
+      <c r="G68" s="11" t="s">
         <v>798</v>
       </c>
-      <c r="H68" s="12" t="s">
+      <c r="H68" s="11" t="s">
         <v>800</v>
       </c>
-      <c r="I68" s="12" t="s">
+      <c r="I68" s="11" t="s">
         <v>801</v>
       </c>
-      <c r="J68" s="12" t="s">
+      <c r="J68" s="11" t="s">
         <v>802</v>
       </c>
-      <c r="K68" s="12" t="s">
+      <c r="K68" s="11" t="s">
         <v>803</v>
       </c>
-      <c r="L68" s="12" t="s">
+      <c r="L68" s="11" t="s">
         <v>804</v>
       </c>
-      <c r="M68" s="12" t="s">
+      <c r="M68" s="11" t="s">
         <v>805</v>
       </c>
-      <c r="N68" s="12" t="s">
+      <c r="N68" s="11" t="s">
         <v>806</v>
       </c>
-      <c r="O68" s="12" t="s">
+      <c r="O68" s="11" t="s">
         <v>807</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="2:15">
-      <c r="B69" s="11">
+      <c r="B69" s="10">
         <v>10064</v>
       </c>
-      <c r="C69" s="12" t="s">
+      <c r="C69" s="11" t="s">
         <v>808</v>
       </c>
-      <c r="D69" s="12" t="s">
+      <c r="D69" s="11" t="s">
         <v>809</v>
       </c>
-      <c r="E69" s="12" t="s">
+      <c r="E69" s="11" t="s">
         <v>810</v>
       </c>
-      <c r="F69" s="12" t="s">
+      <c r="F69" s="11" t="s">
         <v>811</v>
       </c>
-      <c r="G69" s="12" t="s">
+      <c r="G69" s="11" t="s">
         <v>812</v>
       </c>
-      <c r="H69" s="12" t="s">
+      <c r="H69" s="11" t="s">
         <v>813</v>
       </c>
-      <c r="I69" s="12" t="s">
+      <c r="I69" s="11" t="s">
         <v>814</v>
       </c>
-      <c r="J69" s="12" t="s">
+      <c r="J69" s="11" t="s">
         <v>815</v>
       </c>
-      <c r="K69" s="12" t="s">
+      <c r="K69" s="11" t="s">
         <v>816</v>
       </c>
-      <c r="L69" s="12" t="s">
+      <c r="L69" s="11" t="s">
         <v>817</v>
       </c>
-      <c r="M69" s="12" t="s">
+      <c r="M69" s="11" t="s">
         <v>818</v>
       </c>
-      <c r="N69" s="12" t="s">
+      <c r="N69" s="11" t="s">
         <v>819</v>
       </c>
-      <c r="O69" s="12" t="s">
+      <c r="O69" s="11" t="s">
         <v>820</v>
       </c>
     </row>
     <row r="70" ht="19" customHeight="1" spans="2:15">
-      <c r="B70" s="11">
+      <c r="B70" s="10">
         <v>10065</v>
       </c>
-      <c r="C70" s="12" t="s">
+      <c r="C70" s="11" t="s">
         <v>821</v>
       </c>
-      <c r="D70" s="12" t="s">
+      <c r="D70" s="11" t="s">
         <v>822</v>
       </c>
-      <c r="E70" s="12" t="s">
+      <c r="E70" s="11" t="s">
         <v>823</v>
       </c>
-      <c r="F70" s="12" t="s">
+      <c r="F70" s="11" t="s">
         <v>824</v>
       </c>
-      <c r="G70" s="12" t="s">
+      <c r="G70" s="11" t="s">
         <v>825</v>
       </c>
-      <c r="H70" s="12" t="s">
+      <c r="H70" s="11" t="s">
         <v>826</v>
       </c>
-      <c r="I70" s="12" t="s">
+      <c r="I70" s="11" t="s">
         <v>825</v>
       </c>
-      <c r="J70" s="12" t="s">
+      <c r="J70" s="11" t="s">
         <v>827</v>
       </c>
-      <c r="K70" s="12" t="s">
+      <c r="K70" s="11" t="s">
         <v>828</v>
       </c>
-      <c r="L70" s="12" t="s">
+      <c r="L70" s="11" t="s">
         <v>829</v>
       </c>
-      <c r="M70" s="12" t="s">
+      <c r="M70" s="11" t="s">
         <v>830</v>
       </c>
-      <c r="N70" s="12" t="s">
+      <c r="N70" s="11" t="s">
         <v>831</v>
       </c>
-      <c r="O70" s="12" t="s">
+      <c r="O70" s="11" t="s">
         <v>832</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="2:15">
-      <c r="B71" s="11">
+      <c r="B71" s="10">
         <v>10066</v>
       </c>
-      <c r="C71" s="12" t="s">
+      <c r="C71" s="11" t="s">
         <v>833</v>
       </c>
-      <c r="D71" s="13" t="s">
+      <c r="D71" s="12" t="s">
         <v>834</v>
       </c>
-      <c r="E71" s="12" t="s">
+      <c r="E71" s="11" t="s">
         <v>835</v>
       </c>
-      <c r="F71" s="12" t="s">
+      <c r="F71" s="11" t="s">
         <v>836</v>
       </c>
-      <c r="G71" s="12" t="s">
+      <c r="G71" s="11" t="s">
         <v>837</v>
       </c>
-      <c r="H71" s="12" t="s">
+      <c r="H71" s="11" t="s">
         <v>838</v>
       </c>
-      <c r="I71" s="12" t="s">
+      <c r="I71" s="11" t="s">
         <v>837</v>
       </c>
-      <c r="J71" s="12" t="s">
+      <c r="J71" s="11" t="s">
         <v>839</v>
       </c>
-      <c r="K71" s="12" t="s">
+      <c r="K71" s="11" t="s">
         <v>840</v>
       </c>
-      <c r="L71" s="12" t="s">
+      <c r="L71" s="11" t="s">
         <v>841</v>
       </c>
-      <c r="M71" s="12" t="s">
+      <c r="M71" s="11" t="s">
         <v>842</v>
       </c>
-      <c r="N71" s="12" t="s">
+      <c r="N71" s="11" t="s">
         <v>843</v>
       </c>
-      <c r="O71" s="12" t="s">
+      <c r="O71" s="11" t="s">
         <v>844</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="2:15">
-      <c r="B72" s="11">
+      <c r="B72" s="10">
         <v>10067</v>
       </c>
-      <c r="C72" s="12" t="s">
+      <c r="C72" s="11" t="s">
         <v>845</v>
       </c>
-      <c r="D72" s="13" t="s">
+      <c r="D72" s="12" t="s">
         <v>846</v>
       </c>
-      <c r="E72" s="12" t="s">
+      <c r="E72" s="11" t="s">
         <v>847</v>
       </c>
-      <c r="F72" s="12" t="s">
+      <c r="F72" s="11" t="s">
         <v>848</v>
       </c>
-      <c r="G72" s="12" t="s">
+      <c r="G72" s="11" t="s">
         <v>849</v>
       </c>
-      <c r="H72" s="12" t="s">
+      <c r="H72" s="11" t="s">
         <v>850</v>
       </c>
-      <c r="I72" s="12" t="s">
+      <c r="I72" s="11" t="s">
         <v>849</v>
       </c>
-      <c r="J72" s="12" t="s">
+      <c r="J72" s="11" t="s">
         <v>851</v>
       </c>
-      <c r="K72" s="12" t="s">
+      <c r="K72" s="11" t="s">
         <v>849</v>
       </c>
-      <c r="L72" s="12" t="s">
+      <c r="L72" s="11" t="s">
         <v>852</v>
       </c>
-      <c r="M72" s="12" t="s">
+      <c r="M72" s="11" t="s">
         <v>853</v>
       </c>
-      <c r="N72" s="12" t="s">
+      <c r="N72" s="11" t="s">
         <v>854</v>
       </c>
-      <c r="O72" s="12" t="s">
+      <c r="O72" s="11" t="s">
         <v>855</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="2:15">
-      <c r="B73" s="11">
+      <c r="B73" s="10">
         <v>10068</v>
       </c>
-      <c r="C73" s="12" t="s">
+      <c r="C73" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="D73" s="13" t="s">
+      <c r="D73" s="12" t="s">
         <v>857</v>
       </c>
-      <c r="E73" s="12" t="s">
+      <c r="E73" s="11" t="s">
         <v>858</v>
       </c>
-      <c r="F73" s="12" t="s">
+      <c r="F73" s="11" t="s">
         <v>859</v>
       </c>
-      <c r="G73" s="12" t="s">
+      <c r="G73" s="11" t="s">
         <v>860</v>
       </c>
-      <c r="H73" s="12" t="s">
+      <c r="H73" s="11" t="s">
         <v>861</v>
       </c>
-      <c r="I73" s="12" t="s">
+      <c r="I73" s="11" t="s">
         <v>862</v>
       </c>
-      <c r="J73" s="12" t="s">
+      <c r="J73" s="11" t="s">
         <v>863</v>
       </c>
-      <c r="K73" s="12" t="s">
+      <c r="K73" s="11" t="s">
         <v>864</v>
       </c>
-      <c r="L73" s="12" t="s">
+      <c r="L73" s="11" t="s">
         <v>865</v>
       </c>
-      <c r="M73" s="12" t="s">
+      <c r="M73" s="11" t="s">
         <v>866</v>
       </c>
-      <c r="N73" s="12" t="s">
+      <c r="N73" s="11" t="s">
         <v>867</v>
       </c>
-      <c r="O73" s="12" t="s">
+      <c r="O73" s="11" t="s">
         <v>868</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="2:15">
-      <c r="B74" s="11">
+      <c r="B74" s="10">
         <v>10069</v>
       </c>
-      <c r="C74" s="12" t="s">
+      <c r="C74" s="11" t="s">
         <v>869</v>
       </c>
-      <c r="D74" s="13" t="s">
+      <c r="D74" s="12" t="s">
         <v>870</v>
       </c>
-      <c r="E74" s="12" t="s">
+      <c r="E74" s="11" t="s">
         <v>871</v>
       </c>
-      <c r="F74" s="12" t="s">
+      <c r="F74" s="11" t="s">
         <v>872</v>
       </c>
-      <c r="G74" s="12" t="s">
+      <c r="G74" s="11" t="s">
         <v>873</v>
       </c>
-      <c r="H74" s="12" t="s">
+      <c r="H74" s="11" t="s">
         <v>874</v>
       </c>
-      <c r="I74" s="12" t="s">
+      <c r="I74" s="11" t="s">
         <v>875</v>
       </c>
-      <c r="J74" s="12" t="s">
+      <c r="J74" s="11" t="s">
         <v>876</v>
       </c>
-      <c r="K74" s="12" t="s">
+      <c r="K74" s="11" t="s">
         <v>877</v>
       </c>
-      <c r="L74" s="12" t="s">
+      <c r="L74" s="11" t="s">
         <v>878</v>
       </c>
-      <c r="M74" s="12" t="s">
+      <c r="M74" s="11" t="s">
         <v>879</v>
       </c>
-      <c r="N74" s="12" t="s">
+      <c r="N74" s="11" t="s">
         <v>880</v>
       </c>
-      <c r="O74" s="12" t="s">
+      <c r="O74" s="11" t="s">
         <v>881</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="2:15">
-      <c r="B75" s="11">
+      <c r="B75" s="10">
         <v>10070</v>
       </c>
-      <c r="C75" s="12" t="s">
+      <c r="C75" s="11" t="s">
         <v>882</v>
       </c>
-      <c r="D75" s="12" t="s">
+      <c r="D75" s="11" t="s">
         <v>883</v>
       </c>
-      <c r="E75" s="12" t="s">
+      <c r="E75" s="11" t="s">
         <v>884</v>
       </c>
-      <c r="F75" s="12" t="s">
+      <c r="F75" s="11" t="s">
         <v>885</v>
       </c>
-      <c r="G75" s="12" t="s">
+      <c r="G75" s="11" t="s">
         <v>886</v>
       </c>
-      <c r="H75" s="12" t="s">
+      <c r="H75" s="11" t="s">
         <v>887</v>
       </c>
-      <c r="I75" s="12" t="s">
+      <c r="I75" s="11" t="s">
         <v>888</v>
       </c>
-      <c r="J75" s="12" t="s">
+      <c r="J75" s="11" t="s">
         <v>889</v>
       </c>
-      <c r="K75" s="12" t="s">
+      <c r="K75" s="11" t="s">
         <v>890</v>
       </c>
-      <c r="L75" s="12" t="s">
+      <c r="L75" s="11" t="s">
         <v>891</v>
       </c>
-      <c r="M75" s="12" t="s">
+      <c r="M75" s="11" t="s">
         <v>892</v>
       </c>
-      <c r="N75" s="12" t="s">
+      <c r="N75" s="11" t="s">
         <v>893</v>
       </c>
-      <c r="O75" s="12" t="s">
+      <c r="O75" s="11" t="s">
         <v>894</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="2:15">
-      <c r="B76" s="11">
+      <c r="B76" s="10">
         <v>10071</v>
       </c>
-      <c r="C76" s="12" t="s">
+      <c r="C76" s="11" t="s">
         <v>895</v>
       </c>
-      <c r="D76" s="12" t="s">
+      <c r="D76" s="11" t="s">
         <v>896</v>
       </c>
-      <c r="E76" s="12" t="s">
+      <c r="E76" s="11" t="s">
         <v>897</v>
       </c>
-      <c r="F76" s="12" t="s">
+      <c r="F76" s="11" t="s">
         <v>898</v>
       </c>
-      <c r="G76" s="12" t="s">
+      <c r="G76" s="11" t="s">
         <v>899</v>
       </c>
-      <c r="H76" s="12" t="s">
+      <c r="H76" s="11" t="s">
         <v>900</v>
       </c>
-      <c r="I76" s="12" t="s">
+      <c r="I76" s="11" t="s">
         <v>901</v>
       </c>
-      <c r="J76" s="12" t="s">
+      <c r="J76" s="11" t="s">
         <v>902</v>
       </c>
-      <c r="K76" s="12" t="s">
+      <c r="K76" s="11" t="s">
         <v>903</v>
       </c>
-      <c r="L76" s="12" t="s">
+      <c r="L76" s="11" t="s">
         <v>904</v>
       </c>
-      <c r="M76" s="12" t="s">
+      <c r="M76" s="11" t="s">
         <v>905</v>
       </c>
-      <c r="N76" s="12" t="s">
+      <c r="N76" s="11" t="s">
         <v>906</v>
       </c>
-      <c r="O76" s="12" t="s">
+      <c r="O76" s="11" t="s">
         <v>907</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="2:15">
-      <c r="B77" s="11">
+      <c r="B77" s="10">
         <v>10072</v>
       </c>
-      <c r="C77" s="12" t="s">
+      <c r="C77" s="11" t="s">
         <v>908</v>
       </c>
-      <c r="D77" s="12" t="s">
+      <c r="D77" s="11" t="s">
         <v>909</v>
       </c>
-      <c r="E77" s="12" t="s">
+      <c r="E77" s="11" t="s">
         <v>910</v>
       </c>
-      <c r="F77" s="12" t="s">
+      <c r="F77" s="11" t="s">
         <v>911</v>
       </c>
-      <c r="G77" s="12" t="s">
+      <c r="G77" s="11" t="s">
         <v>912</v>
       </c>
-      <c r="H77" s="12" t="s">
+      <c r="H77" s="11" t="s">
         <v>913</v>
       </c>
-      <c r="I77" s="12" t="s">
+      <c r="I77" s="11" t="s">
         <v>914</v>
       </c>
-      <c r="J77" s="12" t="s">
+      <c r="J77" s="11" t="s">
         <v>915</v>
       </c>
-      <c r="K77" s="12" t="s">
+      <c r="K77" s="11" t="s">
         <v>916</v>
       </c>
-      <c r="L77" s="12" t="s">
+      <c r="L77" s="11" t="s">
         <v>917</v>
       </c>
-      <c r="M77" s="12" t="s">
+      <c r="M77" s="11" t="s">
         <v>918</v>
       </c>
-      <c r="N77" s="12" t="s">
+      <c r="N77" s="11" t="s">
         <v>919</v>
       </c>
-      <c r="O77" s="12" t="s">
+      <c r="O77" s="11" t="s">
         <v>920</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="2:15">
-      <c r="B78" s="11">
+      <c r="B78" s="10">
         <v>10073</v>
       </c>
-      <c r="C78" s="12" t="s">
+      <c r="C78" s="11" t="s">
         <v>921</v>
       </c>
-      <c r="D78" s="13" t="s">
+      <c r="D78" s="12" t="s">
         <v>922</v>
       </c>
-      <c r="E78" s="12" t="s">
+      <c r="E78" s="11" t="s">
         <v>923</v>
       </c>
-      <c r="F78" s="12" t="s">
+      <c r="F78" s="11" t="s">
         <v>924</v>
       </c>
-      <c r="G78" s="12" t="s">
+      <c r="G78" s="11" t="s">
         <v>925</v>
       </c>
-      <c r="H78" s="12" t="s">
+      <c r="H78" s="11" t="s">
         <v>926</v>
       </c>
-      <c r="I78" s="12" t="s">
+      <c r="I78" s="11" t="s">
         <v>927</v>
       </c>
-      <c r="J78" s="12" t="s">
+      <c r="J78" s="11" t="s">
         <v>928</v>
       </c>
-      <c r="K78" s="12" t="s">
+      <c r="K78" s="11" t="s">
         <v>929</v>
       </c>
-      <c r="L78" s="12" t="s">
+      <c r="L78" s="11" t="s">
         <v>930</v>
       </c>
-      <c r="M78" s="12" t="s">
+      <c r="M78" s="11" t="s">
         <v>931</v>
       </c>
-      <c r="N78" s="12" t="s">
+      <c r="N78" s="11" t="s">
         <v>932</v>
       </c>
-      <c r="O78" s="12" t="s">
+      <c r="O78" s="11" t="s">
         <v>933</v>
       </c>
     </row>
     <row r="79" ht="19" customHeight="1" spans="2:15">
-      <c r="B79" s="11">
+      <c r="B79" s="10">
         <v>10074</v>
       </c>
-      <c r="C79" s="13" t="s">
+      <c r="C79" s="12" t="s">
         <v>934</v>
       </c>
-      <c r="D79" s="13" t="s">
+      <c r="D79" s="12" t="s">
         <v>935</v>
       </c>
-      <c r="E79" s="12" t="s">
+      <c r="E79" s="11" t="s">
         <v>936</v>
       </c>
-      <c r="F79" s="12" t="s">
+      <c r="F79" s="11" t="s">
         <v>937</v>
       </c>
-      <c r="G79" s="12" t="s">
+      <c r="G79" s="11" t="s">
         <v>938</v>
       </c>
-      <c r="H79" s="12" t="s">
+      <c r="H79" s="11" t="s">
         <v>939</v>
       </c>
-      <c r="I79" s="12" t="s">
+      <c r="I79" s="11" t="s">
         <v>940</v>
       </c>
-      <c r="J79" s="12" t="s">
+      <c r="J79" s="11" t="s">
         <v>941</v>
       </c>
-      <c r="K79" s="12" t="s">
+      <c r="K79" s="11" t="s">
         <v>942</v>
       </c>
-      <c r="L79" s="12" t="s">
+      <c r="L79" s="11" t="s">
         <v>943</v>
       </c>
-      <c r="M79" s="12" t="s">
+      <c r="M79" s="11" t="s">
         <v>944</v>
       </c>
-      <c r="N79" s="12" t="s">
+      <c r="N79" s="11" t="s">
         <v>945</v>
       </c>
-      <c r="O79" s="12" t="s">
+      <c r="O79" s="11" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="2:15">
-      <c r="B80" s="11">
+      <c r="B80" s="10">
         <v>10075</v>
       </c>
-      <c r="C80" s="12" t="s">
+      <c r="C80" s="11" t="s">
         <v>947</v>
       </c>
-      <c r="D80" s="13" t="s">
+      <c r="D80" s="12" t="s">
         <v>948</v>
       </c>
-      <c r="E80" s="12" t="s">
+      <c r="E80" s="11" t="s">
         <v>949</v>
       </c>
-      <c r="F80" s="12" t="s">
+      <c r="F80" s="11" t="s">
         <v>950</v>
       </c>
-      <c r="G80" s="12" t="s">
+      <c r="G80" s="11" t="s">
         <v>951</v>
       </c>
-      <c r="H80" s="12" t="s">
+      <c r="H80" s="11" t="s">
         <v>952</v>
       </c>
-      <c r="I80" s="12" t="s">
+      <c r="I80" s="11" t="s">
         <v>953</v>
       </c>
-      <c r="J80" s="12" t="s">
+      <c r="J80" s="11" t="s">
         <v>954</v>
       </c>
-      <c r="K80" s="12" t="s">
+      <c r="K80" s="11" t="s">
         <v>955</v>
       </c>
-      <c r="L80" s="12" t="s">
+      <c r="L80" s="11" t="s">
         <v>956</v>
       </c>
-      <c r="M80" s="12" t="s">
+      <c r="M80" s="11" t="s">
         <v>957</v>
       </c>
-      <c r="N80" s="12" t="s">
+      <c r="N80" s="11" t="s">
         <v>958</v>
       </c>
-      <c r="O80" s="12" t="s">
+      <c r="O80" s="11" t="s">
         <v>959</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="2:15">
-      <c r="B81" s="11">
+      <c r="B81" s="10">
         <v>10076</v>
       </c>
-      <c r="C81" s="12" t="s">
+      <c r="C81" s="11" t="s">
         <v>960</v>
       </c>
-      <c r="D81" s="13" t="s">
+      <c r="D81" s="12" t="s">
         <v>961</v>
       </c>
-      <c r="E81" s="12" t="s">
+      <c r="E81" s="11" t="s">
         <v>962</v>
       </c>
-      <c r="F81" s="12" t="s">
+      <c r="F81" s="11" t="s">
         <v>963</v>
       </c>
-      <c r="G81" s="12" t="s">
+      <c r="G81" s="11" t="s">
         <v>964</v>
       </c>
-      <c r="H81" s="12" t="s">
+      <c r="H81" s="11" t="s">
         <v>965</v>
       </c>
-      <c r="I81" s="12" t="s">
+      <c r="I81" s="11" t="s">
         <v>966</v>
       </c>
-      <c r="J81" s="12" t="s">
+      <c r="J81" s="11" t="s">
         <v>967</v>
       </c>
-      <c r="K81" s="12" t="s">
+      <c r="K81" s="11" t="s">
         <v>968</v>
       </c>
-      <c r="L81" s="12" t="s">
+      <c r="L81" s="11" t="s">
         <v>969</v>
       </c>
-      <c r="M81" s="12" t="s">
+      <c r="M81" s="11" t="s">
         <v>970</v>
       </c>
-      <c r="N81" s="12" t="s">
+      <c r="N81" s="11" t="s">
         <v>971</v>
       </c>
-      <c r="O81" s="12" t="s">
+      <c r="O81" s="11" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="2:15">
-      <c r="B82" s="11">
+      <c r="B82" s="10">
         <v>10077</v>
       </c>
-      <c r="C82" s="12" t="s">
+      <c r="C82" s="11" t="s">
         <v>973</v>
       </c>
-      <c r="D82" s="13" t="s">
+      <c r="D82" s="12" t="s">
         <v>974</v>
       </c>
-      <c r="E82" s="12" t="s">
+      <c r="E82" s="11" t="s">
         <v>975</v>
       </c>
-      <c r="F82" s="12" t="s">
+      <c r="F82" s="11" t="s">
         <v>976</v>
       </c>
-      <c r="G82" s="12" t="s">
+      <c r="G82" s="11" t="s">
         <v>977</v>
       </c>
-      <c r="H82" s="12" t="s">
+      <c r="H82" s="11" t="s">
         <v>978</v>
       </c>
-      <c r="I82" s="12" t="s">
+      <c r="I82" s="11" t="s">
         <v>979</v>
       </c>
-      <c r="J82" s="12" t="s">
+      <c r="J82" s="11" t="s">
         <v>980</v>
       </c>
-      <c r="K82" s="12" t="s">
+      <c r="K82" s="11" t="s">
         <v>981</v>
       </c>
-      <c r="L82" s="12" t="s">
+      <c r="L82" s="11" t="s">
         <v>982</v>
       </c>
-      <c r="M82" s="12" t="s">
+      <c r="M82" s="11" t="s">
         <v>983</v>
       </c>
-      <c r="N82" s="12" t="s">
+      <c r="N82" s="11" t="s">
         <v>984</v>
       </c>
-      <c r="O82" s="12" t="s">
+      <c r="O82" s="11" t="s">
         <v>985</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="2:15">
-      <c r="B83" s="11">
+      <c r="B83" s="10">
         <v>10078</v>
       </c>
-      <c r="C83" s="12" t="s">
+      <c r="C83" s="11" t="s">
         <v>986</v>
       </c>
-      <c r="D83" s="13" t="s">
+      <c r="D83" s="12" t="s">
         <v>987</v>
       </c>
-      <c r="E83" s="12" t="s">
+      <c r="E83" s="11" t="s">
         <v>988</v>
       </c>
-      <c r="F83" s="12" t="s">
+      <c r="F83" s="11" t="s">
         <v>989</v>
       </c>
-      <c r="G83" s="12" t="s">
+      <c r="G83" s="11" t="s">
         <v>990</v>
       </c>
-      <c r="H83" s="12" t="s">
+      <c r="H83" s="11" t="s">
         <v>991</v>
       </c>
-      <c r="I83" s="12" t="s">
+      <c r="I83" s="11" t="s">
         <v>992</v>
       </c>
-      <c r="J83" s="12" t="s">
+      <c r="J83" s="11" t="s">
         <v>993</v>
       </c>
-      <c r="K83" s="12" t="s">
+      <c r="K83" s="11" t="s">
         <v>994</v>
       </c>
-      <c r="L83" s="12" t="s">
+      <c r="L83" s="11" t="s">
         <v>995</v>
       </c>
-      <c r="M83" s="12" t="s">
+      <c r="M83" s="11" t="s">
         <v>996</v>
       </c>
-      <c r="N83" s="12" t="s">
+      <c r="N83" s="11" t="s">
         <v>997</v>
       </c>
-      <c r="O83" s="12" t="s">
+      <c r="O83" s="11" t="s">
         <v>998</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="2:15">
-      <c r="B84" s="11">
+      <c r="B84" s="10">
         <v>10079</v>
       </c>
-      <c r="C84" s="12" t="s">
+      <c r="C84" s="11" t="s">
         <v>999</v>
       </c>
-      <c r="D84" s="13" t="s">
+      <c r="D84" s="12" t="s">
         <v>1000</v>
       </c>
-      <c r="E84" s="12" t="s">
+      <c r="E84" s="11" t="s">
         <v>1001</v>
       </c>
-      <c r="F84" s="12" t="s">
+      <c r="F84" s="11" t="s">
         <v>1002</v>
       </c>
-      <c r="G84" s="12" t="s">
+      <c r="G84" s="11" t="s">
         <v>1003</v>
       </c>
-      <c r="H84" s="12" t="s">
+      <c r="H84" s="11" t="s">
         <v>1004</v>
       </c>
-      <c r="I84" s="12" t="s">
+      <c r="I84" s="11" t="s">
         <v>1005</v>
       </c>
-      <c r="J84" s="12" t="s">
+      <c r="J84" s="11" t="s">
         <v>1006</v>
       </c>
-      <c r="K84" s="12" t="s">
+      <c r="K84" s="11" t="s">
         <v>1007</v>
       </c>
-      <c r="L84" s="12" t="s">
+      <c r="L84" s="11" t="s">
         <v>1008</v>
       </c>
-      <c r="M84" s="12" t="s">
+      <c r="M84" s="11" t="s">
         <v>1009</v>
       </c>
-      <c r="N84" s="12" t="s">
+      <c r="N84" s="11" t="s">
         <v>1010</v>
       </c>
-      <c r="O84" s="12" t="s">
+      <c r="O84" s="11" t="s">
         <v>1011</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="2:15">
-      <c r="B85" s="11">
+      <c r="B85" s="10">
         <v>10080</v>
       </c>
-      <c r="C85" s="12" t="s">
+      <c r="C85" s="11" t="s">
         <v>1012</v>
       </c>
-      <c r="D85" s="13" t="s">
+      <c r="D85" s="12" t="s">
         <v>1013</v>
       </c>
-      <c r="E85" s="12" t="s">
+      <c r="E85" s="11" t="s">
         <v>1014</v>
       </c>
-      <c r="F85" s="12" t="s">
+      <c r="F85" s="11" t="s">
         <v>1015</v>
       </c>
-      <c r="G85" s="12" t="s">
+      <c r="G85" s="11" t="s">
         <v>1016</v>
       </c>
-      <c r="H85" s="12" t="s">
+      <c r="H85" s="11" t="s">
         <v>1017</v>
       </c>
-      <c r="I85" s="12" t="s">
+      <c r="I85" s="11" t="s">
         <v>1018</v>
       </c>
-      <c r="J85" s="12" t="s">
+      <c r="J85" s="11" t="s">
         <v>1019</v>
       </c>
-      <c r="K85" s="12" t="s">
+      <c r="K85" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L85" s="12" t="s">
+      <c r="L85" s="11" t="s">
         <v>1021</v>
       </c>
-      <c r="M85" s="12" t="s">
+      <c r="M85" s="11" t="s">
         <v>1022</v>
       </c>
-      <c r="N85" s="12" t="s">
+      <c r="N85" s="11" t="s">
         <v>1023</v>
       </c>
-      <c r="O85" s="12" t="s">
+      <c r="O85" s="11" t="s">
         <v>1024</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="2:15">
-      <c r="B86" s="11">
+      <c r="B86" s="10">
         <v>10081</v>
       </c>
-      <c r="C86" s="12" t="s">
+      <c r="C86" s="11" t="s">
         <v>1025</v>
       </c>
-      <c r="D86" s="13" t="s">
+      <c r="D86" s="12" t="s">
         <v>1026</v>
       </c>
-      <c r="E86" s="12" t="s">
+      <c r="E86" s="11" t="s">
         <v>1027</v>
       </c>
-      <c r="F86" s="12" t="s">
+      <c r="F86" s="11" t="s">
         <v>1028</v>
       </c>
-      <c r="G86" s="12" t="s">
+      <c r="G86" s="11" t="s">
         <v>1029</v>
       </c>
-      <c r="H86" s="12" t="s">
+      <c r="H86" s="11" t="s">
         <v>1030</v>
       </c>
-      <c r="I86" s="12" t="s">
+      <c r="I86" s="11" t="s">
         <v>1031</v>
       </c>
-      <c r="J86" s="12" t="s">
+      <c r="J86" s="11" t="s">
         <v>1032</v>
       </c>
-      <c r="K86" s="12" t="s">
+      <c r="K86" s="11" t="s">
         <v>1033</v>
       </c>
-      <c r="L86" s="12" t="s">
+      <c r="L86" s="11" t="s">
         <v>1034</v>
       </c>
-      <c r="M86" s="12" t="s">
+      <c r="M86" s="11" t="s">
         <v>1035</v>
       </c>
-      <c r="N86" s="12" t="s">
+      <c r="N86" s="11" t="s">
         <v>1036</v>
       </c>
-      <c r="O86" s="12" t="s">
+      <c r="O86" s="11" t="s">
         <v>1037</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="2:15">
-      <c r="B87" s="11">
+      <c r="B87" s="10">
         <v>10082</v>
       </c>
-      <c r="C87" s="12" t="s">
+      <c r="C87" s="11" t="s">
         <v>1038</v>
       </c>
-      <c r="D87" s="13" t="s">
+      <c r="D87" s="12" t="s">
         <v>1039</v>
       </c>
-      <c r="E87" s="12" t="s">
+      <c r="E87" s="11" t="s">
         <v>1040</v>
       </c>
-      <c r="F87" s="12" t="s">
+      <c r="F87" s="11" t="s">
         <v>1041</v>
       </c>
-      <c r="G87" s="12" t="s">
+      <c r="G87" s="11" t="s">
         <v>1042</v>
       </c>
-      <c r="H87" s="12" t="s">
+      <c r="H87" s="11" t="s">
         <v>1043</v>
       </c>
-      <c r="I87" s="12" t="s">
+      <c r="I87" s="11" t="s">
         <v>1044</v>
       </c>
-      <c r="J87" s="12" t="s">
+      <c r="J87" s="11" t="s">
         <v>1045</v>
       </c>
-      <c r="K87" s="12" t="s">
+      <c r="K87" s="11" t="s">
         <v>1046</v>
       </c>
-      <c r="L87" s="12" t="s">
+      <c r="L87" s="11" t="s">
         <v>1047</v>
       </c>
-      <c r="M87" s="12" t="s">
+      <c r="M87" s="11" t="s">
         <v>1048</v>
       </c>
-      <c r="N87" s="12" t="s">
+      <c r="N87" s="11" t="s">
         <v>1049</v>
       </c>
-      <c r="O87" s="12" t="s">
+      <c r="O87" s="11" t="s">
         <v>1050</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="2:15">
-      <c r="B88" s="11">
+      <c r="B88" s="10">
         <v>10083</v>
       </c>
-      <c r="C88" s="12" t="s">
+      <c r="C88" s="11" t="s">
         <v>1051</v>
       </c>
-      <c r="D88" s="13" t="s">
+      <c r="D88" s="12" t="s">
         <v>1052</v>
       </c>
-      <c r="E88" s="12" t="s">
+      <c r="E88" s="11" t="s">
         <v>1053</v>
       </c>
-      <c r="F88" s="12" t="s">
+      <c r="F88" s="11" t="s">
         <v>1054</v>
       </c>
-      <c r="G88" s="12" t="s">
+      <c r="G88" s="11" t="s">
         <v>1055</v>
       </c>
-      <c r="H88" s="12" t="s">
+      <c r="H88" s="11" t="s">
         <v>1056</v>
       </c>
-      <c r="I88" s="12" t="s">
+      <c r="I88" s="11" t="s">
         <v>1057</v>
       </c>
-      <c r="J88" s="12" t="s">
+      <c r="J88" s="11" t="s">
         <v>1058</v>
       </c>
-      <c r="K88" s="12" t="s">
+      <c r="K88" s="11" t="s">
         <v>1059</v>
       </c>
-      <c r="L88" s="12" t="s">
+      <c r="L88" s="11" t="s">
         <v>1060</v>
       </c>
-      <c r="M88" s="12" t="s">
+      <c r="M88" s="11" t="s">
         <v>1061</v>
       </c>
-      <c r="N88" s="12" t="s">
+      <c r="N88" s="11" t="s">
         <v>1062</v>
       </c>
-      <c r="O88" s="12" t="s">
+      <c r="O88" s="11" t="s">
         <v>1063</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="2:15">
-      <c r="B89" s="11">
+      <c r="B89" s="10">
         <v>10084</v>
       </c>
-      <c r="C89" s="12" t="s">
+      <c r="C89" s="11" t="s">
         <v>1064</v>
       </c>
-      <c r="D89" s="13" t="s">
+      <c r="D89" s="12" t="s">
         <v>1065</v>
       </c>
-      <c r="E89" s="12" t="s">
+      <c r="E89" s="11" t="s">
         <v>1066</v>
       </c>
-      <c r="F89" s="12" t="s">
+      <c r="F89" s="11" t="s">
         <v>1067</v>
       </c>
-      <c r="G89" s="12" t="s">
+      <c r="G89" s="11" t="s">
         <v>1068</v>
       </c>
-      <c r="H89" s="12" t="s">
+      <c r="H89" s="11" t="s">
         <v>1069</v>
       </c>
-      <c r="I89" s="12" t="s">
+      <c r="I89" s="11" t="s">
         <v>1068</v>
       </c>
-      <c r="J89" s="12" t="s">
+      <c r="J89" s="11" t="s">
         <v>1070</v>
       </c>
-      <c r="K89" s="12" t="s">
+      <c r="K89" s="11" t="s">
         <v>1071</v>
       </c>
-      <c r="L89" s="12" t="s">
+      <c r="L89" s="11" t="s">
         <v>1072</v>
       </c>
-      <c r="M89" s="12" t="s">
+      <c r="M89" s="11" t="s">
         <v>1073</v>
       </c>
-      <c r="N89" s="12" t="s">
+      <c r="N89" s="11" t="s">
         <v>1074</v>
       </c>
-      <c r="O89" s="12" t="s">
+      <c r="O89" s="11" t="s">
         <v>1075</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="2:15">
-      <c r="B90" s="11">
+      <c r="B90" s="10">
         <v>10085</v>
       </c>
-      <c r="C90" s="12" t="s">
+      <c r="C90" s="11" t="s">
         <v>1076</v>
       </c>
-      <c r="D90" s="13" t="s">
+      <c r="D90" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="E90" s="12" t="s">
+      <c r="E90" s="11" t="s">
         <v>1078</v>
       </c>
-      <c r="F90" s="12" t="s">
+      <c r="F90" s="11" t="s">
         <v>1079</v>
       </c>
-      <c r="G90" s="12" t="s">
+      <c r="G90" s="11" t="s">
         <v>1080</v>
       </c>
-      <c r="H90" s="12" t="s">
+      <c r="H90" s="11" t="s">
         <v>1081</v>
       </c>
-      <c r="I90" s="12" t="s">
+      <c r="I90" s="11" t="s">
         <v>1082</v>
       </c>
-      <c r="J90" s="12" t="s">
+      <c r="J90" s="11" t="s">
         <v>1083</v>
       </c>
-      <c r="K90" s="12" t="s">
+      <c r="K90" s="11" t="s">
         <v>1084</v>
       </c>
-      <c r="L90" s="12" t="s">
+      <c r="L90" s="11" t="s">
         <v>1085</v>
       </c>
-      <c r="M90" s="12" t="s">
+      <c r="M90" s="11" t="s">
         <v>1086</v>
       </c>
-      <c r="N90" s="12" t="s">
+      <c r="N90" s="11" t="s">
         <v>1087</v>
       </c>
-      <c r="O90" s="12" t="s">
+      <c r="O90" s="11" t="s">
         <v>1088</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="2:15">
-      <c r="B91" s="11">
+      <c r="B91" s="10">
         <v>10086</v>
       </c>
-      <c r="C91" s="12" t="s">
+      <c r="C91" s="11" t="s">
         <v>1089</v>
       </c>
-      <c r="D91" s="13" t="s">
+      <c r="D91" s="12" t="s">
         <v>1090</v>
       </c>
-      <c r="E91" s="12" t="s">
+      <c r="E91" s="11" t="s">
         <v>1091</v>
       </c>
-      <c r="F91" s="12" t="s">
+      <c r="F91" s="11" t="s">
         <v>1092</v>
       </c>
-      <c r="G91" s="12" t="s">
+      <c r="G91" s="11" t="s">
         <v>1093</v>
       </c>
-      <c r="H91" s="12" t="s">
+      <c r="H91" s="11" t="s">
         <v>1094</v>
       </c>
-      <c r="I91" s="12" t="s">
+      <c r="I91" s="11" t="s">
         <v>1095</v>
       </c>
-      <c r="J91" s="12" t="s">
+      <c r="J91" s="11" t="s">
         <v>1096</v>
       </c>
-      <c r="K91" s="12" t="s">
+      <c r="K91" s="11" t="s">
         <v>1097</v>
       </c>
-      <c r="L91" s="12" t="s">
+      <c r="L91" s="11" t="s">
         <v>1098</v>
       </c>
-      <c r="M91" s="12" t="s">
+      <c r="M91" s="11" t="s">
         <v>1099</v>
       </c>
-      <c r="N91" s="12" t="s">
+      <c r="N91" s="11" t="s">
         <v>1100</v>
       </c>
-      <c r="O91" s="12" t="s">
+      <c r="O91" s="11" t="s">
         <v>1101</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="2:15">
-      <c r="B92" s="11">
+      <c r="B92" s="10">
         <v>10087</v>
       </c>
-      <c r="C92" s="12" t="s">
+      <c r="C92" s="11" t="s">
         <v>1102</v>
       </c>
-      <c r="D92" s="12" t="s">
+      <c r="D92" s="11" t="s">
         <v>1103</v>
       </c>
-      <c r="E92" s="12" t="s">
+      <c r="E92" s="11" t="s">
         <v>1104</v>
       </c>
-      <c r="F92" s="12" t="s">
+      <c r="F92" s="11" t="s">
         <v>1105</v>
       </c>
-      <c r="G92" s="12" t="s">
+      <c r="G92" s="11" t="s">
         <v>1106</v>
       </c>
-      <c r="H92" s="12" t="s">
+      <c r="H92" s="11" t="s">
         <v>1107</v>
       </c>
-      <c r="I92" s="12" t="s">
+      <c r="I92" s="11" t="s">
         <v>1108</v>
       </c>
-      <c r="J92" s="12" t="s">
+      <c r="J92" s="11" t="s">
         <v>1109</v>
       </c>
-      <c r="K92" s="12" t="s">
+      <c r="K92" s="11" t="s">
         <v>1110</v>
       </c>
-      <c r="L92" s="12" t="s">
+      <c r="L92" s="11" t="s">
         <v>1111</v>
       </c>
-      <c r="M92" s="12" t="s">
+      <c r="M92" s="11" t="s">
         <v>1112</v>
       </c>
-      <c r="N92" s="12" t="s">
+      <c r="N92" s="11" t="s">
         <v>1113</v>
       </c>
-      <c r="O92" s="12" t="s">
+      <c r="O92" s="11" t="s">
         <v>1114</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="2:15">
-      <c r="B93" s="11">
+      <c r="B93" s="10">
         <v>10088</v>
       </c>
-      <c r="C93" s="12" t="s">
+      <c r="C93" s="11" t="s">
         <v>1115</v>
       </c>
-      <c r="D93" s="12" t="s">
+      <c r="D93" s="11" t="s">
         <v>1116</v>
       </c>
-      <c r="E93" s="12" t="s">
+      <c r="E93" s="11" t="s">
         <v>1117</v>
       </c>
-      <c r="F93" s="12" t="s">
+      <c r="F93" s="11" t="s">
         <v>1118</v>
       </c>
-      <c r="G93" s="12" t="s">
+      <c r="G93" s="11" t="s">
         <v>1119</v>
       </c>
-      <c r="H93" s="12" t="s">
+      <c r="H93" s="11" t="s">
         <v>1120</v>
       </c>
-      <c r="I93" s="12" t="s">
+      <c r="I93" s="11" t="s">
         <v>1121</v>
       </c>
-      <c r="J93" s="12" t="s">
+      <c r="J93" s="11" t="s">
         <v>1122</v>
       </c>
-      <c r="K93" s="12" t="s">
+      <c r="K93" s="11" t="s">
         <v>1123</v>
       </c>
-      <c r="L93" s="12" t="s">
+      <c r="L93" s="11" t="s">
         <v>1124</v>
       </c>
-      <c r="M93" s="12" t="s">
+      <c r="M93" s="11" t="s">
         <v>1125</v>
       </c>
-      <c r="N93" s="12" t="s">
+      <c r="N93" s="11" t="s">
         <v>1126</v>
       </c>
-      <c r="O93" s="12" t="s">
+      <c r="O93" s="11" t="s">
         <v>1127</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="2:15">
-      <c r="B94" s="11">
+      <c r="B94" s="10">
         <v>10089</v>
       </c>
-      <c r="C94" s="12" t="s">
+      <c r="C94" s="11" t="s">
         <v>1128</v>
       </c>
-      <c r="D94" s="12" t="s">
+      <c r="D94" s="11" t="s">
         <v>1129</v>
       </c>
-      <c r="E94" s="12" t="s">
+      <c r="E94" s="11" t="s">
         <v>1130</v>
       </c>
-      <c r="F94" s="12" t="s">
+      <c r="F94" s="11" t="s">
         <v>1131</v>
       </c>
-      <c r="G94" s="12" t="s">
+      <c r="G94" s="11" t="s">
         <v>1132</v>
       </c>
-      <c r="H94" s="12" t="s">
+      <c r="H94" s="11" t="s">
         <v>1133</v>
       </c>
-      <c r="I94" s="12" t="s">
+      <c r="I94" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="J94" s="12" t="s">
+      <c r="J94" s="11" t="s">
         <v>1135</v>
       </c>
-      <c r="K94" s="12" t="s">
+      <c r="K94" s="11" t="s">
         <v>1136</v>
       </c>
-      <c r="L94" s="12" t="s">
+      <c r="L94" s="11" t="s">
         <v>1137</v>
       </c>
-      <c r="M94" s="12" t="s">
+      <c r="M94" s="11" t="s">
         <v>1138</v>
       </c>
-      <c r="N94" s="12" t="s">
+      <c r="N94" s="11" t="s">
         <v>1139</v>
       </c>
-      <c r="O94" s="12" t="s">
+      <c r="O94" s="11" t="s">
         <v>1140</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="2:15">
-      <c r="B95" s="11">
+      <c r="B95" s="10">
         <v>10090</v>
       </c>
-      <c r="C95" s="12" t="s">
+      <c r="C95" s="11" t="s">
         <v>1141</v>
       </c>
-      <c r="D95" s="13" t="s">
+      <c r="D95" s="12" t="s">
         <v>1142</v>
       </c>
-      <c r="E95" s="12" t="s">
+      <c r="E95" s="11" t="s">
         <v>1143</v>
       </c>
-      <c r="F95" s="12" t="s">
+      <c r="F95" s="11" t="s">
         <v>1144</v>
       </c>
-      <c r="G95" s="12" t="s">
+      <c r="G95" s="11" t="s">
         <v>1145</v>
       </c>
-      <c r="H95" s="12" t="s">
+      <c r="H95" s="11" t="s">
         <v>1146</v>
       </c>
-      <c r="I95" s="12" t="s">
+      <c r="I95" s="11" t="s">
         <v>1147</v>
       </c>
-      <c r="J95" s="12" t="s">
+      <c r="J95" s="11" t="s">
         <v>1148</v>
       </c>
-      <c r="K95" s="12" t="s">
+      <c r="K95" s="11" t="s">
         <v>1149</v>
       </c>
-      <c r="L95" s="12" t="s">
+      <c r="L95" s="11" t="s">
         <v>1150</v>
       </c>
-      <c r="M95" s="12" t="s">
+      <c r="M95" s="11" t="s">
         <v>1151</v>
       </c>
-      <c r="N95" s="12" t="s">
+      <c r="N95" s="11" t="s">
         <v>1152</v>
       </c>
-      <c r="O95" s="12" t="s">
+      <c r="O95" s="11" t="s">
         <v>1153</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="2:15">
-      <c r="B96" s="11">
+      <c r="B96" s="10">
         <v>10091</v>
       </c>
       <c r="C96" t="s">
@@ -10415,7 +10621,7 @@
       </c>
     </row>
     <row r="97" customHeight="1" spans="1:16">
-      <c r="B97" s="11">
+      <c r="B97" s="10">
         <v>10092</v>
       </c>
       <c r="C97" t="s">
@@ -10459,7 +10665,7 @@
       </c>
     </row>
     <row r="98" customHeight="1" spans="1:16">
-      <c r="B98" s="4">
+      <c r="B98" s="3">
         <v>10093</v>
       </c>
       <c r="C98" t="s">
@@ -10471,28 +10677,28 @@
       <c r="E98" t="s">
         <v>1182</v>
       </c>
-      <c r="F98" s="15" t="s">
+      <c r="F98" s="14" t="s">
         <v>1183</v>
       </c>
-      <c r="G98" s="15" t="s">
+      <c r="G98" s="14" t="s">
         <v>1184</v>
       </c>
       <c r="H98" t="s">
         <v>1185</v>
       </c>
-      <c r="I98" s="15" t="s">
+      <c r="I98" s="14" t="s">
         <v>1186</v>
       </c>
-      <c r="J98" s="15" t="s">
+      <c r="J98" s="14" t="s">
         <v>1187</v>
       </c>
-      <c r="K98" s="15" t="s">
+      <c r="K98" s="14" t="s">
         <v>1188</v>
       </c>
       <c r="L98" t="s">
         <v>1189</v>
       </c>
-      <c r="M98" s="15" t="s">
+      <c r="M98" s="14" t="s">
         <v>1190</v>
       </c>
       <c r="N98" t="s">
@@ -10503,7 +10709,7 @@
       </c>
     </row>
     <row r="99" customHeight="1" spans="1:16">
-      <c r="B99" s="4">
+      <c r="B99" s="3">
         <v>10094</v>
       </c>
       <c r="C99" t="s">
@@ -10524,10 +10730,10 @@
       <c r="H99" t="s">
         <v>1198</v>
       </c>
-      <c r="I99" s="15" t="s">
+      <c r="I99" s="14" t="s">
         <v>1199</v>
       </c>
-      <c r="J99" s="15" t="s">
+      <c r="J99" s="14" t="s">
         <v>1200</v>
       </c>
       <c r="K99" t="s">
@@ -10536,18 +10742,18 @@
       <c r="L99" t="s">
         <v>1202</v>
       </c>
-      <c r="M99" s="15" t="s">
+      <c r="M99" s="14" t="s">
         <v>1203</v>
       </c>
-      <c r="N99" s="15" t="s">
+      <c r="N99" s="14" t="s">
         <v>1204</v>
       </c>
-      <c r="O99" s="15" t="s">
+      <c r="O99" s="14" t="s">
         <v>1205</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="1:16">
-      <c r="B100" s="4">
+      <c r="B100" s="3">
         <v>10095</v>
       </c>
       <c r="C100" t="s">
@@ -10580,18 +10786,18 @@
       <c r="L100" t="s">
         <v>1215</v>
       </c>
-      <c r="M100" s="15" t="s">
+      <c r="M100" s="14" t="s">
         <v>1216</v>
       </c>
-      <c r="N100" s="15" t="s">
+      <c r="N100" s="14" t="s">
         <v>1217</v>
       </c>
-      <c r="O100" s="15" t="s">
+      <c r="O100" s="14" t="s">
         <v>1218</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="1:16">
-      <c r="B101" s="4">
+      <c r="B101" s="3">
         <v>10096</v>
       </c>
       <c r="C101" t="s">
@@ -10603,31 +10809,31 @@
       <c r="E101" t="s">
         <v>1221</v>
       </c>
-      <c r="F101" s="15" t="s">
+      <c r="F101" s="14" t="s">
         <v>1222</v>
       </c>
-      <c r="G101" s="15" t="s">
+      <c r="G101" s="14" t="s">
         <v>1223</v>
       </c>
       <c r="H101" t="s">
         <v>1224</v>
       </c>
-      <c r="I101" s="15" t="s">
+      <c r="I101" s="14" t="s">
         <v>1225</v>
       </c>
-      <c r="J101" s="15" t="s">
+      <c r="J101" s="14" t="s">
         <v>1226</v>
       </c>
-      <c r="K101" s="15" t="s">
+      <c r="K101" s="14" t="s">
         <v>1227</v>
       </c>
-      <c r="L101" s="15" t="s">
+      <c r="L101" s="14" t="s">
         <v>1228</v>
       </c>
-      <c r="M101" s="15" t="s">
+      <c r="M101" s="14" t="s">
         <v>1229</v>
       </c>
-      <c r="N101" s="15" t="s">
+      <c r="N101" s="14" t="s">
         <v>1230</v>
       </c>
       <c r="O101" t="s">
@@ -10635,7 +10841,7 @@
       </c>
     </row>
     <row r="102" customHeight="1" spans="1:16">
-      <c r="B102" s="4">
+      <c r="B102" s="3">
         <v>10097</v>
       </c>
       <c r="C102" t="s">
@@ -10647,28 +10853,28 @@
       <c r="E102" t="s">
         <v>1234</v>
       </c>
-      <c r="F102" s="16" t="s">
+      <c r="F102" s="15" t="s">
         <v>1235</v>
       </c>
-      <c r="G102" s="16" t="s">
+      <c r="G102" s="15" t="s">
         <v>1236</v>
       </c>
       <c r="H102" t="s">
         <v>1237</v>
       </c>
-      <c r="I102" s="15" t="s">
+      <c r="I102" s="14" t="s">
         <v>1238</v>
       </c>
-      <c r="J102" s="15" t="s">
+      <c r="J102" s="14" t="s">
         <v>1239</v>
       </c>
-      <c r="K102" s="15" t="s">
+      <c r="K102" s="14" t="s">
         <v>1240</v>
       </c>
       <c r="L102" t="s">
         <v>1241</v>
       </c>
-      <c r="M102" s="15" t="s">
+      <c r="M102" s="14" t="s">
         <v>1242</v>
       </c>
       <c r="N102" t="s">
@@ -10682,7 +10888,7 @@
       <c r="A103" s="2" t="s">
         <v>1245</v>
       </c>
-      <c r="B103" s="4">
+      <c r="B103" s="3">
         <v>10098</v>
       </c>
       <c r="C103" s="2" t="s">
@@ -10729,57 +10935,57 @@
       </c>
     </row>
     <row r="104" customFormat="1" customHeight="1" spans="1:16">
-      <c r="B104" s="4">
+      <c r="B104" s="3">
         <v>10099</v>
       </c>
-      <c r="C104" s="12" t="s">
+      <c r="C104" s="11" t="s">
         <v>1259</v>
       </c>
-      <c r="D104" s="13" t="s">
+      <c r="D104" s="12" t="s">
         <v>1260</v>
       </c>
-      <c r="E104" s="12" t="s">
+      <c r="E104" s="11" t="s">
         <v>1261</v>
       </c>
-      <c r="F104" s="12" t="s">
+      <c r="F104" s="11" t="s">
         <v>1262</v>
       </c>
-      <c r="G104" s="12" t="s">
+      <c r="G104" s="11" t="s">
         <v>1263</v>
       </c>
-      <c r="H104" s="12" t="s">
+      <c r="H104" s="11" t="s">
         <v>1264</v>
       </c>
-      <c r="I104" s="12" t="s">
+      <c r="I104" s="11" t="s">
         <v>1265</v>
       </c>
-      <c r="J104" s="12" t="s">
+      <c r="J104" s="11" t="s">
         <v>1266</v>
       </c>
-      <c r="K104" s="12" t="s">
+      <c r="K104" s="11" t="s">
         <v>1267</v>
       </c>
-      <c r="L104" s="12" t="s">
+      <c r="L104" s="11" t="s">
         <v>1268</v>
       </c>
-      <c r="M104" s="12" t="s">
+      <c r="M104" s="11" t="s">
         <v>1269</v>
       </c>
-      <c r="N104" s="17" t="s">
+      <c r="N104" s="16" t="s">
         <v>1270</v>
       </c>
-      <c r="O104" s="12" t="s">
+      <c r="O104" s="11" t="s">
         <v>1271</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="B105" s="4">
+      <c r="B105" s="3">
         <v>10100</v>
       </c>
       <c r="C105" t="s">
         <v>1272</v>
       </c>
-      <c r="D105" s="14" t="s">
+      <c r="D105" s="13" t="s">
         <v>153</v>
       </c>
       <c r="E105" t="s">
@@ -10788,7 +10994,7 @@
       <c r="F105" t="s">
         <v>1274</v>
       </c>
-      <c r="G105" s="14" t="s">
+      <c r="G105" s="13" t="s">
         <v>1275</v>
       </c>
       <c r="H105" t="s">
@@ -10800,25 +11006,25 @@
       <c r="J105" t="s">
         <v>1278</v>
       </c>
-      <c r="K105" s="14" t="s">
+      <c r="K105" s="13" t="s">
         <v>1279</v>
       </c>
       <c r="L105" t="s">
         <v>1280</v>
       </c>
-      <c r="M105" s="15" t="s">
+      <c r="M105" s="14" t="s">
         <v>1281</v>
       </c>
-      <c r="N105" s="16" t="s">
+      <c r="N105" s="15" t="s">
         <v>1282</v>
       </c>
-      <c r="O105" s="15" t="s">
+      <c r="O105" s="14" t="s">
         <v>1283</v>
       </c>
       <c r="P105"/>
     </row>
     <row r="106" customHeight="1" spans="1:16">
-      <c r="B106" s="4">
+      <c r="B106" s="3">
         <v>10101</v>
       </c>
       <c r="C106" s="2" t="s">
@@ -10862,43 +11068,43 @@
       </c>
     </row>
     <row r="107" customHeight="1" spans="1:16">
-      <c r="B107" s="4">
+      <c r="B107" s="3">
         <v>10102</v>
       </c>
       <c r="C107" t="s">
         <v>1297</v>
       </c>
-      <c r="D107" s="14" t="s">
+      <c r="D107" s="13" t="s">
         <v>1298</v>
       </c>
       <c r="E107" t="s">
         <v>1299</v>
       </c>
-      <c r="F107" s="15" t="s">
+      <c r="F107" s="14" t="s">
         <v>1300</v>
       </c>
-      <c r="G107" s="15" t="s">
+      <c r="G107" s="14" t="s">
         <v>1301</v>
       </c>
-      <c r="H107" s="15" t="s">
+      <c r="H107" s="14" t="s">
         <v>1302</v>
       </c>
-      <c r="I107" s="15" t="s">
+      <c r="I107" s="14" t="s">
         <v>1303</v>
       </c>
-      <c r="J107" s="15" t="s">
+      <c r="J107" s="14" t="s">
         <v>1304</v>
       </c>
-      <c r="K107" s="15" t="s">
+      <c r="K107" s="14" t="s">
         <v>1305</v>
       </c>
-      <c r="L107" s="15" t="s">
+      <c r="L107" s="14" t="s">
         <v>1306</v>
       </c>
-      <c r="M107" s="15" t="s">
+      <c r="M107" s="14" t="s">
         <v>1307</v>
       </c>
-      <c r="N107" s="15" t="s">
+      <c r="N107" s="14" t="s">
         <v>1308</v>
       </c>
       <c r="O107" t="s">
@@ -10906,13 +11112,13 @@
       </c>
     </row>
     <row r="108" customHeight="1" spans="1:16">
-      <c r="B108" s="4">
+      <c r="B108" s="3">
         <v>10103</v>
       </c>
       <c r="C108" t="s">
         <v>1310</v>
       </c>
-      <c r="D108" s="14" t="s">
+      <c r="D108" s="13" t="s">
         <v>1311</v>
       </c>
       <c r="E108" t="s">
@@ -10921,7 +11127,7 @@
       <c r="F108" t="s">
         <v>1313</v>
       </c>
-      <c r="G108" s="14" t="s">
+      <c r="G108" s="13" t="s">
         <v>1314</v>
       </c>
       <c r="H108" t="s">
@@ -10933,13 +11139,13 @@
       <c r="J108" t="s">
         <v>1317</v>
       </c>
-      <c r="K108" s="15" t="s">
+      <c r="K108" s="14" t="s">
         <v>1318</v>
       </c>
-      <c r="L108" s="15" t="s">
+      <c r="L108" s="14" t="s">
         <v>1319</v>
       </c>
-      <c r="M108" s="15" t="s">
+      <c r="M108" s="14" t="s">
         <v>1320</v>
       </c>
       <c r="N108" t="s">
@@ -10950,13 +11156,13 @@
       </c>
     </row>
     <row r="109" customHeight="1" spans="1:16">
-      <c r="B109" s="4">
+      <c r="B109" s="3">
         <v>10104</v>
       </c>
       <c r="C109" t="s">
         <v>1323</v>
       </c>
-      <c r="D109" s="14" t="s">
+      <c r="D109" s="13" t="s">
         <v>1324</v>
       </c>
       <c r="E109" t="s">
@@ -10965,7 +11171,7 @@
       <c r="F109" t="s">
         <v>1326</v>
       </c>
-      <c r="G109" s="14" t="s">
+      <c r="G109" s="13" t="s">
         <v>1327</v>
       </c>
       <c r="H109" t="s">
@@ -10977,24 +11183,24 @@
       <c r="J109" t="s">
         <v>1330</v>
       </c>
-      <c r="K109" s="15" t="s">
+      <c r="K109" s="14" t="s">
         <v>1331</v>
       </c>
-      <c r="L109" s="15" t="s">
+      <c r="L109" s="14" t="s">
         <v>1332</v>
       </c>
-      <c r="M109" s="15" t="s">
+      <c r="M109" s="14" t="s">
         <v>1333</v>
       </c>
-      <c r="N109" s="15" t="s">
+      <c r="N109" s="14" t="s">
         <v>1334</v>
       </c>
-      <c r="O109" s="15" t="s">
+      <c r="O109" s="14" t="s">
         <v>1335</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="1:16">
-      <c r="B110" s="4">
+      <c r="B110" s="3">
         <v>10105</v>
       </c>
       <c r="C110" t="s">
@@ -11006,75 +11212,75 @@
       <c r="E110" t="s">
         <v>1338</v>
       </c>
-      <c r="F110" s="15" t="s">
+      <c r="F110" s="14" t="s">
         <v>1339</v>
       </c>
-      <c r="G110" s="15" t="s">
+      <c r="G110" s="14" t="s">
         <v>1340</v>
       </c>
-      <c r="H110" s="15" t="s">
+      <c r="H110" s="14" t="s">
         <v>1341</v>
       </c>
-      <c r="I110" s="15" t="s">
+      <c r="I110" s="14" t="s">
         <v>1342</v>
       </c>
-      <c r="J110" s="15" t="s">
+      <c r="J110" s="14" t="s">
         <v>1343</v>
       </c>
-      <c r="K110" s="15" t="s">
+      <c r="K110" s="14" t="s">
         <v>1344</v>
       </c>
       <c r="L110" t="s">
         <v>1345</v>
       </c>
-      <c r="M110" s="16" t="s">
+      <c r="M110" s="15" t="s">
         <v>1346</v>
       </c>
-      <c r="N110" s="16" t="s">
+      <c r="N110" s="15" t="s">
         <v>1347</v>
       </c>
-      <c r="O110" s="16" t="s">
+      <c r="O110" s="15" t="s">
         <v>1348</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="1:16">
-      <c r="B111" s="4">
+      <c r="B111" s="3">
         <v>10106</v>
       </c>
-      <c r="C111" s="18" t="s">
+      <c r="C111" s="17" t="s">
         <v>1349</v>
       </c>
-      <c r="D111" s="14" t="s">
+      <c r="D111" s="13" t="s">
         <v>1350</v>
       </c>
       <c r="E111" t="s">
         <v>1351</v>
       </c>
-      <c r="F111" s="15" t="s">
+      <c r="F111" s="14" t="s">
         <v>1352</v>
       </c>
-      <c r="G111" s="14" t="s">
+      <c r="G111" s="13" t="s">
         <v>1353</v>
       </c>
-      <c r="H111" s="15" t="s">
+      <c r="H111" s="14" t="s">
         <v>1354</v>
       </c>
-      <c r="I111" s="15" t="s">
+      <c r="I111" s="14" t="s">
         <v>1355</v>
       </c>
-      <c r="J111" s="15" t="s">
+      <c r="J111" s="14" t="s">
         <v>1356</v>
       </c>
-      <c r="K111" s="15" t="s">
+      <c r="K111" s="14" t="s">
         <v>1357</v>
       </c>
       <c r="L111" t="s">
         <v>1358</v>
       </c>
-      <c r="M111" s="15" t="s">
+      <c r="M111" s="14" t="s">
         <v>1359</v>
       </c>
-      <c r="N111" s="15" t="s">
+      <c r="N111" s="14" t="s">
         <v>1360</v>
       </c>
       <c r="O111" t="s">
@@ -11082,7 +11288,7 @@
       </c>
     </row>
     <row r="112" customHeight="1" spans="1:16">
-      <c r="B112" s="4">
+      <c r="B112" s="3">
         <v>10107</v>
       </c>
       <c r="C112" t="s">
@@ -11094,7 +11300,7 @@
       <c r="E112" t="s">
         <v>1364</v>
       </c>
-      <c r="F112" s="15" t="s">
+      <c r="F112" s="14" t="s">
         <v>1365</v>
       </c>
       <c r="G112" t="s">
@@ -11103,19 +11309,19 @@
       <c r="H112" t="s">
         <v>1367</v>
       </c>
-      <c r="I112" s="15" t="s">
+      <c r="I112" s="14" t="s">
         <v>1368</v>
       </c>
-      <c r="J112" s="15" t="s">
+      <c r="J112" s="14" t="s">
         <v>1369</v>
       </c>
-      <c r="K112" s="15" t="s">
+      <c r="K112" s="14" t="s">
         <v>1370</v>
       </c>
       <c r="L112" t="s">
         <v>1371</v>
       </c>
-      <c r="M112" s="15" t="s">
+      <c r="M112" s="14" t="s">
         <v>1372</v>
       </c>
       <c r="N112" t="s">
@@ -11125,654 +11331,874 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="113" s="3" customFormat="1" ht="13.5" spans="1:16">
-      <c r="A113" s="3" t="s">
+    <row r="113" s="2" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A113" s="2" t="s">
         <v>1245</v>
       </c>
-      <c r="B113" s="4">
+      <c r="B113" s="3">
         <v>10108</v>
       </c>
-      <c r="C113" s="3" t="s">
+      <c r="C113" s="2" t="s">
         <v>1375</v>
       </c>
-      <c r="D113" s="3" t="s">
+      <c r="D113" s="2" t="s">
         <v>1376</v>
       </c>
-      <c r="E113" s="3" t="s">
+      <c r="E113" s="2" t="s">
         <v>1377</v>
       </c>
-      <c r="F113" s="3" t="s">
+      <c r="F113" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="G113" s="3" t="s">
+      <c r="G113" s="2" t="s">
         <v>1378</v>
       </c>
-      <c r="H113" s="3" t="s">
+      <c r="H113" s="2" t="s">
         <v>1379</v>
       </c>
-      <c r="I113" s="3" t="s">
+      <c r="I113" s="2" t="s">
         <v>1380</v>
       </c>
-      <c r="J113" s="3" t="s">
+      <c r="J113" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="K113" s="3" t="s">
+      <c r="K113" s="2" t="s">
         <v>1381</v>
       </c>
-      <c r="L113" s="3" t="s">
+      <c r="L113" s="2" t="s">
         <v>1382</v>
       </c>
-      <c r="M113" s="3" t="s">
+      <c r="M113" s="2" t="s">
         <v>1383</v>
       </c>
-      <c r="N113" s="3" t="s">
+      <c r="N113" s="2" t="s">
         <v>1384</v>
       </c>
-      <c r="O113" s="3" t="s">
+      <c r="O113" s="2" t="s">
         <v>1385</v>
       </c>
-      <c r="P113" s="3" t="s">
+      <c r="P113" s="2" t="s">
         <v>1245</v>
       </c>
     </row>
-    <row r="114" s="3" customFormat="1" ht="13.5" spans="1:16">
-      <c r="A114" s="3" t="s">
+    <row r="114" s="2" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A114" s="2" t="s">
         <v>1245</v>
       </c>
-      <c r="B114" s="4">
+      <c r="B114" s="3">
         <v>10109</v>
       </c>
-      <c r="C114" s="3" t="s">
+      <c r="C114" s="2" t="s">
         <v>1386</v>
       </c>
-      <c r="D114" s="3" t="s">
+      <c r="D114" s="2" t="s">
         <v>1387</v>
       </c>
-      <c r="E114" s="3" t="s">
+      <c r="E114" s="2" t="s">
         <v>1388</v>
       </c>
-      <c r="F114" s="3" t="s">
+      <c r="F114" s="2" t="s">
         <v>1389</v>
       </c>
-      <c r="G114" s="3" t="s">
+      <c r="G114" s="2" t="s">
         <v>1390</v>
       </c>
-      <c r="H114" s="3" t="s">
+      <c r="H114" s="2" t="s">
         <v>1391</v>
       </c>
-      <c r="I114" s="3" t="s">
+      <c r="I114" s="2" t="s">
         <v>1392</v>
       </c>
-      <c r="J114" s="3" t="s">
+      <c r="J114" s="2" t="s">
         <v>1393</v>
       </c>
-      <c r="K114" s="3" t="s">
+      <c r="K114" s="2" t="s">
         <v>1394</v>
       </c>
-      <c r="L114" s="3" t="s">
+      <c r="L114" s="2" t="s">
         <v>1395</v>
       </c>
-      <c r="M114" s="3" t="s">
+      <c r="M114" s="2" t="s">
         <v>1396</v>
       </c>
-      <c r="N114" s="3" t="s">
+      <c r="N114" s="2" t="s">
         <v>1397</v>
       </c>
-      <c r="O114" s="3" t="s">
+      <c r="O114" s="2" t="s">
         <v>1398</v>
       </c>
-      <c r="P114" s="3" t="s">
+      <c r="P114" s="2" t="s">
         <v>1245</v>
       </c>
     </row>
-    <row r="115" s="3" customFormat="1" ht="13.5" spans="1:16">
-      <c r="A115" s="3" t="s">
+    <row r="115" s="2" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A115" s="2" t="s">
         <v>1245</v>
       </c>
-      <c r="B115" s="4">
+      <c r="B115" s="3">
         <v>10110</v>
       </c>
-      <c r="C115" s="3" t="s">
+      <c r="C115" s="2" t="s">
         <v>1399</v>
       </c>
-      <c r="D115" s="3" t="s">
+      <c r="D115" s="2" t="s">
         <v>1400</v>
       </c>
-      <c r="E115" s="3" t="s">
+      <c r="E115" s="2" t="s">
         <v>1401</v>
       </c>
-      <c r="F115" s="3" t="s">
+      <c r="F115" s="2" t="s">
         <v>1402</v>
       </c>
-      <c r="G115" s="3" t="s">
+      <c r="G115" s="2" t="s">
         <v>1403</v>
       </c>
-      <c r="H115" s="3" t="s">
+      <c r="H115" s="2" t="s">
         <v>1404</v>
       </c>
-      <c r="I115" s="3" t="s">
+      <c r="I115" s="2" t="s">
         <v>1405</v>
       </c>
-      <c r="J115" s="3" t="s">
+      <c r="J115" s="2" t="s">
         <v>1406</v>
       </c>
-      <c r="K115" s="3" t="s">
+      <c r="K115" s="2" t="s">
         <v>1407</v>
       </c>
-      <c r="L115" s="3" t="s">
+      <c r="L115" s="2" t="s">
         <v>1408</v>
       </c>
-      <c r="M115" s="3" t="s">
+      <c r="M115" s="2" t="s">
         <v>1409</v>
       </c>
-      <c r="N115" s="3" t="s">
+      <c r="N115" s="2" t="s">
         <v>1410</v>
       </c>
-      <c r="O115" s="3" t="s">
+      <c r="O115" s="2" t="s">
         <v>1411</v>
       </c>
-      <c r="P115" s="3" t="s">
+      <c r="P115" s="2" t="s">
         <v>1245</v>
       </c>
     </row>
-    <row r="116" s="3" customFormat="1" ht="13.5" spans="1:16">
-      <c r="A116" s="3" t="s">
+    <row r="116" s="2" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A116" s="2" t="s">
         <v>1245</v>
       </c>
-      <c r="B116" s="4">
+      <c r="B116" s="3">
         <v>10111</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="C116" s="2" t="s">
         <v>1412</v>
       </c>
-      <c r="D116" s="3" t="s">
+      <c r="D116" s="2" t="s">
         <v>1413</v>
       </c>
-      <c r="E116" s="3" t="s">
+      <c r="E116" s="2" t="s">
         <v>1414</v>
       </c>
-      <c r="F116" s="3" t="s">
+      <c r="F116" s="2" t="s">
         <v>1415</v>
       </c>
-      <c r="G116" s="3" t="s">
+      <c r="G116" s="2" t="s">
         <v>1416</v>
       </c>
-      <c r="H116" s="3" t="s">
+      <c r="H116" s="2" t="s">
         <v>1417</v>
       </c>
-      <c r="I116" s="3" t="s">
+      <c r="I116" s="2" t="s">
         <v>1418</v>
       </c>
-      <c r="J116" s="3" t="s">
+      <c r="J116" s="2" t="s">
         <v>1419</v>
       </c>
-      <c r="K116" s="3" t="s">
+      <c r="K116" s="2" t="s">
         <v>1420</v>
       </c>
-      <c r="L116" s="3" t="s">
+      <c r="L116" s="2" t="s">
         <v>1421</v>
       </c>
-      <c r="M116" s="3" t="s">
+      <c r="M116" s="2" t="s">
         <v>1422</v>
       </c>
-      <c r="N116" s="3" t="s">
+      <c r="N116" s="2" t="s">
         <v>1423</v>
       </c>
-      <c r="O116" s="3" t="s">
+      <c r="O116" s="2" t="s">
         <v>1424</v>
       </c>
-      <c r="P116" s="3" t="s">
+      <c r="P116" s="2" t="s">
         <v>1245</v>
       </c>
     </row>
-    <row r="117" s="3" customFormat="1" ht="13.5" spans="1:16">
-      <c r="A117" s="3" t="s">
+    <row r="117" s="2" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A117" s="2" t="s">
         <v>1245</v>
       </c>
-      <c r="B117" s="4">
+      <c r="B117" s="3">
         <v>10112</v>
       </c>
-      <c r="C117" s="3" t="s">
+      <c r="C117" s="2" t="s">
         <v>1425</v>
       </c>
-      <c r="D117" s="3" t="s">
+      <c r="D117" s="2" t="s">
         <v>1426</v>
       </c>
-      <c r="E117" s="3" t="s">
+      <c r="E117" s="2" t="s">
         <v>1427</v>
       </c>
-      <c r="F117" s="3" t="s">
+      <c r="F117" s="2" t="s">
         <v>1428</v>
       </c>
-      <c r="G117" s="3" t="s">
+      <c r="G117" s="2" t="s">
         <v>1429</v>
       </c>
-      <c r="H117" s="3" t="s">
+      <c r="H117" s="2" t="s">
         <v>1430</v>
       </c>
-      <c r="I117" s="3" t="s">
+      <c r="I117" s="2" t="s">
         <v>1431</v>
       </c>
-      <c r="J117" s="3" t="s">
+      <c r="J117" s="2" t="s">
         <v>1432</v>
       </c>
-      <c r="K117" s="3" t="s">
+      <c r="K117" s="2" t="s">
         <v>1433</v>
       </c>
-      <c r="L117" s="3" t="s">
+      <c r="L117" s="2" t="s">
         <v>1434</v>
       </c>
-      <c r="M117" s="3" t="s">
+      <c r="M117" s="2" t="s">
         <v>1435</v>
       </c>
-      <c r="N117" s="3" t="s">
+      <c r="N117" s="2" t="s">
         <v>1436</v>
       </c>
-      <c r="O117" s="3" t="s">
+      <c r="O117" s="2" t="s">
         <v>1437</v>
       </c>
-      <c r="P117" s="3" t="s">
+      <c r="P117" s="2" t="s">
         <v>1245</v>
       </c>
     </row>
-    <row r="118" s="3" customFormat="1" ht="13.5" spans="1:16">
-      <c r="A118" s="3" t="s">
+    <row r="118" s="2" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A118" s="2" t="s">
         <v>1245</v>
       </c>
-      <c r="B118" s="4">
+      <c r="B118" s="3">
         <v>10113</v>
       </c>
-      <c r="C118" s="3" t="s">
+      <c r="C118" s="2" t="s">
         <v>1438</v>
       </c>
-      <c r="D118" s="3" t="s">
+      <c r="D118" s="2" t="s">
         <v>1439</v>
       </c>
-      <c r="E118" s="3" t="s">
+      <c r="E118" s="2" t="s">
         <v>1440</v>
       </c>
-      <c r="F118" s="3" t="s">
+      <c r="F118" s="2" t="s">
         <v>1441</v>
       </c>
-      <c r="G118" s="3" t="s">
+      <c r="G118" s="2" t="s">
         <v>1442</v>
       </c>
-      <c r="H118" s="3" t="s">
+      <c r="H118" s="2" t="s">
         <v>1443</v>
       </c>
-      <c r="I118" s="3" t="s">
+      <c r="I118" s="2" t="s">
         <v>1444</v>
       </c>
-      <c r="J118" s="3" t="s">
+      <c r="J118" s="2" t="s">
         <v>1445</v>
       </c>
-      <c r="K118" s="3" t="s">
+      <c r="K118" s="2" t="s">
         <v>1446</v>
       </c>
-      <c r="L118" s="3" t="s">
+      <c r="L118" s="2" t="s">
         <v>1447</v>
       </c>
-      <c r="M118" s="3" t="s">
+      <c r="M118" s="2" t="s">
         <v>1448</v>
       </c>
-      <c r="N118" s="3" t="s">
+      <c r="N118" s="2" t="s">
         <v>1449</v>
       </c>
-      <c r="O118" s="3" t="s">
+      <c r="O118" s="2" t="s">
         <v>1450</v>
       </c>
-      <c r="P118" s="3" t="s">
+      <c r="P118" s="2" t="s">
         <v>1245</v>
       </c>
     </row>
-    <row r="119" s="3" customFormat="1" ht="13.5" spans="1:16">
-      <c r="A119" s="3" t="s">
+    <row r="119" s="2" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A119" s="2" t="s">
         <v>1245</v>
       </c>
-      <c r="B119" s="4">
+      <c r="B119" s="3">
         <v>10114</v>
       </c>
-      <c r="C119" s="3" t="s">
+      <c r="C119" s="2" t="s">
         <v>1451</v>
       </c>
-      <c r="D119" s="3" t="s">
+      <c r="D119" s="2" t="s">
         <v>1452</v>
       </c>
-      <c r="E119" s="3" t="s">
+      <c r="E119" s="2" t="s">
         <v>1453</v>
       </c>
-      <c r="F119" s="3" t="s">
+      <c r="F119" s="2" t="s">
         <v>1454</v>
       </c>
-      <c r="G119" s="3" t="s">
+      <c r="G119" s="2" t="s">
         <v>1455</v>
       </c>
-      <c r="H119" s="3" t="s">
+      <c r="H119" s="2" t="s">
         <v>1456</v>
       </c>
-      <c r="I119" s="3" t="s">
+      <c r="I119" s="2" t="s">
         <v>1457</v>
       </c>
-      <c r="J119" s="3" t="s">
+      <c r="J119" s="2" t="s">
         <v>1458</v>
       </c>
-      <c r="K119" s="3" t="s">
+      <c r="K119" s="2" t="s">
         <v>1459</v>
       </c>
-      <c r="L119" s="3" t="s">
+      <c r="L119" s="2" t="s">
         <v>1460</v>
       </c>
-      <c r="M119" s="3" t="s">
+      <c r="M119" s="2" t="s">
         <v>1461</v>
       </c>
-      <c r="N119" s="3" t="s">
+      <c r="N119" s="2" t="s">
         <v>1462</v>
       </c>
-      <c r="O119" s="3" t="s">
+      <c r="O119" s="2" t="s">
         <v>1463</v>
       </c>
-      <c r="P119" s="3" t="s">
+      <c r="P119" s="2" t="s">
         <v>1245</v>
       </c>
     </row>
-    <row r="120" s="3" customFormat="1" ht="13.5" spans="1:16">
-      <c r="A120" s="3" t="s">
+    <row r="120" s="2" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A120" s="2" t="s">
         <v>1245</v>
       </c>
-      <c r="B120" s="4">
+      <c r="B120" s="3">
         <v>10115</v>
       </c>
-      <c r="C120" s="3" t="s">
+      <c r="C120" s="2" t="s">
         <v>1464</v>
       </c>
-      <c r="D120" s="3" t="s">
+      <c r="D120" s="2" t="s">
         <v>1465</v>
       </c>
-      <c r="E120" s="3" t="s">
+      <c r="E120" s="2" t="s">
         <v>1466</v>
       </c>
-      <c r="F120" s="3" t="s">
+      <c r="F120" s="2" t="s">
         <v>1467</v>
       </c>
-      <c r="G120" s="3" t="s">
+      <c r="G120" s="2" t="s">
         <v>1468</v>
       </c>
-      <c r="H120" s="3" t="s">
+      <c r="H120" s="2" t="s">
         <v>1469</v>
       </c>
-      <c r="I120" s="3" t="s">
+      <c r="I120" s="2" t="s">
         <v>1470</v>
       </c>
-      <c r="J120" s="3" t="s">
+      <c r="J120" s="2" t="s">
         <v>1471</v>
       </c>
-      <c r="K120" s="3" t="s">
+      <c r="K120" s="2" t="s">
         <v>1472</v>
       </c>
-      <c r="L120" s="3" t="s">
+      <c r="L120" s="2" t="s">
         <v>1473</v>
       </c>
-      <c r="M120" s="3" t="s">
+      <c r="M120" s="2" t="s">
         <v>1474</v>
       </c>
-      <c r="N120" s="3" t="s">
+      <c r="N120" s="2" t="s">
         <v>1475</v>
       </c>
-      <c r="O120" s="3" t="s">
+      <c r="O120" s="2" t="s">
         <v>1476</v>
       </c>
-      <c r="P120" s="3" t="s">
+      <c r="P120" s="2" t="s">
         <v>1245</v>
       </c>
     </row>
-    <row r="121" s="3" customFormat="1" ht="13.5" spans="1:16">
-      <c r="A121" s="3" t="s">
+    <row r="121" s="2" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A121" s="2" t="s">
         <v>1245</v>
       </c>
-      <c r="B121" s="4">
+      <c r="B121" s="3">
         <v>10116</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="C121" s="2" t="s">
         <v>1477</v>
       </c>
-      <c r="D121" s="3" t="s">
+      <c r="D121" s="2" t="s">
         <v>1478</v>
       </c>
-      <c r="E121" s="3" t="s">
+      <c r="E121" s="2" t="s">
         <v>1479</v>
       </c>
-      <c r="F121" s="3" t="s">
+      <c r="F121" s="2" t="s">
         <v>1480</v>
       </c>
-      <c r="G121" s="3" t="s">
+      <c r="G121" s="2" t="s">
         <v>1481</v>
       </c>
-      <c r="H121" s="3" t="s">
+      <c r="H121" s="2" t="s">
         <v>1482</v>
       </c>
-      <c r="I121" s="3" t="s">
+      <c r="I121" s="2" t="s">
         <v>1483</v>
       </c>
-      <c r="J121" s="3" t="s">
+      <c r="J121" s="2" t="s">
         <v>1484</v>
       </c>
-      <c r="K121" s="3" t="s">
+      <c r="K121" s="2" t="s">
         <v>1485</v>
       </c>
-      <c r="L121" s="3" t="s">
+      <c r="L121" s="2" t="s">
         <v>1486</v>
       </c>
-      <c r="M121" s="3" t="s">
+      <c r="M121" s="2" t="s">
         <v>1487</v>
       </c>
-      <c r="N121" s="3" t="s">
+      <c r="N121" s="2" t="s">
         <v>1488</v>
       </c>
-      <c r="O121" s="3" t="s">
+      <c r="O121" s="2" t="s">
         <v>1489</v>
       </c>
-      <c r="P121" s="3" t="s">
+      <c r="P121" s="2" t="s">
         <v>1245</v>
       </c>
     </row>
-    <row r="122" s="3" customFormat="1" ht="13.5" spans="1:16">
-      <c r="A122" s="3" t="s">
+    <row r="122" s="2" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A122" s="2" t="s">
         <v>1245</v>
       </c>
-      <c r="B122" s="4">
+      <c r="B122" s="3">
         <v>10117</v>
       </c>
-      <c r="C122" s="3" t="s">
+      <c r="C122" s="2" t="s">
         <v>1490</v>
       </c>
-      <c r="D122" s="3" t="s">
+      <c r="D122" s="2" t="s">
         <v>1491</v>
       </c>
-      <c r="E122" s="3" t="s">
+      <c r="E122" s="2" t="s">
         <v>1492</v>
       </c>
-      <c r="F122" s="3" t="s">
+      <c r="F122" s="2" t="s">
         <v>1493</v>
       </c>
-      <c r="G122" s="3" t="s">
+      <c r="G122" s="2" t="s">
         <v>1494</v>
       </c>
-      <c r="H122" s="3" t="s">
+      <c r="H122" s="2" t="s">
         <v>1495</v>
       </c>
-      <c r="I122" s="3" t="s">
+      <c r="I122" s="2" t="s">
         <v>1494</v>
       </c>
-      <c r="J122" s="3" t="s">
+      <c r="J122" s="2" t="s">
         <v>1496</v>
       </c>
-      <c r="K122" s="3" t="s">
+      <c r="K122" s="2" t="s">
         <v>1497</v>
       </c>
-      <c r="L122" s="3" t="s">
+      <c r="L122" s="2" t="s">
         <v>1498</v>
       </c>
-      <c r="M122" s="3" t="s">
+      <c r="M122" s="2" t="s">
         <v>1499</v>
       </c>
-      <c r="N122" s="3" t="s">
+      <c r="N122" s="2" t="s">
         <v>1500</v>
       </c>
-      <c r="O122" s="3" t="s">
+      <c r="O122" s="2" t="s">
         <v>1501</v>
       </c>
-      <c r="P122" s="3" t="s">
+      <c r="P122" s="2" t="s">
         <v>1245</v>
       </c>
     </row>
-    <row r="123" s="3" customFormat="1" ht="13.5" spans="1:16">
-      <c r="A123" s="3" t="s">
+    <row r="123" s="2" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A123" s="2" t="s">
         <v>1245</v>
       </c>
-      <c r="B123" s="4">
+      <c r="B123" s="3">
         <v>10118</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="C123" s="2" t="s">
         <v>1502</v>
       </c>
-      <c r="D123" s="3" t="s">
+      <c r="D123" s="2" t="s">
         <v>1503</v>
       </c>
-      <c r="E123" s="3" t="s">
+      <c r="E123" s="2" t="s">
         <v>1504</v>
       </c>
-      <c r="F123" s="3" t="s">
+      <c r="F123" s="2" t="s">
         <v>1505</v>
       </c>
-      <c r="G123" s="3" t="s">
+      <c r="G123" s="2" t="s">
         <v>1506</v>
       </c>
-      <c r="H123" s="3" t="s">
+      <c r="H123" s="2" t="s">
         <v>1507</v>
       </c>
-      <c r="I123" s="3" t="s">
+      <c r="I123" s="2" t="s">
         <v>1508</v>
       </c>
-      <c r="J123" s="3" t="s">
+      <c r="J123" s="2" t="s">
         <v>1509</v>
       </c>
-      <c r="K123" s="3" t="s">
+      <c r="K123" s="2" t="s">
         <v>1510</v>
       </c>
-      <c r="L123" s="3" t="s">
+      <c r="L123" s="2" t="s">
         <v>1511</v>
       </c>
-      <c r="M123" s="3" t="s">
+      <c r="M123" s="2" t="s">
         <v>1512</v>
       </c>
-      <c r="N123" s="3" t="s">
+      <c r="N123" s="2" t="s">
         <v>1513</v>
       </c>
-      <c r="O123" s="3" t="s">
+      <c r="O123" s="2" t="s">
         <v>1514</v>
       </c>
-      <c r="P123" s="3" t="s">
+      <c r="P123" s="2" t="s">
         <v>1245</v>
       </c>
     </row>
-    <row r="124" s="3" customFormat="1" ht="13.5" spans="1:16">
-      <c r="A124" s="3" t="s">
+    <row r="124" s="2" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A124" s="2" t="s">
         <v>1245</v>
       </c>
-      <c r="B124" s="4">
+      <c r="B124" s="3">
         <v>10119</v>
       </c>
-      <c r="C124" s="3" t="s">
+      <c r="C124" s="2" t="s">
         <v>1515</v>
       </c>
-      <c r="D124" s="3" t="s">
+      <c r="D124" s="2" t="s">
         <v>1516</v>
       </c>
-      <c r="E124" s="3" t="s">
+      <c r="E124" s="2" t="s">
         <v>1517</v>
       </c>
-      <c r="F124" s="3" t="s">
+      <c r="F124" s="2" t="s">
         <v>1518</v>
       </c>
-      <c r="G124" s="3" t="s">
+      <c r="G124" s="2" t="s">
         <v>1519</v>
       </c>
-      <c r="H124" s="3" t="s">
+      <c r="H124" s="2" t="s">
         <v>1520</v>
       </c>
-      <c r="I124" s="3" t="s">
+      <c r="I124" s="2" t="s">
         <v>1521</v>
       </c>
-      <c r="J124" s="3" t="s">
+      <c r="J124" s="2" t="s">
         <v>1522</v>
       </c>
-      <c r="K124" s="3" t="s">
+      <c r="K124" s="2" t="s">
         <v>1523</v>
       </c>
-      <c r="L124" s="3" t="s">
+      <c r="L124" s="2" t="s">
         <v>1524</v>
       </c>
-      <c r="M124" s="3" t="s">
+      <c r="M124" s="2" t="s">
         <v>1525</v>
       </c>
-      <c r="N124" s="3" t="s">
+      <c r="N124" s="2" t="s">
         <v>1526</v>
       </c>
-      <c r="O124" s="3" t="s">
+      <c r="O124" s="2" t="s">
         <v>1527</v>
       </c>
-      <c r="P124" s="3" t="s">
+      <c r="P124" s="2" t="s">
         <v>1245</v>
       </c>
     </row>
-    <row r="125" s="3" customFormat="1" ht="27" spans="1:16">
-      <c r="A125" s="3" t="s">
+    <row r="125" s="2" customFormat="1" ht="27" spans="1:16">
+      <c r="A125" s="2" t="s">
         <v>1245</v>
       </c>
-      <c r="B125" s="4">
+      <c r="B125" s="3">
         <v>10120</v>
       </c>
-      <c r="C125" s="19" t="s">
+      <c r="C125" s="18" t="s">
         <v>1528</v>
       </c>
-      <c r="D125" s="3" t="s">
+      <c r="D125" s="2" t="s">
         <v>1529</v>
       </c>
-      <c r="E125" s="3" t="s">
+      <c r="E125" s="2" t="s">
         <v>1529</v>
       </c>
-      <c r="F125" s="3" t="s">
+      <c r="F125" s="2" t="s">
         <v>1530</v>
       </c>
-      <c r="G125" s="3" t="s">
+      <c r="G125" s="2" t="s">
         <v>1531</v>
       </c>
-      <c r="H125" s="3" t="s">
+      <c r="H125" s="2" t="s">
         <v>1532</v>
       </c>
-      <c r="I125" s="3" t="s">
+      <c r="I125" s="2" t="s">
         <v>1533</v>
       </c>
-      <c r="J125" s="3" t="s">
+      <c r="J125" s="2" t="s">
         <v>1534</v>
       </c>
-      <c r="K125" s="3" t="s">
+      <c r="K125" s="2" t="s">
         <v>1529</v>
       </c>
-      <c r="L125" s="3" t="s">
+      <c r="L125" s="2" t="s">
         <v>1535</v>
       </c>
-      <c r="M125" s="3" t="s">
+      <c r="M125" s="2" t="s">
         <v>1536</v>
       </c>
-      <c r="N125" s="3" t="s">
+      <c r="N125" s="2" t="s">
         <v>1537</v>
       </c>
-      <c r="O125" s="3" t="s">
+      <c r="O125" s="2" t="s">
         <v>1538</v>
       </c>
-      <c r="P125" s="3" t="s">
+      <c r="P125" s="2" t="s">
         <v>1245</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" spans="1:16">
+      <c r="B126" s="3">
+        <v>10121</v>
+      </c>
+      <c r="C126" t="s">
+        <v>1539</v>
+      </c>
+      <c r="D126" s="19" t="s">
+        <v>1540</v>
+      </c>
+      <c r="E126" s="20" t="s">
+        <v>1541</v>
+      </c>
+      <c r="F126" s="20" t="s">
+        <v>1542</v>
+      </c>
+      <c r="G126" s="20" t="s">
+        <v>1543</v>
+      </c>
+      <c r="H126" s="20" t="s">
+        <v>1544</v>
+      </c>
+      <c r="I126" s="20" t="s">
+        <v>1545</v>
+      </c>
+      <c r="J126" s="20" t="s">
+        <v>1546</v>
+      </c>
+      <c r="K126" s="20" t="s">
+        <v>1547</v>
+      </c>
+      <c r="L126" s="20" t="s">
+        <v>1548</v>
+      </c>
+      <c r="M126" s="20" t="s">
+        <v>1549</v>
+      </c>
+      <c r="N126" s="20" t="s">
+        <v>1550</v>
+      </c>
+      <c r="O126" s="20" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="1:16">
+      <c r="B127" s="3">
+        <v>10122</v>
+      </c>
+      <c r="C127" t="s">
+        <v>1552</v>
+      </c>
+      <c r="D127" s="19" t="s">
+        <v>1553</v>
+      </c>
+      <c r="E127" s="20" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F127" s="20" t="s">
+        <v>1555</v>
+      </c>
+      <c r="G127" s="20" t="s">
+        <v>1556</v>
+      </c>
+      <c r="H127" s="20" t="s">
+        <v>1557</v>
+      </c>
+      <c r="I127" s="20" t="s">
+        <v>1558</v>
+      </c>
+      <c r="J127" s="20" t="s">
+        <v>1559</v>
+      </c>
+      <c r="K127" s="20" t="s">
+        <v>1560</v>
+      </c>
+      <c r="L127" s="20" t="s">
+        <v>1561</v>
+      </c>
+      <c r="M127" s="20" t="s">
+        <v>1562</v>
+      </c>
+      <c r="N127" s="20" t="s">
+        <v>1563</v>
+      </c>
+      <c r="O127" s="20" t="s">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" spans="1:16">
+      <c r="B128" s="3">
+        <v>10123</v>
+      </c>
+      <c r="C128" t="s">
+        <v>1565</v>
+      </c>
+      <c r="D128" s="19" t="s">
+        <v>1566</v>
+      </c>
+      <c r="E128" s="20" t="s">
+        <v>1567</v>
+      </c>
+      <c r="F128" s="20" t="s">
+        <v>1568</v>
+      </c>
+      <c r="G128" s="20" t="s">
+        <v>1569</v>
+      </c>
+      <c r="H128" s="20" t="s">
+        <v>1570</v>
+      </c>
+      <c r="I128" s="20" t="s">
+        <v>1571</v>
+      </c>
+      <c r="J128" s="20" t="s">
+        <v>1572</v>
+      </c>
+      <c r="K128" s="20" t="s">
+        <v>1573</v>
+      </c>
+      <c r="L128" s="20" t="s">
+        <v>1574</v>
+      </c>
+      <c r="M128" s="20" t="s">
+        <v>1575</v>
+      </c>
+      <c r="N128" s="20" t="s">
+        <v>1576</v>
+      </c>
+      <c r="O128" s="20" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" spans="2:15">
+      <c r="B129" s="3">
+        <v>10124</v>
+      </c>
+      <c r="C129" t="s">
+        <v>1578</v>
+      </c>
+      <c r="D129" s="19" t="s">
+        <v>1579</v>
+      </c>
+      <c r="E129" s="20" t="s">
+        <v>1580</v>
+      </c>
+      <c r="F129" s="20" t="s">
+        <v>1581</v>
+      </c>
+      <c r="G129" s="20" t="s">
+        <v>1582</v>
+      </c>
+      <c r="H129" s="20" t="s">
+        <v>1583</v>
+      </c>
+      <c r="I129" s="20" t="s">
+        <v>1584</v>
+      </c>
+      <c r="J129" s="20" t="s">
+        <v>1585</v>
+      </c>
+      <c r="K129" s="20" t="s">
+        <v>1586</v>
+      </c>
+      <c r="L129" s="20" t="s">
+        <v>1587</v>
+      </c>
+      <c r="M129" s="20" t="s">
+        <v>1588</v>
+      </c>
+      <c r="N129" s="20" t="s">
+        <v>1589</v>
+      </c>
+      <c r="O129" s="20" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" spans="2:15">
+      <c r="B130" s="3">
+        <v>10125</v>
+      </c>
+      <c r="C130" t="s">
+        <v>1591</v>
+      </c>
+      <c r="D130" s="19" t="s">
+        <v>1592</v>
+      </c>
+      <c r="E130" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="F130" s="20" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G130" s="20" t="s">
+        <v>1595</v>
+      </c>
+      <c r="H130" s="20" t="s">
+        <v>1596</v>
+      </c>
+      <c r="I130" s="20" t="s">
+        <v>1597</v>
+      </c>
+      <c r="J130" s="20" t="s">
+        <v>1598</v>
+      </c>
+      <c r="K130" s="20" t="s">
+        <v>1599</v>
+      </c>
+      <c r="L130" s="20" t="s">
+        <v>1600</v>
+      </c>
+      <c r="M130" s="20" t="s">
+        <v>1601</v>
+      </c>
+      <c r="N130" s="20" t="s">
+        <v>1602</v>
+      </c>
+      <c r="O130" s="20" t="s">
+        <v>1603</v>
       </c>
     </row>
   </sheetData>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="1604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="1610">
   <si>
     <t>##var</t>
   </si>
@@ -1115,220 +1115,406 @@
     <t>Döndür</t>
   </si>
   <si>
-    <t>道具1</t>
-  </si>
-  <si>
-    <t>Prop1</t>
-  </si>
-  <si>
-    <t>Item 1</t>
-  </si>
-  <si>
-    <t>アイテム1</t>
-  </si>
-  <si>
-    <t>Objet 1</t>
-  </si>
-  <si>
-    <t>Objeto 1</t>
-  </si>
-  <si>
-    <t>아이템 1</t>
-  </si>
-  <si>
-    <t>Предмет 1</t>
-  </si>
-  <si>
-    <t>आइटम 1</t>
-  </si>
-  <si>
-    <t>ไอเทม 1</t>
-  </si>
-  <si>
-    <t>Eşya 1</t>
-  </si>
-  <si>
-    <t>道具1介绍</t>
-  </si>
-  <si>
-    <t>Prop1 Introduction</t>
-  </si>
-  <si>
-    <t>Item 1 Beschreibung</t>
-  </si>
-  <si>
-    <t>アイテム1説明</t>
-  </si>
-  <si>
-    <t>Descrição do Item 1</t>
-  </si>
-  <si>
-    <t>Description de l'Objet 1</t>
-  </si>
-  <si>
-    <t>Descripción del Objeto 1</t>
-  </si>
-  <si>
-    <t>아이템 1 설명</t>
-  </si>
-  <si>
-    <t>Deskripsi Item 1</t>
-  </si>
-  <si>
-    <t>Описание Предмета 1</t>
-  </si>
-  <si>
-    <t>आइटम 1 का विवरण</t>
-  </si>
-  <si>
-    <t>คำอธิบายไอเทม 1</t>
-  </si>
-  <si>
-    <t>Eşya 1 Açıklaması</t>
-  </si>
-  <si>
-    <t>道具2</t>
-  </si>
-  <si>
-    <t>Prop2</t>
-  </si>
-  <si>
-    <t>Item 2</t>
-  </si>
-  <si>
-    <t>アイテム2</t>
-  </si>
-  <si>
-    <t>Objet 2</t>
-  </si>
-  <si>
-    <t>Objeto 2</t>
-  </si>
-  <si>
-    <t>아이템 2</t>
-  </si>
-  <si>
-    <t>Предмет 2</t>
-  </si>
-  <si>
-    <t>आइटम 2</t>
-  </si>
-  <si>
-    <t>ไอเทม 2</t>
-  </si>
-  <si>
-    <t>Eşya 2</t>
-  </si>
-  <si>
-    <t>道具2介绍</t>
-  </si>
-  <si>
-    <t>Prop2 Introduction</t>
-  </si>
-  <si>
-    <t>Item 2 Beschreibung</t>
-  </si>
-  <si>
-    <t>アイテム2説明</t>
-  </si>
-  <si>
-    <t>Descrição do Item 2</t>
-  </si>
-  <si>
-    <t>Description de l'Objet 2</t>
-  </si>
-  <si>
-    <t>Descripción del Objeto 2</t>
-  </si>
-  <si>
-    <t>아이템 2 설명</t>
-  </si>
-  <si>
-    <t>Deskripsi Item 2</t>
-  </si>
-  <si>
-    <t>Описание Предмета 2</t>
-  </si>
-  <si>
-    <t>आइटम 2 का विवरण</t>
-  </si>
-  <si>
-    <t>คำอธิบายไอเทม 2</t>
-  </si>
-  <si>
-    <t>Eşya 2 Açıklaması</t>
-  </si>
-  <si>
-    <t>道具3</t>
-  </si>
-  <si>
-    <t>Prop3</t>
-  </si>
-  <si>
-    <t>Item 3</t>
-  </si>
-  <si>
-    <t>アイテム3</t>
-  </si>
-  <si>
-    <t>Objet 3</t>
-  </si>
-  <si>
-    <t>Objeto 3</t>
-  </si>
-  <si>
-    <t>아이템 3</t>
-  </si>
-  <si>
-    <t>Предмет 3</t>
-  </si>
-  <si>
-    <t>आइटम 3</t>
-  </si>
-  <si>
-    <t>ไอเทม 3</t>
-  </si>
-  <si>
-    <t>Eşya 3</t>
-  </si>
-  <si>
-    <t>道具3介绍</t>
-  </si>
-  <si>
-    <t>Prop3 Introduction</t>
-  </si>
-  <si>
-    <t>Item 3 Beschreibung</t>
-  </si>
-  <si>
-    <t>アイテム3説明</t>
-  </si>
-  <si>
-    <t>Descrição do Item 3</t>
-  </si>
-  <si>
-    <t>Description de l'Objet 3</t>
-  </si>
-  <si>
-    <t>Descripción del Objeto 3</t>
-  </si>
-  <si>
-    <t>아이템 3 설명</t>
-  </si>
-  <si>
-    <t>Deskripsi Item 3</t>
-  </si>
-  <si>
-    <t>Описание Предмета 3</t>
-  </si>
-  <si>
-    <t>आइटम 3 का विवरण</t>
-  </si>
-  <si>
-    <t>คำอธิบายไอเทม 3</t>
-  </si>
-  <si>
-    <t>Eşya 3 Açıklaması</t>
+    <t>刷新</t>
+  </si>
+  <si>
+    <t>Refresh</t>
+  </si>
+  <si>
+    <t>Aktualisieren</t>
+  </si>
+  <si>
+    <t>更新</t>
+  </si>
+  <si>
+    <t>Atualizar</t>
+  </si>
+  <si>
+    <t>Actualiser</t>
+  </si>
+  <si>
+    <t>Actualizar</t>
+  </si>
+  <si>
+    <t>새로 고침</t>
+  </si>
+  <si>
+    <t>Muat Ulang</t>
+  </si>
+  <si>
+    <t>Обновить</t>
+  </si>
+  <si>
+    <t>ताज़ा करें</t>
+  </si>
+  <si>
+    <t>รีเฟรช</t>
+  </si>
+  <si>
+    <t>Yenile</t>
+  </si>
+  <si>
+    <t>刷新一个瓶子中的颜色排序</t>
+  </si>
+  <si>
+    <t>Refresh the color sorting inside a bottle</t>
+  </si>
+  <si>
+    <t>Farbreihenfolge in Flasche neu ordnen</t>
+  </si>
+  <si>
+    <t>瓶内色順再整頓</t>
+  </si>
+  <si>
+    <t>Reordenar cores da garrafa</t>
+  </si>
+  <si>
+    <t>Réorganiser couleurs bouteille</t>
+  </si>
+  <si>
+    <t>Reordenar colores botella</t>
+  </si>
+  <si>
+    <t>병 색상 정렬 재설정</t>
+  </si>
+  <si>
+    <t>Urutkan warna botol</t>
+  </si>
+  <si>
+    <t>Пересортировать цвета в бутылке</t>
+  </si>
+  <si>
+    <t>बोतल में रंग क्रम पुनर्व्यवस्थित करें</t>
+  </si>
+  <si>
+    <t>จัดลำดับสีในขวดใหม่</t>
+  </si>
+  <si>
+    <r>
+      <t>Ş</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ş</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>e renk s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ı</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ralamas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ı</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ı</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> yenile</t>
+    </r>
+  </si>
+  <si>
+    <t>撤销</t>
+  </si>
+  <si>
+    <t>Undo</t>
+  </si>
+  <si>
+    <t>Rückgängig</t>
+  </si>
+  <si>
+    <t>元に戻す</t>
+  </si>
+  <si>
+    <t>Desfazer</t>
+  </si>
+  <si>
+    <t>Annuler</t>
+  </si>
+  <si>
+    <t>Deshacer</t>
+  </si>
+  <si>
+    <t>실행 취소</t>
+  </si>
+  <si>
+    <t>Batalkan</t>
+  </si>
+  <si>
+    <t>Отменить</t>
+  </si>
+  <si>
+    <t>पूर्ववत करें</t>
+  </si>
+  <si>
+    <t>ย้อนกลับ</t>
+  </si>
+  <si>
+    <t>Geri Al</t>
+  </si>
+  <si>
+    <t>撤销上一步操作</t>
+  </si>
+  <si>
+    <t>Undo the previous operation</t>
+  </si>
+  <si>
+    <t>Letzten Schritt rückgängig machen</t>
+  </si>
+  <si>
+    <t>直前操作取消</t>
+  </si>
+  <si>
+    <t>Desfazer última ação</t>
+  </si>
+  <si>
+    <t>Annuler dernière action</t>
+  </si>
+  <si>
+    <t>Deshacer última acción</t>
+  </si>
+  <si>
+    <t>이전 작업 취소</t>
+  </si>
+  <si>
+    <t>Batalkan langkah terakhir</t>
+  </si>
+  <si>
+    <t>Отменить последнее действие</t>
+  </si>
+  <si>
+    <t>पिछला कार्य रद्द करें</t>
+  </si>
+  <si>
+    <t>ย้อนการทำงานล่าสุด</t>
+  </si>
+  <si>
+    <t>Son adımı geri al</t>
+  </si>
+  <si>
+    <t>添加瓶子</t>
+  </si>
+  <si>
+    <t>Add Bottle</t>
+  </si>
+  <si>
+    <t>Flasche hinzufügen</t>
+  </si>
+  <si>
+    <t>瓶追加</t>
+  </si>
+  <si>
+    <t>Adicionar Garrafa</t>
+  </si>
+  <si>
+    <t>Ajouter bouteille</t>
+  </si>
+  <si>
+    <t>Añadir botella</t>
+  </si>
+  <si>
+    <t>병 추가</t>
+  </si>
+  <si>
+    <t>Tambah Botol</t>
+  </si>
+  <si>
+    <t>Добавить бутылку</t>
+  </si>
+  <si>
+    <t>बोतल जोड़ें</t>
+  </si>
+  <si>
+    <t>เพิ่มขวด</t>
+  </si>
+  <si>
+    <r>
+      <t>Ş</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ş</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>e Ekle</t>
+    </r>
+  </si>
+  <si>
+    <t>添加一个空瓶子</t>
+  </si>
+  <si>
+    <t>Add an empty bottle</t>
+  </si>
+  <si>
+    <t>Leere Flasche hinzufügen</t>
+  </si>
+  <si>
+    <t>空瓶追加</t>
+  </si>
+  <si>
+    <t>Adicionar garrafa vazia</t>
+  </si>
+  <si>
+    <t>Ajouter bouteille vide</t>
+  </si>
+  <si>
+    <t>Añadir botella vacía</t>
+  </si>
+  <si>
+    <t>빈 병 추가</t>
+  </si>
+  <si>
+    <t>Tambah botol kosong</t>
+  </si>
+  <si>
+    <t>Добавить пустую бутылку</t>
+  </si>
+  <si>
+    <t>खाली बोतल जोड़ें</t>
+  </si>
+  <si>
+    <t>เพิ่มขวดเปล่า</t>
+  </si>
+  <si>
+    <r>
+      <t>Bo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ş</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ş</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ş</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>e ekle</t>
+    </r>
   </si>
   <si>
     <t>当前关卡进度</t>
@@ -5039,7 +5225,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5061,9 +5247,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11.25"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="MS Gothic"/>
       <charset val="134"/>
     </font>
     <font>
@@ -5075,7 +5261,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11.25"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -5214,18 +5406,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="MS Gothic"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="35">
@@ -5575,16 +5755,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5593,115 +5770,118 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5739,29 +5919,29 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -7713,31 +7893,31 @@
         <v>365</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>367</v>
-      </c>
-      <c r="J32" s="11" t="s">
         <v>368</v>
       </c>
+      <c r="J32" s="13" t="s">
+        <v>369</v>
+      </c>
       <c r="K32" s="11" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M32" s="11" t="s">
-        <v>370</v>
-      </c>
-      <c r="N32" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
+      </c>
+      <c r="N32" s="14" t="s">
+        <v>373</v>
       </c>
       <c r="O32" s="11" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="P32"/>
     </row>
@@ -7746,43 +7926,43 @@
         <v>10028</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>379</v>
-      </c>
-      <c r="J33" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
+      </c>
+      <c r="J33" s="13" t="s">
+        <v>382</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="M33" s="11" t="s">
-        <v>383</v>
-      </c>
-      <c r="N33" s="11" t="s">
-        <v>384</v>
-      </c>
-      <c r="O33" s="11" t="s">
         <v>385</v>
+      </c>
+      <c r="N33" s="14" t="s">
+        <v>386</v>
+      </c>
+      <c r="O33" s="15" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
@@ -7790,43 +7970,43 @@
         <v>10029</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>391</v>
-      </c>
-      <c r="J34" s="11" t="s">
-        <v>392</v>
+        <v>394</v>
+      </c>
+      <c r="J34" s="13" t="s">
+        <v>395</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="L34" s="11" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="M34" s="11" t="s">
-        <v>394</v>
-      </c>
-      <c r="N34" s="11" t="s">
-        <v>395</v>
+        <v>398</v>
+      </c>
+      <c r="N34" s="14" t="s">
+        <v>399</v>
       </c>
       <c r="O34" s="11" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q34"/>
       <c r="R34"/>
@@ -7841,43 +8021,43 @@
         <v>10030</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>403</v>
-      </c>
-      <c r="J35" s="11" t="s">
-        <v>404</v>
+        <v>407</v>
+      </c>
+      <c r="J35" s="13" t="s">
+        <v>408</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="L35" s="11" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="M35" s="11" t="s">
-        <v>407</v>
-      </c>
-      <c r="N35" s="11" t="s">
-        <v>408</v>
+        <v>411</v>
+      </c>
+      <c r="N35" s="14" t="s">
+        <v>412</v>
       </c>
       <c r="O35" s="11" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="P35"/>
       <c r="Q35"/>
@@ -7893,43 +8073,43 @@
         <v>10031</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>415</v>
-      </c>
-      <c r="J36" s="11" t="s">
-        <v>416</v>
+        <v>420</v>
+      </c>
+      <c r="J36" s="13" t="s">
+        <v>421</v>
       </c>
       <c r="K36" s="11" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="L36" s="11" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="M36" s="11" t="s">
-        <v>418</v>
-      </c>
-      <c r="N36" s="11" t="s">
-        <v>419</v>
-      </c>
-      <c r="O36" s="11" t="s">
-        <v>420</v>
+        <v>424</v>
+      </c>
+      <c r="N36" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="O36" s="15" t="s">
+        <v>426</v>
       </c>
       <c r="P36"/>
       <c r="Q36"/>
@@ -7945,43 +8125,43 @@
         <v>10032</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>427</v>
-      </c>
-      <c r="J37" s="11" t="s">
-        <v>428</v>
+        <v>433</v>
+      </c>
+      <c r="J37" s="13" t="s">
+        <v>434</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="L37" s="11" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="M37" s="11" t="s">
-        <v>431</v>
-      </c>
-      <c r="N37" s="11" t="s">
-        <v>432</v>
+        <v>437</v>
+      </c>
+      <c r="N37" s="14" t="s">
+        <v>438</v>
       </c>
       <c r="O37" s="11" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
@@ -7996,43 +8176,43 @@
         <v>10033</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="K38" s="11" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="L38" s="11" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="M38" s="11" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="N38" s="11" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="O38" s="11" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
@@ -8048,43 +8228,43 @@
         <v>10034</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="K39" s="11" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="L39" s="11" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="M39" s="11" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="N39" s="11" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="O39" s="11" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" ht="20" customHeight="1" spans="2:23">
@@ -8092,43 +8272,43 @@
         <v>10035</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="L40" s="11" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="M40" s="11" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="N40" s="11" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="O40" s="11" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="P40"/>
       <c r="Q40"/>
@@ -8144,43 +8324,43 @@
         <v>10036</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="L41" s="11" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="M41" s="11" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="N41" s="11" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="O41" s="11" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="P41"/>
       <c r="Q41"/>
@@ -8196,43 +8376,43 @@
         <v>10037</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="K42" s="11" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="L42" s="11" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="M42" s="11" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="N42" s="11" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="O42" s="11" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="P42" s="1"/>
     </row>
@@ -8241,43 +8421,43 @@
         <v>10038</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="K43" s="11" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="L43" s="11" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="M43" s="11" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="N43" s="11" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="O43" s="11" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:23">
@@ -8285,43 +8465,43 @@
         <v>10039</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="K44" s="11" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="L44" s="11" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="M44" s="11" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="N44" s="11" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="O44" s="11" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:23">
@@ -8329,46 +8509,46 @@
         <v>10040</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="K45" s="11" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="L45" s="11" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="M45" s="11" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="N45" s="11" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="O45" s="11" t="s">
-        <v>522</v>
-      </c>
-      <c r="P45" s="13" t="s">
-        <v>522</v>
+        <v>528</v>
+      </c>
+      <c r="P45" s="16" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:23">
@@ -8376,46 +8556,46 @@
         <v>10041</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="K46" s="11" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="L46" s="11" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="M46" s="11" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="N46" s="11" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="O46" s="11" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="P46" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="2:23">
@@ -8423,43 +8603,43 @@
         <v>10042</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="K47" s="11" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="L47" s="11" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="M47" s="11" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="N47" s="11" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="O47" s="11" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="2:23">
@@ -8467,43 +8647,43 @@
         <v>10043</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="K48" s="11" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="L48" s="11" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="M48" s="11" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="N48" s="11" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="O48" s="11" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="2:16">
@@ -8511,43 +8691,43 @@
         <v>10044</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="K49" s="11" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="L49" s="11" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="M49" s="11" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="N49" s="11" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="O49" s="11" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="2:16">
@@ -8555,43 +8735,43 @@
         <v>10045</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="K50" s="11" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="L50" s="11" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="M50" s="11" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="N50" s="11" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="O50" s="11" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="2:16">
@@ -8599,43 +8779,43 @@
         <v>10046</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="K51" s="11" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="L51" s="11" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="M51" s="11" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="N51" s="11" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="O51" s="11" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="2:16">
@@ -8643,43 +8823,43 @@
         <v>10047</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="K52" s="11" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="L52" s="11" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="M52" s="11" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="N52" s="11" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="O52" s="11" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="2:16">
@@ -8687,43 +8867,43 @@
         <v>10048</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="K53" s="11" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="L53" s="11" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="M53" s="11" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="N53" s="11" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="O53" s="11" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="2:16">
@@ -8731,43 +8911,43 @@
         <v>10049</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="K54" s="11" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="L54" s="11" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="M54" s="11" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="N54" s="11" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="O54" s="11" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="2:16">
@@ -8775,43 +8955,43 @@
         <v>10050</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="K55" s="11" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="L55" s="11" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="M55" s="11" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="N55" s="11" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="O55" s="11" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" ht="19" customHeight="1" spans="2:16">
@@ -8819,43 +8999,43 @@
         <v>10051</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="K56" s="11" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="L56" s="11" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="M56" s="11" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="N56" s="11" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="O56" s="11" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="P56"/>
     </row>
@@ -8864,43 +9044,43 @@
         <v>10052</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="K57" s="11" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="L57" s="11" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="M57" s="11" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="N57" s="11" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="O57" s="11" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="P57" s="1"/>
     </row>
@@ -8909,43 +9089,43 @@
         <v>10053</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="K58" s="11" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="L58" s="11" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="M58" s="11" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="N58" s="11" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="O58" s="11" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:16">
@@ -8953,43 +9133,43 @@
         <v>10054</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="K59" s="11" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="L59" s="11" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="M59" s="11" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="N59" s="11" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="O59" s="11" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:16">
@@ -8997,43 +9177,43 @@
         <v>10055</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="K60" s="11" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="L60" s="11" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="M60" s="11" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="N60" s="11" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="O60" s="11" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:16">
@@ -9041,43 +9221,43 @@
         <v>10056</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="K61" s="11" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="L61" s="11" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="M61" s="11" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="N61" s="11" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="O61" s="11" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:16">
@@ -9085,43 +9265,43 @@
         <v>10057</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="K62" s="11" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="L62" s="11" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="M62" s="11" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="N62" s="11" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="O62" s="11" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:16">
@@ -9129,43 +9309,43 @@
         <v>10058</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="G63" s="11" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="K63" s="11" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="L63" s="11" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="M63" s="11" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="N63" s="11" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="O63" s="11" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:16">
@@ -9173,43 +9353,43 @@
         <v>10059</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="G64" s="11" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="K64" s="11" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="L64" s="11" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="M64" s="11" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="N64" s="11" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="O64" s="11" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="2:15">
@@ -9217,43 +9397,43 @@
         <v>10060</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="H65" s="11" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="K65" s="11" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="L65" s="11" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="M65" s="11" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="N65" s="11" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="O65" s="11" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="2:15">
@@ -9261,43 +9441,43 @@
         <v>10061</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="G66" s="11" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="K66" s="11" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="L66" s="11" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="M66" s="11" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="N66" s="11" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="O66" s="11" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="2:15">
@@ -9305,43 +9485,43 @@
         <v>10062</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="G67" s="11" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="H67" s="11" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="K67" s="11" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="L67" s="11" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="M67" s="11" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="N67" s="11" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="O67" s="11" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="2:15">
@@ -9349,43 +9529,43 @@
         <v>10063</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="K68" s="11" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="L68" s="11" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="M68" s="11" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="N68" s="11" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="O68" s="11" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="2:15">
@@ -9393,43 +9573,43 @@
         <v>10064</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="K69" s="11" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="L69" s="11" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="M69" s="11" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="N69" s="11" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="O69" s="11" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
     </row>
     <row r="70" ht="19" customHeight="1" spans="2:15">
@@ -9437,43 +9617,43 @@
         <v>10065</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="G70" s="11" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="K70" s="11" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="L70" s="11" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="M70" s="11" t="s">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="N70" s="11" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="O70" s="11" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="2:15">
@@ -9481,43 +9661,43 @@
         <v>10066</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="G71" s="11" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="H71" s="11" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="K71" s="11" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="L71" s="11" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="M71" s="11" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="N71" s="11" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="O71" s="11" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="2:15">
@@ -9525,43 +9705,43 @@
         <v>10067</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="G72" s="11" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="K72" s="11" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="L72" s="11" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="M72" s="11" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="N72" s="11" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="O72" s="11" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="2:15">
@@ -9569,43 +9749,43 @@
         <v>10068</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="K73" s="11" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="L73" s="11" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="M73" s="11" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="N73" s="11" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="O73" s="11" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="2:15">
@@ -9613,43 +9793,43 @@
         <v>10069</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="G74" s="11" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="H74" s="11" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="K74" s="11" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="L74" s="11" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="M74" s="11" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="N74" s="11" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="O74" s="11" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="2:15">
@@ -9657,43 +9837,43 @@
         <v>10070</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="G75" s="11" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="I75" s="11" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="J75" s="11" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="K75" s="11" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="L75" s="11" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="M75" s="11" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="N75" s="11" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="O75" s="11" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="2:15">
@@ -9701,43 +9881,43 @@
         <v>10071</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="G76" s="11" t="s">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="I76" s="11" t="s">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="J76" s="11" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="K76" s="11" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="L76" s="11" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="M76" s="11" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="N76" s="11" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="O76" s="11" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="2:15">
@@ -9745,43 +9925,43 @@
         <v>10072</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="G77" s="11" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="H77" s="11" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="I77" s="11" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="J77" s="11" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
       <c r="K77" s="11" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="L77" s="11" t="s">
-        <v>917</v>
+        <v>923</v>
       </c>
       <c r="M77" s="11" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="N77" s="11" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="O77" s="11" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="2:15">
@@ -9789,43 +9969,43 @@
         <v>10073</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="E78" s="11" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="G78" s="11" t="s">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="H78" s="11" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="I78" s="11" t="s">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="J78" s="11" t="s">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="K78" s="11" t="s">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="L78" s="11" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="M78" s="11" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="N78" s="11" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="O78" s="11" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
     </row>
     <row r="79" ht="19" customHeight="1" spans="2:15">
@@ -9833,43 +10013,43 @@
         <v>10074</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="E79" s="11" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="G79" s="11" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="H79" s="11" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="I79" s="11" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="J79" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="K79" s="11" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="L79" s="11" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="M79" s="11" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="N79" s="11" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="O79" s="11" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="2:15">
@@ -9877,43 +10057,43 @@
         <v>10075</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="G80" s="11" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="H80" s="11" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="I80" s="11" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="J80" s="11" t="s">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="K80" s="11" t="s">
-        <v>955</v>
+        <v>961</v>
       </c>
       <c r="L80" s="11" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="M80" s="11" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="N80" s="11" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="O80" s="11" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="2:15">
@@ -9921,43 +10101,43 @@
         <v>10076</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>960</v>
+        <v>966</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="E81" s="11" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>964</v>
+        <v>970</v>
       </c>
       <c r="H81" s="11" t="s">
-        <v>965</v>
+        <v>971</v>
       </c>
       <c r="I81" s="11" t="s">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="J81" s="11" t="s">
-        <v>967</v>
+        <v>973</v>
       </c>
       <c r="K81" s="11" t="s">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="L81" s="11" t="s">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="M81" s="11" t="s">
-        <v>970</v>
+        <v>976</v>
       </c>
       <c r="N81" s="11" t="s">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="O81" s="11" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="2:15">
@@ -9965,43 +10145,43 @@
         <v>10077</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="G82" s="11" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="H82" s="11" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="I82" s="11" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="J82" s="11" t="s">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="K82" s="11" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="L82" s="11" t="s">
-        <v>982</v>
+        <v>988</v>
       </c>
       <c r="M82" s="11" t="s">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="N82" s="11" t="s">
-        <v>984</v>
+        <v>990</v>
       </c>
       <c r="O82" s="11" t="s">
-        <v>985</v>
+        <v>991</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="2:15">
@@ -10009,43 +10189,43 @@
         <v>10078</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="E83" s="11" t="s">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="G83" s="11" t="s">
-        <v>990</v>
+        <v>996</v>
       </c>
       <c r="H83" s="11" t="s">
-        <v>991</v>
+        <v>997</v>
       </c>
       <c r="I83" s="11" t="s">
-        <v>992</v>
+        <v>998</v>
       </c>
       <c r="J83" s="11" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="K83" s="11" t="s">
-        <v>994</v>
+        <v>1000</v>
       </c>
       <c r="L83" s="11" t="s">
-        <v>995</v>
+        <v>1001</v>
       </c>
       <c r="M83" s="11" t="s">
-        <v>996</v>
+        <v>1002</v>
       </c>
       <c r="N83" s="11" t="s">
-        <v>997</v>
+        <v>1003</v>
       </c>
       <c r="O83" s="11" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="2:15">
@@ -10053,43 +10233,43 @@
         <v>10079</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
       <c r="E84" s="11" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="G84" s="11" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
       <c r="H84" s="11" t="s">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="I84" s="11" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="J84" s="11" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
       <c r="K84" s="11" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="L84" s="11" t="s">
-        <v>1008</v>
+        <v>1014</v>
       </c>
       <c r="M84" s="11" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
       <c r="N84" s="11" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="O84" s="11" t="s">
-        <v>1011</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="2:15">
@@ -10097,43 +10277,43 @@
         <v>10080</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="E85" s="11" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="G85" s="11" t="s">
-        <v>1016</v>
+        <v>1022</v>
       </c>
       <c r="H85" s="11" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="I85" s="11" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
       <c r="J85" s="11" t="s">
-        <v>1019</v>
+        <v>1025</v>
       </c>
       <c r="K85" s="11" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
       <c r="L85" s="11" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
       <c r="M85" s="11" t="s">
-        <v>1022</v>
+        <v>1028</v>
       </c>
       <c r="N85" s="11" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
       <c r="O85" s="11" t="s">
-        <v>1024</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="2:15">
@@ -10141,43 +10321,43 @@
         <v>10081</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
       <c r="E86" s="11" t="s">
-        <v>1027</v>
+        <v>1033</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>1028</v>
+        <v>1034</v>
       </c>
       <c r="G86" s="11" t="s">
-        <v>1029</v>
+        <v>1035</v>
       </c>
       <c r="H86" s="11" t="s">
-        <v>1030</v>
+        <v>1036</v>
       </c>
       <c r="I86" s="11" t="s">
-        <v>1031</v>
+        <v>1037</v>
       </c>
       <c r="J86" s="11" t="s">
-        <v>1032</v>
+        <v>1038</v>
       </c>
       <c r="K86" s="11" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="L86" s="11" t="s">
-        <v>1034</v>
+        <v>1040</v>
       </c>
       <c r="M86" s="11" t="s">
-        <v>1035</v>
+        <v>1041</v>
       </c>
       <c r="N86" s="11" t="s">
-        <v>1036</v>
+        <v>1042</v>
       </c>
       <c r="O86" s="11" t="s">
-        <v>1037</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="2:15">
@@ -10185,43 +10365,43 @@
         <v>10082</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>1038</v>
+        <v>1044</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>1039</v>
+        <v>1045</v>
       </c>
       <c r="E87" s="11" t="s">
-        <v>1040</v>
+        <v>1046</v>
       </c>
       <c r="F87" s="11" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="G87" s="11" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
       <c r="H87" s="11" t="s">
-        <v>1043</v>
+        <v>1049</v>
       </c>
       <c r="I87" s="11" t="s">
-        <v>1044</v>
+        <v>1050</v>
       </c>
       <c r="J87" s="11" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="K87" s="11" t="s">
-        <v>1046</v>
+        <v>1052</v>
       </c>
       <c r="L87" s="11" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="M87" s="11" t="s">
-        <v>1048</v>
+        <v>1054</v>
       </c>
       <c r="N87" s="11" t="s">
-        <v>1049</v>
+        <v>1055</v>
       </c>
       <c r="O87" s="11" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="2:15">
@@ -10229,43 +10409,43 @@
         <v>10083</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="F88" s="11" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
       <c r="G88" s="11" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="H88" s="11" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="I88" s="11" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="J88" s="11" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="K88" s="11" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
       <c r="L88" s="11" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="M88" s="11" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="N88" s="11" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="O88" s="11" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="2:15">
@@ -10273,43 +10453,43 @@
         <v>10084</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>1065</v>
+        <v>1071</v>
       </c>
       <c r="E89" s="11" t="s">
-        <v>1066</v>
+        <v>1072</v>
       </c>
       <c r="F89" s="11" t="s">
-        <v>1067</v>
+        <v>1073</v>
       </c>
       <c r="G89" s="11" t="s">
-        <v>1068</v>
+        <v>1074</v>
       </c>
       <c r="H89" s="11" t="s">
-        <v>1069</v>
+        <v>1075</v>
       </c>
       <c r="I89" s="11" t="s">
-        <v>1068</v>
+        <v>1074</v>
       </c>
       <c r="J89" s="11" t="s">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="K89" s="11" t="s">
-        <v>1071</v>
+        <v>1077</v>
       </c>
       <c r="L89" s="11" t="s">
-        <v>1072</v>
+        <v>1078</v>
       </c>
       <c r="M89" s="11" t="s">
-        <v>1073</v>
+        <v>1079</v>
       </c>
       <c r="N89" s="11" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="O89" s="11" t="s">
-        <v>1075</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="2:15">
@@ -10317,43 +10497,43 @@
         <v>10085</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>1077</v>
+        <v>1083</v>
       </c>
       <c r="E90" s="11" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
       <c r="G90" s="11" t="s">
-        <v>1080</v>
+        <v>1086</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>1081</v>
+        <v>1087</v>
       </c>
       <c r="I90" s="11" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="J90" s="11" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
       <c r="K90" s="11" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="L90" s="11" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="M90" s="11" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="N90" s="11" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="O90" s="11" t="s">
-        <v>1088</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="2:15">
@@ -10361,43 +10541,43 @@
         <v>10086</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>1090</v>
+        <v>1096</v>
       </c>
       <c r="E91" s="11" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
       <c r="F91" s="11" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
       <c r="G91" s="11" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="H91" s="11" t="s">
-        <v>1094</v>
+        <v>1100</v>
       </c>
       <c r="I91" s="11" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="J91" s="11" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="K91" s="11" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="L91" s="11" t="s">
-        <v>1098</v>
+        <v>1104</v>
       </c>
       <c r="M91" s="11" t="s">
-        <v>1099</v>
+        <v>1105</v>
       </c>
       <c r="N91" s="11" t="s">
-        <v>1100</v>
+        <v>1106</v>
       </c>
       <c r="O91" s="11" t="s">
-        <v>1101</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="2:15">
@@ -10405,43 +10585,43 @@
         <v>10087</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>1102</v>
+        <v>1108</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>1103</v>
+        <v>1109</v>
       </c>
       <c r="E92" s="11" t="s">
-        <v>1104</v>
+        <v>1110</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>1105</v>
+        <v>1111</v>
       </c>
       <c r="G92" s="11" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="H92" s="11" t="s">
-        <v>1107</v>
+        <v>1113</v>
       </c>
       <c r="I92" s="11" t="s">
-        <v>1108</v>
+        <v>1114</v>
       </c>
       <c r="J92" s="11" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="K92" s="11" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
       <c r="L92" s="11" t="s">
-        <v>1111</v>
+        <v>1117</v>
       </c>
       <c r="M92" s="11" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
       <c r="N92" s="11" t="s">
-        <v>1113</v>
+        <v>1119</v>
       </c>
       <c r="O92" s="11" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="2:15">
@@ -10449,43 +10629,43 @@
         <v>10088</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>1115</v>
+        <v>1121</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>1116</v>
+        <v>1122</v>
       </c>
       <c r="E93" s="11" t="s">
-        <v>1117</v>
+        <v>1123</v>
       </c>
       <c r="F93" s="11" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="G93" s="11" t="s">
-        <v>1119</v>
+        <v>1125</v>
       </c>
       <c r="H93" s="11" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="I93" s="11" t="s">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="J93" s="11" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
       <c r="K93" s="11" t="s">
-        <v>1123</v>
+        <v>1129</v>
       </c>
       <c r="L93" s="11" t="s">
-        <v>1124</v>
+        <v>1130</v>
       </c>
       <c r="M93" s="11" t="s">
-        <v>1125</v>
+        <v>1131</v>
       </c>
       <c r="N93" s="11" t="s">
-        <v>1126</v>
+        <v>1132</v>
       </c>
       <c r="O93" s="11" t="s">
-        <v>1127</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="2:15">
@@ -10493,43 +10673,43 @@
         <v>10089</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>1128</v>
+        <v>1134</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="E94" s="11" t="s">
-        <v>1130</v>
+        <v>1136</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>1131</v>
+        <v>1137</v>
       </c>
       <c r="G94" s="11" t="s">
-        <v>1132</v>
+        <v>1138</v>
       </c>
       <c r="H94" s="11" t="s">
-        <v>1133</v>
+        <v>1139</v>
       </c>
       <c r="I94" s="11" t="s">
-        <v>1134</v>
+        <v>1140</v>
       </c>
       <c r="J94" s="11" t="s">
-        <v>1135</v>
+        <v>1141</v>
       </c>
       <c r="K94" s="11" t="s">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="L94" s="11" t="s">
-        <v>1137</v>
+        <v>1143</v>
       </c>
       <c r="M94" s="11" t="s">
-        <v>1138</v>
+        <v>1144</v>
       </c>
       <c r="N94" s="11" t="s">
-        <v>1139</v>
+        <v>1145</v>
       </c>
       <c r="O94" s="11" t="s">
-        <v>1140</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="2:15">
@@ -10537,43 +10717,43 @@
         <v>10090</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>1141</v>
+        <v>1147</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>1142</v>
+        <v>1148</v>
       </c>
       <c r="E95" s="11" t="s">
-        <v>1143</v>
+        <v>1149</v>
       </c>
       <c r="F95" s="11" t="s">
-        <v>1144</v>
+        <v>1150</v>
       </c>
       <c r="G95" s="11" t="s">
-        <v>1145</v>
+        <v>1151</v>
       </c>
       <c r="H95" s="11" t="s">
-        <v>1146</v>
+        <v>1152</v>
       </c>
       <c r="I95" s="11" t="s">
-        <v>1147</v>
+        <v>1153</v>
       </c>
       <c r="J95" s="11" t="s">
-        <v>1148</v>
+        <v>1154</v>
       </c>
       <c r="K95" s="11" t="s">
-        <v>1149</v>
+        <v>1155</v>
       </c>
       <c r="L95" s="11" t="s">
-        <v>1150</v>
+        <v>1156</v>
       </c>
       <c r="M95" s="11" t="s">
-        <v>1151</v>
+        <v>1157</v>
       </c>
       <c r="N95" s="11" t="s">
-        <v>1152</v>
+        <v>1158</v>
       </c>
       <c r="O95" s="11" t="s">
-        <v>1153</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="2:15">
@@ -10581,43 +10761,43 @@
         <v>10091</v>
       </c>
       <c r="C96" t="s">
-        <v>1154</v>
+        <v>1160</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>1155</v>
+        <v>1161</v>
       </c>
       <c r="E96" t="s">
-        <v>1156</v>
+        <v>1162</v>
       </c>
       <c r="F96" t="s">
-        <v>1157</v>
+        <v>1163</v>
       </c>
       <c r="G96" t="s">
-        <v>1158</v>
+        <v>1164</v>
       </c>
       <c r="H96" t="s">
-        <v>1159</v>
+        <v>1165</v>
       </c>
       <c r="I96" t="s">
-        <v>1160</v>
+        <v>1166</v>
       </c>
       <c r="J96" t="s">
-        <v>1161</v>
+        <v>1167</v>
       </c>
       <c r="K96" t="s">
-        <v>1162</v>
+        <v>1168</v>
       </c>
       <c r="L96" t="s">
-        <v>1163</v>
+        <v>1169</v>
       </c>
       <c r="M96" t="s">
-        <v>1164</v>
+        <v>1170</v>
       </c>
       <c r="N96" t="s">
-        <v>1165</v>
+        <v>1171</v>
       </c>
       <c r="O96" t="s">
-        <v>1166</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="1:16">
@@ -10625,43 +10805,43 @@
         <v>10092</v>
       </c>
       <c r="C97" t="s">
-        <v>1167</v>
+        <v>1173</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>1168</v>
+        <v>1174</v>
       </c>
       <c r="E97" t="s">
-        <v>1169</v>
+        <v>1175</v>
       </c>
       <c r="F97" t="s">
-        <v>1170</v>
+        <v>1176</v>
       </c>
       <c r="G97" t="s">
-        <v>1171</v>
+        <v>1177</v>
       </c>
       <c r="H97" t="s">
-        <v>1172</v>
+        <v>1178</v>
       </c>
       <c r="I97" t="s">
-        <v>1173</v>
+        <v>1179</v>
       </c>
       <c r="J97" t="s">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="K97" t="s">
-        <v>1175</v>
+        <v>1181</v>
       </c>
       <c r="L97" t="s">
-        <v>1176</v>
+        <v>1182</v>
       </c>
       <c r="M97" t="s">
-        <v>1177</v>
+        <v>1183</v>
       </c>
       <c r="N97" t="s">
-        <v>1178</v>
+        <v>1184</v>
       </c>
       <c r="O97" t="s">
-        <v>1179</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="1:16">
@@ -10669,43 +10849,43 @@
         <v>10093</v>
       </c>
       <c r="C98" t="s">
-        <v>1180</v>
+        <v>1186</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>1181</v>
+        <v>1187</v>
       </c>
       <c r="E98" t="s">
-        <v>1182</v>
-      </c>
-      <c r="F98" s="14" t="s">
-        <v>1183</v>
-      </c>
-      <c r="G98" s="14" t="s">
-        <v>1184</v>
+        <v>1188</v>
+      </c>
+      <c r="F98" s="17" t="s">
+        <v>1189</v>
+      </c>
+      <c r="G98" s="17" t="s">
+        <v>1190</v>
       </c>
       <c r="H98" t="s">
-        <v>1185</v>
-      </c>
-      <c r="I98" s="14" t="s">
-        <v>1186</v>
-      </c>
-      <c r="J98" s="14" t="s">
-        <v>1187</v>
-      </c>
-      <c r="K98" s="14" t="s">
-        <v>1188</v>
+        <v>1191</v>
+      </c>
+      <c r="I98" s="17" t="s">
+        <v>1192</v>
+      </c>
+      <c r="J98" s="17" t="s">
+        <v>1193</v>
+      </c>
+      <c r="K98" s="17" t="s">
+        <v>1194</v>
       </c>
       <c r="L98" t="s">
-        <v>1189</v>
-      </c>
-      <c r="M98" s="14" t="s">
-        <v>1190</v>
+        <v>1195</v>
+      </c>
+      <c r="M98" s="17" t="s">
+        <v>1196</v>
       </c>
       <c r="N98" t="s">
-        <v>1191</v>
+        <v>1197</v>
       </c>
       <c r="O98" t="s">
-        <v>1192</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="1:16">
@@ -10713,43 +10893,43 @@
         <v>10094</v>
       </c>
       <c r="C99" t="s">
-        <v>1193</v>
+        <v>1199</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>1194</v>
+        <v>1200</v>
       </c>
       <c r="E99" t="s">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="F99" t="s">
-        <v>1196</v>
+        <v>1202</v>
       </c>
       <c r="G99" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
       <c r="H99" t="s">
-        <v>1198</v>
-      </c>
-      <c r="I99" s="14" t="s">
-        <v>1199</v>
-      </c>
-      <c r="J99" s="14" t="s">
-        <v>1200</v>
+        <v>1204</v>
+      </c>
+      <c r="I99" s="17" t="s">
+        <v>1205</v>
+      </c>
+      <c r="J99" s="17" t="s">
+        <v>1206</v>
       </c>
       <c r="K99" t="s">
-        <v>1201</v>
+        <v>1207</v>
       </c>
       <c r="L99" t="s">
-        <v>1202</v>
-      </c>
-      <c r="M99" s="14" t="s">
-        <v>1203</v>
-      </c>
-      <c r="N99" s="14" t="s">
-        <v>1204</v>
-      </c>
-      <c r="O99" s="14" t="s">
-        <v>1205</v>
+        <v>1208</v>
+      </c>
+      <c r="M99" s="17" t="s">
+        <v>1209</v>
+      </c>
+      <c r="N99" s="17" t="s">
+        <v>1210</v>
+      </c>
+      <c r="O99" s="17" t="s">
+        <v>1211</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="1:16">
@@ -10757,43 +10937,43 @@
         <v>10095</v>
       </c>
       <c r="C100" t="s">
-        <v>1206</v>
+        <v>1212</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>1207</v>
+        <v>1213</v>
       </c>
       <c r="E100" t="s">
-        <v>1208</v>
+        <v>1214</v>
       </c>
       <c r="F100" t="s">
-        <v>1209</v>
+        <v>1215</v>
       </c>
       <c r="G100" t="s">
-        <v>1210</v>
+        <v>1216</v>
       </c>
       <c r="H100" t="s">
-        <v>1211</v>
+        <v>1217</v>
       </c>
       <c r="I100" t="s">
-        <v>1212</v>
+        <v>1218</v>
       </c>
       <c r="J100" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="K100" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="L100" t="s">
-        <v>1215</v>
-      </c>
-      <c r="M100" s="14" t="s">
-        <v>1216</v>
-      </c>
-      <c r="N100" s="14" t="s">
-        <v>1217</v>
-      </c>
-      <c r="O100" s="14" t="s">
-        <v>1218</v>
+        <v>1221</v>
+      </c>
+      <c r="M100" s="17" t="s">
+        <v>1222</v>
+      </c>
+      <c r="N100" s="17" t="s">
+        <v>1223</v>
+      </c>
+      <c r="O100" s="17" t="s">
+        <v>1224</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="1:16">
@@ -10801,43 +10981,43 @@
         <v>10096</v>
       </c>
       <c r="C101" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>1220</v>
+        <v>1226</v>
       </c>
       <c r="E101" t="s">
-        <v>1221</v>
-      </c>
-      <c r="F101" s="14" t="s">
-        <v>1222</v>
-      </c>
-      <c r="G101" s="14" t="s">
-        <v>1223</v>
+        <v>1227</v>
+      </c>
+      <c r="F101" s="17" t="s">
+        <v>1228</v>
+      </c>
+      <c r="G101" s="17" t="s">
+        <v>1229</v>
       </c>
       <c r="H101" t="s">
-        <v>1224</v>
-      </c>
-      <c r="I101" s="14" t="s">
-        <v>1225</v>
-      </c>
-      <c r="J101" s="14" t="s">
-        <v>1226</v>
-      </c>
-      <c r="K101" s="14" t="s">
-        <v>1227</v>
-      </c>
-      <c r="L101" s="14" t="s">
-        <v>1228</v>
-      </c>
-      <c r="M101" s="14" t="s">
-        <v>1229</v>
-      </c>
-      <c r="N101" s="14" t="s">
         <v>1230</v>
       </c>
+      <c r="I101" s="17" t="s">
+        <v>1231</v>
+      </c>
+      <c r="J101" s="17" t="s">
+        <v>1232</v>
+      </c>
+      <c r="K101" s="17" t="s">
+        <v>1233</v>
+      </c>
+      <c r="L101" s="17" t="s">
+        <v>1234</v>
+      </c>
+      <c r="M101" s="17" t="s">
+        <v>1235</v>
+      </c>
+      <c r="N101" s="17" t="s">
+        <v>1236</v>
+      </c>
       <c r="O101" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="1:16">
@@ -10845,93 +11025,93 @@
         <v>10097</v>
       </c>
       <c r="C102" t="s">
-        <v>1232</v>
+        <v>1238</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>1233</v>
+        <v>1239</v>
       </c>
       <c r="E102" t="s">
-        <v>1234</v>
-      </c>
-      <c r="F102" s="15" t="s">
-        <v>1235</v>
-      </c>
-      <c r="G102" s="15" t="s">
-        <v>1236</v>
+        <v>1240</v>
+      </c>
+      <c r="F102" s="18" t="s">
+        <v>1241</v>
+      </c>
+      <c r="G102" s="18" t="s">
+        <v>1242</v>
       </c>
       <c r="H102" t="s">
-        <v>1237</v>
-      </c>
-      <c r="I102" s="14" t="s">
-        <v>1238</v>
-      </c>
-      <c r="J102" s="14" t="s">
-        <v>1239</v>
-      </c>
-      <c r="K102" s="14" t="s">
-        <v>1240</v>
+        <v>1243</v>
+      </c>
+      <c r="I102" s="17" t="s">
+        <v>1244</v>
+      </c>
+      <c r="J102" s="17" t="s">
+        <v>1245</v>
+      </c>
+      <c r="K102" s="17" t="s">
+        <v>1246</v>
       </c>
       <c r="L102" t="s">
-        <v>1241</v>
-      </c>
-      <c r="M102" s="14" t="s">
-        <v>1242</v>
+        <v>1247</v>
+      </c>
+      <c r="M102" s="17" t="s">
+        <v>1248</v>
       </c>
       <c r="N102" t="s">
-        <v>1243</v>
+        <v>1249</v>
       </c>
       <c r="O102" t="s">
-        <v>1244</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="103" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A103" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B103" s="3">
         <v>10098</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>1246</v>
+        <v>1252</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>1247</v>
+        <v>1253</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>1248</v>
+        <v>1254</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>1249</v>
+        <v>1255</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>1250</v>
+        <v>1256</v>
       </c>
       <c r="H103" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="J103" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="K103" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="L103" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="M103" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="N103" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="O103" s="2" t="s">
+        <v>1264</v>
+      </c>
+      <c r="P103" s="2" t="s">
         <v>1251</v>
-      </c>
-      <c r="I103" s="2" t="s">
-        <v>1252</v>
-      </c>
-      <c r="J103" s="2" t="s">
-        <v>1253</v>
-      </c>
-      <c r="K103" s="2" t="s">
-        <v>1254</v>
-      </c>
-      <c r="L103" s="2" t="s">
-        <v>1255</v>
-      </c>
-      <c r="M103" s="2" t="s">
-        <v>1256</v>
-      </c>
-      <c r="N103" s="2" t="s">
-        <v>1257</v>
-      </c>
-      <c r="O103" s="2" t="s">
-        <v>1258</v>
-      </c>
-      <c r="P103" s="2" t="s">
-        <v>1245</v>
       </c>
     </row>
     <row r="104" customFormat="1" customHeight="1" spans="1:16">
@@ -10939,43 +11119,43 @@
         <v>10099</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>1260</v>
+        <v>1266</v>
       </c>
       <c r="E104" s="11" t="s">
-        <v>1261</v>
+        <v>1267</v>
       </c>
       <c r="F104" s="11" t="s">
-        <v>1262</v>
+        <v>1268</v>
       </c>
       <c r="G104" s="11" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="H104" s="11" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="I104" s="11" t="s">
-        <v>1265</v>
+        <v>1271</v>
       </c>
       <c r="J104" s="11" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="K104" s="11" t="s">
-        <v>1267</v>
+        <v>1273</v>
       </c>
       <c r="L104" s="11" t="s">
-        <v>1268</v>
+        <v>1274</v>
       </c>
       <c r="M104" s="11" t="s">
-        <v>1269</v>
-      </c>
-      <c r="N104" s="16" t="s">
-        <v>1270</v>
+        <v>1275</v>
+      </c>
+      <c r="N104" s="14" t="s">
+        <v>1276</v>
       </c>
       <c r="O104" s="11" t="s">
-        <v>1271</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
@@ -10983,43 +11163,43 @@
         <v>10100</v>
       </c>
       <c r="C105" t="s">
-        <v>1272</v>
-      </c>
-      <c r="D105" s="13" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D105" s="16" t="s">
         <v>153</v>
       </c>
       <c r="E105" t="s">
-        <v>1273</v>
+        <v>1279</v>
       </c>
       <c r="F105" t="s">
-        <v>1274</v>
-      </c>
-      <c r="G105" s="13" t="s">
-        <v>1275</v>
+        <v>1280</v>
+      </c>
+      <c r="G105" s="16" t="s">
+        <v>1281</v>
       </c>
       <c r="H105" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="I105" t="s">
-        <v>1277</v>
+        <v>1283</v>
       </c>
       <c r="J105" t="s">
-        <v>1278</v>
-      </c>
-      <c r="K105" s="13" t="s">
-        <v>1279</v>
+        <v>1284</v>
+      </c>
+      <c r="K105" s="16" t="s">
+        <v>1285</v>
       </c>
       <c r="L105" t="s">
-        <v>1280</v>
-      </c>
-      <c r="M105" s="14" t="s">
-        <v>1281</v>
-      </c>
-      <c r="N105" s="15" t="s">
-        <v>1282</v>
-      </c>
-      <c r="O105" s="14" t="s">
-        <v>1283</v>
+        <v>1286</v>
+      </c>
+      <c r="M105" s="17" t="s">
+        <v>1287</v>
+      </c>
+      <c r="N105" s="18" t="s">
+        <v>1288</v>
+      </c>
+      <c r="O105" s="17" t="s">
+        <v>1289</v>
       </c>
       <c r="P105"/>
     </row>
@@ -11028,43 +11208,43 @@
         <v>10101</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>1284</v>
+        <v>1290</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>1286</v>
+        <v>1292</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>1287</v>
+        <v>1293</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>1288</v>
+        <v>1294</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>1290</v>
+        <v>1296</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>1291</v>
+        <v>1297</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>1292</v>
+        <v>1298</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>1293</v>
+        <v>1299</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>1294</v>
+        <v>1300</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>1295</v>
+        <v>1301</v>
       </c>
       <c r="O106" s="2" t="s">
-        <v>1296</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="1:16">
@@ -11072,43 +11252,43 @@
         <v>10102</v>
       </c>
       <c r="C107" t="s">
-        <v>1297</v>
-      </c>
-      <c r="D107" s="13" t="s">
-        <v>1298</v>
+        <v>1303</v>
+      </c>
+      <c r="D107" s="16" t="s">
+        <v>1304</v>
       </c>
       <c r="E107" t="s">
-        <v>1299</v>
-      </c>
-      <c r="F107" s="14" t="s">
-        <v>1300</v>
-      </c>
-      <c r="G107" s="14" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H107" s="14" t="s">
-        <v>1302</v>
-      </c>
-      <c r="I107" s="14" t="s">
-        <v>1303</v>
-      </c>
-      <c r="J107" s="14" t="s">
-        <v>1304</v>
-      </c>
-      <c r="K107" s="14" t="s">
         <v>1305</v>
       </c>
-      <c r="L107" s="14" t="s">
+      <c r="F107" s="17" t="s">
         <v>1306</v>
       </c>
-      <c r="M107" s="14" t="s">
+      <c r="G107" s="17" t="s">
         <v>1307</v>
       </c>
-      <c r="N107" s="14" t="s">
+      <c r="H107" s="17" t="s">
         <v>1308</v>
       </c>
+      <c r="I107" s="17" t="s">
+        <v>1309</v>
+      </c>
+      <c r="J107" s="17" t="s">
+        <v>1310</v>
+      </c>
+      <c r="K107" s="17" t="s">
+        <v>1311</v>
+      </c>
+      <c r="L107" s="17" t="s">
+        <v>1312</v>
+      </c>
+      <c r="M107" s="17" t="s">
+        <v>1313</v>
+      </c>
+      <c r="N107" s="17" t="s">
+        <v>1314</v>
+      </c>
       <c r="O107" t="s">
-        <v>1309</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="1:16">
@@ -11116,43 +11296,43 @@
         <v>10103</v>
       </c>
       <c r="C108" t="s">
-        <v>1310</v>
-      </c>
-      <c r="D108" s="13" t="s">
-        <v>1311</v>
+        <v>1316</v>
+      </c>
+      <c r="D108" s="16" t="s">
+        <v>1317</v>
       </c>
       <c r="E108" t="s">
-        <v>1312</v>
+        <v>1318</v>
       </c>
       <c r="F108" t="s">
-        <v>1313</v>
-      </c>
-      <c r="G108" s="13" t="s">
-        <v>1314</v>
+        <v>1319</v>
+      </c>
+      <c r="G108" s="16" t="s">
+        <v>1320</v>
       </c>
       <c r="H108" t="s">
-        <v>1315</v>
+        <v>1321</v>
       </c>
       <c r="I108" t="s">
-        <v>1316</v>
+        <v>1322</v>
       </c>
       <c r="J108" t="s">
-        <v>1317</v>
-      </c>
-      <c r="K108" s="14" t="s">
-        <v>1318</v>
-      </c>
-      <c r="L108" s="14" t="s">
-        <v>1319</v>
-      </c>
-      <c r="M108" s="14" t="s">
-        <v>1320</v>
+        <v>1323</v>
+      </c>
+      <c r="K108" s="17" t="s">
+        <v>1324</v>
+      </c>
+      <c r="L108" s="17" t="s">
+        <v>1325</v>
+      </c>
+      <c r="M108" s="17" t="s">
+        <v>1326</v>
       </c>
       <c r="N108" t="s">
-        <v>1321</v>
+        <v>1327</v>
       </c>
       <c r="O108" t="s">
-        <v>1322</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="1:16">
@@ -11160,43 +11340,43 @@
         <v>10104</v>
       </c>
       <c r="C109" t="s">
-        <v>1323</v>
-      </c>
-      <c r="D109" s="13" t="s">
-        <v>1324</v>
+        <v>1329</v>
+      </c>
+      <c r="D109" s="16" t="s">
+        <v>1330</v>
       </c>
       <c r="E109" t="s">
-        <v>1325</v>
+        <v>1331</v>
       </c>
       <c r="F109" t="s">
-        <v>1326</v>
-      </c>
-      <c r="G109" s="13" t="s">
-        <v>1327</v>
+        <v>1332</v>
+      </c>
+      <c r="G109" s="16" t="s">
+        <v>1333</v>
       </c>
       <c r="H109" t="s">
-        <v>1328</v>
+        <v>1334</v>
       </c>
       <c r="I109" t="s">
-        <v>1329</v>
+        <v>1335</v>
       </c>
       <c r="J109" t="s">
-        <v>1330</v>
-      </c>
-      <c r="K109" s="14" t="s">
-        <v>1331</v>
-      </c>
-      <c r="L109" s="14" t="s">
-        <v>1332</v>
-      </c>
-      <c r="M109" s="14" t="s">
-        <v>1333</v>
-      </c>
-      <c r="N109" s="14" t="s">
-        <v>1334</v>
-      </c>
-      <c r="O109" s="14" t="s">
-        <v>1335</v>
+        <v>1336</v>
+      </c>
+      <c r="K109" s="17" t="s">
+        <v>1337</v>
+      </c>
+      <c r="L109" s="17" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M109" s="17" t="s">
+        <v>1339</v>
+      </c>
+      <c r="N109" s="17" t="s">
+        <v>1340</v>
+      </c>
+      <c r="O109" s="17" t="s">
+        <v>1341</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="1:16">
@@ -11204,87 +11384,87 @@
         <v>10105</v>
       </c>
       <c r="C110" t="s">
-        <v>1336</v>
+        <v>1342</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>1337</v>
+        <v>1343</v>
       </c>
       <c r="E110" t="s">
-        <v>1338</v>
-      </c>
-      <c r="F110" s="14" t="s">
-        <v>1339</v>
-      </c>
-      <c r="G110" s="14" t="s">
-        <v>1340</v>
-      </c>
-      <c r="H110" s="14" t="s">
-        <v>1341</v>
-      </c>
-      <c r="I110" s="14" t="s">
-        <v>1342</v>
-      </c>
-      <c r="J110" s="14" t="s">
-        <v>1343</v>
-      </c>
-      <c r="K110" s="14" t="s">
         <v>1344</v>
       </c>
+      <c r="F110" s="17" t="s">
+        <v>1345</v>
+      </c>
+      <c r="G110" s="17" t="s">
+        <v>1346</v>
+      </c>
+      <c r="H110" s="17" t="s">
+        <v>1347</v>
+      </c>
+      <c r="I110" s="17" t="s">
+        <v>1348</v>
+      </c>
+      <c r="J110" s="17" t="s">
+        <v>1349</v>
+      </c>
+      <c r="K110" s="17" t="s">
+        <v>1350</v>
+      </c>
       <c r="L110" t="s">
-        <v>1345</v>
-      </c>
-      <c r="M110" s="15" t="s">
-        <v>1346</v>
-      </c>
-      <c r="N110" s="15" t="s">
-        <v>1347</v>
-      </c>
-      <c r="O110" s="15" t="s">
-        <v>1348</v>
+        <v>1351</v>
+      </c>
+      <c r="M110" s="18" t="s">
+        <v>1352</v>
+      </c>
+      <c r="N110" s="18" t="s">
+        <v>1353</v>
+      </c>
+      <c r="O110" s="18" t="s">
+        <v>1354</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="1:16">
       <c r="B111" s="3">
         <v>10106</v>
       </c>
-      <c r="C111" s="17" t="s">
-        <v>1349</v>
-      </c>
-      <c r="D111" s="13" t="s">
-        <v>1350</v>
+      <c r="C111" s="19" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D111" s="16" t="s">
+        <v>1356</v>
       </c>
       <c r="E111" t="s">
-        <v>1351</v>
-      </c>
-      <c r="F111" s="14" t="s">
-        <v>1352</v>
-      </c>
-      <c r="G111" s="13" t="s">
-        <v>1353</v>
-      </c>
-      <c r="H111" s="14" t="s">
-        <v>1354</v>
-      </c>
-      <c r="I111" s="14" t="s">
-        <v>1355</v>
-      </c>
-      <c r="J111" s="14" t="s">
-        <v>1356</v>
-      </c>
-      <c r="K111" s="14" t="s">
         <v>1357</v>
       </c>
+      <c r="F111" s="17" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G111" s="16" t="s">
+        <v>1359</v>
+      </c>
+      <c r="H111" s="17" t="s">
+        <v>1360</v>
+      </c>
+      <c r="I111" s="17" t="s">
+        <v>1361</v>
+      </c>
+      <c r="J111" s="17" t="s">
+        <v>1362</v>
+      </c>
+      <c r="K111" s="17" t="s">
+        <v>1363</v>
+      </c>
       <c r="L111" t="s">
-        <v>1358</v>
-      </c>
-      <c r="M111" s="14" t="s">
-        <v>1359</v>
-      </c>
-      <c r="N111" s="14" t="s">
-        <v>1360</v>
+        <v>1364</v>
+      </c>
+      <c r="M111" s="17" t="s">
+        <v>1365</v>
+      </c>
+      <c r="N111" s="17" t="s">
+        <v>1366</v>
       </c>
       <c r="O111" t="s">
-        <v>1361</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="1:16">
@@ -11292,693 +11472,693 @@
         <v>10107</v>
       </c>
       <c r="C112" t="s">
-        <v>1362</v>
+        <v>1368</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>1363</v>
+        <v>1369</v>
       </c>
       <c r="E112" t="s">
-        <v>1364</v>
-      </c>
-      <c r="F112" s="14" t="s">
-        <v>1365</v>
+        <v>1370</v>
+      </c>
+      <c r="F112" s="17" t="s">
+        <v>1371</v>
       </c>
       <c r="G112" t="s">
-        <v>1366</v>
+        <v>1372</v>
       </c>
       <c r="H112" t="s">
-        <v>1367</v>
-      </c>
-      <c r="I112" s="14" t="s">
-        <v>1368</v>
-      </c>
-      <c r="J112" s="14" t="s">
-        <v>1369</v>
-      </c>
-      <c r="K112" s="14" t="s">
-        <v>1370</v>
+        <v>1373</v>
+      </c>
+      <c r="I112" s="17" t="s">
+        <v>1374</v>
+      </c>
+      <c r="J112" s="17" t="s">
+        <v>1375</v>
+      </c>
+      <c r="K112" s="17" t="s">
+        <v>1376</v>
       </c>
       <c r="L112" t="s">
-        <v>1371</v>
-      </c>
-      <c r="M112" s="14" t="s">
-        <v>1372</v>
+        <v>1377</v>
+      </c>
+      <c r="M112" s="17" t="s">
+        <v>1378</v>
       </c>
       <c r="N112" t="s">
-        <v>1373</v>
+        <v>1379</v>
       </c>
       <c r="O112" t="s">
-        <v>1374</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="113" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A113" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B113" s="3">
         <v>10108</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>1375</v>
+        <v>1381</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>1376</v>
+        <v>1382</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>1377</v>
+        <v>1383</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>340</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>1379</v>
+        <v>1385</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>344</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>1381</v>
+        <v>1387</v>
       </c>
       <c r="L113" s="2" t="s">
-        <v>1382</v>
+        <v>1388</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>1383</v>
+        <v>1389</v>
       </c>
       <c r="N113" s="2" t="s">
-        <v>1384</v>
+        <v>1390</v>
       </c>
       <c r="O113" s="2" t="s">
-        <v>1385</v>
+        <v>1391</v>
       </c>
       <c r="P113" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="114" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A114" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B114" s="3">
         <v>10109</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>1386</v>
+        <v>1392</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>1387</v>
+        <v>1393</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>1390</v>
+        <v>1396</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>1391</v>
+        <v>1397</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="L114" s="2" t="s">
-        <v>1395</v>
+        <v>1401</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>1396</v>
+        <v>1402</v>
       </c>
       <c r="N114" s="2" t="s">
-        <v>1397</v>
+        <v>1403</v>
       </c>
       <c r="O114" s="2" t="s">
-        <v>1398</v>
+        <v>1404</v>
       </c>
       <c r="P114" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="115" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A115" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B115" s="3">
         <v>10110</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>1399</v>
+        <v>1405</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>1400</v>
+        <v>1406</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>1401</v>
+        <v>1407</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>1402</v>
+        <v>1408</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>1403</v>
+        <v>1409</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>1404</v>
+        <v>1410</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>1405</v>
+        <v>1411</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
       <c r="K115" s="2" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="L115" s="2" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>1409</v>
+        <v>1415</v>
       </c>
       <c r="N115" s="2" t="s">
-        <v>1410</v>
+        <v>1416</v>
       </c>
       <c r="O115" s="2" t="s">
-        <v>1411</v>
+        <v>1417</v>
       </c>
       <c r="P115" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="116" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A116" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B116" s="3">
         <v>10111</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>1412</v>
+        <v>1418</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>1413</v>
+        <v>1419</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>1414</v>
+        <v>1420</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>1415</v>
+        <v>1421</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>1416</v>
+        <v>1422</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>1417</v>
+        <v>1423</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>1418</v>
+        <v>1424</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>1419</v>
+        <v>1425</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>1420</v>
+        <v>1426</v>
       </c>
       <c r="L116" s="2" t="s">
-        <v>1421</v>
+        <v>1427</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>1422</v>
+        <v>1428</v>
       </c>
       <c r="N116" s="2" t="s">
-        <v>1423</v>
+        <v>1429</v>
       </c>
       <c r="O116" s="2" t="s">
-        <v>1424</v>
+        <v>1430</v>
       </c>
       <c r="P116" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="117" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A117" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B117" s="3">
         <v>10112</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>1425</v>
+        <v>1431</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>1426</v>
+        <v>1432</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>1427</v>
+        <v>1433</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>1428</v>
+        <v>1434</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>1429</v>
+        <v>1435</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>1430</v>
+        <v>1436</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>1431</v>
+        <v>1437</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>1432</v>
+        <v>1438</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>1433</v>
+        <v>1439</v>
       </c>
       <c r="L117" s="2" t="s">
-        <v>1434</v>
+        <v>1440</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>1435</v>
+        <v>1441</v>
       </c>
       <c r="N117" s="2" t="s">
-        <v>1436</v>
+        <v>1442</v>
       </c>
       <c r="O117" s="2" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="P117" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="118" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A118" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B118" s="3">
         <v>10113</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>1438</v>
+        <v>1444</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>1439</v>
+        <v>1445</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>1440</v>
+        <v>1446</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>1441</v>
+        <v>1447</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>1442</v>
+        <v>1448</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>1443</v>
+        <v>1449</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>1444</v>
+        <v>1450</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>1445</v>
+        <v>1451</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>1446</v>
+        <v>1452</v>
       </c>
       <c r="L118" s="2" t="s">
-        <v>1447</v>
+        <v>1453</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>1448</v>
+        <v>1454</v>
       </c>
       <c r="N118" s="2" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="O118" s="2" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="P118" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="119" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A119" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B119" s="3">
         <v>10114</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>1451</v>
+        <v>1457</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>1452</v>
+        <v>1458</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>1453</v>
+        <v>1459</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>1457</v>
+        <v>1463</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>1458</v>
+        <v>1464</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>1459</v>
+        <v>1465</v>
       </c>
       <c r="L119" s="2" t="s">
-        <v>1460</v>
+        <v>1466</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>1461</v>
+        <v>1467</v>
       </c>
       <c r="N119" s="2" t="s">
-        <v>1462</v>
+        <v>1468</v>
       </c>
       <c r="O119" s="2" t="s">
-        <v>1463</v>
+        <v>1469</v>
       </c>
       <c r="P119" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="120" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A120" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B120" s="3">
         <v>10115</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>1464</v>
+        <v>1470</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>1465</v>
+        <v>1471</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>1466</v>
+        <v>1472</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>1467</v>
+        <v>1473</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>1468</v>
+        <v>1474</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>1469</v>
+        <v>1475</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>1470</v>
+        <v>1476</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>1472</v>
+        <v>1478</v>
       </c>
       <c r="L120" s="2" t="s">
-        <v>1473</v>
+        <v>1479</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>1474</v>
+        <v>1480</v>
       </c>
       <c r="N120" s="2" t="s">
-        <v>1475</v>
+        <v>1481</v>
       </c>
       <c r="O120" s="2" t="s">
-        <v>1476</v>
+        <v>1482</v>
       </c>
       <c r="P120" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="121" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A121" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B121" s="3">
         <v>10116</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>1477</v>
+        <v>1483</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>1478</v>
+        <v>1484</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>1479</v>
+        <v>1485</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>1480</v>
+        <v>1486</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>1481</v>
+        <v>1487</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>1482</v>
+        <v>1488</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>1483</v>
+        <v>1489</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>1484</v>
+        <v>1490</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>1485</v>
+        <v>1491</v>
       </c>
       <c r="L121" s="2" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>1487</v>
+        <v>1493</v>
       </c>
       <c r="N121" s="2" t="s">
-        <v>1488</v>
+        <v>1494</v>
       </c>
       <c r="O121" s="2" t="s">
-        <v>1489</v>
+        <v>1495</v>
       </c>
       <c r="P121" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="122" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A122" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B122" s="3">
         <v>10117</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>1490</v>
+        <v>1496</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>1492</v>
+        <v>1498</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>1493</v>
+        <v>1499</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>1494</v>
+        <v>1500</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>1495</v>
+        <v>1501</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>1494</v>
+        <v>1500</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>1496</v>
+        <v>1502</v>
       </c>
       <c r="K122" s="2" t="s">
-        <v>1497</v>
+        <v>1503</v>
       </c>
       <c r="L122" s="2" t="s">
-        <v>1498</v>
+        <v>1504</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>1499</v>
+        <v>1505</v>
       </c>
       <c r="N122" s="2" t="s">
-        <v>1500</v>
+        <v>1506</v>
       </c>
       <c r="O122" s="2" t="s">
-        <v>1501</v>
+        <v>1507</v>
       </c>
       <c r="P122" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="123" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A123" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B123" s="3">
         <v>10118</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>1502</v>
+        <v>1508</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>1503</v>
+        <v>1509</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>1504</v>
+        <v>1510</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>1505</v>
+        <v>1511</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>1506</v>
+        <v>1512</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>1507</v>
+        <v>1513</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>1508</v>
+        <v>1514</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>1509</v>
+        <v>1515</v>
       </c>
       <c r="K123" s="2" t="s">
-        <v>1510</v>
+        <v>1516</v>
       </c>
       <c r="L123" s="2" t="s">
-        <v>1511</v>
+        <v>1517</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>1512</v>
+        <v>1518</v>
       </c>
       <c r="N123" s="2" t="s">
-        <v>1513</v>
+        <v>1519</v>
       </c>
       <c r="O123" s="2" t="s">
-        <v>1514</v>
+        <v>1520</v>
       </c>
       <c r="P123" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="124" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A124" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B124" s="3">
         <v>10119</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>1515</v>
+        <v>1521</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>1516</v>
+        <v>1522</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>1517</v>
+        <v>1523</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>1518</v>
+        <v>1524</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>1519</v>
+        <v>1525</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>1520</v>
+        <v>1526</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>1521</v>
+        <v>1527</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>1522</v>
+        <v>1528</v>
       </c>
       <c r="K124" s="2" t="s">
-        <v>1523</v>
+        <v>1529</v>
       </c>
       <c r="L124" s="2" t="s">
-        <v>1524</v>
+        <v>1530</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>1525</v>
+        <v>1531</v>
       </c>
       <c r="N124" s="2" t="s">
-        <v>1526</v>
+        <v>1532</v>
       </c>
       <c r="O124" s="2" t="s">
-        <v>1527</v>
+        <v>1533</v>
       </c>
       <c r="P124" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="125" s="2" customFormat="1" ht="27" spans="1:16">
       <c r="A125" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B125" s="3">
         <v>10120</v>
       </c>
-      <c r="C125" s="18" t="s">
-        <v>1528</v>
+      <c r="C125" s="20" t="s">
+        <v>1534</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>1529</v>
+        <v>1535</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>1529</v>
+        <v>1535</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>1530</v>
+        <v>1536</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>1531</v>
+        <v>1537</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>1532</v>
+        <v>1538</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>1533</v>
+        <v>1539</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>1534</v>
+        <v>1540</v>
       </c>
       <c r="K125" s="2" t="s">
-        <v>1529</v>
+        <v>1535</v>
       </c>
       <c r="L125" s="2" t="s">
-        <v>1535</v>
+        <v>1541</v>
       </c>
       <c r="M125" s="2" t="s">
-        <v>1536</v>
+        <v>1542</v>
       </c>
       <c r="N125" s="2" t="s">
-        <v>1537</v>
+        <v>1543</v>
       </c>
       <c r="O125" s="2" t="s">
-        <v>1538</v>
+        <v>1544</v>
       </c>
       <c r="P125" s="2" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="126" customHeight="1" spans="1:16">
@@ -11986,43 +12166,43 @@
         <v>10121</v>
       </c>
       <c r="C126" t="s">
-        <v>1539</v>
-      </c>
-      <c r="D126" s="19" t="s">
-        <v>1540</v>
-      </c>
-      <c r="E126" s="20" t="s">
-        <v>1541</v>
-      </c>
-      <c r="F126" s="20" t="s">
-        <v>1542</v>
-      </c>
-      <c r="G126" s="20" t="s">
-        <v>1543</v>
-      </c>
-      <c r="H126" s="20" t="s">
-        <v>1544</v>
-      </c>
-      <c r="I126" s="20" t="s">
         <v>1545</v>
       </c>
-      <c r="J126" s="20" t="s">
+      <c r="D126" s="12" t="s">
         <v>1546</v>
       </c>
-      <c r="K126" s="20" t="s">
+      <c r="E126" s="11" t="s">
         <v>1547</v>
       </c>
-      <c r="L126" s="20" t="s">
+      <c r="F126" s="11" t="s">
         <v>1548</v>
       </c>
-      <c r="M126" s="20" t="s">
+      <c r="G126" s="11" t="s">
         <v>1549</v>
       </c>
-      <c r="N126" s="20" t="s">
+      <c r="H126" s="11" t="s">
         <v>1550</v>
       </c>
-      <c r="O126" s="20" t="s">
+      <c r="I126" s="11" t="s">
         <v>1551</v>
+      </c>
+      <c r="J126" s="11" t="s">
+        <v>1552</v>
+      </c>
+      <c r="K126" s="11" t="s">
+        <v>1553</v>
+      </c>
+      <c r="L126" s="11" t="s">
+        <v>1554</v>
+      </c>
+      <c r="M126" s="11" t="s">
+        <v>1555</v>
+      </c>
+      <c r="N126" s="11" t="s">
+        <v>1556</v>
+      </c>
+      <c r="O126" s="11" t="s">
+        <v>1557</v>
       </c>
     </row>
     <row r="127" customHeight="1" spans="1:16">
@@ -12030,43 +12210,43 @@
         <v>10122</v>
       </c>
       <c r="C127" t="s">
-        <v>1552</v>
-      </c>
-      <c r="D127" s="19" t="s">
-        <v>1553</v>
-      </c>
-      <c r="E127" s="20" t="s">
-        <v>1554</v>
-      </c>
-      <c r="F127" s="20" t="s">
-        <v>1555</v>
-      </c>
-      <c r="G127" s="20" t="s">
-        <v>1556</v>
-      </c>
-      <c r="H127" s="20" t="s">
-        <v>1557</v>
-      </c>
-      <c r="I127" s="20" t="s">
         <v>1558</v>
       </c>
-      <c r="J127" s="20" t="s">
+      <c r="D127" s="12" t="s">
         <v>1559</v>
       </c>
-      <c r="K127" s="20" t="s">
+      <c r="E127" s="11" t="s">
         <v>1560</v>
       </c>
-      <c r="L127" s="20" t="s">
+      <c r="F127" s="11" t="s">
         <v>1561</v>
       </c>
-      <c r="M127" s="20" t="s">
+      <c r="G127" s="11" t="s">
         <v>1562</v>
       </c>
-      <c r="N127" s="20" t="s">
+      <c r="H127" s="11" t="s">
         <v>1563</v>
       </c>
-      <c r="O127" s="20" t="s">
+      <c r="I127" s="11" t="s">
         <v>1564</v>
+      </c>
+      <c r="J127" s="11" t="s">
+        <v>1565</v>
+      </c>
+      <c r="K127" s="11" t="s">
+        <v>1566</v>
+      </c>
+      <c r="L127" s="11" t="s">
+        <v>1567</v>
+      </c>
+      <c r="M127" s="11" t="s">
+        <v>1568</v>
+      </c>
+      <c r="N127" s="11" t="s">
+        <v>1569</v>
+      </c>
+      <c r="O127" s="11" t="s">
+        <v>1570</v>
       </c>
     </row>
     <row r="128" customHeight="1" spans="1:16">
@@ -12074,43 +12254,43 @@
         <v>10123</v>
       </c>
       <c r="C128" t="s">
-        <v>1565</v>
-      </c>
-      <c r="D128" s="19" t="s">
-        <v>1566</v>
-      </c>
-      <c r="E128" s="20" t="s">
-        <v>1567</v>
-      </c>
-      <c r="F128" s="20" t="s">
-        <v>1568</v>
-      </c>
-      <c r="G128" s="20" t="s">
-        <v>1569</v>
-      </c>
-      <c r="H128" s="20" t="s">
-        <v>1570</v>
-      </c>
-      <c r="I128" s="20" t="s">
         <v>1571</v>
       </c>
-      <c r="J128" s="20" t="s">
+      <c r="D128" s="12" t="s">
         <v>1572</v>
       </c>
-      <c r="K128" s="20" t="s">
+      <c r="E128" s="11" t="s">
         <v>1573</v>
       </c>
-      <c r="L128" s="20" t="s">
+      <c r="F128" s="11" t="s">
         <v>1574</v>
       </c>
-      <c r="M128" s="20" t="s">
+      <c r="G128" s="11" t="s">
         <v>1575</v>
       </c>
-      <c r="N128" s="20" t="s">
+      <c r="H128" s="11" t="s">
         <v>1576</v>
       </c>
-      <c r="O128" s="20" t="s">
+      <c r="I128" s="11" t="s">
         <v>1577</v>
+      </c>
+      <c r="J128" s="11" t="s">
+        <v>1578</v>
+      </c>
+      <c r="K128" s="11" t="s">
+        <v>1579</v>
+      </c>
+      <c r="L128" s="11" t="s">
+        <v>1580</v>
+      </c>
+      <c r="M128" s="11" t="s">
+        <v>1581</v>
+      </c>
+      <c r="N128" s="11" t="s">
+        <v>1582</v>
+      </c>
+      <c r="O128" s="11" t="s">
+        <v>1583</v>
       </c>
     </row>
     <row r="129" customHeight="1" spans="2:15">
@@ -12118,43 +12298,43 @@
         <v>10124</v>
       </c>
       <c r="C129" t="s">
-        <v>1578</v>
-      </c>
-      <c r="D129" s="19" t="s">
-        <v>1579</v>
-      </c>
-      <c r="E129" s="20" t="s">
-        <v>1580</v>
-      </c>
-      <c r="F129" s="20" t="s">
-        <v>1581</v>
-      </c>
-      <c r="G129" s="20" t="s">
-        <v>1582</v>
-      </c>
-      <c r="H129" s="20" t="s">
-        <v>1583</v>
-      </c>
-      <c r="I129" s="20" t="s">
         <v>1584</v>
       </c>
-      <c r="J129" s="20" t="s">
+      <c r="D129" s="12" t="s">
         <v>1585</v>
       </c>
-      <c r="K129" s="20" t="s">
+      <c r="E129" s="11" t="s">
         <v>1586</v>
       </c>
-      <c r="L129" s="20" t="s">
+      <c r="F129" s="11" t="s">
         <v>1587</v>
       </c>
-      <c r="M129" s="20" t="s">
+      <c r="G129" s="11" t="s">
         <v>1588</v>
       </c>
-      <c r="N129" s="20" t="s">
+      <c r="H129" s="11" t="s">
         <v>1589</v>
       </c>
-      <c r="O129" s="20" t="s">
+      <c r="I129" s="11" t="s">
         <v>1590</v>
+      </c>
+      <c r="J129" s="11" t="s">
+        <v>1591</v>
+      </c>
+      <c r="K129" s="11" t="s">
+        <v>1592</v>
+      </c>
+      <c r="L129" s="11" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M129" s="11" t="s">
+        <v>1594</v>
+      </c>
+      <c r="N129" s="11" t="s">
+        <v>1595</v>
+      </c>
+      <c r="O129" s="11" t="s">
+        <v>1596</v>
       </c>
     </row>
     <row r="130" customHeight="1" spans="2:15">
@@ -12162,43 +12342,43 @@
         <v>10125</v>
       </c>
       <c r="C130" t="s">
-        <v>1591</v>
-      </c>
-      <c r="D130" s="19" t="s">
-        <v>1592</v>
-      </c>
-      <c r="E130" s="20" t="s">
-        <v>1593</v>
-      </c>
-      <c r="F130" s="20" t="s">
-        <v>1594</v>
-      </c>
-      <c r="G130" s="20" t="s">
-        <v>1595</v>
-      </c>
-      <c r="H130" s="20" t="s">
-        <v>1596</v>
-      </c>
-      <c r="I130" s="20" t="s">
         <v>1597</v>
       </c>
-      <c r="J130" s="20" t="s">
+      <c r="D130" s="12" t="s">
         <v>1598</v>
       </c>
-      <c r="K130" s="20" t="s">
+      <c r="E130" s="11" t="s">
         <v>1599</v>
       </c>
-      <c r="L130" s="20" t="s">
+      <c r="F130" s="11" t="s">
         <v>1600</v>
       </c>
-      <c r="M130" s="20" t="s">
+      <c r="G130" s="11" t="s">
         <v>1601</v>
       </c>
-      <c r="N130" s="20" t="s">
+      <c r="H130" s="11" t="s">
         <v>1602</v>
       </c>
-      <c r="O130" s="20" t="s">
+      <c r="I130" s="11" t="s">
         <v>1603</v>
+      </c>
+      <c r="J130" s="11" t="s">
+        <v>1604</v>
+      </c>
+      <c r="K130" s="11" t="s">
+        <v>1605</v>
+      </c>
+      <c r="L130" s="11" t="s">
+        <v>1606</v>
+      </c>
+      <c r="M130" s="11" t="s">
+        <v>1607</v>
+      </c>
+      <c r="N130" s="11" t="s">
+        <v>1608</v>
+      </c>
+      <c r="O130" s="11" t="s">
+        <v>1609</v>
       </c>
     </row>
   </sheetData>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="1610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1733" uniqueCount="1621">
   <si>
     <t>##var</t>
   </si>
@@ -1191,6 +1191,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>Ş</t>
     </r>
     <r>
@@ -1391,6 +1397,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>Ş</t>
     </r>
     <r>
@@ -1459,6 +1471,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>Bo</t>
     </r>
     <r>
@@ -5213,6 +5231,39 @@
   </si>
   <si>
     <t>&lt;color=#FFED74&gt;{0}&lt;/color&gt; oyuncu &lt;color=#FFED74&gt;{1} dakika&lt;/color&gt; içinde hedefe ulaştı, tüm &lt;color=#FFED74&gt;{2}&lt;/color&gt; çekti</t>
+  </si>
+  <si>
+    <t>{0} 分钟</t>
+  </si>
+  <si>
+    <t>{0} Minute</t>
+  </si>
+  <si>
+    <t>{0} 分</t>
+  </si>
+  <si>
+    <t>{0} minuto</t>
+  </si>
+  <si>
+    <t>{0} minute</t>
+  </si>
+  <si>
+    <t>{0}분</t>
+  </si>
+  <si>
+    <t>{0} menit</t>
+  </si>
+  <si>
+    <t>{0} минута</t>
+  </si>
+  <si>
+    <t>{0} मिनट</t>
+  </si>
+  <si>
+    <t>{0} นาที</t>
+  </si>
+  <si>
+    <t>{0} dakika</t>
   </si>
 </sst>
 </file>
@@ -6476,7 +6527,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W130"/>
+  <dimension ref="A1:W131"/>
   <sheetFormatPr defaultColWidth="9.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.875" customWidth="1"/>
@@ -12381,6 +12432,50 @@
         <v>1609</v>
       </c>
     </row>
+    <row r="131" customHeight="1" spans="2:15">
+      <c r="B131" s="3">
+        <v>10126</v>
+      </c>
+      <c r="C131" t="s">
+        <v>1610</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="E131" t="s">
+        <v>1611</v>
+      </c>
+      <c r="F131" t="s">
+        <v>1612</v>
+      </c>
+      <c r="G131" t="s">
+        <v>1613</v>
+      </c>
+      <c r="H131" t="s">
+        <v>1614</v>
+      </c>
+      <c r="I131" t="s">
+        <v>1613</v>
+      </c>
+      <c r="J131" t="s">
+        <v>1615</v>
+      </c>
+      <c r="K131" t="s">
+        <v>1616</v>
+      </c>
+      <c r="L131" t="s">
+        <v>1617</v>
+      </c>
+      <c r="M131" t="s">
+        <v>1618</v>
+      </c>
+      <c r="N131" t="s">
+        <v>1619</v>
+      </c>
+      <c r="O131" t="s">
+        <v>1620</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -5194,43 +5194,274 @@
     <t>VERİ GÖSTERİMİ</t>
   </si>
   <si>
-    <t>&lt;color=#FFED74&gt;{0}&lt;/color&gt;的玩家在&lt;color=#FFED74&gt;{1} 分钟&lt;/color&gt;内达到了目标, 提现了所有 &lt;color=#FFED74&gt;{2}&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=#FFED74&gt;{0}&lt;/color&gt; of player reached the goal within &lt;color=#FFED74&gt;{1} minutes&lt;/color&gt;, withdrawn all &lt;color=#FFED74&gt;{2}&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=#FFED74&gt;{0}&lt;/color&gt; Spieler erreichten Ziel in &lt;color=#FFED74&gt;{1} Min.&lt;/color&gt;, hoben alle &lt;color=#FFED74&gt;{2}&lt;/color&gt; ab</t>
-  </si>
-  <si>
-    <t>&lt;color=#FFED74&gt;{0}&lt;/color&gt;のプレイヤーが&lt;color=#FFED74&gt;{1}分&lt;/color&gt;以内に目標達成、&lt;color=#FFED74&gt;{2}&lt;/color&gt;を全額出金</t>
-  </si>
-  <si>
-    <t>&lt;color=#FFED74&gt;{0}&lt;/color&gt; dos jogadores atingiram o objetivo em &lt;color=#FFED74&gt;{1} min.&lt;/color&gt;, sacaram todo o &lt;color=#FFED74&gt;{2}&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=#FFED74&gt;{0}&lt;/color&gt; des joueurs ont atteint l'objectif en &lt;color=#FFED74&gt;{1} min.&lt;/color&gt;, ont retiré tout le &lt;color=#FFED74&gt;{2}&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=#FFED74&gt;{0}&lt;/color&gt; de los jugadores alcanzaron el objetivo en &lt;color=#FFED74&gt;{1} min.&lt;/color&gt;, retiraron todo el &lt;color=#FFED74&gt;{2}&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=#FFED74&gt;{0}&lt;/color&gt; 플레이어 &lt;color=#FFED74&gt;{1}분&lt;/color&gt; 내 목표 달성, &lt;color=#FFED74&gt;{2}&lt;/color&gt; 전액 출금</t>
-  </si>
-  <si>
-    <t>&lt;color=#FFED74&gt;{0}&lt;/color&gt; pemain capai tujuan dalam &lt;color=#FFED74&gt;{1} menit&lt;/color&gt;, tarik semua &lt;color=#FFED74&gt;{2}&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=#FFED74&gt;{0}&lt;/color&gt; игроков достигли цели за &lt;color=#FFED74&gt;{1} мин.&lt;/color&gt;, вывели все &lt;color=#FFED74&gt;{2}&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=#FFED74&gt;{0}&lt;/color&gt; खिलाड़ियों ने &lt;color=#FFED74&gt;{1} मिनट&lt;/color&gt; में लक्ष्य हासिल, सभी &lt;color=#FFED74&gt;{2}&lt;/color&gt; निकाल लिया</t>
-  </si>
-  <si>
-    <t>ผู้เล่น &lt;color=#FFED74&gt;{0}&lt;/color&gt; ครบเป้าหมายภายใน &lt;color=#FFED74&gt;{1} นาที&lt;/color&gt; ถอน &lt;color=#FFED74&gt;{2}&lt;/color&gt; ทั้งหมด</t>
-  </si>
-  <si>
-    <t>&lt;color=#FFED74&gt;{0}&lt;/color&gt; oyuncu &lt;color=#FFED74&gt;{1} dakika&lt;/color&gt; içinde hedefe ulaştı, tüm &lt;color=#FFED74&gt;{2}&lt;/color&gt; çekti</t>
+    <t>&lt;color=#FFED74&gt;{0}%&lt;/color&gt;的玩家在&lt;color=#FFED74&gt;{1} 分钟&lt;/color&gt;内达到了目标, 提现了所有 &lt;color=#FFED74&gt;{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFED74&gt;{0}%&lt;/color&gt; of player reached the goal within &lt;color=#FFED74&gt;{1} minutes&lt;/color&gt;, withdrawn all &lt;color=#FFED74&gt;{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFED74&gt;{0}%&lt;/color&gt; Spieler erreichten Ziel in &lt;color=#FFED74&gt;{1} Min.&lt;/color&gt;, hoben alle &lt;color=#FFED74&gt;{2}&lt;/color&gt; ab</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFED74&gt;{0}%&lt;/color&gt;のプレイヤーが&lt;color=#FFED74&gt;{1}分&lt;/color&gt;以内に目標達成、&lt;color=#FFED74&gt;{2}&lt;/color&gt;を全額出金</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFED74&gt;{0}%&lt;/color&gt; dos jogadores atingiram o objetivo em &lt;color=#FFED74&gt;{1} min.&lt;/color&gt;, sacaram todo o &lt;color=#FFED74&gt;{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFED74&gt;{0}%&lt;/color&gt; des joueurs ont atteint l'objectif en &lt;color=#FFED74&gt;{1} min.&lt;/color&gt;, ont retiré tout le &lt;color=#FFED74&gt;{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFED74&gt;{0}%&lt;/color&gt; de los jugadores alcanzaron el objetivo en &lt;color=#FFED74&gt;{1} min.&lt;/color&gt;, retiraron todo el &lt;color=#FFED74&gt;{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;color=#FFED74&gt;{0}%&lt;/color&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>플레이어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;color=#FFED74&gt;{1}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>분</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/color&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>달성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">, &lt;color=#FFED74&gt;{2}&lt;/color&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>전액</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>출금</t>
+    </r>
+  </si>
+  <si>
+    <t>&lt;color=#FFED74&gt;{0}%&lt;/color&gt; pemain capai tujuan dalam &lt;color=#FFED74&gt;{1} menit&lt;/color&gt;, tarik semua &lt;color=#FFED74&gt;{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFED74&gt;{0}%&lt;/color&gt; игроков достигли цели за &lt;color=#FFED74&gt;{1} мин.&lt;/color&gt;, вывели все &lt;color=#FFED74&gt;{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFED74&gt;{0}%&lt;/color&gt; खिलाड़ियों ने &lt;color=#FFED74&gt;{1} मिनट&lt;/color&gt; में लक्ष्य हासिल, सभी &lt;color=#FFED74&gt;{2}&lt;/color&gt; निकाल लिया</t>
+  </si>
+  <si>
+    <r>
+      <t>ผู้เล่น</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;color=#FFED74&gt;{0}%&lt;/color&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Tahoma"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ครบเป้าหมายภายใน</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;color=#FFED74&gt;{1} </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Tahoma"/>
+        <charset val="134"/>
+      </rPr>
+      <t>นาที</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/color&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Tahoma"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ถอน</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;color=#FFED74&gt;{2}&lt;/color&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Tahoma"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ทั้งหมด</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>&lt;color=#FFED74&gt;{0}%&lt;/color&gt; oyuncu &lt;color=#FFED74&gt;{1} dakika&lt;/color&gt; içinde hedefe ula</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ş</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ı</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>, tüm &lt;color=#FFED74&gt;{2}&lt;/color&gt; çekti</t>
+    </r>
   </si>
   <si>
     <t>{0} 分钟</t>
@@ -12425,7 +12656,7 @@
       <c r="M130" s="11" t="s">
         <v>1607</v>
       </c>
-      <c r="N130" s="11" t="s">
+      <c r="N130" s="14" t="s">
         <v>1608</v>
       </c>
       <c r="O130" s="11" t="s">

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -5216,6 +5216,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">&lt;color=#FFED74&gt;{0}%&lt;/color&gt; </t>
     </r>
     <r>
@@ -5347,6 +5353,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Tahoma"/>
+        <charset val="134"/>
+      </rPr>
       <t>ผู้เล่น</t>
     </r>
     <r>
@@ -5424,6 +5436,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>&lt;color=#FFED74&gt;{0}%&lt;/color&gt; oyuncu &lt;color=#FFED74&gt;{1} dakika&lt;/color&gt; içinde hedefe ula</t>
     </r>
     <r>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1733" uniqueCount="1621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="1634">
   <si>
     <t>##var</t>
   </si>
@@ -5513,6 +5513,58 @@
   </si>
   <si>
     <t>{0} dakika</t>
+  </si>
+  <si>
+    <t>观看完整视频
+领取现金奖励</t>
+  </si>
+  <si>
+    <t>Watch full video
+Claim Cash Reward</t>
+  </si>
+  <si>
+    <t>Gesamtes Video ansehen
+Bargeldprämie erhalten</t>
+  </si>
+  <si>
+    <t>動画を最後まで視聴
+現金報酬を受け取る</t>
+  </si>
+  <si>
+    <t>Assistir ao vídeo completo
+Resgatar recompensa em dinheiro</t>
+  </si>
+  <si>
+    <t>Regarder la vidéo en entier
+Réclamer la récompense en argent</t>
+  </si>
+  <si>
+    <t>Ver el video completo
+Reclamar recompensa en efectivo</t>
+  </si>
+  <si>
+    <t>전체 영상 시청
+현금 보상 받기</t>
+  </si>
+  <si>
+    <t>Tonton video lengkap
+Klaim hadiah uang tunai</t>
+  </si>
+  <si>
+    <t>Посмотреть видео до конца
+Получить денежную награду</t>
+  </si>
+  <si>
+    <t>पूरा वीडियो देखें
+नकद इनाम प्राप्त करें</t>
+  </si>
+  <si>
+    <t>ดูวิดีโอจนจบ
+รับรางวัลเงินสด</t>
+  </si>
+  <si>
+    <t>Videoyu sonuna kadar izle
+Nakit ödülü al</t>
   </si>
 </sst>
 </file>
@@ -6185,13 +6237,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -6239,6 +6292,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -6776,11 +6832,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W131"/>
+  <dimension ref="A1:W132"/>
   <sheetFormatPr defaultColWidth="9.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.875" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="4" customWidth="1"/>
     <col min="3" max="3" width="31.625" customWidth="1"/>
     <col min="4" max="4" width="54.25" style="1" customWidth="1"/>
     <col min="5" max="6" width="28.125" customWidth="1"/>
@@ -6790,49 +6846,49 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:16">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="8" t="s">
         <v>14</v>
       </c>
       <c r="P1" t="s">
@@ -6840,68 +6896,68 @@
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:16">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
     </row>
     <row r="3" customHeight="1" spans="1:16">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P3" t="s">
@@ -6909,49 +6965,49 @@
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:16">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="M4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="N4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="9" t="s">
+      <c r="O4" s="10" t="s">
         <v>19</v>
       </c>
       <c r="P4" t="s">
@@ -6959,49 +7015,49 @@
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:16">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="O5" s="7" t="s">
         <v>33</v>
       </c>
       <c r="P5" t="s">
@@ -7009,1059 +7065,1059 @@
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="13.5" spans="1:16">
-      <c r="B6" s="10">
+      <c r="B6" s="11">
         <v>10001</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="N6" s="11" t="s">
+      <c r="N6" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="O6" s="11" t="s">
+      <c r="O6" s="12" t="s">
         <v>47</v>
       </c>
       <c r="P6"/>
     </row>
     <row r="7" customFormat="1" customHeight="1" spans="1:16">
-      <c r="B7" s="10">
+      <c r="B7" s="11">
         <v>10002</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="L7" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="M7" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="N7" s="11" t="s">
+      <c r="N7" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="O7" s="11" t="s">
+      <c r="O7" s="12" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:16">
-      <c r="B8" s="10">
+      <c r="B8" s="11">
         <v>10003</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="J8" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="L8" s="11" t="s">
+      <c r="L8" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="M8" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="N8" s="11" t="s">
+      <c r="N8" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="O8" s="11" t="s">
+      <c r="O8" s="12" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:16">
-      <c r="B9" s="10">
+      <c r="B9" s="11">
         <v>10004</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="J9" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="L9" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="M9" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="N9" s="11" t="s">
+      <c r="N9" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="O9" s="11" t="s">
+      <c r="O9" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:16">
-      <c r="B10" s="10">
+      <c r="B10" s="11">
         <v>10005</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J10" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="L10" s="11" t="s">
+      <c r="L10" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="M10" s="11" t="s">
+      <c r="M10" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="N10" s="11" t="s">
+      <c r="N10" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="O10" s="11" t="s">
+      <c r="O10" s="12" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:16">
-      <c r="B11" s="10">
+      <c r="B11" s="11">
         <v>10006</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="J11" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="L11" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="M11" s="11" t="s">
+      <c r="M11" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="N11" s="11" t="s">
+      <c r="N11" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="O11" s="11" t="s">
+      <c r="O11" s="12" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="B12" s="10">
+      <c r="B12" s="11">
         <v>10007</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="J12" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K12" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="L12" s="11" t="s">
+      <c r="L12" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="M12" s="11" t="s">
+      <c r="M12" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="N12" s="11" t="s">
+      <c r="N12" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="O12" s="11" t="s">
+      <c r="O12" s="12" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="B13" s="10">
+      <c r="B13" s="11">
         <v>10008</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="J13" s="11" t="s">
+      <c r="J13" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K13" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="L13" s="11" t="s">
+      <c r="L13" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="M13" s="11" t="s">
+      <c r="M13" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="N13" s="11" t="s">
+      <c r="N13" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="O13" s="11" t="s">
+      <c r="O13" s="12" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:16">
-      <c r="B14" s="10">
+      <c r="B14" s="11">
         <v>10009</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K14" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="L14" s="11" t="s">
+      <c r="L14" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="M14" s="11" t="s">
+      <c r="M14" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="N14" s="11" t="s">
+      <c r="N14" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="O14" s="11" t="s">
+      <c r="O14" s="12" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:16">
-      <c r="B15" s="10">
+      <c r="B15" s="11">
         <v>10010</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J15" s="11" t="s">
+      <c r="J15" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="K15" s="11" t="s">
+      <c r="K15" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="L15" s="11" t="s">
+      <c r="L15" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="M15" s="11" t="s">
+      <c r="M15" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="N15" s="11" t="s">
+      <c r="N15" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="O15" s="11" t="s">
+      <c r="O15" s="12" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:16">
-      <c r="B16" s="10">
+      <c r="B16" s="11">
         <v>10011</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="H16" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="I16" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="J16" s="11" t="s">
+      <c r="J16" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="K16" s="11" t="s">
+      <c r="K16" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="L16" s="11" t="s">
+      <c r="L16" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="M16" s="11" t="s">
+      <c r="M16" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="N16" s="11" t="s">
+      <c r="N16" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="O16" s="11" t="s">
+      <c r="O16" s="12" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:23">
-      <c r="B17" s="10">
+      <c r="B17" s="11">
         <v>10012</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="H17" s="11" t="s">
+      <c r="H17" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="I17" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="J17" s="11" t="s">
+      <c r="J17" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="K17" s="11" t="s">
+      <c r="K17" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="L17" s="11" t="s">
+      <c r="L17" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="M17" s="11" t="s">
+      <c r="M17" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="N17" s="11" t="s">
+      <c r="N17" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="O17" s="11" t="s">
+      <c r="O17" s="12" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:23">
-      <c r="B18" s="10">
+      <c r="B18" s="11">
         <v>10013</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="H18" s="11" t="s">
+      <c r="H18" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="I18" s="11" t="s">
+      <c r="I18" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="J18" s="11" t="s">
+      <c r="J18" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="K18" s="11" t="s">
+      <c r="K18" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="L18" s="11" t="s">
+      <c r="L18" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="M18" s="11" t="s">
+      <c r="M18" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="N18" s="11" t="s">
+      <c r="N18" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="O18" s="11" t="s">
+      <c r="O18" s="12" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:23">
-      <c r="B19" s="10">
+      <c r="B19" s="11">
         <v>10014</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="H19" s="11" t="s">
+      <c r="H19" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="I19" s="11" t="s">
+      <c r="I19" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="J19" s="11" t="s">
+      <c r="J19" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="K19" s="11" t="s">
+      <c r="K19" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="L19" s="11" t="s">
+      <c r="L19" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="M19" s="11" t="s">
+      <c r="M19" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="N19" s="11" t="s">
+      <c r="N19" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="O19" s="11" t="s">
+      <c r="O19" s="12" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:23">
-      <c r="B20" s="10">
+      <c r="B20" s="11">
         <v>10015</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="G20" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="H20" s="11" t="s">
+      <c r="H20" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="I20" s="11" t="s">
+      <c r="I20" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="J20" s="11" t="s">
+      <c r="J20" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="K20" s="11" t="s">
+      <c r="K20" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="L20" s="11" t="s">
+      <c r="L20" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="M20" s="11" t="s">
+      <c r="M20" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="N20" s="11" t="s">
+      <c r="N20" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="O20" s="11" t="s">
+      <c r="O20" s="12" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:23">
-      <c r="B21" s="10">
+      <c r="B21" s="11">
         <v>10016</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="G21" s="11" t="s">
+      <c r="G21" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="H21" s="11" t="s">
+      <c r="H21" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="I21" s="11" t="s">
+      <c r="I21" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="J21" s="11" t="s">
+      <c r="J21" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="K21" s="11" t="s">
+      <c r="K21" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="L21" s="11" t="s">
+      <c r="L21" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="M21" s="11" t="s">
+      <c r="M21" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="N21" s="11" t="s">
+      <c r="N21" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="O21" s="11" t="s">
+      <c r="O21" s="12" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:23">
-      <c r="B22" s="10">
+      <c r="B22" s="11">
         <v>10017</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G22" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="H22" s="11" t="s">
+      <c r="H22" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="I22" s="11" t="s">
+      <c r="I22" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="J22" s="11" t="s">
+      <c r="J22" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="K22" s="11" t="s">
+      <c r="K22" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="L22" s="11" t="s">
+      <c r="L22" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="M22" s="11" t="s">
+      <c r="M22" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="N22" s="11" t="s">
+      <c r="N22" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="O22" s="11" t="s">
+      <c r="O22" s="12" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:23">
-      <c r="B23" s="10">
+      <c r="B23" s="11">
         <v>10018</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="G23" s="11" t="s">
+      <c r="G23" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="H23" s="11" t="s">
+      <c r="H23" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="I23" s="11" t="s">
+      <c r="I23" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="J23" s="11" t="s">
+      <c r="J23" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="K23" s="11" t="s">
+      <c r="K23" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="L23" s="11" t="s">
+      <c r="L23" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="M23" s="11" t="s">
+      <c r="M23" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="N23" s="11" t="s">
+      <c r="N23" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="O23" s="11" t="s">
+      <c r="O23" s="12" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="2:23">
-      <c r="B24" s="10">
+      <c r="B24" s="11">
         <v>10019</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="I24" s="11" t="s">
+      <c r="I24" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="J24" s="11" t="s">
+      <c r="J24" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="K24" s="11" t="s">
+      <c r="K24" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="L24" s="11" t="s">
+      <c r="L24" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="M24" s="11" t="s">
+      <c r="M24" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="N24" s="11" t="s">
+      <c r="N24" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="O24" s="11" t="s">
+      <c r="O24" s="12" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="2:23">
-      <c r="B25" s="10">
+      <c r="B25" s="11">
         <v>10020</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="G25" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="H25" s="11" t="s">
+      <c r="H25" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="I25" s="11" t="s">
+      <c r="I25" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="J25" s="11" t="s">
+      <c r="J25" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="K25" s="11" t="s">
+      <c r="K25" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="L25" s="11" t="s">
+      <c r="L25" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="M25" s="11" t="s">
+      <c r="M25" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="N25" s="11" t="s">
+      <c r="N25" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="O25" s="11" t="s">
+      <c r="O25" s="12" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:23">
-      <c r="B26" s="10">
+      <c r="B26" s="11">
         <v>10021</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="G26" s="11" t="s">
+      <c r="G26" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="H26" s="11" t="s">
+      <c r="H26" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="I26" s="11" t="s">
+      <c r="I26" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="J26" s="11" t="s">
+      <c r="J26" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="K26" s="11" t="s">
+      <c r="K26" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="L26" s="11" t="s">
+      <c r="L26" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="M26" s="11" t="s">
+      <c r="M26" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="N26" s="11" t="s">
+      <c r="N26" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="O26" s="11" t="s">
+      <c r="O26" s="12" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:23">
-      <c r="B27" s="10">
+      <c r="B27" s="11">
         <v>10022</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="G27" s="11" t="s">
+      <c r="G27" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="H27" s="11" t="s">
+      <c r="H27" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="I27" s="11" t="s">
+      <c r="I27" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="J27" s="11" t="s">
+      <c r="J27" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="K27" s="11" t="s">
+      <c r="K27" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="L27" s="11" t="s">
+      <c r="L27" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="M27" s="11" t="s">
+      <c r="M27" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="N27" s="11" t="s">
+      <c r="N27" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="O27" s="11" t="s">
+      <c r="O27" s="12" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="28" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B28" s="10">
+      <c r="B28" s="11">
         <v>10023</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="12" t="s">
         <v>312</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E28" s="12" t="s">
         <v>314</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="G28" s="11" t="s">
+      <c r="G28" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="H28" s="11" t="s">
+      <c r="H28" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="I28" s="11" t="s">
+      <c r="I28" s="12" t="s">
         <v>318</v>
       </c>
-      <c r="J28" s="11" t="s">
+      <c r="J28" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="K28" s="11" t="s">
+      <c r="K28" s="12" t="s">
         <v>320</v>
       </c>
-      <c r="L28" s="11" t="s">
+      <c r="L28" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="M28" s="11" t="s">
+      <c r="M28" s="12" t="s">
         <v>322</v>
       </c>
-      <c r="N28" s="11" t="s">
+      <c r="N28" s="12" t="s">
         <v>323</v>
       </c>
-      <c r="O28" s="11" t="s">
+      <c r="O28" s="12" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="29" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B29" s="10">
+      <c r="B29" s="11">
         <v>10024</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="12" t="s">
         <v>328</v>
       </c>
-      <c r="G29" s="11" t="s">
+      <c r="G29" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="H29" s="11" t="s">
+      <c r="H29" s="12" t="s">
         <v>330</v>
       </c>
-      <c r="I29" s="11" t="s">
+      <c r="I29" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="J29" s="11" t="s">
+      <c r="J29" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="K29" s="11" t="s">
+      <c r="K29" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="L29" s="11" t="s">
+      <c r="L29" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="M29" s="11" t="s">
+      <c r="M29" s="12" t="s">
         <v>335</v>
       </c>
-      <c r="N29" s="11" t="s">
+      <c r="N29" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="O29" s="11" t="s">
+      <c r="O29" s="12" t="s">
         <v>337</v>
       </c>
       <c r="Q29" s="1"/>
@@ -8073,46 +8129,46 @@
       <c r="W29" s="1"/>
     </row>
     <row r="30" customHeight="1" spans="2:23">
-      <c r="B30" s="10">
+      <c r="B30" s="11">
         <v>10025</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="13" t="s">
         <v>338</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="12" t="s">
         <v>340</v>
       </c>
-      <c r="G30" s="11" t="s">
+      <c r="G30" s="12" t="s">
         <v>341</v>
       </c>
-      <c r="H30" s="11" t="s">
+      <c r="H30" s="12" t="s">
         <v>342</v>
       </c>
-      <c r="I30" s="11" t="s">
+      <c r="I30" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="J30" s="11" t="s">
+      <c r="J30" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="K30" s="11" t="s">
+      <c r="K30" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="L30" s="11" t="s">
+      <c r="L30" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="M30" s="11" t="s">
+      <c r="M30" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="N30" s="11" t="s">
+      <c r="N30" s="12" t="s">
         <v>348</v>
       </c>
-      <c r="O30" s="11" t="s">
+      <c r="O30" s="12" t="s">
         <v>349</v>
       </c>
       <c r="P30" s="1"/>
@@ -8125,46 +8181,46 @@
       <c r="W30" s="1"/>
     </row>
     <row r="31" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B31" s="10">
+      <c r="B31" s="11">
         <v>10026</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="12" t="s">
         <v>353</v>
       </c>
-      <c r="G31" s="11" t="s">
+      <c r="G31" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="H31" s="11" t="s">
+      <c r="H31" s="12" t="s">
         <v>355</v>
       </c>
-      <c r="I31" s="11" t="s">
+      <c r="I31" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="J31" s="11" t="s">
+      <c r="J31" s="12" t="s">
         <v>356</v>
       </c>
-      <c r="K31" s="11" t="s">
+      <c r="K31" s="12" t="s">
         <v>357</v>
       </c>
-      <c r="L31" s="11" t="s">
+      <c r="L31" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="M31" s="11" t="s">
+      <c r="M31" s="12" t="s">
         <v>359</v>
       </c>
-      <c r="N31" s="11" t="s">
+      <c r="N31" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="O31" s="11" t="s">
+      <c r="O31" s="12" t="s">
         <v>361</v>
       </c>
       <c r="P31"/>
@@ -8177,135 +8233,135 @@
       <c r="W31" s="1"/>
     </row>
     <row r="32" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B32" s="10">
+      <c r="B32" s="11">
         <v>10027</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="12" t="s">
         <v>362</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E32" s="12" t="s">
         <v>364</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="12" t="s">
         <v>365</v>
       </c>
-      <c r="G32" s="11" t="s">
+      <c r="G32" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="H32" s="11" t="s">
+      <c r="H32" s="12" t="s">
         <v>367</v>
       </c>
-      <c r="I32" s="11" t="s">
+      <c r="I32" s="12" t="s">
         <v>368</v>
       </c>
-      <c r="J32" s="13" t="s">
+      <c r="J32" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="K32" s="11" t="s">
+      <c r="K32" s="12" t="s">
         <v>370</v>
       </c>
-      <c r="L32" s="11" t="s">
+      <c r="L32" s="12" t="s">
         <v>371</v>
       </c>
-      <c r="M32" s="11" t="s">
+      <c r="M32" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="N32" s="14" t="s">
+      <c r="N32" s="15" t="s">
         <v>373</v>
       </c>
-      <c r="O32" s="11" t="s">
+      <c r="O32" s="12" t="s">
         <v>374</v>
       </c>
       <c r="P32"/>
     </row>
     <row r="33" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B33" s="10">
+      <c r="B33" s="11">
         <v>10028</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="13" t="s">
         <v>375</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" s="12" t="s">
         <v>376</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="E33" s="12" t="s">
         <v>377</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="F33" s="12" t="s">
         <v>378</v>
       </c>
-      <c r="G33" s="11" t="s">
+      <c r="G33" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="H33" s="11" t="s">
+      <c r="H33" s="12" t="s">
         <v>380</v>
       </c>
-      <c r="I33" s="11" t="s">
+      <c r="I33" s="12" t="s">
         <v>381</v>
       </c>
-      <c r="J33" s="13" t="s">
+      <c r="J33" s="14" t="s">
         <v>382</v>
       </c>
-      <c r="K33" s="11" t="s">
+      <c r="K33" s="12" t="s">
         <v>383</v>
       </c>
-      <c r="L33" s="11" t="s">
+      <c r="L33" s="12" t="s">
         <v>384</v>
       </c>
-      <c r="M33" s="11" t="s">
+      <c r="M33" s="12" t="s">
         <v>385</v>
       </c>
-      <c r="N33" s="14" t="s">
+      <c r="N33" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="O33" s="15" t="s">
+      <c r="O33" s="16" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B34" s="10">
+      <c r="B34" s="11">
         <v>10029</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="12" t="s">
         <v>388</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="E34" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="12" t="s">
         <v>391</v>
       </c>
-      <c r="G34" s="11" t="s">
+      <c r="G34" s="12" t="s">
         <v>392</v>
       </c>
-      <c r="H34" s="11" t="s">
+      <c r="H34" s="12" t="s">
         <v>393</v>
       </c>
-      <c r="I34" s="11" t="s">
+      <c r="I34" s="12" t="s">
         <v>394</v>
       </c>
-      <c r="J34" s="13" t="s">
+      <c r="J34" s="14" t="s">
         <v>395</v>
       </c>
-      <c r="K34" s="11" t="s">
+      <c r="K34" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="L34" s="11" t="s">
+      <c r="L34" s="12" t="s">
         <v>397</v>
       </c>
-      <c r="M34" s="11" t="s">
+      <c r="M34" s="12" t="s">
         <v>398</v>
       </c>
-      <c r="N34" s="14" t="s">
+      <c r="N34" s="15" t="s">
         <v>399</v>
       </c>
-      <c r="O34" s="11" t="s">
+      <c r="O34" s="12" t="s">
         <v>400</v>
       </c>
       <c r="Q34"/>
@@ -8317,46 +8373,46 @@
       <c r="W34"/>
     </row>
     <row r="35" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B35" s="10">
+      <c r="B35" s="11">
         <v>10030</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="13" t="s">
         <v>401</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D35" s="12" t="s">
         <v>402</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="E35" s="12" t="s">
         <v>403</v>
       </c>
-      <c r="F35" s="11" t="s">
+      <c r="F35" s="12" t="s">
         <v>404</v>
       </c>
-      <c r="G35" s="11" t="s">
+      <c r="G35" s="12" t="s">
         <v>405</v>
       </c>
-      <c r="H35" s="11" t="s">
+      <c r="H35" s="12" t="s">
         <v>406</v>
       </c>
-      <c r="I35" s="11" t="s">
+      <c r="I35" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J35" s="13" t="s">
+      <c r="J35" s="14" t="s">
         <v>408</v>
       </c>
-      <c r="K35" s="11" t="s">
+      <c r="K35" s="12" t="s">
         <v>409</v>
       </c>
-      <c r="L35" s="11" t="s">
+      <c r="L35" s="12" t="s">
         <v>410</v>
       </c>
-      <c r="M35" s="11" t="s">
+      <c r="M35" s="12" t="s">
         <v>411</v>
       </c>
-      <c r="N35" s="14" t="s">
+      <c r="N35" s="15" t="s">
         <v>412</v>
       </c>
-      <c r="O35" s="11" t="s">
+      <c r="O35" s="12" t="s">
         <v>413</v>
       </c>
       <c r="P35"/>
@@ -8369,46 +8425,46 @@
       <c r="W35"/>
     </row>
     <row r="36" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B36" s="10">
+      <c r="B36" s="11">
         <v>10031</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C36" s="12" t="s">
         <v>414</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="D36" s="12" t="s">
         <v>415</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E36" s="12" t="s">
         <v>416</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="F36" s="12" t="s">
         <v>417</v>
       </c>
-      <c r="G36" s="11" t="s">
+      <c r="G36" s="12" t="s">
         <v>418</v>
       </c>
-      <c r="H36" s="11" t="s">
+      <c r="H36" s="12" t="s">
         <v>419</v>
       </c>
-      <c r="I36" s="11" t="s">
+      <c r="I36" s="12" t="s">
         <v>420</v>
       </c>
-      <c r="J36" s="13" t="s">
+      <c r="J36" s="14" t="s">
         <v>421</v>
       </c>
-      <c r="K36" s="11" t="s">
+      <c r="K36" s="12" t="s">
         <v>422</v>
       </c>
-      <c r="L36" s="11" t="s">
+      <c r="L36" s="12" t="s">
         <v>423</v>
       </c>
-      <c r="M36" s="11" t="s">
+      <c r="M36" s="12" t="s">
         <v>424</v>
       </c>
-      <c r="N36" s="14" t="s">
+      <c r="N36" s="15" t="s">
         <v>425</v>
       </c>
-      <c r="O36" s="15" t="s">
+      <c r="O36" s="16" t="s">
         <v>426</v>
       </c>
       <c r="P36"/>
@@ -8421,46 +8477,46 @@
       <c r="W36"/>
     </row>
     <row r="37" customHeight="1" spans="2:23">
-      <c r="B37" s="10">
+      <c r="B37" s="11">
         <v>10032</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="13" t="s">
         <v>427</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" s="12" t="s">
         <v>428</v>
       </c>
-      <c r="E37" s="11" t="s">
+      <c r="E37" s="12" t="s">
         <v>429</v>
       </c>
-      <c r="F37" s="11" t="s">
+      <c r="F37" s="12" t="s">
         <v>430</v>
       </c>
-      <c r="G37" s="11" t="s">
+      <c r="G37" s="12" t="s">
         <v>431</v>
       </c>
-      <c r="H37" s="11" t="s">
+      <c r="H37" s="12" t="s">
         <v>432</v>
       </c>
-      <c r="I37" s="11" t="s">
+      <c r="I37" s="12" t="s">
         <v>433</v>
       </c>
-      <c r="J37" s="13" t="s">
+      <c r="J37" s="14" t="s">
         <v>434</v>
       </c>
-      <c r="K37" s="11" t="s">
+      <c r="K37" s="12" t="s">
         <v>435</v>
       </c>
-      <c r="L37" s="11" t="s">
+      <c r="L37" s="12" t="s">
         <v>436</v>
       </c>
-      <c r="M37" s="11" t="s">
+      <c r="M37" s="12" t="s">
         <v>437</v>
       </c>
-      <c r="N37" s="14" t="s">
+      <c r="N37" s="15" t="s">
         <v>438</v>
       </c>
-      <c r="O37" s="11" t="s">
+      <c r="O37" s="12" t="s">
         <v>439</v>
       </c>
       <c r="Q37" s="1"/>
@@ -8472,46 +8528,46 @@
       <c r="W37" s="1"/>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B38" s="10">
+      <c r="B38" s="11">
         <v>10033</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="12" t="s">
         <v>440</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="D38" s="12" t="s">
         <v>441</v>
       </c>
-      <c r="E38" s="11" t="s">
+      <c r="E38" s="12" t="s">
         <v>442</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="F38" s="12" t="s">
         <v>443</v>
       </c>
-      <c r="G38" s="11" t="s">
+      <c r="G38" s="12" t="s">
         <v>444</v>
       </c>
-      <c r="H38" s="11" t="s">
+      <c r="H38" s="12" t="s">
         <v>445</v>
       </c>
-      <c r="I38" s="11" t="s">
+      <c r="I38" s="12" t="s">
         <v>446</v>
       </c>
-      <c r="J38" s="11" t="s">
+      <c r="J38" s="12" t="s">
         <v>447</v>
       </c>
-      <c r="K38" s="11" t="s">
+      <c r="K38" s="12" t="s">
         <v>448</v>
       </c>
-      <c r="L38" s="11" t="s">
+      <c r="L38" s="12" t="s">
         <v>449</v>
       </c>
-      <c r="M38" s="11" t="s">
+      <c r="M38" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="N38" s="11" t="s">
+      <c r="N38" s="12" t="s">
         <v>451</v>
       </c>
-      <c r="O38" s="11" t="s">
+      <c r="O38" s="12" t="s">
         <v>452</v>
       </c>
       <c r="P38" s="1"/>
@@ -8524,90 +8580,90 @@
       <c r="W38" s="1"/>
     </row>
     <row r="39" customHeight="1" spans="2:23">
-      <c r="B39" s="10">
+      <c r="B39" s="11">
         <v>10034</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="12" t="s">
         <v>453</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="D39" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="E39" s="11" t="s">
+      <c r="E39" s="12" t="s">
         <v>455</v>
       </c>
-      <c r="F39" s="11" t="s">
+      <c r="F39" s="12" t="s">
         <v>456</v>
       </c>
-      <c r="G39" s="11" t="s">
+      <c r="G39" s="12" t="s">
         <v>457</v>
       </c>
-      <c r="H39" s="11" t="s">
+      <c r="H39" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="I39" s="11" t="s">
+      <c r="I39" s="12" t="s">
         <v>459</v>
       </c>
-      <c r="J39" s="11" t="s">
+      <c r="J39" s="12" t="s">
         <v>460</v>
       </c>
-      <c r="K39" s="11" t="s">
+      <c r="K39" s="12" t="s">
         <v>461</v>
       </c>
-      <c r="L39" s="11" t="s">
+      <c r="L39" s="12" t="s">
         <v>462</v>
       </c>
-      <c r="M39" s="11" t="s">
+      <c r="M39" s="12" t="s">
         <v>463</v>
       </c>
-      <c r="N39" s="11" t="s">
+      <c r="N39" s="12" t="s">
         <v>464</v>
       </c>
-      <c r="O39" s="11" t="s">
+      <c r="O39" s="12" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" ht="20" customHeight="1" spans="2:23">
-      <c r="B40" s="10">
+      <c r="B40" s="11">
         <v>10035</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C40" s="12" t="s">
         <v>466</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="D40" s="12" t="s">
         <v>467</v>
       </c>
-      <c r="E40" s="11" t="s">
+      <c r="E40" s="12" t="s">
         <v>468</v>
       </c>
-      <c r="F40" s="11" t="s">
+      <c r="F40" s="12" t="s">
         <v>469</v>
       </c>
-      <c r="G40" s="11" t="s">
+      <c r="G40" s="12" t="s">
         <v>470</v>
       </c>
-      <c r="H40" s="11" t="s">
+      <c r="H40" s="12" t="s">
         <v>471</v>
       </c>
-      <c r="I40" s="11" t="s">
+      <c r="I40" s="12" t="s">
         <v>472</v>
       </c>
-      <c r="J40" s="11" t="s">
+      <c r="J40" s="12" t="s">
         <v>473</v>
       </c>
-      <c r="K40" s="11" t="s">
+      <c r="K40" s="12" t="s">
         <v>474</v>
       </c>
-      <c r="L40" s="11" t="s">
+      <c r="L40" s="12" t="s">
         <v>475</v>
       </c>
-      <c r="M40" s="11" t="s">
+      <c r="M40" s="12" t="s">
         <v>476</v>
       </c>
-      <c r="N40" s="11" t="s">
+      <c r="N40" s="12" t="s">
         <v>477</v>
       </c>
-      <c r="O40" s="11" t="s">
+      <c r="O40" s="12" t="s">
         <v>478</v>
       </c>
       <c r="P40"/>
@@ -8620,46 +8676,46 @@
       <c r="W40"/>
     </row>
     <row r="41" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B41" s="10">
+      <c r="B41" s="11">
         <v>10036</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="13" t="s">
         <v>479</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D41" s="12" t="s">
         <v>480</v>
       </c>
-      <c r="E41" s="11" t="s">
+      <c r="E41" s="12" t="s">
         <v>481</v>
       </c>
-      <c r="F41" s="11" t="s">
+      <c r="F41" s="12" t="s">
         <v>482</v>
       </c>
-      <c r="G41" s="11" t="s">
+      <c r="G41" s="12" t="s">
         <v>483</v>
       </c>
-      <c r="H41" s="11" t="s">
+      <c r="H41" s="12" t="s">
         <v>484</v>
       </c>
-      <c r="I41" s="11" t="s">
+      <c r="I41" s="12" t="s">
         <v>483</v>
       </c>
-      <c r="J41" s="11" t="s">
+      <c r="J41" s="12" t="s">
         <v>485</v>
       </c>
-      <c r="K41" s="11" t="s">
+      <c r="K41" s="12" t="s">
         <v>486</v>
       </c>
-      <c r="L41" s="11" t="s">
+      <c r="L41" s="12" t="s">
         <v>487</v>
       </c>
-      <c r="M41" s="11" t="s">
+      <c r="M41" s="12" t="s">
         <v>488</v>
       </c>
-      <c r="N41" s="11" t="s">
+      <c r="N41" s="12" t="s">
         <v>489</v>
       </c>
-      <c r="O41" s="11" t="s">
+      <c r="O41" s="12" t="s">
         <v>490</v>
       </c>
       <c r="P41"/>
@@ -8672,226 +8728,226 @@
       <c r="W41"/>
     </row>
     <row r="42" customHeight="1" spans="2:23">
-      <c r="B42" s="10">
+      <c r="B42" s="11">
         <v>10037</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="13" t="s">
         <v>491</v>
       </c>
-      <c r="D42" s="11" t="s">
+      <c r="D42" s="12" t="s">
         <v>492</v>
       </c>
-      <c r="E42" s="11" t="s">
+      <c r="E42" s="12" t="s">
         <v>493</v>
       </c>
-      <c r="F42" s="11" t="s">
+      <c r="F42" s="12" t="s">
         <v>494</v>
       </c>
-      <c r="G42" s="11" t="s">
+      <c r="G42" s="12" t="s">
         <v>495</v>
       </c>
-      <c r="H42" s="11" t="s">
+      <c r="H42" s="12" t="s">
         <v>496</v>
       </c>
-      <c r="I42" s="11" t="s">
+      <c r="I42" s="12" t="s">
         <v>497</v>
       </c>
-      <c r="J42" s="11" t="s">
+      <c r="J42" s="12" t="s">
         <v>498</v>
       </c>
-      <c r="K42" s="11" t="s">
+      <c r="K42" s="12" t="s">
         <v>499</v>
       </c>
-      <c r="L42" s="11" t="s">
+      <c r="L42" s="12" t="s">
         <v>500</v>
       </c>
-      <c r="M42" s="11" t="s">
+      <c r="M42" s="12" t="s">
         <v>501</v>
       </c>
-      <c r="N42" s="11" t="s">
+      <c r="N42" s="12" t="s">
         <v>502</v>
       </c>
-      <c r="O42" s="11" t="s">
+      <c r="O42" s="12" t="s">
         <v>503</v>
       </c>
       <c r="P42" s="1"/>
     </row>
     <row r="43" customHeight="1" spans="2:23">
-      <c r="B43" s="10">
+      <c r="B43" s="11">
         <v>10038</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C43" s="12" t="s">
         <v>504</v>
       </c>
-      <c r="D43" s="11" t="s">
+      <c r="D43" s="12" t="s">
         <v>505</v>
       </c>
-      <c r="E43" s="11" t="s">
+      <c r="E43" s="12" t="s">
         <v>506</v>
       </c>
-      <c r="F43" s="11" t="s">
+      <c r="F43" s="12" t="s">
         <v>507</v>
       </c>
-      <c r="G43" s="11" t="s">
+      <c r="G43" s="12" t="s">
         <v>508</v>
       </c>
-      <c r="H43" s="11" t="s">
+      <c r="H43" s="12" t="s">
         <v>509</v>
       </c>
-      <c r="I43" s="11" t="s">
+      <c r="I43" s="12" t="s">
         <v>510</v>
       </c>
-      <c r="J43" s="11" t="s">
+      <c r="J43" s="12" t="s">
         <v>511</v>
       </c>
-      <c r="K43" s="11" t="s">
+      <c r="K43" s="12" t="s">
         <v>512</v>
       </c>
-      <c r="L43" s="11" t="s">
+      <c r="L43" s="12" t="s">
         <v>513</v>
       </c>
-      <c r="M43" s="11" t="s">
+      <c r="M43" s="12" t="s">
         <v>514</v>
       </c>
-      <c r="N43" s="11" t="s">
+      <c r="N43" s="12" t="s">
         <v>515</v>
       </c>
-      <c r="O43" s="11" t="s">
+      <c r="O43" s="12" t="s">
         <v>516</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:23">
-      <c r="B44" s="10">
+      <c r="B44" s="11">
         <v>10039</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C44" s="12" t="s">
         <v>517</v>
       </c>
-      <c r="D44" s="11" t="s">
+      <c r="D44" s="12" t="s">
         <v>518</v>
       </c>
-      <c r="E44" s="11" t="s">
+      <c r="E44" s="12" t="s">
         <v>518</v>
       </c>
-      <c r="F44" s="11" t="s">
+      <c r="F44" s="12" t="s">
         <v>519</v>
       </c>
-      <c r="G44" s="11" t="s">
+      <c r="G44" s="12" t="s">
         <v>520</v>
       </c>
-      <c r="H44" s="11" t="s">
+      <c r="H44" s="12" t="s">
         <v>518</v>
       </c>
-      <c r="I44" s="11" t="s">
+      <c r="I44" s="12" t="s">
         <v>521</v>
       </c>
-      <c r="J44" s="11" t="s">
+      <c r="J44" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="K44" s="11" t="s">
+      <c r="K44" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="L44" s="11" t="s">
+      <c r="L44" s="12" t="s">
         <v>524</v>
       </c>
-      <c r="M44" s="11" t="s">
+      <c r="M44" s="12" t="s">
         <v>525</v>
       </c>
-      <c r="N44" s="11" t="s">
+      <c r="N44" s="12" t="s">
         <v>526</v>
       </c>
-      <c r="O44" s="11" t="s">
+      <c r="O44" s="12" t="s">
         <v>527</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:23">
-      <c r="B45" s="10">
+      <c r="B45" s="11">
         <v>10040</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="D45" s="11" t="s">
+      <c r="D45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="E45" s="11" t="s">
+      <c r="E45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="F45" s="11" t="s">
+      <c r="F45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="G45" s="11" t="s">
+      <c r="G45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="H45" s="11" t="s">
+      <c r="H45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="I45" s="11" t="s">
+      <c r="I45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="J45" s="11" t="s">
+      <c r="J45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="K45" s="11" t="s">
+      <c r="K45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="L45" s="11" t="s">
+      <c r="L45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="M45" s="11" t="s">
+      <c r="M45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="N45" s="11" t="s">
+      <c r="N45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="O45" s="11" t="s">
+      <c r="O45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="P45" s="16" t="s">
+      <c r="P45" s="17" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:23">
-      <c r="B46" s="10">
+      <c r="B46" s="11">
         <v>10041</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C46" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="D46" s="11" t="s">
+      <c r="D46" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E46" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="F46" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="G46" s="11" t="s">
+      <c r="G46" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="H46" s="11" t="s">
+      <c r="H46" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="I46" s="11" t="s">
+      <c r="I46" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="J46" s="11" t="s">
+      <c r="J46" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="K46" s="11" t="s">
+      <c r="K46" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="L46" s="11" t="s">
+      <c r="L46" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="M46" s="11" t="s">
+      <c r="M46" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="N46" s="11" t="s">
+      <c r="N46" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="O46" s="11" t="s">
+      <c r="O46" s="12" t="s">
         <v>529</v>
       </c>
       <c r="P46" t="s">
@@ -8899,2165 +8955,2165 @@
       </c>
     </row>
     <row r="47" customHeight="1" spans="2:23">
-      <c r="B47" s="10">
+      <c r="B47" s="11">
         <v>10042</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="12" t="s">
         <v>530</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D47" s="13" t="s">
         <v>531</v>
       </c>
-      <c r="E47" s="11" t="s">
+      <c r="E47" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="F47" s="11" t="s">
+      <c r="F47" s="12" t="s">
         <v>533</v>
       </c>
-      <c r="G47" s="11" t="s">
+      <c r="G47" s="12" t="s">
         <v>534</v>
       </c>
-      <c r="H47" s="11" t="s">
+      <c r="H47" s="12" t="s">
         <v>535</v>
       </c>
-      <c r="I47" s="11" t="s">
+      <c r="I47" s="12" t="s">
         <v>536</v>
       </c>
-      <c r="J47" s="11" t="s">
+      <c r="J47" s="12" t="s">
         <v>537</v>
       </c>
-      <c r="K47" s="11" t="s">
+      <c r="K47" s="12" t="s">
         <v>538</v>
       </c>
-      <c r="L47" s="11" t="s">
+      <c r="L47" s="12" t="s">
         <v>539</v>
       </c>
-      <c r="M47" s="11" t="s">
+      <c r="M47" s="12" t="s">
         <v>540</v>
       </c>
-      <c r="N47" s="11" t="s">
+      <c r="N47" s="12" t="s">
         <v>541</v>
       </c>
-      <c r="O47" s="11" t="s">
+      <c r="O47" s="12" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="2:23">
-      <c r="B48" s="10">
+      <c r="B48" s="11">
         <v>10043</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C48" s="12" t="s">
         <v>543</v>
       </c>
-      <c r="D48" s="12" t="s">
+      <c r="D48" s="13" t="s">
         <v>544</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E48" s="12" t="s">
         <v>545</v>
       </c>
-      <c r="F48" s="11" t="s">
+      <c r="F48" s="12" t="s">
         <v>546</v>
       </c>
-      <c r="G48" s="11" t="s">
+      <c r="G48" s="12" t="s">
         <v>547</v>
       </c>
-      <c r="H48" s="11" t="s">
+      <c r="H48" s="12" t="s">
         <v>548</v>
       </c>
-      <c r="I48" s="11" t="s">
+      <c r="I48" s="12" t="s">
         <v>549</v>
       </c>
-      <c r="J48" s="11" t="s">
+      <c r="J48" s="12" t="s">
         <v>550</v>
       </c>
-      <c r="K48" s="11" t="s">
+      <c r="K48" s="12" t="s">
         <v>551</v>
       </c>
-      <c r="L48" s="11" t="s">
+      <c r="L48" s="12" t="s">
         <v>552</v>
       </c>
-      <c r="M48" s="11" t="s">
+      <c r="M48" s="12" t="s">
         <v>553</v>
       </c>
-      <c r="N48" s="11" t="s">
+      <c r="N48" s="12" t="s">
         <v>554</v>
       </c>
-      <c r="O48" s="11" t="s">
+      <c r="O48" s="12" t="s">
         <v>555</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="2:16">
-      <c r="B49" s="10">
+      <c r="B49" s="11">
         <v>10044</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C49" s="12" t="s">
         <v>556</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="D49" s="13" t="s">
         <v>557</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="E49" s="12" t="s">
         <v>558</v>
       </c>
-      <c r="F49" s="11" t="s">
+      <c r="F49" s="12" t="s">
         <v>559</v>
       </c>
-      <c r="G49" s="11" t="s">
+      <c r="G49" s="12" t="s">
         <v>560</v>
       </c>
-      <c r="H49" s="11" t="s">
+      <c r="H49" s="12" t="s">
         <v>561</v>
       </c>
-      <c r="I49" s="11" t="s">
+      <c r="I49" s="12" t="s">
         <v>562</v>
       </c>
-      <c r="J49" s="11" t="s">
+      <c r="J49" s="12" t="s">
         <v>563</v>
       </c>
-      <c r="K49" s="11" t="s">
+      <c r="K49" s="12" t="s">
         <v>564</v>
       </c>
-      <c r="L49" s="11" t="s">
+      <c r="L49" s="12" t="s">
         <v>565</v>
       </c>
-      <c r="M49" s="11" t="s">
+      <c r="M49" s="12" t="s">
         <v>566</v>
       </c>
-      <c r="N49" s="11" t="s">
+      <c r="N49" s="12" t="s">
         <v>567</v>
       </c>
-      <c r="O49" s="11" t="s">
+      <c r="O49" s="12" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="2:16">
-      <c r="B50" s="10">
+      <c r="B50" s="11">
         <v>10045</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C50" s="12" t="s">
         <v>569</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="13" t="s">
         <v>570</v>
       </c>
-      <c r="E50" s="11" t="s">
+      <c r="E50" s="12" t="s">
         <v>571</v>
       </c>
-      <c r="F50" s="11" t="s">
+      <c r="F50" s="12" t="s">
         <v>572</v>
       </c>
-      <c r="G50" s="11" t="s">
+      <c r="G50" s="12" t="s">
         <v>573</v>
       </c>
-      <c r="H50" s="11" t="s">
+      <c r="H50" s="12" t="s">
         <v>574</v>
       </c>
-      <c r="I50" s="11" t="s">
+      <c r="I50" s="12" t="s">
         <v>575</v>
       </c>
-      <c r="J50" s="11" t="s">
+      <c r="J50" s="12" t="s">
         <v>576</v>
       </c>
-      <c r="K50" s="11" t="s">
+      <c r="K50" s="12" t="s">
         <v>577</v>
       </c>
-      <c r="L50" s="11" t="s">
+      <c r="L50" s="12" t="s">
         <v>578</v>
       </c>
-      <c r="M50" s="11" t="s">
+      <c r="M50" s="12" t="s">
         <v>579</v>
       </c>
-      <c r="N50" s="11" t="s">
+      <c r="N50" s="12" t="s">
         <v>580</v>
       </c>
-      <c r="O50" s="11" t="s">
+      <c r="O50" s="12" t="s">
         <v>581</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="2:16">
-      <c r="B51" s="10">
+      <c r="B51" s="11">
         <v>10046</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="12" t="s">
         <v>582</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="13" t="s">
         <v>583</v>
       </c>
-      <c r="E51" s="11" t="s">
+      <c r="E51" s="12" t="s">
         <v>584</v>
       </c>
-      <c r="F51" s="11" t="s">
+      <c r="F51" s="12" t="s">
         <v>585</v>
       </c>
-      <c r="G51" s="11" t="s">
+      <c r="G51" s="12" t="s">
         <v>586</v>
       </c>
-      <c r="H51" s="11" t="s">
+      <c r="H51" s="12" t="s">
         <v>587</v>
       </c>
-      <c r="I51" s="11" t="s">
+      <c r="I51" s="12" t="s">
         <v>588</v>
       </c>
-      <c r="J51" s="11" t="s">
+      <c r="J51" s="12" t="s">
         <v>589</v>
       </c>
-      <c r="K51" s="11" t="s">
+      <c r="K51" s="12" t="s">
         <v>590</v>
       </c>
-      <c r="L51" s="11" t="s">
+      <c r="L51" s="12" t="s">
         <v>591</v>
       </c>
-      <c r="M51" s="11" t="s">
+      <c r="M51" s="12" t="s">
         <v>592</v>
       </c>
-      <c r="N51" s="11" t="s">
+      <c r="N51" s="12" t="s">
         <v>593</v>
       </c>
-      <c r="O51" s="11" t="s">
+      <c r="O51" s="12" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="2:16">
-      <c r="B52" s="10">
+      <c r="B52" s="11">
         <v>10047</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="C52" s="12" t="s">
         <v>595</v>
       </c>
-      <c r="D52" s="11" t="s">
+      <c r="D52" s="12" t="s">
         <v>596</v>
       </c>
-      <c r="E52" s="11" t="s">
+      <c r="E52" s="12" t="s">
         <v>597</v>
       </c>
-      <c r="F52" s="11" t="s">
+      <c r="F52" s="12" t="s">
         <v>598</v>
       </c>
-      <c r="G52" s="11" t="s">
+      <c r="G52" s="12" t="s">
         <v>599</v>
       </c>
-      <c r="H52" s="11" t="s">
+      <c r="H52" s="12" t="s">
         <v>600</v>
       </c>
-      <c r="I52" s="11" t="s">
+      <c r="I52" s="12" t="s">
         <v>601</v>
       </c>
-      <c r="J52" s="11" t="s">
+      <c r="J52" s="12" t="s">
         <v>602</v>
       </c>
-      <c r="K52" s="11" t="s">
+      <c r="K52" s="12" t="s">
         <v>603</v>
       </c>
-      <c r="L52" s="11" t="s">
+      <c r="L52" s="12" t="s">
         <v>604</v>
       </c>
-      <c r="M52" s="11" t="s">
+      <c r="M52" s="12" t="s">
         <v>605</v>
       </c>
-      <c r="N52" s="11" t="s">
+      <c r="N52" s="12" t="s">
         <v>606</v>
       </c>
-      <c r="O52" s="11" t="s">
+      <c r="O52" s="12" t="s">
         <v>607</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="2:16">
-      <c r="B53" s="10">
+      <c r="B53" s="11">
         <v>10048</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="C53" s="12" t="s">
         <v>608</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D53" s="12" t="s">
         <v>609</v>
       </c>
-      <c r="E53" s="11" t="s">
+      <c r="E53" s="12" t="s">
         <v>610</v>
       </c>
-      <c r="F53" s="11" t="s">
+      <c r="F53" s="12" t="s">
         <v>611</v>
       </c>
-      <c r="G53" s="11" t="s">
+      <c r="G53" s="12" t="s">
         <v>612</v>
       </c>
-      <c r="H53" s="11" t="s">
+      <c r="H53" s="12" t="s">
         <v>613</v>
       </c>
-      <c r="I53" s="11" t="s">
+      <c r="I53" s="12" t="s">
         <v>614</v>
       </c>
-      <c r="J53" s="11" t="s">
+      <c r="J53" s="12" t="s">
         <v>615</v>
       </c>
-      <c r="K53" s="11" t="s">
+      <c r="K53" s="12" t="s">
         <v>616</v>
       </c>
-      <c r="L53" s="11" t="s">
+      <c r="L53" s="12" t="s">
         <v>617</v>
       </c>
-      <c r="M53" s="11" t="s">
+      <c r="M53" s="12" t="s">
         <v>618</v>
       </c>
-      <c r="N53" s="11" t="s">
+      <c r="N53" s="12" t="s">
         <v>619</v>
       </c>
-      <c r="O53" s="11" t="s">
+      <c r="O53" s="12" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="2:16">
-      <c r="B54" s="10">
+      <c r="B54" s="11">
         <v>10049</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="C54" s="12" t="s">
         <v>621</v>
       </c>
-      <c r="D54" s="11" t="s">
+      <c r="D54" s="12" t="s">
         <v>622</v>
       </c>
-      <c r="E54" s="11" t="s">
+      <c r="E54" s="12" t="s">
         <v>623</v>
       </c>
-      <c r="F54" s="11" t="s">
+      <c r="F54" s="12" t="s">
         <v>624</v>
       </c>
-      <c r="G54" s="11" t="s">
+      <c r="G54" s="12" t="s">
         <v>625</v>
       </c>
-      <c r="H54" s="11" t="s">
+      <c r="H54" s="12" t="s">
         <v>626</v>
       </c>
-      <c r="I54" s="11" t="s">
+      <c r="I54" s="12" t="s">
         <v>627</v>
       </c>
-      <c r="J54" s="11" t="s">
+      <c r="J54" s="12" t="s">
         <v>628</v>
       </c>
-      <c r="K54" s="11" t="s">
+      <c r="K54" s="12" t="s">
         <v>629</v>
       </c>
-      <c r="L54" s="11" t="s">
+      <c r="L54" s="12" t="s">
         <v>630</v>
       </c>
-      <c r="M54" s="11" t="s">
+      <c r="M54" s="12" t="s">
         <v>631</v>
       </c>
-      <c r="N54" s="11" t="s">
+      <c r="N54" s="12" t="s">
         <v>632</v>
       </c>
-      <c r="O54" s="11" t="s">
+      <c r="O54" s="12" t="s">
         <v>633</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="2:16">
-      <c r="B55" s="10">
+      <c r="B55" s="11">
         <v>10050</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C55" s="12" t="s">
         <v>634</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D55" s="12" t="s">
         <v>635</v>
       </c>
-      <c r="E55" s="11" t="s">
+      <c r="E55" s="12" t="s">
         <v>636</v>
       </c>
-      <c r="F55" s="11" t="s">
+      <c r="F55" s="12" t="s">
         <v>637</v>
       </c>
-      <c r="G55" s="11" t="s">
+      <c r="G55" s="12" t="s">
         <v>638</v>
       </c>
-      <c r="H55" s="11" t="s">
+      <c r="H55" s="12" t="s">
         <v>639</v>
       </c>
-      <c r="I55" s="11" t="s">
+      <c r="I55" s="12" t="s">
         <v>640</v>
       </c>
-      <c r="J55" s="11" t="s">
+      <c r="J55" s="12" t="s">
         <v>641</v>
       </c>
-      <c r="K55" s="11" t="s">
+      <c r="K55" s="12" t="s">
         <v>642</v>
       </c>
-      <c r="L55" s="11" t="s">
+      <c r="L55" s="12" t="s">
         <v>643</v>
       </c>
-      <c r="M55" s="11" t="s">
+      <c r="M55" s="12" t="s">
         <v>644</v>
       </c>
-      <c r="N55" s="11" t="s">
+      <c r="N55" s="12" t="s">
         <v>645</v>
       </c>
-      <c r="O55" s="11" t="s">
+      <c r="O55" s="12" t="s">
         <v>646</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" ht="19" customHeight="1" spans="2:16">
-      <c r="B56" s="10">
+      <c r="B56" s="11">
         <v>10051</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C56" s="12" t="s">
         <v>647</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D56" s="12" t="s">
         <v>648</v>
       </c>
-      <c r="E56" s="11" t="s">
+      <c r="E56" s="12" t="s">
         <v>649</v>
       </c>
-      <c r="F56" s="11" t="s">
+      <c r="F56" s="12" t="s">
         <v>650</v>
       </c>
-      <c r="G56" s="11" t="s">
+      <c r="G56" s="12" t="s">
         <v>651</v>
       </c>
-      <c r="H56" s="11" t="s">
+      <c r="H56" s="12" t="s">
         <v>652</v>
       </c>
-      <c r="I56" s="11" t="s">
+      <c r="I56" s="12" t="s">
         <v>653</v>
       </c>
-      <c r="J56" s="11" t="s">
+      <c r="J56" s="12" t="s">
         <v>654</v>
       </c>
-      <c r="K56" s="11" t="s">
+      <c r="K56" s="12" t="s">
         <v>655</v>
       </c>
-      <c r="L56" s="11" t="s">
+      <c r="L56" s="12" t="s">
         <v>656</v>
       </c>
-      <c r="M56" s="11" t="s">
+      <c r="M56" s="12" t="s">
         <v>657</v>
       </c>
-      <c r="N56" s="11" t="s">
+      <c r="N56" s="12" t="s">
         <v>658</v>
       </c>
-      <c r="O56" s="11" t="s">
+      <c r="O56" s="12" t="s">
         <v>659</v>
       </c>
       <c r="P56"/>
     </row>
     <row r="57" customHeight="1" spans="2:16">
-      <c r="B57" s="10">
+      <c r="B57" s="11">
         <v>10052</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C57" s="12" t="s">
         <v>660</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="D57" s="13" t="s">
         <v>661</v>
       </c>
-      <c r="E57" s="11" t="s">
+      <c r="E57" s="12" t="s">
         <v>662</v>
       </c>
-      <c r="F57" s="11" t="s">
+      <c r="F57" s="12" t="s">
         <v>663</v>
       </c>
-      <c r="G57" s="11" t="s">
+      <c r="G57" s="12" t="s">
         <v>664</v>
       </c>
-      <c r="H57" s="11" t="s">
+      <c r="H57" s="12" t="s">
         <v>665</v>
       </c>
-      <c r="I57" s="11" t="s">
+      <c r="I57" s="12" t="s">
         <v>666</v>
       </c>
-      <c r="J57" s="11" t="s">
+      <c r="J57" s="12" t="s">
         <v>667</v>
       </c>
-      <c r="K57" s="11" t="s">
+      <c r="K57" s="12" t="s">
         <v>668</v>
       </c>
-      <c r="L57" s="11" t="s">
+      <c r="L57" s="12" t="s">
         <v>669</v>
       </c>
-      <c r="M57" s="11" t="s">
+      <c r="M57" s="12" t="s">
         <v>670</v>
       </c>
-      <c r="N57" s="11" t="s">
+      <c r="N57" s="12" t="s">
         <v>671</v>
       </c>
-      <c r="O57" s="11" t="s">
+      <c r="O57" s="12" t="s">
         <v>672</v>
       </c>
       <c r="P57" s="1"/>
     </row>
     <row r="58" customHeight="1" spans="2:16">
-      <c r="B58" s="10">
+      <c r="B58" s="11">
         <v>10053</v>
       </c>
-      <c r="C58" s="11" t="s">
+      <c r="C58" s="12" t="s">
         <v>673</v>
       </c>
-      <c r="D58" s="12" t="s">
+      <c r="D58" s="13" t="s">
         <v>674</v>
       </c>
-      <c r="E58" s="11" t="s">
+      <c r="E58" s="12" t="s">
         <v>675</v>
       </c>
-      <c r="F58" s="11" t="s">
+      <c r="F58" s="12" t="s">
         <v>676</v>
       </c>
-      <c r="G58" s="11" t="s">
+      <c r="G58" s="12" t="s">
         <v>677</v>
       </c>
-      <c r="H58" s="11" t="s">
+      <c r="H58" s="12" t="s">
         <v>678</v>
       </c>
-      <c r="I58" s="11" t="s">
+      <c r="I58" s="12" t="s">
         <v>679</v>
       </c>
-      <c r="J58" s="11" t="s">
+      <c r="J58" s="12" t="s">
         <v>680</v>
       </c>
-      <c r="K58" s="11" t="s">
+      <c r="K58" s="12" t="s">
         <v>681</v>
       </c>
-      <c r="L58" s="11" t="s">
+      <c r="L58" s="12" t="s">
         <v>682</v>
       </c>
-      <c r="M58" s="11" t="s">
+      <c r="M58" s="12" t="s">
         <v>683</v>
       </c>
-      <c r="N58" s="11" t="s">
+      <c r="N58" s="12" t="s">
         <v>684</v>
       </c>
-      <c r="O58" s="11" t="s">
+      <c r="O58" s="12" t="s">
         <v>685</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:16">
-      <c r="B59" s="10">
+      <c r="B59" s="11">
         <v>10054</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C59" s="12" t="s">
         <v>686</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="D59" s="13" t="s">
         <v>687</v>
       </c>
-      <c r="E59" s="11" t="s">
+      <c r="E59" s="12" t="s">
         <v>688</v>
       </c>
-      <c r="F59" s="11" t="s">
+      <c r="F59" s="12" t="s">
         <v>689</v>
       </c>
-      <c r="G59" s="11" t="s">
+      <c r="G59" s="12" t="s">
         <v>690</v>
       </c>
-      <c r="H59" s="11" t="s">
+      <c r="H59" s="12" t="s">
         <v>691</v>
       </c>
-      <c r="I59" s="11" t="s">
+      <c r="I59" s="12" t="s">
         <v>692</v>
       </c>
-      <c r="J59" s="11" t="s">
+      <c r="J59" s="12" t="s">
         <v>693</v>
       </c>
-      <c r="K59" s="11" t="s">
+      <c r="K59" s="12" t="s">
         <v>694</v>
       </c>
-      <c r="L59" s="11" t="s">
+      <c r="L59" s="12" t="s">
         <v>695</v>
       </c>
-      <c r="M59" s="11" t="s">
+      <c r="M59" s="12" t="s">
         <v>696</v>
       </c>
-      <c r="N59" s="11" t="s">
+      <c r="N59" s="12" t="s">
         <v>697</v>
       </c>
-      <c r="O59" s="11" t="s">
+      <c r="O59" s="12" t="s">
         <v>698</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:16">
-      <c r="B60" s="10">
+      <c r="B60" s="11">
         <v>10055</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="C60" s="13" t="s">
         <v>699</v>
       </c>
-      <c r="D60" s="11" t="s">
+      <c r="D60" s="12" t="s">
         <v>700</v>
       </c>
-      <c r="E60" s="11" t="s">
+      <c r="E60" s="12" t="s">
         <v>701</v>
       </c>
-      <c r="F60" s="11" t="s">
+      <c r="F60" s="12" t="s">
         <v>702</v>
       </c>
-      <c r="G60" s="11" t="s">
+      <c r="G60" s="12" t="s">
         <v>703</v>
       </c>
-      <c r="H60" s="11" t="s">
+      <c r="H60" s="12" t="s">
         <v>704</v>
       </c>
-      <c r="I60" s="11" t="s">
+      <c r="I60" s="12" t="s">
         <v>705</v>
       </c>
-      <c r="J60" s="11" t="s">
+      <c r="J60" s="12" t="s">
         <v>706</v>
       </c>
-      <c r="K60" s="11" t="s">
+      <c r="K60" s="12" t="s">
         <v>707</v>
       </c>
-      <c r="L60" s="11" t="s">
+      <c r="L60" s="12" t="s">
         <v>708</v>
       </c>
-      <c r="M60" s="11" t="s">
+      <c r="M60" s="12" t="s">
         <v>709</v>
       </c>
-      <c r="N60" s="11" t="s">
+      <c r="N60" s="12" t="s">
         <v>710</v>
       </c>
-      <c r="O60" s="11" t="s">
+      <c r="O60" s="12" t="s">
         <v>711</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:16">
-      <c r="B61" s="10">
+      <c r="B61" s="11">
         <v>10056</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C61" s="12" t="s">
         <v>712</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="D61" s="13" t="s">
         <v>713</v>
       </c>
-      <c r="E61" s="11" t="s">
+      <c r="E61" s="12" t="s">
         <v>714</v>
       </c>
-      <c r="F61" s="11" t="s">
+      <c r="F61" s="12" t="s">
         <v>715</v>
       </c>
-      <c r="G61" s="11" t="s">
+      <c r="G61" s="12" t="s">
         <v>716</v>
       </c>
-      <c r="H61" s="11" t="s">
+      <c r="H61" s="12" t="s">
         <v>717</v>
       </c>
-      <c r="I61" s="11" t="s">
+      <c r="I61" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="J61" s="11" t="s">
+      <c r="J61" s="12" t="s">
         <v>719</v>
       </c>
-      <c r="K61" s="11" t="s">
+      <c r="K61" s="12" t="s">
         <v>720</v>
       </c>
-      <c r="L61" s="11" t="s">
+      <c r="L61" s="12" t="s">
         <v>721</v>
       </c>
-      <c r="M61" s="11" t="s">
+      <c r="M61" s="12" t="s">
         <v>722</v>
       </c>
-      <c r="N61" s="11" t="s">
+      <c r="N61" s="12" t="s">
         <v>723</v>
       </c>
-      <c r="O61" s="11" t="s">
+      <c r="O61" s="12" t="s">
         <v>724</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:16">
-      <c r="B62" s="10">
+      <c r="B62" s="11">
         <v>10057</v>
       </c>
-      <c r="C62" s="11" t="s">
+      <c r="C62" s="12" t="s">
         <v>725</v>
       </c>
-      <c r="D62" s="11" t="s">
+      <c r="D62" s="12" t="s">
         <v>726</v>
       </c>
-      <c r="E62" s="11" t="s">
+      <c r="E62" s="12" t="s">
         <v>727</v>
       </c>
-      <c r="F62" s="11" t="s">
+      <c r="F62" s="12" t="s">
         <v>728</v>
       </c>
-      <c r="G62" s="11" t="s">
+      <c r="G62" s="12" t="s">
         <v>729</v>
       </c>
-      <c r="H62" s="11" t="s">
+      <c r="H62" s="12" t="s">
         <v>730</v>
       </c>
-      <c r="I62" s="11" t="s">
+      <c r="I62" s="12" t="s">
         <v>731</v>
       </c>
-      <c r="J62" s="11" t="s">
+      <c r="J62" s="12" t="s">
         <v>732</v>
       </c>
-      <c r="K62" s="11" t="s">
+      <c r="K62" s="12" t="s">
         <v>733</v>
       </c>
-      <c r="L62" s="11" t="s">
+      <c r="L62" s="12" t="s">
         <v>734</v>
       </c>
-      <c r="M62" s="11" t="s">
+      <c r="M62" s="12" t="s">
         <v>735</v>
       </c>
-      <c r="N62" s="11" t="s">
+      <c r="N62" s="12" t="s">
         <v>736</v>
       </c>
-      <c r="O62" s="11" t="s">
+      <c r="O62" s="12" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:16">
-      <c r="B63" s="10">
+      <c r="B63" s="11">
         <v>10058</v>
       </c>
-      <c r="C63" s="11" t="s">
+      <c r="C63" s="12" t="s">
         <v>738</v>
       </c>
-      <c r="D63" s="11" t="s">
+      <c r="D63" s="12" t="s">
         <v>739</v>
       </c>
-      <c r="E63" s="11" t="s">
+      <c r="E63" s="12" t="s">
         <v>740</v>
       </c>
-      <c r="F63" s="11" t="s">
+      <c r="F63" s="12" t="s">
         <v>741</v>
       </c>
-      <c r="G63" s="11" t="s">
+      <c r="G63" s="12" t="s">
         <v>742</v>
       </c>
-      <c r="H63" s="11" t="s">
+      <c r="H63" s="12" t="s">
         <v>743</v>
       </c>
-      <c r="I63" s="11" t="s">
+      <c r="I63" s="12" t="s">
         <v>744</v>
       </c>
-      <c r="J63" s="11" t="s">
+      <c r="J63" s="12" t="s">
         <v>745</v>
       </c>
-      <c r="K63" s="11" t="s">
+      <c r="K63" s="12" t="s">
         <v>746</v>
       </c>
-      <c r="L63" s="11" t="s">
+      <c r="L63" s="12" t="s">
         <v>747</v>
       </c>
-      <c r="M63" s="11" t="s">
+      <c r="M63" s="12" t="s">
         <v>748</v>
       </c>
-      <c r="N63" s="11" t="s">
+      <c r="N63" s="12" t="s">
         <v>749</v>
       </c>
-      <c r="O63" s="11" t="s">
+      <c r="O63" s="12" t="s">
         <v>750</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:16">
-      <c r="B64" s="10">
+      <c r="B64" s="11">
         <v>10059</v>
       </c>
-      <c r="C64" s="11" t="s">
+      <c r="C64" s="12" t="s">
         <v>751</v>
       </c>
-      <c r="D64" s="11" t="s">
+      <c r="D64" s="12" t="s">
         <v>752</v>
       </c>
-      <c r="E64" s="11" t="s">
+      <c r="E64" s="12" t="s">
         <v>753</v>
       </c>
-      <c r="F64" s="11" t="s">
+      <c r="F64" s="12" t="s">
         <v>754</v>
       </c>
-      <c r="G64" s="11" t="s">
+      <c r="G64" s="12" t="s">
         <v>755</v>
       </c>
-      <c r="H64" s="11" t="s">
+      <c r="H64" s="12" t="s">
         <v>756</v>
       </c>
-      <c r="I64" s="11" t="s">
+      <c r="I64" s="12" t="s">
         <v>757</v>
       </c>
-      <c r="J64" s="11" t="s">
+      <c r="J64" s="12" t="s">
         <v>758</v>
       </c>
-      <c r="K64" s="11" t="s">
+      <c r="K64" s="12" t="s">
         <v>759</v>
       </c>
-      <c r="L64" s="11" t="s">
+      <c r="L64" s="12" t="s">
         <v>760</v>
       </c>
-      <c r="M64" s="11" t="s">
+      <c r="M64" s="12" t="s">
         <v>761</v>
       </c>
-      <c r="N64" s="11" t="s">
+      <c r="N64" s="12" t="s">
         <v>762</v>
       </c>
-      <c r="O64" s="11" t="s">
+      <c r="O64" s="12" t="s">
         <v>763</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="2:15">
-      <c r="B65" s="10">
+      <c r="B65" s="11">
         <v>10060</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="C65" s="12" t="s">
         <v>764</v>
       </c>
-      <c r="D65" s="11" t="s">
+      <c r="D65" s="12" t="s">
         <v>765</v>
       </c>
-      <c r="E65" s="11" t="s">
+      <c r="E65" s="12" t="s">
         <v>766</v>
       </c>
-      <c r="F65" s="11" t="s">
+      <c r="F65" s="12" t="s">
         <v>767</v>
       </c>
-      <c r="G65" s="11" t="s">
+      <c r="G65" s="12" t="s">
         <v>768</v>
       </c>
-      <c r="H65" s="11" t="s">
+      <c r="H65" s="12" t="s">
         <v>769</v>
       </c>
-      <c r="I65" s="11" t="s">
+      <c r="I65" s="12" t="s">
         <v>770</v>
       </c>
-      <c r="J65" s="11" t="s">
+      <c r="J65" s="12" t="s">
         <v>771</v>
       </c>
-      <c r="K65" s="11" t="s">
+      <c r="K65" s="12" t="s">
         <v>772</v>
       </c>
-      <c r="L65" s="11" t="s">
+      <c r="L65" s="12" t="s">
         <v>773</v>
       </c>
-      <c r="M65" s="11" t="s">
+      <c r="M65" s="12" t="s">
         <v>774</v>
       </c>
-      <c r="N65" s="11" t="s">
+      <c r="N65" s="12" t="s">
         <v>775</v>
       </c>
-      <c r="O65" s="11" t="s">
+      <c r="O65" s="12" t="s">
         <v>776</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="2:15">
-      <c r="B66" s="10">
+      <c r="B66" s="11">
         <v>10061</v>
       </c>
-      <c r="C66" s="11" t="s">
+      <c r="C66" s="12" t="s">
         <v>777</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="D66" s="12" t="s">
         <v>778</v>
       </c>
-      <c r="E66" s="11" t="s">
+      <c r="E66" s="12" t="s">
         <v>779</v>
       </c>
-      <c r="F66" s="11" t="s">
+      <c r="F66" s="12" t="s">
         <v>780</v>
       </c>
-      <c r="G66" s="11" t="s">
+      <c r="G66" s="12" t="s">
         <v>781</v>
       </c>
-      <c r="H66" s="11" t="s">
+      <c r="H66" s="12" t="s">
         <v>782</v>
       </c>
-      <c r="I66" s="11" t="s">
+      <c r="I66" s="12" t="s">
         <v>783</v>
       </c>
-      <c r="J66" s="11" t="s">
+      <c r="J66" s="12" t="s">
         <v>784</v>
       </c>
-      <c r="K66" s="11" t="s">
+      <c r="K66" s="12" t="s">
         <v>785</v>
       </c>
-      <c r="L66" s="11" t="s">
+      <c r="L66" s="12" t="s">
         <v>786</v>
       </c>
-      <c r="M66" s="11" t="s">
+      <c r="M66" s="12" t="s">
         <v>787</v>
       </c>
-      <c r="N66" s="11" t="s">
+      <c r="N66" s="12" t="s">
         <v>788</v>
       </c>
-      <c r="O66" s="11" t="s">
+      <c r="O66" s="12" t="s">
         <v>789</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="2:15">
-      <c r="B67" s="10">
+      <c r="B67" s="11">
         <v>10062</v>
       </c>
-      <c r="C67" s="11" t="s">
+      <c r="C67" s="12" t="s">
         <v>790</v>
       </c>
-      <c r="D67" s="11" t="s">
+      <c r="D67" s="12" t="s">
         <v>791</v>
       </c>
-      <c r="E67" s="11" t="s">
+      <c r="E67" s="12" t="s">
         <v>792</v>
       </c>
-      <c r="F67" s="11" t="s">
+      <c r="F67" s="12" t="s">
         <v>793</v>
       </c>
-      <c r="G67" s="11" t="s">
+      <c r="G67" s="12" t="s">
         <v>794</v>
       </c>
-      <c r="H67" s="11" t="s">
+      <c r="H67" s="12" t="s">
         <v>795</v>
       </c>
-      <c r="I67" s="11" t="s">
+      <c r="I67" s="12" t="s">
         <v>796</v>
       </c>
-      <c r="J67" s="11" t="s">
+      <c r="J67" s="12" t="s">
         <v>797</v>
       </c>
-      <c r="K67" s="11" t="s">
+      <c r="K67" s="12" t="s">
         <v>798</v>
       </c>
-      <c r="L67" s="11" t="s">
+      <c r="L67" s="12" t="s">
         <v>799</v>
       </c>
-      <c r="M67" s="11" t="s">
+      <c r="M67" s="12" t="s">
         <v>800</v>
       </c>
-      <c r="N67" s="11" t="s">
+      <c r="N67" s="12" t="s">
         <v>801</v>
       </c>
-      <c r="O67" s="11" t="s">
+      <c r="O67" s="12" t="s">
         <v>802</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="2:15">
-      <c r="B68" s="10">
+      <c r="B68" s="11">
         <v>10063</v>
       </c>
-      <c r="C68" s="11" t="s">
+      <c r="C68" s="12" t="s">
         <v>803</v>
       </c>
-      <c r="D68" s="12" t="s">
+      <c r="D68" s="13" t="s">
         <v>804</v>
       </c>
-      <c r="E68" s="11" t="s">
+      <c r="E68" s="12" t="s">
         <v>804</v>
       </c>
-      <c r="F68" s="11" t="s">
+      <c r="F68" s="12" t="s">
         <v>805</v>
       </c>
-      <c r="G68" s="11" t="s">
+      <c r="G68" s="12" t="s">
         <v>804</v>
       </c>
-      <c r="H68" s="11" t="s">
+      <c r="H68" s="12" t="s">
         <v>806</v>
       </c>
-      <c r="I68" s="11" t="s">
+      <c r="I68" s="12" t="s">
         <v>807</v>
       </c>
-      <c r="J68" s="11" t="s">
+      <c r="J68" s="12" t="s">
         <v>808</v>
       </c>
-      <c r="K68" s="11" t="s">
+      <c r="K68" s="12" t="s">
         <v>809</v>
       </c>
-      <c r="L68" s="11" t="s">
+      <c r="L68" s="12" t="s">
         <v>810</v>
       </c>
-      <c r="M68" s="11" t="s">
+      <c r="M68" s="12" t="s">
         <v>811</v>
       </c>
-      <c r="N68" s="11" t="s">
+      <c r="N68" s="12" t="s">
         <v>812</v>
       </c>
-      <c r="O68" s="11" t="s">
+      <c r="O68" s="12" t="s">
         <v>813</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="2:15">
-      <c r="B69" s="10">
+      <c r="B69" s="11">
         <v>10064</v>
       </c>
-      <c r="C69" s="11" t="s">
+      <c r="C69" s="12" t="s">
         <v>814</v>
       </c>
-      <c r="D69" s="11" t="s">
+      <c r="D69" s="12" t="s">
         <v>815</v>
       </c>
-      <c r="E69" s="11" t="s">
+      <c r="E69" s="12" t="s">
         <v>816</v>
       </c>
-      <c r="F69" s="11" t="s">
+      <c r="F69" s="12" t="s">
         <v>817</v>
       </c>
-      <c r="G69" s="11" t="s">
+      <c r="G69" s="12" t="s">
         <v>818</v>
       </c>
-      <c r="H69" s="11" t="s">
+      <c r="H69" s="12" t="s">
         <v>819</v>
       </c>
-      <c r="I69" s="11" t="s">
+      <c r="I69" s="12" t="s">
         <v>820</v>
       </c>
-      <c r="J69" s="11" t="s">
+      <c r="J69" s="12" t="s">
         <v>821</v>
       </c>
-      <c r="K69" s="11" t="s">
+      <c r="K69" s="12" t="s">
         <v>822</v>
       </c>
-      <c r="L69" s="11" t="s">
+      <c r="L69" s="12" t="s">
         <v>823</v>
       </c>
-      <c r="M69" s="11" t="s">
+      <c r="M69" s="12" t="s">
         <v>824</v>
       </c>
-      <c r="N69" s="11" t="s">
+      <c r="N69" s="12" t="s">
         <v>825</v>
       </c>
-      <c r="O69" s="11" t="s">
+      <c r="O69" s="12" t="s">
         <v>826</v>
       </c>
     </row>
     <row r="70" ht="19" customHeight="1" spans="2:15">
-      <c r="B70" s="10">
+      <c r="B70" s="11">
         <v>10065</v>
       </c>
-      <c r="C70" s="11" t="s">
+      <c r="C70" s="12" t="s">
         <v>827</v>
       </c>
-      <c r="D70" s="11" t="s">
+      <c r="D70" s="12" t="s">
         <v>828</v>
       </c>
-      <c r="E70" s="11" t="s">
+      <c r="E70" s="12" t="s">
         <v>829</v>
       </c>
-      <c r="F70" s="11" t="s">
+      <c r="F70" s="12" t="s">
         <v>830</v>
       </c>
-      <c r="G70" s="11" t="s">
+      <c r="G70" s="12" t="s">
         <v>831</v>
       </c>
-      <c r="H70" s="11" t="s">
+      <c r="H70" s="12" t="s">
         <v>832</v>
       </c>
-      <c r="I70" s="11" t="s">
+      <c r="I70" s="12" t="s">
         <v>831</v>
       </c>
-      <c r="J70" s="11" t="s">
+      <c r="J70" s="12" t="s">
         <v>833</v>
       </c>
-      <c r="K70" s="11" t="s">
+      <c r="K70" s="12" t="s">
         <v>834</v>
       </c>
-      <c r="L70" s="11" t="s">
+      <c r="L70" s="12" t="s">
         <v>835</v>
       </c>
-      <c r="M70" s="11" t="s">
+      <c r="M70" s="12" t="s">
         <v>836</v>
       </c>
-      <c r="N70" s="11" t="s">
+      <c r="N70" s="12" t="s">
         <v>837</v>
       </c>
-      <c r="O70" s="11" t="s">
+      <c r="O70" s="12" t="s">
         <v>838</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="2:15">
-      <c r="B71" s="10">
+      <c r="B71" s="11">
         <v>10066</v>
       </c>
-      <c r="C71" s="11" t="s">
+      <c r="C71" s="12" t="s">
         <v>839</v>
       </c>
-      <c r="D71" s="12" t="s">
+      <c r="D71" s="13" t="s">
         <v>840</v>
       </c>
-      <c r="E71" s="11" t="s">
+      <c r="E71" s="12" t="s">
         <v>841</v>
       </c>
-      <c r="F71" s="11" t="s">
+      <c r="F71" s="12" t="s">
         <v>842</v>
       </c>
-      <c r="G71" s="11" t="s">
+      <c r="G71" s="12" t="s">
         <v>843</v>
       </c>
-      <c r="H71" s="11" t="s">
+      <c r="H71" s="12" t="s">
         <v>844</v>
       </c>
-      <c r="I71" s="11" t="s">
+      <c r="I71" s="12" t="s">
         <v>843</v>
       </c>
-      <c r="J71" s="11" t="s">
+      <c r="J71" s="12" t="s">
         <v>845</v>
       </c>
-      <c r="K71" s="11" t="s">
+      <c r="K71" s="12" t="s">
         <v>846</v>
       </c>
-      <c r="L71" s="11" t="s">
+      <c r="L71" s="12" t="s">
         <v>847</v>
       </c>
-      <c r="M71" s="11" t="s">
+      <c r="M71" s="12" t="s">
         <v>848</v>
       </c>
-      <c r="N71" s="11" t="s">
+      <c r="N71" s="12" t="s">
         <v>849</v>
       </c>
-      <c r="O71" s="11" t="s">
+      <c r="O71" s="12" t="s">
         <v>850</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="2:15">
-      <c r="B72" s="10">
+      <c r="B72" s="11">
         <v>10067</v>
       </c>
-      <c r="C72" s="11" t="s">
+      <c r="C72" s="12" t="s">
         <v>851</v>
       </c>
-      <c r="D72" s="12" t="s">
+      <c r="D72" s="13" t="s">
         <v>852</v>
       </c>
-      <c r="E72" s="11" t="s">
+      <c r="E72" s="12" t="s">
         <v>853</v>
       </c>
-      <c r="F72" s="11" t="s">
+      <c r="F72" s="12" t="s">
         <v>854</v>
       </c>
-      <c r="G72" s="11" t="s">
+      <c r="G72" s="12" t="s">
         <v>855</v>
       </c>
-      <c r="H72" s="11" t="s">
+      <c r="H72" s="12" t="s">
         <v>856</v>
       </c>
-      <c r="I72" s="11" t="s">
+      <c r="I72" s="12" t="s">
         <v>855</v>
       </c>
-      <c r="J72" s="11" t="s">
+      <c r="J72" s="12" t="s">
         <v>857</v>
       </c>
-      <c r="K72" s="11" t="s">
+      <c r="K72" s="12" t="s">
         <v>855</v>
       </c>
-      <c r="L72" s="11" t="s">
+      <c r="L72" s="12" t="s">
         <v>858</v>
       </c>
-      <c r="M72" s="11" t="s">
+      <c r="M72" s="12" t="s">
         <v>859</v>
       </c>
-      <c r="N72" s="11" t="s">
+      <c r="N72" s="12" t="s">
         <v>860</v>
       </c>
-      <c r="O72" s="11" t="s">
+      <c r="O72" s="12" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="2:15">
-      <c r="B73" s="10">
+      <c r="B73" s="11">
         <v>10068</v>
       </c>
-      <c r="C73" s="11" t="s">
+      <c r="C73" s="12" t="s">
         <v>862</v>
       </c>
-      <c r="D73" s="12" t="s">
+      <c r="D73" s="13" t="s">
         <v>863</v>
       </c>
-      <c r="E73" s="11" t="s">
+      <c r="E73" s="12" t="s">
         <v>864</v>
       </c>
-      <c r="F73" s="11" t="s">
+      <c r="F73" s="12" t="s">
         <v>865</v>
       </c>
-      <c r="G73" s="11" t="s">
+      <c r="G73" s="12" t="s">
         <v>866</v>
       </c>
-      <c r="H73" s="11" t="s">
+      <c r="H73" s="12" t="s">
         <v>867</v>
       </c>
-      <c r="I73" s="11" t="s">
+      <c r="I73" s="12" t="s">
         <v>868</v>
       </c>
-      <c r="J73" s="11" t="s">
+      <c r="J73" s="12" t="s">
         <v>869</v>
       </c>
-      <c r="K73" s="11" t="s">
+      <c r="K73" s="12" t="s">
         <v>870</v>
       </c>
-      <c r="L73" s="11" t="s">
+      <c r="L73" s="12" t="s">
         <v>871</v>
       </c>
-      <c r="M73" s="11" t="s">
+      <c r="M73" s="12" t="s">
         <v>872</v>
       </c>
-      <c r="N73" s="11" t="s">
+      <c r="N73" s="12" t="s">
         <v>873</v>
       </c>
-      <c r="O73" s="11" t="s">
+      <c r="O73" s="12" t="s">
         <v>874</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="2:15">
-      <c r="B74" s="10">
+      <c r="B74" s="11">
         <v>10069</v>
       </c>
-      <c r="C74" s="11" t="s">
+      <c r="C74" s="12" t="s">
         <v>875</v>
       </c>
-      <c r="D74" s="12" t="s">
+      <c r="D74" s="13" t="s">
         <v>876</v>
       </c>
-      <c r="E74" s="11" t="s">
+      <c r="E74" s="12" t="s">
         <v>877</v>
       </c>
-      <c r="F74" s="11" t="s">
+      <c r="F74" s="12" t="s">
         <v>878</v>
       </c>
-      <c r="G74" s="11" t="s">
+      <c r="G74" s="12" t="s">
         <v>879</v>
       </c>
-      <c r="H74" s="11" t="s">
+      <c r="H74" s="12" t="s">
         <v>880</v>
       </c>
-      <c r="I74" s="11" t="s">
+      <c r="I74" s="12" t="s">
         <v>881</v>
       </c>
-      <c r="J74" s="11" t="s">
+      <c r="J74" s="12" t="s">
         <v>882</v>
       </c>
-      <c r="K74" s="11" t="s">
+      <c r="K74" s="12" t="s">
         <v>883</v>
       </c>
-      <c r="L74" s="11" t="s">
+      <c r="L74" s="12" t="s">
         <v>884</v>
       </c>
-      <c r="M74" s="11" t="s">
+      <c r="M74" s="12" t="s">
         <v>885</v>
       </c>
-      <c r="N74" s="11" t="s">
+      <c r="N74" s="12" t="s">
         <v>886</v>
       </c>
-      <c r="O74" s="11" t="s">
+      <c r="O74" s="12" t="s">
         <v>887</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="2:15">
-      <c r="B75" s="10">
+      <c r="B75" s="11">
         <v>10070</v>
       </c>
-      <c r="C75" s="11" t="s">
+      <c r="C75" s="12" t="s">
         <v>888</v>
       </c>
-      <c r="D75" s="11" t="s">
+      <c r="D75" s="12" t="s">
         <v>889</v>
       </c>
-      <c r="E75" s="11" t="s">
+      <c r="E75" s="12" t="s">
         <v>890</v>
       </c>
-      <c r="F75" s="11" t="s">
+      <c r="F75" s="12" t="s">
         <v>891</v>
       </c>
-      <c r="G75" s="11" t="s">
+      <c r="G75" s="12" t="s">
         <v>892</v>
       </c>
-      <c r="H75" s="11" t="s">
+      <c r="H75" s="12" t="s">
         <v>893</v>
       </c>
-      <c r="I75" s="11" t="s">
+      <c r="I75" s="12" t="s">
         <v>894</v>
       </c>
-      <c r="J75" s="11" t="s">
+      <c r="J75" s="12" t="s">
         <v>895</v>
       </c>
-      <c r="K75" s="11" t="s">
+      <c r="K75" s="12" t="s">
         <v>896</v>
       </c>
-      <c r="L75" s="11" t="s">
+      <c r="L75" s="12" t="s">
         <v>897</v>
       </c>
-      <c r="M75" s="11" t="s">
+      <c r="M75" s="12" t="s">
         <v>898</v>
       </c>
-      <c r="N75" s="11" t="s">
+      <c r="N75" s="12" t="s">
         <v>899</v>
       </c>
-      <c r="O75" s="11" t="s">
+      <c r="O75" s="12" t="s">
         <v>900</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="2:15">
-      <c r="B76" s="10">
+      <c r="B76" s="11">
         <v>10071</v>
       </c>
-      <c r="C76" s="11" t="s">
+      <c r="C76" s="12" t="s">
         <v>901</v>
       </c>
-      <c r="D76" s="11" t="s">
+      <c r="D76" s="12" t="s">
         <v>902</v>
       </c>
-      <c r="E76" s="11" t="s">
+      <c r="E76" s="12" t="s">
         <v>903</v>
       </c>
-      <c r="F76" s="11" t="s">
+      <c r="F76" s="12" t="s">
         <v>904</v>
       </c>
-      <c r="G76" s="11" t="s">
+      <c r="G76" s="12" t="s">
         <v>905</v>
       </c>
-      <c r="H76" s="11" t="s">
+      <c r="H76" s="12" t="s">
         <v>906</v>
       </c>
-      <c r="I76" s="11" t="s">
+      <c r="I76" s="12" t="s">
         <v>907</v>
       </c>
-      <c r="J76" s="11" t="s">
+      <c r="J76" s="12" t="s">
         <v>908</v>
       </c>
-      <c r="K76" s="11" t="s">
+      <c r="K76" s="12" t="s">
         <v>909</v>
       </c>
-      <c r="L76" s="11" t="s">
+      <c r="L76" s="12" t="s">
         <v>910</v>
       </c>
-      <c r="M76" s="11" t="s">
+      <c r="M76" s="12" t="s">
         <v>911</v>
       </c>
-      <c r="N76" s="11" t="s">
+      <c r="N76" s="12" t="s">
         <v>912</v>
       </c>
-      <c r="O76" s="11" t="s">
+      <c r="O76" s="12" t="s">
         <v>913</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="2:15">
-      <c r="B77" s="10">
+      <c r="B77" s="11">
         <v>10072</v>
       </c>
-      <c r="C77" s="11" t="s">
+      <c r="C77" s="12" t="s">
         <v>914</v>
       </c>
-      <c r="D77" s="11" t="s">
+      <c r="D77" s="12" t="s">
         <v>915</v>
       </c>
-      <c r="E77" s="11" t="s">
+      <c r="E77" s="12" t="s">
         <v>916</v>
       </c>
-      <c r="F77" s="11" t="s">
+      <c r="F77" s="12" t="s">
         <v>917</v>
       </c>
-      <c r="G77" s="11" t="s">
+      <c r="G77" s="12" t="s">
         <v>918</v>
       </c>
-      <c r="H77" s="11" t="s">
+      <c r="H77" s="12" t="s">
         <v>919</v>
       </c>
-      <c r="I77" s="11" t="s">
+      <c r="I77" s="12" t="s">
         <v>920</v>
       </c>
-      <c r="J77" s="11" t="s">
+      <c r="J77" s="12" t="s">
         <v>921</v>
       </c>
-      <c r="K77" s="11" t="s">
+      <c r="K77" s="12" t="s">
         <v>922</v>
       </c>
-      <c r="L77" s="11" t="s">
+      <c r="L77" s="12" t="s">
         <v>923</v>
       </c>
-      <c r="M77" s="11" t="s">
+      <c r="M77" s="12" t="s">
         <v>924</v>
       </c>
-      <c r="N77" s="11" t="s">
+      <c r="N77" s="12" t="s">
         <v>925</v>
       </c>
-      <c r="O77" s="11" t="s">
+      <c r="O77" s="12" t="s">
         <v>926</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="2:15">
-      <c r="B78" s="10">
+      <c r="B78" s="11">
         <v>10073</v>
       </c>
-      <c r="C78" s="11" t="s">
+      <c r="C78" s="12" t="s">
         <v>927</v>
       </c>
-      <c r="D78" s="12" t="s">
+      <c r="D78" s="13" t="s">
         <v>928</v>
       </c>
-      <c r="E78" s="11" t="s">
+      <c r="E78" s="12" t="s">
         <v>929</v>
       </c>
-      <c r="F78" s="11" t="s">
+      <c r="F78" s="12" t="s">
         <v>930</v>
       </c>
-      <c r="G78" s="11" t="s">
+      <c r="G78" s="12" t="s">
         <v>931</v>
       </c>
-      <c r="H78" s="11" t="s">
+      <c r="H78" s="12" t="s">
         <v>932</v>
       </c>
-      <c r="I78" s="11" t="s">
+      <c r="I78" s="12" t="s">
         <v>933</v>
       </c>
-      <c r="J78" s="11" t="s">
+      <c r="J78" s="12" t="s">
         <v>934</v>
       </c>
-      <c r="K78" s="11" t="s">
+      <c r="K78" s="12" t="s">
         <v>935</v>
       </c>
-      <c r="L78" s="11" t="s">
+      <c r="L78" s="12" t="s">
         <v>936</v>
       </c>
-      <c r="M78" s="11" t="s">
+      <c r="M78" s="12" t="s">
         <v>937</v>
       </c>
-      <c r="N78" s="11" t="s">
+      <c r="N78" s="12" t="s">
         <v>938</v>
       </c>
-      <c r="O78" s="11" t="s">
+      <c r="O78" s="12" t="s">
         <v>939</v>
       </c>
     </row>
     <row r="79" ht="19" customHeight="1" spans="2:15">
-      <c r="B79" s="10">
+      <c r="B79" s="11">
         <v>10074</v>
       </c>
-      <c r="C79" s="12" t="s">
+      <c r="C79" s="13" t="s">
         <v>940</v>
       </c>
-      <c r="D79" s="12" t="s">
+      <c r="D79" s="13" t="s">
         <v>941</v>
       </c>
-      <c r="E79" s="11" t="s">
+      <c r="E79" s="12" t="s">
         <v>942</v>
       </c>
-      <c r="F79" s="11" t="s">
+      <c r="F79" s="12" t="s">
         <v>943</v>
       </c>
-      <c r="G79" s="11" t="s">
+      <c r="G79" s="12" t="s">
         <v>944</v>
       </c>
-      <c r="H79" s="11" t="s">
+      <c r="H79" s="12" t="s">
         <v>945</v>
       </c>
-      <c r="I79" s="11" t="s">
+      <c r="I79" s="12" t="s">
         <v>946</v>
       </c>
-      <c r="J79" s="11" t="s">
+      <c r="J79" s="12" t="s">
         <v>947</v>
       </c>
-      <c r="K79" s="11" t="s">
+      <c r="K79" s="12" t="s">
         <v>948</v>
       </c>
-      <c r="L79" s="11" t="s">
+      <c r="L79" s="12" t="s">
         <v>949</v>
       </c>
-      <c r="M79" s="11" t="s">
+      <c r="M79" s="12" t="s">
         <v>950</v>
       </c>
-      <c r="N79" s="11" t="s">
+      <c r="N79" s="12" t="s">
         <v>951</v>
       </c>
-      <c r="O79" s="11" t="s">
+      <c r="O79" s="12" t="s">
         <v>952</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="2:15">
-      <c r="B80" s="10">
+      <c r="B80" s="11">
         <v>10075</v>
       </c>
-      <c r="C80" s="11" t="s">
+      <c r="C80" s="12" t="s">
         <v>953</v>
       </c>
-      <c r="D80" s="12" t="s">
+      <c r="D80" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="E80" s="11" t="s">
+      <c r="E80" s="12" t="s">
         <v>955</v>
       </c>
-      <c r="F80" s="11" t="s">
+      <c r="F80" s="12" t="s">
         <v>956</v>
       </c>
-      <c r="G80" s="11" t="s">
+      <c r="G80" s="12" t="s">
         <v>957</v>
       </c>
-      <c r="H80" s="11" t="s">
+      <c r="H80" s="12" t="s">
         <v>958</v>
       </c>
-      <c r="I80" s="11" t="s">
+      <c r="I80" s="12" t="s">
         <v>959</v>
       </c>
-      <c r="J80" s="11" t="s">
+      <c r="J80" s="12" t="s">
         <v>960</v>
       </c>
-      <c r="K80" s="11" t="s">
+      <c r="K80" s="12" t="s">
         <v>961</v>
       </c>
-      <c r="L80" s="11" t="s">
+      <c r="L80" s="12" t="s">
         <v>962</v>
       </c>
-      <c r="M80" s="11" t="s">
+      <c r="M80" s="12" t="s">
         <v>963</v>
       </c>
-      <c r="N80" s="11" t="s">
+      <c r="N80" s="12" t="s">
         <v>964</v>
       </c>
-      <c r="O80" s="11" t="s">
+      <c r="O80" s="12" t="s">
         <v>965</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="2:15">
-      <c r="B81" s="10">
+      <c r="B81" s="11">
         <v>10076</v>
       </c>
-      <c r="C81" s="11" t="s">
+      <c r="C81" s="12" t="s">
         <v>966</v>
       </c>
-      <c r="D81" s="12" t="s">
+      <c r="D81" s="13" t="s">
         <v>967</v>
       </c>
-      <c r="E81" s="11" t="s">
+      <c r="E81" s="12" t="s">
         <v>968</v>
       </c>
-      <c r="F81" s="11" t="s">
+      <c r="F81" s="12" t="s">
         <v>969</v>
       </c>
-      <c r="G81" s="11" t="s">
+      <c r="G81" s="12" t="s">
         <v>970</v>
       </c>
-      <c r="H81" s="11" t="s">
+      <c r="H81" s="12" t="s">
         <v>971</v>
       </c>
-      <c r="I81" s="11" t="s">
+      <c r="I81" s="12" t="s">
         <v>972</v>
       </c>
-      <c r="J81" s="11" t="s">
+      <c r="J81" s="12" t="s">
         <v>973</v>
       </c>
-      <c r="K81" s="11" t="s">
+      <c r="K81" s="12" t="s">
         <v>974</v>
       </c>
-      <c r="L81" s="11" t="s">
+      <c r="L81" s="12" t="s">
         <v>975</v>
       </c>
-      <c r="M81" s="11" t="s">
+      <c r="M81" s="12" t="s">
         <v>976</v>
       </c>
-      <c r="N81" s="11" t="s">
+      <c r="N81" s="12" t="s">
         <v>977</v>
       </c>
-      <c r="O81" s="11" t="s">
+      <c r="O81" s="12" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="2:15">
-      <c r="B82" s="10">
+      <c r="B82" s="11">
         <v>10077</v>
       </c>
-      <c r="C82" s="11" t="s">
+      <c r="C82" s="12" t="s">
         <v>979</v>
       </c>
-      <c r="D82" s="12" t="s">
+      <c r="D82" s="13" t="s">
         <v>980</v>
       </c>
-      <c r="E82" s="11" t="s">
+      <c r="E82" s="12" t="s">
         <v>981</v>
       </c>
-      <c r="F82" s="11" t="s">
+      <c r="F82" s="12" t="s">
         <v>982</v>
       </c>
-      <c r="G82" s="11" t="s">
+      <c r="G82" s="12" t="s">
         <v>983</v>
       </c>
-      <c r="H82" s="11" t="s">
+      <c r="H82" s="12" t="s">
         <v>984</v>
       </c>
-      <c r="I82" s="11" t="s">
+      <c r="I82" s="12" t="s">
         <v>985</v>
       </c>
-      <c r="J82" s="11" t="s">
+      <c r="J82" s="12" t="s">
         <v>986</v>
       </c>
-      <c r="K82" s="11" t="s">
+      <c r="K82" s="12" t="s">
         <v>987</v>
       </c>
-      <c r="L82" s="11" t="s">
+      <c r="L82" s="12" t="s">
         <v>988</v>
       </c>
-      <c r="M82" s="11" t="s">
+      <c r="M82" s="12" t="s">
         <v>989</v>
       </c>
-      <c r="N82" s="11" t="s">
+      <c r="N82" s="12" t="s">
         <v>990</v>
       </c>
-      <c r="O82" s="11" t="s">
+      <c r="O82" s="12" t="s">
         <v>991</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="2:15">
-      <c r="B83" s="10">
+      <c r="B83" s="11">
         <v>10078</v>
       </c>
-      <c r="C83" s="11" t="s">
+      <c r="C83" s="12" t="s">
         <v>992</v>
       </c>
-      <c r="D83" s="12" t="s">
+      <c r="D83" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="E83" s="11" t="s">
+      <c r="E83" s="12" t="s">
         <v>994</v>
       </c>
-      <c r="F83" s="11" t="s">
+      <c r="F83" s="12" t="s">
         <v>995</v>
       </c>
-      <c r="G83" s="11" t="s">
+      <c r="G83" s="12" t="s">
         <v>996</v>
       </c>
-      <c r="H83" s="11" t="s">
+      <c r="H83" s="12" t="s">
         <v>997</v>
       </c>
-      <c r="I83" s="11" t="s">
+      <c r="I83" s="12" t="s">
         <v>998</v>
       </c>
-      <c r="J83" s="11" t="s">
+      <c r="J83" s="12" t="s">
         <v>999</v>
       </c>
-      <c r="K83" s="11" t="s">
+      <c r="K83" s="12" t="s">
         <v>1000</v>
       </c>
-      <c r="L83" s="11" t="s">
+      <c r="L83" s="12" t="s">
         <v>1001</v>
       </c>
-      <c r="M83" s="11" t="s">
+      <c r="M83" s="12" t="s">
         <v>1002</v>
       </c>
-      <c r="N83" s="11" t="s">
+      <c r="N83" s="12" t="s">
         <v>1003</v>
       </c>
-      <c r="O83" s="11" t="s">
+      <c r="O83" s="12" t="s">
         <v>1004</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="2:15">
-      <c r="B84" s="10">
+      <c r="B84" s="11">
         <v>10079</v>
       </c>
-      <c r="C84" s="11" t="s">
+      <c r="C84" s="12" t="s">
         <v>1005</v>
       </c>
-      <c r="D84" s="12" t="s">
+      <c r="D84" s="13" t="s">
         <v>1006</v>
       </c>
-      <c r="E84" s="11" t="s">
+      <c r="E84" s="12" t="s">
         <v>1007</v>
       </c>
-      <c r="F84" s="11" t="s">
+      <c r="F84" s="12" t="s">
         <v>1008</v>
       </c>
-      <c r="G84" s="11" t="s">
+      <c r="G84" s="12" t="s">
         <v>1009</v>
       </c>
-      <c r="H84" s="11" t="s">
+      <c r="H84" s="12" t="s">
         <v>1010</v>
       </c>
-      <c r="I84" s="11" t="s">
+      <c r="I84" s="12" t="s">
         <v>1011</v>
       </c>
-      <c r="J84" s="11" t="s">
+      <c r="J84" s="12" t="s">
         <v>1012</v>
       </c>
-      <c r="K84" s="11" t="s">
+      <c r="K84" s="12" t="s">
         <v>1013</v>
       </c>
-      <c r="L84" s="11" t="s">
+      <c r="L84" s="12" t="s">
         <v>1014</v>
       </c>
-      <c r="M84" s="11" t="s">
+      <c r="M84" s="12" t="s">
         <v>1015</v>
       </c>
-      <c r="N84" s="11" t="s">
+      <c r="N84" s="12" t="s">
         <v>1016</v>
       </c>
-      <c r="O84" s="11" t="s">
+      <c r="O84" s="12" t="s">
         <v>1017</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="2:15">
-      <c r="B85" s="10">
+      <c r="B85" s="11">
         <v>10080</v>
       </c>
-      <c r="C85" s="11" t="s">
+      <c r="C85" s="12" t="s">
         <v>1018</v>
       </c>
-      <c r="D85" s="12" t="s">
+      <c r="D85" s="13" t="s">
         <v>1019</v>
       </c>
-      <c r="E85" s="11" t="s">
+      <c r="E85" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="F85" s="11" t="s">
+      <c r="F85" s="12" t="s">
         <v>1021</v>
       </c>
-      <c r="G85" s="11" t="s">
+      <c r="G85" s="12" t="s">
         <v>1022</v>
       </c>
-      <c r="H85" s="11" t="s">
+      <c r="H85" s="12" t="s">
         <v>1023</v>
       </c>
-      <c r="I85" s="11" t="s">
+      <c r="I85" s="12" t="s">
         <v>1024</v>
       </c>
-      <c r="J85" s="11" t="s">
+      <c r="J85" s="12" t="s">
         <v>1025</v>
       </c>
-      <c r="K85" s="11" t="s">
+      <c r="K85" s="12" t="s">
         <v>1026</v>
       </c>
-      <c r="L85" s="11" t="s">
+      <c r="L85" s="12" t="s">
         <v>1027</v>
       </c>
-      <c r="M85" s="11" t="s">
+      <c r="M85" s="12" t="s">
         <v>1028</v>
       </c>
-      <c r="N85" s="11" t="s">
+      <c r="N85" s="12" t="s">
         <v>1029</v>
       </c>
-      <c r="O85" s="11" t="s">
+      <c r="O85" s="12" t="s">
         <v>1030</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="2:15">
-      <c r="B86" s="10">
+      <c r="B86" s="11">
         <v>10081</v>
       </c>
-      <c r="C86" s="11" t="s">
+      <c r="C86" s="12" t="s">
         <v>1031</v>
       </c>
-      <c r="D86" s="12" t="s">
+      <c r="D86" s="13" t="s">
         <v>1032</v>
       </c>
-      <c r="E86" s="11" t="s">
+      <c r="E86" s="12" t="s">
         <v>1033</v>
       </c>
-      <c r="F86" s="11" t="s">
+      <c r="F86" s="12" t="s">
         <v>1034</v>
       </c>
-      <c r="G86" s="11" t="s">
+      <c r="G86" s="12" t="s">
         <v>1035</v>
       </c>
-      <c r="H86" s="11" t="s">
+      <c r="H86" s="12" t="s">
         <v>1036</v>
       </c>
-      <c r="I86" s="11" t="s">
+      <c r="I86" s="12" t="s">
         <v>1037</v>
       </c>
-      <c r="J86" s="11" t="s">
+      <c r="J86" s="12" t="s">
         <v>1038</v>
       </c>
-      <c r="K86" s="11" t="s">
+      <c r="K86" s="12" t="s">
         <v>1039</v>
       </c>
-      <c r="L86" s="11" t="s">
+      <c r="L86" s="12" t="s">
         <v>1040</v>
       </c>
-      <c r="M86" s="11" t="s">
+      <c r="M86" s="12" t="s">
         <v>1041</v>
       </c>
-      <c r="N86" s="11" t="s">
+      <c r="N86" s="12" t="s">
         <v>1042</v>
       </c>
-      <c r="O86" s="11" t="s">
+      <c r="O86" s="12" t="s">
         <v>1043</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="2:15">
-      <c r="B87" s="10">
+      <c r="B87" s="11">
         <v>10082</v>
       </c>
-      <c r="C87" s="11" t="s">
+      <c r="C87" s="12" t="s">
         <v>1044</v>
       </c>
-      <c r="D87" s="12" t="s">
+      <c r="D87" s="13" t="s">
         <v>1045</v>
       </c>
-      <c r="E87" s="11" t="s">
+      <c r="E87" s="12" t="s">
         <v>1046</v>
       </c>
-      <c r="F87" s="11" t="s">
+      <c r="F87" s="12" t="s">
         <v>1047</v>
       </c>
-      <c r="G87" s="11" t="s">
+      <c r="G87" s="12" t="s">
         <v>1048</v>
       </c>
-      <c r="H87" s="11" t="s">
+      <c r="H87" s="12" t="s">
         <v>1049</v>
       </c>
-      <c r="I87" s="11" t="s">
+      <c r="I87" s="12" t="s">
         <v>1050</v>
       </c>
-      <c r="J87" s="11" t="s">
+      <c r="J87" s="12" t="s">
         <v>1051</v>
       </c>
-      <c r="K87" s="11" t="s">
+      <c r="K87" s="12" t="s">
         <v>1052</v>
       </c>
-      <c r="L87" s="11" t="s">
+      <c r="L87" s="12" t="s">
         <v>1053</v>
       </c>
-      <c r="M87" s="11" t="s">
+      <c r="M87" s="12" t="s">
         <v>1054</v>
       </c>
-      <c r="N87" s="11" t="s">
+      <c r="N87" s="12" t="s">
         <v>1055</v>
       </c>
-      <c r="O87" s="11" t="s">
+      <c r="O87" s="12" t="s">
         <v>1056</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="2:15">
-      <c r="B88" s="10">
+      <c r="B88" s="11">
         <v>10083</v>
       </c>
-      <c r="C88" s="11" t="s">
+      <c r="C88" s="12" t="s">
         <v>1057</v>
       </c>
-      <c r="D88" s="12" t="s">
+      <c r="D88" s="13" t="s">
         <v>1058</v>
       </c>
-      <c r="E88" s="11" t="s">
+      <c r="E88" s="12" t="s">
         <v>1059</v>
       </c>
-      <c r="F88" s="11" t="s">
+      <c r="F88" s="12" t="s">
         <v>1060</v>
       </c>
-      <c r="G88" s="11" t="s">
+      <c r="G88" s="12" t="s">
         <v>1061</v>
       </c>
-      <c r="H88" s="11" t="s">
+      <c r="H88" s="12" t="s">
         <v>1062</v>
       </c>
-      <c r="I88" s="11" t="s">
+      <c r="I88" s="12" t="s">
         <v>1063</v>
       </c>
-      <c r="J88" s="11" t="s">
+      <c r="J88" s="12" t="s">
         <v>1064</v>
       </c>
-      <c r="K88" s="11" t="s">
+      <c r="K88" s="12" t="s">
         <v>1065</v>
       </c>
-      <c r="L88" s="11" t="s">
+      <c r="L88" s="12" t="s">
         <v>1066</v>
       </c>
-      <c r="M88" s="11" t="s">
+      <c r="M88" s="12" t="s">
         <v>1067</v>
       </c>
-      <c r="N88" s="11" t="s">
+      <c r="N88" s="12" t="s">
         <v>1068</v>
       </c>
-      <c r="O88" s="11" t="s">
+      <c r="O88" s="12" t="s">
         <v>1069</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="2:15">
-      <c r="B89" s="10">
+      <c r="B89" s="11">
         <v>10084</v>
       </c>
-      <c r="C89" s="11" t="s">
+      <c r="C89" s="12" t="s">
         <v>1070</v>
       </c>
-      <c r="D89" s="12" t="s">
+      <c r="D89" s="13" t="s">
         <v>1071</v>
       </c>
-      <c r="E89" s="11" t="s">
+      <c r="E89" s="12" t="s">
         <v>1072</v>
       </c>
-      <c r="F89" s="11" t="s">
+      <c r="F89" s="12" t="s">
         <v>1073</v>
       </c>
-      <c r="G89" s="11" t="s">
+      <c r="G89" s="12" t="s">
         <v>1074</v>
       </c>
-      <c r="H89" s="11" t="s">
+      <c r="H89" s="12" t="s">
         <v>1075</v>
       </c>
-      <c r="I89" s="11" t="s">
+      <c r="I89" s="12" t="s">
         <v>1074</v>
       </c>
-      <c r="J89" s="11" t="s">
+      <c r="J89" s="12" t="s">
         <v>1076</v>
       </c>
-      <c r="K89" s="11" t="s">
+      <c r="K89" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="L89" s="11" t="s">
+      <c r="L89" s="12" t="s">
         <v>1078</v>
       </c>
-      <c r="M89" s="11" t="s">
+      <c r="M89" s="12" t="s">
         <v>1079</v>
       </c>
-      <c r="N89" s="11" t="s">
+      <c r="N89" s="12" t="s">
         <v>1080</v>
       </c>
-      <c r="O89" s="11" t="s">
+      <c r="O89" s="12" t="s">
         <v>1081</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="2:15">
-      <c r="B90" s="10">
+      <c r="B90" s="11">
         <v>10085</v>
       </c>
-      <c r="C90" s="11" t="s">
+      <c r="C90" s="12" t="s">
         <v>1082</v>
       </c>
-      <c r="D90" s="12" t="s">
+      <c r="D90" s="13" t="s">
         <v>1083</v>
       </c>
-      <c r="E90" s="11" t="s">
+      <c r="E90" s="12" t="s">
         <v>1084</v>
       </c>
-      <c r="F90" s="11" t="s">
+      <c r="F90" s="12" t="s">
         <v>1085</v>
       </c>
-      <c r="G90" s="11" t="s">
+      <c r="G90" s="12" t="s">
         <v>1086</v>
       </c>
-      <c r="H90" s="11" t="s">
+      <c r="H90" s="12" t="s">
         <v>1087</v>
       </c>
-      <c r="I90" s="11" t="s">
+      <c r="I90" s="12" t="s">
         <v>1088</v>
       </c>
-      <c r="J90" s="11" t="s">
+      <c r="J90" s="12" t="s">
         <v>1089</v>
       </c>
-      <c r="K90" s="11" t="s">
+      <c r="K90" s="12" t="s">
         <v>1090</v>
       </c>
-      <c r="L90" s="11" t="s">
+      <c r="L90" s="12" t="s">
         <v>1091</v>
       </c>
-      <c r="M90" s="11" t="s">
+      <c r="M90" s="12" t="s">
         <v>1092</v>
       </c>
-      <c r="N90" s="11" t="s">
+      <c r="N90" s="12" t="s">
         <v>1093</v>
       </c>
-      <c r="O90" s="11" t="s">
+      <c r="O90" s="12" t="s">
         <v>1094</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="2:15">
-      <c r="B91" s="10">
+      <c r="B91" s="11">
         <v>10086</v>
       </c>
-      <c r="C91" s="11" t="s">
+      <c r="C91" s="12" t="s">
         <v>1095</v>
       </c>
-      <c r="D91" s="12" t="s">
+      <c r="D91" s="13" t="s">
         <v>1096</v>
       </c>
-      <c r="E91" s="11" t="s">
+      <c r="E91" s="12" t="s">
         <v>1097</v>
       </c>
-      <c r="F91" s="11" t="s">
+      <c r="F91" s="12" t="s">
         <v>1098</v>
       </c>
-      <c r="G91" s="11" t="s">
+      <c r="G91" s="12" t="s">
         <v>1099</v>
       </c>
-      <c r="H91" s="11" t="s">
+      <c r="H91" s="12" t="s">
         <v>1100</v>
       </c>
-      <c r="I91" s="11" t="s">
+      <c r="I91" s="12" t="s">
         <v>1101</v>
       </c>
-      <c r="J91" s="11" t="s">
+      <c r="J91" s="12" t="s">
         <v>1102</v>
       </c>
-      <c r="K91" s="11" t="s">
+      <c r="K91" s="12" t="s">
         <v>1103</v>
       </c>
-      <c r="L91" s="11" t="s">
+      <c r="L91" s="12" t="s">
         <v>1104</v>
       </c>
-      <c r="M91" s="11" t="s">
+      <c r="M91" s="12" t="s">
         <v>1105</v>
       </c>
-      <c r="N91" s="11" t="s">
+      <c r="N91" s="12" t="s">
         <v>1106</v>
       </c>
-      <c r="O91" s="11" t="s">
+      <c r="O91" s="12" t="s">
         <v>1107</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="2:15">
-      <c r="B92" s="10">
+      <c r="B92" s="11">
         <v>10087</v>
       </c>
-      <c r="C92" s="11" t="s">
+      <c r="C92" s="12" t="s">
         <v>1108</v>
       </c>
-      <c r="D92" s="11" t="s">
+      <c r="D92" s="12" t="s">
         <v>1109</v>
       </c>
-      <c r="E92" s="11" t="s">
+      <c r="E92" s="12" t="s">
         <v>1110</v>
       </c>
-      <c r="F92" s="11" t="s">
+      <c r="F92" s="12" t="s">
         <v>1111</v>
       </c>
-      <c r="G92" s="11" t="s">
+      <c r="G92" s="12" t="s">
         <v>1112</v>
       </c>
-      <c r="H92" s="11" t="s">
+      <c r="H92" s="12" t="s">
         <v>1113</v>
       </c>
-      <c r="I92" s="11" t="s">
+      <c r="I92" s="12" t="s">
         <v>1114</v>
       </c>
-      <c r="J92" s="11" t="s">
+      <c r="J92" s="12" t="s">
         <v>1115</v>
       </c>
-      <c r="K92" s="11" t="s">
+      <c r="K92" s="12" t="s">
         <v>1116</v>
       </c>
-      <c r="L92" s="11" t="s">
+      <c r="L92" s="12" t="s">
         <v>1117</v>
       </c>
-      <c r="M92" s="11" t="s">
+      <c r="M92" s="12" t="s">
         <v>1118</v>
       </c>
-      <c r="N92" s="11" t="s">
+      <c r="N92" s="12" t="s">
         <v>1119</v>
       </c>
-      <c r="O92" s="11" t="s">
+      <c r="O92" s="12" t="s">
         <v>1120</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="2:15">
-      <c r="B93" s="10">
+      <c r="B93" s="11">
         <v>10088</v>
       </c>
-      <c r="C93" s="11" t="s">
+      <c r="C93" s="12" t="s">
         <v>1121</v>
       </c>
-      <c r="D93" s="11" t="s">
+      <c r="D93" s="12" t="s">
         <v>1122</v>
       </c>
-      <c r="E93" s="11" t="s">
+      <c r="E93" s="12" t="s">
         <v>1123</v>
       </c>
-      <c r="F93" s="11" t="s">
+      <c r="F93" s="12" t="s">
         <v>1124</v>
       </c>
-      <c r="G93" s="11" t="s">
+      <c r="G93" s="12" t="s">
         <v>1125</v>
       </c>
-      <c r="H93" s="11" t="s">
+      <c r="H93" s="12" t="s">
         <v>1126</v>
       </c>
-      <c r="I93" s="11" t="s">
+      <c r="I93" s="12" t="s">
         <v>1127</v>
       </c>
-      <c r="J93" s="11" t="s">
+      <c r="J93" s="12" t="s">
         <v>1128</v>
       </c>
-      <c r="K93" s="11" t="s">
+      <c r="K93" s="12" t="s">
         <v>1129</v>
       </c>
-      <c r="L93" s="11" t="s">
+      <c r="L93" s="12" t="s">
         <v>1130</v>
       </c>
-      <c r="M93" s="11" t="s">
+      <c r="M93" s="12" t="s">
         <v>1131</v>
       </c>
-      <c r="N93" s="11" t="s">
+      <c r="N93" s="12" t="s">
         <v>1132</v>
       </c>
-      <c r="O93" s="11" t="s">
+      <c r="O93" s="12" t="s">
         <v>1133</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="2:15">
-      <c r="B94" s="10">
+      <c r="B94" s="11">
         <v>10089</v>
       </c>
-      <c r="C94" s="11" t="s">
+      <c r="C94" s="12" t="s">
         <v>1134</v>
       </c>
-      <c r="D94" s="11" t="s">
+      <c r="D94" s="12" t="s">
         <v>1135</v>
       </c>
-      <c r="E94" s="11" t="s">
+      <c r="E94" s="12" t="s">
         <v>1136</v>
       </c>
-      <c r="F94" s="11" t="s">
+      <c r="F94" s="12" t="s">
         <v>1137</v>
       </c>
-      <c r="G94" s="11" t="s">
+      <c r="G94" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="H94" s="11" t="s">
+      <c r="H94" s="12" t="s">
         <v>1139</v>
       </c>
-      <c r="I94" s="11" t="s">
+      <c r="I94" s="12" t="s">
         <v>1140</v>
       </c>
-      <c r="J94" s="11" t="s">
+      <c r="J94" s="12" t="s">
         <v>1141</v>
       </c>
-      <c r="K94" s="11" t="s">
+      <c r="K94" s="12" t="s">
         <v>1142</v>
       </c>
-      <c r="L94" s="11" t="s">
+      <c r="L94" s="12" t="s">
         <v>1143</v>
       </c>
-      <c r="M94" s="11" t="s">
+      <c r="M94" s="12" t="s">
         <v>1144</v>
       </c>
-      <c r="N94" s="11" t="s">
+      <c r="N94" s="12" t="s">
         <v>1145</v>
       </c>
-      <c r="O94" s="11" t="s">
+      <c r="O94" s="12" t="s">
         <v>1146</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="2:15">
-      <c r="B95" s="10">
+      <c r="B95" s="11">
         <v>10090</v>
       </c>
-      <c r="C95" s="11" t="s">
+      <c r="C95" s="12" t="s">
         <v>1147</v>
       </c>
-      <c r="D95" s="12" t="s">
+      <c r="D95" s="13" t="s">
         <v>1148</v>
       </c>
-      <c r="E95" s="11" t="s">
+      <c r="E95" s="12" t="s">
         <v>1149</v>
       </c>
-      <c r="F95" s="11" t="s">
+      <c r="F95" s="12" t="s">
         <v>1150</v>
       </c>
-      <c r="G95" s="11" t="s">
+      <c r="G95" s="12" t="s">
         <v>1151</v>
       </c>
-      <c r="H95" s="11" t="s">
+      <c r="H95" s="12" t="s">
         <v>1152</v>
       </c>
-      <c r="I95" s="11" t="s">
+      <c r="I95" s="12" t="s">
         <v>1153</v>
       </c>
-      <c r="J95" s="11" t="s">
+      <c r="J95" s="12" t="s">
         <v>1154</v>
       </c>
-      <c r="K95" s="11" t="s">
+      <c r="K95" s="12" t="s">
         <v>1155</v>
       </c>
-      <c r="L95" s="11" t="s">
+      <c r="L95" s="12" t="s">
         <v>1156</v>
       </c>
-      <c r="M95" s="11" t="s">
+      <c r="M95" s="12" t="s">
         <v>1157</v>
       </c>
-      <c r="N95" s="11" t="s">
+      <c r="N95" s="12" t="s">
         <v>1158</v>
       </c>
-      <c r="O95" s="11" t="s">
+      <c r="O95" s="12" t="s">
         <v>1159</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="2:15">
-      <c r="B96" s="10">
+      <c r="B96" s="11">
         <v>10091</v>
       </c>
       <c r="C96" t="s">
@@ -11101,7 +11157,7 @@
       </c>
     </row>
     <row r="97" customHeight="1" spans="1:16">
-      <c r="B97" s="10">
+      <c r="B97" s="11">
         <v>10092</v>
       </c>
       <c r="C97" t="s">
@@ -11145,7 +11201,7 @@
       </c>
     </row>
     <row r="98" customHeight="1" spans="1:16">
-      <c r="B98" s="3">
+      <c r="B98" s="4">
         <v>10093</v>
       </c>
       <c r="C98" t="s">
@@ -11157,28 +11213,28 @@
       <c r="E98" t="s">
         <v>1188</v>
       </c>
-      <c r="F98" s="17" t="s">
+      <c r="F98" s="18" t="s">
         <v>1189</v>
       </c>
-      <c r="G98" s="17" t="s">
+      <c r="G98" s="18" t="s">
         <v>1190</v>
       </c>
       <c r="H98" t="s">
         <v>1191</v>
       </c>
-      <c r="I98" s="17" t="s">
+      <c r="I98" s="18" t="s">
         <v>1192</v>
       </c>
-      <c r="J98" s="17" t="s">
+      <c r="J98" s="18" t="s">
         <v>1193</v>
       </c>
-      <c r="K98" s="17" t="s">
+      <c r="K98" s="18" t="s">
         <v>1194</v>
       </c>
       <c r="L98" t="s">
         <v>1195</v>
       </c>
-      <c r="M98" s="17" t="s">
+      <c r="M98" s="18" t="s">
         <v>1196</v>
       </c>
       <c r="N98" t="s">
@@ -11189,7 +11245,7 @@
       </c>
     </row>
     <row r="99" customHeight="1" spans="1:16">
-      <c r="B99" s="3">
+      <c r="B99" s="4">
         <v>10094</v>
       </c>
       <c r="C99" t="s">
@@ -11210,10 +11266,10 @@
       <c r="H99" t="s">
         <v>1204</v>
       </c>
-      <c r="I99" s="17" t="s">
+      <c r="I99" s="18" t="s">
         <v>1205</v>
       </c>
-      <c r="J99" s="17" t="s">
+      <c r="J99" s="18" t="s">
         <v>1206</v>
       </c>
       <c r="K99" t="s">
@@ -11222,18 +11278,18 @@
       <c r="L99" t="s">
         <v>1208</v>
       </c>
-      <c r="M99" s="17" t="s">
+      <c r="M99" s="18" t="s">
         <v>1209</v>
       </c>
-      <c r="N99" s="17" t="s">
+      <c r="N99" s="18" t="s">
         <v>1210</v>
       </c>
-      <c r="O99" s="17" t="s">
+      <c r="O99" s="18" t="s">
         <v>1211</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="1:16">
-      <c r="B100" s="3">
+      <c r="B100" s="4">
         <v>10095</v>
       </c>
       <c r="C100" t="s">
@@ -11266,18 +11322,18 @@
       <c r="L100" t="s">
         <v>1221</v>
       </c>
-      <c r="M100" s="17" t="s">
+      <c r="M100" s="18" t="s">
         <v>1222</v>
       </c>
-      <c r="N100" s="17" t="s">
+      <c r="N100" s="18" t="s">
         <v>1223</v>
       </c>
-      <c r="O100" s="17" t="s">
+      <c r="O100" s="18" t="s">
         <v>1224</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="1:16">
-      <c r="B101" s="3">
+      <c r="B101" s="4">
         <v>10096</v>
       </c>
       <c r="C101" t="s">
@@ -11289,31 +11345,31 @@
       <c r="E101" t="s">
         <v>1227</v>
       </c>
-      <c r="F101" s="17" t="s">
+      <c r="F101" s="18" t="s">
         <v>1228</v>
       </c>
-      <c r="G101" s="17" t="s">
+      <c r="G101" s="18" t="s">
         <v>1229</v>
       </c>
       <c r="H101" t="s">
         <v>1230</v>
       </c>
-      <c r="I101" s="17" t="s">
+      <c r="I101" s="18" t="s">
         <v>1231</v>
       </c>
-      <c r="J101" s="17" t="s">
+      <c r="J101" s="18" t="s">
         <v>1232</v>
       </c>
-      <c r="K101" s="17" t="s">
+      <c r="K101" s="18" t="s">
         <v>1233</v>
       </c>
-      <c r="L101" s="17" t="s">
+      <c r="L101" s="18" t="s">
         <v>1234</v>
       </c>
-      <c r="M101" s="17" t="s">
+      <c r="M101" s="18" t="s">
         <v>1235</v>
       </c>
-      <c r="N101" s="17" t="s">
+      <c r="N101" s="18" t="s">
         <v>1236</v>
       </c>
       <c r="O101" t="s">
@@ -11321,7 +11377,7 @@
       </c>
     </row>
     <row r="102" customHeight="1" spans="1:16">
-      <c r="B102" s="3">
+      <c r="B102" s="4">
         <v>10097</v>
       </c>
       <c r="C102" t="s">
@@ -11333,28 +11389,28 @@
       <c r="E102" t="s">
         <v>1240</v>
       </c>
-      <c r="F102" s="18" t="s">
+      <c r="F102" s="19" t="s">
         <v>1241</v>
       </c>
-      <c r="G102" s="18" t="s">
+      <c r="G102" s="19" t="s">
         <v>1242</v>
       </c>
       <c r="H102" t="s">
         <v>1243</v>
       </c>
-      <c r="I102" s="17" t="s">
+      <c r="I102" s="18" t="s">
         <v>1244</v>
       </c>
-      <c r="J102" s="17" t="s">
+      <c r="J102" s="18" t="s">
         <v>1245</v>
       </c>
-      <c r="K102" s="17" t="s">
+      <c r="K102" s="18" t="s">
         <v>1246</v>
       </c>
       <c r="L102" t="s">
         <v>1247</v>
       </c>
-      <c r="M102" s="17" t="s">
+      <c r="M102" s="18" t="s">
         <v>1248</v>
       </c>
       <c r="N102" t="s">
@@ -11368,7 +11424,7 @@
       <c r="A103" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B103" s="3">
+      <c r="B103" s="4">
         <v>10098</v>
       </c>
       <c r="C103" s="2" t="s">
@@ -11415,57 +11471,57 @@
       </c>
     </row>
     <row r="104" customFormat="1" customHeight="1" spans="1:16">
-      <c r="B104" s="3">
+      <c r="B104" s="4">
         <v>10099</v>
       </c>
-      <c r="C104" s="11" t="s">
+      <c r="C104" s="12" t="s">
         <v>1265</v>
       </c>
-      <c r="D104" s="12" t="s">
+      <c r="D104" s="13" t="s">
         <v>1266</v>
       </c>
-      <c r="E104" s="11" t="s">
+      <c r="E104" s="12" t="s">
         <v>1267</v>
       </c>
-      <c r="F104" s="11" t="s">
+      <c r="F104" s="12" t="s">
         <v>1268</v>
       </c>
-      <c r="G104" s="11" t="s">
+      <c r="G104" s="12" t="s">
         <v>1269</v>
       </c>
-      <c r="H104" s="11" t="s">
+      <c r="H104" s="12" t="s">
         <v>1270</v>
       </c>
-      <c r="I104" s="11" t="s">
+      <c r="I104" s="12" t="s">
         <v>1271</v>
       </c>
-      <c r="J104" s="11" t="s">
+      <c r="J104" s="12" t="s">
         <v>1272</v>
       </c>
-      <c r="K104" s="11" t="s">
+      <c r="K104" s="12" t="s">
         <v>1273</v>
       </c>
-      <c r="L104" s="11" t="s">
+      <c r="L104" s="12" t="s">
         <v>1274</v>
       </c>
-      <c r="M104" s="11" t="s">
+      <c r="M104" s="12" t="s">
         <v>1275</v>
       </c>
-      <c r="N104" s="14" t="s">
+      <c r="N104" s="15" t="s">
         <v>1276</v>
       </c>
-      <c r="O104" s="11" t="s">
+      <c r="O104" s="12" t="s">
         <v>1277</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="B105" s="3">
+      <c r="B105" s="4">
         <v>10100</v>
       </c>
       <c r="C105" t="s">
         <v>1278</v>
       </c>
-      <c r="D105" s="16" t="s">
+      <c r="D105" s="17" t="s">
         <v>153</v>
       </c>
       <c r="E105" t="s">
@@ -11474,7 +11530,7 @@
       <c r="F105" t="s">
         <v>1280</v>
       </c>
-      <c r="G105" s="16" t="s">
+      <c r="G105" s="17" t="s">
         <v>1281</v>
       </c>
       <c r="H105" t="s">
@@ -11486,25 +11542,25 @@
       <c r="J105" t="s">
         <v>1284</v>
       </c>
-      <c r="K105" s="16" t="s">
+      <c r="K105" s="17" t="s">
         <v>1285</v>
       </c>
       <c r="L105" t="s">
         <v>1286</v>
       </c>
-      <c r="M105" s="17" t="s">
+      <c r="M105" s="18" t="s">
         <v>1287</v>
       </c>
-      <c r="N105" s="18" t="s">
+      <c r="N105" s="19" t="s">
         <v>1288</v>
       </c>
-      <c r="O105" s="17" t="s">
+      <c r="O105" s="18" t="s">
         <v>1289</v>
       </c>
       <c r="P105"/>
     </row>
     <row r="106" customHeight="1" spans="1:16">
-      <c r="B106" s="3">
+      <c r="B106" s="4">
         <v>10101</v>
       </c>
       <c r="C106" s="2" t="s">
@@ -11548,43 +11604,43 @@
       </c>
     </row>
     <row r="107" customHeight="1" spans="1:16">
-      <c r="B107" s="3">
+      <c r="B107" s="4">
         <v>10102</v>
       </c>
       <c r="C107" t="s">
         <v>1303</v>
       </c>
-      <c r="D107" s="16" t="s">
+      <c r="D107" s="17" t="s">
         <v>1304</v>
       </c>
       <c r="E107" t="s">
         <v>1305</v>
       </c>
-      <c r="F107" s="17" t="s">
+      <c r="F107" s="18" t="s">
         <v>1306</v>
       </c>
-      <c r="G107" s="17" t="s">
+      <c r="G107" s="18" t="s">
         <v>1307</v>
       </c>
-      <c r="H107" s="17" t="s">
+      <c r="H107" s="18" t="s">
         <v>1308</v>
       </c>
-      <c r="I107" s="17" t="s">
+      <c r="I107" s="18" t="s">
         <v>1309</v>
       </c>
-      <c r="J107" s="17" t="s">
+      <c r="J107" s="18" t="s">
         <v>1310</v>
       </c>
-      <c r="K107" s="17" t="s">
+      <c r="K107" s="18" t="s">
         <v>1311</v>
       </c>
-      <c r="L107" s="17" t="s">
+      <c r="L107" s="18" t="s">
         <v>1312</v>
       </c>
-      <c r="M107" s="17" t="s">
+      <c r="M107" s="18" t="s">
         <v>1313</v>
       </c>
-      <c r="N107" s="17" t="s">
+      <c r="N107" s="18" t="s">
         <v>1314</v>
       </c>
       <c r="O107" t="s">
@@ -11592,13 +11648,13 @@
       </c>
     </row>
     <row r="108" customHeight="1" spans="1:16">
-      <c r="B108" s="3">
+      <c r="B108" s="4">
         <v>10103</v>
       </c>
       <c r="C108" t="s">
         <v>1316</v>
       </c>
-      <c r="D108" s="16" t="s">
+      <c r="D108" s="17" t="s">
         <v>1317</v>
       </c>
       <c r="E108" t="s">
@@ -11607,7 +11663,7 @@
       <c r="F108" t="s">
         <v>1319</v>
       </c>
-      <c r="G108" s="16" t="s">
+      <c r="G108" s="17" t="s">
         <v>1320</v>
       </c>
       <c r="H108" t="s">
@@ -11619,13 +11675,13 @@
       <c r="J108" t="s">
         <v>1323</v>
       </c>
-      <c r="K108" s="17" t="s">
+      <c r="K108" s="18" t="s">
         <v>1324</v>
       </c>
-      <c r="L108" s="17" t="s">
+      <c r="L108" s="18" t="s">
         <v>1325</v>
       </c>
-      <c r="M108" s="17" t="s">
+      <c r="M108" s="18" t="s">
         <v>1326</v>
       </c>
       <c r="N108" t="s">
@@ -11636,13 +11692,13 @@
       </c>
     </row>
     <row r="109" customHeight="1" spans="1:16">
-      <c r="B109" s="3">
+      <c r="B109" s="4">
         <v>10104</v>
       </c>
       <c r="C109" t="s">
         <v>1329</v>
       </c>
-      <c r="D109" s="16" t="s">
+      <c r="D109" s="17" t="s">
         <v>1330</v>
       </c>
       <c r="E109" t="s">
@@ -11651,7 +11707,7 @@
       <c r="F109" t="s">
         <v>1332</v>
       </c>
-      <c r="G109" s="16" t="s">
+      <c r="G109" s="17" t="s">
         <v>1333</v>
       </c>
       <c r="H109" t="s">
@@ -11663,24 +11719,24 @@
       <c r="J109" t="s">
         <v>1336</v>
       </c>
-      <c r="K109" s="17" t="s">
+      <c r="K109" s="18" t="s">
         <v>1337</v>
       </c>
-      <c r="L109" s="17" t="s">
+      <c r="L109" s="18" t="s">
         <v>1338</v>
       </c>
-      <c r="M109" s="17" t="s">
+      <c r="M109" s="18" t="s">
         <v>1339</v>
       </c>
-      <c r="N109" s="17" t="s">
+      <c r="N109" s="18" t="s">
         <v>1340</v>
       </c>
-      <c r="O109" s="17" t="s">
+      <c r="O109" s="18" t="s">
         <v>1341</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="1:16">
-      <c r="B110" s="3">
+      <c r="B110" s="4">
         <v>10105</v>
       </c>
       <c r="C110" t="s">
@@ -11692,75 +11748,75 @@
       <c r="E110" t="s">
         <v>1344</v>
       </c>
-      <c r="F110" s="17" t="s">
+      <c r="F110" s="18" t="s">
         <v>1345</v>
       </c>
-      <c r="G110" s="17" t="s">
+      <c r="G110" s="18" t="s">
         <v>1346</v>
       </c>
-      <c r="H110" s="17" t="s">
+      <c r="H110" s="18" t="s">
         <v>1347</v>
       </c>
-      <c r="I110" s="17" t="s">
+      <c r="I110" s="18" t="s">
         <v>1348</v>
       </c>
-      <c r="J110" s="17" t="s">
+      <c r="J110" s="18" t="s">
         <v>1349</v>
       </c>
-      <c r="K110" s="17" t="s">
+      <c r="K110" s="18" t="s">
         <v>1350</v>
       </c>
       <c r="L110" t="s">
         <v>1351</v>
       </c>
-      <c r="M110" s="18" t="s">
+      <c r="M110" s="19" t="s">
         <v>1352</v>
       </c>
-      <c r="N110" s="18" t="s">
+      <c r="N110" s="19" t="s">
         <v>1353</v>
       </c>
-      <c r="O110" s="18" t="s">
+      <c r="O110" s="19" t="s">
         <v>1354</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="1:16">
-      <c r="B111" s="3">
+      <c r="B111" s="4">
         <v>10106</v>
       </c>
-      <c r="C111" s="19" t="s">
+      <c r="C111" s="20" t="s">
         <v>1355</v>
       </c>
-      <c r="D111" s="16" t="s">
+      <c r="D111" s="17" t="s">
         <v>1356</v>
       </c>
       <c r="E111" t="s">
         <v>1357</v>
       </c>
-      <c r="F111" s="17" t="s">
+      <c r="F111" s="18" t="s">
         <v>1358</v>
       </c>
-      <c r="G111" s="16" t="s">
+      <c r="G111" s="17" t="s">
         <v>1359</v>
       </c>
-      <c r="H111" s="17" t="s">
+      <c r="H111" s="18" t="s">
         <v>1360</v>
       </c>
-      <c r="I111" s="17" t="s">
+      <c r="I111" s="18" t="s">
         <v>1361</v>
       </c>
-      <c r="J111" s="17" t="s">
+      <c r="J111" s="18" t="s">
         <v>1362</v>
       </c>
-      <c r="K111" s="17" t="s">
+      <c r="K111" s="18" t="s">
         <v>1363</v>
       </c>
       <c r="L111" t="s">
         <v>1364</v>
       </c>
-      <c r="M111" s="17" t="s">
+      <c r="M111" s="18" t="s">
         <v>1365</v>
       </c>
-      <c r="N111" s="17" t="s">
+      <c r="N111" s="18" t="s">
         <v>1366</v>
       </c>
       <c r="O111" t="s">
@@ -11768,7 +11824,7 @@
       </c>
     </row>
     <row r="112" customHeight="1" spans="1:16">
-      <c r="B112" s="3">
+      <c r="B112" s="4">
         <v>10107</v>
       </c>
       <c r="C112" t="s">
@@ -11780,7 +11836,7 @@
       <c r="E112" t="s">
         <v>1370</v>
       </c>
-      <c r="F112" s="17" t="s">
+      <c r="F112" s="18" t="s">
         <v>1371</v>
       </c>
       <c r="G112" t="s">
@@ -11789,19 +11845,19 @@
       <c r="H112" t="s">
         <v>1373</v>
       </c>
-      <c r="I112" s="17" t="s">
+      <c r="I112" s="18" t="s">
         <v>1374</v>
       </c>
-      <c r="J112" s="17" t="s">
+      <c r="J112" s="18" t="s">
         <v>1375</v>
       </c>
-      <c r="K112" s="17" t="s">
+      <c r="K112" s="18" t="s">
         <v>1376</v>
       </c>
       <c r="L112" t="s">
         <v>1377</v>
       </c>
-      <c r="M112" s="17" t="s">
+      <c r="M112" s="18" t="s">
         <v>1378</v>
       </c>
       <c r="N112" t="s">
@@ -11815,7 +11871,7 @@
       <c r="A113" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B113" s="3">
+      <c r="B113" s="4">
         <v>10108</v>
       </c>
       <c r="C113" s="2" t="s">
@@ -11865,7 +11921,7 @@
       <c r="A114" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B114" s="3">
+      <c r="B114" s="4">
         <v>10109</v>
       </c>
       <c r="C114" s="2" t="s">
@@ -11915,7 +11971,7 @@
       <c r="A115" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B115" s="3">
+      <c r="B115" s="4">
         <v>10110</v>
       </c>
       <c r="C115" s="2" t="s">
@@ -11965,7 +12021,7 @@
       <c r="A116" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B116" s="3">
+      <c r="B116" s="4">
         <v>10111</v>
       </c>
       <c r="C116" s="2" t="s">
@@ -12015,7 +12071,7 @@
       <c r="A117" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B117" s="3">
+      <c r="B117" s="4">
         <v>10112</v>
       </c>
       <c r="C117" s="2" t="s">
@@ -12065,7 +12121,7 @@
       <c r="A118" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B118" s="3">
+      <c r="B118" s="4">
         <v>10113</v>
       </c>
       <c r="C118" s="2" t="s">
@@ -12115,7 +12171,7 @@
       <c r="A119" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B119" s="3">
+      <c r="B119" s="4">
         <v>10114</v>
       </c>
       <c r="C119" s="2" t="s">
@@ -12165,7 +12221,7 @@
       <c r="A120" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B120" s="3">
+      <c r="B120" s="4">
         <v>10115</v>
       </c>
       <c r="C120" s="2" t="s">
@@ -12215,7 +12271,7 @@
       <c r="A121" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B121" s="3">
+      <c r="B121" s="4">
         <v>10116</v>
       </c>
       <c r="C121" s="2" t="s">
@@ -12265,7 +12321,7 @@
       <c r="A122" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B122" s="3">
+      <c r="B122" s="4">
         <v>10117</v>
       </c>
       <c r="C122" s="2" t="s">
@@ -12315,7 +12371,7 @@
       <c r="A123" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B123" s="3">
+      <c r="B123" s="4">
         <v>10118</v>
       </c>
       <c r="C123" s="2" t="s">
@@ -12365,7 +12421,7 @@
       <c r="A124" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B124" s="3">
+      <c r="B124" s="4">
         <v>10119</v>
       </c>
       <c r="C124" s="2" t="s">
@@ -12415,10 +12471,10 @@
       <c r="A125" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B125" s="3">
+      <c r="B125" s="4">
         <v>10120</v>
       </c>
-      <c r="C125" s="20" t="s">
+      <c r="C125" s="21" t="s">
         <v>1534</v>
       </c>
       <c r="D125" s="2" t="s">
@@ -12462,227 +12518,227 @@
       </c>
     </row>
     <row r="126" customHeight="1" spans="1:16">
-      <c r="B126" s="3">
+      <c r="B126" s="4">
         <v>10121</v>
       </c>
       <c r="C126" t="s">
         <v>1545</v>
       </c>
-      <c r="D126" s="12" t="s">
+      <c r="D126" s="13" t="s">
         <v>1546</v>
       </c>
-      <c r="E126" s="11" t="s">
+      <c r="E126" s="12" t="s">
         <v>1547</v>
       </c>
-      <c r="F126" s="11" t="s">
+      <c r="F126" s="12" t="s">
         <v>1548</v>
       </c>
-      <c r="G126" s="11" t="s">
+      <c r="G126" s="12" t="s">
         <v>1549</v>
       </c>
-      <c r="H126" s="11" t="s">
+      <c r="H126" s="12" t="s">
         <v>1550</v>
       </c>
-      <c r="I126" s="11" t="s">
+      <c r="I126" s="12" t="s">
         <v>1551</v>
       </c>
-      <c r="J126" s="11" t="s">
+      <c r="J126" s="12" t="s">
         <v>1552</v>
       </c>
-      <c r="K126" s="11" t="s">
+      <c r="K126" s="12" t="s">
         <v>1553</v>
       </c>
-      <c r="L126" s="11" t="s">
+      <c r="L126" s="12" t="s">
         <v>1554</v>
       </c>
-      <c r="M126" s="11" t="s">
+      <c r="M126" s="12" t="s">
         <v>1555</v>
       </c>
-      <c r="N126" s="11" t="s">
+      <c r="N126" s="12" t="s">
         <v>1556</v>
       </c>
-      <c r="O126" s="11" t="s">
+      <c r="O126" s="12" t="s">
         <v>1557</v>
       </c>
     </row>
     <row r="127" customHeight="1" spans="1:16">
-      <c r="B127" s="3">
+      <c r="B127" s="4">
         <v>10122</v>
       </c>
       <c r="C127" t="s">
         <v>1558</v>
       </c>
-      <c r="D127" s="12" t="s">
+      <c r="D127" s="13" t="s">
         <v>1559</v>
       </c>
-      <c r="E127" s="11" t="s">
+      <c r="E127" s="12" t="s">
         <v>1560</v>
       </c>
-      <c r="F127" s="11" t="s">
+      <c r="F127" s="12" t="s">
         <v>1561</v>
       </c>
-      <c r="G127" s="11" t="s">
+      <c r="G127" s="12" t="s">
         <v>1562</v>
       </c>
-      <c r="H127" s="11" t="s">
+      <c r="H127" s="12" t="s">
         <v>1563</v>
       </c>
-      <c r="I127" s="11" t="s">
+      <c r="I127" s="12" t="s">
         <v>1564</v>
       </c>
-      <c r="J127" s="11" t="s">
+      <c r="J127" s="12" t="s">
         <v>1565</v>
       </c>
-      <c r="K127" s="11" t="s">
+      <c r="K127" s="12" t="s">
         <v>1566</v>
       </c>
-      <c r="L127" s="11" t="s">
+      <c r="L127" s="12" t="s">
         <v>1567</v>
       </c>
-      <c r="M127" s="11" t="s">
+      <c r="M127" s="12" t="s">
         <v>1568</v>
       </c>
-      <c r="N127" s="11" t="s">
+      <c r="N127" s="12" t="s">
         <v>1569</v>
       </c>
-      <c r="O127" s="11" t="s">
+      <c r="O127" s="12" t="s">
         <v>1570</v>
       </c>
     </row>
     <row r="128" customHeight="1" spans="1:16">
-      <c r="B128" s="3">
+      <c r="B128" s="4">
         <v>10123</v>
       </c>
       <c r="C128" t="s">
         <v>1571</v>
       </c>
-      <c r="D128" s="12" t="s">
+      <c r="D128" s="13" t="s">
         <v>1572</v>
       </c>
-      <c r="E128" s="11" t="s">
+      <c r="E128" s="12" t="s">
         <v>1573</v>
       </c>
-      <c r="F128" s="11" t="s">
+      <c r="F128" s="12" t="s">
         <v>1574</v>
       </c>
-      <c r="G128" s="11" t="s">
+      <c r="G128" s="12" t="s">
         <v>1575</v>
       </c>
-      <c r="H128" s="11" t="s">
+      <c r="H128" s="12" t="s">
         <v>1576</v>
       </c>
-      <c r="I128" s="11" t="s">
+      <c r="I128" s="12" t="s">
         <v>1577</v>
       </c>
-      <c r="J128" s="11" t="s">
+      <c r="J128" s="12" t="s">
         <v>1578</v>
       </c>
-      <c r="K128" s="11" t="s">
+      <c r="K128" s="12" t="s">
         <v>1579</v>
       </c>
-      <c r="L128" s="11" t="s">
+      <c r="L128" s="12" t="s">
         <v>1580</v>
       </c>
-      <c r="M128" s="11" t="s">
+      <c r="M128" s="12" t="s">
         <v>1581</v>
       </c>
-      <c r="N128" s="11" t="s">
+      <c r="N128" s="12" t="s">
         <v>1582</v>
       </c>
-      <c r="O128" s="11" t="s">
+      <c r="O128" s="12" t="s">
         <v>1583</v>
       </c>
     </row>
-    <row r="129" customHeight="1" spans="2:15">
-      <c r="B129" s="3">
+    <row r="129" customHeight="1" spans="1:16">
+      <c r="B129" s="4">
         <v>10124</v>
       </c>
       <c r="C129" t="s">
         <v>1584</v>
       </c>
-      <c r="D129" s="12" t="s">
+      <c r="D129" s="13" t="s">
         <v>1585</v>
       </c>
-      <c r="E129" s="11" t="s">
+      <c r="E129" s="12" t="s">
         <v>1586</v>
       </c>
-      <c r="F129" s="11" t="s">
+      <c r="F129" s="12" t="s">
         <v>1587</v>
       </c>
-      <c r="G129" s="11" t="s">
+      <c r="G129" s="12" t="s">
         <v>1588</v>
       </c>
-      <c r="H129" s="11" t="s">
+      <c r="H129" s="12" t="s">
         <v>1589</v>
       </c>
-      <c r="I129" s="11" t="s">
+      <c r="I129" s="12" t="s">
         <v>1590</v>
       </c>
-      <c r="J129" s="11" t="s">
+      <c r="J129" s="12" t="s">
         <v>1591</v>
       </c>
-      <c r="K129" s="11" t="s">
+      <c r="K129" s="12" t="s">
         <v>1592</v>
       </c>
-      <c r="L129" s="11" t="s">
+      <c r="L129" s="12" t="s">
         <v>1593</v>
       </c>
-      <c r="M129" s="11" t="s">
+      <c r="M129" s="12" t="s">
         <v>1594</v>
       </c>
-      <c r="N129" s="11" t="s">
+      <c r="N129" s="12" t="s">
         <v>1595</v>
       </c>
-      <c r="O129" s="11" t="s">
+      <c r="O129" s="12" t="s">
         <v>1596</v>
       </c>
     </row>
-    <row r="130" customHeight="1" spans="2:15">
-      <c r="B130" s="3">
+    <row r="130" customHeight="1" spans="1:16">
+      <c r="B130" s="4">
         <v>10125</v>
       </c>
       <c r="C130" t="s">
         <v>1597</v>
       </c>
-      <c r="D130" s="12" t="s">
+      <c r="D130" s="13" t="s">
         <v>1598</v>
       </c>
-      <c r="E130" s="11" t="s">
+      <c r="E130" s="12" t="s">
         <v>1599</v>
       </c>
-      <c r="F130" s="11" t="s">
+      <c r="F130" s="12" t="s">
         <v>1600</v>
       </c>
-      <c r="G130" s="11" t="s">
+      <c r="G130" s="12" t="s">
         <v>1601</v>
       </c>
-      <c r="H130" s="11" t="s">
+      <c r="H130" s="12" t="s">
         <v>1602</v>
       </c>
-      <c r="I130" s="11" t="s">
+      <c r="I130" s="12" t="s">
         <v>1603</v>
       </c>
-      <c r="J130" s="11" t="s">
+      <c r="J130" s="12" t="s">
         <v>1604</v>
       </c>
-      <c r="K130" s="11" t="s">
+      <c r="K130" s="12" t="s">
         <v>1605</v>
       </c>
-      <c r="L130" s="11" t="s">
+      <c r="L130" s="12" t="s">
         <v>1606</v>
       </c>
-      <c r="M130" s="11" t="s">
+      <c r="M130" s="12" t="s">
         <v>1607</v>
       </c>
-      <c r="N130" s="14" t="s">
+      <c r="N130" s="15" t="s">
         <v>1608</v>
       </c>
-      <c r="O130" s="11" t="s">
+      <c r="O130" s="12" t="s">
         <v>1609</v>
       </c>
     </row>
-    <row r="131" customHeight="1" spans="2:15">
-      <c r="B131" s="3">
+    <row r="131" customHeight="1" spans="1:16">
+      <c r="B131" s="4">
         <v>10126</v>
       </c>
       <c r="C131" t="s">
@@ -12723,6 +12779,56 @@
       </c>
       <c r="O131" t="s">
         <v>1620</v>
+      </c>
+    </row>
+    <row r="132" s="3" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A132" s="3" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B132" s="4">
+        <v>10127</v>
+      </c>
+      <c r="C132" s="22" t="s">
+        <v>1621</v>
+      </c>
+      <c r="D132" s="22" t="s">
+        <v>1622</v>
+      </c>
+      <c r="E132" s="22" t="s">
+        <v>1623</v>
+      </c>
+      <c r="F132" s="22" t="s">
+        <v>1624</v>
+      </c>
+      <c r="G132" s="22" t="s">
+        <v>1625</v>
+      </c>
+      <c r="H132" s="22" t="s">
+        <v>1626</v>
+      </c>
+      <c r="I132" s="22" t="s">
+        <v>1627</v>
+      </c>
+      <c r="J132" s="22" t="s">
+        <v>1628</v>
+      </c>
+      <c r="K132" s="22" t="s">
+        <v>1629</v>
+      </c>
+      <c r="L132" s="3" t="s">
+        <v>1630</v>
+      </c>
+      <c r="M132" s="22" t="s">
+        <v>1631</v>
+      </c>
+      <c r="N132" s="22" t="s">
+        <v>1632</v>
+      </c>
+      <c r="O132" s="22" t="s">
+        <v>1633</v>
+      </c>
+      <c r="P132" s="3" t="s">
+        <v>1251</v>
       </c>
     </row>
   </sheetData>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1733" uniqueCount="1621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1747" uniqueCount="1634">
   <si>
     <t>##var</t>
   </si>
@@ -5077,43 +5077,43 @@
     <t>Yeni Oynanış</t>
   </si>
   <si>
-    <t>当任意一瓶瓶子颜色装满时，它将解锁为一个瓶子</t>
-  </si>
-  <si>
-    <t>Fill 1 bottle with any single color to turn the milk tea into a botle</t>
-  </si>
-  <si>
-    <t>Fülle 1 Flasche mit einer Farbe zum Freischalten</t>
-  </si>
-  <si>
-    <t>単色でボトルを満たすとアンロック</t>
-  </si>
-  <si>
-    <t>Encha 1 garrafa com uma cor para desbloquear</t>
-  </si>
-  <si>
-    <t>Remplissez 1 bouteille d'une couleur pour la déverrouiller</t>
-  </si>
-  <si>
-    <t>Llena 1 botella con un color para desbloquearla</t>
-  </si>
-  <si>
-    <t>단색으로 병 채우면 잠금 해제</t>
-  </si>
-  <si>
-    <t>Isi 1 botol dengan satu warna untuk membuka</t>
-  </si>
-  <si>
-    <t>Заполните бутылку одним цветом для разблокировки</t>
-  </si>
-  <si>
-    <t>1 बोतल को एक रंग से भरें ताकि अनलॉक हो</t>
-  </si>
-  <si>
-    <t>เติมขวดด้วยสีเดียวเพื่อปลดล็อก</t>
-  </si>
-  <si>
-    <t>1 şişeyi tek renkle doldurarak kilidini aç</t>
+    <t>装满任意颜色的瓶子将解除彩虹色的包装</t>
+  </si>
+  <si>
+    <t>Fill 1 bottle with any single color to release the rainbow colored packaging</t>
+  </si>
+  <si>
+    <t>Fülle Flasche mit beliebiger Farbe, um Regenbogen-Verpackung freizuschalten</t>
+  </si>
+  <si>
+    <t>任意の色でボトル満タンで虹色パッケージ解除</t>
+  </si>
+  <si>
+    <t>Encha garrafa com qualquer cor para liberar embalagem arco-íris</t>
+  </si>
+  <si>
+    <t>Remplissez bouteille d'une couleur pour déverrouiller emballage arc-en-ciel</t>
+  </si>
+  <si>
+    <t>Llena botella con cualquier color para liberar empaque arcoíris</t>
+  </si>
+  <si>
+    <t>아무 색으로 병 채우면 무지개 포장 해제</t>
+  </si>
+  <si>
+    <t>Isi botol dengan warna apa saja untuk buka kemasan pelangi</t>
+  </si>
+  <si>
+    <t>Наполните бутылку любым цветом, чтобы разблокировать радужную упаковку</t>
+  </si>
+  <si>
+    <t>किसी भी रंग से बोतल भरें, इंद्रधनुष पैकेजिंग खुलेगी</t>
+  </si>
+  <si>
+    <t>เติมขวดด้วยสีใดก็ได้ ปลดล็อกบรรจุุสีรุ้ง</t>
+  </si>
+  <si>
+    <t>Şişeyi herhangi renkle doldur, gökkuşağı ambalajını aç</t>
   </si>
   <si>
     <t>倒出顶层，露出未知的颜色</t>
@@ -5514,6 +5514,45 @@
   <si>
     <t>{0} dakika</t>
   </si>
+  <si>
+    <t>装满蓝色的瓶子将解除彩虹色的包装</t>
+  </si>
+  <si>
+    <t>Fill 1 bottle with blue color to release the rainbow colored packaging</t>
+  </si>
+  <si>
+    <t>Fülle Flasche mit blauer Farbe, um Regenbogen-Verpackung freizuschalten</t>
+  </si>
+  <si>
+    <t>青色でボトル満タンで虹色パッケージ解除</t>
+  </si>
+  <si>
+    <t>Encha garrafa com cor azul para liberar embalagem arco-íris</t>
+  </si>
+  <si>
+    <t>Remplissez bouteille de bleu pour déverrouiller emballage arc-en-ciel</t>
+  </si>
+  <si>
+    <t>Llena botella con color azul para liberar empaque arcoíris</t>
+  </si>
+  <si>
+    <t>파란색으로 병 채우면 무지개 포장 해제</t>
+  </si>
+  <si>
+    <t>Isi botol dengan warna biru untuk buka kemasan pelangi</t>
+  </si>
+  <si>
+    <t>Наполните бутылку синим цветом, чтобы разблокировать радужную упаковку</t>
+  </si>
+  <si>
+    <t>नीले रंग से बोतल भरें, इंद्रधनुष पैकेजिंग खुलेगी</t>
+  </si>
+  <si>
+    <t>เติมขวดด้วยสีน้ำเงิน ปลดล็อกบรรจุุสีรุ้ง</t>
+  </si>
+  <si>
+    <t>Şişeyi mavi renkle doldur, gökkuşağı ambalajını aç</t>
+  </si>
 </sst>
 </file>
 
@@ -5525,7 +5564,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5568,6 +5607,12 @@
       <sz val="11.25"/>
       <color rgb="FF0F1115"/>
       <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -5914,7 +5959,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -5934,6 +5979,21 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
       </bottom>
       <diagonal/>
     </border>
@@ -6055,16 +6115,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -6073,119 +6130,122 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6242,6 +6302,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -6776,7 +6839,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W131"/>
+  <dimension ref="A1:W132"/>
   <sheetFormatPr defaultColWidth="9.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.875" customWidth="1"/>
@@ -12512,40 +12575,43 @@
       <c r="C127" t="s">
         <v>1558</v>
       </c>
-      <c r="D127" s="12" t="s">
+      <c r="D127" s="21" t="s">
         <v>1559</v>
       </c>
-      <c r="E127" s="11" t="s">
+      <c r="E127" s="21" t="s">
         <v>1560</v>
       </c>
-      <c r="F127" s="11" t="s">
+      <c r="F127" s="21" t="s">
         <v>1561</v>
       </c>
-      <c r="G127" s="11" t="s">
+      <c r="G127" s="21" t="s">
         <v>1562</v>
       </c>
-      <c r="H127" s="11" t="s">
+      <c r="H127" s="21" t="s">
         <v>1563</v>
       </c>
-      <c r="I127" s="11" t="s">
+      <c r="I127" s="21" t="s">
         <v>1564</v>
       </c>
-      <c r="J127" s="11" t="s">
+      <c r="J127" s="21" t="s">
         <v>1565</v>
       </c>
-      <c r="K127" s="11" t="s">
+      <c r="K127" s="21" t="s">
         <v>1566</v>
       </c>
-      <c r="L127" s="11" t="s">
+      <c r="L127" s="21" t="s">
         <v>1567</v>
       </c>
-      <c r="M127" s="11" t="s">
+      <c r="M127" s="21" t="s">
         <v>1568</v>
       </c>
-      <c r="N127" s="11" t="s">
+      <c r="N127" s="21" t="s">
         <v>1569</v>
       </c>
-      <c r="O127" s="11" t="s">
+      <c r="O127" s="21" t="s">
+        <v>1570</v>
+      </c>
+      <c r="P127" s="21" t="s">
         <v>1570</v>
       </c>
     </row>
@@ -12723,6 +12789,50 @@
       </c>
       <c r="O131" t="s">
         <v>1620</v>
+      </c>
+    </row>
+    <row r="132" customFormat="1" customHeight="1" spans="2:15">
+      <c r="B132" s="3">
+        <v>10127</v>
+      </c>
+      <c r="C132" t="s">
+        <v>1621</v>
+      </c>
+      <c r="D132" s="12" t="s">
+        <v>1622</v>
+      </c>
+      <c r="E132" s="21" t="s">
+        <v>1623</v>
+      </c>
+      <c r="F132" s="21" t="s">
+        <v>1624</v>
+      </c>
+      <c r="G132" s="21" t="s">
+        <v>1625</v>
+      </c>
+      <c r="H132" s="21" t="s">
+        <v>1626</v>
+      </c>
+      <c r="I132" s="21" t="s">
+        <v>1627</v>
+      </c>
+      <c r="J132" s="21" t="s">
+        <v>1628</v>
+      </c>
+      <c r="K132" s="21" t="s">
+        <v>1629</v>
+      </c>
+      <c r="L132" s="21" t="s">
+        <v>1630</v>
+      </c>
+      <c r="M132" s="21" t="s">
+        <v>1631</v>
+      </c>
+      <c r="N132" s="21" t="s">
+        <v>1632</v>
+      </c>
+      <c r="O132" s="21" t="s">
+        <v>1633</v>
       </c>
     </row>
   </sheetData>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1747" uniqueCount="1634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="1647">
   <si>
     <t>##var</t>
   </si>
@@ -5552,6 +5552,58 @@
   </si>
   <si>
     <t>Şişeyi mavi renkle doldur, gökkuşağı ambalajını aç</t>
+  </si>
+  <si>
+    <t>观看完整视频
+领取现金奖励</t>
+  </si>
+  <si>
+    <t>Watch full video
+Claim Cash Reward</t>
+  </si>
+  <si>
+    <t>Gesamtes Video ansehen
+Bargeldprämie erhalten</t>
+  </si>
+  <si>
+    <t>動画を最後まで視聴
+現金報酬を受け取る</t>
+  </si>
+  <si>
+    <t>Assistir ao vídeo completo
+Resgatar recompensa em dinheiro</t>
+  </si>
+  <si>
+    <t>Regarder la vidéo en entier
+Réclamer la récompense en argent</t>
+  </si>
+  <si>
+    <t>Ver el video completo
+Reclamar recompensa en efectivo</t>
+  </si>
+  <si>
+    <t>전체 영상 시청
+현금 보상 받기</t>
+  </si>
+  <si>
+    <t>Tonton video lengkap
+Klaim hadiah uang tunai</t>
+  </si>
+  <si>
+    <t>Посмотреть видео до конца
+Получить денежную награду</t>
+  </si>
+  <si>
+    <t>पूरा वीडियो देखें
+नकद इनाम प्राप्त करें</t>
+  </si>
+  <si>
+    <t>ดูวิดีโอจนจบ
+รับรางวัลเงินสด</t>
+  </si>
+  <si>
+    <t>Videoyu sonuna kadar izle
+Nakit ödülü al</t>
   </si>
 </sst>
 </file>
@@ -6839,7 +6891,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W132"/>
+  <dimension ref="A1:W133"/>
   <sheetFormatPr defaultColWidth="9.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.875" customWidth="1"/>
@@ -12659,7 +12711,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="129" customHeight="1" spans="2:15">
+    <row r="129" customHeight="1" spans="1:16">
       <c r="B129" s="3">
         <v>10124</v>
       </c>
@@ -12703,7 +12755,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="130" customHeight="1" spans="2:15">
+    <row r="130" customHeight="1" spans="1:16">
       <c r="B130" s="3">
         <v>10125</v>
       </c>
@@ -12747,7 +12799,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="131" customHeight="1" spans="2:15">
+    <row r="131" customHeight="1" spans="1:16">
       <c r="B131" s="3">
         <v>10126</v>
       </c>
@@ -12791,7 +12843,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="132" customFormat="1" customHeight="1" spans="2:15">
+    <row r="132" customFormat="1" customHeight="1" spans="1:16">
       <c r="B132" s="3">
         <v>10127</v>
       </c>
@@ -12833,6 +12885,56 @@
       </c>
       <c r="O132" s="21" t="s">
         <v>1633</v>
+      </c>
+    </row>
+    <row r="133" s="2" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A133" s="2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B133" s="3">
+        <v>10128</v>
+      </c>
+      <c r="C133" s="20" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D133" s="20" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E133" s="20" t="s">
+        <v>1636</v>
+      </c>
+      <c r="F133" s="20" t="s">
+        <v>1637</v>
+      </c>
+      <c r="G133" s="20" t="s">
+        <v>1638</v>
+      </c>
+      <c r="H133" s="20" t="s">
+        <v>1639</v>
+      </c>
+      <c r="I133" s="20" t="s">
+        <v>1640</v>
+      </c>
+      <c r="J133" s="20" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K133" s="20" t="s">
+        <v>1642</v>
+      </c>
+      <c r="L133" s="2" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M133" s="20" t="s">
+        <v>1644</v>
+      </c>
+      <c r="N133" s="20" t="s">
+        <v>1645</v>
+      </c>
+      <c r="O133" s="20" t="s">
+        <v>1646</v>
+      </c>
+      <c r="P133" s="2" t="s">
+        <v>1251</v>
       </c>
     </row>
   </sheetData>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1747" uniqueCount="1634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="1651">
   <si>
     <t>##var</t>
   </si>
@@ -524,6 +524,9 @@
     <t>Nakde Dönüştür</t>
   </si>
   <si>
+    <t>通过&lt;color=#FF0300&gt;此关&lt;/color&gt;即可提取所有现金</t>
+  </si>
+  <si>
     <t>Pass &lt;color=#FF0300&gt;this Level&lt;/color&gt; withdraw all cash</t>
   </si>
   <si>
@@ -560,6 +563,9 @@
     <t>Tüm parayı çekmek için &lt;color=#FF0300&gt;bu seviyeyi&lt;/color&gt; geçin</t>
   </si>
   <si>
+    <t>通过&lt;color=#FF0300&gt;关卡{0}&lt;/color&gt;即可提取所有现金</t>
+  </si>
+  <si>
     <t>Pass &lt;color=#FF0300&gt;Level {0}&lt;/color&gt; withdraw all cash</t>
   </si>
   <si>
@@ -632,6 +638,9 @@
     <t>Tüm parayı çekmek için &lt;color=#FF0300&gt;{0}&lt;/color&gt; daha kazan</t>
   </si>
   <si>
+    <t>再通过&lt;color=#FF0300&gt;{0}&lt;/color&gt;个关卡即可完成当日签到</t>
+  </si>
+  <si>
     <t>Pass &lt;color=#FF0300&gt;{0}&lt;/color&gt; more levels to daily Check-in</t>
   </si>
   <si>
@@ -666,6 +675,9 @@
   </si>
   <si>
     <t>Günlük check-in'i tamamlamak için &lt;color=#FF0300&gt;{0}&lt;/color&gt; seviye daha geç</t>
+  </si>
+  <si>
+    <t>当日签到&lt;color=#FF0300&gt;已完成&lt;/color&gt;</t>
   </si>
   <si>
     <t>Daily check-in &lt;color=#FF0300&gt;completed&lt;/color&gt;</t>
@@ -5552,6 +5564,45 @@
   </si>
   <si>
     <t>Şişeyi mavi renkle doldur, gökkuşağı ambalajını aç</t>
+  </si>
+  <si>
+    <t>签到完成，点击提现</t>
+  </si>
+  <si>
+    <t>Check-in completed, click to withdraw</t>
+  </si>
+  <si>
+    <t>Check-in abgeschlossen, zum Auszahlen tippen</t>
+  </si>
+  <si>
+    <t>チェックイン完了、出金タップ</t>
+  </si>
+  <si>
+    <t>Check-in concluído, toque para sacar</t>
+  </si>
+  <si>
+    <t>Check-in terminé, touchez pour retirer</t>
+  </si>
+  <si>
+    <t>Check-in completado, toque para retirar</t>
+  </si>
+  <si>
+    <t>체크인 완료, 출금 탭</t>
+  </si>
+  <si>
+    <t>Check-in selesai, tap untuk tarik</t>
+  </si>
+  <si>
+    <t>Чек-ин завершен, нажмите для вывода</t>
+  </si>
+  <si>
+    <t>चेक-इन पूरा, निकालने के लिए टैप करें</t>
+  </si>
+  <si>
+    <t>เช็คอินเสร็จ, แตะเพื่อถอนเงิน</t>
+  </si>
+  <si>
+    <t>Check-in tamamlandı, çekmek için dokunun</t>
   </si>
 </sst>
 </file>
@@ -6839,7 +6890,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W132"/>
+  <dimension ref="A1:W133"/>
   <sheetFormatPr defaultColWidth="9.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.875" customWidth="1"/>
@@ -7517,43 +7568,43 @@
         <v>10011</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>74</v>
+        <v>165</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O16" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:23">
@@ -7561,43 +7612,43 @@
         <v>10012</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>87</v>
+        <v>178</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="O17" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:23">
@@ -7608,40 +7659,40 @@
         <v>100</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O18" s="11" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:23">
@@ -7649,43 +7700,43 @@
         <v>10014</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>113</v>
+        <v>203</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N19" s="11" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="O19" s="11" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:23">
@@ -7693,43 +7744,43 @@
         <v>10015</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>126</v>
+        <v>216</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="M20" s="11" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="N20" s="11" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="O20" s="11" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:23">
@@ -7737,43 +7788,43 @@
         <v>10016</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I21" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="K21" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="J21" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="K21" s="11" t="s">
-        <v>226</v>
-      </c>
       <c r="L21" s="11" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="M21" s="11" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="N21" s="11" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="O21" s="11" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:23">
@@ -7781,43 +7832,43 @@
         <v>10017</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="M22" s="11" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="N22" s="11" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:23">
@@ -7825,43 +7876,43 @@
         <v>10018</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="G23" s="11" t="s">
         <v>156</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="N23" s="11" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="O23" s="11" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="2:23">
@@ -7869,43 +7920,43 @@
         <v>10019</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="N24" s="11" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O24" s="11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="2:23">
@@ -7913,43 +7964,43 @@
         <v>10020</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="N25" s="11" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="O25" s="11" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:23">
@@ -7957,43 +8008,43 @@
         <v>10021</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="M26" s="11" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="N26" s="11" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="O26" s="11" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:23">
@@ -8001,43 +8052,43 @@
         <v>10022</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="L27" s="11" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="M27" s="11" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="N27" s="11" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="O27" s="11" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28" customFormat="1" customHeight="1" spans="2:23">
@@ -8045,43 +8096,43 @@
         <v>10023</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="M28" s="11" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="N28" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="O28" s="11" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="29" customFormat="1" customHeight="1" spans="2:23">
@@ -8089,43 +8140,43 @@
         <v>10024</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="L29" s="11" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="M29" s="11" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="N29" s="11" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="O29" s="11" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
@@ -8143,40 +8194,40 @@
         <v>152</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="M30" s="11" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="N30" s="11" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="O30" s="11" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
@@ -8192,43 +8243,43 @@
         <v>10026</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="M31" s="11" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="N31" s="11" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="O31" s="11" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="P31"/>
       <c r="Q31" s="1"/>
@@ -8244,43 +8295,43 @@
         <v>10027</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="M32" s="11" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="N32" s="14" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="O32" s="11" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="P32"/>
     </row>
@@ -8289,43 +8340,43 @@
         <v>10028</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="J33" s="13" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="M33" s="11" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="N33" s="14" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="O33" s="15" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
@@ -8333,43 +8384,43 @@
         <v>10029</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="L34" s="11" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="M34" s="11" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="N34" s="14" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="O34" s="11" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="Q34"/>
       <c r="R34"/>
@@ -8384,43 +8435,43 @@
         <v>10030</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L35" s="11" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="M35" s="11" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="N35" s="14" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="O35" s="11" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="P35"/>
       <c r="Q35"/>
@@ -8436,43 +8487,43 @@
         <v>10031</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K36" s="11" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="L36" s="11" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="M36" s="11" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="N36" s="14" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="O36" s="15" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="P36"/>
       <c r="Q36"/>
@@ -8488,43 +8539,43 @@
         <v>10032</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="L37" s="11" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="M37" s="11" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="N37" s="14" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="O37" s="11" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
@@ -8539,43 +8590,43 @@
         <v>10033</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="K38" s="11" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="L38" s="11" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="M38" s="11" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="N38" s="11" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="O38" s="11" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
@@ -8591,43 +8642,43 @@
         <v>10034</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="K39" s="11" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="L39" s="11" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="M39" s="11" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="N39" s="11" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="O39" s="11" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" ht="20" customHeight="1" spans="2:23">
@@ -8635,43 +8686,43 @@
         <v>10035</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="L40" s="11" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="M40" s="11" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="N40" s="11" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="O40" s="11" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="P40"/>
       <c r="Q40"/>
@@ -8687,43 +8738,43 @@
         <v>10036</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="L41" s="11" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="M41" s="11" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="N41" s="11" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="O41" s="11" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="P41"/>
       <c r="Q41"/>
@@ -8739,43 +8790,43 @@
         <v>10037</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="K42" s="11" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L42" s="11" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="M42" s="11" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="N42" s="11" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="O42" s="11" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="P42" s="1"/>
     </row>
@@ -8784,43 +8835,43 @@
         <v>10038</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="K43" s="11" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="L43" s="11" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="M43" s="11" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="N43" s="11" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="O43" s="11" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:23">
@@ -8828,43 +8879,43 @@
         <v>10039</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="K44" s="11" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="L44" s="11" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="M44" s="11" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="N44" s="11" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="O44" s="11" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:23">
@@ -8872,46 +8923,46 @@
         <v>10040</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="K45" s="11" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="L45" s="11" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="M45" s="11" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="N45" s="11" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="O45" s="11" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="P45" s="16" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:23">
@@ -8919,46 +8970,46 @@
         <v>10041</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="K46" s="11" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="L46" s="11" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="M46" s="11" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="N46" s="11" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="O46" s="11" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="P46" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="2:23">
@@ -8966,43 +9017,43 @@
         <v>10042</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="K47" s="11" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="L47" s="11" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="M47" s="11" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="N47" s="11" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="O47" s="11" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="2:23">
@@ -9010,43 +9061,43 @@
         <v>10043</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="K48" s="11" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="L48" s="11" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="M48" s="11" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="N48" s="11" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="O48" s="11" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="2:16">
@@ -9054,43 +9105,43 @@
         <v>10044</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="K49" s="11" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="L49" s="11" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="M49" s="11" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="N49" s="11" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="O49" s="11" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="2:16">
@@ -9098,43 +9149,43 @@
         <v>10045</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="K50" s="11" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="L50" s="11" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="M50" s="11" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="N50" s="11" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="O50" s="11" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="2:16">
@@ -9142,43 +9193,43 @@
         <v>10046</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="K51" s="11" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="L51" s="11" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="M51" s="11" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="N51" s="11" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="O51" s="11" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="2:16">
@@ -9186,43 +9237,43 @@
         <v>10047</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="K52" s="11" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="L52" s="11" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="M52" s="11" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="N52" s="11" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="O52" s="11" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="2:16">
@@ -9230,43 +9281,43 @@
         <v>10048</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="K53" s="11" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="L53" s="11" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="M53" s="11" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="N53" s="11" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="O53" s="11" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="2:16">
@@ -9274,43 +9325,43 @@
         <v>10049</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="K54" s="11" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="L54" s="11" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="M54" s="11" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="N54" s="11" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="O54" s="11" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="2:16">
@@ -9318,43 +9369,43 @@
         <v>10050</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="K55" s="11" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="L55" s="11" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="M55" s="11" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="N55" s="11" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="O55" s="11" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" ht="19" customHeight="1" spans="2:16">
@@ -9362,43 +9413,43 @@
         <v>10051</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="K56" s="11" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="L56" s="11" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="M56" s="11" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="N56" s="11" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="O56" s="11" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="P56"/>
     </row>
@@ -9407,43 +9458,43 @@
         <v>10052</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="K57" s="11" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="L57" s="11" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="M57" s="11" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="N57" s="11" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="O57" s="11" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="P57" s="1"/>
     </row>
@@ -9452,43 +9503,43 @@
         <v>10053</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="K58" s="11" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="L58" s="11" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="M58" s="11" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="N58" s="11" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="O58" s="11" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:16">
@@ -9496,43 +9547,43 @@
         <v>10054</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="K59" s="11" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="L59" s="11" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="M59" s="11" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="N59" s="11" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="O59" s="11" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:16">
@@ -9540,43 +9591,43 @@
         <v>10055</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="K60" s="11" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="L60" s="11" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="M60" s="11" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="N60" s="11" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="O60" s="11" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:16">
@@ -9584,43 +9635,43 @@
         <v>10056</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="K61" s="11" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="L61" s="11" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="M61" s="11" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="N61" s="11" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="O61" s="11" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:16">
@@ -9628,43 +9679,43 @@
         <v>10057</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="K62" s="11" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="L62" s="11" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="M62" s="11" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="N62" s="11" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="O62" s="11" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:16">
@@ -9672,43 +9723,43 @@
         <v>10058</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="G63" s="11" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="K63" s="11" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="L63" s="11" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="M63" s="11" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="N63" s="11" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="O63" s="11" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:16">
@@ -9716,43 +9767,43 @@
         <v>10059</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="G64" s="11" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="K64" s="11" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="L64" s="11" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="M64" s="11" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="N64" s="11" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="O64" s="11" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="2:15">
@@ -9760,43 +9811,43 @@
         <v>10060</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="H65" s="11" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="K65" s="11" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L65" s="11" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="M65" s="11" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="N65" s="11" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="O65" s="11" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="2:15">
@@ -9804,43 +9855,43 @@
         <v>10061</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="G66" s="11" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="K66" s="11" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="L66" s="11" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="M66" s="11" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="N66" s="11" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="O66" s="11" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="2:15">
@@ -9848,43 +9899,43 @@
         <v>10062</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="G67" s="11" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="H67" s="11" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="K67" s="11" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="L67" s="11" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="M67" s="11" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="N67" s="11" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="O67" s="11" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="2:15">
@@ -9892,43 +9943,43 @@
         <v>10063</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="K68" s="11" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="L68" s="11" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="M68" s="11" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="N68" s="11" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="O68" s="11" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="2:15">
@@ -9936,43 +9987,43 @@
         <v>10064</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="K69" s="11" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="L69" s="11" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="M69" s="11" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="N69" s="11" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="O69" s="11" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
     </row>
     <row r="70" ht="19" customHeight="1" spans="2:15">
@@ -9980,43 +10031,43 @@
         <v>10065</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="G70" s="11" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="K70" s="11" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="L70" s="11" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="M70" s="11" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="N70" s="11" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="O70" s="11" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="2:15">
@@ -10024,43 +10075,43 @@
         <v>10066</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="G71" s="11" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="H71" s="11" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="K71" s="11" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="L71" s="11" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="M71" s="11" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="N71" s="11" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="O71" s="11" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="2:15">
@@ -10068,43 +10119,43 @@
         <v>10067</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="G72" s="11" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="K72" s="11" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="L72" s="11" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="M72" s="11" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="N72" s="11" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="O72" s="11" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="2:15">
@@ -10112,43 +10163,43 @@
         <v>10068</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="K73" s="11" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="L73" s="11" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="M73" s="11" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="N73" s="11" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="O73" s="11" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="2:15">
@@ -10156,43 +10207,43 @@
         <v>10069</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="G74" s="11" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="H74" s="11" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="K74" s="11" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="L74" s="11" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="M74" s="11" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="N74" s="11" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="O74" s="11" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="2:15">
@@ -10200,43 +10251,43 @@
         <v>10070</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="G75" s="11" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="I75" s="11" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="J75" s="11" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="K75" s="11" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="L75" s="11" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="M75" s="11" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="N75" s="11" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="O75" s="11" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="2:15">
@@ -10244,43 +10295,43 @@
         <v>10071</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="G76" s="11" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="I76" s="11" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="J76" s="11" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="K76" s="11" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="L76" s="11" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="M76" s="11" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="N76" s="11" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="O76" s="11" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="2:15">
@@ -10288,43 +10339,43 @@
         <v>10072</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="G77" s="11" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="H77" s="11" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="I77" s="11" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="J77" s="11" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="K77" s="11" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="L77" s="11" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="M77" s="11" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="N77" s="11" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="O77" s="11" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="2:15">
@@ -10332,43 +10383,43 @@
         <v>10073</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="E78" s="11" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="G78" s="11" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="H78" s="11" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="I78" s="11" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="J78" s="11" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="K78" s="11" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="L78" s="11" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="M78" s="11" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="N78" s="11" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="O78" s="11" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
     </row>
     <row r="79" ht="19" customHeight="1" spans="2:15">
@@ -10376,43 +10427,43 @@
         <v>10074</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="E79" s="11" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="G79" s="11" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="H79" s="11" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="I79" s="11" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="J79" s="11" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="K79" s="11" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="L79" s="11" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="M79" s="11" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="N79" s="11" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="O79" s="11" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="2:15">
@@ -10420,43 +10471,43 @@
         <v>10075</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="G80" s="11" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="H80" s="11" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="I80" s="11" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="J80" s="11" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="K80" s="11" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="L80" s="11" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="M80" s="11" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="N80" s="11" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="O80" s="11" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="2:15">
@@ -10464,43 +10515,43 @@
         <v>10076</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="E81" s="11" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="H81" s="11" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="I81" s="11" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="J81" s="11" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="K81" s="11" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="L81" s="11" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="M81" s="11" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="N81" s="11" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="O81" s="11" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="2:15">
@@ -10508,43 +10559,43 @@
         <v>10077</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="G82" s="11" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="H82" s="11" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="I82" s="11" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="J82" s="11" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="K82" s="11" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="L82" s="11" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="M82" s="11" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="N82" s="11" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="O82" s="11" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="2:15">
@@ -10552,43 +10603,43 @@
         <v>10078</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="E83" s="11" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="G83" s="11" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="H83" s="11" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="I83" s="11" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="J83" s="11" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="K83" s="11" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="L83" s="11" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="M83" s="11" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="N83" s="11" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="O83" s="11" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="2:15">
@@ -10596,43 +10647,43 @@
         <v>10079</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="E84" s="11" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="G84" s="11" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="H84" s="11" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="I84" s="11" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="J84" s="11" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="K84" s="11" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="L84" s="11" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="M84" s="11" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="N84" s="11" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="O84" s="11" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="2:15">
@@ -10640,43 +10691,43 @@
         <v>10080</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="E85" s="11" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="G85" s="11" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="H85" s="11" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="I85" s="11" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="J85" s="11" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="K85" s="11" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="L85" s="11" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="M85" s="11" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="N85" s="11" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="O85" s="11" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="2:15">
@@ -10684,43 +10735,43 @@
         <v>10081</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="E86" s="11" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="G86" s="11" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="H86" s="11" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="I86" s="11" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="J86" s="11" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="K86" s="11" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="L86" s="11" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="M86" s="11" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="N86" s="11" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="O86" s="11" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="2:15">
@@ -10728,43 +10779,43 @@
         <v>10082</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="E87" s="11" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="F87" s="11" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="G87" s="11" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="H87" s="11" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="I87" s="11" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="J87" s="11" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="K87" s="11" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="L87" s="11" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="M87" s="11" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="N87" s="11" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="O87" s="11" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="2:15">
@@ -10772,43 +10823,43 @@
         <v>10083</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="F88" s="11" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="G88" s="11" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="H88" s="11" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="I88" s="11" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="J88" s="11" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="K88" s="11" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="L88" s="11" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="M88" s="11" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="N88" s="11" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="O88" s="11" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="2:15">
@@ -10816,43 +10867,43 @@
         <v>10084</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="E89" s="11" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="F89" s="11" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="G89" s="11" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="H89" s="11" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="I89" s="11" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="J89" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="K89" s="11" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="L89" s="11" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="M89" s="11" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="N89" s="11" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="O89" s="11" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="2:15">
@@ -10860,43 +10911,43 @@
         <v>10085</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="E90" s="11" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="G90" s="11" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="I90" s="11" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="J90" s="11" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="K90" s="11" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="L90" s="11" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="M90" s="11" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="N90" s="11" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="O90" s="11" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="2:15">
@@ -10904,43 +10955,43 @@
         <v>10086</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="E91" s="11" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="F91" s="11" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="G91" s="11" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="H91" s="11" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="I91" s="11" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="J91" s="11" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="K91" s="11" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="L91" s="11" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="M91" s="11" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="N91" s="11" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="O91" s="11" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="2:15">
@@ -10948,43 +10999,43 @@
         <v>10087</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="E92" s="11" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="G92" s="11" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="H92" s="11" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="I92" s="11" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="J92" s="11" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="K92" s="11" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="L92" s="11" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="M92" s="11" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="N92" s="11" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="O92" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="2:15">
@@ -10992,43 +11043,43 @@
         <v>10088</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="E93" s="11" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="F93" s="11" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="G93" s="11" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="H93" s="11" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="I93" s="11" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="J93" s="11" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="K93" s="11" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="L93" s="11" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="M93" s="11" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="N93" s="11" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="O93" s="11" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="2:15">
@@ -11036,43 +11087,43 @@
         <v>10089</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="E94" s="11" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="G94" s="11" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
       <c r="H94" s="11" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="I94" s="11" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="J94" s="11" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="K94" s="11" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="L94" s="11" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="M94" s="11" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="N94" s="11" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="O94" s="11" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="2:15">
@@ -11080,43 +11131,43 @@
         <v>10090</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="E95" s="11" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="F95" s="11" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="G95" s="11" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="H95" s="11" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="I95" s="11" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="J95" s="11" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="K95" s="11" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="L95" s="11" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="M95" s="11" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="N95" s="11" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="O95" s="11" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="2:15">
@@ -11124,43 +11175,43 @@
         <v>10091</v>
       </c>
       <c r="C96" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="E96" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="F96" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
       <c r="G96" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="H96" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="I96" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
       <c r="J96" t="s">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="K96" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
       <c r="L96" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="M96" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="N96" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="O96" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="1:16">
@@ -11168,43 +11219,43 @@
         <v>10092</v>
       </c>
       <c r="C97" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="E97" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
       <c r="F97" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="G97" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
       <c r="H97" t="s">
-        <v>1178</v>
+        <v>1182</v>
       </c>
       <c r="I97" t="s">
-        <v>1179</v>
+        <v>1183</v>
       </c>
       <c r="J97" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
       <c r="K97" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="L97" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="M97" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="N97" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="O97" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="1:16">
@@ -11212,43 +11263,43 @@
         <v>10093</v>
       </c>
       <c r="C98" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
       <c r="E98" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
       <c r="F98" s="17" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="G98" s="17" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="H98" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="I98" s="17" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="J98" s="17" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="K98" s="17" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="L98" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="M98" s="17" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="N98" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
       <c r="O98" t="s">
-        <v>1198</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="1:16">
@@ -11256,43 +11307,43 @@
         <v>10094</v>
       </c>
       <c r="C99" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="E99" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
       <c r="F99" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="G99" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
       <c r="H99" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="I99" s="17" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="J99" s="17" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
       <c r="K99" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
       <c r="L99" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="M99" s="17" t="s">
-        <v>1209</v>
+        <v>1213</v>
       </c>
       <c r="N99" s="17" t="s">
-        <v>1210</v>
+        <v>1214</v>
       </c>
       <c r="O99" s="17" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="1:16">
@@ -11300,43 +11351,43 @@
         <v>10095</v>
       </c>
       <c r="C100" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="E100" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="F100" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="G100" t="s">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="H100" t="s">
-        <v>1217</v>
+        <v>1221</v>
       </c>
       <c r="I100" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="J100" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
       <c r="K100" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="L100" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="M100" s="17" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
       <c r="N100" s="17" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="O100" s="17" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="1:16">
@@ -11344,43 +11395,43 @@
         <v>10096</v>
       </c>
       <c r="C101" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="E101" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="F101" s="17" t="s">
-        <v>1228</v>
+        <v>1232</v>
       </c>
       <c r="G101" s="17" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="H101" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="I101" s="17" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="J101" s="17" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="K101" s="17" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="L101" s="17" t="s">
-        <v>1234</v>
+        <v>1238</v>
       </c>
       <c r="M101" s="17" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="N101" s="17" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="O101" t="s">
-        <v>1237</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="1:16">
@@ -11388,93 +11439,93 @@
         <v>10097</v>
       </c>
       <c r="C102" t="s">
-        <v>1238</v>
+        <v>1242</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="E102" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="F102" s="18" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="G102" s="18" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="H102" t="s">
-        <v>1243</v>
+        <v>1247</v>
       </c>
       <c r="I102" s="17" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="J102" s="17" t="s">
-        <v>1245</v>
+        <v>1249</v>
       </c>
       <c r="K102" s="17" t="s">
-        <v>1246</v>
+        <v>1250</v>
       </c>
       <c r="L102" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="M102" s="17" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="N102" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
       <c r="O102" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="103" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A103" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="B103" s="3">
         <v>10098</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="F103" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="J103" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="K103" s="2" t="s">
+        <v>1264</v>
+      </c>
+      <c r="L103" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="M103" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="N103" s="2" t="s">
+        <v>1267</v>
+      </c>
+      <c r="O103" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="P103" s="2" t="s">
         <v>1255</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>1256</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>1257</v>
-      </c>
-      <c r="I103" s="2" t="s">
-        <v>1258</v>
-      </c>
-      <c r="J103" s="2" t="s">
-        <v>1259</v>
-      </c>
-      <c r="K103" s="2" t="s">
-        <v>1260</v>
-      </c>
-      <c r="L103" s="2" t="s">
-        <v>1261</v>
-      </c>
-      <c r="M103" s="2" t="s">
-        <v>1262</v>
-      </c>
-      <c r="N103" s="2" t="s">
-        <v>1263</v>
-      </c>
-      <c r="O103" s="2" t="s">
-        <v>1264</v>
-      </c>
-      <c r="P103" s="2" t="s">
-        <v>1251</v>
       </c>
     </row>
     <row r="104" customFormat="1" customHeight="1" spans="1:16">
@@ -11482,43 +11533,43 @@
         <v>10099</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="E104" s="11" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="F104" s="11" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="G104" s="11" t="s">
-        <v>1269</v>
+        <v>1273</v>
       </c>
       <c r="H104" s="11" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
       <c r="I104" s="11" t="s">
-        <v>1271</v>
+        <v>1275</v>
       </c>
       <c r="J104" s="11" t="s">
-        <v>1272</v>
+        <v>1276</v>
       </c>
       <c r="K104" s="11" t="s">
-        <v>1273</v>
+        <v>1277</v>
       </c>
       <c r="L104" s="11" t="s">
-        <v>1274</v>
+        <v>1278</v>
       </c>
       <c r="M104" s="11" t="s">
-        <v>1275</v>
+        <v>1279</v>
       </c>
       <c r="N104" s="14" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="O104" s="11" t="s">
-        <v>1277</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
@@ -11526,43 +11577,43 @@
         <v>10100</v>
       </c>
       <c r="C105" t="s">
-        <v>1278</v>
+        <v>1282</v>
       </c>
       <c r="D105" s="16" t="s">
         <v>153</v>
       </c>
       <c r="E105" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="F105" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="G105" s="16" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
       <c r="H105" t="s">
-        <v>1282</v>
+        <v>1286</v>
       </c>
       <c r="I105" t="s">
-        <v>1283</v>
+        <v>1287</v>
       </c>
       <c r="J105" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="K105" s="16" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="L105" t="s">
-        <v>1286</v>
+        <v>1290</v>
       </c>
       <c r="M105" s="17" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="N105" s="18" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="O105" s="17" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
       <c r="P105"/>
     </row>
@@ -11571,43 +11622,43 @@
         <v>10101</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>1291</v>
+        <v>1295</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>1298</v>
+        <v>1302</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>1299</v>
+        <v>1303</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
       <c r="O106" s="2" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="1:16">
@@ -11615,43 +11666,43 @@
         <v>10102</v>
       </c>
       <c r="C107" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="D107" s="16" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="E107" t="s">
-        <v>1305</v>
+        <v>1309</v>
       </c>
       <c r="F107" s="17" t="s">
-        <v>1306</v>
+        <v>1310</v>
       </c>
       <c r="G107" s="17" t="s">
-        <v>1307</v>
+        <v>1311</v>
       </c>
       <c r="H107" s="17" t="s">
-        <v>1308</v>
+        <v>1312</v>
       </c>
       <c r="I107" s="17" t="s">
-        <v>1309</v>
+        <v>1313</v>
       </c>
       <c r="J107" s="17" t="s">
-        <v>1310</v>
+        <v>1314</v>
       </c>
       <c r="K107" s="17" t="s">
-        <v>1311</v>
+        <v>1315</v>
       </c>
       <c r="L107" s="17" t="s">
-        <v>1312</v>
+        <v>1316</v>
       </c>
       <c r="M107" s="17" t="s">
-        <v>1313</v>
+        <v>1317</v>
       </c>
       <c r="N107" s="17" t="s">
-        <v>1314</v>
+        <v>1318</v>
       </c>
       <c r="O107" t="s">
-        <v>1315</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="1:16">
@@ -11659,43 +11710,43 @@
         <v>10103</v>
       </c>
       <c r="C108" t="s">
-        <v>1316</v>
+        <v>1320</v>
       </c>
       <c r="D108" s="16" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="E108" t="s">
-        <v>1318</v>
+        <v>1322</v>
       </c>
       <c r="F108" t="s">
-        <v>1319</v>
+        <v>1323</v>
       </c>
       <c r="G108" s="16" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
       <c r="H108" t="s">
-        <v>1321</v>
+        <v>1325</v>
       </c>
       <c r="I108" t="s">
-        <v>1322</v>
+        <v>1326</v>
       </c>
       <c r="J108" t="s">
-        <v>1323</v>
+        <v>1327</v>
       </c>
       <c r="K108" s="17" t="s">
-        <v>1324</v>
+        <v>1328</v>
       </c>
       <c r="L108" s="17" t="s">
-        <v>1325</v>
+        <v>1329</v>
       </c>
       <c r="M108" s="17" t="s">
-        <v>1326</v>
+        <v>1330</v>
       </c>
       <c r="N108" t="s">
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="O108" t="s">
-        <v>1328</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="1:16">
@@ -11703,43 +11754,43 @@
         <v>10104</v>
       </c>
       <c r="C109" t="s">
-        <v>1329</v>
+        <v>1333</v>
       </c>
       <c r="D109" s="16" t="s">
-        <v>1330</v>
+        <v>1334</v>
       </c>
       <c r="E109" t="s">
-        <v>1331</v>
+        <v>1335</v>
       </c>
       <c r="F109" t="s">
-        <v>1332</v>
+        <v>1336</v>
       </c>
       <c r="G109" s="16" t="s">
-        <v>1333</v>
+        <v>1337</v>
       </c>
       <c r="H109" t="s">
-        <v>1334</v>
+        <v>1338</v>
       </c>
       <c r="I109" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="J109" t="s">
-        <v>1336</v>
+        <v>1340</v>
       </c>
       <c r="K109" s="17" t="s">
-        <v>1337</v>
+        <v>1341</v>
       </c>
       <c r="L109" s="17" t="s">
-        <v>1338</v>
+        <v>1342</v>
       </c>
       <c r="M109" s="17" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
       <c r="N109" s="17" t="s">
-        <v>1340</v>
+        <v>1344</v>
       </c>
       <c r="O109" s="17" t="s">
-        <v>1341</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="1:16">
@@ -11747,43 +11798,43 @@
         <v>10105</v>
       </c>
       <c r="C110" t="s">
-        <v>1342</v>
+        <v>1346</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>1343</v>
+        <v>1347</v>
       </c>
       <c r="E110" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
       <c r="F110" s="17" t="s">
-        <v>1345</v>
+        <v>1349</v>
       </c>
       <c r="G110" s="17" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
       <c r="H110" s="17" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="I110" s="17" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="J110" s="17" t="s">
-        <v>1349</v>
+        <v>1353</v>
       </c>
       <c r="K110" s="17" t="s">
-        <v>1350</v>
+        <v>1354</v>
       </c>
       <c r="L110" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
       <c r="M110" s="18" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
       <c r="N110" s="18" t="s">
-        <v>1353</v>
+        <v>1357</v>
       </c>
       <c r="O110" s="18" t="s">
-        <v>1354</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="1:16">
@@ -11791,43 +11842,43 @@
         <v>10106</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>1355</v>
+        <v>1359</v>
       </c>
       <c r="D111" s="16" t="s">
-        <v>1356</v>
+        <v>1360</v>
       </c>
       <c r="E111" t="s">
-        <v>1357</v>
+        <v>1361</v>
       </c>
       <c r="F111" s="17" t="s">
-        <v>1358</v>
+        <v>1362</v>
       </c>
       <c r="G111" s="16" t="s">
-        <v>1359</v>
+        <v>1363</v>
       </c>
       <c r="H111" s="17" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="I111" s="17" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="J111" s="17" t="s">
-        <v>1362</v>
+        <v>1366</v>
       </c>
       <c r="K111" s="17" t="s">
-        <v>1363</v>
+        <v>1367</v>
       </c>
       <c r="L111" t="s">
-        <v>1364</v>
+        <v>1368</v>
       </c>
       <c r="M111" s="17" t="s">
-        <v>1365</v>
+        <v>1369</v>
       </c>
       <c r="N111" s="17" t="s">
-        <v>1366</v>
+        <v>1370</v>
       </c>
       <c r="O111" t="s">
-        <v>1367</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="1:16">
@@ -11835,693 +11886,693 @@
         <v>10107</v>
       </c>
       <c r="C112" t="s">
-        <v>1368</v>
+        <v>1372</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>1369</v>
+        <v>1373</v>
       </c>
       <c r="E112" t="s">
-        <v>1370</v>
+        <v>1374</v>
       </c>
       <c r="F112" s="17" t="s">
-        <v>1371</v>
+        <v>1375</v>
       </c>
       <c r="G112" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="H112" t="s">
-        <v>1373</v>
+        <v>1377</v>
       </c>
       <c r="I112" s="17" t="s">
-        <v>1374</v>
+        <v>1378</v>
       </c>
       <c r="J112" s="17" t="s">
-        <v>1375</v>
+        <v>1379</v>
       </c>
       <c r="K112" s="17" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="L112" t="s">
-        <v>1377</v>
+        <v>1381</v>
       </c>
       <c r="M112" s="17" t="s">
-        <v>1378</v>
+        <v>1382</v>
       </c>
       <c r="N112" t="s">
-        <v>1379</v>
+        <v>1383</v>
       </c>
       <c r="O112" t="s">
-        <v>1380</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="113" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A113" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="B113" s="3">
         <v>10108</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>1381</v>
+        <v>1385</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>1382</v>
+        <v>1386</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>1383</v>
+        <v>1387</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>1384</v>
+        <v>1388</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>1385</v>
+        <v>1389</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>1386</v>
+        <v>1390</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="L113" s="2" t="s">
-        <v>1388</v>
+        <v>1392</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>1389</v>
+        <v>1393</v>
       </c>
       <c r="N113" s="2" t="s">
-        <v>1390</v>
+        <v>1394</v>
       </c>
       <c r="O113" s="2" t="s">
-        <v>1391</v>
+        <v>1395</v>
       </c>
       <c r="P113" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="114" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A114" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="B114" s="3">
         <v>10109</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>1392</v>
+        <v>1396</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>1396</v>
+        <v>1400</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>1397</v>
+        <v>1401</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>1400</v>
+        <v>1404</v>
       </c>
       <c r="L114" s="2" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>1402</v>
+        <v>1406</v>
       </c>
       <c r="N114" s="2" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
       <c r="O114" s="2" t="s">
-        <v>1404</v>
+        <v>1408</v>
       </c>
       <c r="P114" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="115" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A115" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="B115" s="3">
         <v>10110</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
       <c r="K115" s="2" t="s">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="L115" s="2" t="s">
-        <v>1414</v>
+        <v>1418</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="N115" s="2" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
       <c r="O115" s="2" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
       <c r="P115" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="116" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A116" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="B116" s="3">
         <v>10111</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>1418</v>
+        <v>1422</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>1419</v>
+        <v>1423</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>1420</v>
+        <v>1424</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>1421</v>
+        <v>1425</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>1425</v>
+        <v>1429</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>1426</v>
+        <v>1430</v>
       </c>
       <c r="L116" s="2" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
       <c r="N116" s="2" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="O116" s="2" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="P116" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="117" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A117" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="B117" s="3">
         <v>10112</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>1431</v>
+        <v>1435</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>1432</v>
+        <v>1436</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>1435</v>
+        <v>1439</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>1436</v>
+        <v>1440</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>1437</v>
+        <v>1441</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="L117" s="2" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>1441</v>
+        <v>1445</v>
       </c>
       <c r="N117" s="2" t="s">
-        <v>1442</v>
+        <v>1446</v>
       </c>
       <c r="O117" s="2" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="P117" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="118" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A118" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="B118" s="3">
         <v>10113</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>1445</v>
+        <v>1449</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>1447</v>
+        <v>1451</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>1448</v>
+        <v>1452</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>1450</v>
+        <v>1454</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>1451</v>
+        <v>1455</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="L118" s="2" t="s">
-        <v>1453</v>
+        <v>1457</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>1454</v>
+        <v>1458</v>
       </c>
       <c r="N118" s="2" t="s">
-        <v>1455</v>
+        <v>1459</v>
       </c>
       <c r="O118" s="2" t="s">
-        <v>1456</v>
+        <v>1460</v>
       </c>
       <c r="P118" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="119" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A119" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="B119" s="3">
         <v>10114</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>1458</v>
+        <v>1462</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>1459</v>
+        <v>1463</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>1460</v>
+        <v>1464</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>1461</v>
+        <v>1465</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>1463</v>
+        <v>1467</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="L119" s="2" t="s">
-        <v>1466</v>
+        <v>1470</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="N119" s="2" t="s">
-        <v>1468</v>
+        <v>1472</v>
       </c>
       <c r="O119" s="2" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
       <c r="P119" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="120" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A120" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="B120" s="3">
         <v>10115</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>1471</v>
+        <v>1475</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>1472</v>
+        <v>1476</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>1474</v>
+        <v>1478</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>1475</v>
+        <v>1479</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>1476</v>
+        <v>1480</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>1477</v>
+        <v>1481</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="L120" s="2" t="s">
-        <v>1479</v>
+        <v>1483</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>1480</v>
+        <v>1484</v>
       </c>
       <c r="N120" s="2" t="s">
-        <v>1481</v>
+        <v>1485</v>
       </c>
       <c r="O120" s="2" t="s">
-        <v>1482</v>
+        <v>1486</v>
       </c>
       <c r="P120" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="121" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A121" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="B121" s="3">
         <v>10116</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>1483</v>
+        <v>1487</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>1484</v>
+        <v>1488</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>1485</v>
+        <v>1489</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>1486</v>
+        <v>1490</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>1487</v>
+        <v>1491</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>1488</v>
+        <v>1492</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>1489</v>
+        <v>1493</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>1490</v>
+        <v>1494</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>1491</v>
+        <v>1495</v>
       </c>
       <c r="L121" s="2" t="s">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>1493</v>
+        <v>1497</v>
       </c>
       <c r="N121" s="2" t="s">
-        <v>1494</v>
+        <v>1498</v>
       </c>
       <c r="O121" s="2" t="s">
-        <v>1495</v>
+        <v>1499</v>
       </c>
       <c r="P121" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="122" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A122" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="B122" s="3">
         <v>10117</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>1496</v>
+        <v>1500</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>1497</v>
+        <v>1501</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>1498</v>
+        <v>1502</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>1499</v>
+        <v>1503</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>1500</v>
+        <v>1504</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>1501</v>
+        <v>1505</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>1500</v>
+        <v>1504</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>1502</v>
+        <v>1506</v>
       </c>
       <c r="K122" s="2" t="s">
-        <v>1503</v>
+        <v>1507</v>
       </c>
       <c r="L122" s="2" t="s">
-        <v>1504</v>
+        <v>1508</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="N122" s="2" t="s">
-        <v>1506</v>
+        <v>1510</v>
       </c>
       <c r="O122" s="2" t="s">
-        <v>1507</v>
+        <v>1511</v>
       </c>
       <c r="P122" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="123" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A123" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="B123" s="3">
         <v>10118</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>1508</v>
+        <v>1512</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>1509</v>
+        <v>1513</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>1510</v>
+        <v>1514</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>1511</v>
+        <v>1515</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>1512</v>
+        <v>1516</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>1513</v>
+        <v>1517</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>1514</v>
+        <v>1518</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="K123" s="2" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="L123" s="2" t="s">
-        <v>1517</v>
+        <v>1521</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>1518</v>
+        <v>1522</v>
       </c>
       <c r="N123" s="2" t="s">
-        <v>1519</v>
+        <v>1523</v>
       </c>
       <c r="O123" s="2" t="s">
-        <v>1520</v>
+        <v>1524</v>
       </c>
       <c r="P123" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="124" s="2" customFormat="1" ht="13.5" spans="1:16">
       <c r="A124" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="B124" s="3">
         <v>10119</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>1522</v>
+        <v>1526</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>1523</v>
+        <v>1527</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>1524</v>
+        <v>1528</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>1525</v>
+        <v>1529</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>1526</v>
+        <v>1530</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>1527</v>
+        <v>1531</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>1528</v>
+        <v>1532</v>
       </c>
       <c r="K124" s="2" t="s">
-        <v>1529</v>
+        <v>1533</v>
       </c>
       <c r="L124" s="2" t="s">
-        <v>1530</v>
+        <v>1534</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>1531</v>
+        <v>1535</v>
       </c>
       <c r="N124" s="2" t="s">
-        <v>1532</v>
+        <v>1536</v>
       </c>
       <c r="O124" s="2" t="s">
-        <v>1533</v>
+        <v>1537</v>
       </c>
       <c r="P124" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="125" s="2" customFormat="1" ht="27" spans="1:16">
       <c r="A125" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="B125" s="3">
         <v>10120</v>
       </c>
       <c r="C125" s="20" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>1535</v>
+        <v>1539</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>1535</v>
+        <v>1539</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>1536</v>
+        <v>1540</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>1537</v>
+        <v>1541</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>1538</v>
+        <v>1542</v>
       </c>
       <c r="I125" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="J125" s="2" t="s">
+        <v>1544</v>
+      </c>
+      <c r="K125" s="2" t="s">
         <v>1539</v>
       </c>
-      <c r="J125" s="2" t="s">
-        <v>1540</v>
-      </c>
-      <c r="K125" s="2" t="s">
-        <v>1535</v>
-      </c>
       <c r="L125" s="2" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="M125" s="2" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="N125" s="2" t="s">
-        <v>1543</v>
+        <v>1547</v>
       </c>
       <c r="O125" s="2" t="s">
-        <v>1544</v>
+        <v>1548</v>
       </c>
       <c r="P125" s="2" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="126" customHeight="1" spans="1:16">
@@ -12529,43 +12580,43 @@
         <v>10121</v>
       </c>
       <c r="C126" t="s">
-        <v>1545</v>
+        <v>1549</v>
       </c>
       <c r="D126" s="12" t="s">
-        <v>1546</v>
+        <v>1550</v>
       </c>
       <c r="E126" s="11" t="s">
-        <v>1547</v>
+        <v>1551</v>
       </c>
       <c r="F126" s="11" t="s">
-        <v>1548</v>
+        <v>1552</v>
       </c>
       <c r="G126" s="11" t="s">
-        <v>1549</v>
+        <v>1553</v>
       </c>
       <c r="H126" s="11" t="s">
-        <v>1550</v>
+        <v>1554</v>
       </c>
       <c r="I126" s="11" t="s">
-        <v>1551</v>
+        <v>1555</v>
       </c>
       <c r="J126" s="11" t="s">
-        <v>1552</v>
+        <v>1556</v>
       </c>
       <c r="K126" s="11" t="s">
-        <v>1553</v>
+        <v>1557</v>
       </c>
       <c r="L126" s="11" t="s">
-        <v>1554</v>
+        <v>1558</v>
       </c>
       <c r="M126" s="11" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="N126" s="11" t="s">
-        <v>1556</v>
+        <v>1560</v>
       </c>
       <c r="O126" s="11" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="127" customHeight="1" spans="1:16">
@@ -12573,46 +12624,46 @@
         <v>10122</v>
       </c>
       <c r="C127" t="s">
-        <v>1558</v>
+        <v>1562</v>
       </c>
       <c r="D127" s="21" t="s">
-        <v>1559</v>
+        <v>1563</v>
       </c>
       <c r="E127" s="21" t="s">
-        <v>1560</v>
+        <v>1564</v>
       </c>
       <c r="F127" s="21" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="G127" s="21" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="H127" s="21" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="I127" s="21" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
       <c r="J127" s="21" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
       <c r="K127" s="21" t="s">
-        <v>1566</v>
+        <v>1570</v>
       </c>
       <c r="L127" s="21" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
       <c r="M127" s="21" t="s">
-        <v>1568</v>
+        <v>1572</v>
       </c>
       <c r="N127" s="21" t="s">
-        <v>1569</v>
+        <v>1573</v>
       </c>
       <c r="O127" s="21" t="s">
-        <v>1570</v>
+        <v>1574</v>
       </c>
       <c r="P127" s="21" t="s">
-        <v>1570</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="128" customHeight="1" spans="1:16">
@@ -12620,43 +12671,43 @@
         <v>10123</v>
       </c>
       <c r="C128" t="s">
-        <v>1571</v>
+        <v>1575</v>
       </c>
       <c r="D128" s="12" t="s">
-        <v>1572</v>
+        <v>1576</v>
       </c>
       <c r="E128" s="11" t="s">
-        <v>1573</v>
+        <v>1577</v>
       </c>
       <c r="F128" s="11" t="s">
-        <v>1574</v>
+        <v>1578</v>
       </c>
       <c r="G128" s="11" t="s">
-        <v>1575</v>
+        <v>1579</v>
       </c>
       <c r="H128" s="11" t="s">
-        <v>1576</v>
+        <v>1580</v>
       </c>
       <c r="I128" s="11" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
       <c r="J128" s="11" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="K128" s="11" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="L128" s="11" t="s">
-        <v>1580</v>
+        <v>1584</v>
       </c>
       <c r="M128" s="11" t="s">
-        <v>1581</v>
+        <v>1585</v>
       </c>
       <c r="N128" s="11" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="O128" s="11" t="s">
-        <v>1583</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="129" customHeight="1" spans="2:15">
@@ -12664,43 +12715,43 @@
         <v>10124</v>
       </c>
       <c r="C129" t="s">
-        <v>1584</v>
+        <v>1588</v>
       </c>
       <c r="D129" s="12" t="s">
-        <v>1585</v>
+        <v>1589</v>
       </c>
       <c r="E129" s="11" t="s">
-        <v>1586</v>
+        <v>1590</v>
       </c>
       <c r="F129" s="11" t="s">
-        <v>1587</v>
+        <v>1591</v>
       </c>
       <c r="G129" s="11" t="s">
-        <v>1588</v>
+        <v>1592</v>
       </c>
       <c r="H129" s="11" t="s">
-        <v>1589</v>
+        <v>1593</v>
       </c>
       <c r="I129" s="11" t="s">
-        <v>1590</v>
+        <v>1594</v>
       </c>
       <c r="J129" s="11" t="s">
-        <v>1591</v>
+        <v>1595</v>
       </c>
       <c r="K129" s="11" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
       <c r="L129" s="11" t="s">
-        <v>1593</v>
+        <v>1597</v>
       </c>
       <c r="M129" s="11" t="s">
-        <v>1594</v>
+        <v>1598</v>
       </c>
       <c r="N129" s="11" t="s">
-        <v>1595</v>
+        <v>1599</v>
       </c>
       <c r="O129" s="11" t="s">
-        <v>1596</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="130" customHeight="1" spans="2:15">
@@ -12708,43 +12759,43 @@
         <v>10125</v>
       </c>
       <c r="C130" t="s">
-        <v>1597</v>
+        <v>1601</v>
       </c>
       <c r="D130" s="12" t="s">
-        <v>1598</v>
+        <v>1602</v>
       </c>
       <c r="E130" s="11" t="s">
-        <v>1599</v>
+        <v>1603</v>
       </c>
       <c r="F130" s="11" t="s">
-        <v>1600</v>
+        <v>1604</v>
       </c>
       <c r="G130" s="11" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
       <c r="H130" s="11" t="s">
-        <v>1602</v>
+        <v>1606</v>
       </c>
       <c r="I130" s="11" t="s">
-        <v>1603</v>
+        <v>1607</v>
       </c>
       <c r="J130" s="11" t="s">
-        <v>1604</v>
+        <v>1608</v>
       </c>
       <c r="K130" s="11" t="s">
-        <v>1605</v>
+        <v>1609</v>
       </c>
       <c r="L130" s="11" t="s">
-        <v>1606</v>
+        <v>1610</v>
       </c>
       <c r="M130" s="11" t="s">
-        <v>1607</v>
+        <v>1611</v>
       </c>
       <c r="N130" s="14" t="s">
-        <v>1608</v>
+        <v>1612</v>
       </c>
       <c r="O130" s="11" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="131" customHeight="1" spans="2:15">
@@ -12752,43 +12803,43 @@
         <v>10126</v>
       </c>
       <c r="C131" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>1611</v>
+        <v>1615</v>
       </c>
       <c r="E131" t="s">
-        <v>1611</v>
+        <v>1615</v>
       </c>
       <c r="F131" t="s">
-        <v>1612</v>
+        <v>1616</v>
       </c>
       <c r="G131" t="s">
-        <v>1613</v>
+        <v>1617</v>
       </c>
       <c r="H131" t="s">
-        <v>1614</v>
+        <v>1618</v>
       </c>
       <c r="I131" t="s">
-        <v>1613</v>
+        <v>1617</v>
       </c>
       <c r="J131" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="K131" t="s">
-        <v>1616</v>
+        <v>1620</v>
       </c>
       <c r="L131" t="s">
-        <v>1617</v>
+        <v>1621</v>
       </c>
       <c r="M131" t="s">
-        <v>1618</v>
+        <v>1622</v>
       </c>
       <c r="N131" t="s">
-        <v>1619</v>
+        <v>1623</v>
       </c>
       <c r="O131" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="132" customFormat="1" customHeight="1" spans="2:15">
@@ -12796,43 +12847,87 @@
         <v>10127</v>
       </c>
       <c r="C132" t="s">
-        <v>1621</v>
+        <v>1625</v>
       </c>
       <c r="D132" s="12" t="s">
-        <v>1622</v>
+        <v>1626</v>
       </c>
       <c r="E132" s="21" t="s">
-        <v>1623</v>
+        <v>1627</v>
       </c>
       <c r="F132" s="21" t="s">
-        <v>1624</v>
+        <v>1628</v>
       </c>
       <c r="G132" s="21" t="s">
-        <v>1625</v>
+        <v>1629</v>
       </c>
       <c r="H132" s="21" t="s">
-        <v>1626</v>
+        <v>1630</v>
       </c>
       <c r="I132" s="21" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
       <c r="J132" s="21" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="K132" s="21" t="s">
-        <v>1629</v>
+        <v>1633</v>
       </c>
       <c r="L132" s="21" t="s">
-        <v>1630</v>
+        <v>1634</v>
       </c>
       <c r="M132" s="21" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="N132" s="21" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="O132" s="21" t="s">
-        <v>1633</v>
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="133" customHeight="1" spans="2:15">
+      <c r="B133" s="3">
+        <v>10128</v>
+      </c>
+      <c r="C133" t="s">
+        <v>1638</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>1639</v>
+      </c>
+      <c r="E133" t="s">
+        <v>1640</v>
+      </c>
+      <c r="F133" t="s">
+        <v>1641</v>
+      </c>
+      <c r="G133" t="s">
+        <v>1642</v>
+      </c>
+      <c r="H133" t="s">
+        <v>1643</v>
+      </c>
+      <c r="I133" t="s">
+        <v>1644</v>
+      </c>
+      <c r="J133" t="s">
+        <v>1645</v>
+      </c>
+      <c r="K133" t="s">
+        <v>1646</v>
+      </c>
+      <c r="L133" t="s">
+        <v>1647</v>
+      </c>
+      <c r="M133" t="s">
+        <v>1648</v>
+      </c>
+      <c r="N133" t="s">
+        <v>1649</v>
+      </c>
+      <c r="O133" t="s">
+        <v>1650</v>
       </c>
     </row>
   </sheetData>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="1651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="1676">
   <si>
     <t>##var</t>
   </si>
@@ -5603,6 +5603,91 @@
   </si>
   <si>
     <t>Check-in tamamlandı, çekmek için dokunun</t>
+  </si>
+  <si>
+    <t>确认账户信息</t>
+  </si>
+  <si>
+    <t>Confirm Account Info</t>
+  </si>
+  <si>
+    <t>Kontodaten bestätigen</t>
+  </si>
+  <si>
+    <t>口座情報を確認</t>
+  </si>
+  <si>
+    <t>Confirmar dados da conta</t>
+  </si>
+  <si>
+    <t>提现申请已提交</t>
+  </si>
+  <si>
+    <t>Withdrawal request submitted</t>
+  </si>
+  <si>
+    <t>Auszahlungsanfrage eingereicht</t>
+  </si>
+  <si>
+    <t>出金申請を送信しました</t>
+  </si>
+  <si>
+    <t>Solicitação de saque enviada</t>
+  </si>
+  <si>
+    <t>签到 &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; 天</t>
+  </si>
+  <si>
+    <t>Check-in: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; days</t>
+  </si>
+  <si>
+    <t>Check-in: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; Tage</t>
+  </si>
+  <si>
+    <t>サインイン &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; 日</t>
+  </si>
+  <si>
+    <t>Check-in: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; dias</t>
+  </si>
+  <si>
+    <t>为确认账户已启用且您为真实玩家（防止机器人刷取），请连续签到{0}天完成身份核实。
+再通过{1}个关卡即可完成今日签到。
+此步骤有助于保障提现顺利到账。</t>
+  </si>
+  <si>
+    <t>To confirm your account is active and you are a real player (not a bot), check in for {0} consecutive days to verify your identity.
+Clear {1} more levels to complete today's check-in.
+This helps ensure smooth withdrawals.</t>
+  </si>
+  <si>
+    <t>Um zu bestätigen, dass dein Konto aktiv ist und du ein echter Spieler bist (kein Bot), melde dich {0} Tage hintereinander an, um deine Identität zu bestätigen.
+Schließe {1} weitere Level ab, um den heutigen Check-in abzuschließen.
+Dies hilft, reibungslose Auszahlungen zu gewährleisten.</t>
+  </si>
+  <si>
+    <t>アカウントが有効で実在のプレイヤーであること（ボット防止）を確認するため、{0}日連続サインインで本人確認を行います。
+あと{1}レベルクリアで本日のサインインが完了します。
+スムーズな出金のための手続きです。</t>
+  </si>
+  <si>
+    <t>Para confirmar que sua conta está ativa e que você é um jogador real (não um bot), faça check-in por {0} dias seguidos para verificar sua identidade.
+Passe mais {1} níveis para completar o check-in de hoje.
+Isso ajuda a garantir saques sem problemas.</t>
+  </si>
+  <si>
+    <t>提现成功</t>
+  </si>
+  <si>
+    <t>Withdrawal successful</t>
+  </si>
+  <si>
+    <t>Auszahlung erfolgreich</t>
+  </si>
+  <si>
+    <t>出金成功</t>
+  </si>
+  <si>
+    <t>Saque realizado com sucesso</t>
   </si>
 </sst>
 </file>
@@ -6296,7 +6381,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6355,6 +6440,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -6890,7 +6978,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W133"/>
+  <dimension ref="A1:W138"/>
   <sheetFormatPr defaultColWidth="9.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.875" customWidth="1"/>
@@ -12930,6 +13018,106 @@
         <v>1650</v>
       </c>
     </row>
+    <row r="134" customHeight="1" spans="2:15">
+      <c r="B134" s="3">
+        <v>10129</v>
+      </c>
+      <c r="C134" s="22" t="s">
+        <v>1651</v>
+      </c>
+      <c r="D134" s="22" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E134" s="22" t="s">
+        <v>1653</v>
+      </c>
+      <c r="F134" s="22" t="s">
+        <v>1654</v>
+      </c>
+      <c r="G134" s="22" t="s">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="135" customHeight="1" spans="2:15">
+      <c r="B135" s="3">
+        <v>10130</v>
+      </c>
+      <c r="C135" s="22" t="s">
+        <v>1656</v>
+      </c>
+      <c r="D135" s="22" t="s">
+        <v>1657</v>
+      </c>
+      <c r="E135" s="22" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F135" s="22" t="s">
+        <v>1659</v>
+      </c>
+      <c r="G135" s="22" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="136" customHeight="1" spans="2:15">
+      <c r="B136" s="3">
+        <v>10131</v>
+      </c>
+      <c r="C136" s="22" t="s">
+        <v>1661</v>
+      </c>
+      <c r="D136" s="22" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E136" s="22" t="s">
+        <v>1663</v>
+      </c>
+      <c r="F136" s="22" t="s">
+        <v>1664</v>
+      </c>
+      <c r="G136" s="22" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="137" customHeight="1" spans="2:15">
+      <c r="B137" s="3">
+        <v>10132</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>1666</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>1667</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>1668</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>1669</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="138" customHeight="1" spans="2:15">
+      <c r="B138" s="3">
+        <v>10133</v>
+      </c>
+      <c r="C138" s="22" t="s">
+        <v>1671</v>
+      </c>
+      <c r="D138" s="22" t="s">
+        <v>1672</v>
+      </c>
+      <c r="E138" s="22" t="s">
+        <v>1673</v>
+      </c>
+      <c r="F138" s="22" t="s">
+        <v>1674</v>
+      </c>
+      <c r="G138" s="22" t="s">
+        <v>1675</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="1676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1864" uniqueCount="1752">
   <si>
     <t>##var</t>
   </si>
@@ -5620,6 +5620,21 @@
     <t>Confirmar dados da conta</t>
   </si>
   <si>
+    <t>Confirmer les infos du compte</t>
+  </si>
+  <si>
+    <t>Confirmar datos de la cuenta</t>
+  </si>
+  <si>
+    <t>Konfirmasi info akun</t>
+  </si>
+  <si>
+    <t>Подтвердите данные аккаунта</t>
+  </si>
+  <si>
+    <t>खाता जानकारी पुष्टि करें</t>
+  </si>
+  <si>
     <t>提现申请已提交</t>
   </si>
   <si>
@@ -5635,6 +5650,30 @@
     <t>Solicitação de saque enviada</t>
   </si>
   <si>
+    <t>Demande de retrait envoyée</t>
+  </si>
+  <si>
+    <t>Solicitud de retiro enviada</t>
+  </si>
+  <si>
+    <t>출금 신청이 제출되었습니다</t>
+  </si>
+  <si>
+    <t>Permintaan penarikan telah dikirim</t>
+  </si>
+  <si>
+    <t>Заявка на вывод отправлена</t>
+  </si>
+  <si>
+    <t>निकासी अनुरोध जमा हो गया</t>
+  </si>
+  <si>
+    <t>ส่งคำขอถอนแล้ว</t>
+  </si>
+  <si>
+    <t>Çekim talebi gönderildi</t>
+  </si>
+  <si>
     <t>签到 &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; 天</t>
   </si>
   <si>
@@ -5650,31 +5689,95 @@
     <t>Check-in: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; dias</t>
   </si>
   <si>
-    <t>为确认账户已启用且您为真实玩家（防止机器人刷取），请连续签到{0}天完成身份核实。
-再通过{1}个关卡即可完成今日签到。
+    <t>Check-in : &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; jours</t>
+  </si>
+  <si>
+    <t>Check-in: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; días</t>
+  </si>
+  <si>
+    <t>출석: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt;일</t>
+  </si>
+  <si>
+    <t>Check-in: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; hari</t>
+  </si>
+  <si>
+    <t>Check-in: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; дн.</t>
+  </si>
+  <si>
+    <t>चेक-इन: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; दिन</t>
+  </si>
+  <si>
+    <t>เช็คอิน &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; วัน</t>
+  </si>
+  <si>
+    <t>Check-in: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; gün</t>
+  </si>
+  <si>
+    <t>为确认账户已启用且您为真实玩家（防止机器人刷取），请连续签到8天完成身份核实。
+再通过{0}个关卡即可完成今日签到。
 此步骤有助于保障提现顺利到账。</t>
   </si>
   <si>
-    <t>To confirm your account is active and you are a real player (not a bot), check in for {0} consecutive days to verify your identity.
-Clear {1} more levels to complete today's check-in.
+    <t>To confirm your account is active and you are a real player (not a bot), check in for 8 consecutive days to verify your identity.
+Clear {0} more levels to complete today's check-in.
 This helps ensure smooth withdrawals.</t>
   </si>
   <si>
-    <t>Um zu bestätigen, dass dein Konto aktiv ist und du ein echter Spieler bist (kein Bot), melde dich {0} Tage hintereinander an, um deine Identität zu bestätigen.
-Schließe {1} weitere Level ab, um den heutigen Check-in abzuschließen.
+    <t>Um zu bestätigen, dass dein Konto aktiv ist und du ein echter Spieler bist (kein Bot), melde dich 8 Tage hintereinander an, um deine Identität zu bestätigen.
+Schließe {0} weitere Level ab, um den heutigen Check-in abzuschließen.
 Dies hilft, reibungslose Auszahlungen zu gewährleisten.</t>
   </si>
   <si>
-    <t>アカウントが有効で実在のプレイヤーであること（ボット防止）を確認するため、{0}日連続サインインで本人確認を行います。
-あと{1}レベルクリアで本日のサインインが完了します。
+    <t>アカウントが有効で実在のプレイヤーであること（ボット防止）を確認するため、8日連続サインインで本人確認を行います。
+あと{0}レベルクリアで本日のサインインが完了します。
 スムーズな出金のための手続きです。</t>
   </si>
   <si>
-    <t>Para confirmar que sua conta está ativa e que você é um jogador real (não um bot), faça check-in por {0} dias seguidos para verificar sua identidade.
-Passe mais {1} níveis para completar o check-in de hoje.
+    <t>Para confirmar que sua conta está ativa e que você é um jogador real (não um bot), faça check-in por 8 dias seguidos para verificar sua identidade.
+Passe mais {0} níveis para completar o check-in de hoje.
 Isso ajuda a garantir saques sem problemas.</t>
   </si>
   <si>
+    <t>Pour confirmer que votre compte est actif et que vous êtes un vrai joueur (pas un bot), effectuez le check-in pendant 8 jours consécutifs pour vérifier votre identité.
+Passez encore {0} niveaux pour terminer le check-in du jour.
+Cela aide à assurer des retraits fluides.</t>
+  </si>
+  <si>
+    <t>Para confirmar que tu cuenta está activa y que eres un jugador real (no un bot), haz check-in durante 8 días seguidos para verificar tu identidad.
+Supera {0} niveles más para completar el check-in de hoy.
+Esto ayuda a garantizar retiros sin problemas.</t>
+  </si>
+  <si>
+    <t>계정이 활성화되어 있고 봇이 아닌 실제 플레이어임을 확인하기 위해 8일 연속 출석으로 본인 인증을 완료해 주세요.
+{0}개 레벨을 더 클리어하면 오늘 출석이 완료됩니다.
+원활한 출금을 위한 절차입니다.</t>
+  </si>
+  <si>
+    <t>Untuk memastikan akun aktif dan Anda pemain asli (bukan bot), lakukan check-in selama 8 hari berturut-turut untuk verifikasi identitas.
+Lewati {0} level lagi untuk menyelesaikan check-in hari ini.
+Ini membantu memastikan penarikan lancar.</t>
+  </si>
+  <si>
+    <t>Чтобы подтвердить, что аккаунт активен и вы реальный игрок (не бот), выполняйте check-in 8 дней подряд для верификации личности.
+Пройдите ещё {0} уровней, чтобы завершить сегодняшний check-in.
+Это помогает обеспечить бесперебойный вывод.</t>
+  </si>
+  <si>
+    <t>खाता सक्रिय है और आप वास्तविक खिलाड़ी हैं (बॉट नहीं) यह सुनिश्चित करने के लिए, पहचान सत्यापन हेतु लगातार 8 दिन चेक-इन करें।
+{0} और लेवल पूरे करें तो आज का चेक-इन हो जाएगा।
+यह सुचारू निकासी में मदद करता है।</t>
+  </si>
+  <si>
+    <t>เพื่อยืนยันว่าบัญชีเปิดใช้งานและคุณเป็นผู้เล่นจริง (ไม่ใช่บอท) กรุณาเช็คอินติดต่อกัน 8 วันเพื่อยืนยันตัวตน
+ผ่านอีก {0} ด่านเพื่อเช็คอินวันนี้ให้ครบ
+ช่วยให้การถอนเงินราบรื่นขึ้น</t>
+  </si>
+  <si>
+    <t>Hesabınızın aktif olduğunu ve gerçek bir oyuncu olduğunuzu (bot olmadığınızı) doğrulamak için kimlik doğrulaması amacıyla 8 gün üst üste check-in yapın.
+Bugünkü check-in için {0} seviye daha geçin.
+Bu, sorunsuz çekimlere yardımcı olur.</t>
+  </si>
+  <si>
     <t>提现成功</t>
   </si>
   <si>
@@ -5688,6 +5791,147 @@
   </si>
   <si>
     <t>Saque realizado com sucesso</t>
+  </si>
+  <si>
+    <t>Retrait réussi</t>
+  </si>
+  <si>
+    <t>Retiro exitoso</t>
+  </si>
+  <si>
+    <t>출금 성공</t>
+  </si>
+  <si>
+    <t>Penarikan berhasil</t>
+  </si>
+  <si>
+    <t>Вывод успешен</t>
+  </si>
+  <si>
+    <t>निकासी सफल</t>
+  </si>
+  <si>
+    <t>ถอนเงินสำเร็จ</t>
+  </si>
+  <si>
+    <t>Çekim başarılı</t>
+  </si>
+  <si>
+    <t>银行审核 &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; 天</t>
+  </si>
+  <si>
+    <t>Bank review: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; days</t>
+  </si>
+  <si>
+    <t>Bankprüfung: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; Tage</t>
+  </si>
+  <si>
+    <t>銀行審査 &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; 日</t>
+  </si>
+  <si>
+    <t>Revisão bancária: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; dias</t>
+  </si>
+  <si>
+    <t>Vérification bancaire : &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; jours</t>
+  </si>
+  <si>
+    <t>Revisión bancaria: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; días</t>
+  </si>
+  <si>
+    <t>은행 심사 &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt;일</t>
+  </si>
+  <si>
+    <t>Tinjauan bank: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; hari</t>
+  </si>
+  <si>
+    <t>Банк. проверка: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; дн.</t>
+  </si>
+  <si>
+    <t>बैंक समीक्षा: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; दिन</t>
+  </si>
+  <si>
+    <t>ตรวจธนาคาร &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; วัน</t>
+  </si>
+  <si>
+    <t>Banka incelemesi: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; gün</t>
+  </si>
+  <si>
+    <t>银行审核约需&lt;color=#EA2111&gt;{0}&lt;/color&gt;天，请保持账号活跃。不活跃账号可能被插队，导致审核进度延迟。再通过&lt;color=#EA2111&gt;{1}&lt;/color&gt;关完成今日签到，这有助于维持正常提现进度。</t>
+  </si>
+  <si>
+    <t>Bank review takes about &lt;color=#EA2111&gt;{0}&lt;/color&gt; days. Keep your account active—inactive accounts may be skipped in queue and delay review progress. Clear &lt;color=#EA2111&gt;{1}&lt;/color&gt; more levels for today's check-in. This helps maintain normal withdrawal progress.</t>
+  </si>
+  <si>
+    <t>Bankprüfung dauert ca. &lt;color=#EA2111&gt;{0}&lt;/color&gt; Tage. Konto aktiv halten—inaktive Konten können übersprungen werden und die Prüfung verzögern. Noch &lt;color=#EA2111&gt;{1}&lt;/color&gt; Level für heutigen Check-in. Dies hilft, den Auszahlungsfortschritt aufrechtzuerhalten.</t>
+  </si>
+  <si>
+    <t>銀行審査は約&lt;color=#EA2111&gt;{0}&lt;/color&gt;日。口座をアクティブに保ってください。非アクティブだと順番が飛ばされ審査が遅延する場合があります。あと&lt;color=#EA2111&gt;{1}&lt;/color&gt;レベルで本日サインイン完了。正常な出金進行の維持に役立ちます。</t>
+  </si>
+  <si>
+    <t>Revisão bancária leva cerca de &lt;color=#EA2111&gt;{0}&lt;/color&gt; dias. Mantenha a conta ativa—contas inativas podem perder a vez e atrasar a revisão. Mais &lt;color=#EA2111&gt;{1}&lt;/color&gt; níveis para o check-in de hoje. Isso ajuda a manter o progresso normal de saque.</t>
+  </si>
+  <si>
+    <t>Vérification bancaire : environ &lt;color=#EA2111&gt;{0}&lt;/color&gt; jours. Gardez le compte actif—les comptes inactifs peuvent être dépassés et retarder la vérification. Encore &lt;color=#EA2111&gt;{1}&lt;/color&gt; niveaux pour le check-in du jour. Cela aide à maintenir la progression normale du retrait.</t>
+  </si>
+  <si>
+    <t>Revisión bancaria: unos &lt;color=#EA2111&gt;{0}&lt;/color&gt; días. Mantén la cuenta activa—las cuentas inactivas pueden ser superadas y retrasar la revisión. &lt;color=#EA2111&gt;{1}&lt;/color&gt; niveles más para el check-in de hoy. Esto ayuda a mantener el progreso normal de retiro.</t>
+  </si>
+  <si>
+    <t>은행 심사 약 &lt;color=#EA2111&gt;{0}&lt;/color&gt;일. 계정을 활성 상태로 유지하세요. 비활성 계정은 순서가 밀려 심사 진행이 지연될 수 있습니다. 오늘 출석까지 &lt;color=#EA2111&gt;{1}&lt;/color&gt;레벨 더. 정상 출금 진행 유지에 도움이 됩니다.</t>
+  </si>
+  <si>
+    <t>Tinjauan bank sekitar &lt;color=#EA2111&gt;{0}&lt;/color&gt; hari. Jaga akun tetap aktif—akun tidak aktif bisa didahului dan menunda tinjauan. &lt;color=#EA2111&gt;{1}&lt;/color&gt; level lagi untuk check-in hari ini. Ini membantu menjaga progres penarikan normal.</t>
+  </si>
+  <si>
+    <t>Банковская проверка ~&lt;color=#EA2111&gt;{0}&lt;/color&gt; дн. Держите аккаунт активным—неактивные могут быть пропущены в очереди и задержать проверку. Ещё &lt;color=#EA2111&gt;{1}&lt;/color&gt; уровней для сегодняшнего check-in. Это помогает сохранить нормальный прогресс вывода.</t>
+  </si>
+  <si>
+    <t>बैंक समीक्षा लगभग &lt;color=#EA2111&gt;{0}&lt;/color&gt; दिन। खाता सक्रिय रखें—निष्क्रिय खाते कतार में पीछे हो सकते हैं और समीक्षा में देरी हो सकती है। आज का चेक-इन: &lt;color=#EA2111&gt;{1}&lt;/color&gt; लेवल और। सामान्य निकासी प्रगति बनाए रखने में मदद करता है।</t>
+  </si>
+  <si>
+    <t>ตรวจธนาคารประมาณ &lt;color=#EA2111&gt;{0}&lt;/color&gt; วัน รักษาบัญชีให้ใช้งาน บัญชีไม่ใช้งานอาจถูกแทรกคิวและทำให้ความคืบหน้าล่าช้า ผ่านอีก &lt;color=#EA2111&gt;{1}&lt;/color&gt; ด่านเพื่อเช็คอินวันนี้ ช่วยรักษาความคืบหน้าการถอนปกติ</t>
+  </si>
+  <si>
+    <t>Banka incelemesi yaklaşık &lt;color=#EA2111&gt;{0}&lt;/color&gt; gün. Hesabı aktif tutun—pasif hesaplar sıra atlanabilir ve inceleme ilerlemesini geciktirebilir. Bugünkü check-in için &lt;color=#EA2111&gt;{1}&lt;/color&gt; seviye daha. Normal çekim ilerlemesini sürdürmeye yardımcı olur.</t>
+  </si>
+  <si>
+    <t>当前提现申请较多，银行按提交顺序分批处理。请保持账号活跃，再通过&lt;color=#EA2111&gt;{0}&lt;/color&gt;关完成今日签到，有助于维持审核顺位。请耐心等待。</t>
+  </si>
+  <si>
+    <t>High withdrawal volume currently. Banks process in batches by submission order. Keep your account active and clear &lt;color=#EA2111&gt;{0}&lt;/color&gt; more levels for today's check-in to maintain your queue position. Please wait patiently.</t>
+  </si>
+  <si>
+    <t>Derzeit viele Auszahlungsanfragen. Banken bearbeiten in Chargen nach Einreichungsreihenfolge. Konto aktiv halten und noch &lt;color=#EA2111&gt;{0}&lt;/color&gt; Level für heutigen Check-in abschließen, um die Warteschlangenposition zu behalten. Bitte Geduld.</t>
+  </si>
+  <si>
+    <t>現在出金申請が多く、銀行は提出順にバッチ処理しています。口座をアクティブに保ち、あと&lt;color=#EA2111&gt;{0}&lt;/color&gt;レベルで本日サインイン完了。審査順位の維持に役立ちます。しばらくお待ちください。</t>
+  </si>
+  <si>
+    <t>Muitas solicitações de saque no momento. Os bancos processam em lotes por ordem de envio. Mantenha a conta ativa e conclua mais &lt;color=#EA2111&gt;{0}&lt;/color&gt; níveis para o check-in de hoje, ajudando a manter sua posição na fila. Aguarde com paciência.</t>
+  </si>
+  <si>
+    <t>Volume élevé de demandes de retrait. Les banques traitent par lots selon l'ordre de soumission. Gardez le compte actif et terminez encore &lt;color=#EA2111&gt;{0}&lt;/color&gt; niveaux pour le check-in du jour, afin de maintenir votre place dans la file. Veuillez patienter.</t>
+  </si>
+  <si>
+    <t>Hay muchas solicitudes de retiro. Los bancos procesan por lotes según el orden de envío. Mantén la cuenta activa y completa &lt;color=#EA2111&gt;{0}&lt;/color&gt; niveles más para el check-in de hoy, ayudando a mantener tu posición en la cola. Espera con paciencia.</t>
+  </si>
+  <si>
+    <t>현재 출금 신청이 많아 은행이 제출 순서대로 배치 처리 중입니다. 계정을 활성 상태로 유지하고 오늘 출석까지 &lt;color=#EA2111&gt;{0}&lt;/color&gt;레벨 더 완료하세요. 심사 순위 유지에 도움이 됩니다. 잠시만 기다려 주세요.</t>
+  </si>
+  <si>
+    <t>Permintaan penarikan sedang tinggi. Bank memproses per batch sesuai urutan pengajuan. Jaga akun tetap aktif dan selesaikan &lt;color=#EA2111&gt;{0}&lt;/color&gt; level lagi untuk check-in hari ini, membantu mempertahankan posisi antrean. Harap bersabar.</t>
+  </si>
+  <si>
+    <t>Сейчас много заявок на вывод. Банки обрабатывают партиями по порядку подачи. Держите аккаунт активным и пройдите ещё &lt;color=#EA2111&gt;{0}&lt;/color&gt; уровней для сегодняшнего check-in, чтобы сохранить место в очереди. Пожалуйста, подождите.</t>
+  </si>
+  <si>
+    <t>वर्तमान में निकासी अनुरोध अधिक हैं। बैंक जमा क्रम से बैच में प्रोसेस करते हैं। खाता सक्रिय रखें और आज का चेक-इन: &lt;color=#EA2111&gt;{0}&lt;/color&gt; लेवल और पूरे करें, समीक्षा क्रम बनाए रखने में मदद करता है। कृपया धैर्य रखें।</t>
+  </si>
+  <si>
+    <t>ขณะนี้มีคำขอถอนมาก ธนาคารดำเนินการเป็นชุดตามลำดับส่ง รักษาบัญชีให้ใช้งานและผ่านอีก &lt;color=#EA2111&gt;{0}&lt;/color&gt; ด่านเพื่อเช็คอินวันนี้ ช่วยรักษาลำดับการตรวจ โปรดรออย่างใจเย็น</t>
+  </si>
+  <si>
+    <t>Şu anda çok sayıda çekim talebi var. Bankalar gönderim sırasına göre toplu işliyor. Hesabı aktif tutun ve bugünkü check-in için &lt;color=#EA2111&gt;{0}&lt;/color&gt; seviye daha tamamlayın, sıra konumunuzu korumanıza yardımcı olur. Lütfen sabırla bekleyin.</t>
   </si>
 </sst>
 </file>
@@ -6381,7 +6625,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6389,6 +6633,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -6442,9 +6689,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6978,11 +7223,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W138"/>
+  <dimension ref="A1:W141"/>
   <sheetFormatPr defaultColWidth="9.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.875" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="4" customWidth="1"/>
     <col min="3" max="3" width="31.625" customWidth="1"/>
     <col min="4" max="4" width="54.25" style="1" customWidth="1"/>
     <col min="5" max="6" width="28.125" customWidth="1"/>
@@ -6992,49 +7237,49 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:16">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="8" t="s">
         <v>14</v>
       </c>
       <c r="P1" t="s">
@@ -7042,68 +7287,68 @@
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:16">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
     </row>
     <row r="3" customHeight="1" spans="1:16">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P3" t="s">
@@ -7111,49 +7356,49 @@
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:16">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="M4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="N4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="9" t="s">
+      <c r="O4" s="10" t="s">
         <v>19</v>
       </c>
       <c r="P4" t="s">
@@ -7161,49 +7406,49 @@
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:16">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="O5" s="7" t="s">
         <v>33</v>
       </c>
       <c r="P5" t="s">
@@ -7211,1059 +7456,1059 @@
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="13.5" spans="1:16">
-      <c r="B6" s="10">
+      <c r="B6" s="11">
         <v>10001</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="N6" s="11" t="s">
+      <c r="N6" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="O6" s="11" t="s">
+      <c r="O6" s="12" t="s">
         <v>47</v>
       </c>
       <c r="P6"/>
     </row>
     <row r="7" customFormat="1" customHeight="1" spans="1:16">
-      <c r="B7" s="10">
+      <c r="B7" s="11">
         <v>10002</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="L7" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="M7" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="N7" s="11" t="s">
+      <c r="N7" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="O7" s="11" t="s">
+      <c r="O7" s="12" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:16">
-      <c r="B8" s="10">
+      <c r="B8" s="11">
         <v>10003</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="J8" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="L8" s="11" t="s">
+      <c r="L8" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="M8" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="N8" s="11" t="s">
+      <c r="N8" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="O8" s="11" t="s">
+      <c r="O8" s="12" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:16">
-      <c r="B9" s="10">
+      <c r="B9" s="11">
         <v>10004</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="J9" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="L9" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="M9" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="N9" s="11" t="s">
+      <c r="N9" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="O9" s="11" t="s">
+      <c r="O9" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:16">
-      <c r="B10" s="10">
+      <c r="B10" s="11">
         <v>10005</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J10" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="L10" s="11" t="s">
+      <c r="L10" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="M10" s="11" t="s">
+      <c r="M10" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="N10" s="11" t="s">
+      <c r="N10" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="O10" s="11" t="s">
+      <c r="O10" s="12" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:16">
-      <c r="B11" s="10">
+      <c r="B11" s="11">
         <v>10006</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="J11" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="L11" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="M11" s="11" t="s">
+      <c r="M11" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="N11" s="11" t="s">
+      <c r="N11" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="O11" s="11" t="s">
+      <c r="O11" s="12" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="B12" s="10">
+      <c r="B12" s="11">
         <v>10007</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="J12" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K12" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="L12" s="11" t="s">
+      <c r="L12" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="M12" s="11" t="s">
+      <c r="M12" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="N12" s="11" t="s">
+      <c r="N12" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="O12" s="11" t="s">
+      <c r="O12" s="12" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="B13" s="10">
+      <c r="B13" s="11">
         <v>10008</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="J13" s="11" t="s">
+      <c r="J13" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K13" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="L13" s="11" t="s">
+      <c r="L13" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="M13" s="11" t="s">
+      <c r="M13" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="N13" s="11" t="s">
+      <c r="N13" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="O13" s="11" t="s">
+      <c r="O13" s="12" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:16">
-      <c r="B14" s="10">
+      <c r="B14" s="11">
         <v>10009</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K14" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="L14" s="11" t="s">
+      <c r="L14" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="M14" s="11" t="s">
+      <c r="M14" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="N14" s="11" t="s">
+      <c r="N14" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="O14" s="11" t="s">
+      <c r="O14" s="12" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:16">
-      <c r="B15" s="10">
+      <c r="B15" s="11">
         <v>10010</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J15" s="11" t="s">
+      <c r="J15" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="K15" s="11" t="s">
+      <c r="K15" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="L15" s="11" t="s">
+      <c r="L15" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="M15" s="11" t="s">
+      <c r="M15" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="N15" s="11" t="s">
+      <c r="N15" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="O15" s="11" t="s">
+      <c r="O15" s="12" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:16">
-      <c r="B16" s="10">
+      <c r="B16" s="11">
         <v>10011</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="H16" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="I16" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="J16" s="11" t="s">
+      <c r="J16" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="K16" s="11" t="s">
+      <c r="K16" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="L16" s="11" t="s">
+      <c r="L16" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="M16" s="11" t="s">
+      <c r="M16" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="N16" s="11" t="s">
+      <c r="N16" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="O16" s="11" t="s">
+      <c r="O16" s="12" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:23">
-      <c r="B17" s="10">
+      <c r="B17" s="11">
         <v>10012</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="H17" s="11" t="s">
+      <c r="H17" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="I17" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="J17" s="11" t="s">
+      <c r="J17" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="K17" s="11" t="s">
+      <c r="K17" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="L17" s="11" t="s">
+      <c r="L17" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="M17" s="11" t="s">
+      <c r="M17" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="N17" s="11" t="s">
+      <c r="N17" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="O17" s="11" t="s">
+      <c r="O17" s="12" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:23">
-      <c r="B18" s="10">
+      <c r="B18" s="11">
         <v>10013</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="H18" s="11" t="s">
+      <c r="H18" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="I18" s="11" t="s">
+      <c r="I18" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="J18" s="11" t="s">
+      <c r="J18" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="K18" s="11" t="s">
+      <c r="K18" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="L18" s="11" t="s">
+      <c r="L18" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="M18" s="11" t="s">
+      <c r="M18" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="N18" s="11" t="s">
+      <c r="N18" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="O18" s="11" t="s">
+      <c r="O18" s="12" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:23">
-      <c r="B19" s="10">
+      <c r="B19" s="11">
         <v>10014</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="H19" s="11" t="s">
+      <c r="H19" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="I19" s="11" t="s">
+      <c r="I19" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="J19" s="11" t="s">
+      <c r="J19" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="K19" s="11" t="s">
+      <c r="K19" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="L19" s="11" t="s">
+      <c r="L19" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="M19" s="11" t="s">
+      <c r="M19" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="N19" s="11" t="s">
+      <c r="N19" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="O19" s="11" t="s">
+      <c r="O19" s="12" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:23">
-      <c r="B20" s="10">
+      <c r="B20" s="11">
         <v>10015</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="G20" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="H20" s="11" t="s">
+      <c r="H20" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="I20" s="11" t="s">
+      <c r="I20" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="J20" s="11" t="s">
+      <c r="J20" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="K20" s="11" t="s">
+      <c r="K20" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="L20" s="11" t="s">
+      <c r="L20" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="M20" s="11" t="s">
+      <c r="M20" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="N20" s="11" t="s">
+      <c r="N20" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="O20" s="11" t="s">
+      <c r="O20" s="12" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:23">
-      <c r="B21" s="10">
+      <c r="B21" s="11">
         <v>10016</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="G21" s="11" t="s">
+      <c r="G21" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="H21" s="11" t="s">
+      <c r="H21" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="I21" s="11" t="s">
+      <c r="I21" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="J21" s="11" t="s">
+      <c r="J21" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="K21" s="11" t="s">
+      <c r="K21" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="L21" s="11" t="s">
+      <c r="L21" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="M21" s="11" t="s">
+      <c r="M21" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="N21" s="11" t="s">
+      <c r="N21" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="O21" s="11" t="s">
+      <c r="O21" s="12" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:23">
-      <c r="B22" s="10">
+      <c r="B22" s="11">
         <v>10017</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G22" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="H22" s="11" t="s">
+      <c r="H22" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="I22" s="11" t="s">
+      <c r="I22" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="J22" s="11" t="s">
+      <c r="J22" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="K22" s="11" t="s">
+      <c r="K22" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="L22" s="11" t="s">
+      <c r="L22" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="M22" s="11" t="s">
+      <c r="M22" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="N22" s="11" t="s">
+      <c r="N22" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="O22" s="11" t="s">
+      <c r="O22" s="12" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:23">
-      <c r="B23" s="10">
+      <c r="B23" s="11">
         <v>10018</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="G23" s="11" t="s">
+      <c r="G23" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="H23" s="11" t="s">
+      <c r="H23" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="I23" s="11" t="s">
+      <c r="I23" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="J23" s="11" t="s">
+      <c r="J23" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="K23" s="11" t="s">
+      <c r="K23" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="L23" s="11" t="s">
+      <c r="L23" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="M23" s="11" t="s">
+      <c r="M23" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="N23" s="11" t="s">
+      <c r="N23" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="O23" s="11" t="s">
+      <c r="O23" s="12" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="2:23">
-      <c r="B24" s="10">
+      <c r="B24" s="11">
         <v>10019</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="I24" s="11" t="s">
+      <c r="I24" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="J24" s="11" t="s">
+      <c r="J24" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="K24" s="11" t="s">
+      <c r="K24" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="L24" s="11" t="s">
+      <c r="L24" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="M24" s="11" t="s">
+      <c r="M24" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="N24" s="11" t="s">
+      <c r="N24" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="O24" s="11" t="s">
+      <c r="O24" s="12" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="2:23">
-      <c r="B25" s="10">
+      <c r="B25" s="11">
         <v>10020</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="G25" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="H25" s="11" t="s">
+      <c r="H25" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="I25" s="11" t="s">
+      <c r="I25" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="J25" s="11" t="s">
+      <c r="J25" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="K25" s="11" t="s">
+      <c r="K25" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="L25" s="11" t="s">
+      <c r="L25" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="M25" s="11" t="s">
+      <c r="M25" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="N25" s="11" t="s">
+      <c r="N25" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="O25" s="11" t="s">
+      <c r="O25" s="12" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:23">
-      <c r="B26" s="10">
+      <c r="B26" s="11">
         <v>10021</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="G26" s="11" t="s">
+      <c r="G26" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="H26" s="11" t="s">
+      <c r="H26" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="I26" s="11" t="s">
+      <c r="I26" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="J26" s="11" t="s">
+      <c r="J26" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="K26" s="11" t="s">
+      <c r="K26" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="L26" s="11" t="s">
+      <c r="L26" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="M26" s="11" t="s">
+      <c r="M26" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="N26" s="11" t="s">
+      <c r="N26" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="O26" s="11" t="s">
+      <c r="O26" s="12" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:23">
-      <c r="B27" s="10">
+      <c r="B27" s="11">
         <v>10022</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="G27" s="11" t="s">
+      <c r="G27" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="H27" s="11" t="s">
+      <c r="H27" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="I27" s="11" t="s">
+      <c r="I27" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="J27" s="11" t="s">
+      <c r="J27" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="K27" s="11" t="s">
+      <c r="K27" s="12" t="s">
         <v>311</v>
       </c>
-      <c r="L27" s="11" t="s">
+      <c r="L27" s="12" t="s">
         <v>312</v>
       </c>
-      <c r="M27" s="11" t="s">
+      <c r="M27" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="N27" s="11" t="s">
+      <c r="N27" s="12" t="s">
         <v>314</v>
       </c>
-      <c r="O27" s="11" t="s">
+      <c r="O27" s="12" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="28" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B28" s="10">
+      <c r="B28" s="11">
         <v>10023</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E28" s="12" t="s">
         <v>318</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="G28" s="11" t="s">
+      <c r="G28" s="12" t="s">
         <v>320</v>
       </c>
-      <c r="H28" s="11" t="s">
+      <c r="H28" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="I28" s="11" t="s">
+      <c r="I28" s="12" t="s">
         <v>322</v>
       </c>
-      <c r="J28" s="11" t="s">
+      <c r="J28" s="12" t="s">
         <v>323</v>
       </c>
-      <c r="K28" s="11" t="s">
+      <c r="K28" s="12" t="s">
         <v>324</v>
       </c>
-      <c r="L28" s="11" t="s">
+      <c r="L28" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="M28" s="11" t="s">
+      <c r="M28" s="12" t="s">
         <v>326</v>
       </c>
-      <c r="N28" s="11" t="s">
+      <c r="N28" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="O28" s="11" t="s">
+      <c r="O28" s="12" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="29" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B29" s="10">
+      <c r="B29" s="11">
         <v>10024</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="G29" s="11" t="s">
+      <c r="G29" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="H29" s="11" t="s">
+      <c r="H29" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="I29" s="11" t="s">
+      <c r="I29" s="12" t="s">
         <v>335</v>
       </c>
-      <c r="J29" s="11" t="s">
+      <c r="J29" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="K29" s="11" t="s">
+      <c r="K29" s="12" t="s">
         <v>337</v>
       </c>
-      <c r="L29" s="11" t="s">
+      <c r="L29" s="12" t="s">
         <v>338</v>
       </c>
-      <c r="M29" s="11" t="s">
+      <c r="M29" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="N29" s="11" t="s">
+      <c r="N29" s="12" t="s">
         <v>340</v>
       </c>
-      <c r="O29" s="11" t="s">
+      <c r="O29" s="12" t="s">
         <v>341</v>
       </c>
       <c r="Q29" s="1"/>
@@ -8275,46 +8520,46 @@
       <c r="W29" s="1"/>
     </row>
     <row r="30" customHeight="1" spans="2:23">
-      <c r="B30" s="10">
+      <c r="B30" s="11">
         <v>10025</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="G30" s="11" t="s">
+      <c r="G30" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="H30" s="11" t="s">
+      <c r="H30" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="I30" s="11" t="s">
+      <c r="I30" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="J30" s="11" t="s">
+      <c r="J30" s="12" t="s">
         <v>348</v>
       </c>
-      <c r="K30" s="11" t="s">
+      <c r="K30" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="L30" s="11" t="s">
+      <c r="L30" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="M30" s="11" t="s">
+      <c r="M30" s="12" t="s">
         <v>351</v>
       </c>
-      <c r="N30" s="11" t="s">
+      <c r="N30" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="O30" s="11" t="s">
+      <c r="O30" s="12" t="s">
         <v>353</v>
       </c>
       <c r="P30" s="1"/>
@@ -8327,46 +8572,46 @@
       <c r="W30" s="1"/>
     </row>
     <row r="31" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B31" s="10">
+      <c r="B31" s="11">
         <v>10026</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="12" t="s">
         <v>356</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="12" t="s">
         <v>357</v>
       </c>
-      <c r="G31" s="11" t="s">
+      <c r="G31" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="H31" s="11" t="s">
+      <c r="H31" s="12" t="s">
         <v>359</v>
       </c>
-      <c r="I31" s="11" t="s">
+      <c r="I31" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="J31" s="11" t="s">
+      <c r="J31" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="K31" s="11" t="s">
+      <c r="K31" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="L31" s="11" t="s">
+      <c r="L31" s="12" t="s">
         <v>362</v>
       </c>
-      <c r="M31" s="11" t="s">
+      <c r="M31" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="N31" s="11" t="s">
+      <c r="N31" s="12" t="s">
         <v>364</v>
       </c>
-      <c r="O31" s="11" t="s">
+      <c r="O31" s="12" t="s">
         <v>365</v>
       </c>
       <c r="P31"/>
@@ -8379,135 +8624,135 @@
       <c r="W31" s="1"/>
     </row>
     <row r="32" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B32" s="10">
+      <c r="B32" s="11">
         <v>10027</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="12" t="s">
         <v>367</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E32" s="12" t="s">
         <v>368</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="12" t="s">
         <v>369</v>
       </c>
-      <c r="G32" s="11" t="s">
+      <c r="G32" s="12" t="s">
         <v>370</v>
       </c>
-      <c r="H32" s="11" t="s">
+      <c r="H32" s="12" t="s">
         <v>371</v>
       </c>
-      <c r="I32" s="11" t="s">
+      <c r="I32" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="J32" s="13" t="s">
+      <c r="J32" s="14" t="s">
         <v>373</v>
       </c>
-      <c r="K32" s="11" t="s">
+      <c r="K32" s="12" t="s">
         <v>374</v>
       </c>
-      <c r="L32" s="11" t="s">
+      <c r="L32" s="12" t="s">
         <v>375</v>
       </c>
-      <c r="M32" s="11" t="s">
+      <c r="M32" s="12" t="s">
         <v>376</v>
       </c>
-      <c r="N32" s="14" t="s">
+      <c r="N32" s="15" t="s">
         <v>377</v>
       </c>
-      <c r="O32" s="11" t="s">
+      <c r="O32" s="12" t="s">
         <v>378</v>
       </c>
       <c r="P32"/>
     </row>
     <row r="33" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B33" s="10">
+      <c r="B33" s="11">
         <v>10028</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="13" t="s">
         <v>379</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" s="12" t="s">
         <v>380</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="E33" s="12" t="s">
         <v>381</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="F33" s="12" t="s">
         <v>382</v>
       </c>
-      <c r="G33" s="11" t="s">
+      <c r="G33" s="12" t="s">
         <v>383</v>
       </c>
-      <c r="H33" s="11" t="s">
+      <c r="H33" s="12" t="s">
         <v>384</v>
       </c>
-      <c r="I33" s="11" t="s">
+      <c r="I33" s="12" t="s">
         <v>385</v>
       </c>
-      <c r="J33" s="13" t="s">
+      <c r="J33" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="K33" s="11" t="s">
+      <c r="K33" s="12" t="s">
         <v>387</v>
       </c>
-      <c r="L33" s="11" t="s">
+      <c r="L33" s="12" t="s">
         <v>388</v>
       </c>
-      <c r="M33" s="11" t="s">
+      <c r="M33" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="N33" s="14" t="s">
+      <c r="N33" s="15" t="s">
         <v>390</v>
       </c>
-      <c r="O33" s="15" t="s">
+      <c r="O33" s="16" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B34" s="10">
+      <c r="B34" s="11">
         <v>10029</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="12" t="s">
         <v>392</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="12" t="s">
         <v>393</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="E34" s="12" t="s">
         <v>394</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="12" t="s">
         <v>395</v>
       </c>
-      <c r="G34" s="11" t="s">
+      <c r="G34" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="H34" s="11" t="s">
+      <c r="H34" s="12" t="s">
         <v>397</v>
       </c>
-      <c r="I34" s="11" t="s">
+      <c r="I34" s="12" t="s">
         <v>398</v>
       </c>
-      <c r="J34" s="13" t="s">
+      <c r="J34" s="14" t="s">
         <v>399</v>
       </c>
-      <c r="K34" s="11" t="s">
+      <c r="K34" s="12" t="s">
         <v>400</v>
       </c>
-      <c r="L34" s="11" t="s">
+      <c r="L34" s="12" t="s">
         <v>401</v>
       </c>
-      <c r="M34" s="11" t="s">
+      <c r="M34" s="12" t="s">
         <v>402</v>
       </c>
-      <c r="N34" s="14" t="s">
+      <c r="N34" s="15" t="s">
         <v>403</v>
       </c>
-      <c r="O34" s="11" t="s">
+      <c r="O34" s="12" t="s">
         <v>404</v>
       </c>
       <c r="Q34"/>
@@ -8519,46 +8764,46 @@
       <c r="W34"/>
     </row>
     <row r="35" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B35" s="10">
+      <c r="B35" s="11">
         <v>10030</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D35" s="12" t="s">
         <v>406</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="E35" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="F35" s="11" t="s">
+      <c r="F35" s="12" t="s">
         <v>408</v>
       </c>
-      <c r="G35" s="11" t="s">
+      <c r="G35" s="12" t="s">
         <v>409</v>
       </c>
-      <c r="H35" s="11" t="s">
+      <c r="H35" s="12" t="s">
         <v>410</v>
       </c>
-      <c r="I35" s="11" t="s">
+      <c r="I35" s="12" t="s">
         <v>411</v>
       </c>
-      <c r="J35" s="13" t="s">
+      <c r="J35" s="14" t="s">
         <v>412</v>
       </c>
-      <c r="K35" s="11" t="s">
+      <c r="K35" s="12" t="s">
         <v>413</v>
       </c>
-      <c r="L35" s="11" t="s">
+      <c r="L35" s="12" t="s">
         <v>414</v>
       </c>
-      <c r="M35" s="11" t="s">
+      <c r="M35" s="12" t="s">
         <v>415</v>
       </c>
-      <c r="N35" s="14" t="s">
+      <c r="N35" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="O35" s="11" t="s">
+      <c r="O35" s="12" t="s">
         <v>417</v>
       </c>
       <c r="P35"/>
@@ -8571,46 +8816,46 @@
       <c r="W35"/>
     </row>
     <row r="36" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B36" s="10">
+      <c r="B36" s="11">
         <v>10031</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C36" s="12" t="s">
         <v>418</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="D36" s="12" t="s">
         <v>419</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E36" s="12" t="s">
         <v>420</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="F36" s="12" t="s">
         <v>421</v>
       </c>
-      <c r="G36" s="11" t="s">
+      <c r="G36" s="12" t="s">
         <v>422</v>
       </c>
-      <c r="H36" s="11" t="s">
+      <c r="H36" s="12" t="s">
         <v>423</v>
       </c>
-      <c r="I36" s="11" t="s">
+      <c r="I36" s="12" t="s">
         <v>424</v>
       </c>
-      <c r="J36" s="13" t="s">
+      <c r="J36" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="K36" s="11" t="s">
+      <c r="K36" s="12" t="s">
         <v>426</v>
       </c>
-      <c r="L36" s="11" t="s">
+      <c r="L36" s="12" t="s">
         <v>427</v>
       </c>
-      <c r="M36" s="11" t="s">
+      <c r="M36" s="12" t="s">
         <v>428</v>
       </c>
-      <c r="N36" s="14" t="s">
+      <c r="N36" s="15" t="s">
         <v>429</v>
       </c>
-      <c r="O36" s="15" t="s">
+      <c r="O36" s="16" t="s">
         <v>430</v>
       </c>
       <c r="P36"/>
@@ -8623,46 +8868,46 @@
       <c r="W36"/>
     </row>
     <row r="37" customHeight="1" spans="2:23">
-      <c r="B37" s="10">
+      <c r="B37" s="11">
         <v>10032</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" s="12" t="s">
         <v>432</v>
       </c>
-      <c r="E37" s="11" t="s">
+      <c r="E37" s="12" t="s">
         <v>433</v>
       </c>
-      <c r="F37" s="11" t="s">
+      <c r="F37" s="12" t="s">
         <v>434</v>
       </c>
-      <c r="G37" s="11" t="s">
+      <c r="G37" s="12" t="s">
         <v>435</v>
       </c>
-      <c r="H37" s="11" t="s">
+      <c r="H37" s="12" t="s">
         <v>436</v>
       </c>
-      <c r="I37" s="11" t="s">
+      <c r="I37" s="12" t="s">
         <v>437</v>
       </c>
-      <c r="J37" s="13" t="s">
+      <c r="J37" s="14" t="s">
         <v>438</v>
       </c>
-      <c r="K37" s="11" t="s">
+      <c r="K37" s="12" t="s">
         <v>439</v>
       </c>
-      <c r="L37" s="11" t="s">
+      <c r="L37" s="12" t="s">
         <v>440</v>
       </c>
-      <c r="M37" s="11" t="s">
+      <c r="M37" s="12" t="s">
         <v>441</v>
       </c>
-      <c r="N37" s="14" t="s">
+      <c r="N37" s="15" t="s">
         <v>442</v>
       </c>
-      <c r="O37" s="11" t="s">
+      <c r="O37" s="12" t="s">
         <v>443</v>
       </c>
       <c r="Q37" s="1"/>
@@ -8674,46 +8919,46 @@
       <c r="W37" s="1"/>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B38" s="10">
+      <c r="B38" s="11">
         <v>10033</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="12" t="s">
         <v>444</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="D38" s="12" t="s">
         <v>445</v>
       </c>
-      <c r="E38" s="11" t="s">
+      <c r="E38" s="12" t="s">
         <v>446</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="F38" s="12" t="s">
         <v>447</v>
       </c>
-      <c r="G38" s="11" t="s">
+      <c r="G38" s="12" t="s">
         <v>448</v>
       </c>
-      <c r="H38" s="11" t="s">
+      <c r="H38" s="12" t="s">
         <v>449</v>
       </c>
-      <c r="I38" s="11" t="s">
+      <c r="I38" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="J38" s="11" t="s">
+      <c r="J38" s="12" t="s">
         <v>451</v>
       </c>
-      <c r="K38" s="11" t="s">
+      <c r="K38" s="12" t="s">
         <v>452</v>
       </c>
-      <c r="L38" s="11" t="s">
+      <c r="L38" s="12" t="s">
         <v>453</v>
       </c>
-      <c r="M38" s="11" t="s">
+      <c r="M38" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="N38" s="11" t="s">
+      <c r="N38" s="12" t="s">
         <v>455</v>
       </c>
-      <c r="O38" s="11" t="s">
+      <c r="O38" s="12" t="s">
         <v>456</v>
       </c>
       <c r="P38" s="1"/>
@@ -8726,90 +8971,90 @@
       <c r="W38" s="1"/>
     </row>
     <row r="39" customHeight="1" spans="2:23">
-      <c r="B39" s="10">
+      <c r="B39" s="11">
         <v>10034</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="12" t="s">
         <v>457</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="D39" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="E39" s="11" t="s">
+      <c r="E39" s="12" t="s">
         <v>459</v>
       </c>
-      <c r="F39" s="11" t="s">
+      <c r="F39" s="12" t="s">
         <v>460</v>
       </c>
-      <c r="G39" s="11" t="s">
+      <c r="G39" s="12" t="s">
         <v>461</v>
       </c>
-      <c r="H39" s="11" t="s">
+      <c r="H39" s="12" t="s">
         <v>462</v>
       </c>
-      <c r="I39" s="11" t="s">
+      <c r="I39" s="12" t="s">
         <v>463</v>
       </c>
-      <c r="J39" s="11" t="s">
+      <c r="J39" s="12" t="s">
         <v>464</v>
       </c>
-      <c r="K39" s="11" t="s">
+      <c r="K39" s="12" t="s">
         <v>465</v>
       </c>
-      <c r="L39" s="11" t="s">
+      <c r="L39" s="12" t="s">
         <v>466</v>
       </c>
-      <c r="M39" s="11" t="s">
+      <c r="M39" s="12" t="s">
         <v>467</v>
       </c>
-      <c r="N39" s="11" t="s">
+      <c r="N39" s="12" t="s">
         <v>468</v>
       </c>
-      <c r="O39" s="11" t="s">
+      <c r="O39" s="12" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" ht="20" customHeight="1" spans="2:23">
-      <c r="B40" s="10">
+      <c r="B40" s="11">
         <v>10035</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C40" s="12" t="s">
         <v>470</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="D40" s="12" t="s">
         <v>471</v>
       </c>
-      <c r="E40" s="11" t="s">
+      <c r="E40" s="12" t="s">
         <v>472</v>
       </c>
-      <c r="F40" s="11" t="s">
+      <c r="F40" s="12" t="s">
         <v>473</v>
       </c>
-      <c r="G40" s="11" t="s">
+      <c r="G40" s="12" t="s">
         <v>474</v>
       </c>
-      <c r="H40" s="11" t="s">
+      <c r="H40" s="12" t="s">
         <v>475</v>
       </c>
-      <c r="I40" s="11" t="s">
+      <c r="I40" s="12" t="s">
         <v>476</v>
       </c>
-      <c r="J40" s="11" t="s">
+      <c r="J40" s="12" t="s">
         <v>477</v>
       </c>
-      <c r="K40" s="11" t="s">
+      <c r="K40" s="12" t="s">
         <v>478</v>
       </c>
-      <c r="L40" s="11" t="s">
+      <c r="L40" s="12" t="s">
         <v>479</v>
       </c>
-      <c r="M40" s="11" t="s">
+      <c r="M40" s="12" t="s">
         <v>480</v>
       </c>
-      <c r="N40" s="11" t="s">
+      <c r="N40" s="12" t="s">
         <v>481</v>
       </c>
-      <c r="O40" s="11" t="s">
+      <c r="O40" s="12" t="s">
         <v>482</v>
       </c>
       <c r="P40"/>
@@ -8822,46 +9067,46 @@
       <c r="W40"/>
     </row>
     <row r="41" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B41" s="10">
+      <c r="B41" s="11">
         <v>10036</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="13" t="s">
         <v>483</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D41" s="12" t="s">
         <v>484</v>
       </c>
-      <c r="E41" s="11" t="s">
+      <c r="E41" s="12" t="s">
         <v>485</v>
       </c>
-      <c r="F41" s="11" t="s">
+      <c r="F41" s="12" t="s">
         <v>486</v>
       </c>
-      <c r="G41" s="11" t="s">
+      <c r="G41" s="12" t="s">
         <v>487</v>
       </c>
-      <c r="H41" s="11" t="s">
+      <c r="H41" s="12" t="s">
         <v>488</v>
       </c>
-      <c r="I41" s="11" t="s">
+      <c r="I41" s="12" t="s">
         <v>487</v>
       </c>
-      <c r="J41" s="11" t="s">
+      <c r="J41" s="12" t="s">
         <v>489</v>
       </c>
-      <c r="K41" s="11" t="s">
+      <c r="K41" s="12" t="s">
         <v>490</v>
       </c>
-      <c r="L41" s="11" t="s">
+      <c r="L41" s="12" t="s">
         <v>491</v>
       </c>
-      <c r="M41" s="11" t="s">
+      <c r="M41" s="12" t="s">
         <v>492</v>
       </c>
-      <c r="N41" s="11" t="s">
+      <c r="N41" s="12" t="s">
         <v>493</v>
       </c>
-      <c r="O41" s="11" t="s">
+      <c r="O41" s="12" t="s">
         <v>494</v>
       </c>
       <c r="P41"/>
@@ -8874,226 +9119,226 @@
       <c r="W41"/>
     </row>
     <row r="42" customHeight="1" spans="2:23">
-      <c r="B42" s="10">
+      <c r="B42" s="11">
         <v>10037</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="13" t="s">
         <v>495</v>
       </c>
-      <c r="D42" s="11" t="s">
+      <c r="D42" s="12" t="s">
         <v>496</v>
       </c>
-      <c r="E42" s="11" t="s">
+      <c r="E42" s="12" t="s">
         <v>497</v>
       </c>
-      <c r="F42" s="11" t="s">
+      <c r="F42" s="12" t="s">
         <v>498</v>
       </c>
-      <c r="G42" s="11" t="s">
+      <c r="G42" s="12" t="s">
         <v>499</v>
       </c>
-      <c r="H42" s="11" t="s">
+      <c r="H42" s="12" t="s">
         <v>500</v>
       </c>
-      <c r="I42" s="11" t="s">
+      <c r="I42" s="12" t="s">
         <v>501</v>
       </c>
-      <c r="J42" s="11" t="s">
+      <c r="J42" s="12" t="s">
         <v>502</v>
       </c>
-      <c r="K42" s="11" t="s">
+      <c r="K42" s="12" t="s">
         <v>503</v>
       </c>
-      <c r="L42" s="11" t="s">
+      <c r="L42" s="12" t="s">
         <v>504</v>
       </c>
-      <c r="M42" s="11" t="s">
+      <c r="M42" s="12" t="s">
         <v>505</v>
       </c>
-      <c r="N42" s="11" t="s">
+      <c r="N42" s="12" t="s">
         <v>506</v>
       </c>
-      <c r="O42" s="11" t="s">
+      <c r="O42" s="12" t="s">
         <v>507</v>
       </c>
       <c r="P42" s="1"/>
     </row>
     <row r="43" customHeight="1" spans="2:23">
-      <c r="B43" s="10">
+      <c r="B43" s="11">
         <v>10038</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C43" s="12" t="s">
         <v>508</v>
       </c>
-      <c r="D43" s="11" t="s">
+      <c r="D43" s="12" t="s">
         <v>509</v>
       </c>
-      <c r="E43" s="11" t="s">
+      <c r="E43" s="12" t="s">
         <v>510</v>
       </c>
-      <c r="F43" s="11" t="s">
+      <c r="F43" s="12" t="s">
         <v>511</v>
       </c>
-      <c r="G43" s="11" t="s">
+      <c r="G43" s="12" t="s">
         <v>512</v>
       </c>
-      <c r="H43" s="11" t="s">
+      <c r="H43" s="12" t="s">
         <v>513</v>
       </c>
-      <c r="I43" s="11" t="s">
+      <c r="I43" s="12" t="s">
         <v>514</v>
       </c>
-      <c r="J43" s="11" t="s">
+      <c r="J43" s="12" t="s">
         <v>515</v>
       </c>
-      <c r="K43" s="11" t="s">
+      <c r="K43" s="12" t="s">
         <v>516</v>
       </c>
-      <c r="L43" s="11" t="s">
+      <c r="L43" s="12" t="s">
         <v>517</v>
       </c>
-      <c r="M43" s="11" t="s">
+      <c r="M43" s="12" t="s">
         <v>518</v>
       </c>
-      <c r="N43" s="11" t="s">
+      <c r="N43" s="12" t="s">
         <v>519</v>
       </c>
-      <c r="O43" s="11" t="s">
+      <c r="O43" s="12" t="s">
         <v>520</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:23">
-      <c r="B44" s="10">
+      <c r="B44" s="11">
         <v>10039</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C44" s="12" t="s">
         <v>521</v>
       </c>
-      <c r="D44" s="11" t="s">
+      <c r="D44" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="E44" s="11" t="s">
+      <c r="E44" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="F44" s="11" t="s">
+      <c r="F44" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="G44" s="11" t="s">
+      <c r="G44" s="12" t="s">
         <v>524</v>
       </c>
-      <c r="H44" s="11" t="s">
+      <c r="H44" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="I44" s="11" t="s">
+      <c r="I44" s="12" t="s">
         <v>525</v>
       </c>
-      <c r="J44" s="11" t="s">
+      <c r="J44" s="12" t="s">
         <v>526</v>
       </c>
-      <c r="K44" s="11" t="s">
+      <c r="K44" s="12" t="s">
         <v>527</v>
       </c>
-      <c r="L44" s="11" t="s">
+      <c r="L44" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="M44" s="11" t="s">
+      <c r="M44" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="N44" s="11" t="s">
+      <c r="N44" s="12" t="s">
         <v>530</v>
       </c>
-      <c r="O44" s="11" t="s">
+      <c r="O44" s="12" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:23">
-      <c r="B45" s="10">
+      <c r="B45" s="11">
         <v>10040</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C45" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="D45" s="11" t="s">
+      <c r="D45" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="E45" s="11" t="s">
+      <c r="E45" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="F45" s="11" t="s">
+      <c r="F45" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="G45" s="11" t="s">
+      <c r="G45" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="H45" s="11" t="s">
+      <c r="H45" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="I45" s="11" t="s">
+      <c r="I45" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="J45" s="11" t="s">
+      <c r="J45" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="K45" s="11" t="s">
+      <c r="K45" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="L45" s="11" t="s">
+      <c r="L45" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="M45" s="11" t="s">
+      <c r="M45" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="N45" s="11" t="s">
+      <c r="N45" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="O45" s="11" t="s">
+      <c r="O45" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="P45" s="16" t="s">
+      <c r="P45" s="17" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:23">
-      <c r="B46" s="10">
+      <c r="B46" s="11">
         <v>10041</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C46" s="12" t="s">
         <v>533</v>
       </c>
-      <c r="D46" s="11" t="s">
+      <c r="D46" s="12" t="s">
         <v>533</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E46" s="12" t="s">
         <v>533</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="F46" s="12" t="s">
         <v>533</v>
       </c>
-      <c r="G46" s="11" t="s">
+      <c r="G46" s="12" t="s">
         <v>533</v>
       </c>
-      <c r="H46" s="11" t="s">
+      <c r="H46" s="12" t="s">
         <v>533</v>
       </c>
-      <c r="I46" s="11" t="s">
+      <c r="I46" s="12" t="s">
         <v>533</v>
       </c>
-      <c r="J46" s="11" t="s">
+      <c r="J46" s="12" t="s">
         <v>533</v>
       </c>
-      <c r="K46" s="11" t="s">
+      <c r="K46" s="12" t="s">
         <v>533</v>
       </c>
-      <c r="L46" s="11" t="s">
+      <c r="L46" s="12" t="s">
         <v>533</v>
       </c>
-      <c r="M46" s="11" t="s">
+      <c r="M46" s="12" t="s">
         <v>533</v>
       </c>
-      <c r="N46" s="11" t="s">
+      <c r="N46" s="12" t="s">
         <v>533</v>
       </c>
-      <c r="O46" s="11" t="s">
+      <c r="O46" s="12" t="s">
         <v>533</v>
       </c>
       <c r="P46" t="s">
@@ -9101,2165 +9346,2165 @@
       </c>
     </row>
     <row r="47" customHeight="1" spans="2:23">
-      <c r="B47" s="10">
+      <c r="B47" s="11">
         <v>10042</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="12" t="s">
         <v>534</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D47" s="13" t="s">
         <v>535</v>
       </c>
-      <c r="E47" s="11" t="s">
+      <c r="E47" s="12" t="s">
         <v>536</v>
       </c>
-      <c r="F47" s="11" t="s">
+      <c r="F47" s="12" t="s">
         <v>537</v>
       </c>
-      <c r="G47" s="11" t="s">
+      <c r="G47" s="12" t="s">
         <v>538</v>
       </c>
-      <c r="H47" s="11" t="s">
+      <c r="H47" s="12" t="s">
         <v>539</v>
       </c>
-      <c r="I47" s="11" t="s">
+      <c r="I47" s="12" t="s">
         <v>540</v>
       </c>
-      <c r="J47" s="11" t="s">
+      <c r="J47" s="12" t="s">
         <v>541</v>
       </c>
-      <c r="K47" s="11" t="s">
+      <c r="K47" s="12" t="s">
         <v>542</v>
       </c>
-      <c r="L47" s="11" t="s">
+      <c r="L47" s="12" t="s">
         <v>543</v>
       </c>
-      <c r="M47" s="11" t="s">
+      <c r="M47" s="12" t="s">
         <v>544</v>
       </c>
-      <c r="N47" s="11" t="s">
+      <c r="N47" s="12" t="s">
         <v>545</v>
       </c>
-      <c r="O47" s="11" t="s">
+      <c r="O47" s="12" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="2:23">
-      <c r="B48" s="10">
+      <c r="B48" s="11">
         <v>10043</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C48" s="12" t="s">
         <v>547</v>
       </c>
-      <c r="D48" s="12" t="s">
+      <c r="D48" s="13" t="s">
         <v>548</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E48" s="12" t="s">
         <v>549</v>
       </c>
-      <c r="F48" s="11" t="s">
+      <c r="F48" s="12" t="s">
         <v>550</v>
       </c>
-      <c r="G48" s="11" t="s">
+      <c r="G48" s="12" t="s">
         <v>551</v>
       </c>
-      <c r="H48" s="11" t="s">
+      <c r="H48" s="12" t="s">
         <v>552</v>
       </c>
-      <c r="I48" s="11" t="s">
+      <c r="I48" s="12" t="s">
         <v>553</v>
       </c>
-      <c r="J48" s="11" t="s">
+      <c r="J48" s="12" t="s">
         <v>554</v>
       </c>
-      <c r="K48" s="11" t="s">
+      <c r="K48" s="12" t="s">
         <v>555</v>
       </c>
-      <c r="L48" s="11" t="s">
+      <c r="L48" s="12" t="s">
         <v>556</v>
       </c>
-      <c r="M48" s="11" t="s">
+      <c r="M48" s="12" t="s">
         <v>557</v>
       </c>
-      <c r="N48" s="11" t="s">
+      <c r="N48" s="12" t="s">
         <v>558</v>
       </c>
-      <c r="O48" s="11" t="s">
+      <c r="O48" s="12" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="2:16">
-      <c r="B49" s="10">
+      <c r="B49" s="11">
         <v>10044</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C49" s="12" t="s">
         <v>560</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="D49" s="13" t="s">
         <v>561</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="E49" s="12" t="s">
         <v>562</v>
       </c>
-      <c r="F49" s="11" t="s">
+      <c r="F49" s="12" t="s">
         <v>563</v>
       </c>
-      <c r="G49" s="11" t="s">
+      <c r="G49" s="12" t="s">
         <v>564</v>
       </c>
-      <c r="H49" s="11" t="s">
+      <c r="H49" s="12" t="s">
         <v>565</v>
       </c>
-      <c r="I49" s="11" t="s">
+      <c r="I49" s="12" t="s">
         <v>566</v>
       </c>
-      <c r="J49" s="11" t="s">
+      <c r="J49" s="12" t="s">
         <v>567</v>
       </c>
-      <c r="K49" s="11" t="s">
+      <c r="K49" s="12" t="s">
         <v>568</v>
       </c>
-      <c r="L49" s="11" t="s">
+      <c r="L49" s="12" t="s">
         <v>569</v>
       </c>
-      <c r="M49" s="11" t="s">
+      <c r="M49" s="12" t="s">
         <v>570</v>
       </c>
-      <c r="N49" s="11" t="s">
+      <c r="N49" s="12" t="s">
         <v>571</v>
       </c>
-      <c r="O49" s="11" t="s">
+      <c r="O49" s="12" t="s">
         <v>572</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="2:16">
-      <c r="B50" s="10">
+      <c r="B50" s="11">
         <v>10045</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C50" s="12" t="s">
         <v>573</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="13" t="s">
         <v>574</v>
       </c>
-      <c r="E50" s="11" t="s">
+      <c r="E50" s="12" t="s">
         <v>575</v>
       </c>
-      <c r="F50" s="11" t="s">
+      <c r="F50" s="12" t="s">
         <v>576</v>
       </c>
-      <c r="G50" s="11" t="s">
+      <c r="G50" s="12" t="s">
         <v>577</v>
       </c>
-      <c r="H50" s="11" t="s">
+      <c r="H50" s="12" t="s">
         <v>578</v>
       </c>
-      <c r="I50" s="11" t="s">
+      <c r="I50" s="12" t="s">
         <v>579</v>
       </c>
-      <c r="J50" s="11" t="s">
+      <c r="J50" s="12" t="s">
         <v>580</v>
       </c>
-      <c r="K50" s="11" t="s">
+      <c r="K50" s="12" t="s">
         <v>581</v>
       </c>
-      <c r="L50" s="11" t="s">
+      <c r="L50" s="12" t="s">
         <v>582</v>
       </c>
-      <c r="M50" s="11" t="s">
+      <c r="M50" s="12" t="s">
         <v>583</v>
       </c>
-      <c r="N50" s="11" t="s">
+      <c r="N50" s="12" t="s">
         <v>584</v>
       </c>
-      <c r="O50" s="11" t="s">
+      <c r="O50" s="12" t="s">
         <v>585</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="2:16">
-      <c r="B51" s="10">
+      <c r="B51" s="11">
         <v>10046</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="12" t="s">
         <v>586</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="13" t="s">
         <v>587</v>
       </c>
-      <c r="E51" s="11" t="s">
+      <c r="E51" s="12" t="s">
         <v>588</v>
       </c>
-      <c r="F51" s="11" t="s">
+      <c r="F51" s="12" t="s">
         <v>589</v>
       </c>
-      <c r="G51" s="11" t="s">
+      <c r="G51" s="12" t="s">
         <v>590</v>
       </c>
-      <c r="H51" s="11" t="s">
+      <c r="H51" s="12" t="s">
         <v>591</v>
       </c>
-      <c r="I51" s="11" t="s">
+      <c r="I51" s="12" t="s">
         <v>592</v>
       </c>
-      <c r="J51" s="11" t="s">
+      <c r="J51" s="12" t="s">
         <v>593</v>
       </c>
-      <c r="K51" s="11" t="s">
+      <c r="K51" s="12" t="s">
         <v>594</v>
       </c>
-      <c r="L51" s="11" t="s">
+      <c r="L51" s="12" t="s">
         <v>595</v>
       </c>
-      <c r="M51" s="11" t="s">
+      <c r="M51" s="12" t="s">
         <v>596</v>
       </c>
-      <c r="N51" s="11" t="s">
+      <c r="N51" s="12" t="s">
         <v>597</v>
       </c>
-      <c r="O51" s="11" t="s">
+      <c r="O51" s="12" t="s">
         <v>598</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="2:16">
-      <c r="B52" s="10">
+      <c r="B52" s="11">
         <v>10047</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="C52" s="12" t="s">
         <v>599</v>
       </c>
-      <c r="D52" s="11" t="s">
+      <c r="D52" s="12" t="s">
         <v>600</v>
       </c>
-      <c r="E52" s="11" t="s">
+      <c r="E52" s="12" t="s">
         <v>601</v>
       </c>
-      <c r="F52" s="11" t="s">
+      <c r="F52" s="12" t="s">
         <v>602</v>
       </c>
-      <c r="G52" s="11" t="s">
+      <c r="G52" s="12" t="s">
         <v>603</v>
       </c>
-      <c r="H52" s="11" t="s">
+      <c r="H52" s="12" t="s">
         <v>604</v>
       </c>
-      <c r="I52" s="11" t="s">
+      <c r="I52" s="12" t="s">
         <v>605</v>
       </c>
-      <c r="J52" s="11" t="s">
+      <c r="J52" s="12" t="s">
         <v>606</v>
       </c>
-      <c r="K52" s="11" t="s">
+      <c r="K52" s="12" t="s">
         <v>607</v>
       </c>
-      <c r="L52" s="11" t="s">
+      <c r="L52" s="12" t="s">
         <v>608</v>
       </c>
-      <c r="M52" s="11" t="s">
+      <c r="M52" s="12" t="s">
         <v>609</v>
       </c>
-      <c r="N52" s="11" t="s">
+      <c r="N52" s="12" t="s">
         <v>610</v>
       </c>
-      <c r="O52" s="11" t="s">
+      <c r="O52" s="12" t="s">
         <v>611</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="2:16">
-      <c r="B53" s="10">
+      <c r="B53" s="11">
         <v>10048</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="C53" s="12" t="s">
         <v>612</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D53" s="12" t="s">
         <v>613</v>
       </c>
-      <c r="E53" s="11" t="s">
+      <c r="E53" s="12" t="s">
         <v>614</v>
       </c>
-      <c r="F53" s="11" t="s">
+      <c r="F53" s="12" t="s">
         <v>615</v>
       </c>
-      <c r="G53" s="11" t="s">
+      <c r="G53" s="12" t="s">
         <v>616</v>
       </c>
-      <c r="H53" s="11" t="s">
+      <c r="H53" s="12" t="s">
         <v>617</v>
       </c>
-      <c r="I53" s="11" t="s">
+      <c r="I53" s="12" t="s">
         <v>618</v>
       </c>
-      <c r="J53" s="11" t="s">
+      <c r="J53" s="12" t="s">
         <v>619</v>
       </c>
-      <c r="K53" s="11" t="s">
+      <c r="K53" s="12" t="s">
         <v>620</v>
       </c>
-      <c r="L53" s="11" t="s">
+      <c r="L53" s="12" t="s">
         <v>621</v>
       </c>
-      <c r="M53" s="11" t="s">
+      <c r="M53" s="12" t="s">
         <v>622</v>
       </c>
-      <c r="N53" s="11" t="s">
+      <c r="N53" s="12" t="s">
         <v>623</v>
       </c>
-      <c r="O53" s="11" t="s">
+      <c r="O53" s="12" t="s">
         <v>624</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="2:16">
-      <c r="B54" s="10">
+      <c r="B54" s="11">
         <v>10049</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="C54" s="12" t="s">
         <v>625</v>
       </c>
-      <c r="D54" s="11" t="s">
+      <c r="D54" s="12" t="s">
         <v>626</v>
       </c>
-      <c r="E54" s="11" t="s">
+      <c r="E54" s="12" t="s">
         <v>627</v>
       </c>
-      <c r="F54" s="11" t="s">
+      <c r="F54" s="12" t="s">
         <v>628</v>
       </c>
-      <c r="G54" s="11" t="s">
+      <c r="G54" s="12" t="s">
         <v>629</v>
       </c>
-      <c r="H54" s="11" t="s">
+      <c r="H54" s="12" t="s">
         <v>630</v>
       </c>
-      <c r="I54" s="11" t="s">
+      <c r="I54" s="12" t="s">
         <v>631</v>
       </c>
-      <c r="J54" s="11" t="s">
+      <c r="J54" s="12" t="s">
         <v>632</v>
       </c>
-      <c r="K54" s="11" t="s">
+      <c r="K54" s="12" t="s">
         <v>633</v>
       </c>
-      <c r="L54" s="11" t="s">
+      <c r="L54" s="12" t="s">
         <v>634</v>
       </c>
-      <c r="M54" s="11" t="s">
+      <c r="M54" s="12" t="s">
         <v>635</v>
       </c>
-      <c r="N54" s="11" t="s">
+      <c r="N54" s="12" t="s">
         <v>636</v>
       </c>
-      <c r="O54" s="11" t="s">
+      <c r="O54" s="12" t="s">
         <v>637</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="2:16">
-      <c r="B55" s="10">
+      <c r="B55" s="11">
         <v>10050</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C55" s="12" t="s">
         <v>638</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D55" s="12" t="s">
         <v>639</v>
       </c>
-      <c r="E55" s="11" t="s">
+      <c r="E55" s="12" t="s">
         <v>640</v>
       </c>
-      <c r="F55" s="11" t="s">
+      <c r="F55" s="12" t="s">
         <v>641</v>
       </c>
-      <c r="G55" s="11" t="s">
+      <c r="G55" s="12" t="s">
         <v>642</v>
       </c>
-      <c r="H55" s="11" t="s">
+      <c r="H55" s="12" t="s">
         <v>643</v>
       </c>
-      <c r="I55" s="11" t="s">
+      <c r="I55" s="12" t="s">
         <v>644</v>
       </c>
-      <c r="J55" s="11" t="s">
+      <c r="J55" s="12" t="s">
         <v>645</v>
       </c>
-      <c r="K55" s="11" t="s">
+      <c r="K55" s="12" t="s">
         <v>646</v>
       </c>
-      <c r="L55" s="11" t="s">
+      <c r="L55" s="12" t="s">
         <v>647</v>
       </c>
-      <c r="M55" s="11" t="s">
+      <c r="M55" s="12" t="s">
         <v>648</v>
       </c>
-      <c r="N55" s="11" t="s">
+      <c r="N55" s="12" t="s">
         <v>649</v>
       </c>
-      <c r="O55" s="11" t="s">
+      <c r="O55" s="12" t="s">
         <v>650</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" ht="19" customHeight="1" spans="2:16">
-      <c r="B56" s="10">
+      <c r="B56" s="11">
         <v>10051</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C56" s="12" t="s">
         <v>651</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D56" s="12" t="s">
         <v>652</v>
       </c>
-      <c r="E56" s="11" t="s">
+      <c r="E56" s="12" t="s">
         <v>653</v>
       </c>
-      <c r="F56" s="11" t="s">
+      <c r="F56" s="12" t="s">
         <v>654</v>
       </c>
-      <c r="G56" s="11" t="s">
+      <c r="G56" s="12" t="s">
         <v>655</v>
       </c>
-      <c r="H56" s="11" t="s">
+      <c r="H56" s="12" t="s">
         <v>656</v>
       </c>
-      <c r="I56" s="11" t="s">
+      <c r="I56" s="12" t="s">
         <v>657</v>
       </c>
-      <c r="J56" s="11" t="s">
+      <c r="J56" s="12" t="s">
         <v>658</v>
       </c>
-      <c r="K56" s="11" t="s">
+      <c r="K56" s="12" t="s">
         <v>659</v>
       </c>
-      <c r="L56" s="11" t="s">
+      <c r="L56" s="12" t="s">
         <v>660</v>
       </c>
-      <c r="M56" s="11" t="s">
+      <c r="M56" s="12" t="s">
         <v>661</v>
       </c>
-      <c r="N56" s="11" t="s">
+      <c r="N56" s="12" t="s">
         <v>662</v>
       </c>
-      <c r="O56" s="11" t="s">
+      <c r="O56" s="12" t="s">
         <v>663</v>
       </c>
       <c r="P56"/>
     </row>
     <row r="57" customHeight="1" spans="2:16">
-      <c r="B57" s="10">
+      <c r="B57" s="11">
         <v>10052</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C57" s="12" t="s">
         <v>664</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="D57" s="13" t="s">
         <v>665</v>
       </c>
-      <c r="E57" s="11" t="s">
+      <c r="E57" s="12" t="s">
         <v>666</v>
       </c>
-      <c r="F57" s="11" t="s">
+      <c r="F57" s="12" t="s">
         <v>667</v>
       </c>
-      <c r="G57" s="11" t="s">
+      <c r="G57" s="12" t="s">
         <v>668</v>
       </c>
-      <c r="H57" s="11" t="s">
+      <c r="H57" s="12" t="s">
         <v>669</v>
       </c>
-      <c r="I57" s="11" t="s">
+      <c r="I57" s="12" t="s">
         <v>670</v>
       </c>
-      <c r="J57" s="11" t="s">
+      <c r="J57" s="12" t="s">
         <v>671</v>
       </c>
-      <c r="K57" s="11" t="s">
+      <c r="K57" s="12" t="s">
         <v>672</v>
       </c>
-      <c r="L57" s="11" t="s">
+      <c r="L57" s="12" t="s">
         <v>673</v>
       </c>
-      <c r="M57" s="11" t="s">
+      <c r="M57" s="12" t="s">
         <v>674</v>
       </c>
-      <c r="N57" s="11" t="s">
+      <c r="N57" s="12" t="s">
         <v>675</v>
       </c>
-      <c r="O57" s="11" t="s">
+      <c r="O57" s="12" t="s">
         <v>676</v>
       </c>
       <c r="P57" s="1"/>
     </row>
     <row r="58" customHeight="1" spans="2:16">
-      <c r="B58" s="10">
+      <c r="B58" s="11">
         <v>10053</v>
       </c>
-      <c r="C58" s="11" t="s">
+      <c r="C58" s="12" t="s">
         <v>677</v>
       </c>
-      <c r="D58" s="12" t="s">
+      <c r="D58" s="13" t="s">
         <v>678</v>
       </c>
-      <c r="E58" s="11" t="s">
+      <c r="E58" s="12" t="s">
         <v>679</v>
       </c>
-      <c r="F58" s="11" t="s">
+      <c r="F58" s="12" t="s">
         <v>680</v>
       </c>
-      <c r="G58" s="11" t="s">
+      <c r="G58" s="12" t="s">
         <v>681</v>
       </c>
-      <c r="H58" s="11" t="s">
+      <c r="H58" s="12" t="s">
         <v>682</v>
       </c>
-      <c r="I58" s="11" t="s">
+      <c r="I58" s="12" t="s">
         <v>683</v>
       </c>
-      <c r="J58" s="11" t="s">
+      <c r="J58" s="12" t="s">
         <v>684</v>
       </c>
-      <c r="K58" s="11" t="s">
+      <c r="K58" s="12" t="s">
         <v>685</v>
       </c>
-      <c r="L58" s="11" t="s">
+      <c r="L58" s="12" t="s">
         <v>686</v>
       </c>
-      <c r="M58" s="11" t="s">
+      <c r="M58" s="12" t="s">
         <v>687</v>
       </c>
-      <c r="N58" s="11" t="s">
+      <c r="N58" s="12" t="s">
         <v>688</v>
       </c>
-      <c r="O58" s="11" t="s">
+      <c r="O58" s="12" t="s">
         <v>689</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:16">
-      <c r="B59" s="10">
+      <c r="B59" s="11">
         <v>10054</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C59" s="12" t="s">
         <v>690</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="D59" s="13" t="s">
         <v>691</v>
       </c>
-      <c r="E59" s="11" t="s">
+      <c r="E59" s="12" t="s">
         <v>692</v>
       </c>
-      <c r="F59" s="11" t="s">
+      <c r="F59" s="12" t="s">
         <v>693</v>
       </c>
-      <c r="G59" s="11" t="s">
+      <c r="G59" s="12" t="s">
         <v>694</v>
       </c>
-      <c r="H59" s="11" t="s">
+      <c r="H59" s="12" t="s">
         <v>695</v>
       </c>
-      <c r="I59" s="11" t="s">
+      <c r="I59" s="12" t="s">
         <v>696</v>
       </c>
-      <c r="J59" s="11" t="s">
+      <c r="J59" s="12" t="s">
         <v>697</v>
       </c>
-      <c r="K59" s="11" t="s">
+      <c r="K59" s="12" t="s">
         <v>698</v>
       </c>
-      <c r="L59" s="11" t="s">
+      <c r="L59" s="12" t="s">
         <v>699</v>
       </c>
-      <c r="M59" s="11" t="s">
+      <c r="M59" s="12" t="s">
         <v>700</v>
       </c>
-      <c r="N59" s="11" t="s">
+      <c r="N59" s="12" t="s">
         <v>701</v>
       </c>
-      <c r="O59" s="11" t="s">
+      <c r="O59" s="12" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:16">
-      <c r="B60" s="10">
+      <c r="B60" s="11">
         <v>10055</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="C60" s="13" t="s">
         <v>703</v>
       </c>
-      <c r="D60" s="11" t="s">
+      <c r="D60" s="12" t="s">
         <v>704</v>
       </c>
-      <c r="E60" s="11" t="s">
+      <c r="E60" s="12" t="s">
         <v>705</v>
       </c>
-      <c r="F60" s="11" t="s">
+      <c r="F60" s="12" t="s">
         <v>706</v>
       </c>
-      <c r="G60" s="11" t="s">
+      <c r="G60" s="12" t="s">
         <v>707</v>
       </c>
-      <c r="H60" s="11" t="s">
+      <c r="H60" s="12" t="s">
         <v>708</v>
       </c>
-      <c r="I60" s="11" t="s">
+      <c r="I60" s="12" t="s">
         <v>709</v>
       </c>
-      <c r="J60" s="11" t="s">
+      <c r="J60" s="12" t="s">
         <v>710</v>
       </c>
-      <c r="K60" s="11" t="s">
+      <c r="K60" s="12" t="s">
         <v>711</v>
       </c>
-      <c r="L60" s="11" t="s">
+      <c r="L60" s="12" t="s">
         <v>712</v>
       </c>
-      <c r="M60" s="11" t="s">
+      <c r="M60" s="12" t="s">
         <v>713</v>
       </c>
-      <c r="N60" s="11" t="s">
+      <c r="N60" s="12" t="s">
         <v>714</v>
       </c>
-      <c r="O60" s="11" t="s">
+      <c r="O60" s="12" t="s">
         <v>715</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:16">
-      <c r="B61" s="10">
+      <c r="B61" s="11">
         <v>10056</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C61" s="12" t="s">
         <v>716</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="D61" s="13" t="s">
         <v>717</v>
       </c>
-      <c r="E61" s="11" t="s">
+      <c r="E61" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="F61" s="11" t="s">
+      <c r="F61" s="12" t="s">
         <v>719</v>
       </c>
-      <c r="G61" s="11" t="s">
+      <c r="G61" s="12" t="s">
         <v>720</v>
       </c>
-      <c r="H61" s="11" t="s">
+      <c r="H61" s="12" t="s">
         <v>721</v>
       </c>
-      <c r="I61" s="11" t="s">
+      <c r="I61" s="12" t="s">
         <v>722</v>
       </c>
-      <c r="J61" s="11" t="s">
+      <c r="J61" s="12" t="s">
         <v>723</v>
       </c>
-      <c r="K61" s="11" t="s">
+      <c r="K61" s="12" t="s">
         <v>724</v>
       </c>
-      <c r="L61" s="11" t="s">
+      <c r="L61" s="12" t="s">
         <v>725</v>
       </c>
-      <c r="M61" s="11" t="s">
+      <c r="M61" s="12" t="s">
         <v>726</v>
       </c>
-      <c r="N61" s="11" t="s">
+      <c r="N61" s="12" t="s">
         <v>727</v>
       </c>
-      <c r="O61" s="11" t="s">
+      <c r="O61" s="12" t="s">
         <v>728</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:16">
-      <c r="B62" s="10">
+      <c r="B62" s="11">
         <v>10057</v>
       </c>
-      <c r="C62" s="11" t="s">
+      <c r="C62" s="12" t="s">
         <v>729</v>
       </c>
-      <c r="D62" s="11" t="s">
+      <c r="D62" s="12" t="s">
         <v>730</v>
       </c>
-      <c r="E62" s="11" t="s">
+      <c r="E62" s="12" t="s">
         <v>731</v>
       </c>
-      <c r="F62" s="11" t="s">
+      <c r="F62" s="12" t="s">
         <v>732</v>
       </c>
-      <c r="G62" s="11" t="s">
+      <c r="G62" s="12" t="s">
         <v>733</v>
       </c>
-      <c r="H62" s="11" t="s">
+      <c r="H62" s="12" t="s">
         <v>734</v>
       </c>
-      <c r="I62" s="11" t="s">
+      <c r="I62" s="12" t="s">
         <v>735</v>
       </c>
-      <c r="J62" s="11" t="s">
+      <c r="J62" s="12" t="s">
         <v>736</v>
       </c>
-      <c r="K62" s="11" t="s">
+      <c r="K62" s="12" t="s">
         <v>737</v>
       </c>
-      <c r="L62" s="11" t="s">
+      <c r="L62" s="12" t="s">
         <v>738</v>
       </c>
-      <c r="M62" s="11" t="s">
+      <c r="M62" s="12" t="s">
         <v>739</v>
       </c>
-      <c r="N62" s="11" t="s">
+      <c r="N62" s="12" t="s">
         <v>740</v>
       </c>
-      <c r="O62" s="11" t="s">
+      <c r="O62" s="12" t="s">
         <v>741</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:16">
-      <c r="B63" s="10">
+      <c r="B63" s="11">
         <v>10058</v>
       </c>
-      <c r="C63" s="11" t="s">
+      <c r="C63" s="12" t="s">
         <v>742</v>
       </c>
-      <c r="D63" s="11" t="s">
+      <c r="D63" s="12" t="s">
         <v>743</v>
       </c>
-      <c r="E63" s="11" t="s">
+      <c r="E63" s="12" t="s">
         <v>744</v>
       </c>
-      <c r="F63" s="11" t="s">
+      <c r="F63" s="12" t="s">
         <v>745</v>
       </c>
-      <c r="G63" s="11" t="s">
+      <c r="G63" s="12" t="s">
         <v>746</v>
       </c>
-      <c r="H63" s="11" t="s">
+      <c r="H63" s="12" t="s">
         <v>747</v>
       </c>
-      <c r="I63" s="11" t="s">
+      <c r="I63" s="12" t="s">
         <v>748</v>
       </c>
-      <c r="J63" s="11" t="s">
+      <c r="J63" s="12" t="s">
         <v>749</v>
       </c>
-      <c r="K63" s="11" t="s">
+      <c r="K63" s="12" t="s">
         <v>750</v>
       </c>
-      <c r="L63" s="11" t="s">
+      <c r="L63" s="12" t="s">
         <v>751</v>
       </c>
-      <c r="M63" s="11" t="s">
+      <c r="M63" s="12" t="s">
         <v>752</v>
       </c>
-      <c r="N63" s="11" t="s">
+      <c r="N63" s="12" t="s">
         <v>753</v>
       </c>
-      <c r="O63" s="11" t="s">
+      <c r="O63" s="12" t="s">
         <v>754</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:16">
-      <c r="B64" s="10">
+      <c r="B64" s="11">
         <v>10059</v>
       </c>
-      <c r="C64" s="11" t="s">
+      <c r="C64" s="12" t="s">
         <v>755</v>
       </c>
-      <c r="D64" s="11" t="s">
+      <c r="D64" s="12" t="s">
         <v>756</v>
       </c>
-      <c r="E64" s="11" t="s">
+      <c r="E64" s="12" t="s">
         <v>757</v>
       </c>
-      <c r="F64" s="11" t="s">
+      <c r="F64" s="12" t="s">
         <v>758</v>
       </c>
-      <c r="G64" s="11" t="s">
+      <c r="G64" s="12" t="s">
         <v>759</v>
       </c>
-      <c r="H64" s="11" t="s">
+      <c r="H64" s="12" t="s">
         <v>760</v>
       </c>
-      <c r="I64" s="11" t="s">
+      <c r="I64" s="12" t="s">
         <v>761</v>
       </c>
-      <c r="J64" s="11" t="s">
+      <c r="J64" s="12" t="s">
         <v>762</v>
       </c>
-      <c r="K64" s="11" t="s">
+      <c r="K64" s="12" t="s">
         <v>763</v>
       </c>
-      <c r="L64" s="11" t="s">
+      <c r="L64" s="12" t="s">
         <v>764</v>
       </c>
-      <c r="M64" s="11" t="s">
+      <c r="M64" s="12" t="s">
         <v>765</v>
       </c>
-      <c r="N64" s="11" t="s">
+      <c r="N64" s="12" t="s">
         <v>766</v>
       </c>
-      <c r="O64" s="11" t="s">
+      <c r="O64" s="12" t="s">
         <v>767</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="2:15">
-      <c r="B65" s="10">
+      <c r="B65" s="11">
         <v>10060</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="C65" s="12" t="s">
         <v>768</v>
       </c>
-      <c r="D65" s="11" t="s">
+      <c r="D65" s="12" t="s">
         <v>769</v>
       </c>
-      <c r="E65" s="11" t="s">
+      <c r="E65" s="12" t="s">
         <v>770</v>
       </c>
-      <c r="F65" s="11" t="s">
+      <c r="F65" s="12" t="s">
         <v>771</v>
       </c>
-      <c r="G65" s="11" t="s">
+      <c r="G65" s="12" t="s">
         <v>772</v>
       </c>
-      <c r="H65" s="11" t="s">
+      <c r="H65" s="12" t="s">
         <v>773</v>
       </c>
-      <c r="I65" s="11" t="s">
+      <c r="I65" s="12" t="s">
         <v>774</v>
       </c>
-      <c r="J65" s="11" t="s">
+      <c r="J65" s="12" t="s">
         <v>775</v>
       </c>
-      <c r="K65" s="11" t="s">
+      <c r="K65" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L65" s="11" t="s">
+      <c r="L65" s="12" t="s">
         <v>777</v>
       </c>
-      <c r="M65" s="11" t="s">
+      <c r="M65" s="12" t="s">
         <v>778</v>
       </c>
-      <c r="N65" s="11" t="s">
+      <c r="N65" s="12" t="s">
         <v>779</v>
       </c>
-      <c r="O65" s="11" t="s">
+      <c r="O65" s="12" t="s">
         <v>780</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="2:15">
-      <c r="B66" s="10">
+      <c r="B66" s="11">
         <v>10061</v>
       </c>
-      <c r="C66" s="11" t="s">
+      <c r="C66" s="12" t="s">
         <v>781</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="D66" s="12" t="s">
         <v>782</v>
       </c>
-      <c r="E66" s="11" t="s">
+      <c r="E66" s="12" t="s">
         <v>783</v>
       </c>
-      <c r="F66" s="11" t="s">
+      <c r="F66" s="12" t="s">
         <v>784</v>
       </c>
-      <c r="G66" s="11" t="s">
+      <c r="G66" s="12" t="s">
         <v>785</v>
       </c>
-      <c r="H66" s="11" t="s">
+      <c r="H66" s="12" t="s">
         <v>786</v>
       </c>
-      <c r="I66" s="11" t="s">
+      <c r="I66" s="12" t="s">
         <v>787</v>
       </c>
-      <c r="J66" s="11" t="s">
+      <c r="J66" s="12" t="s">
         <v>788</v>
       </c>
-      <c r="K66" s="11" t="s">
+      <c r="K66" s="12" t="s">
         <v>789</v>
       </c>
-      <c r="L66" s="11" t="s">
+      <c r="L66" s="12" t="s">
         <v>790</v>
       </c>
-      <c r="M66" s="11" t="s">
+      <c r="M66" s="12" t="s">
         <v>791</v>
       </c>
-      <c r="N66" s="11" t="s">
+      <c r="N66" s="12" t="s">
         <v>792</v>
       </c>
-      <c r="O66" s="11" t="s">
+      <c r="O66" s="12" t="s">
         <v>793</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="2:15">
-      <c r="B67" s="10">
+      <c r="B67" s="11">
         <v>10062</v>
       </c>
-      <c r="C67" s="11" t="s">
+      <c r="C67" s="12" t="s">
         <v>794</v>
       </c>
-      <c r="D67" s="11" t="s">
+      <c r="D67" s="12" t="s">
         <v>795</v>
       </c>
-      <c r="E67" s="11" t="s">
+      <c r="E67" s="12" t="s">
         <v>796</v>
       </c>
-      <c r="F67" s="11" t="s">
+      <c r="F67" s="12" t="s">
         <v>797</v>
       </c>
-      <c r="G67" s="11" t="s">
+      <c r="G67" s="12" t="s">
         <v>798</v>
       </c>
-      <c r="H67" s="11" t="s">
+      <c r="H67" s="12" t="s">
         <v>799</v>
       </c>
-      <c r="I67" s="11" t="s">
+      <c r="I67" s="12" t="s">
         <v>800</v>
       </c>
-      <c r="J67" s="11" t="s">
+      <c r="J67" s="12" t="s">
         <v>801</v>
       </c>
-      <c r="K67" s="11" t="s">
+      <c r="K67" s="12" t="s">
         <v>802</v>
       </c>
-      <c r="L67" s="11" t="s">
+      <c r="L67" s="12" t="s">
         <v>803</v>
       </c>
-      <c r="M67" s="11" t="s">
+      <c r="M67" s="12" t="s">
         <v>804</v>
       </c>
-      <c r="N67" s="11" t="s">
+      <c r="N67" s="12" t="s">
         <v>805</v>
       </c>
-      <c r="O67" s="11" t="s">
+      <c r="O67" s="12" t="s">
         <v>806</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="2:15">
-      <c r="B68" s="10">
+      <c r="B68" s="11">
         <v>10063</v>
       </c>
-      <c r="C68" s="11" t="s">
+      <c r="C68" s="12" t="s">
         <v>807</v>
       </c>
-      <c r="D68" s="12" t="s">
+      <c r="D68" s="13" t="s">
         <v>808</v>
       </c>
-      <c r="E68" s="11" t="s">
+      <c r="E68" s="12" t="s">
         <v>808</v>
       </c>
-      <c r="F68" s="11" t="s">
+      <c r="F68" s="12" t="s">
         <v>809</v>
       </c>
-      <c r="G68" s="11" t="s">
+      <c r="G68" s="12" t="s">
         <v>808</v>
       </c>
-      <c r="H68" s="11" t="s">
+      <c r="H68" s="12" t="s">
         <v>810</v>
       </c>
-      <c r="I68" s="11" t="s">
+      <c r="I68" s="12" t="s">
         <v>811</v>
       </c>
-      <c r="J68" s="11" t="s">
+      <c r="J68" s="12" t="s">
         <v>812</v>
       </c>
-      <c r="K68" s="11" t="s">
+      <c r="K68" s="12" t="s">
         <v>813</v>
       </c>
-      <c r="L68" s="11" t="s">
+      <c r="L68" s="12" t="s">
         <v>814</v>
       </c>
-      <c r="M68" s="11" t="s">
+      <c r="M68" s="12" t="s">
         <v>815</v>
       </c>
-      <c r="N68" s="11" t="s">
+      <c r="N68" s="12" t="s">
         <v>816</v>
       </c>
-      <c r="O68" s="11" t="s">
+      <c r="O68" s="12" t="s">
         <v>817</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="2:15">
-      <c r="B69" s="10">
+      <c r="B69" s="11">
         <v>10064</v>
       </c>
-      <c r="C69" s="11" t="s">
+      <c r="C69" s="12" t="s">
         <v>818</v>
       </c>
-      <c r="D69" s="11" t="s">
+      <c r="D69" s="12" t="s">
         <v>819</v>
       </c>
-      <c r="E69" s="11" t="s">
+      <c r="E69" s="12" t="s">
         <v>820</v>
       </c>
-      <c r="F69" s="11" t="s">
+      <c r="F69" s="12" t="s">
         <v>821</v>
       </c>
-      <c r="G69" s="11" t="s">
+      <c r="G69" s="12" t="s">
         <v>822</v>
       </c>
-      <c r="H69" s="11" t="s">
+      <c r="H69" s="12" t="s">
         <v>823</v>
       </c>
-      <c r="I69" s="11" t="s">
+      <c r="I69" s="12" t="s">
         <v>824</v>
       </c>
-      <c r="J69" s="11" t="s">
+      <c r="J69" s="12" t="s">
         <v>825</v>
       </c>
-      <c r="K69" s="11" t="s">
+      <c r="K69" s="12" t="s">
         <v>826</v>
       </c>
-      <c r="L69" s="11" t="s">
+      <c r="L69" s="12" t="s">
         <v>827</v>
       </c>
-      <c r="M69" s="11" t="s">
+      <c r="M69" s="12" t="s">
         <v>828</v>
       </c>
-      <c r="N69" s="11" t="s">
+      <c r="N69" s="12" t="s">
         <v>829</v>
       </c>
-      <c r="O69" s="11" t="s">
+      <c r="O69" s="12" t="s">
         <v>830</v>
       </c>
     </row>
     <row r="70" ht="19" customHeight="1" spans="2:15">
-      <c r="B70" s="10">
+      <c r="B70" s="11">
         <v>10065</v>
       </c>
-      <c r="C70" s="11" t="s">
+      <c r="C70" s="12" t="s">
         <v>831</v>
       </c>
-      <c r="D70" s="11" t="s">
+      <c r="D70" s="12" t="s">
         <v>832</v>
       </c>
-      <c r="E70" s="11" t="s">
+      <c r="E70" s="12" t="s">
         <v>833</v>
       </c>
-      <c r="F70" s="11" t="s">
+      <c r="F70" s="12" t="s">
         <v>834</v>
       </c>
-      <c r="G70" s="11" t="s">
+      <c r="G70" s="12" t="s">
         <v>835</v>
       </c>
-      <c r="H70" s="11" t="s">
+      <c r="H70" s="12" t="s">
         <v>836</v>
       </c>
-      <c r="I70" s="11" t="s">
+      <c r="I70" s="12" t="s">
         <v>835</v>
       </c>
-      <c r="J70" s="11" t="s">
+      <c r="J70" s="12" t="s">
         <v>837</v>
       </c>
-      <c r="K70" s="11" t="s">
+      <c r="K70" s="12" t="s">
         <v>838</v>
       </c>
-      <c r="L70" s="11" t="s">
+      <c r="L70" s="12" t="s">
         <v>839</v>
       </c>
-      <c r="M70" s="11" t="s">
+      <c r="M70" s="12" t="s">
         <v>840</v>
       </c>
-      <c r="N70" s="11" t="s">
+      <c r="N70" s="12" t="s">
         <v>841</v>
       </c>
-      <c r="O70" s="11" t="s">
+      <c r="O70" s="12" t="s">
         <v>842</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="2:15">
-      <c r="B71" s="10">
+      <c r="B71" s="11">
         <v>10066</v>
       </c>
-      <c r="C71" s="11" t="s">
+      <c r="C71" s="12" t="s">
         <v>843</v>
       </c>
-      <c r="D71" s="12" t="s">
+      <c r="D71" s="13" t="s">
         <v>844</v>
       </c>
-      <c r="E71" s="11" t="s">
+      <c r="E71" s="12" t="s">
         <v>845</v>
       </c>
-      <c r="F71" s="11" t="s">
+      <c r="F71" s="12" t="s">
         <v>846</v>
       </c>
-      <c r="G71" s="11" t="s">
+      <c r="G71" s="12" t="s">
         <v>847</v>
       </c>
-      <c r="H71" s="11" t="s">
+      <c r="H71" s="12" t="s">
         <v>848</v>
       </c>
-      <c r="I71" s="11" t="s">
+      <c r="I71" s="12" t="s">
         <v>847</v>
       </c>
-      <c r="J71" s="11" t="s">
+      <c r="J71" s="12" t="s">
         <v>849</v>
       </c>
-      <c r="K71" s="11" t="s">
+      <c r="K71" s="12" t="s">
         <v>850</v>
       </c>
-      <c r="L71" s="11" t="s">
+      <c r="L71" s="12" t="s">
         <v>851</v>
       </c>
-      <c r="M71" s="11" t="s">
+      <c r="M71" s="12" t="s">
         <v>852</v>
       </c>
-      <c r="N71" s="11" t="s">
+      <c r="N71" s="12" t="s">
         <v>853</v>
       </c>
-      <c r="O71" s="11" t="s">
+      <c r="O71" s="12" t="s">
         <v>854</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="2:15">
-      <c r="B72" s="10">
+      <c r="B72" s="11">
         <v>10067</v>
       </c>
-      <c r="C72" s="11" t="s">
+      <c r="C72" s="12" t="s">
         <v>855</v>
       </c>
-      <c r="D72" s="12" t="s">
+      <c r="D72" s="13" t="s">
         <v>856</v>
       </c>
-      <c r="E72" s="11" t="s">
+      <c r="E72" s="12" t="s">
         <v>857</v>
       </c>
-      <c r="F72" s="11" t="s">
+      <c r="F72" s="12" t="s">
         <v>858</v>
       </c>
-      <c r="G72" s="11" t="s">
+      <c r="G72" s="12" t="s">
         <v>859</v>
       </c>
-      <c r="H72" s="11" t="s">
+      <c r="H72" s="12" t="s">
         <v>860</v>
       </c>
-      <c r="I72" s="11" t="s">
+      <c r="I72" s="12" t="s">
         <v>859</v>
       </c>
-      <c r="J72" s="11" t="s">
+      <c r="J72" s="12" t="s">
         <v>861</v>
       </c>
-      <c r="K72" s="11" t="s">
+      <c r="K72" s="12" t="s">
         <v>859</v>
       </c>
-      <c r="L72" s="11" t="s">
+      <c r="L72" s="12" t="s">
         <v>862</v>
       </c>
-      <c r="M72" s="11" t="s">
+      <c r="M72" s="12" t="s">
         <v>863</v>
       </c>
-      <c r="N72" s="11" t="s">
+      <c r="N72" s="12" t="s">
         <v>864</v>
       </c>
-      <c r="O72" s="11" t="s">
+      <c r="O72" s="12" t="s">
         <v>865</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="2:15">
-      <c r="B73" s="10">
+      <c r="B73" s="11">
         <v>10068</v>
       </c>
-      <c r="C73" s="11" t="s">
+      <c r="C73" s="12" t="s">
         <v>866</v>
       </c>
-      <c r="D73" s="12" t="s">
+      <c r="D73" s="13" t="s">
         <v>867</v>
       </c>
-      <c r="E73" s="11" t="s">
+      <c r="E73" s="12" t="s">
         <v>868</v>
       </c>
-      <c r="F73" s="11" t="s">
+      <c r="F73" s="12" t="s">
         <v>869</v>
       </c>
-      <c r="G73" s="11" t="s">
+      <c r="G73" s="12" t="s">
         <v>870</v>
       </c>
-      <c r="H73" s="11" t="s">
+      <c r="H73" s="12" t="s">
         <v>871</v>
       </c>
-      <c r="I73" s="11" t="s">
+      <c r="I73" s="12" t="s">
         <v>872</v>
       </c>
-      <c r="J73" s="11" t="s">
+      <c r="J73" s="12" t="s">
         <v>873</v>
       </c>
-      <c r="K73" s="11" t="s">
+      <c r="K73" s="12" t="s">
         <v>874</v>
       </c>
-      <c r="L73" s="11" t="s">
+      <c r="L73" s="12" t="s">
         <v>875</v>
       </c>
-      <c r="M73" s="11" t="s">
+      <c r="M73" s="12" t="s">
         <v>876</v>
       </c>
-      <c r="N73" s="11" t="s">
+      <c r="N73" s="12" t="s">
         <v>877</v>
       </c>
-      <c r="O73" s="11" t="s">
+      <c r="O73" s="12" t="s">
         <v>878</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="2:15">
-      <c r="B74" s="10">
+      <c r="B74" s="11">
         <v>10069</v>
       </c>
-      <c r="C74" s="11" t="s">
+      <c r="C74" s="12" t="s">
         <v>879</v>
       </c>
-      <c r="D74" s="12" t="s">
+      <c r="D74" s="13" t="s">
         <v>880</v>
       </c>
-      <c r="E74" s="11" t="s">
+      <c r="E74" s="12" t="s">
         <v>881</v>
       </c>
-      <c r="F74" s="11" t="s">
+      <c r="F74" s="12" t="s">
         <v>882</v>
       </c>
-      <c r="G74" s="11" t="s">
+      <c r="G74" s="12" t="s">
         <v>883</v>
       </c>
-      <c r="H74" s="11" t="s">
+      <c r="H74" s="12" t="s">
         <v>884</v>
       </c>
-      <c r="I74" s="11" t="s">
+      <c r="I74" s="12" t="s">
         <v>885</v>
       </c>
-      <c r="J74" s="11" t="s">
+      <c r="J74" s="12" t="s">
         <v>886</v>
       </c>
-      <c r="K74" s="11" t="s">
+      <c r="K74" s="12" t="s">
         <v>887</v>
       </c>
-      <c r="L74" s="11" t="s">
+      <c r="L74" s="12" t="s">
         <v>888</v>
       </c>
-      <c r="M74" s="11" t="s">
+      <c r="M74" s="12" t="s">
         <v>889</v>
       </c>
-      <c r="N74" s="11" t="s">
+      <c r="N74" s="12" t="s">
         <v>890</v>
       </c>
-      <c r="O74" s="11" t="s">
+      <c r="O74" s="12" t="s">
         <v>891</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="2:15">
-      <c r="B75" s="10">
+      <c r="B75" s="11">
         <v>10070</v>
       </c>
-      <c r="C75" s="11" t="s">
+      <c r="C75" s="12" t="s">
         <v>892</v>
       </c>
-      <c r="D75" s="11" t="s">
+      <c r="D75" s="12" t="s">
         <v>893</v>
       </c>
-      <c r="E75" s="11" t="s">
+      <c r="E75" s="12" t="s">
         <v>894</v>
       </c>
-      <c r="F75" s="11" t="s">
+      <c r="F75" s="12" t="s">
         <v>895</v>
       </c>
-      <c r="G75" s="11" t="s">
+      <c r="G75" s="12" t="s">
         <v>896</v>
       </c>
-      <c r="H75" s="11" t="s">
+      <c r="H75" s="12" t="s">
         <v>897</v>
       </c>
-      <c r="I75" s="11" t="s">
+      <c r="I75" s="12" t="s">
         <v>898</v>
       </c>
-      <c r="J75" s="11" t="s">
+      <c r="J75" s="12" t="s">
         <v>899</v>
       </c>
-      <c r="K75" s="11" t="s">
+      <c r="K75" s="12" t="s">
         <v>900</v>
       </c>
-      <c r="L75" s="11" t="s">
+      <c r="L75" s="12" t="s">
         <v>901</v>
       </c>
-      <c r="M75" s="11" t="s">
+      <c r="M75" s="12" t="s">
         <v>902</v>
       </c>
-      <c r="N75" s="11" t="s">
+      <c r="N75" s="12" t="s">
         <v>903</v>
       </c>
-      <c r="O75" s="11" t="s">
+      <c r="O75" s="12" t="s">
         <v>904</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="2:15">
-      <c r="B76" s="10">
+      <c r="B76" s="11">
         <v>10071</v>
       </c>
-      <c r="C76" s="11" t="s">
+      <c r="C76" s="12" t="s">
         <v>905</v>
       </c>
-      <c r="D76" s="11" t="s">
+      <c r="D76" s="12" t="s">
         <v>906</v>
       </c>
-      <c r="E76" s="11" t="s">
+      <c r="E76" s="12" t="s">
         <v>907</v>
       </c>
-      <c r="F76" s="11" t="s">
+      <c r="F76" s="12" t="s">
         <v>908</v>
       </c>
-      <c r="G76" s="11" t="s">
+      <c r="G76" s="12" t="s">
         <v>909</v>
       </c>
-      <c r="H76" s="11" t="s">
+      <c r="H76" s="12" t="s">
         <v>910</v>
       </c>
-      <c r="I76" s="11" t="s">
+      <c r="I76" s="12" t="s">
         <v>911</v>
       </c>
-      <c r="J76" s="11" t="s">
+      <c r="J76" s="12" t="s">
         <v>912</v>
       </c>
-      <c r="K76" s="11" t="s">
+      <c r="K76" s="12" t="s">
         <v>913</v>
       </c>
-      <c r="L76" s="11" t="s">
+      <c r="L76" s="12" t="s">
         <v>914</v>
       </c>
-      <c r="M76" s="11" t="s">
+      <c r="M76" s="12" t="s">
         <v>915</v>
       </c>
-      <c r="N76" s="11" t="s">
+      <c r="N76" s="12" t="s">
         <v>916</v>
       </c>
-      <c r="O76" s="11" t="s">
+      <c r="O76" s="12" t="s">
         <v>917</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="2:15">
-      <c r="B77" s="10">
+      <c r="B77" s="11">
         <v>10072</v>
       </c>
-      <c r="C77" s="11" t="s">
+      <c r="C77" s="12" t="s">
         <v>918</v>
       </c>
-      <c r="D77" s="11" t="s">
+      <c r="D77" s="12" t="s">
         <v>919</v>
       </c>
-      <c r="E77" s="11" t="s">
+      <c r="E77" s="12" t="s">
         <v>920</v>
       </c>
-      <c r="F77" s="11" t="s">
+      <c r="F77" s="12" t="s">
         <v>921</v>
       </c>
-      <c r="G77" s="11" t="s">
+      <c r="G77" s="12" t="s">
         <v>922</v>
       </c>
-      <c r="H77" s="11" t="s">
+      <c r="H77" s="12" t="s">
         <v>923</v>
       </c>
-      <c r="I77" s="11" t="s">
+      <c r="I77" s="12" t="s">
         <v>924</v>
       </c>
-      <c r="J77" s="11" t="s">
+      <c r="J77" s="12" t="s">
         <v>925</v>
       </c>
-      <c r="K77" s="11" t="s">
+      <c r="K77" s="12" t="s">
         <v>926</v>
       </c>
-      <c r="L77" s="11" t="s">
+      <c r="L77" s="12" t="s">
         <v>927</v>
       </c>
-      <c r="M77" s="11" t="s">
+      <c r="M77" s="12" t="s">
         <v>928</v>
       </c>
-      <c r="N77" s="11" t="s">
+      <c r="N77" s="12" t="s">
         <v>929</v>
       </c>
-      <c r="O77" s="11" t="s">
+      <c r="O77" s="12" t="s">
         <v>930</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="2:15">
-      <c r="B78" s="10">
+      <c r="B78" s="11">
         <v>10073</v>
       </c>
-      <c r="C78" s="11" t="s">
+      <c r="C78" s="12" t="s">
         <v>931</v>
       </c>
-      <c r="D78" s="12" t="s">
+      <c r="D78" s="13" t="s">
         <v>932</v>
       </c>
-      <c r="E78" s="11" t="s">
+      <c r="E78" s="12" t="s">
         <v>933</v>
       </c>
-      <c r="F78" s="11" t="s">
+      <c r="F78" s="12" t="s">
         <v>934</v>
       </c>
-      <c r="G78" s="11" t="s">
+      <c r="G78" s="12" t="s">
         <v>935</v>
       </c>
-      <c r="H78" s="11" t="s">
+      <c r="H78" s="12" t="s">
         <v>936</v>
       </c>
-      <c r="I78" s="11" t="s">
+      <c r="I78" s="12" t="s">
         <v>937</v>
       </c>
-      <c r="J78" s="11" t="s">
+      <c r="J78" s="12" t="s">
         <v>938</v>
       </c>
-      <c r="K78" s="11" t="s">
+      <c r="K78" s="12" t="s">
         <v>939</v>
       </c>
-      <c r="L78" s="11" t="s">
+      <c r="L78" s="12" t="s">
         <v>940</v>
       </c>
-      <c r="M78" s="11" t="s">
+      <c r="M78" s="12" t="s">
         <v>941</v>
       </c>
-      <c r="N78" s="11" t="s">
+      <c r="N78" s="12" t="s">
         <v>942</v>
       </c>
-      <c r="O78" s="11" t="s">
+      <c r="O78" s="12" t="s">
         <v>943</v>
       </c>
     </row>
     <row r="79" ht="19" customHeight="1" spans="2:15">
-      <c r="B79" s="10">
+      <c r="B79" s="11">
         <v>10074</v>
       </c>
-      <c r="C79" s="12" t="s">
+      <c r="C79" s="13" t="s">
         <v>944</v>
       </c>
-      <c r="D79" s="12" t="s">
+      <c r="D79" s="13" t="s">
         <v>945</v>
       </c>
-      <c r="E79" s="11" t="s">
+      <c r="E79" s="12" t="s">
         <v>946</v>
       </c>
-      <c r="F79" s="11" t="s">
+      <c r="F79" s="12" t="s">
         <v>947</v>
       </c>
-      <c r="G79" s="11" t="s">
+      <c r="G79" s="12" t="s">
         <v>948</v>
       </c>
-      <c r="H79" s="11" t="s">
+      <c r="H79" s="12" t="s">
         <v>949</v>
       </c>
-      <c r="I79" s="11" t="s">
+      <c r="I79" s="12" t="s">
         <v>950</v>
       </c>
-      <c r="J79" s="11" t="s">
+      <c r="J79" s="12" t="s">
         <v>951</v>
       </c>
-      <c r="K79" s="11" t="s">
+      <c r="K79" s="12" t="s">
         <v>952</v>
       </c>
-      <c r="L79" s="11" t="s">
+      <c r="L79" s="12" t="s">
         <v>953</v>
       </c>
-      <c r="M79" s="11" t="s">
+      <c r="M79" s="12" t="s">
         <v>954</v>
       </c>
-      <c r="N79" s="11" t="s">
+      <c r="N79" s="12" t="s">
         <v>955</v>
       </c>
-      <c r="O79" s="11" t="s">
+      <c r="O79" s="12" t="s">
         <v>956</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="2:15">
-      <c r="B80" s="10">
+      <c r="B80" s="11">
         <v>10075</v>
       </c>
-      <c r="C80" s="11" t="s">
+      <c r="C80" s="12" t="s">
         <v>957</v>
       </c>
-      <c r="D80" s="12" t="s">
+      <c r="D80" s="13" t="s">
         <v>958</v>
       </c>
-      <c r="E80" s="11" t="s">
+      <c r="E80" s="12" t="s">
         <v>959</v>
       </c>
-      <c r="F80" s="11" t="s">
+      <c r="F80" s="12" t="s">
         <v>960</v>
       </c>
-      <c r="G80" s="11" t="s">
+      <c r="G80" s="12" t="s">
         <v>961</v>
       </c>
-      <c r="H80" s="11" t="s">
+      <c r="H80" s="12" t="s">
         <v>962</v>
       </c>
-      <c r="I80" s="11" t="s">
+      <c r="I80" s="12" t="s">
         <v>963</v>
       </c>
-      <c r="J80" s="11" t="s">
+      <c r="J80" s="12" t="s">
         <v>964</v>
       </c>
-      <c r="K80" s="11" t="s">
+      <c r="K80" s="12" t="s">
         <v>965</v>
       </c>
-      <c r="L80" s="11" t="s">
+      <c r="L80" s="12" t="s">
         <v>966</v>
       </c>
-      <c r="M80" s="11" t="s">
+      <c r="M80" s="12" t="s">
         <v>967</v>
       </c>
-      <c r="N80" s="11" t="s">
+      <c r="N80" s="12" t="s">
         <v>968</v>
       </c>
-      <c r="O80" s="11" t="s">
+      <c r="O80" s="12" t="s">
         <v>969</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="2:15">
-      <c r="B81" s="10">
+      <c r="B81" s="11">
         <v>10076</v>
       </c>
-      <c r="C81" s="11" t="s">
+      <c r="C81" s="12" t="s">
         <v>970</v>
       </c>
-      <c r="D81" s="12" t="s">
+      <c r="D81" s="13" t="s">
         <v>971</v>
       </c>
-      <c r="E81" s="11" t="s">
+      <c r="E81" s="12" t="s">
         <v>972</v>
       </c>
-      <c r="F81" s="11" t="s">
+      <c r="F81" s="12" t="s">
         <v>973</v>
       </c>
-      <c r="G81" s="11" t="s">
+      <c r="G81" s="12" t="s">
         <v>974</v>
       </c>
-      <c r="H81" s="11" t="s">
+      <c r="H81" s="12" t="s">
         <v>975</v>
       </c>
-      <c r="I81" s="11" t="s">
+      <c r="I81" s="12" t="s">
         <v>976</v>
       </c>
-      <c r="J81" s="11" t="s">
+      <c r="J81" s="12" t="s">
         <v>977</v>
       </c>
-      <c r="K81" s="11" t="s">
+      <c r="K81" s="12" t="s">
         <v>978</v>
       </c>
-      <c r="L81" s="11" t="s">
+      <c r="L81" s="12" t="s">
         <v>979</v>
       </c>
-      <c r="M81" s="11" t="s">
+      <c r="M81" s="12" t="s">
         <v>980</v>
       </c>
-      <c r="N81" s="11" t="s">
+      <c r="N81" s="12" t="s">
         <v>981</v>
       </c>
-      <c r="O81" s="11" t="s">
+      <c r="O81" s="12" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="2:15">
-      <c r="B82" s="10">
+      <c r="B82" s="11">
         <v>10077</v>
       </c>
-      <c r="C82" s="11" t="s">
+      <c r="C82" s="12" t="s">
         <v>983</v>
       </c>
-      <c r="D82" s="12" t="s">
+      <c r="D82" s="13" t="s">
         <v>984</v>
       </c>
-      <c r="E82" s="11" t="s">
+      <c r="E82" s="12" t="s">
         <v>985</v>
       </c>
-      <c r="F82" s="11" t="s">
+      <c r="F82" s="12" t="s">
         <v>986</v>
       </c>
-      <c r="G82" s="11" t="s">
+      <c r="G82" s="12" t="s">
         <v>987</v>
       </c>
-      <c r="H82" s="11" t="s">
+      <c r="H82" s="12" t="s">
         <v>988</v>
       </c>
-      <c r="I82" s="11" t="s">
+      <c r="I82" s="12" t="s">
         <v>989</v>
       </c>
-      <c r="J82" s="11" t="s">
+      <c r="J82" s="12" t="s">
         <v>990</v>
       </c>
-      <c r="K82" s="11" t="s">
+      <c r="K82" s="12" t="s">
         <v>991</v>
       </c>
-      <c r="L82" s="11" t="s">
+      <c r="L82" s="12" t="s">
         <v>992</v>
       </c>
-      <c r="M82" s="11" t="s">
+      <c r="M82" s="12" t="s">
         <v>993</v>
       </c>
-      <c r="N82" s="11" t="s">
+      <c r="N82" s="12" t="s">
         <v>994</v>
       </c>
-      <c r="O82" s="11" t="s">
+      <c r="O82" s="12" t="s">
         <v>995</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="2:15">
-      <c r="B83" s="10">
+      <c r="B83" s="11">
         <v>10078</v>
       </c>
-      <c r="C83" s="11" t="s">
+      <c r="C83" s="12" t="s">
         <v>996</v>
       </c>
-      <c r="D83" s="12" t="s">
+      <c r="D83" s="13" t="s">
         <v>997</v>
       </c>
-      <c r="E83" s="11" t="s">
+      <c r="E83" s="12" t="s">
         <v>998</v>
       </c>
-      <c r="F83" s="11" t="s">
+      <c r="F83" s="12" t="s">
         <v>999</v>
       </c>
-      <c r="G83" s="11" t="s">
+      <c r="G83" s="12" t="s">
         <v>1000</v>
       </c>
-      <c r="H83" s="11" t="s">
+      <c r="H83" s="12" t="s">
         <v>1001</v>
       </c>
-      <c r="I83" s="11" t="s">
+      <c r="I83" s="12" t="s">
         <v>1002</v>
       </c>
-      <c r="J83" s="11" t="s">
+      <c r="J83" s="12" t="s">
         <v>1003</v>
       </c>
-      <c r="K83" s="11" t="s">
+      <c r="K83" s="12" t="s">
         <v>1004</v>
       </c>
-      <c r="L83" s="11" t="s">
+      <c r="L83" s="12" t="s">
         <v>1005</v>
       </c>
-      <c r="M83" s="11" t="s">
+      <c r="M83" s="12" t="s">
         <v>1006</v>
       </c>
-      <c r="N83" s="11" t="s">
+      <c r="N83" s="12" t="s">
         <v>1007</v>
       </c>
-      <c r="O83" s="11" t="s">
+      <c r="O83" s="12" t="s">
         <v>1008</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="2:15">
-      <c r="B84" s="10">
+      <c r="B84" s="11">
         <v>10079</v>
       </c>
-      <c r="C84" s="11" t="s">
+      <c r="C84" s="12" t="s">
         <v>1009</v>
       </c>
-      <c r="D84" s="12" t="s">
+      <c r="D84" s="13" t="s">
         <v>1010</v>
       </c>
-      <c r="E84" s="11" t="s">
+      <c r="E84" s="12" t="s">
         <v>1011</v>
       </c>
-      <c r="F84" s="11" t="s">
+      <c r="F84" s="12" t="s">
         <v>1012</v>
       </c>
-      <c r="G84" s="11" t="s">
+      <c r="G84" s="12" t="s">
         <v>1013</v>
       </c>
-      <c r="H84" s="11" t="s">
+      <c r="H84" s="12" t="s">
         <v>1014</v>
       </c>
-      <c r="I84" s="11" t="s">
+      <c r="I84" s="12" t="s">
         <v>1015</v>
       </c>
-      <c r="J84" s="11" t="s">
+      <c r="J84" s="12" t="s">
         <v>1016</v>
       </c>
-      <c r="K84" s="11" t="s">
+      <c r="K84" s="12" t="s">
         <v>1017</v>
       </c>
-      <c r="L84" s="11" t="s">
+      <c r="L84" s="12" t="s">
         <v>1018</v>
       </c>
-      <c r="M84" s="11" t="s">
+      <c r="M84" s="12" t="s">
         <v>1019</v>
       </c>
-      <c r="N84" s="11" t="s">
+      <c r="N84" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="O84" s="11" t="s">
+      <c r="O84" s="12" t="s">
         <v>1021</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="2:15">
-      <c r="B85" s="10">
+      <c r="B85" s="11">
         <v>10080</v>
       </c>
-      <c r="C85" s="11" t="s">
+      <c r="C85" s="12" t="s">
         <v>1022</v>
       </c>
-      <c r="D85" s="12" t="s">
+      <c r="D85" s="13" t="s">
         <v>1023</v>
       </c>
-      <c r="E85" s="11" t="s">
+      <c r="E85" s="12" t="s">
         <v>1024</v>
       </c>
-      <c r="F85" s="11" t="s">
+      <c r="F85" s="12" t="s">
         <v>1025</v>
       </c>
-      <c r="G85" s="11" t="s">
+      <c r="G85" s="12" t="s">
         <v>1026</v>
       </c>
-      <c r="H85" s="11" t="s">
+      <c r="H85" s="12" t="s">
         <v>1027</v>
       </c>
-      <c r="I85" s="11" t="s">
+      <c r="I85" s="12" t="s">
         <v>1028</v>
       </c>
-      <c r="J85" s="11" t="s">
+      <c r="J85" s="12" t="s">
         <v>1029</v>
       </c>
-      <c r="K85" s="11" t="s">
+      <c r="K85" s="12" t="s">
         <v>1030</v>
       </c>
-      <c r="L85" s="11" t="s">
+      <c r="L85" s="12" t="s">
         <v>1031</v>
       </c>
-      <c r="M85" s="11" t="s">
+      <c r="M85" s="12" t="s">
         <v>1032</v>
       </c>
-      <c r="N85" s="11" t="s">
+      <c r="N85" s="12" t="s">
         <v>1033</v>
       </c>
-      <c r="O85" s="11" t="s">
+      <c r="O85" s="12" t="s">
         <v>1034</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="2:15">
-      <c r="B86" s="10">
+      <c r="B86" s="11">
         <v>10081</v>
       </c>
-      <c r="C86" s="11" t="s">
+      <c r="C86" s="12" t="s">
         <v>1035</v>
       </c>
-      <c r="D86" s="12" t="s">
+      <c r="D86" s="13" t="s">
         <v>1036</v>
       </c>
-      <c r="E86" s="11" t="s">
+      <c r="E86" s="12" t="s">
         <v>1037</v>
       </c>
-      <c r="F86" s="11" t="s">
+      <c r="F86" s="12" t="s">
         <v>1038</v>
       </c>
-      <c r="G86" s="11" t="s">
+      <c r="G86" s="12" t="s">
         <v>1039</v>
       </c>
-      <c r="H86" s="11" t="s">
+      <c r="H86" s="12" t="s">
         <v>1040</v>
       </c>
-      <c r="I86" s="11" t="s">
+      <c r="I86" s="12" t="s">
         <v>1041</v>
       </c>
-      <c r="J86" s="11" t="s">
+      <c r="J86" s="12" t="s">
         <v>1042</v>
       </c>
-      <c r="K86" s="11" t="s">
+      <c r="K86" s="12" t="s">
         <v>1043</v>
       </c>
-      <c r="L86" s="11" t="s">
+      <c r="L86" s="12" t="s">
         <v>1044</v>
       </c>
-      <c r="M86" s="11" t="s">
+      <c r="M86" s="12" t="s">
         <v>1045</v>
       </c>
-      <c r="N86" s="11" t="s">
+      <c r="N86" s="12" t="s">
         <v>1046</v>
       </c>
-      <c r="O86" s="11" t="s">
+      <c r="O86" s="12" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="2:15">
-      <c r="B87" s="10">
+      <c r="B87" s="11">
         <v>10082</v>
       </c>
-      <c r="C87" s="11" t="s">
+      <c r="C87" s="12" t="s">
         <v>1048</v>
       </c>
-      <c r="D87" s="12" t="s">
+      <c r="D87" s="13" t="s">
         <v>1049</v>
       </c>
-      <c r="E87" s="11" t="s">
+      <c r="E87" s="12" t="s">
         <v>1050</v>
       </c>
-      <c r="F87" s="11" t="s">
+      <c r="F87" s="12" t="s">
         <v>1051</v>
       </c>
-      <c r="G87" s="11" t="s">
+      <c r="G87" s="12" t="s">
         <v>1052</v>
       </c>
-      <c r="H87" s="11" t="s">
+      <c r="H87" s="12" t="s">
         <v>1053</v>
       </c>
-      <c r="I87" s="11" t="s">
+      <c r="I87" s="12" t="s">
         <v>1054</v>
       </c>
-      <c r="J87" s="11" t="s">
+      <c r="J87" s="12" t="s">
         <v>1055</v>
       </c>
-      <c r="K87" s="11" t="s">
+      <c r="K87" s="12" t="s">
         <v>1056</v>
       </c>
-      <c r="L87" s="11" t="s">
+      <c r="L87" s="12" t="s">
         <v>1057</v>
       </c>
-      <c r="M87" s="11" t="s">
+      <c r="M87" s="12" t="s">
         <v>1058</v>
       </c>
-      <c r="N87" s="11" t="s">
+      <c r="N87" s="12" t="s">
         <v>1059</v>
       </c>
-      <c r="O87" s="11" t="s">
+      <c r="O87" s="12" t="s">
         <v>1060</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="2:15">
-      <c r="B88" s="10">
+      <c r="B88" s="11">
         <v>10083</v>
       </c>
-      <c r="C88" s="11" t="s">
+      <c r="C88" s="12" t="s">
         <v>1061</v>
       </c>
-      <c r="D88" s="12" t="s">
+      <c r="D88" s="13" t="s">
         <v>1062</v>
       </c>
-      <c r="E88" s="11" t="s">
+      <c r="E88" s="12" t="s">
         <v>1063</v>
       </c>
-      <c r="F88" s="11" t="s">
+      <c r="F88" s="12" t="s">
         <v>1064</v>
       </c>
-      <c r="G88" s="11" t="s">
+      <c r="G88" s="12" t="s">
         <v>1065</v>
       </c>
-      <c r="H88" s="11" t="s">
+      <c r="H88" s="12" t="s">
         <v>1066</v>
       </c>
-      <c r="I88" s="11" t="s">
+      <c r="I88" s="12" t="s">
         <v>1067</v>
       </c>
-      <c r="J88" s="11" t="s">
+      <c r="J88" s="12" t="s">
         <v>1068</v>
       </c>
-      <c r="K88" s="11" t="s">
+      <c r="K88" s="12" t="s">
         <v>1069</v>
       </c>
-      <c r="L88" s="11" t="s">
+      <c r="L88" s="12" t="s">
         <v>1070</v>
       </c>
-      <c r="M88" s="11" t="s">
+      <c r="M88" s="12" t="s">
         <v>1071</v>
       </c>
-      <c r="N88" s="11" t="s">
+      <c r="N88" s="12" t="s">
         <v>1072</v>
       </c>
-      <c r="O88" s="11" t="s">
+      <c r="O88" s="12" t="s">
         <v>1073</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="2:15">
-      <c r="B89" s="10">
+      <c r="B89" s="11">
         <v>10084</v>
       </c>
-      <c r="C89" s="11" t="s">
+      <c r="C89" s="12" t="s">
         <v>1074</v>
       </c>
-      <c r="D89" s="12" t="s">
+      <c r="D89" s="13" t="s">
         <v>1075</v>
       </c>
-      <c r="E89" s="11" t="s">
+      <c r="E89" s="12" t="s">
         <v>1076</v>
       </c>
-      <c r="F89" s="11" t="s">
+      <c r="F89" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="G89" s="11" t="s">
+      <c r="G89" s="12" t="s">
         <v>1078</v>
       </c>
-      <c r="H89" s="11" t="s">
+      <c r="H89" s="12" t="s">
         <v>1079</v>
       </c>
-      <c r="I89" s="11" t="s">
+      <c r="I89" s="12" t="s">
         <v>1078</v>
       </c>
-      <c r="J89" s="11" t="s">
+      <c r="J89" s="12" t="s">
         <v>1080</v>
       </c>
-      <c r="K89" s="11" t="s">
+      <c r="K89" s="12" t="s">
         <v>1081</v>
       </c>
-      <c r="L89" s="11" t="s">
+      <c r="L89" s="12" t="s">
         <v>1082</v>
       </c>
-      <c r="M89" s="11" t="s">
+      <c r="M89" s="12" t="s">
         <v>1083</v>
       </c>
-      <c r="N89" s="11" t="s">
+      <c r="N89" s="12" t="s">
         <v>1084</v>
       </c>
-      <c r="O89" s="11" t="s">
+      <c r="O89" s="12" t="s">
         <v>1085</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="2:15">
-      <c r="B90" s="10">
+      <c r="B90" s="11">
         <v>10085</v>
       </c>
-      <c r="C90" s="11" t="s">
+      <c r="C90" s="12" t="s">
         <v>1086</v>
       </c>
-      <c r="D90" s="12" t="s">
+      <c r="D90" s="13" t="s">
         <v>1087</v>
       </c>
-      <c r="E90" s="11" t="s">
+      <c r="E90" s="12" t="s">
         <v>1088</v>
       </c>
-      <c r="F90" s="11" t="s">
+      <c r="F90" s="12" t="s">
         <v>1089</v>
       </c>
-      <c r="G90" s="11" t="s">
+      <c r="G90" s="12" t="s">
         <v>1090</v>
       </c>
-      <c r="H90" s="11" t="s">
+      <c r="H90" s="12" t="s">
         <v>1091</v>
       </c>
-      <c r="I90" s="11" t="s">
+      <c r="I90" s="12" t="s">
         <v>1092</v>
       </c>
-      <c r="J90" s="11" t="s">
+      <c r="J90" s="12" t="s">
         <v>1093</v>
       </c>
-      <c r="K90" s="11" t="s">
+      <c r="K90" s="12" t="s">
         <v>1094</v>
       </c>
-      <c r="L90" s="11" t="s">
+      <c r="L90" s="12" t="s">
         <v>1095</v>
       </c>
-      <c r="M90" s="11" t="s">
+      <c r="M90" s="12" t="s">
         <v>1096</v>
       </c>
-      <c r="N90" s="11" t="s">
+      <c r="N90" s="12" t="s">
         <v>1097</v>
       </c>
-      <c r="O90" s="11" t="s">
+      <c r="O90" s="12" t="s">
         <v>1098</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="2:15">
-      <c r="B91" s="10">
+      <c r="B91" s="11">
         <v>10086</v>
       </c>
-      <c r="C91" s="11" t="s">
+      <c r="C91" s="12" t="s">
         <v>1099</v>
       </c>
-      <c r="D91" s="12" t="s">
+      <c r="D91" s="13" t="s">
         <v>1100</v>
       </c>
-      <c r="E91" s="11" t="s">
+      <c r="E91" s="12" t="s">
         <v>1101</v>
       </c>
-      <c r="F91" s="11" t="s">
+      <c r="F91" s="12" t="s">
         <v>1102</v>
       </c>
-      <c r="G91" s="11" t="s">
+      <c r="G91" s="12" t="s">
         <v>1103</v>
       </c>
-      <c r="H91" s="11" t="s">
+      <c r="H91" s="12" t="s">
         <v>1104</v>
       </c>
-      <c r="I91" s="11" t="s">
+      <c r="I91" s="12" t="s">
         <v>1105</v>
       </c>
-      <c r="J91" s="11" t="s">
+      <c r="J91" s="12" t="s">
         <v>1106</v>
       </c>
-      <c r="K91" s="11" t="s">
+      <c r="K91" s="12" t="s">
         <v>1107</v>
       </c>
-      <c r="L91" s="11" t="s">
+      <c r="L91" s="12" t="s">
         <v>1108</v>
       </c>
-      <c r="M91" s="11" t="s">
+      <c r="M91" s="12" t="s">
         <v>1109</v>
       </c>
-      <c r="N91" s="11" t="s">
+      <c r="N91" s="12" t="s">
         <v>1110</v>
       </c>
-      <c r="O91" s="11" t="s">
+      <c r="O91" s="12" t="s">
         <v>1111</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="2:15">
-      <c r="B92" s="10">
+      <c r="B92" s="11">
         <v>10087</v>
       </c>
-      <c r="C92" s="11" t="s">
+      <c r="C92" s="12" t="s">
         <v>1112</v>
       </c>
-      <c r="D92" s="11" t="s">
+      <c r="D92" s="12" t="s">
         <v>1113</v>
       </c>
-      <c r="E92" s="11" t="s">
+      <c r="E92" s="12" t="s">
         <v>1114</v>
       </c>
-      <c r="F92" s="11" t="s">
+      <c r="F92" s="12" t="s">
         <v>1115</v>
       </c>
-      <c r="G92" s="11" t="s">
+      <c r="G92" s="12" t="s">
         <v>1116</v>
       </c>
-      <c r="H92" s="11" t="s">
+      <c r="H92" s="12" t="s">
         <v>1117</v>
       </c>
-      <c r="I92" s="11" t="s">
+      <c r="I92" s="12" t="s">
         <v>1118</v>
       </c>
-      <c r="J92" s="11" t="s">
+      <c r="J92" s="12" t="s">
         <v>1119</v>
       </c>
-      <c r="K92" s="11" t="s">
+      <c r="K92" s="12" t="s">
         <v>1120</v>
       </c>
-      <c r="L92" s="11" t="s">
+      <c r="L92" s="12" t="s">
         <v>1121</v>
       </c>
-      <c r="M92" s="11" t="s">
+      <c r="M92" s="12" t="s">
         <v>1122</v>
       </c>
-      <c r="N92" s="11" t="s">
+      <c r="N92" s="12" t="s">
         <v>1123</v>
       </c>
-      <c r="O92" s="11" t="s">
+      <c r="O92" s="12" t="s">
         <v>1124</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="2:15">
-      <c r="B93" s="10">
+      <c r="B93" s="11">
         <v>10088</v>
       </c>
-      <c r="C93" s="11" t="s">
+      <c r="C93" s="12" t="s">
         <v>1125</v>
       </c>
-      <c r="D93" s="11" t="s">
+      <c r="D93" s="12" t="s">
         <v>1126</v>
       </c>
-      <c r="E93" s="11" t="s">
+      <c r="E93" s="12" t="s">
         <v>1127</v>
       </c>
-      <c r="F93" s="11" t="s">
+      <c r="F93" s="12" t="s">
         <v>1128</v>
       </c>
-      <c r="G93" s="11" t="s">
+      <c r="G93" s="12" t="s">
         <v>1129</v>
       </c>
-      <c r="H93" s="11" t="s">
+      <c r="H93" s="12" t="s">
         <v>1130</v>
       </c>
-      <c r="I93" s="11" t="s">
+      <c r="I93" s="12" t="s">
         <v>1131</v>
       </c>
-      <c r="J93" s="11" t="s">
+      <c r="J93" s="12" t="s">
         <v>1132</v>
       </c>
-      <c r="K93" s="11" t="s">
+      <c r="K93" s="12" t="s">
         <v>1133</v>
       </c>
-      <c r="L93" s="11" t="s">
+      <c r="L93" s="12" t="s">
         <v>1134</v>
       </c>
-      <c r="M93" s="11" t="s">
+      <c r="M93" s="12" t="s">
         <v>1135</v>
       </c>
-      <c r="N93" s="11" t="s">
+      <c r="N93" s="12" t="s">
         <v>1136</v>
       </c>
-      <c r="O93" s="11" t="s">
+      <c r="O93" s="12" t="s">
         <v>1137</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="2:15">
-      <c r="B94" s="10">
+      <c r="B94" s="11">
         <v>10089</v>
       </c>
-      <c r="C94" s="11" t="s">
+      <c r="C94" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="D94" s="11" t="s">
+      <c r="D94" s="12" t="s">
         <v>1139</v>
       </c>
-      <c r="E94" s="11" t="s">
+      <c r="E94" s="12" t="s">
         <v>1140</v>
       </c>
-      <c r="F94" s="11" t="s">
+      <c r="F94" s="12" t="s">
         <v>1141</v>
       </c>
-      <c r="G94" s="11" t="s">
+      <c r="G94" s="12" t="s">
         <v>1142</v>
       </c>
-      <c r="H94" s="11" t="s">
+      <c r="H94" s="12" t="s">
         <v>1143</v>
       </c>
-      <c r="I94" s="11" t="s">
+      <c r="I94" s="12" t="s">
         <v>1144</v>
       </c>
-      <c r="J94" s="11" t="s">
+      <c r="J94" s="12" t="s">
         <v>1145</v>
       </c>
-      <c r="K94" s="11" t="s">
+      <c r="K94" s="12" t="s">
         <v>1146</v>
       </c>
-      <c r="L94" s="11" t="s">
+      <c r="L94" s="12" t="s">
         <v>1147</v>
       </c>
-      <c r="M94" s="11" t="s">
+      <c r="M94" s="12" t="s">
         <v>1148</v>
       </c>
-      <c r="N94" s="11" t="s">
+      <c r="N94" s="12" t="s">
         <v>1149</v>
       </c>
-      <c r="O94" s="11" t="s">
+      <c r="O94" s="12" t="s">
         <v>1150</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="2:15">
-      <c r="B95" s="10">
+      <c r="B95" s="11">
         <v>10090</v>
       </c>
-      <c r="C95" s="11" t="s">
+      <c r="C95" s="12" t="s">
         <v>1151</v>
       </c>
-      <c r="D95" s="12" t="s">
+      <c r="D95" s="13" t="s">
         <v>1152</v>
       </c>
-      <c r="E95" s="11" t="s">
+      <c r="E95" s="12" t="s">
         <v>1153</v>
       </c>
-      <c r="F95" s="11" t="s">
+      <c r="F95" s="12" t="s">
         <v>1154</v>
       </c>
-      <c r="G95" s="11" t="s">
+      <c r="G95" s="12" t="s">
         <v>1155</v>
       </c>
-      <c r="H95" s="11" t="s">
+      <c r="H95" s="12" t="s">
         <v>1156</v>
       </c>
-      <c r="I95" s="11" t="s">
+      <c r="I95" s="12" t="s">
         <v>1157</v>
       </c>
-      <c r="J95" s="11" t="s">
+      <c r="J95" s="12" t="s">
         <v>1158</v>
       </c>
-      <c r="K95" s="11" t="s">
+      <c r="K95" s="12" t="s">
         <v>1159</v>
       </c>
-      <c r="L95" s="11" t="s">
+      <c r="L95" s="12" t="s">
         <v>1160</v>
       </c>
-      <c r="M95" s="11" t="s">
+      <c r="M95" s="12" t="s">
         <v>1161</v>
       </c>
-      <c r="N95" s="11" t="s">
+      <c r="N95" s="12" t="s">
         <v>1162</v>
       </c>
-      <c r="O95" s="11" t="s">
+      <c r="O95" s="12" t="s">
         <v>1163</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="2:15">
-      <c r="B96" s="10">
+      <c r="B96" s="11">
         <v>10091</v>
       </c>
       <c r="C96" t="s">
@@ -11303,7 +11548,7 @@
       </c>
     </row>
     <row r="97" customHeight="1" spans="1:16">
-      <c r="B97" s="10">
+      <c r="B97" s="11">
         <v>10092</v>
       </c>
       <c r="C97" t="s">
@@ -11347,7 +11592,7 @@
       </c>
     </row>
     <row r="98" customHeight="1" spans="1:16">
-      <c r="B98" s="3">
+      <c r="B98" s="4">
         <v>10093</v>
       </c>
       <c r="C98" t="s">
@@ -11359,28 +11604,28 @@
       <c r="E98" t="s">
         <v>1192</v>
       </c>
-      <c r="F98" s="17" t="s">
+      <c r="F98" s="18" t="s">
         <v>1193</v>
       </c>
-      <c r="G98" s="17" t="s">
+      <c r="G98" s="18" t="s">
         <v>1194</v>
       </c>
       <c r="H98" t="s">
         <v>1195</v>
       </c>
-      <c r="I98" s="17" t="s">
+      <c r="I98" s="18" t="s">
         <v>1196</v>
       </c>
-      <c r="J98" s="17" t="s">
+      <c r="J98" s="18" t="s">
         <v>1197</v>
       </c>
-      <c r="K98" s="17" t="s">
+      <c r="K98" s="18" t="s">
         <v>1198</v>
       </c>
       <c r="L98" t="s">
         <v>1199</v>
       </c>
-      <c r="M98" s="17" t="s">
+      <c r="M98" s="18" t="s">
         <v>1200</v>
       </c>
       <c r="N98" t="s">
@@ -11391,7 +11636,7 @@
       </c>
     </row>
     <row r="99" customHeight="1" spans="1:16">
-      <c r="B99" s="3">
+      <c r="B99" s="4">
         <v>10094</v>
       </c>
       <c r="C99" t="s">
@@ -11412,10 +11657,10 @@
       <c r="H99" t="s">
         <v>1208</v>
       </c>
-      <c r="I99" s="17" t="s">
+      <c r="I99" s="18" t="s">
         <v>1209</v>
       </c>
-      <c r="J99" s="17" t="s">
+      <c r="J99" s="18" t="s">
         <v>1210</v>
       </c>
       <c r="K99" t="s">
@@ -11424,18 +11669,18 @@
       <c r="L99" t="s">
         <v>1212</v>
       </c>
-      <c r="M99" s="17" t="s">
+      <c r="M99" s="18" t="s">
         <v>1213</v>
       </c>
-      <c r="N99" s="17" t="s">
+      <c r="N99" s="18" t="s">
         <v>1214</v>
       </c>
-      <c r="O99" s="17" t="s">
+      <c r="O99" s="18" t="s">
         <v>1215</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="1:16">
-      <c r="B100" s="3">
+      <c r="B100" s="4">
         <v>10095</v>
       </c>
       <c r="C100" t="s">
@@ -11468,18 +11713,18 @@
       <c r="L100" t="s">
         <v>1225</v>
       </c>
-      <c r="M100" s="17" t="s">
+      <c r="M100" s="18" t="s">
         <v>1226</v>
       </c>
-      <c r="N100" s="17" t="s">
+      <c r="N100" s="18" t="s">
         <v>1227</v>
       </c>
-      <c r="O100" s="17" t="s">
+      <c r="O100" s="18" t="s">
         <v>1228</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="1:16">
-      <c r="B101" s="3">
+      <c r="B101" s="4">
         <v>10096</v>
       </c>
       <c r="C101" t="s">
@@ -11491,31 +11736,31 @@
       <c r="E101" t="s">
         <v>1231</v>
       </c>
-      <c r="F101" s="17" t="s">
+      <c r="F101" s="18" t="s">
         <v>1232</v>
       </c>
-      <c r="G101" s="17" t="s">
+      <c r="G101" s="18" t="s">
         <v>1233</v>
       </c>
       <c r="H101" t="s">
         <v>1234</v>
       </c>
-      <c r="I101" s="17" t="s">
+      <c r="I101" s="18" t="s">
         <v>1235</v>
       </c>
-      <c r="J101" s="17" t="s">
+      <c r="J101" s="18" t="s">
         <v>1236</v>
       </c>
-      <c r="K101" s="17" t="s">
+      <c r="K101" s="18" t="s">
         <v>1237</v>
       </c>
-      <c r="L101" s="17" t="s">
+      <c r="L101" s="18" t="s">
         <v>1238</v>
       </c>
-      <c r="M101" s="17" t="s">
+      <c r="M101" s="18" t="s">
         <v>1239</v>
       </c>
-      <c r="N101" s="17" t="s">
+      <c r="N101" s="18" t="s">
         <v>1240</v>
       </c>
       <c r="O101" t="s">
@@ -11523,7 +11768,7 @@
       </c>
     </row>
     <row r="102" customHeight="1" spans="1:16">
-      <c r="B102" s="3">
+      <c r="B102" s="4">
         <v>10097</v>
       </c>
       <c r="C102" t="s">
@@ -11535,28 +11780,28 @@
       <c r="E102" t="s">
         <v>1244</v>
       </c>
-      <c r="F102" s="18" t="s">
+      <c r="F102" s="19" t="s">
         <v>1245</v>
       </c>
-      <c r="G102" s="18" t="s">
+      <c r="G102" s="19" t="s">
         <v>1246</v>
       </c>
       <c r="H102" t="s">
         <v>1247</v>
       </c>
-      <c r="I102" s="17" t="s">
+      <c r="I102" s="18" t="s">
         <v>1248</v>
       </c>
-      <c r="J102" s="17" t="s">
+      <c r="J102" s="18" t="s">
         <v>1249</v>
       </c>
-      <c r="K102" s="17" t="s">
+      <c r="K102" s="18" t="s">
         <v>1250</v>
       </c>
       <c r="L102" t="s">
         <v>1251</v>
       </c>
-      <c r="M102" s="17" t="s">
+      <c r="M102" s="18" t="s">
         <v>1252</v>
       </c>
       <c r="N102" t="s">
@@ -11570,7 +11815,7 @@
       <c r="A103" s="2" t="s">
         <v>1255</v>
       </c>
-      <c r="B103" s="3">
+      <c r="B103" s="4">
         <v>10098</v>
       </c>
       <c r="C103" s="2" t="s">
@@ -11617,57 +11862,57 @@
       </c>
     </row>
     <row r="104" customFormat="1" customHeight="1" spans="1:16">
-      <c r="B104" s="3">
+      <c r="B104" s="4">
         <v>10099</v>
       </c>
-      <c r="C104" s="11" t="s">
+      <c r="C104" s="12" t="s">
         <v>1269</v>
       </c>
-      <c r="D104" s="12" t="s">
+      <c r="D104" s="13" t="s">
         <v>1270</v>
       </c>
-      <c r="E104" s="11" t="s">
+      <c r="E104" s="12" t="s">
         <v>1271</v>
       </c>
-      <c r="F104" s="11" t="s">
+      <c r="F104" s="12" t="s">
         <v>1272</v>
       </c>
-      <c r="G104" s="11" t="s">
+      <c r="G104" s="12" t="s">
         <v>1273</v>
       </c>
-      <c r="H104" s="11" t="s">
+      <c r="H104" s="12" t="s">
         <v>1274</v>
       </c>
-      <c r="I104" s="11" t="s">
+      <c r="I104" s="12" t="s">
         <v>1275</v>
       </c>
-      <c r="J104" s="11" t="s">
+      <c r="J104" s="12" t="s">
         <v>1276</v>
       </c>
-      <c r="K104" s="11" t="s">
+      <c r="K104" s="12" t="s">
         <v>1277</v>
       </c>
-      <c r="L104" s="11" t="s">
+      <c r="L104" s="12" t="s">
         <v>1278</v>
       </c>
-      <c r="M104" s="11" t="s">
+      <c r="M104" s="12" t="s">
         <v>1279</v>
       </c>
-      <c r="N104" s="14" t="s">
+      <c r="N104" s="15" t="s">
         <v>1280</v>
       </c>
-      <c r="O104" s="11" t="s">
+      <c r="O104" s="12" t="s">
         <v>1281</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="B105" s="3">
+      <c r="B105" s="4">
         <v>10100</v>
       </c>
       <c r="C105" t="s">
         <v>1282</v>
       </c>
-      <c r="D105" s="16" t="s">
+      <c r="D105" s="17" t="s">
         <v>153</v>
       </c>
       <c r="E105" t="s">
@@ -11676,7 +11921,7 @@
       <c r="F105" t="s">
         <v>1284</v>
       </c>
-      <c r="G105" s="16" t="s">
+      <c r="G105" s="17" t="s">
         <v>1285</v>
       </c>
       <c r="H105" t="s">
@@ -11688,25 +11933,25 @@
       <c r="J105" t="s">
         <v>1288</v>
       </c>
-      <c r="K105" s="16" t="s">
+      <c r="K105" s="17" t="s">
         <v>1289</v>
       </c>
       <c r="L105" t="s">
         <v>1290</v>
       </c>
-      <c r="M105" s="17" t="s">
+      <c r="M105" s="18" t="s">
         <v>1291</v>
       </c>
-      <c r="N105" s="18" t="s">
+      <c r="N105" s="19" t="s">
         <v>1292</v>
       </c>
-      <c r="O105" s="17" t="s">
+      <c r="O105" s="18" t="s">
         <v>1293</v>
       </c>
       <c r="P105"/>
     </row>
     <row r="106" customHeight="1" spans="1:16">
-      <c r="B106" s="3">
+      <c r="B106" s="4">
         <v>10101</v>
       </c>
       <c r="C106" s="2" t="s">
@@ -11750,43 +11995,43 @@
       </c>
     </row>
     <row r="107" customHeight="1" spans="1:16">
-      <c r="B107" s="3">
+      <c r="B107" s="4">
         <v>10102</v>
       </c>
       <c r="C107" t="s">
         <v>1307</v>
       </c>
-      <c r="D107" s="16" t="s">
+      <c r="D107" s="17" t="s">
         <v>1308</v>
       </c>
       <c r="E107" t="s">
         <v>1309</v>
       </c>
-      <c r="F107" s="17" t="s">
+      <c r="F107" s="18" t="s">
         <v>1310</v>
       </c>
-      <c r="G107" s="17" t="s">
+      <c r="G107" s="18" t="s">
         <v>1311</v>
       </c>
-      <c r="H107" s="17" t="s">
+      <c r="H107" s="18" t="s">
         <v>1312</v>
       </c>
-      <c r="I107" s="17" t="s">
+      <c r="I107" s="18" t="s">
         <v>1313</v>
       </c>
-      <c r="J107" s="17" t="s">
+      <c r="J107" s="18" t="s">
         <v>1314</v>
       </c>
-      <c r="K107" s="17" t="s">
+      <c r="K107" s="18" t="s">
         <v>1315</v>
       </c>
-      <c r="L107" s="17" t="s">
+      <c r="L107" s="18" t="s">
         <v>1316</v>
       </c>
-      <c r="M107" s="17" t="s">
+      <c r="M107" s="18" t="s">
         <v>1317</v>
       </c>
-      <c r="N107" s="17" t="s">
+      <c r="N107" s="18" t="s">
         <v>1318</v>
       </c>
       <c r="O107" t="s">
@@ -11794,13 +12039,13 @@
       </c>
     </row>
     <row r="108" customHeight="1" spans="1:16">
-      <c r="B108" s="3">
+      <c r="B108" s="4">
         <v>10103</v>
       </c>
       <c r="C108" t="s">
         <v>1320</v>
       </c>
-      <c r="D108" s="16" t="s">
+      <c r="D108" s="17" t="s">
         <v>1321</v>
       </c>
       <c r="E108" t="s">
@@ -11809,7 +12054,7 @@
       <c r="F108" t="s">
         <v>1323</v>
       </c>
-      <c r="G108" s="16" t="s">
+      <c r="G108" s="17" t="s">
         <v>1324</v>
       </c>
       <c r="H108" t="s">
@@ -11821,13 +12066,13 @@
       <c r="J108" t="s">
         <v>1327</v>
       </c>
-      <c r="K108" s="17" t="s">
+      <c r="K108" s="18" t="s">
         <v>1328</v>
       </c>
-      <c r="L108" s="17" t="s">
+      <c r="L108" s="18" t="s">
         <v>1329</v>
       </c>
-      <c r="M108" s="17" t="s">
+      <c r="M108" s="18" t="s">
         <v>1330</v>
       </c>
       <c r="N108" t="s">
@@ -11838,13 +12083,13 @@
       </c>
     </row>
     <row r="109" customHeight="1" spans="1:16">
-      <c r="B109" s="3">
+      <c r="B109" s="4">
         <v>10104</v>
       </c>
       <c r="C109" t="s">
         <v>1333</v>
       </c>
-      <c r="D109" s="16" t="s">
+      <c r="D109" s="17" t="s">
         <v>1334</v>
       </c>
       <c r="E109" t="s">
@@ -11853,7 +12098,7 @@
       <c r="F109" t="s">
         <v>1336</v>
       </c>
-      <c r="G109" s="16" t="s">
+      <c r="G109" s="17" t="s">
         <v>1337</v>
       </c>
       <c r="H109" t="s">
@@ -11865,24 +12110,24 @@
       <c r="J109" t="s">
         <v>1340</v>
       </c>
-      <c r="K109" s="17" t="s">
+      <c r="K109" s="18" t="s">
         <v>1341</v>
       </c>
-      <c r="L109" s="17" t="s">
+      <c r="L109" s="18" t="s">
         <v>1342</v>
       </c>
-      <c r="M109" s="17" t="s">
+      <c r="M109" s="18" t="s">
         <v>1343</v>
       </c>
-      <c r="N109" s="17" t="s">
+      <c r="N109" s="18" t="s">
         <v>1344</v>
       </c>
-      <c r="O109" s="17" t="s">
+      <c r="O109" s="18" t="s">
         <v>1345</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="1:16">
-      <c r="B110" s="3">
+      <c r="B110" s="4">
         <v>10105</v>
       </c>
       <c r="C110" t="s">
@@ -11894,75 +12139,75 @@
       <c r="E110" t="s">
         <v>1348</v>
       </c>
-      <c r="F110" s="17" t="s">
+      <c r="F110" s="18" t="s">
         <v>1349</v>
       </c>
-      <c r="G110" s="17" t="s">
+      <c r="G110" s="18" t="s">
         <v>1350</v>
       </c>
-      <c r="H110" s="17" t="s">
+      <c r="H110" s="18" t="s">
         <v>1351</v>
       </c>
-      <c r="I110" s="17" t="s">
+      <c r="I110" s="18" t="s">
         <v>1352</v>
       </c>
-      <c r="J110" s="17" t="s">
+      <c r="J110" s="18" t="s">
         <v>1353</v>
       </c>
-      <c r="K110" s="17" t="s">
+      <c r="K110" s="18" t="s">
         <v>1354</v>
       </c>
       <c r="L110" t="s">
         <v>1355</v>
       </c>
-      <c r="M110" s="18" t="s">
+      <c r="M110" s="19" t="s">
         <v>1356</v>
       </c>
-      <c r="N110" s="18" t="s">
+      <c r="N110" s="19" t="s">
         <v>1357</v>
       </c>
-      <c r="O110" s="18" t="s">
+      <c r="O110" s="19" t="s">
         <v>1358</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="1:16">
-      <c r="B111" s="3">
+      <c r="B111" s="4">
         <v>10106</v>
       </c>
-      <c r="C111" s="19" t="s">
+      <c r="C111" s="20" t="s">
         <v>1359</v>
       </c>
-      <c r="D111" s="16" t="s">
+      <c r="D111" s="17" t="s">
         <v>1360</v>
       </c>
       <c r="E111" t="s">
         <v>1361</v>
       </c>
-      <c r="F111" s="17" t="s">
+      <c r="F111" s="18" t="s">
         <v>1362</v>
       </c>
-      <c r="G111" s="16" t="s">
+      <c r="G111" s="17" t="s">
         <v>1363</v>
       </c>
-      <c r="H111" s="17" t="s">
+      <c r="H111" s="18" t="s">
         <v>1364</v>
       </c>
-      <c r="I111" s="17" t="s">
+      <c r="I111" s="18" t="s">
         <v>1365</v>
       </c>
-      <c r="J111" s="17" t="s">
+      <c r="J111" s="18" t="s">
         <v>1366</v>
       </c>
-      <c r="K111" s="17" t="s">
+      <c r="K111" s="18" t="s">
         <v>1367</v>
       </c>
       <c r="L111" t="s">
         <v>1368</v>
       </c>
-      <c r="M111" s="17" t="s">
+      <c r="M111" s="18" t="s">
         <v>1369</v>
       </c>
-      <c r="N111" s="17" t="s">
+      <c r="N111" s="18" t="s">
         <v>1370</v>
       </c>
       <c r="O111" t="s">
@@ -11970,7 +12215,7 @@
       </c>
     </row>
     <row r="112" customHeight="1" spans="1:16">
-      <c r="B112" s="3">
+      <c r="B112" s="4">
         <v>10107</v>
       </c>
       <c r="C112" t="s">
@@ -11982,7 +12227,7 @@
       <c r="E112" t="s">
         <v>1374</v>
       </c>
-      <c r="F112" s="17" t="s">
+      <c r="F112" s="18" t="s">
         <v>1375</v>
       </c>
       <c r="G112" t="s">
@@ -11991,19 +12236,19 @@
       <c r="H112" t="s">
         <v>1377</v>
       </c>
-      <c r="I112" s="17" t="s">
+      <c r="I112" s="18" t="s">
         <v>1378</v>
       </c>
-      <c r="J112" s="17" t="s">
+      <c r="J112" s="18" t="s">
         <v>1379</v>
       </c>
-      <c r="K112" s="17" t="s">
+      <c r="K112" s="18" t="s">
         <v>1380</v>
       </c>
       <c r="L112" t="s">
         <v>1381</v>
       </c>
-      <c r="M112" s="17" t="s">
+      <c r="M112" s="18" t="s">
         <v>1382</v>
       </c>
       <c r="N112" t="s">
@@ -12017,7 +12262,7 @@
       <c r="A113" s="2" t="s">
         <v>1255</v>
       </c>
-      <c r="B113" s="3">
+      <c r="B113" s="4">
         <v>10108</v>
       </c>
       <c r="C113" s="2" t="s">
@@ -12067,7 +12312,7 @@
       <c r="A114" s="2" t="s">
         <v>1255</v>
       </c>
-      <c r="B114" s="3">
+      <c r="B114" s="4">
         <v>10109</v>
       </c>
       <c r="C114" s="2" t="s">
@@ -12117,7 +12362,7 @@
       <c r="A115" s="2" t="s">
         <v>1255</v>
       </c>
-      <c r="B115" s="3">
+      <c r="B115" s="4">
         <v>10110</v>
       </c>
       <c r="C115" s="2" t="s">
@@ -12167,7 +12412,7 @@
       <c r="A116" s="2" t="s">
         <v>1255</v>
       </c>
-      <c r="B116" s="3">
+      <c r="B116" s="4">
         <v>10111</v>
       </c>
       <c r="C116" s="2" t="s">
@@ -12217,7 +12462,7 @@
       <c r="A117" s="2" t="s">
         <v>1255</v>
       </c>
-      <c r="B117" s="3">
+      <c r="B117" s="4">
         <v>10112</v>
       </c>
       <c r="C117" s="2" t="s">
@@ -12267,7 +12512,7 @@
       <c r="A118" s="2" t="s">
         <v>1255</v>
       </c>
-      <c r="B118" s="3">
+      <c r="B118" s="4">
         <v>10113</v>
       </c>
       <c r="C118" s="2" t="s">
@@ -12317,7 +12562,7 @@
       <c r="A119" s="2" t="s">
         <v>1255</v>
       </c>
-      <c r="B119" s="3">
+      <c r="B119" s="4">
         <v>10114</v>
       </c>
       <c r="C119" s="2" t="s">
@@ -12367,7 +12612,7 @@
       <c r="A120" s="2" t="s">
         <v>1255</v>
       </c>
-      <c r="B120" s="3">
+      <c r="B120" s="4">
         <v>10115</v>
       </c>
       <c r="C120" s="2" t="s">
@@ -12417,7 +12662,7 @@
       <c r="A121" s="2" t="s">
         <v>1255</v>
       </c>
-      <c r="B121" s="3">
+      <c r="B121" s="4">
         <v>10116</v>
       </c>
       <c r="C121" s="2" t="s">
@@ -12467,7 +12712,7 @@
       <c r="A122" s="2" t="s">
         <v>1255</v>
       </c>
-      <c r="B122" s="3">
+      <c r="B122" s="4">
         <v>10117</v>
       </c>
       <c r="C122" s="2" t="s">
@@ -12517,7 +12762,7 @@
       <c r="A123" s="2" t="s">
         <v>1255</v>
       </c>
-      <c r="B123" s="3">
+      <c r="B123" s="4">
         <v>10118</v>
       </c>
       <c r="C123" s="2" t="s">
@@ -12567,7 +12812,7 @@
       <c r="A124" s="2" t="s">
         <v>1255</v>
       </c>
-      <c r="B124" s="3">
+      <c r="B124" s="4">
         <v>10119</v>
       </c>
       <c r="C124" s="2" t="s">
@@ -12617,10 +12862,10 @@
       <c r="A125" s="2" t="s">
         <v>1255</v>
       </c>
-      <c r="B125" s="3">
+      <c r="B125" s="4">
         <v>10120</v>
       </c>
-      <c r="C125" s="20" t="s">
+      <c r="C125" s="21" t="s">
         <v>1538</v>
       </c>
       <c r="D125" s="2" t="s">
@@ -12664,230 +12909,230 @@
       </c>
     </row>
     <row r="126" customHeight="1" spans="1:16">
-      <c r="B126" s="3">
+      <c r="B126" s="4">
         <v>10121</v>
       </c>
       <c r="C126" t="s">
         <v>1549</v>
       </c>
-      <c r="D126" s="12" t="s">
+      <c r="D126" s="13" t="s">
         <v>1550</v>
       </c>
-      <c r="E126" s="11" t="s">
+      <c r="E126" s="12" t="s">
         <v>1551</v>
       </c>
-      <c r="F126" s="11" t="s">
+      <c r="F126" s="12" t="s">
         <v>1552</v>
       </c>
-      <c r="G126" s="11" t="s">
+      <c r="G126" s="12" t="s">
         <v>1553</v>
       </c>
-      <c r="H126" s="11" t="s">
+      <c r="H126" s="12" t="s">
         <v>1554</v>
       </c>
-      <c r="I126" s="11" t="s">
+      <c r="I126" s="12" t="s">
         <v>1555</v>
       </c>
-      <c r="J126" s="11" t="s">
+      <c r="J126" s="12" t="s">
         <v>1556</v>
       </c>
-      <c r="K126" s="11" t="s">
+      <c r="K126" s="12" t="s">
         <v>1557</v>
       </c>
-      <c r="L126" s="11" t="s">
+      <c r="L126" s="12" t="s">
         <v>1558</v>
       </c>
-      <c r="M126" s="11" t="s">
+      <c r="M126" s="12" t="s">
         <v>1559</v>
       </c>
-      <c r="N126" s="11" t="s">
+      <c r="N126" s="12" t="s">
         <v>1560</v>
       </c>
-      <c r="O126" s="11" t="s">
+      <c r="O126" s="12" t="s">
         <v>1561</v>
       </c>
     </row>
     <row r="127" customHeight="1" spans="1:16">
-      <c r="B127" s="3">
+      <c r="B127" s="4">
         <v>10122</v>
       </c>
       <c r="C127" t="s">
         <v>1562</v>
       </c>
-      <c r="D127" s="21" t="s">
+      <c r="D127" s="22" t="s">
         <v>1563</v>
       </c>
-      <c r="E127" s="21" t="s">
+      <c r="E127" s="22" t="s">
         <v>1564</v>
       </c>
-      <c r="F127" s="21" t="s">
+      <c r="F127" s="22" t="s">
         <v>1565</v>
       </c>
-      <c r="G127" s="21" t="s">
+      <c r="G127" s="22" t="s">
         <v>1566</v>
       </c>
-      <c r="H127" s="21" t="s">
+      <c r="H127" s="22" t="s">
         <v>1567</v>
       </c>
-      <c r="I127" s="21" t="s">
+      <c r="I127" s="22" t="s">
         <v>1568</v>
       </c>
-      <c r="J127" s="21" t="s">
+      <c r="J127" s="22" t="s">
         <v>1569</v>
       </c>
-      <c r="K127" s="21" t="s">
+      <c r="K127" s="22" t="s">
         <v>1570</v>
       </c>
-      <c r="L127" s="21" t="s">
+      <c r="L127" s="22" t="s">
         <v>1571</v>
       </c>
-      <c r="M127" s="21" t="s">
+      <c r="M127" s="22" t="s">
         <v>1572</v>
       </c>
-      <c r="N127" s="21" t="s">
+      <c r="N127" s="22" t="s">
         <v>1573</v>
       </c>
-      <c r="O127" s="21" t="s">
+      <c r="O127" s="22" t="s">
         <v>1574</v>
       </c>
-      <c r="P127" s="21" t="s">
+      <c r="P127" s="22" t="s">
         <v>1574</v>
       </c>
     </row>
     <row r="128" customHeight="1" spans="1:16">
-      <c r="B128" s="3">
+      <c r="B128" s="4">
         <v>10123</v>
       </c>
       <c r="C128" t="s">
         <v>1575</v>
       </c>
-      <c r="D128" s="12" t="s">
+      <c r="D128" s="13" t="s">
         <v>1576</v>
       </c>
-      <c r="E128" s="11" t="s">
+      <c r="E128" s="12" t="s">
         <v>1577</v>
       </c>
-      <c r="F128" s="11" t="s">
+      <c r="F128" s="12" t="s">
         <v>1578</v>
       </c>
-      <c r="G128" s="11" t="s">
+      <c r="G128" s="12" t="s">
         <v>1579</v>
       </c>
-      <c r="H128" s="11" t="s">
+      <c r="H128" s="12" t="s">
         <v>1580</v>
       </c>
-      <c r="I128" s="11" t="s">
+      <c r="I128" s="12" t="s">
         <v>1581</v>
       </c>
-      <c r="J128" s="11" t="s">
+      <c r="J128" s="12" t="s">
         <v>1582</v>
       </c>
-      <c r="K128" s="11" t="s">
+      <c r="K128" s="12" t="s">
         <v>1583</v>
       </c>
-      <c r="L128" s="11" t="s">
+      <c r="L128" s="12" t="s">
         <v>1584</v>
       </c>
-      <c r="M128" s="11" t="s">
+      <c r="M128" s="12" t="s">
         <v>1585</v>
       </c>
-      <c r="N128" s="11" t="s">
+      <c r="N128" s="12" t="s">
         <v>1586</v>
       </c>
-      <c r="O128" s="11" t="s">
+      <c r="O128" s="12" t="s">
         <v>1587</v>
       </c>
     </row>
-    <row r="129" customHeight="1" spans="2:15">
-      <c r="B129" s="3">
+    <row r="129" customHeight="1" spans="1:15">
+      <c r="B129" s="4">
         <v>10124</v>
       </c>
       <c r="C129" t="s">
         <v>1588</v>
       </c>
-      <c r="D129" s="12" t="s">
+      <c r="D129" s="13" t="s">
         <v>1589</v>
       </c>
-      <c r="E129" s="11" t="s">
+      <c r="E129" s="12" t="s">
         <v>1590</v>
       </c>
-      <c r="F129" s="11" t="s">
+      <c r="F129" s="12" t="s">
         <v>1591</v>
       </c>
-      <c r="G129" s="11" t="s">
+      <c r="G129" s="12" t="s">
         <v>1592</v>
       </c>
-      <c r="H129" s="11" t="s">
+      <c r="H129" s="12" t="s">
         <v>1593</v>
       </c>
-      <c r="I129" s="11" t="s">
+      <c r="I129" s="12" t="s">
         <v>1594</v>
       </c>
-      <c r="J129" s="11" t="s">
+      <c r="J129" s="12" t="s">
         <v>1595</v>
       </c>
-      <c r="K129" s="11" t="s">
+      <c r="K129" s="12" t="s">
         <v>1596</v>
       </c>
-      <c r="L129" s="11" t="s">
+      <c r="L129" s="12" t="s">
         <v>1597</v>
       </c>
-      <c r="M129" s="11" t="s">
+      <c r="M129" s="12" t="s">
         <v>1598</v>
       </c>
-      <c r="N129" s="11" t="s">
+      <c r="N129" s="12" t="s">
         <v>1599</v>
       </c>
-      <c r="O129" s="11" t="s">
+      <c r="O129" s="12" t="s">
         <v>1600</v>
       </c>
     </row>
-    <row r="130" customHeight="1" spans="2:15">
-      <c r="B130" s="3">
+    <row r="130" customHeight="1" spans="1:15">
+      <c r="B130" s="4">
         <v>10125</v>
       </c>
       <c r="C130" t="s">
         <v>1601</v>
       </c>
-      <c r="D130" s="12" t="s">
+      <c r="D130" s="13" t="s">
         <v>1602</v>
       </c>
-      <c r="E130" s="11" t="s">
+      <c r="E130" s="12" t="s">
         <v>1603</v>
       </c>
-      <c r="F130" s="11" t="s">
+      <c r="F130" s="12" t="s">
         <v>1604</v>
       </c>
-      <c r="G130" s="11" t="s">
+      <c r="G130" s="12" t="s">
         <v>1605</v>
       </c>
-      <c r="H130" s="11" t="s">
+      <c r="H130" s="12" t="s">
         <v>1606</v>
       </c>
-      <c r="I130" s="11" t="s">
+      <c r="I130" s="12" t="s">
         <v>1607</v>
       </c>
-      <c r="J130" s="11" t="s">
+      <c r="J130" s="12" t="s">
         <v>1608</v>
       </c>
-      <c r="K130" s="11" t="s">
+      <c r="K130" s="12" t="s">
         <v>1609</v>
       </c>
-      <c r="L130" s="11" t="s">
+      <c r="L130" s="12" t="s">
         <v>1610</v>
       </c>
-      <c r="M130" s="11" t="s">
+      <c r="M130" s="12" t="s">
         <v>1611</v>
       </c>
-      <c r="N130" s="14" t="s">
+      <c r="N130" s="15" t="s">
         <v>1612</v>
       </c>
-      <c r="O130" s="11" t="s">
+      <c r="O130" s="12" t="s">
         <v>1613</v>
       </c>
     </row>
-    <row r="131" customHeight="1" spans="2:15">
-      <c r="B131" s="3">
+    <row r="131" customHeight="1" spans="1:15">
+      <c r="B131" s="4">
         <v>10126</v>
       </c>
       <c r="C131" t="s">
@@ -12930,52 +13175,52 @@
         <v>1624</v>
       </c>
     </row>
-    <row r="132" customFormat="1" customHeight="1" spans="2:15">
-      <c r="B132" s="3">
+    <row r="132" customFormat="1" customHeight="1" spans="1:15">
+      <c r="B132" s="4">
         <v>10127</v>
       </c>
       <c r="C132" t="s">
         <v>1625</v>
       </c>
-      <c r="D132" s="12" t="s">
+      <c r="D132" s="13" t="s">
         <v>1626</v>
       </c>
-      <c r="E132" s="21" t="s">
+      <c r="E132" s="22" t="s">
         <v>1627</v>
       </c>
-      <c r="F132" s="21" t="s">
+      <c r="F132" s="22" t="s">
         <v>1628</v>
       </c>
-      <c r="G132" s="21" t="s">
+      <c r="G132" s="22" t="s">
         <v>1629</v>
       </c>
-      <c r="H132" s="21" t="s">
+      <c r="H132" s="22" t="s">
         <v>1630</v>
       </c>
-      <c r="I132" s="21" t="s">
+      <c r="I132" s="22" t="s">
         <v>1631</v>
       </c>
-      <c r="J132" s="21" t="s">
+      <c r="J132" s="22" t="s">
         <v>1632</v>
       </c>
-      <c r="K132" s="21" t="s">
+      <c r="K132" s="22" t="s">
         <v>1633</v>
       </c>
-      <c r="L132" s="21" t="s">
+      <c r="L132" s="22" t="s">
         <v>1634</v>
       </c>
-      <c r="M132" s="21" t="s">
+      <c r="M132" s="22" t="s">
         <v>1635</v>
       </c>
-      <c r="N132" s="21" t="s">
+      <c r="N132" s="22" t="s">
         <v>1636</v>
       </c>
-      <c r="O132" s="21" t="s">
+      <c r="O132" s="22" t="s">
         <v>1637</v>
       </c>
     </row>
-    <row r="133" customHeight="1" spans="2:15">
-      <c r="B133" s="3">
+    <row r="133" customHeight="1" spans="1:15">
+      <c r="B133" s="4">
         <v>10128</v>
       </c>
       <c r="C133" t="s">
@@ -13018,104 +13263,364 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="134" customHeight="1" spans="2:15">
-      <c r="B134" s="3">
+    <row r="134" s="3" customFormat="1" ht="16" customHeight="1" spans="1:15">
+      <c r="A134" s="23"/>
+      <c r="B134" s="4">
         <v>10129</v>
       </c>
-      <c r="C134" s="22" t="s">
+      <c r="C134" s="3" t="s">
         <v>1651</v>
       </c>
-      <c r="D134" s="22" t="s">
+      <c r="D134" s="3" t="s">
         <v>1652</v>
       </c>
-      <c r="E134" s="22" t="s">
+      <c r="E134" s="3" t="s">
         <v>1653</v>
       </c>
-      <c r="F134" s="22" t="s">
+      <c r="F134" s="3" t="s">
         <v>1654</v>
       </c>
-      <c r="G134" s="22" t="s">
+      <c r="G134" s="3" t="s">
         <v>1655</v>
       </c>
-    </row>
-    <row r="135" customHeight="1" spans="2:15">
-      <c r="B135" s="3">
+      <c r="H134" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="I134" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="J134" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="K134" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="L134" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="M134" s="3" t="s">
+        <v>1660</v>
+      </c>
+      <c r="N134" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="O134" s="3" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="135" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A135" s="23"/>
+      <c r="B135" s="4">
         <v>10130</v>
       </c>
-      <c r="C135" s="22" t="s">
-        <v>1656</v>
-      </c>
-      <c r="D135" s="22" t="s">
-        <v>1657</v>
-      </c>
-      <c r="E135" s="22" t="s">
-        <v>1658</v>
-      </c>
-      <c r="F135" s="22" t="s">
-        <v>1659</v>
-      </c>
-      <c r="G135" s="22" t="s">
-        <v>1660</v>
-      </c>
-    </row>
-    <row r="136" customHeight="1" spans="2:15">
-      <c r="B136" s="3">
+      <c r="C135" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>1663</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>1664</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>1665</v>
+      </c>
+      <c r="H135" s="3" t="s">
+        <v>1666</v>
+      </c>
+      <c r="I135" s="3" t="s">
+        <v>1667</v>
+      </c>
+      <c r="J135" s="3" t="s">
+        <v>1668</v>
+      </c>
+      <c r="K135" s="3" t="s">
+        <v>1669</v>
+      </c>
+      <c r="L135" s="3" t="s">
+        <v>1670</v>
+      </c>
+      <c r="M135" s="3" t="s">
+        <v>1671</v>
+      </c>
+      <c r="N135" s="3" t="s">
+        <v>1672</v>
+      </c>
+      <c r="O135" s="3" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="136" s="3" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A136" s="23"/>
+      <c r="B136" s="4">
         <v>10131</v>
       </c>
-      <c r="C136" s="22" t="s">
-        <v>1661</v>
-      </c>
-      <c r="D136" s="22" t="s">
-        <v>1662</v>
-      </c>
-      <c r="E136" s="22" t="s">
-        <v>1663</v>
-      </c>
-      <c r="F136" s="22" t="s">
-        <v>1664</v>
-      </c>
-      <c r="G136" s="22" t="s">
-        <v>1665</v>
-      </c>
-    </row>
-    <row r="137" customHeight="1" spans="2:15">
-      <c r="B137" s="3">
+      <c r="C136" s="3" t="s">
+        <v>1674</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>1675</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>1677</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>1678</v>
+      </c>
+      <c r="H136" s="3" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I136" s="3" t="s">
+        <v>1680</v>
+      </c>
+      <c r="J136" s="3" t="s">
+        <v>1681</v>
+      </c>
+      <c r="K136" s="3" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L136" s="3" t="s">
+        <v>1683</v>
+      </c>
+      <c r="M136" s="3" t="s">
+        <v>1684</v>
+      </c>
+      <c r="N136" s="3" t="s">
+        <v>1685</v>
+      </c>
+      <c r="O136" s="3" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="137" s="3" customFormat="1" ht="70" customHeight="1" spans="1:15">
+      <c r="A137" s="23"/>
+      <c r="B137" s="4">
         <v>10132</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>1666</v>
+        <v>1687</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>1667</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>1668</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>1669</v>
-      </c>
-      <c r="G137" s="1" t="s">
-        <v>1670</v>
-      </c>
-    </row>
-    <row r="138" customHeight="1" spans="2:15">
-      <c r="B138" s="3">
+        <v>1688</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>1689</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>1690</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>1691</v>
+      </c>
+      <c r="H137" s="1" t="s">
+        <v>1692</v>
+      </c>
+      <c r="I137" s="3" t="s">
+        <v>1693</v>
+      </c>
+      <c r="J137" s="3" t="s">
+        <v>1694</v>
+      </c>
+      <c r="K137" s="3" t="s">
+        <v>1695</v>
+      </c>
+      <c r="L137" s="3" t="s">
+        <v>1696</v>
+      </c>
+      <c r="M137" s="3" t="s">
+        <v>1697</v>
+      </c>
+      <c r="N137" s="3" t="s">
+        <v>1698</v>
+      </c>
+      <c r="O137" s="3" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="138" s="3" customFormat="1" ht="19" customHeight="1" spans="1:15">
+      <c r="A138" s="23"/>
+      <c r="B138" s="4">
         <v>10133</v>
       </c>
-      <c r="C138" s="22" t="s">
-        <v>1671</v>
-      </c>
-      <c r="D138" s="22" t="s">
-        <v>1672</v>
-      </c>
-      <c r="E138" s="22" t="s">
-        <v>1673</v>
-      </c>
-      <c r="F138" s="22" t="s">
-        <v>1674</v>
-      </c>
-      <c r="G138" s="22" t="s">
-        <v>1675</v>
+      <c r="C138" s="3" t="s">
+        <v>1700</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>1701</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>1702</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>1703</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>1704</v>
+      </c>
+      <c r="H138" s="3" t="s">
+        <v>1705</v>
+      </c>
+      <c r="I138" s="3" t="s">
+        <v>1706</v>
+      </c>
+      <c r="J138" s="3" t="s">
+        <v>1707</v>
+      </c>
+      <c r="K138" s="3" t="s">
+        <v>1708</v>
+      </c>
+      <c r="L138" s="3" t="s">
+        <v>1709</v>
+      </c>
+      <c r="M138" s="3" t="s">
+        <v>1710</v>
+      </c>
+      <c r="N138" s="3" t="s">
+        <v>1711</v>
+      </c>
+      <c r="O138" s="3" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="139" s="3" customFormat="1" ht="13.5" spans="1:15">
+      <c r="A139" s="23"/>
+      <c r="B139" s="4">
+        <v>10134</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>1713</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>1714</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>1715</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>1716</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>1717</v>
+      </c>
+      <c r="H139" s="3" t="s">
+        <v>1718</v>
+      </c>
+      <c r="I139" s="3" t="s">
+        <v>1719</v>
+      </c>
+      <c r="J139" s="3" t="s">
+        <v>1720</v>
+      </c>
+      <c r="K139" s="3" t="s">
+        <v>1721</v>
+      </c>
+      <c r="L139" s="3" t="s">
+        <v>1722</v>
+      </c>
+      <c r="M139" s="3" t="s">
+        <v>1723</v>
+      </c>
+      <c r="N139" s="3" t="s">
+        <v>1724</v>
+      </c>
+      <c r="O139" s="3" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="140" s="3" customFormat="1" ht="13.5" spans="1:15">
+      <c r="A140" s="23"/>
+      <c r="B140" s="4">
+        <v>10135</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>1726</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>1728</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>1729</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>1730</v>
+      </c>
+      <c r="H140" s="3" t="s">
+        <v>1731</v>
+      </c>
+      <c r="I140" s="3" t="s">
+        <v>1732</v>
+      </c>
+      <c r="J140" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="K140" s="3" t="s">
+        <v>1734</v>
+      </c>
+      <c r="L140" s="3" t="s">
+        <v>1735</v>
+      </c>
+      <c r="M140" s="3" t="s">
+        <v>1736</v>
+      </c>
+      <c r="N140" s="3" t="s">
+        <v>1737</v>
+      </c>
+      <c r="O140" s="3" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="141" s="3" customFormat="1" ht="31" customHeight="1" spans="1:15">
+      <c r="A141" s="23"/>
+      <c r="B141" s="4">
+        <v>10136</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>1740</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>1741</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>1742</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>1743</v>
+      </c>
+      <c r="H141" s="3" t="s">
+        <v>1744</v>
+      </c>
+      <c r="I141" s="3" t="s">
+        <v>1745</v>
+      </c>
+      <c r="J141" s="3" t="s">
+        <v>1746</v>
+      </c>
+      <c r="K141" s="3" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L141" s="3" t="s">
+        <v>1748</v>
+      </c>
+      <c r="M141" s="3" t="s">
+        <v>1749</v>
+      </c>
+      <c r="N141" s="3" t="s">
+        <v>1750</v>
+      </c>
+      <c r="O141" s="3" t="s">
+        <v>1751</v>
       </c>
     </row>
   </sheetData>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -5713,68 +5713,68 @@
     <t>Check-in: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; gün</t>
   </si>
   <si>
-    <t>为确认账户已启用且您为真实玩家（防止机器人刷取），请连续签到8天完成身份核实。
-再通过{0}个关卡即可完成今日签到。
+    <t>为确认账户已启用且您为真实玩家（防止机器人刷取），请连续签到{0}天完成身份核实。
+再通过{1}个关卡即可完成今日签到。
 此步骤有助于保障提现顺利到账。</t>
   </si>
   <si>
-    <t>To confirm your account is active and you are a real player (not a bot), check in for 8 consecutive days to verify your identity.
-Clear {0} more levels to complete today's check-in.
+    <t>To confirm your account is active and you are a real player (not a bot), check in for {0} consecutive days to verify your identity.
+Clear {1} more levels to complete today's check-in.
 This helps ensure smooth withdrawals.</t>
   </si>
   <si>
-    <t>Um zu bestätigen, dass dein Konto aktiv ist und du ein echter Spieler bist (kein Bot), melde dich 8 Tage hintereinander an, um deine Identität zu bestätigen.
-Schließe {0} weitere Level ab, um den heutigen Check-in abzuschließen.
+    <t>Um zu bestätigen, dass dein Konto aktiv ist und du ein echter Spieler bist (kein Bot), melde dich {0} Tage hintereinander an, um deine Identität zu bestätigen.
+Schließe {1} weitere Level ab, um den heutigen Check-in abzuschließen.
 Dies hilft, reibungslose Auszahlungen zu gewährleisten.</t>
   </si>
   <si>
-    <t>アカウントが有効で実在のプレイヤーであること（ボット防止）を確認するため、8日連続サインインで本人確認を行います。
-あと{0}レベルクリアで本日のサインインが完了します。
+    <t>アカウントが有効で実在のプレイヤーであること（ボット防止）を確認するため、{0}日連続サインインで本人確認を行います。
+あと{1}レベルクリアで本日のサインインが完了します。
 スムーズな出金のための手続きです。</t>
   </si>
   <si>
-    <t>Para confirmar que sua conta está ativa e que você é um jogador real (não um bot), faça check-in por 8 dias seguidos para verificar sua identidade.
-Passe mais {0} níveis para completar o check-in de hoje.
+    <t>Para confirmar que sua conta está ativa e que você é um jogador real (não um bot), faça check-in por {0} dias seguidos para verificar sua identidade.
+Passe mais {1} níveis para completar o check-in de hoje.
 Isso ajuda a garantir saques sem problemas.</t>
   </si>
   <si>
-    <t>Pour confirmer que votre compte est actif et que vous êtes un vrai joueur (pas un bot), effectuez le check-in pendant 8 jours consécutifs pour vérifier votre identité.
-Passez encore {0} niveaux pour terminer le check-in du jour.
+    <t>Pour confirmer que votre compte est actif et que vous êtes un vrai joueur (pas un bot), effectuez le check-in pendant {0} jours consécutifs pour vérifier votre identité.
+Passez encore {1} niveaux pour terminer le check-in du jour.
 Cela aide à assurer des retraits fluides.</t>
   </si>
   <si>
-    <t>Para confirmar que tu cuenta está activa y que eres un jugador real (no un bot), haz check-in durante 8 días seguidos para verificar tu identidad.
-Supera {0} niveles más para completar el check-in de hoy.
+    <t>Para confirmar que tu cuenta está activa y que eres un jugador real (no un bot), haz check-in durante {0} días seguidos para verificar tu identidad.
+Supera {1} niveles más para completar el check-in de hoy.
 Esto ayuda a garantizar retiros sin problemas.</t>
   </si>
   <si>
-    <t>계정이 활성화되어 있고 봇이 아닌 실제 플레이어임을 확인하기 위해 8일 연속 출석으로 본인 인증을 완료해 주세요.
-{0}개 레벨을 더 클리어하면 오늘 출석이 완료됩니다.
+    <t>계정이 활성화되어 있고 봇이 아닌 실제 플레이어임을 확인하기 위해 {0}일 연속 출석으로 본인 인증을 완료해 주세요.
+{1}개 레벨을 더 클리어하면 오늘 출석이 완료됩니다.
 원활한 출금을 위한 절차입니다.</t>
   </si>
   <si>
-    <t>Untuk memastikan akun aktif dan Anda pemain asli (bukan bot), lakukan check-in selama 8 hari berturut-turut untuk verifikasi identitas.
-Lewati {0} level lagi untuk menyelesaikan check-in hari ini.
+    <t>Untuk memastikan akun aktif dan Anda pemain asli (bukan bot), lakukan check-in selama {0} hari berturut-turut untuk verifikasi identitas.
+Lewati {1} level lagi untuk menyelesaikan check-in hari ini.
 Ini membantu memastikan penarikan lancar.</t>
   </si>
   <si>
-    <t>Чтобы подтвердить, что аккаунт активен и вы реальный игрок (не бот), выполняйте check-in 8 дней подряд для верификации личности.
-Пройдите ещё {0} уровней, чтобы завершить сегодняшний check-in.
+    <t>Чтобы подтвердить, что аккаунт активен и вы реальный игрок (не бот), выполняйте check-in {0} дней подряд для верификации личности.
+Пройдите ещё {1} уровней, чтобы завершить сегодняшний check-in.
 Это помогает обеспечить бесперебойный вывод.</t>
   </si>
   <si>
-    <t>खाता सक्रिय है और आप वास्तविक खिलाड़ी हैं (बॉट नहीं) यह सुनिश्चित करने के लिए, पहचान सत्यापन हेतु लगातार 8 दिन चेक-इन करें।
-{0} और लेवल पूरे करें तो आज का चेक-इन हो जाएगा।
+    <t>खाता सक्रिय है और आप वास्तविक खिलाड़ी हैं (बॉट नहीं) यह सुनिश्चित करने के लिए, पहचान सत्यापन हेतु लगातार {0} दिन चेक-इन करें।
+{1} और लेवल पूरे करें तो आज का चेक-इन हो जाएगा।
 यह सुचारू निकासी में मदद करता है।</t>
   </si>
   <si>
-    <t>เพื่อยืนยันว่าบัญชีเปิดใช้งานและคุณเป็นผู้เล่นจริง (ไม่ใช่บอท) กรุณาเช็คอินติดต่อกัน 8 วันเพื่อยืนยันตัวตน
-ผ่านอีก {0} ด่านเพื่อเช็คอินวันนี้ให้ครบ
+    <t>เพื่อยืนยันว่าบัญชีเปิดใช้งานและคุณเป็นผู้เล่นจริง (ไม่ใช่บอท) กรุณาเช็คอินติดต่อกัน {0} วันเพื่อยืนยันตัวตน
+ผ่านอีก {1} ด่านเพื่อเช็คอินวันนี้ให้ครบ
 ช่วยให้การถอนเงินราบรื่นขึ้น</t>
   </si>
   <si>
-    <t>Hesabınızın aktif olduğunu ve gerçek bir oyuncu olduğunuzu (bot olmadığınızı) doğrulamak için kimlik doğrulaması amacıyla 8 gün üst üste check-in yapın.
-Bugünkü check-in için {0} seviye daha geçin.
+    <t>Hesabınızın aktif olduğunu ve gerçek bir oyuncu olduğunuzu (bot olmadığınızı) doğrulamak için kimlik doğrulaması amacıyla {0} gün üst üste check-in yapın.
+Bugünkü check-in için {1} seviye daha geçin.
 Bu, sorunsuz çekimlere yardımcı olur.</t>
   </si>
   <si>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="1647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1879" uniqueCount="1761">
   <si>
     <t>##var</t>
   </si>
@@ -5552,6 +5552,374 @@
   </si>
   <si>
     <t>Şişeyi mavi renkle doldur, gökkuşağı ambalajını aç</t>
+  </si>
+  <si>
+    <t>签到完成，点击提现</t>
+  </si>
+  <si>
+    <t>Check-in completed, click to withdraw</t>
+  </si>
+  <si>
+    <t>Check-in abgeschlossen, zum Auszahlen tippen</t>
+  </si>
+  <si>
+    <t>チェックイン完了、出金タップ</t>
+  </si>
+  <si>
+    <t>Check-in concluído, toque para sacar</t>
+  </si>
+  <si>
+    <t>Check-in terminé, touchez pour retirer</t>
+  </si>
+  <si>
+    <t>Check-in completado, toque para retirar</t>
+  </si>
+  <si>
+    <t>체크인 완료, 출금 탭</t>
+  </si>
+  <si>
+    <t>Check-in selesai, tap untuk tarik</t>
+  </si>
+  <si>
+    <t>Чек-ин завершен, нажмите для вывода</t>
+  </si>
+  <si>
+    <t>चेक-इन पूरा, निकालने के लिए टैप करें</t>
+  </si>
+  <si>
+    <t>เช็คอินเสร็จ, แตะเพื่อถอนเงิน</t>
+  </si>
+  <si>
+    <t>Check-in tamamlandı, çekmek için dokunun</t>
+  </si>
+  <si>
+    <t>确认账户信息</t>
+  </si>
+  <si>
+    <t>Confirm Account Info</t>
+  </si>
+  <si>
+    <t>Kontodaten bestätigen</t>
+  </si>
+  <si>
+    <t>口座情報を確認</t>
+  </si>
+  <si>
+    <t>Confirmar dados da conta</t>
+  </si>
+  <si>
+    <t>Confirmer les infos du compte</t>
+  </si>
+  <si>
+    <t>Confirmar datos de la cuenta</t>
+  </si>
+  <si>
+    <t>Konfirmasi info akun</t>
+  </si>
+  <si>
+    <t>Подтвердите данные аккаунта</t>
+  </si>
+  <si>
+    <t>खाता जानकारी पुष्टि करें</t>
+  </si>
+  <si>
+    <t>提现申请已提交</t>
+  </si>
+  <si>
+    <t>Withdrawal request submitted</t>
+  </si>
+  <si>
+    <t>Auszahlungsanfrage eingereicht</t>
+  </si>
+  <si>
+    <t>出金申請を送信しました</t>
+  </si>
+  <si>
+    <t>Solicitação de saque enviada</t>
+  </si>
+  <si>
+    <t>Demande de retrait envoyée</t>
+  </si>
+  <si>
+    <t>Solicitud de retiro enviada</t>
+  </si>
+  <si>
+    <t>출금 신청이 제출되었습니다</t>
+  </si>
+  <si>
+    <t>Permintaan penarikan telah dikirim</t>
+  </si>
+  <si>
+    <t>Заявка на вывод отправлена</t>
+  </si>
+  <si>
+    <t>निकासी अनुरोध जमा हो गया</t>
+  </si>
+  <si>
+    <t>ส่งคำขอถอนแล้ว</t>
+  </si>
+  <si>
+    <t>Çekim talebi gönderildi</t>
+  </si>
+  <si>
+    <t>签到 &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; 天</t>
+  </si>
+  <si>
+    <t>Check-in: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; days</t>
+  </si>
+  <si>
+    <t>Check-in: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; Tage</t>
+  </si>
+  <si>
+    <t>サインイン &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; 日</t>
+  </si>
+  <si>
+    <t>Check-in: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; dias</t>
+  </si>
+  <si>
+    <t>Check-in : &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; jours</t>
+  </si>
+  <si>
+    <t>Check-in: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; días</t>
+  </si>
+  <si>
+    <t>출석: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt;일</t>
+  </si>
+  <si>
+    <t>Check-in: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; hari</t>
+  </si>
+  <si>
+    <t>Check-in: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; дн.</t>
+  </si>
+  <si>
+    <t>चेक-इन: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; दिन</t>
+  </si>
+  <si>
+    <t>เช็คอิน &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; วัน</t>
+  </si>
+  <si>
+    <t>Check-in: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; gün</t>
+  </si>
+  <si>
+    <t>为确认账户已启用且您为真实玩家（防止机器人刷取），请连续签到{0}天完成身份核实。
+再通过{1}个关卡即可完成今日签到。
+此步骤有助于保障提现顺利到账。</t>
+  </si>
+  <si>
+    <t>To confirm your account is active and you are a real player (not a bot), check in for {0} consecutive days to verify your identity.
+Clear {1} more levels to complete today's check-in.
+This helps ensure smooth withdrawals.</t>
+  </si>
+  <si>
+    <t>Um zu bestätigen, dass dein Konto aktiv ist und du ein echter Spieler bist (kein Bot), melde dich {0} Tage hintereinander an, um deine Identität zu bestätigen.
+Schließe {1} weitere Level ab, um den heutigen Check-in abzuschließen.
+Dies hilft, reibungslose Auszahlungen zu gewährleisten.</t>
+  </si>
+  <si>
+    <t>アカウントが有効で実在のプレイヤーであること（ボット防止）を確認するため、{0}日連続サインインで本人確認を行います。
+あと{1}レベルクリアで本日のサインインが完了します。
+スムーズな出金のための手続きです。</t>
+  </si>
+  <si>
+    <t>Para confirmar que sua conta está ativa e que você é um jogador real (não um bot), faça check-in por {0} dias seguidos para verificar sua identidade.
+Passe mais {1} níveis para completar o check-in de hoje.
+Isso ajuda a garantir saques sem problemas.</t>
+  </si>
+  <si>
+    <t>Pour confirmer que votre compte est actif et que vous êtes un vrai joueur (pas un bot), effectuez le check-in pendant {0} jours consécutifs pour vérifier votre identité.
+Passez encore {1} niveaux pour terminer le check-in du jour.
+Cela aide à assurer des retraits fluides.</t>
+  </si>
+  <si>
+    <t>Para confirmar que tu cuenta está activa y que eres un jugador real (no un bot), haz check-in durante {0} días seguidos para verificar tu identidad.
+Supera {1} niveles más para completar el check-in de hoy.
+Esto ayuda a garantizar retiros sin problemas.</t>
+  </si>
+  <si>
+    <t>계정이 활성화되어 있고 봇이 아닌 실제 플레이어임을 확인하기 위해 {0}일 연속 출석으로 본인 인증을 완료해 주세요.
+{1}개 레벨을 더 클리어하면 오늘 출석이 완료됩니다.
+원활한 출금을 위한 절차입니다.</t>
+  </si>
+  <si>
+    <t>Untuk memastikan akun aktif dan Anda pemain asli (bukan bot), lakukan check-in selama {0} hari berturut-turut untuk verifikasi identitas.
+Lewati {1} level lagi untuk menyelesaikan check-in hari ini.
+Ini membantu memastikan penarikan lancar.</t>
+  </si>
+  <si>
+    <t>Чтобы подтвердить, что аккаунт активен и вы реальный игрок (не бот), выполняйте check-in {0} дней подряд для верификации личности.
+Пройдите ещё {1} уровней, чтобы завершить сегодняшний check-in.
+Это помогает обеспечить бесперебойный вывод.</t>
+  </si>
+  <si>
+    <t>खाता सक्रिय है और आप वास्तविक खिलाड़ी हैं (बॉट नहीं) यह सुनिश्चित करने के लिए, पहचान सत्यापन हेतु लगातार {0} दिन चेक-इन करें।
+{1} और लेवल पूरे करें तो आज का चेक-इन हो जाएगा।
+यह सुचारू निकासी में मदद करता है।</t>
+  </si>
+  <si>
+    <t>เพื่อยืนยันว่าบัญชีเปิดใช้งานและคุณเป็นผู้เล่นจริง (ไม่ใช่บอท) กรุณาเช็คอินติดต่อกัน {0} วันเพื่อยืนยันตัวตน
+ผ่านอีก {1} ด่านเพื่อเช็คอินวันนี้ให้ครบ
+ช่วยให้การถอนเงินราบรื่นขึ้น</t>
+  </si>
+  <si>
+    <t>Hesabınızın aktif olduğunu ve gerçek bir oyuncu olduğunuzu (bot olmadığınızı) doğrulamak için kimlik doğrulaması amacıyla {0} gün üst üste check-in yapın.
+Bugünkü check-in için {1} seviye daha geçin.
+Bu, sorunsuz çekimlere yardımcı olur.</t>
+  </si>
+  <si>
+    <t>提现成功</t>
+  </si>
+  <si>
+    <t>Withdrawal successful</t>
+  </si>
+  <si>
+    <t>Auszahlung erfolgreich</t>
+  </si>
+  <si>
+    <t>出金成功</t>
+  </si>
+  <si>
+    <t>Saque realizado com sucesso</t>
+  </si>
+  <si>
+    <t>Retrait réussi</t>
+  </si>
+  <si>
+    <t>Retiro exitoso</t>
+  </si>
+  <si>
+    <t>출금 성공</t>
+  </si>
+  <si>
+    <t>Penarikan berhasil</t>
+  </si>
+  <si>
+    <t>Вывод успешен</t>
+  </si>
+  <si>
+    <t>निकासी सफल</t>
+  </si>
+  <si>
+    <t>ถอนเงินสำเร็จ</t>
+  </si>
+  <si>
+    <t>Çekim başarılı</t>
+  </si>
+  <si>
+    <t>银行审核 &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; 天</t>
+  </si>
+  <si>
+    <t>Bank review: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; days</t>
+  </si>
+  <si>
+    <t>Bankprüfung: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; Tage</t>
+  </si>
+  <si>
+    <t>銀行審査 &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; 日</t>
+  </si>
+  <si>
+    <t>Revisão bancária: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; dias</t>
+  </si>
+  <si>
+    <t>Vérification bancaire : &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; jours</t>
+  </si>
+  <si>
+    <t>Revisión bancaria: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; días</t>
+  </si>
+  <si>
+    <t>은행 심사 &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt;일</t>
+  </si>
+  <si>
+    <t>Tinjauan bank: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; hari</t>
+  </si>
+  <si>
+    <t>Банк. проверка: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; дн.</t>
+  </si>
+  <si>
+    <t>बैंक समीक्षा: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; दिन</t>
+  </si>
+  <si>
+    <t>ตรวจธนาคาร &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; วัน</t>
+  </si>
+  <si>
+    <t>Banka incelemesi: &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; gün</t>
+  </si>
+  <si>
+    <t>银行审核约需&lt;color=#EA2111&gt;{0}&lt;/color&gt;天，请保持账号活跃。不活跃账号可能被插队，导致审核进度延迟。再通过&lt;color=#EA2111&gt;{1}&lt;/color&gt;关完成今日签到，这有助于维持正常提现进度。</t>
+  </si>
+  <si>
+    <t>Bank review takes about &lt;color=#EA2111&gt;{0}&lt;/color&gt; days. Keep your account active—inactive accounts may be skipped in queue and delay review progress. Clear &lt;color=#EA2111&gt;{1}&lt;/color&gt; more levels for today's check-in. This helps maintain normal withdrawal progress.</t>
+  </si>
+  <si>
+    <t>Bankprüfung dauert ca. &lt;color=#EA2111&gt;{0}&lt;/color&gt; Tage. Konto aktiv halten—inaktive Konten können übersprungen werden und die Prüfung verzögern. Noch &lt;color=#EA2111&gt;{1}&lt;/color&gt; Level für heutigen Check-in. Dies hilft, den Auszahlungsfortschritt aufrechtzuerhalten.</t>
+  </si>
+  <si>
+    <t>銀行審査は約&lt;color=#EA2111&gt;{0}&lt;/color&gt;日。口座をアクティブに保ってください。非アクティブだと順番が飛ばされ審査が遅延する場合があります。あと&lt;color=#EA2111&gt;{1}&lt;/color&gt;レベルで本日サインイン完了。正常な出金進行の維持に役立ちます。</t>
+  </si>
+  <si>
+    <t>Revisão bancária leva cerca de &lt;color=#EA2111&gt;{0}&lt;/color&gt; dias. Mantenha a conta ativa—contas inativas podem perder a vez e atrasar a revisão. Mais &lt;color=#EA2111&gt;{1}&lt;/color&gt; níveis para o check-in de hoje. Isso ajuda a manter o progresso normal de saque.</t>
+  </si>
+  <si>
+    <t>Vérification bancaire : environ &lt;color=#EA2111&gt;{0}&lt;/color&gt; jours. Gardez le compte actif—les comptes inactifs peuvent être dépassés et retarder la vérification. Encore &lt;color=#EA2111&gt;{1}&lt;/color&gt; niveaux pour le check-in du jour. Cela aide à maintenir la progression normale du retrait.</t>
+  </si>
+  <si>
+    <t>Revisión bancaria: unos &lt;color=#EA2111&gt;{0}&lt;/color&gt; días. Mantén la cuenta activa—las cuentas inactivas pueden ser superadas y retrasar la revisión. &lt;color=#EA2111&gt;{1}&lt;/color&gt; niveles más para el check-in de hoy. Esto ayuda a mantener el progreso normal de retiro.</t>
+  </si>
+  <si>
+    <t>은행 심사 약 &lt;color=#EA2111&gt;{0}&lt;/color&gt;일. 계정을 활성 상태로 유지하세요. 비활성 계정은 순서가 밀려 심사 진행이 지연될 수 있습니다. 오늘 출석까지 &lt;color=#EA2111&gt;{1}&lt;/color&gt;레벨 더. 정상 출금 진행 유지에 도움이 됩니다.</t>
+  </si>
+  <si>
+    <t>Tinjauan bank sekitar &lt;color=#EA2111&gt;{0}&lt;/color&gt; hari. Jaga akun tetap aktif—akun tidak aktif bisa didahului dan menunda tinjauan. &lt;color=#EA2111&gt;{1}&lt;/color&gt; level lagi untuk check-in hari ini. Ini membantu menjaga progres penarikan normal.</t>
+  </si>
+  <si>
+    <t>Банковская проверка ~&lt;color=#EA2111&gt;{0}&lt;/color&gt; дн. Держите аккаунт активным—неактивные могут быть пропущены в очереди и задержать проверку. Ещё &lt;color=#EA2111&gt;{1}&lt;/color&gt; уровней для сегодняшнего check-in. Это помогает сохранить нормальный прогресс вывода.</t>
+  </si>
+  <si>
+    <t>बैंक समीक्षा लगभग &lt;color=#EA2111&gt;{0}&lt;/color&gt; दिन। खाता सक्रिय रखें—निष्क्रिय खाते कतार में पीछे हो सकते हैं और समीक्षा में देरी हो सकती है। आज का चेक-इन: &lt;color=#EA2111&gt;{1}&lt;/color&gt; लेवल और। सामान्य निकासी प्रगति बनाए रखने में मदद करता है।</t>
+  </si>
+  <si>
+    <t>ตรวจธนาคารประมาณ &lt;color=#EA2111&gt;{0}&lt;/color&gt; วัน รักษาบัญชีให้ใช้งาน บัญชีไม่ใช้งานอาจถูกแทรกคิวและทำให้ความคืบหน้าล่าช้า ผ่านอีก &lt;color=#EA2111&gt;{1}&lt;/color&gt; ด่านเพื่อเช็คอินวันนี้ ช่วยรักษาความคืบหน้าการถอนปกติ</t>
+  </si>
+  <si>
+    <t>Banka incelemesi yaklaşık &lt;color=#EA2111&gt;{0}&lt;/color&gt; gün. Hesabı aktif tutun—pasif hesaplar sıra atlanabilir ve inceleme ilerlemesini geciktirebilir. Bugünkü check-in için &lt;color=#EA2111&gt;{1}&lt;/color&gt; seviye daha. Normal çekim ilerlemesini sürdürmeye yardımcı olur.</t>
+  </si>
+  <si>
+    <t>当前提现申请较多，银行按提交顺序分批处理。请保持账号活跃，再通过&lt;color=#EA2111&gt;{0}&lt;/color&gt;关完成今日签到，有助于维持审核顺位。请耐心等待。</t>
+  </si>
+  <si>
+    <t>High withdrawal volume currently. Banks process in batches by submission order. Keep your account active and clear &lt;color=#EA2111&gt;{0}&lt;/color&gt; more levels for today's check-in to maintain your queue position. Please wait patiently.</t>
+  </si>
+  <si>
+    <t>Derzeit viele Auszahlungsanfragen. Banken bearbeiten in Chargen nach Einreichungsreihenfolge. Konto aktiv halten und noch &lt;color=#EA2111&gt;{0}&lt;/color&gt; Level für heutigen Check-in abschließen, um die Warteschlangenposition zu behalten. Bitte Geduld.</t>
+  </si>
+  <si>
+    <t>現在出金申請が多く、銀行は提出順にバッチ処理しています。口座をアクティブに保ち、あと&lt;color=#EA2111&gt;{0}&lt;/color&gt;レベルで本日サインイン完了。審査順位の維持に役立ちます。しばらくお待ちください。</t>
+  </si>
+  <si>
+    <t>Muitas solicitações de saque no momento. Os bancos processam em lotes por ordem de envio. Mantenha a conta ativa e conclua mais &lt;color=#EA2111&gt;{0}&lt;/color&gt; níveis para o check-in de hoje, ajudando a manter sua posição na fila. Aguarde com paciência.</t>
+  </si>
+  <si>
+    <t>Volume élevé de demandes de retrait. Les banques traitent par lots selon l'ordre de soumission. Gardez le compte actif et terminez encore &lt;color=#EA2111&gt;{0}&lt;/color&gt; niveaux pour le check-in du jour, afin de maintenir votre place dans la file. Veuillez patienter.</t>
+  </si>
+  <si>
+    <t>Hay muchas solicitudes de retiro. Los bancos procesan por lotes según el orden de envío. Mantén la cuenta activa y completa &lt;color=#EA2111&gt;{0}&lt;/color&gt; niveles más para el check-in de hoy, ayudando a mantener tu posición en la cola. Espera con paciencia.</t>
+  </si>
+  <si>
+    <t>현재 출금 신청이 많아 은행이 제출 순서대로 배치 처리 중입니다. 계정을 활성 상태로 유지하고 오늘 출석까지 &lt;color=#EA2111&gt;{0}&lt;/color&gt;레벨 더 완료하세요. 심사 순위 유지에 도움이 됩니다. 잠시만 기다려 주세요.</t>
+  </si>
+  <si>
+    <t>Permintaan penarikan sedang tinggi. Bank memproses per batch sesuai urutan pengajuan. Jaga akun tetap aktif dan selesaikan &lt;color=#EA2111&gt;{0}&lt;/color&gt; level lagi untuk check-in hari ini, membantu mempertahankan posisi antrean. Harap bersabar.</t>
+  </si>
+  <si>
+    <t>Сейчас много заявок на вывод. Банки обрабатывают партиями по порядку подачи. Держите аккаунт активным и пройдите ещё &lt;color=#EA2111&gt;{0}&lt;/color&gt; уровней для сегодняшнего check-in, чтобы сохранить место в очереди. Пожалуйста, подождите.</t>
+  </si>
+  <si>
+    <t>वर्तमान में निकासी अनुरोध अधिक हैं। बैंक जमा क्रम से बैच में प्रोसेस करते हैं। खाता सक्रिय रखें और आज का चेक-इन: &lt;color=#EA2111&gt;{0}&lt;/color&gt; लेवल और पूरे करें, समीक्षा क्रम बनाए रखने में मदद करता है। कृपया धैर्य रखें।</t>
+  </si>
+  <si>
+    <t>ขณะนี้มีคำขอถอนมาก ธนาคารดำเนินการเป็นชุดตามลำดับส่ง รักษาบัญชีให้ใช้งานและผ่านอีก &lt;color=#EA2111&gt;{0}&lt;/color&gt; ด่านเพื่อเช็คอินวันนี้ ช่วยรักษาลำดับการตรวจ โปรดรออย่างใจเย็น</t>
+  </si>
+  <si>
+    <t>Şu anda çok sayıda çekim talebi var. Bankalar gönderim sırasına göre toplu işliyor. Hesabı aktif tutun ve bugünkü check-in için &lt;color=#EA2111&gt;{0}&lt;/color&gt; seviye daha tamamlayın, sıra konumunuzu korumanıza yardımcı olur. Lütfen sabırla bekleyin.</t>
   </si>
   <si>
     <t>观看完整视频
@@ -6297,7 +6665,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6305,6 +6673,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -6358,6 +6729,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6891,11 +7263,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W133"/>
+  <dimension ref="A1:W142"/>
   <sheetFormatPr defaultColWidth="9.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.875" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="4" customWidth="1"/>
     <col min="3" max="3" width="31.625" customWidth="1"/>
     <col min="4" max="4" width="54.25" style="1" customWidth="1"/>
     <col min="5" max="6" width="28.125" customWidth="1"/>
@@ -6905,49 +7277,49 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:16">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="8" t="s">
         <v>14</v>
       </c>
       <c r="P1" t="s">
@@ -6955,68 +7327,68 @@
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:16">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
     </row>
     <row r="3" customHeight="1" spans="1:16">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P3" t="s">
@@ -7024,49 +7396,49 @@
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:16">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="M4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="N4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="9" t="s">
+      <c r="O4" s="10" t="s">
         <v>19</v>
       </c>
       <c r="P4" t="s">
@@ -7074,49 +7446,49 @@
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:16">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="O5" s="7" t="s">
         <v>33</v>
       </c>
       <c r="P5" t="s">
@@ -7124,1059 +7496,1059 @@
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="13.5" spans="1:16">
-      <c r="B6" s="10">
+      <c r="B6" s="11">
         <v>10001</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="N6" s="11" t="s">
+      <c r="N6" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="O6" s="11" t="s">
+      <c r="O6" s="12" t="s">
         <v>47</v>
       </c>
       <c r="P6"/>
     </row>
     <row r="7" customFormat="1" customHeight="1" spans="1:16">
-      <c r="B7" s="10">
+      <c r="B7" s="11">
         <v>10002</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="L7" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="M7" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="N7" s="11" t="s">
+      <c r="N7" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="O7" s="11" t="s">
+      <c r="O7" s="12" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:16">
-      <c r="B8" s="10">
+      <c r="B8" s="11">
         <v>10003</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="J8" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="L8" s="11" t="s">
+      <c r="L8" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="M8" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="N8" s="11" t="s">
+      <c r="N8" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="O8" s="11" t="s">
+      <c r="O8" s="12" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:16">
-      <c r="B9" s="10">
+      <c r="B9" s="11">
         <v>10004</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="J9" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="L9" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="M9" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="N9" s="11" t="s">
+      <c r="N9" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="O9" s="11" t="s">
+      <c r="O9" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:16">
-      <c r="B10" s="10">
+      <c r="B10" s="11">
         <v>10005</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J10" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="L10" s="11" t="s">
+      <c r="L10" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="M10" s="11" t="s">
+      <c r="M10" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="N10" s="11" t="s">
+      <c r="N10" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="O10" s="11" t="s">
+      <c r="O10" s="12" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:16">
-      <c r="B11" s="10">
+      <c r="B11" s="11">
         <v>10006</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="J11" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="L11" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="M11" s="11" t="s">
+      <c r="M11" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="N11" s="11" t="s">
+      <c r="N11" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="O11" s="11" t="s">
+      <c r="O11" s="12" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="B12" s="10">
+      <c r="B12" s="11">
         <v>10007</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="J12" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K12" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="L12" s="11" t="s">
+      <c r="L12" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="M12" s="11" t="s">
+      <c r="M12" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="N12" s="11" t="s">
+      <c r="N12" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="O12" s="11" t="s">
+      <c r="O12" s="12" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="B13" s="10">
+      <c r="B13" s="11">
         <v>10008</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="J13" s="11" t="s">
+      <c r="J13" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K13" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="L13" s="11" t="s">
+      <c r="L13" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="M13" s="11" t="s">
+      <c r="M13" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="N13" s="11" t="s">
+      <c r="N13" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="O13" s="11" t="s">
+      <c r="O13" s="12" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:16">
-      <c r="B14" s="10">
+      <c r="B14" s="11">
         <v>10009</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K14" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="L14" s="11" t="s">
+      <c r="L14" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="M14" s="11" t="s">
+      <c r="M14" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="N14" s="11" t="s">
+      <c r="N14" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="O14" s="11" t="s">
+      <c r="O14" s="12" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:16">
-      <c r="B15" s="10">
+      <c r="B15" s="11">
         <v>10010</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="J15" s="11" t="s">
+      <c r="J15" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="K15" s="11" t="s">
+      <c r="K15" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="L15" s="11" t="s">
+      <c r="L15" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="M15" s="11" t="s">
+      <c r="M15" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="N15" s="11" t="s">
+      <c r="N15" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="O15" s="11" t="s">
+      <c r="O15" s="12" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:16">
-      <c r="B16" s="10">
+      <c r="B16" s="11">
         <v>10011</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="H16" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="I16" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="J16" s="11" t="s">
+      <c r="J16" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="K16" s="11" t="s">
+      <c r="K16" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="L16" s="11" t="s">
+      <c r="L16" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="M16" s="11" t="s">
+      <c r="M16" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="N16" s="11" t="s">
+      <c r="N16" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="O16" s="11" t="s">
+      <c r="O16" s="12" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:23">
-      <c r="B17" s="10">
+      <c r="B17" s="11">
         <v>10012</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="H17" s="11" t="s">
+      <c r="H17" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="I17" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="J17" s="11" t="s">
+      <c r="J17" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="K17" s="11" t="s">
+      <c r="K17" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="L17" s="11" t="s">
+      <c r="L17" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="M17" s="11" t="s">
+      <c r="M17" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="N17" s="11" t="s">
+      <c r="N17" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="O17" s="11" t="s">
+      <c r="O17" s="12" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:23">
-      <c r="B18" s="10">
+      <c r="B18" s="11">
         <v>10013</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="H18" s="11" t="s">
+      <c r="H18" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="I18" s="11" t="s">
+      <c r="I18" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="J18" s="11" t="s">
+      <c r="J18" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="K18" s="11" t="s">
+      <c r="K18" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="L18" s="11" t="s">
+      <c r="L18" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="M18" s="11" t="s">
+      <c r="M18" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="N18" s="11" t="s">
+      <c r="N18" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="O18" s="11" t="s">
+      <c r="O18" s="12" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:23">
-      <c r="B19" s="10">
+      <c r="B19" s="11">
         <v>10014</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="H19" s="11" t="s">
+      <c r="H19" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="I19" s="11" t="s">
+      <c r="I19" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="J19" s="11" t="s">
+      <c r="J19" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="K19" s="11" t="s">
+      <c r="K19" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="L19" s="11" t="s">
+      <c r="L19" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="M19" s="11" t="s">
+      <c r="M19" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="N19" s="11" t="s">
+      <c r="N19" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="O19" s="11" t="s">
+      <c r="O19" s="12" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:23">
-      <c r="B20" s="10">
+      <c r="B20" s="11">
         <v>10015</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="G20" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="H20" s="11" t="s">
+      <c r="H20" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="I20" s="11" t="s">
+      <c r="I20" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="J20" s="11" t="s">
+      <c r="J20" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="K20" s="11" t="s">
+      <c r="K20" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="L20" s="11" t="s">
+      <c r="L20" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="M20" s="11" t="s">
+      <c r="M20" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="N20" s="11" t="s">
+      <c r="N20" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="O20" s="11" t="s">
+      <c r="O20" s="12" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:23">
-      <c r="B21" s="10">
+      <c r="B21" s="11">
         <v>10016</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="G21" s="11" t="s">
+      <c r="G21" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="H21" s="11" t="s">
+      <c r="H21" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="I21" s="11" t="s">
+      <c r="I21" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="J21" s="11" t="s">
+      <c r="J21" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="K21" s="11" t="s">
+      <c r="K21" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="L21" s="11" t="s">
+      <c r="L21" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="M21" s="11" t="s">
+      <c r="M21" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="N21" s="11" t="s">
+      <c r="N21" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="O21" s="11" t="s">
+      <c r="O21" s="12" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:23">
-      <c r="B22" s="10">
+      <c r="B22" s="11">
         <v>10017</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G22" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="H22" s="11" t="s">
+      <c r="H22" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="I22" s="11" t="s">
+      <c r="I22" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="J22" s="11" t="s">
+      <c r="J22" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="K22" s="11" t="s">
+      <c r="K22" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="L22" s="11" t="s">
+      <c r="L22" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="M22" s="11" t="s">
+      <c r="M22" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="N22" s="11" t="s">
+      <c r="N22" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="O22" s="11" t="s">
+      <c r="O22" s="12" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:23">
-      <c r="B23" s="10">
+      <c r="B23" s="11">
         <v>10018</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="G23" s="11" t="s">
+      <c r="G23" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="H23" s="11" t="s">
+      <c r="H23" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="I23" s="11" t="s">
+      <c r="I23" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="J23" s="11" t="s">
+      <c r="J23" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="K23" s="11" t="s">
+      <c r="K23" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="L23" s="11" t="s">
+      <c r="L23" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="M23" s="11" t="s">
+      <c r="M23" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="N23" s="11" t="s">
+      <c r="N23" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="O23" s="11" t="s">
+      <c r="O23" s="12" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="2:23">
-      <c r="B24" s="10">
+      <c r="B24" s="11">
         <v>10019</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="I24" s="11" t="s">
+      <c r="I24" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="J24" s="11" t="s">
+      <c r="J24" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="K24" s="11" t="s">
+      <c r="K24" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="L24" s="11" t="s">
+      <c r="L24" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="M24" s="11" t="s">
+      <c r="M24" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="N24" s="11" t="s">
+      <c r="N24" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="O24" s="11" t="s">
+      <c r="O24" s="12" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="2:23">
-      <c r="B25" s="10">
+      <c r="B25" s="11">
         <v>10020</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="G25" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="H25" s="11" t="s">
+      <c r="H25" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="I25" s="11" t="s">
+      <c r="I25" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="J25" s="11" t="s">
+      <c r="J25" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="K25" s="11" t="s">
+      <c r="K25" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="L25" s="11" t="s">
+      <c r="L25" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="M25" s="11" t="s">
+      <c r="M25" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="N25" s="11" t="s">
+      <c r="N25" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="O25" s="11" t="s">
+      <c r="O25" s="12" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:23">
-      <c r="B26" s="10">
+      <c r="B26" s="11">
         <v>10021</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="G26" s="11" t="s">
+      <c r="G26" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="H26" s="11" t="s">
+      <c r="H26" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="I26" s="11" t="s">
+      <c r="I26" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="J26" s="11" t="s">
+      <c r="J26" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="K26" s="11" t="s">
+      <c r="K26" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="L26" s="11" t="s">
+      <c r="L26" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="M26" s="11" t="s">
+      <c r="M26" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="N26" s="11" t="s">
+      <c r="N26" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="O26" s="11" t="s">
+      <c r="O26" s="12" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:23">
-      <c r="B27" s="10">
+      <c r="B27" s="11">
         <v>10022</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="G27" s="11" t="s">
+      <c r="G27" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="H27" s="11" t="s">
+      <c r="H27" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="I27" s="11" t="s">
+      <c r="I27" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="J27" s="11" t="s">
+      <c r="J27" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="K27" s="11" t="s">
+      <c r="K27" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="L27" s="11" t="s">
+      <c r="L27" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="M27" s="11" t="s">
+      <c r="M27" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="N27" s="11" t="s">
+      <c r="N27" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="O27" s="11" t="s">
+      <c r="O27" s="12" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="28" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B28" s="10">
+      <c r="B28" s="11">
         <v>10023</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="12" t="s">
         <v>312</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E28" s="12" t="s">
         <v>314</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="G28" s="11" t="s">
+      <c r="G28" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="H28" s="11" t="s">
+      <c r="H28" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="I28" s="11" t="s">
+      <c r="I28" s="12" t="s">
         <v>318</v>
       </c>
-      <c r="J28" s="11" t="s">
+      <c r="J28" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="K28" s="11" t="s">
+      <c r="K28" s="12" t="s">
         <v>320</v>
       </c>
-      <c r="L28" s="11" t="s">
+      <c r="L28" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="M28" s="11" t="s">
+      <c r="M28" s="12" t="s">
         <v>322</v>
       </c>
-      <c r="N28" s="11" t="s">
+      <c r="N28" s="12" t="s">
         <v>323</v>
       </c>
-      <c r="O28" s="11" t="s">
+      <c r="O28" s="12" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="29" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B29" s="10">
+      <c r="B29" s="11">
         <v>10024</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="12" t="s">
         <v>328</v>
       </c>
-      <c r="G29" s="11" t="s">
+      <c r="G29" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="H29" s="11" t="s">
+      <c r="H29" s="12" t="s">
         <v>330</v>
       </c>
-      <c r="I29" s="11" t="s">
+      <c r="I29" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="J29" s="11" t="s">
+      <c r="J29" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="K29" s="11" t="s">
+      <c r="K29" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="L29" s="11" t="s">
+      <c r="L29" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="M29" s="11" t="s">
+      <c r="M29" s="12" t="s">
         <v>335</v>
       </c>
-      <c r="N29" s="11" t="s">
+      <c r="N29" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="O29" s="11" t="s">
+      <c r="O29" s="12" t="s">
         <v>337</v>
       </c>
       <c r="Q29" s="1"/>
@@ -8188,46 +8560,46 @@
       <c r="W29" s="1"/>
     </row>
     <row r="30" customHeight="1" spans="2:23">
-      <c r="B30" s="10">
+      <c r="B30" s="11">
         <v>10025</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="13" t="s">
         <v>338</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="12" t="s">
         <v>340</v>
       </c>
-      <c r="G30" s="11" t="s">
+      <c r="G30" s="12" t="s">
         <v>341</v>
       </c>
-      <c r="H30" s="11" t="s">
+      <c r="H30" s="12" t="s">
         <v>342</v>
       </c>
-      <c r="I30" s="11" t="s">
+      <c r="I30" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="J30" s="11" t="s">
+      <c r="J30" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="K30" s="11" t="s">
+      <c r="K30" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="L30" s="11" t="s">
+      <c r="L30" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="M30" s="11" t="s">
+      <c r="M30" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="N30" s="11" t="s">
+      <c r="N30" s="12" t="s">
         <v>348</v>
       </c>
-      <c r="O30" s="11" t="s">
+      <c r="O30" s="12" t="s">
         <v>349</v>
       </c>
       <c r="P30" s="1"/>
@@ -8240,46 +8612,46 @@
       <c r="W30" s="1"/>
     </row>
     <row r="31" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B31" s="10">
+      <c r="B31" s="11">
         <v>10026</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="12" t="s">
         <v>353</v>
       </c>
-      <c r="G31" s="11" t="s">
+      <c r="G31" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="H31" s="11" t="s">
+      <c r="H31" s="12" t="s">
         <v>355</v>
       </c>
-      <c r="I31" s="11" t="s">
+      <c r="I31" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="J31" s="11" t="s">
+      <c r="J31" s="12" t="s">
         <v>356</v>
       </c>
-      <c r="K31" s="11" t="s">
+      <c r="K31" s="12" t="s">
         <v>357</v>
       </c>
-      <c r="L31" s="11" t="s">
+      <c r="L31" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="M31" s="11" t="s">
+      <c r="M31" s="12" t="s">
         <v>359</v>
       </c>
-      <c r="N31" s="11" t="s">
+      <c r="N31" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="O31" s="11" t="s">
+      <c r="O31" s="12" t="s">
         <v>361</v>
       </c>
       <c r="P31"/>
@@ -8292,135 +8664,135 @@
       <c r="W31" s="1"/>
     </row>
     <row r="32" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B32" s="10">
+      <c r="B32" s="11">
         <v>10027</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="12" t="s">
         <v>362</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E32" s="12" t="s">
         <v>364</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="12" t="s">
         <v>365</v>
       </c>
-      <c r="G32" s="11" t="s">
+      <c r="G32" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="H32" s="11" t="s">
+      <c r="H32" s="12" t="s">
         <v>367</v>
       </c>
-      <c r="I32" s="11" t="s">
+      <c r="I32" s="12" t="s">
         <v>368</v>
       </c>
-      <c r="J32" s="13" t="s">
+      <c r="J32" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="K32" s="11" t="s">
+      <c r="K32" s="12" t="s">
         <v>370</v>
       </c>
-      <c r="L32" s="11" t="s">
+      <c r="L32" s="12" t="s">
         <v>371</v>
       </c>
-      <c r="M32" s="11" t="s">
+      <c r="M32" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="N32" s="14" t="s">
+      <c r="N32" s="15" t="s">
         <v>373</v>
       </c>
-      <c r="O32" s="11" t="s">
+      <c r="O32" s="12" t="s">
         <v>374</v>
       </c>
       <c r="P32"/>
     </row>
     <row r="33" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B33" s="10">
+      <c r="B33" s="11">
         <v>10028</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="13" t="s">
         <v>375</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" s="12" t="s">
         <v>376</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="E33" s="12" t="s">
         <v>377</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="F33" s="12" t="s">
         <v>378</v>
       </c>
-      <c r="G33" s="11" t="s">
+      <c r="G33" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="H33" s="11" t="s">
+      <c r="H33" s="12" t="s">
         <v>380</v>
       </c>
-      <c r="I33" s="11" t="s">
+      <c r="I33" s="12" t="s">
         <v>381</v>
       </c>
-      <c r="J33" s="13" t="s">
+      <c r="J33" s="14" t="s">
         <v>382</v>
       </c>
-      <c r="K33" s="11" t="s">
+      <c r="K33" s="12" t="s">
         <v>383</v>
       </c>
-      <c r="L33" s="11" t="s">
+      <c r="L33" s="12" t="s">
         <v>384</v>
       </c>
-      <c r="M33" s="11" t="s">
+      <c r="M33" s="12" t="s">
         <v>385</v>
       </c>
-      <c r="N33" s="14" t="s">
+      <c r="N33" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="O33" s="15" t="s">
+      <c r="O33" s="16" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B34" s="10">
+      <c r="B34" s="11">
         <v>10029</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="12" t="s">
         <v>388</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="E34" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="12" t="s">
         <v>391</v>
       </c>
-      <c r="G34" s="11" t="s">
+      <c r="G34" s="12" t="s">
         <v>392</v>
       </c>
-      <c r="H34" s="11" t="s">
+      <c r="H34" s="12" t="s">
         <v>393</v>
       </c>
-      <c r="I34" s="11" t="s">
+      <c r="I34" s="12" t="s">
         <v>394</v>
       </c>
-      <c r="J34" s="13" t="s">
+      <c r="J34" s="14" t="s">
         <v>395</v>
       </c>
-      <c r="K34" s="11" t="s">
+      <c r="K34" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="L34" s="11" t="s">
+      <c r="L34" s="12" t="s">
         <v>397</v>
       </c>
-      <c r="M34" s="11" t="s">
+      <c r="M34" s="12" t="s">
         <v>398</v>
       </c>
-      <c r="N34" s="14" t="s">
+      <c r="N34" s="15" t="s">
         <v>399</v>
       </c>
-      <c r="O34" s="11" t="s">
+      <c r="O34" s="12" t="s">
         <v>400</v>
       </c>
       <c r="Q34"/>
@@ -8432,46 +8804,46 @@
       <c r="W34"/>
     </row>
     <row r="35" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B35" s="10">
+      <c r="B35" s="11">
         <v>10030</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="13" t="s">
         <v>401</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D35" s="12" t="s">
         <v>402</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="E35" s="12" t="s">
         <v>403</v>
       </c>
-      <c r="F35" s="11" t="s">
+      <c r="F35" s="12" t="s">
         <v>404</v>
       </c>
-      <c r="G35" s="11" t="s">
+      <c r="G35" s="12" t="s">
         <v>405</v>
       </c>
-      <c r="H35" s="11" t="s">
+      <c r="H35" s="12" t="s">
         <v>406</v>
       </c>
-      <c r="I35" s="11" t="s">
+      <c r="I35" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="J35" s="13" t="s">
+      <c r="J35" s="14" t="s">
         <v>408</v>
       </c>
-      <c r="K35" s="11" t="s">
+      <c r="K35" s="12" t="s">
         <v>409</v>
       </c>
-      <c r="L35" s="11" t="s">
+      <c r="L35" s="12" t="s">
         <v>410</v>
       </c>
-      <c r="M35" s="11" t="s">
+      <c r="M35" s="12" t="s">
         <v>411</v>
       </c>
-      <c r="N35" s="14" t="s">
+      <c r="N35" s="15" t="s">
         <v>412</v>
       </c>
-      <c r="O35" s="11" t="s">
+      <c r="O35" s="12" t="s">
         <v>413</v>
       </c>
       <c r="P35"/>
@@ -8484,46 +8856,46 @@
       <c r="W35"/>
     </row>
     <row r="36" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B36" s="10">
+      <c r="B36" s="11">
         <v>10031</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C36" s="12" t="s">
         <v>414</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="D36" s="12" t="s">
         <v>415</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E36" s="12" t="s">
         <v>416</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="F36" s="12" t="s">
         <v>417</v>
       </c>
-      <c r="G36" s="11" t="s">
+      <c r="G36" s="12" t="s">
         <v>418</v>
       </c>
-      <c r="H36" s="11" t="s">
+      <c r="H36" s="12" t="s">
         <v>419</v>
       </c>
-      <c r="I36" s="11" t="s">
+      <c r="I36" s="12" t="s">
         <v>420</v>
       </c>
-      <c r="J36" s="13" t="s">
+      <c r="J36" s="14" t="s">
         <v>421</v>
       </c>
-      <c r="K36" s="11" t="s">
+      <c r="K36" s="12" t="s">
         <v>422</v>
       </c>
-      <c r="L36" s="11" t="s">
+      <c r="L36" s="12" t="s">
         <v>423</v>
       </c>
-      <c r="M36" s="11" t="s">
+      <c r="M36" s="12" t="s">
         <v>424</v>
       </c>
-      <c r="N36" s="14" t="s">
+      <c r="N36" s="15" t="s">
         <v>425</v>
       </c>
-      <c r="O36" s="15" t="s">
+      <c r="O36" s="16" t="s">
         <v>426</v>
       </c>
       <c r="P36"/>
@@ -8536,46 +8908,46 @@
       <c r="W36"/>
     </row>
     <row r="37" customHeight="1" spans="2:23">
-      <c r="B37" s="10">
+      <c r="B37" s="11">
         <v>10032</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="13" t="s">
         <v>427</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" s="12" t="s">
         <v>428</v>
       </c>
-      <c r="E37" s="11" t="s">
+      <c r="E37" s="12" t="s">
         <v>429</v>
       </c>
-      <c r="F37" s="11" t="s">
+      <c r="F37" s="12" t="s">
         <v>430</v>
       </c>
-      <c r="G37" s="11" t="s">
+      <c r="G37" s="12" t="s">
         <v>431</v>
       </c>
-      <c r="H37" s="11" t="s">
+      <c r="H37" s="12" t="s">
         <v>432</v>
       </c>
-      <c r="I37" s="11" t="s">
+      <c r="I37" s="12" t="s">
         <v>433</v>
       </c>
-      <c r="J37" s="13" t="s">
+      <c r="J37" s="14" t="s">
         <v>434</v>
       </c>
-      <c r="K37" s="11" t="s">
+      <c r="K37" s="12" t="s">
         <v>435</v>
       </c>
-      <c r="L37" s="11" t="s">
+      <c r="L37" s="12" t="s">
         <v>436</v>
       </c>
-      <c r="M37" s="11" t="s">
+      <c r="M37" s="12" t="s">
         <v>437</v>
       </c>
-      <c r="N37" s="14" t="s">
+      <c r="N37" s="15" t="s">
         <v>438</v>
       </c>
-      <c r="O37" s="11" t="s">
+      <c r="O37" s="12" t="s">
         <v>439</v>
       </c>
       <c r="Q37" s="1"/>
@@ -8587,46 +8959,46 @@
       <c r="W37" s="1"/>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="2:23">
-      <c r="B38" s="10">
+      <c r="B38" s="11">
         <v>10033</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="12" t="s">
         <v>440</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="D38" s="12" t="s">
         <v>441</v>
       </c>
-      <c r="E38" s="11" t="s">
+      <c r="E38" s="12" t="s">
         <v>442</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="F38" s="12" t="s">
         <v>443</v>
       </c>
-      <c r="G38" s="11" t="s">
+      <c r="G38" s="12" t="s">
         <v>444</v>
       </c>
-      <c r="H38" s="11" t="s">
+      <c r="H38" s="12" t="s">
         <v>445</v>
       </c>
-      <c r="I38" s="11" t="s">
+      <c r="I38" s="12" t="s">
         <v>446</v>
       </c>
-      <c r="J38" s="11" t="s">
+      <c r="J38" s="12" t="s">
         <v>447</v>
       </c>
-      <c r="K38" s="11" t="s">
+      <c r="K38" s="12" t="s">
         <v>448</v>
       </c>
-      <c r="L38" s="11" t="s">
+      <c r="L38" s="12" t="s">
         <v>449</v>
       </c>
-      <c r="M38" s="11" t="s">
+      <c r="M38" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="N38" s="11" t="s">
+      <c r="N38" s="12" t="s">
         <v>451</v>
       </c>
-      <c r="O38" s="11" t="s">
+      <c r="O38" s="12" t="s">
         <v>452</v>
       </c>
       <c r="P38" s="1"/>
@@ -8639,90 +9011,90 @@
       <c r="W38" s="1"/>
     </row>
     <row r="39" customHeight="1" spans="2:23">
-      <c r="B39" s="10">
+      <c r="B39" s="11">
         <v>10034</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="12" t="s">
         <v>453</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="D39" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="E39" s="11" t="s">
+      <c r="E39" s="12" t="s">
         <v>455</v>
       </c>
-      <c r="F39" s="11" t="s">
+      <c r="F39" s="12" t="s">
         <v>456</v>
       </c>
-      <c r="G39" s="11" t="s">
+      <c r="G39" s="12" t="s">
         <v>457</v>
       </c>
-      <c r="H39" s="11" t="s">
+      <c r="H39" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="I39" s="11" t="s">
+      <c r="I39" s="12" t="s">
         <v>459</v>
       </c>
-      <c r="J39" s="11" t="s">
+      <c r="J39" s="12" t="s">
         <v>460</v>
       </c>
-      <c r="K39" s="11" t="s">
+      <c r="K39" s="12" t="s">
         <v>461</v>
       </c>
-      <c r="L39" s="11" t="s">
+      <c r="L39" s="12" t="s">
         <v>462</v>
       </c>
-      <c r="M39" s="11" t="s">
+      <c r="M39" s="12" t="s">
         <v>463</v>
       </c>
-      <c r="N39" s="11" t="s">
+      <c r="N39" s="12" t="s">
         <v>464</v>
       </c>
-      <c r="O39" s="11" t="s">
+      <c r="O39" s="12" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" ht="20" customHeight="1" spans="2:23">
-      <c r="B40" s="10">
+      <c r="B40" s="11">
         <v>10035</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C40" s="12" t="s">
         <v>466</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="D40" s="12" t="s">
         <v>467</v>
       </c>
-      <c r="E40" s="11" t="s">
+      <c r="E40" s="12" t="s">
         <v>468</v>
       </c>
-      <c r="F40" s="11" t="s">
+      <c r="F40" s="12" t="s">
         <v>469</v>
       </c>
-      <c r="G40" s="11" t="s">
+      <c r="G40" s="12" t="s">
         <v>470</v>
       </c>
-      <c r="H40" s="11" t="s">
+      <c r="H40" s="12" t="s">
         <v>471</v>
       </c>
-      <c r="I40" s="11" t="s">
+      <c r="I40" s="12" t="s">
         <v>472</v>
       </c>
-      <c r="J40" s="11" t="s">
+      <c r="J40" s="12" t="s">
         <v>473</v>
       </c>
-      <c r="K40" s="11" t="s">
+      <c r="K40" s="12" t="s">
         <v>474</v>
       </c>
-      <c r="L40" s="11" t="s">
+      <c r="L40" s="12" t="s">
         <v>475</v>
       </c>
-      <c r="M40" s="11" t="s">
+      <c r="M40" s="12" t="s">
         <v>476</v>
       </c>
-      <c r="N40" s="11" t="s">
+      <c r="N40" s="12" t="s">
         <v>477</v>
       </c>
-      <c r="O40" s="11" t="s">
+      <c r="O40" s="12" t="s">
         <v>478</v>
       </c>
       <c r="P40"/>
@@ -8735,46 +9107,46 @@
       <c r="W40"/>
     </row>
     <row r="41" s="1" customFormat="1" ht="19" customHeight="1" spans="2:23">
-      <c r="B41" s="10">
+      <c r="B41" s="11">
         <v>10036</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="13" t="s">
         <v>479</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D41" s="12" t="s">
         <v>480</v>
       </c>
-      <c r="E41" s="11" t="s">
+      <c r="E41" s="12" t="s">
         <v>481</v>
       </c>
-      <c r="F41" s="11" t="s">
+      <c r="F41" s="12" t="s">
         <v>482</v>
       </c>
-      <c r="G41" s="11" t="s">
+      <c r="G41" s="12" t="s">
         <v>483</v>
       </c>
-      <c r="H41" s="11" t="s">
+      <c r="H41" s="12" t="s">
         <v>484</v>
       </c>
-      <c r="I41" s="11" t="s">
+      <c r="I41" s="12" t="s">
         <v>483</v>
       </c>
-      <c r="J41" s="11" t="s">
+      <c r="J41" s="12" t="s">
         <v>485</v>
       </c>
-      <c r="K41" s="11" t="s">
+      <c r="K41" s="12" t="s">
         <v>486</v>
       </c>
-      <c r="L41" s="11" t="s">
+      <c r="L41" s="12" t="s">
         <v>487</v>
       </c>
-      <c r="M41" s="11" t="s">
+      <c r="M41" s="12" t="s">
         <v>488</v>
       </c>
-      <c r="N41" s="11" t="s">
+      <c r="N41" s="12" t="s">
         <v>489</v>
       </c>
-      <c r="O41" s="11" t="s">
+      <c r="O41" s="12" t="s">
         <v>490</v>
       </c>
       <c r="P41"/>
@@ -8787,226 +9159,226 @@
       <c r="W41"/>
     </row>
     <row r="42" customHeight="1" spans="2:23">
-      <c r="B42" s="10">
+      <c r="B42" s="11">
         <v>10037</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="13" t="s">
         <v>491</v>
       </c>
-      <c r="D42" s="11" t="s">
+      <c r="D42" s="12" t="s">
         <v>492</v>
       </c>
-      <c r="E42" s="11" t="s">
+      <c r="E42" s="12" t="s">
         <v>493</v>
       </c>
-      <c r="F42" s="11" t="s">
+      <c r="F42" s="12" t="s">
         <v>494</v>
       </c>
-      <c r="G42" s="11" t="s">
+      <c r="G42" s="12" t="s">
         <v>495</v>
       </c>
-      <c r="H42" s="11" t="s">
+      <c r="H42" s="12" t="s">
         <v>496</v>
       </c>
-      <c r="I42" s="11" t="s">
+      <c r="I42" s="12" t="s">
         <v>497</v>
       </c>
-      <c r="J42" s="11" t="s">
+      <c r="J42" s="12" t="s">
         <v>498</v>
       </c>
-      <c r="K42" s="11" t="s">
+      <c r="K42" s="12" t="s">
         <v>499</v>
       </c>
-      <c r="L42" s="11" t="s">
+      <c r="L42" s="12" t="s">
         <v>500</v>
       </c>
-      <c r="M42" s="11" t="s">
+      <c r="M42" s="12" t="s">
         <v>501</v>
       </c>
-      <c r="N42" s="11" t="s">
+      <c r="N42" s="12" t="s">
         <v>502</v>
       </c>
-      <c r="O42" s="11" t="s">
+      <c r="O42" s="12" t="s">
         <v>503</v>
       </c>
       <c r="P42" s="1"/>
     </row>
     <row r="43" customHeight="1" spans="2:23">
-      <c r="B43" s="10">
+      <c r="B43" s="11">
         <v>10038</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C43" s="12" t="s">
         <v>504</v>
       </c>
-      <c r="D43" s="11" t="s">
+      <c r="D43" s="12" t="s">
         <v>505</v>
       </c>
-      <c r="E43" s="11" t="s">
+      <c r="E43" s="12" t="s">
         <v>506</v>
       </c>
-      <c r="F43" s="11" t="s">
+      <c r="F43" s="12" t="s">
         <v>507</v>
       </c>
-      <c r="G43" s="11" t="s">
+      <c r="G43" s="12" t="s">
         <v>508</v>
       </c>
-      <c r="H43" s="11" t="s">
+      <c r="H43" s="12" t="s">
         <v>509</v>
       </c>
-      <c r="I43" s="11" t="s">
+      <c r="I43" s="12" t="s">
         <v>510</v>
       </c>
-      <c r="J43" s="11" t="s">
+      <c r="J43" s="12" t="s">
         <v>511</v>
       </c>
-      <c r="K43" s="11" t="s">
+      <c r="K43" s="12" t="s">
         <v>512</v>
       </c>
-      <c r="L43" s="11" t="s">
+      <c r="L43" s="12" t="s">
         <v>513</v>
       </c>
-      <c r="M43" s="11" t="s">
+      <c r="M43" s="12" t="s">
         <v>514</v>
       </c>
-      <c r="N43" s="11" t="s">
+      <c r="N43" s="12" t="s">
         <v>515</v>
       </c>
-      <c r="O43" s="11" t="s">
+      <c r="O43" s="12" t="s">
         <v>516</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:23">
-      <c r="B44" s="10">
+      <c r="B44" s="11">
         <v>10039</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C44" s="12" t="s">
         <v>517</v>
       </c>
-      <c r="D44" s="11" t="s">
+      <c r="D44" s="12" t="s">
         <v>518</v>
       </c>
-      <c r="E44" s="11" t="s">
+      <c r="E44" s="12" t="s">
         <v>518</v>
       </c>
-      <c r="F44" s="11" t="s">
+      <c r="F44" s="12" t="s">
         <v>519</v>
       </c>
-      <c r="G44" s="11" t="s">
+      <c r="G44" s="12" t="s">
         <v>520</v>
       </c>
-      <c r="H44" s="11" t="s">
+      <c r="H44" s="12" t="s">
         <v>518</v>
       </c>
-      <c r="I44" s="11" t="s">
+      <c r="I44" s="12" t="s">
         <v>521</v>
       </c>
-      <c r="J44" s="11" t="s">
+      <c r="J44" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="K44" s="11" t="s">
+      <c r="K44" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="L44" s="11" t="s">
+      <c r="L44" s="12" t="s">
         <v>524</v>
       </c>
-      <c r="M44" s="11" t="s">
+      <c r="M44" s="12" t="s">
         <v>525</v>
       </c>
-      <c r="N44" s="11" t="s">
+      <c r="N44" s="12" t="s">
         <v>526</v>
       </c>
-      <c r="O44" s="11" t="s">
+      <c r="O44" s="12" t="s">
         <v>527</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:23">
-      <c r="B45" s="10">
+      <c r="B45" s="11">
         <v>10040</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="D45" s="11" t="s">
+      <c r="D45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="E45" s="11" t="s">
+      <c r="E45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="F45" s="11" t="s">
+      <c r="F45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="G45" s="11" t="s">
+      <c r="G45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="H45" s="11" t="s">
+      <c r="H45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="I45" s="11" t="s">
+      <c r="I45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="J45" s="11" t="s">
+      <c r="J45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="K45" s="11" t="s">
+      <c r="K45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="L45" s="11" t="s">
+      <c r="L45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="M45" s="11" t="s">
+      <c r="M45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="N45" s="11" t="s">
+      <c r="N45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="O45" s="11" t="s">
+      <c r="O45" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="P45" s="16" t="s">
+      <c r="P45" s="17" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:23">
-      <c r="B46" s="10">
+      <c r="B46" s="11">
         <v>10041</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C46" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="D46" s="11" t="s">
+      <c r="D46" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E46" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="F46" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="G46" s="11" t="s">
+      <c r="G46" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="H46" s="11" t="s">
+      <c r="H46" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="I46" s="11" t="s">
+      <c r="I46" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="J46" s="11" t="s">
+      <c r="J46" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="K46" s="11" t="s">
+      <c r="K46" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="L46" s="11" t="s">
+      <c r="L46" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="M46" s="11" t="s">
+      <c r="M46" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="N46" s="11" t="s">
+      <c r="N46" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="O46" s="11" t="s">
+      <c r="O46" s="12" t="s">
         <v>529</v>
       </c>
       <c r="P46" t="s">
@@ -9014,2165 +9386,2165 @@
       </c>
     </row>
     <row r="47" customHeight="1" spans="2:23">
-      <c r="B47" s="10">
+      <c r="B47" s="11">
         <v>10042</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="12" t="s">
         <v>530</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D47" s="13" t="s">
         <v>531</v>
       </c>
-      <c r="E47" s="11" t="s">
+      <c r="E47" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="F47" s="11" t="s">
+      <c r="F47" s="12" t="s">
         <v>533</v>
       </c>
-      <c r="G47" s="11" t="s">
+      <c r="G47" s="12" t="s">
         <v>534</v>
       </c>
-      <c r="H47" s="11" t="s">
+      <c r="H47" s="12" t="s">
         <v>535</v>
       </c>
-      <c r="I47" s="11" t="s">
+      <c r="I47" s="12" t="s">
         <v>536</v>
       </c>
-      <c r="J47" s="11" t="s">
+      <c r="J47" s="12" t="s">
         <v>537</v>
       </c>
-      <c r="K47" s="11" t="s">
+      <c r="K47" s="12" t="s">
         <v>538</v>
       </c>
-      <c r="L47" s="11" t="s">
+      <c r="L47" s="12" t="s">
         <v>539</v>
       </c>
-      <c r="M47" s="11" t="s">
+      <c r="M47" s="12" t="s">
         <v>540</v>
       </c>
-      <c r="N47" s="11" t="s">
+      <c r="N47" s="12" t="s">
         <v>541</v>
       </c>
-      <c r="O47" s="11" t="s">
+      <c r="O47" s="12" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="2:23">
-      <c r="B48" s="10">
+      <c r="B48" s="11">
         <v>10043</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C48" s="12" t="s">
         <v>543</v>
       </c>
-      <c r="D48" s="12" t="s">
+      <c r="D48" s="13" t="s">
         <v>544</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E48" s="12" t="s">
         <v>545</v>
       </c>
-      <c r="F48" s="11" t="s">
+      <c r="F48" s="12" t="s">
         <v>546</v>
       </c>
-      <c r="G48" s="11" t="s">
+      <c r="G48" s="12" t="s">
         <v>547</v>
       </c>
-      <c r="H48" s="11" t="s">
+      <c r="H48" s="12" t="s">
         <v>548</v>
       </c>
-      <c r="I48" s="11" t="s">
+      <c r="I48" s="12" t="s">
         <v>549</v>
       </c>
-      <c r="J48" s="11" t="s">
+      <c r="J48" s="12" t="s">
         <v>550</v>
       </c>
-      <c r="K48" s="11" t="s">
+      <c r="K48" s="12" t="s">
         <v>551</v>
       </c>
-      <c r="L48" s="11" t="s">
+      <c r="L48" s="12" t="s">
         <v>552</v>
       </c>
-      <c r="M48" s="11" t="s">
+      <c r="M48" s="12" t="s">
         <v>553</v>
       </c>
-      <c r="N48" s="11" t="s">
+      <c r="N48" s="12" t="s">
         <v>554</v>
       </c>
-      <c r="O48" s="11" t="s">
+      <c r="O48" s="12" t="s">
         <v>555</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="2:16">
-      <c r="B49" s="10">
+      <c r="B49" s="11">
         <v>10044</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C49" s="12" t="s">
         <v>556</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="D49" s="13" t="s">
         <v>557</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="E49" s="12" t="s">
         <v>558</v>
       </c>
-      <c r="F49" s="11" t="s">
+      <c r="F49" s="12" t="s">
         <v>559</v>
       </c>
-      <c r="G49" s="11" t="s">
+      <c r="G49" s="12" t="s">
         <v>560</v>
       </c>
-      <c r="H49" s="11" t="s">
+      <c r="H49" s="12" t="s">
         <v>561</v>
       </c>
-      <c r="I49" s="11" t="s">
+      <c r="I49" s="12" t="s">
         <v>562</v>
       </c>
-      <c r="J49" s="11" t="s">
+      <c r="J49" s="12" t="s">
         <v>563</v>
       </c>
-      <c r="K49" s="11" t="s">
+      <c r="K49" s="12" t="s">
         <v>564</v>
       </c>
-      <c r="L49" s="11" t="s">
+      <c r="L49" s="12" t="s">
         <v>565</v>
       </c>
-      <c r="M49" s="11" t="s">
+      <c r="M49" s="12" t="s">
         <v>566</v>
       </c>
-      <c r="N49" s="11" t="s">
+      <c r="N49" s="12" t="s">
         <v>567</v>
       </c>
-      <c r="O49" s="11" t="s">
+      <c r="O49" s="12" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="2:16">
-      <c r="B50" s="10">
+      <c r="B50" s="11">
         <v>10045</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C50" s="12" t="s">
         <v>569</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="13" t="s">
         <v>570</v>
       </c>
-      <c r="E50" s="11" t="s">
+      <c r="E50" s="12" t="s">
         <v>571</v>
       </c>
-      <c r="F50" s="11" t="s">
+      <c r="F50" s="12" t="s">
         <v>572</v>
       </c>
-      <c r="G50" s="11" t="s">
+      <c r="G50" s="12" t="s">
         <v>573</v>
       </c>
-      <c r="H50" s="11" t="s">
+      <c r="H50" s="12" t="s">
         <v>574</v>
       </c>
-      <c r="I50" s="11" t="s">
+      <c r="I50" s="12" t="s">
         <v>575</v>
       </c>
-      <c r="J50" s="11" t="s">
+      <c r="J50" s="12" t="s">
         <v>576</v>
       </c>
-      <c r="K50" s="11" t="s">
+      <c r="K50" s="12" t="s">
         <v>577</v>
       </c>
-      <c r="L50" s="11" t="s">
+      <c r="L50" s="12" t="s">
         <v>578</v>
       </c>
-      <c r="M50" s="11" t="s">
+      <c r="M50" s="12" t="s">
         <v>579</v>
       </c>
-      <c r="N50" s="11" t="s">
+      <c r="N50" s="12" t="s">
         <v>580</v>
       </c>
-      <c r="O50" s="11" t="s">
+      <c r="O50" s="12" t="s">
         <v>581</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="2:16">
-      <c r="B51" s="10">
+      <c r="B51" s="11">
         <v>10046</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="12" t="s">
         <v>582</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="13" t="s">
         <v>583</v>
       </c>
-      <c r="E51" s="11" t="s">
+      <c r="E51" s="12" t="s">
         <v>584</v>
       </c>
-      <c r="F51" s="11" t="s">
+      <c r="F51" s="12" t="s">
         <v>585</v>
       </c>
-      <c r="G51" s="11" t="s">
+      <c r="G51" s="12" t="s">
         <v>586</v>
       </c>
-      <c r="H51" s="11" t="s">
+      <c r="H51" s="12" t="s">
         <v>587</v>
       </c>
-      <c r="I51" s="11" t="s">
+      <c r="I51" s="12" t="s">
         <v>588</v>
       </c>
-      <c r="J51" s="11" t="s">
+      <c r="J51" s="12" t="s">
         <v>589</v>
       </c>
-      <c r="K51" s="11" t="s">
+      <c r="K51" s="12" t="s">
         <v>590</v>
       </c>
-      <c r="L51" s="11" t="s">
+      <c r="L51" s="12" t="s">
         <v>591</v>
       </c>
-      <c r="M51" s="11" t="s">
+      <c r="M51" s="12" t="s">
         <v>592</v>
       </c>
-      <c r="N51" s="11" t="s">
+      <c r="N51" s="12" t="s">
         <v>593</v>
       </c>
-      <c r="O51" s="11" t="s">
+      <c r="O51" s="12" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="2:16">
-      <c r="B52" s="10">
+      <c r="B52" s="11">
         <v>10047</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="C52" s="12" t="s">
         <v>595</v>
       </c>
-      <c r="D52" s="11" t="s">
+      <c r="D52" s="12" t="s">
         <v>596</v>
       </c>
-      <c r="E52" s="11" t="s">
+      <c r="E52" s="12" t="s">
         <v>597</v>
       </c>
-      <c r="F52" s="11" t="s">
+      <c r="F52" s="12" t="s">
         <v>598</v>
       </c>
-      <c r="G52" s="11" t="s">
+      <c r="G52" s="12" t="s">
         <v>599</v>
       </c>
-      <c r="H52" s="11" t="s">
+      <c r="H52" s="12" t="s">
         <v>600</v>
       </c>
-      <c r="I52" s="11" t="s">
+      <c r="I52" s="12" t="s">
         <v>601</v>
       </c>
-      <c r="J52" s="11" t="s">
+      <c r="J52" s="12" t="s">
         <v>602</v>
       </c>
-      <c r="K52" s="11" t="s">
+      <c r="K52" s="12" t="s">
         <v>603</v>
       </c>
-      <c r="L52" s="11" t="s">
+      <c r="L52" s="12" t="s">
         <v>604</v>
       </c>
-      <c r="M52" s="11" t="s">
+      <c r="M52" s="12" t="s">
         <v>605</v>
       </c>
-      <c r="N52" s="11" t="s">
+      <c r="N52" s="12" t="s">
         <v>606</v>
       </c>
-      <c r="O52" s="11" t="s">
+      <c r="O52" s="12" t="s">
         <v>607</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="2:16">
-      <c r="B53" s="10">
+      <c r="B53" s="11">
         <v>10048</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="C53" s="12" t="s">
         <v>608</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D53" s="12" t="s">
         <v>609</v>
       </c>
-      <c r="E53" s="11" t="s">
+      <c r="E53" s="12" t="s">
         <v>610</v>
       </c>
-      <c r="F53" s="11" t="s">
+      <c r="F53" s="12" t="s">
         <v>611</v>
       </c>
-      <c r="G53" s="11" t="s">
+      <c r="G53" s="12" t="s">
         <v>612</v>
       </c>
-      <c r="H53" s="11" t="s">
+      <c r="H53" s="12" t="s">
         <v>613</v>
       </c>
-      <c r="I53" s="11" t="s">
+      <c r="I53" s="12" t="s">
         <v>614</v>
       </c>
-      <c r="J53" s="11" t="s">
+      <c r="J53" s="12" t="s">
         <v>615</v>
       </c>
-      <c r="K53" s="11" t="s">
+      <c r="K53" s="12" t="s">
         <v>616</v>
       </c>
-      <c r="L53" s="11" t="s">
+      <c r="L53" s="12" t="s">
         <v>617</v>
       </c>
-      <c r="M53" s="11" t="s">
+      <c r="M53" s="12" t="s">
         <v>618</v>
       </c>
-      <c r="N53" s="11" t="s">
+      <c r="N53" s="12" t="s">
         <v>619</v>
       </c>
-      <c r="O53" s="11" t="s">
+      <c r="O53" s="12" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="2:16">
-      <c r="B54" s="10">
+      <c r="B54" s="11">
         <v>10049</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="C54" s="12" t="s">
         <v>621</v>
       </c>
-      <c r="D54" s="11" t="s">
+      <c r="D54" s="12" t="s">
         <v>622</v>
       </c>
-      <c r="E54" s="11" t="s">
+      <c r="E54" s="12" t="s">
         <v>623</v>
       </c>
-      <c r="F54" s="11" t="s">
+      <c r="F54" s="12" t="s">
         <v>624</v>
       </c>
-      <c r="G54" s="11" t="s">
+      <c r="G54" s="12" t="s">
         <v>625</v>
       </c>
-      <c r="H54" s="11" t="s">
+      <c r="H54" s="12" t="s">
         <v>626</v>
       </c>
-      <c r="I54" s="11" t="s">
+      <c r="I54" s="12" t="s">
         <v>627</v>
       </c>
-      <c r="J54" s="11" t="s">
+      <c r="J54" s="12" t="s">
         <v>628</v>
       </c>
-      <c r="K54" s="11" t="s">
+      <c r="K54" s="12" t="s">
         <v>629</v>
       </c>
-      <c r="L54" s="11" t="s">
+      <c r="L54" s="12" t="s">
         <v>630</v>
       </c>
-      <c r="M54" s="11" t="s">
+      <c r="M54" s="12" t="s">
         <v>631</v>
       </c>
-      <c r="N54" s="11" t="s">
+      <c r="N54" s="12" t="s">
         <v>632</v>
       </c>
-      <c r="O54" s="11" t="s">
+      <c r="O54" s="12" t="s">
         <v>633</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="2:16">
-      <c r="B55" s="10">
+      <c r="B55" s="11">
         <v>10050</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C55" s="12" t="s">
         <v>634</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D55" s="12" t="s">
         <v>635</v>
       </c>
-      <c r="E55" s="11" t="s">
+      <c r="E55" s="12" t="s">
         <v>636</v>
       </c>
-      <c r="F55" s="11" t="s">
+      <c r="F55" s="12" t="s">
         <v>637</v>
       </c>
-      <c r="G55" s="11" t="s">
+      <c r="G55" s="12" t="s">
         <v>638</v>
       </c>
-      <c r="H55" s="11" t="s">
+      <c r="H55" s="12" t="s">
         <v>639</v>
       </c>
-      <c r="I55" s="11" t="s">
+      <c r="I55" s="12" t="s">
         <v>640</v>
       </c>
-      <c r="J55" s="11" t="s">
+      <c r="J55" s="12" t="s">
         <v>641</v>
       </c>
-      <c r="K55" s="11" t="s">
+      <c r="K55" s="12" t="s">
         <v>642</v>
       </c>
-      <c r="L55" s="11" t="s">
+      <c r="L55" s="12" t="s">
         <v>643</v>
       </c>
-      <c r="M55" s="11" t="s">
+      <c r="M55" s="12" t="s">
         <v>644</v>
       </c>
-      <c r="N55" s="11" t="s">
+      <c r="N55" s="12" t="s">
         <v>645</v>
       </c>
-      <c r="O55" s="11" t="s">
+      <c r="O55" s="12" t="s">
         <v>646</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" ht="19" customHeight="1" spans="2:16">
-      <c r="B56" s="10">
+      <c r="B56" s="11">
         <v>10051</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C56" s="12" t="s">
         <v>647</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D56" s="12" t="s">
         <v>648</v>
       </c>
-      <c r="E56" s="11" t="s">
+      <c r="E56" s="12" t="s">
         <v>649</v>
       </c>
-      <c r="F56" s="11" t="s">
+      <c r="F56" s="12" t="s">
         <v>650</v>
       </c>
-      <c r="G56" s="11" t="s">
+      <c r="G56" s="12" t="s">
         <v>651</v>
       </c>
-      <c r="H56" s="11" t="s">
+      <c r="H56" s="12" t="s">
         <v>652</v>
       </c>
-      <c r="I56" s="11" t="s">
+      <c r="I56" s="12" t="s">
         <v>653</v>
       </c>
-      <c r="J56" s="11" t="s">
+      <c r="J56" s="12" t="s">
         <v>654</v>
       </c>
-      <c r="K56" s="11" t="s">
+      <c r="K56" s="12" t="s">
         <v>655</v>
       </c>
-      <c r="L56" s="11" t="s">
+      <c r="L56" s="12" t="s">
         <v>656</v>
       </c>
-      <c r="M56" s="11" t="s">
+      <c r="M56" s="12" t="s">
         <v>657</v>
       </c>
-      <c r="N56" s="11" t="s">
+      <c r="N56" s="12" t="s">
         <v>658</v>
       </c>
-      <c r="O56" s="11" t="s">
+      <c r="O56" s="12" t="s">
         <v>659</v>
       </c>
       <c r="P56"/>
     </row>
     <row r="57" customHeight="1" spans="2:16">
-      <c r="B57" s="10">
+      <c r="B57" s="11">
         <v>10052</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C57" s="12" t="s">
         <v>660</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="D57" s="13" t="s">
         <v>661</v>
       </c>
-      <c r="E57" s="11" t="s">
+      <c r="E57" s="12" t="s">
         <v>662</v>
       </c>
-      <c r="F57" s="11" t="s">
+      <c r="F57" s="12" t="s">
         <v>663</v>
       </c>
-      <c r="G57" s="11" t="s">
+      <c r="G57" s="12" t="s">
         <v>664</v>
       </c>
-      <c r="H57" s="11" t="s">
+      <c r="H57" s="12" t="s">
         <v>665</v>
       </c>
-      <c r="I57" s="11" t="s">
+      <c r="I57" s="12" t="s">
         <v>666</v>
       </c>
-      <c r="J57" s="11" t="s">
+      <c r="J57" s="12" t="s">
         <v>667</v>
       </c>
-      <c r="K57" s="11" t="s">
+      <c r="K57" s="12" t="s">
         <v>668</v>
       </c>
-      <c r="L57" s="11" t="s">
+      <c r="L57" s="12" t="s">
         <v>669</v>
       </c>
-      <c r="M57" s="11" t="s">
+      <c r="M57" s="12" t="s">
         <v>670</v>
       </c>
-      <c r="N57" s="11" t="s">
+      <c r="N57" s="12" t="s">
         <v>671</v>
       </c>
-      <c r="O57" s="11" t="s">
+      <c r="O57" s="12" t="s">
         <v>672</v>
       </c>
       <c r="P57" s="1"/>
     </row>
     <row r="58" customHeight="1" spans="2:16">
-      <c r="B58" s="10">
+      <c r="B58" s="11">
         <v>10053</v>
       </c>
-      <c r="C58" s="11" t="s">
+      <c r="C58" s="12" t="s">
         <v>673</v>
       </c>
-      <c r="D58" s="12" t="s">
+      <c r="D58" s="13" t="s">
         <v>674</v>
       </c>
-      <c r="E58" s="11" t="s">
+      <c r="E58" s="12" t="s">
         <v>675</v>
       </c>
-      <c r="F58" s="11" t="s">
+      <c r="F58" s="12" t="s">
         <v>676</v>
       </c>
-      <c r="G58" s="11" t="s">
+      <c r="G58" s="12" t="s">
         <v>677</v>
       </c>
-      <c r="H58" s="11" t="s">
+      <c r="H58" s="12" t="s">
         <v>678</v>
       </c>
-      <c r="I58" s="11" t="s">
+      <c r="I58" s="12" t="s">
         <v>679</v>
       </c>
-      <c r="J58" s="11" t="s">
+      <c r="J58" s="12" t="s">
         <v>680</v>
       </c>
-      <c r="K58" s="11" t="s">
+      <c r="K58" s="12" t="s">
         <v>681</v>
       </c>
-      <c r="L58" s="11" t="s">
+      <c r="L58" s="12" t="s">
         <v>682</v>
       </c>
-      <c r="M58" s="11" t="s">
+      <c r="M58" s="12" t="s">
         <v>683</v>
       </c>
-      <c r="N58" s="11" t="s">
+      <c r="N58" s="12" t="s">
         <v>684</v>
       </c>
-      <c r="O58" s="11" t="s">
+      <c r="O58" s="12" t="s">
         <v>685</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:16">
-      <c r="B59" s="10">
+      <c r="B59" s="11">
         <v>10054</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C59" s="12" t="s">
         <v>686</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="D59" s="13" t="s">
         <v>687</v>
       </c>
-      <c r="E59" s="11" t="s">
+      <c r="E59" s="12" t="s">
         <v>688</v>
       </c>
-      <c r="F59" s="11" t="s">
+      <c r="F59" s="12" t="s">
         <v>689</v>
       </c>
-      <c r="G59" s="11" t="s">
+      <c r="G59" s="12" t="s">
         <v>690</v>
       </c>
-      <c r="H59" s="11" t="s">
+      <c r="H59" s="12" t="s">
         <v>691</v>
       </c>
-      <c r="I59" s="11" t="s">
+      <c r="I59" s="12" t="s">
         <v>692</v>
       </c>
-      <c r="J59" s="11" t="s">
+      <c r="J59" s="12" t="s">
         <v>693</v>
       </c>
-      <c r="K59" s="11" t="s">
+      <c r="K59" s="12" t="s">
         <v>694</v>
       </c>
-      <c r="L59" s="11" t="s">
+      <c r="L59" s="12" t="s">
         <v>695</v>
       </c>
-      <c r="M59" s="11" t="s">
+      <c r="M59" s="12" t="s">
         <v>696</v>
       </c>
-      <c r="N59" s="11" t="s">
+      <c r="N59" s="12" t="s">
         <v>697</v>
       </c>
-      <c r="O59" s="11" t="s">
+      <c r="O59" s="12" t="s">
         <v>698</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:16">
-      <c r="B60" s="10">
+      <c r="B60" s="11">
         <v>10055</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="C60" s="13" t="s">
         <v>699</v>
       </c>
-      <c r="D60" s="11" t="s">
+      <c r="D60" s="12" t="s">
         <v>700</v>
       </c>
-      <c r="E60" s="11" t="s">
+      <c r="E60" s="12" t="s">
         <v>701</v>
       </c>
-      <c r="F60" s="11" t="s">
+      <c r="F60" s="12" t="s">
         <v>702</v>
       </c>
-      <c r="G60" s="11" t="s">
+      <c r="G60" s="12" t="s">
         <v>703</v>
       </c>
-      <c r="H60" s="11" t="s">
+      <c r="H60" s="12" t="s">
         <v>704</v>
       </c>
-      <c r="I60" s="11" t="s">
+      <c r="I60" s="12" t="s">
         <v>705</v>
       </c>
-      <c r="J60" s="11" t="s">
+      <c r="J60" s="12" t="s">
         <v>706</v>
       </c>
-      <c r="K60" s="11" t="s">
+      <c r="K60" s="12" t="s">
         <v>707</v>
       </c>
-      <c r="L60" s="11" t="s">
+      <c r="L60" s="12" t="s">
         <v>708</v>
       </c>
-      <c r="M60" s="11" t="s">
+      <c r="M60" s="12" t="s">
         <v>709</v>
       </c>
-      <c r="N60" s="11" t="s">
+      <c r="N60" s="12" t="s">
         <v>710</v>
       </c>
-      <c r="O60" s="11" t="s">
+      <c r="O60" s="12" t="s">
         <v>711</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:16">
-      <c r="B61" s="10">
+      <c r="B61" s="11">
         <v>10056</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C61" s="12" t="s">
         <v>712</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="D61" s="13" t="s">
         <v>713</v>
       </c>
-      <c r="E61" s="11" t="s">
+      <c r="E61" s="12" t="s">
         <v>714</v>
       </c>
-      <c r="F61" s="11" t="s">
+      <c r="F61" s="12" t="s">
         <v>715</v>
       </c>
-      <c r="G61" s="11" t="s">
+      <c r="G61" s="12" t="s">
         <v>716</v>
       </c>
-      <c r="H61" s="11" t="s">
+      <c r="H61" s="12" t="s">
         <v>717</v>
       </c>
-      <c r="I61" s="11" t="s">
+      <c r="I61" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="J61" s="11" t="s">
+      <c r="J61" s="12" t="s">
         <v>719</v>
       </c>
-      <c r="K61" s="11" t="s">
+      <c r="K61" s="12" t="s">
         <v>720</v>
       </c>
-      <c r="L61" s="11" t="s">
+      <c r="L61" s="12" t="s">
         <v>721</v>
       </c>
-      <c r="M61" s="11" t="s">
+      <c r="M61" s="12" t="s">
         <v>722</v>
       </c>
-      <c r="N61" s="11" t="s">
+      <c r="N61" s="12" t="s">
         <v>723</v>
       </c>
-      <c r="O61" s="11" t="s">
+      <c r="O61" s="12" t="s">
         <v>724</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:16">
-      <c r="B62" s="10">
+      <c r="B62" s="11">
         <v>10057</v>
       </c>
-      <c r="C62" s="11" t="s">
+      <c r="C62" s="12" t="s">
         <v>725</v>
       </c>
-      <c r="D62" s="11" t="s">
+      <c r="D62" s="12" t="s">
         <v>726</v>
       </c>
-      <c r="E62" s="11" t="s">
+      <c r="E62" s="12" t="s">
         <v>727</v>
       </c>
-      <c r="F62" s="11" t="s">
+      <c r="F62" s="12" t="s">
         <v>728</v>
       </c>
-      <c r="G62" s="11" t="s">
+      <c r="G62" s="12" t="s">
         <v>729</v>
       </c>
-      <c r="H62" s="11" t="s">
+      <c r="H62" s="12" t="s">
         <v>730</v>
       </c>
-      <c r="I62" s="11" t="s">
+      <c r="I62" s="12" t="s">
         <v>731</v>
       </c>
-      <c r="J62" s="11" t="s">
+      <c r="J62" s="12" t="s">
         <v>732</v>
       </c>
-      <c r="K62" s="11" t="s">
+      <c r="K62" s="12" t="s">
         <v>733</v>
       </c>
-      <c r="L62" s="11" t="s">
+      <c r="L62" s="12" t="s">
         <v>734</v>
       </c>
-      <c r="M62" s="11" t="s">
+      <c r="M62" s="12" t="s">
         <v>735</v>
       </c>
-      <c r="N62" s="11" t="s">
+      <c r="N62" s="12" t="s">
         <v>736</v>
       </c>
-      <c r="O62" s="11" t="s">
+      <c r="O62" s="12" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:16">
-      <c r="B63" s="10">
+      <c r="B63" s="11">
         <v>10058</v>
       </c>
-      <c r="C63" s="11" t="s">
+      <c r="C63" s="12" t="s">
         <v>738</v>
       </c>
-      <c r="D63" s="11" t="s">
+      <c r="D63" s="12" t="s">
         <v>739</v>
       </c>
-      <c r="E63" s="11" t="s">
+      <c r="E63" s="12" t="s">
         <v>740</v>
       </c>
-      <c r="F63" s="11" t="s">
+      <c r="F63" s="12" t="s">
         <v>741</v>
       </c>
-      <c r="G63" s="11" t="s">
+      <c r="G63" s="12" t="s">
         <v>742</v>
       </c>
-      <c r="H63" s="11" t="s">
+      <c r="H63" s="12" t="s">
         <v>743</v>
       </c>
-      <c r="I63" s="11" t="s">
+      <c r="I63" s="12" t="s">
         <v>744</v>
       </c>
-      <c r="J63" s="11" t="s">
+      <c r="J63" s="12" t="s">
         <v>745</v>
       </c>
-      <c r="K63" s="11" t="s">
+      <c r="K63" s="12" t="s">
         <v>746</v>
       </c>
-      <c r="L63" s="11" t="s">
+      <c r="L63" s="12" t="s">
         <v>747</v>
       </c>
-      <c r="M63" s="11" t="s">
+      <c r="M63" s="12" t="s">
         <v>748</v>
       </c>
-      <c r="N63" s="11" t="s">
+      <c r="N63" s="12" t="s">
         <v>749</v>
       </c>
-      <c r="O63" s="11" t="s">
+      <c r="O63" s="12" t="s">
         <v>750</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:16">
-      <c r="B64" s="10">
+      <c r="B64" s="11">
         <v>10059</v>
       </c>
-      <c r="C64" s="11" t="s">
+      <c r="C64" s="12" t="s">
         <v>751</v>
       </c>
-      <c r="D64" s="11" t="s">
+      <c r="D64" s="12" t="s">
         <v>752</v>
       </c>
-      <c r="E64" s="11" t="s">
+      <c r="E64" s="12" t="s">
         <v>753</v>
       </c>
-      <c r="F64" s="11" t="s">
+      <c r="F64" s="12" t="s">
         <v>754</v>
       </c>
-      <c r="G64" s="11" t="s">
+      <c r="G64" s="12" t="s">
         <v>755</v>
       </c>
-      <c r="H64" s="11" t="s">
+      <c r="H64" s="12" t="s">
         <v>756</v>
       </c>
-      <c r="I64" s="11" t="s">
+      <c r="I64" s="12" t="s">
         <v>757</v>
       </c>
-      <c r="J64" s="11" t="s">
+      <c r="J64" s="12" t="s">
         <v>758</v>
       </c>
-      <c r="K64" s="11" t="s">
+      <c r="K64" s="12" t="s">
         <v>759</v>
       </c>
-      <c r="L64" s="11" t="s">
+      <c r="L64" s="12" t="s">
         <v>760</v>
       </c>
-      <c r="M64" s="11" t="s">
+      <c r="M64" s="12" t="s">
         <v>761</v>
       </c>
-      <c r="N64" s="11" t="s">
+      <c r="N64" s="12" t="s">
         <v>762</v>
       </c>
-      <c r="O64" s="11" t="s">
+      <c r="O64" s="12" t="s">
         <v>763</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="2:15">
-      <c r="B65" s="10">
+      <c r="B65" s="11">
         <v>10060</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="C65" s="12" t="s">
         <v>764</v>
       </c>
-      <c r="D65" s="11" t="s">
+      <c r="D65" s="12" t="s">
         <v>765</v>
       </c>
-      <c r="E65" s="11" t="s">
+      <c r="E65" s="12" t="s">
         <v>766</v>
       </c>
-      <c r="F65" s="11" t="s">
+      <c r="F65" s="12" t="s">
         <v>767</v>
       </c>
-      <c r="G65" s="11" t="s">
+      <c r="G65" s="12" t="s">
         <v>768</v>
       </c>
-      <c r="H65" s="11" t="s">
+      <c r="H65" s="12" t="s">
         <v>769</v>
       </c>
-      <c r="I65" s="11" t="s">
+      <c r="I65" s="12" t="s">
         <v>770</v>
       </c>
-      <c r="J65" s="11" t="s">
+      <c r="J65" s="12" t="s">
         <v>771</v>
       </c>
-      <c r="K65" s="11" t="s">
+      <c r="K65" s="12" t="s">
         <v>772</v>
       </c>
-      <c r="L65" s="11" t="s">
+      <c r="L65" s="12" t="s">
         <v>773</v>
       </c>
-      <c r="M65" s="11" t="s">
+      <c r="M65" s="12" t="s">
         <v>774</v>
       </c>
-      <c r="N65" s="11" t="s">
+      <c r="N65" s="12" t="s">
         <v>775</v>
       </c>
-      <c r="O65" s="11" t="s">
+      <c r="O65" s="12" t="s">
         <v>776</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="2:15">
-      <c r="B66" s="10">
+      <c r="B66" s="11">
         <v>10061</v>
       </c>
-      <c r="C66" s="11" t="s">
+      <c r="C66" s="12" t="s">
         <v>777</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="D66" s="12" t="s">
         <v>778</v>
       </c>
-      <c r="E66" s="11" t="s">
+      <c r="E66" s="12" t="s">
         <v>779</v>
       </c>
-      <c r="F66" s="11" t="s">
+      <c r="F66" s="12" t="s">
         <v>780</v>
       </c>
-      <c r="G66" s="11" t="s">
+      <c r="G66" s="12" t="s">
         <v>781</v>
       </c>
-      <c r="H66" s="11" t="s">
+      <c r="H66" s="12" t="s">
         <v>782</v>
       </c>
-      <c r="I66" s="11" t="s">
+      <c r="I66" s="12" t="s">
         <v>783</v>
       </c>
-      <c r="J66" s="11" t="s">
+      <c r="J66" s="12" t="s">
         <v>784</v>
       </c>
-      <c r="K66" s="11" t="s">
+      <c r="K66" s="12" t="s">
         <v>785</v>
       </c>
-      <c r="L66" s="11" t="s">
+      <c r="L66" s="12" t="s">
         <v>786</v>
       </c>
-      <c r="M66" s="11" t="s">
+      <c r="M66" s="12" t="s">
         <v>787</v>
       </c>
-      <c r="N66" s="11" t="s">
+      <c r="N66" s="12" t="s">
         <v>788</v>
       </c>
-      <c r="O66" s="11" t="s">
+      <c r="O66" s="12" t="s">
         <v>789</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="2:15">
-      <c r="B67" s="10">
+      <c r="B67" s="11">
         <v>10062</v>
       </c>
-      <c r="C67" s="11" t="s">
+      <c r="C67" s="12" t="s">
         <v>790</v>
       </c>
-      <c r="D67" s="11" t="s">
+      <c r="D67" s="12" t="s">
         <v>791</v>
       </c>
-      <c r="E67" s="11" t="s">
+      <c r="E67" s="12" t="s">
         <v>792</v>
       </c>
-      <c r="F67" s="11" t="s">
+      <c r="F67" s="12" t="s">
         <v>793</v>
       </c>
-      <c r="G67" s="11" t="s">
+      <c r="G67" s="12" t="s">
         <v>794</v>
       </c>
-      <c r="H67" s="11" t="s">
+      <c r="H67" s="12" t="s">
         <v>795</v>
       </c>
-      <c r="I67" s="11" t="s">
+      <c r="I67" s="12" t="s">
         <v>796</v>
       </c>
-      <c r="J67" s="11" t="s">
+      <c r="J67" s="12" t="s">
         <v>797</v>
       </c>
-      <c r="K67" s="11" t="s">
+      <c r="K67" s="12" t="s">
         <v>798</v>
       </c>
-      <c r="L67" s="11" t="s">
+      <c r="L67" s="12" t="s">
         <v>799</v>
       </c>
-      <c r="M67" s="11" t="s">
+      <c r="M67" s="12" t="s">
         <v>800</v>
       </c>
-      <c r="N67" s="11" t="s">
+      <c r="N67" s="12" t="s">
         <v>801</v>
       </c>
-      <c r="O67" s="11" t="s">
+      <c r="O67" s="12" t="s">
         <v>802</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="2:15">
-      <c r="B68" s="10">
+      <c r="B68" s="11">
         <v>10063</v>
       </c>
-      <c r="C68" s="11" t="s">
+      <c r="C68" s="12" t="s">
         <v>803</v>
       </c>
-      <c r="D68" s="12" t="s">
+      <c r="D68" s="13" t="s">
         <v>804</v>
       </c>
-      <c r="E68" s="11" t="s">
+      <c r="E68" s="12" t="s">
         <v>804</v>
       </c>
-      <c r="F68" s="11" t="s">
+      <c r="F68" s="12" t="s">
         <v>805</v>
       </c>
-      <c r="G68" s="11" t="s">
+      <c r="G68" s="12" t="s">
         <v>804</v>
       </c>
-      <c r="H68" s="11" t="s">
+      <c r="H68" s="12" t="s">
         <v>806</v>
       </c>
-      <c r="I68" s="11" t="s">
+      <c r="I68" s="12" t="s">
         <v>807</v>
       </c>
-      <c r="J68" s="11" t="s">
+      <c r="J68" s="12" t="s">
         <v>808</v>
       </c>
-      <c r="K68" s="11" t="s">
+      <c r="K68" s="12" t="s">
         <v>809</v>
       </c>
-      <c r="L68" s="11" t="s">
+      <c r="L68" s="12" t="s">
         <v>810</v>
       </c>
-      <c r="M68" s="11" t="s">
+      <c r="M68" s="12" t="s">
         <v>811</v>
       </c>
-      <c r="N68" s="11" t="s">
+      <c r="N68" s="12" t="s">
         <v>812</v>
       </c>
-      <c r="O68" s="11" t="s">
+      <c r="O68" s="12" t="s">
         <v>813</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="2:15">
-      <c r="B69" s="10">
+      <c r="B69" s="11">
         <v>10064</v>
       </c>
-      <c r="C69" s="11" t="s">
+      <c r="C69" s="12" t="s">
         <v>814</v>
       </c>
-      <c r="D69" s="11" t="s">
+      <c r="D69" s="12" t="s">
         <v>815</v>
       </c>
-      <c r="E69" s="11" t="s">
+      <c r="E69" s="12" t="s">
         <v>816</v>
       </c>
-      <c r="F69" s="11" t="s">
+      <c r="F69" s="12" t="s">
         <v>817</v>
       </c>
-      <c r="G69" s="11" t="s">
+      <c r="G69" s="12" t="s">
         <v>818</v>
       </c>
-      <c r="H69" s="11" t="s">
+      <c r="H69" s="12" t="s">
         <v>819</v>
       </c>
-      <c r="I69" s="11" t="s">
+      <c r="I69" s="12" t="s">
         <v>820</v>
       </c>
-      <c r="J69" s="11" t="s">
+      <c r="J69" s="12" t="s">
         <v>821</v>
       </c>
-      <c r="K69" s="11" t="s">
+      <c r="K69" s="12" t="s">
         <v>822</v>
       </c>
-      <c r="L69" s="11" t="s">
+      <c r="L69" s="12" t="s">
         <v>823</v>
       </c>
-      <c r="M69" s="11" t="s">
+      <c r="M69" s="12" t="s">
         <v>824</v>
       </c>
-      <c r="N69" s="11" t="s">
+      <c r="N69" s="12" t="s">
         <v>825</v>
       </c>
-      <c r="O69" s="11" t="s">
+      <c r="O69" s="12" t="s">
         <v>826</v>
       </c>
     </row>
     <row r="70" ht="19" customHeight="1" spans="2:15">
-      <c r="B70" s="10">
+      <c r="B70" s="11">
         <v>10065</v>
       </c>
-      <c r="C70" s="11" t="s">
+      <c r="C70" s="12" t="s">
         <v>827</v>
       </c>
-      <c r="D70" s="11" t="s">
+      <c r="D70" s="12" t="s">
         <v>828</v>
       </c>
-      <c r="E70" s="11" t="s">
+      <c r="E70" s="12" t="s">
         <v>829</v>
       </c>
-      <c r="F70" s="11" t="s">
+      <c r="F70" s="12" t="s">
         <v>830</v>
       </c>
-      <c r="G70" s="11" t="s">
+      <c r="G70" s="12" t="s">
         <v>831</v>
       </c>
-      <c r="H70" s="11" t="s">
+      <c r="H70" s="12" t="s">
         <v>832</v>
       </c>
-      <c r="I70" s="11" t="s">
+      <c r="I70" s="12" t="s">
         <v>831</v>
       </c>
-      <c r="J70" s="11" t="s">
+      <c r="J70" s="12" t="s">
         <v>833</v>
       </c>
-      <c r="K70" s="11" t="s">
+      <c r="K70" s="12" t="s">
         <v>834</v>
       </c>
-      <c r="L70" s="11" t="s">
+      <c r="L70" s="12" t="s">
         <v>835</v>
       </c>
-      <c r="M70" s="11" t="s">
+      <c r="M70" s="12" t="s">
         <v>836</v>
       </c>
-      <c r="N70" s="11" t="s">
+      <c r="N70" s="12" t="s">
         <v>837</v>
       </c>
-      <c r="O70" s="11" t="s">
+      <c r="O70" s="12" t="s">
         <v>838</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="2:15">
-      <c r="B71" s="10">
+      <c r="B71" s="11">
         <v>10066</v>
       </c>
-      <c r="C71" s="11" t="s">
+      <c r="C71" s="12" t="s">
         <v>839</v>
       </c>
-      <c r="D71" s="12" t="s">
+      <c r="D71" s="13" t="s">
         <v>840</v>
       </c>
-      <c r="E71" s="11" t="s">
+      <c r="E71" s="12" t="s">
         <v>841</v>
       </c>
-      <c r="F71" s="11" t="s">
+      <c r="F71" s="12" t="s">
         <v>842</v>
       </c>
-      <c r="G71" s="11" t="s">
+      <c r="G71" s="12" t="s">
         <v>843</v>
       </c>
-      <c r="H71" s="11" t="s">
+      <c r="H71" s="12" t="s">
         <v>844</v>
       </c>
-      <c r="I71" s="11" t="s">
+      <c r="I71" s="12" t="s">
         <v>843</v>
       </c>
-      <c r="J71" s="11" t="s">
+      <c r="J71" s="12" t="s">
         <v>845</v>
       </c>
-      <c r="K71" s="11" t="s">
+      <c r="K71" s="12" t="s">
         <v>846</v>
       </c>
-      <c r="L71" s="11" t="s">
+      <c r="L71" s="12" t="s">
         <v>847</v>
       </c>
-      <c r="M71" s="11" t="s">
+      <c r="M71" s="12" t="s">
         <v>848</v>
       </c>
-      <c r="N71" s="11" t="s">
+      <c r="N71" s="12" t="s">
         <v>849</v>
       </c>
-      <c r="O71" s="11" t="s">
+      <c r="O71" s="12" t="s">
         <v>850</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="2:15">
-      <c r="B72" s="10">
+      <c r="B72" s="11">
         <v>10067</v>
       </c>
-      <c r="C72" s="11" t="s">
+      <c r="C72" s="12" t="s">
         <v>851</v>
       </c>
-      <c r="D72" s="12" t="s">
+      <c r="D72" s="13" t="s">
         <v>852</v>
       </c>
-      <c r="E72" s="11" t="s">
+      <c r="E72" s="12" t="s">
         <v>853</v>
       </c>
-      <c r="F72" s="11" t="s">
+      <c r="F72" s="12" t="s">
         <v>854</v>
       </c>
-      <c r="G72" s="11" t="s">
+      <c r="G72" s="12" t="s">
         <v>855</v>
       </c>
-      <c r="H72" s="11" t="s">
+      <c r="H72" s="12" t="s">
         <v>856</v>
       </c>
-      <c r="I72" s="11" t="s">
+      <c r="I72" s="12" t="s">
         <v>855</v>
       </c>
-      <c r="J72" s="11" t="s">
+      <c r="J72" s="12" t="s">
         <v>857</v>
       </c>
-      <c r="K72" s="11" t="s">
+      <c r="K72" s="12" t="s">
         <v>855</v>
       </c>
-      <c r="L72" s="11" t="s">
+      <c r="L72" s="12" t="s">
         <v>858</v>
       </c>
-      <c r="M72" s="11" t="s">
+      <c r="M72" s="12" t="s">
         <v>859</v>
       </c>
-      <c r="N72" s="11" t="s">
+      <c r="N72" s="12" t="s">
         <v>860</v>
       </c>
-      <c r="O72" s="11" t="s">
+      <c r="O72" s="12" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="2:15">
-      <c r="B73" s="10">
+      <c r="B73" s="11">
         <v>10068</v>
       </c>
-      <c r="C73" s="11" t="s">
+      <c r="C73" s="12" t="s">
         <v>862</v>
       </c>
-      <c r="D73" s="12" t="s">
+      <c r="D73" s="13" t="s">
         <v>863</v>
       </c>
-      <c r="E73" s="11" t="s">
+      <c r="E73" s="12" t="s">
         <v>864</v>
       </c>
-      <c r="F73" s="11" t="s">
+      <c r="F73" s="12" t="s">
         <v>865</v>
       </c>
-      <c r="G73" s="11" t="s">
+      <c r="G73" s="12" t="s">
         <v>866</v>
       </c>
-      <c r="H73" s="11" t="s">
+      <c r="H73" s="12" t="s">
         <v>867</v>
       </c>
-      <c r="I73" s="11" t="s">
+      <c r="I73" s="12" t="s">
         <v>868</v>
       </c>
-      <c r="J73" s="11" t="s">
+      <c r="J73" s="12" t="s">
         <v>869</v>
       </c>
-      <c r="K73" s="11" t="s">
+      <c r="K73" s="12" t="s">
         <v>870</v>
       </c>
-      <c r="L73" s="11" t="s">
+      <c r="L73" s="12" t="s">
         <v>871</v>
       </c>
-      <c r="M73" s="11" t="s">
+      <c r="M73" s="12" t="s">
         <v>872</v>
       </c>
-      <c r="N73" s="11" t="s">
+      <c r="N73" s="12" t="s">
         <v>873</v>
       </c>
-      <c r="O73" s="11" t="s">
+      <c r="O73" s="12" t="s">
         <v>874</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="2:15">
-      <c r="B74" s="10">
+      <c r="B74" s="11">
         <v>10069</v>
       </c>
-      <c r="C74" s="11" t="s">
+      <c r="C74" s="12" t="s">
         <v>875</v>
       </c>
-      <c r="D74" s="12" t="s">
+      <c r="D74" s="13" t="s">
         <v>876</v>
       </c>
-      <c r="E74" s="11" t="s">
+      <c r="E74" s="12" t="s">
         <v>877</v>
       </c>
-      <c r="F74" s="11" t="s">
+      <c r="F74" s="12" t="s">
         <v>878</v>
       </c>
-      <c r="G74" s="11" t="s">
+      <c r="G74" s="12" t="s">
         <v>879</v>
       </c>
-      <c r="H74" s="11" t="s">
+      <c r="H74" s="12" t="s">
         <v>880</v>
       </c>
-      <c r="I74" s="11" t="s">
+      <c r="I74" s="12" t="s">
         <v>881</v>
       </c>
-      <c r="J74" s="11" t="s">
+      <c r="J74" s="12" t="s">
         <v>882</v>
       </c>
-      <c r="K74" s="11" t="s">
+      <c r="K74" s="12" t="s">
         <v>883</v>
       </c>
-      <c r="L74" s="11" t="s">
+      <c r="L74" s="12" t="s">
         <v>884</v>
       </c>
-      <c r="M74" s="11" t="s">
+      <c r="M74" s="12" t="s">
         <v>885</v>
       </c>
-      <c r="N74" s="11" t="s">
+      <c r="N74" s="12" t="s">
         <v>886</v>
       </c>
-      <c r="O74" s="11" t="s">
+      <c r="O74" s="12" t="s">
         <v>887</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="2:15">
-      <c r="B75" s="10">
+      <c r="B75" s="11">
         <v>10070</v>
       </c>
-      <c r="C75" s="11" t="s">
+      <c r="C75" s="12" t="s">
         <v>888</v>
       </c>
-      <c r="D75" s="11" t="s">
+      <c r="D75" s="12" t="s">
         <v>889</v>
       </c>
-      <c r="E75" s="11" t="s">
+      <c r="E75" s="12" t="s">
         <v>890</v>
       </c>
-      <c r="F75" s="11" t="s">
+      <c r="F75" s="12" t="s">
         <v>891</v>
       </c>
-      <c r="G75" s="11" t="s">
+      <c r="G75" s="12" t="s">
         <v>892</v>
       </c>
-      <c r="H75" s="11" t="s">
+      <c r="H75" s="12" t="s">
         <v>893</v>
       </c>
-      <c r="I75" s="11" t="s">
+      <c r="I75" s="12" t="s">
         <v>894</v>
       </c>
-      <c r="J75" s="11" t="s">
+      <c r="J75" s="12" t="s">
         <v>895</v>
       </c>
-      <c r="K75" s="11" t="s">
+      <c r="K75" s="12" t="s">
         <v>896</v>
       </c>
-      <c r="L75" s="11" t="s">
+      <c r="L75" s="12" t="s">
         <v>897</v>
       </c>
-      <c r="M75" s="11" t="s">
+      <c r="M75" s="12" t="s">
         <v>898</v>
       </c>
-      <c r="N75" s="11" t="s">
+      <c r="N75" s="12" t="s">
         <v>899</v>
       </c>
-      <c r="O75" s="11" t="s">
+      <c r="O75" s="12" t="s">
         <v>900</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="2:15">
-      <c r="B76" s="10">
+      <c r="B76" s="11">
         <v>10071</v>
       </c>
-      <c r="C76" s="11" t="s">
+      <c r="C76" s="12" t="s">
         <v>901</v>
       </c>
-      <c r="D76" s="11" t="s">
+      <c r="D76" s="12" t="s">
         <v>902</v>
       </c>
-      <c r="E76" s="11" t="s">
+      <c r="E76" s="12" t="s">
         <v>903</v>
       </c>
-      <c r="F76" s="11" t="s">
+      <c r="F76" s="12" t="s">
         <v>904</v>
       </c>
-      <c r="G76" s="11" t="s">
+      <c r="G76" s="12" t="s">
         <v>905</v>
       </c>
-      <c r="H76" s="11" t="s">
+      <c r="H76" s="12" t="s">
         <v>906</v>
       </c>
-      <c r="I76" s="11" t="s">
+      <c r="I76" s="12" t="s">
         <v>907</v>
       </c>
-      <c r="J76" s="11" t="s">
+      <c r="J76" s="12" t="s">
         <v>908</v>
       </c>
-      <c r="K76" s="11" t="s">
+      <c r="K76" s="12" t="s">
         <v>909</v>
       </c>
-      <c r="L76" s="11" t="s">
+      <c r="L76" s="12" t="s">
         <v>910</v>
       </c>
-      <c r="M76" s="11" t="s">
+      <c r="M76" s="12" t="s">
         <v>911</v>
       </c>
-      <c r="N76" s="11" t="s">
+      <c r="N76" s="12" t="s">
         <v>912</v>
       </c>
-      <c r="O76" s="11" t="s">
+      <c r="O76" s="12" t="s">
         <v>913</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="2:15">
-      <c r="B77" s="10">
+      <c r="B77" s="11">
         <v>10072</v>
       </c>
-      <c r="C77" s="11" t="s">
+      <c r="C77" s="12" t="s">
         <v>914</v>
       </c>
-      <c r="D77" s="11" t="s">
+      <c r="D77" s="12" t="s">
         <v>915</v>
       </c>
-      <c r="E77" s="11" t="s">
+      <c r="E77" s="12" t="s">
         <v>916</v>
       </c>
-      <c r="F77" s="11" t="s">
+      <c r="F77" s="12" t="s">
         <v>917</v>
       </c>
-      <c r="G77" s="11" t="s">
+      <c r="G77" s="12" t="s">
         <v>918</v>
       </c>
-      <c r="H77" s="11" t="s">
+      <c r="H77" s="12" t="s">
         <v>919</v>
       </c>
-      <c r="I77" s="11" t="s">
+      <c r="I77" s="12" t="s">
         <v>920</v>
       </c>
-      <c r="J77" s="11" t="s">
+      <c r="J77" s="12" t="s">
         <v>921</v>
       </c>
-      <c r="K77" s="11" t="s">
+      <c r="K77" s="12" t="s">
         <v>922</v>
       </c>
-      <c r="L77" s="11" t="s">
+      <c r="L77" s="12" t="s">
         <v>923</v>
       </c>
-      <c r="M77" s="11" t="s">
+      <c r="M77" s="12" t="s">
         <v>924</v>
       </c>
-      <c r="N77" s="11" t="s">
+      <c r="N77" s="12" t="s">
         <v>925</v>
       </c>
-      <c r="O77" s="11" t="s">
+      <c r="O77" s="12" t="s">
         <v>926</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="2:15">
-      <c r="B78" s="10">
+      <c r="B78" s="11">
         <v>10073</v>
       </c>
-      <c r="C78" s="11" t="s">
+      <c r="C78" s="12" t="s">
         <v>927</v>
       </c>
-      <c r="D78" s="12" t="s">
+      <c r="D78" s="13" t="s">
         <v>928</v>
       </c>
-      <c r="E78" s="11" t="s">
+      <c r="E78" s="12" t="s">
         <v>929</v>
       </c>
-      <c r="F78" s="11" t="s">
+      <c r="F78" s="12" t="s">
         <v>930</v>
       </c>
-      <c r="G78" s="11" t="s">
+      <c r="G78" s="12" t="s">
         <v>931</v>
       </c>
-      <c r="H78" s="11" t="s">
+      <c r="H78" s="12" t="s">
         <v>932</v>
       </c>
-      <c r="I78" s="11" t="s">
+      <c r="I78" s="12" t="s">
         <v>933</v>
       </c>
-      <c r="J78" s="11" t="s">
+      <c r="J78" s="12" t="s">
         <v>934</v>
       </c>
-      <c r="K78" s="11" t="s">
+      <c r="K78" s="12" t="s">
         <v>935</v>
       </c>
-      <c r="L78" s="11" t="s">
+      <c r="L78" s="12" t="s">
         <v>936</v>
       </c>
-      <c r="M78" s="11" t="s">
+      <c r="M78" s="12" t="s">
         <v>937</v>
       </c>
-      <c r="N78" s="11" t="s">
+      <c r="N78" s="12" t="s">
         <v>938</v>
       </c>
-      <c r="O78" s="11" t="s">
+      <c r="O78" s="12" t="s">
         <v>939</v>
       </c>
     </row>
     <row r="79" ht="19" customHeight="1" spans="2:15">
-      <c r="B79" s="10">
+      <c r="B79" s="11">
         <v>10074</v>
       </c>
-      <c r="C79" s="12" t="s">
+      <c r="C79" s="13" t="s">
         <v>940</v>
       </c>
-      <c r="D79" s="12" t="s">
+      <c r="D79" s="13" t="s">
         <v>941</v>
       </c>
-      <c r="E79" s="11" t="s">
+      <c r="E79" s="12" t="s">
         <v>942</v>
       </c>
-      <c r="F79" s="11" t="s">
+      <c r="F79" s="12" t="s">
         <v>943</v>
       </c>
-      <c r="G79" s="11" t="s">
+      <c r="G79" s="12" t="s">
         <v>944</v>
       </c>
-      <c r="H79" s="11" t="s">
+      <c r="H79" s="12" t="s">
         <v>945</v>
       </c>
-      <c r="I79" s="11" t="s">
+      <c r="I79" s="12" t="s">
         <v>946</v>
       </c>
-      <c r="J79" s="11" t="s">
+      <c r="J79" s="12" t="s">
         <v>947</v>
       </c>
-      <c r="K79" s="11" t="s">
+      <c r="K79" s="12" t="s">
         <v>948</v>
       </c>
-      <c r="L79" s="11" t="s">
+      <c r="L79" s="12" t="s">
         <v>949</v>
       </c>
-      <c r="M79" s="11" t="s">
+      <c r="M79" s="12" t="s">
         <v>950</v>
       </c>
-      <c r="N79" s="11" t="s">
+      <c r="N79" s="12" t="s">
         <v>951</v>
       </c>
-      <c r="O79" s="11" t="s">
+      <c r="O79" s="12" t="s">
         <v>952</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="2:15">
-      <c r="B80" s="10">
+      <c r="B80" s="11">
         <v>10075</v>
       </c>
-      <c r="C80" s="11" t="s">
+      <c r="C80" s="12" t="s">
         <v>953</v>
       </c>
-      <c r="D80" s="12" t="s">
+      <c r="D80" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="E80" s="11" t="s">
+      <c r="E80" s="12" t="s">
         <v>955</v>
       </c>
-      <c r="F80" s="11" t="s">
+      <c r="F80" s="12" t="s">
         <v>956</v>
       </c>
-      <c r="G80" s="11" t="s">
+      <c r="G80" s="12" t="s">
         <v>957</v>
       </c>
-      <c r="H80" s="11" t="s">
+      <c r="H80" s="12" t="s">
         <v>958</v>
       </c>
-      <c r="I80" s="11" t="s">
+      <c r="I80" s="12" t="s">
         <v>959</v>
       </c>
-      <c r="J80" s="11" t="s">
+      <c r="J80" s="12" t="s">
         <v>960</v>
       </c>
-      <c r="K80" s="11" t="s">
+      <c r="K80" s="12" t="s">
         <v>961</v>
       </c>
-      <c r="L80" s="11" t="s">
+      <c r="L80" s="12" t="s">
         <v>962</v>
       </c>
-      <c r="M80" s="11" t="s">
+      <c r="M80" s="12" t="s">
         <v>963</v>
       </c>
-      <c r="N80" s="11" t="s">
+      <c r="N80" s="12" t="s">
         <v>964</v>
       </c>
-      <c r="O80" s="11" t="s">
+      <c r="O80" s="12" t="s">
         <v>965</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="2:15">
-      <c r="B81" s="10">
+      <c r="B81" s="11">
         <v>10076</v>
       </c>
-      <c r="C81" s="11" t="s">
+      <c r="C81" s="12" t="s">
         <v>966</v>
       </c>
-      <c r="D81" s="12" t="s">
+      <c r="D81" s="13" t="s">
         <v>967</v>
       </c>
-      <c r="E81" s="11" t="s">
+      <c r="E81" s="12" t="s">
         <v>968</v>
       </c>
-      <c r="F81" s="11" t="s">
+      <c r="F81" s="12" t="s">
         <v>969</v>
       </c>
-      <c r="G81" s="11" t="s">
+      <c r="G81" s="12" t="s">
         <v>970</v>
       </c>
-      <c r="H81" s="11" t="s">
+      <c r="H81" s="12" t="s">
         <v>971</v>
       </c>
-      <c r="I81" s="11" t="s">
+      <c r="I81" s="12" t="s">
         <v>972</v>
       </c>
-      <c r="J81" s="11" t="s">
+      <c r="J81" s="12" t="s">
         <v>973</v>
       </c>
-      <c r="K81" s="11" t="s">
+      <c r="K81" s="12" t="s">
         <v>974</v>
       </c>
-      <c r="L81" s="11" t="s">
+      <c r="L81" s="12" t="s">
         <v>975</v>
       </c>
-      <c r="M81" s="11" t="s">
+      <c r="M81" s="12" t="s">
         <v>976</v>
       </c>
-      <c r="N81" s="11" t="s">
+      <c r="N81" s="12" t="s">
         <v>977</v>
       </c>
-      <c r="O81" s="11" t="s">
+      <c r="O81" s="12" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="2:15">
-      <c r="B82" s="10">
+      <c r="B82" s="11">
         <v>10077</v>
       </c>
-      <c r="C82" s="11" t="s">
+      <c r="C82" s="12" t="s">
         <v>979</v>
       </c>
-      <c r="D82" s="12" t="s">
+      <c r="D82" s="13" t="s">
         <v>980</v>
       </c>
-      <c r="E82" s="11" t="s">
+      <c r="E82" s="12" t="s">
         <v>981</v>
       </c>
-      <c r="F82" s="11" t="s">
+      <c r="F82" s="12" t="s">
         <v>982</v>
       </c>
-      <c r="G82" s="11" t="s">
+      <c r="G82" s="12" t="s">
         <v>983</v>
       </c>
-      <c r="H82" s="11" t="s">
+      <c r="H82" s="12" t="s">
         <v>984</v>
       </c>
-      <c r="I82" s="11" t="s">
+      <c r="I82" s="12" t="s">
         <v>985</v>
       </c>
-      <c r="J82" s="11" t="s">
+      <c r="J82" s="12" t="s">
         <v>986</v>
       </c>
-      <c r="K82" s="11" t="s">
+      <c r="K82" s="12" t="s">
         <v>987</v>
       </c>
-      <c r="L82" s="11" t="s">
+      <c r="L82" s="12" t="s">
         <v>988</v>
       </c>
-      <c r="M82" s="11" t="s">
+      <c r="M82" s="12" t="s">
         <v>989</v>
       </c>
-      <c r="N82" s="11" t="s">
+      <c r="N82" s="12" t="s">
         <v>990</v>
       </c>
-      <c r="O82" s="11" t="s">
+      <c r="O82" s="12" t="s">
         <v>991</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="2:15">
-      <c r="B83" s="10">
+      <c r="B83" s="11">
         <v>10078</v>
       </c>
-      <c r="C83" s="11" t="s">
+      <c r="C83" s="12" t="s">
         <v>992</v>
       </c>
-      <c r="D83" s="12" t="s">
+      <c r="D83" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="E83" s="11" t="s">
+      <c r="E83" s="12" t="s">
         <v>994</v>
       </c>
-      <c r="F83" s="11" t="s">
+      <c r="F83" s="12" t="s">
         <v>995</v>
       </c>
-      <c r="G83" s="11" t="s">
+      <c r="G83" s="12" t="s">
         <v>996</v>
       </c>
-      <c r="H83" s="11" t="s">
+      <c r="H83" s="12" t="s">
         <v>997</v>
       </c>
-      <c r="I83" s="11" t="s">
+      <c r="I83" s="12" t="s">
         <v>998</v>
       </c>
-      <c r="J83" s="11" t="s">
+      <c r="J83" s="12" t="s">
         <v>999</v>
       </c>
-      <c r="K83" s="11" t="s">
+      <c r="K83" s="12" t="s">
         <v>1000</v>
       </c>
-      <c r="L83" s="11" t="s">
+      <c r="L83" s="12" t="s">
         <v>1001</v>
       </c>
-      <c r="M83" s="11" t="s">
+      <c r="M83" s="12" t="s">
         <v>1002</v>
       </c>
-      <c r="N83" s="11" t="s">
+      <c r="N83" s="12" t="s">
         <v>1003</v>
       </c>
-      <c r="O83" s="11" t="s">
+      <c r="O83" s="12" t="s">
         <v>1004</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="2:15">
-      <c r="B84" s="10">
+      <c r="B84" s="11">
         <v>10079</v>
       </c>
-      <c r="C84" s="11" t="s">
+      <c r="C84" s="12" t="s">
         <v>1005</v>
       </c>
-      <c r="D84" s="12" t="s">
+      <c r="D84" s="13" t="s">
         <v>1006</v>
       </c>
-      <c r="E84" s="11" t="s">
+      <c r="E84" s="12" t="s">
         <v>1007</v>
       </c>
-      <c r="F84" s="11" t="s">
+      <c r="F84" s="12" t="s">
         <v>1008</v>
       </c>
-      <c r="G84" s="11" t="s">
+      <c r="G84" s="12" t="s">
         <v>1009</v>
       </c>
-      <c r="H84" s="11" t="s">
+      <c r="H84" s="12" t="s">
         <v>1010</v>
       </c>
-      <c r="I84" s="11" t="s">
+      <c r="I84" s="12" t="s">
         <v>1011</v>
       </c>
-      <c r="J84" s="11" t="s">
+      <c r="J84" s="12" t="s">
         <v>1012</v>
       </c>
-      <c r="K84" s="11" t="s">
+      <c r="K84" s="12" t="s">
         <v>1013</v>
       </c>
-      <c r="L84" s="11" t="s">
+      <c r="L84" s="12" t="s">
         <v>1014</v>
       </c>
-      <c r="M84" s="11" t="s">
+      <c r="M84" s="12" t="s">
         <v>1015</v>
       </c>
-      <c r="N84" s="11" t="s">
+      <c r="N84" s="12" t="s">
         <v>1016</v>
       </c>
-      <c r="O84" s="11" t="s">
+      <c r="O84" s="12" t="s">
         <v>1017</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="2:15">
-      <c r="B85" s="10">
+      <c r="B85" s="11">
         <v>10080</v>
       </c>
-      <c r="C85" s="11" t="s">
+      <c r="C85" s="12" t="s">
         <v>1018</v>
       </c>
-      <c r="D85" s="12" t="s">
+      <c r="D85" s="13" t="s">
         <v>1019</v>
       </c>
-      <c r="E85" s="11" t="s">
+      <c r="E85" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="F85" s="11" t="s">
+      <c r="F85" s="12" t="s">
         <v>1021</v>
       </c>
-      <c r="G85" s="11" t="s">
+      <c r="G85" s="12" t="s">
         <v>1022</v>
       </c>
-      <c r="H85" s="11" t="s">
+      <c r="H85" s="12" t="s">
         <v>1023</v>
       </c>
-      <c r="I85" s="11" t="s">
+      <c r="I85" s="12" t="s">
         <v>1024</v>
       </c>
-      <c r="J85" s="11" t="s">
+      <c r="J85" s="12" t="s">
         <v>1025</v>
       </c>
-      <c r="K85" s="11" t="s">
+      <c r="K85" s="12" t="s">
         <v>1026</v>
       </c>
-      <c r="L85" s="11" t="s">
+      <c r="L85" s="12" t="s">
         <v>1027</v>
       </c>
-      <c r="M85" s="11" t="s">
+      <c r="M85" s="12" t="s">
         <v>1028</v>
       </c>
-      <c r="N85" s="11" t="s">
+      <c r="N85" s="12" t="s">
         <v>1029</v>
       </c>
-      <c r="O85" s="11" t="s">
+      <c r="O85" s="12" t="s">
         <v>1030</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="2:15">
-      <c r="B86" s="10">
+      <c r="B86" s="11">
         <v>10081</v>
       </c>
-      <c r="C86" s="11" t="s">
+      <c r="C86" s="12" t="s">
         <v>1031</v>
       </c>
-      <c r="D86" s="12" t="s">
+      <c r="D86" s="13" t="s">
         <v>1032</v>
       </c>
-      <c r="E86" s="11" t="s">
+      <c r="E86" s="12" t="s">
         <v>1033</v>
       </c>
-      <c r="F86" s="11" t="s">
+      <c r="F86" s="12" t="s">
         <v>1034</v>
       </c>
-      <c r="G86" s="11" t="s">
+      <c r="G86" s="12" t="s">
         <v>1035</v>
       </c>
-      <c r="H86" s="11" t="s">
+      <c r="H86" s="12" t="s">
         <v>1036</v>
       </c>
-      <c r="I86" s="11" t="s">
+      <c r="I86" s="12" t="s">
         <v>1037</v>
       </c>
-      <c r="J86" s="11" t="s">
+      <c r="J86" s="12" t="s">
         <v>1038</v>
       </c>
-      <c r="K86" s="11" t="s">
+      <c r="K86" s="12" t="s">
         <v>1039</v>
       </c>
-      <c r="L86" s="11" t="s">
+      <c r="L86" s="12" t="s">
         <v>1040</v>
       </c>
-      <c r="M86" s="11" t="s">
+      <c r="M86" s="12" t="s">
         <v>1041</v>
       </c>
-      <c r="N86" s="11" t="s">
+      <c r="N86" s="12" t="s">
         <v>1042</v>
       </c>
-      <c r="O86" s="11" t="s">
+      <c r="O86" s="12" t="s">
         <v>1043</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="2:15">
-      <c r="B87" s="10">
+      <c r="B87" s="11">
         <v>10082</v>
       </c>
-      <c r="C87" s="11" t="s">
+      <c r="C87" s="12" t="s">
         <v>1044</v>
       </c>
-      <c r="D87" s="12" t="s">
+      <c r="D87" s="13" t="s">
         <v>1045</v>
       </c>
-      <c r="E87" s="11" t="s">
+      <c r="E87" s="12" t="s">
         <v>1046</v>
       </c>
-      <c r="F87" s="11" t="s">
+      <c r="F87" s="12" t="s">
         <v>1047</v>
       </c>
-      <c r="G87" s="11" t="s">
+      <c r="G87" s="12" t="s">
         <v>1048</v>
       </c>
-      <c r="H87" s="11" t="s">
+      <c r="H87" s="12" t="s">
         <v>1049</v>
       </c>
-      <c r="I87" s="11" t="s">
+      <c r="I87" s="12" t="s">
         <v>1050</v>
       </c>
-      <c r="J87" s="11" t="s">
+      <c r="J87" s="12" t="s">
         <v>1051</v>
       </c>
-      <c r="K87" s="11" t="s">
+      <c r="K87" s="12" t="s">
         <v>1052</v>
       </c>
-      <c r="L87" s="11" t="s">
+      <c r="L87" s="12" t="s">
         <v>1053</v>
       </c>
-      <c r="M87" s="11" t="s">
+      <c r="M87" s="12" t="s">
         <v>1054</v>
       </c>
-      <c r="N87" s="11" t="s">
+      <c r="N87" s="12" t="s">
         <v>1055</v>
       </c>
-      <c r="O87" s="11" t="s">
+      <c r="O87" s="12" t="s">
         <v>1056</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="2:15">
-      <c r="B88" s="10">
+      <c r="B88" s="11">
         <v>10083</v>
       </c>
-      <c r="C88" s="11" t="s">
+      <c r="C88" s="12" t="s">
         <v>1057</v>
       </c>
-      <c r="D88" s="12" t="s">
+      <c r="D88" s="13" t="s">
         <v>1058</v>
       </c>
-      <c r="E88" s="11" t="s">
+      <c r="E88" s="12" t="s">
         <v>1059</v>
       </c>
-      <c r="F88" s="11" t="s">
+      <c r="F88" s="12" t="s">
         <v>1060</v>
       </c>
-      <c r="G88" s="11" t="s">
+      <c r="G88" s="12" t="s">
         <v>1061</v>
       </c>
-      <c r="H88" s="11" t="s">
+      <c r="H88" s="12" t="s">
         <v>1062</v>
       </c>
-      <c r="I88" s="11" t="s">
+      <c r="I88" s="12" t="s">
         <v>1063</v>
       </c>
-      <c r="J88" s="11" t="s">
+      <c r="J88" s="12" t="s">
         <v>1064</v>
       </c>
-      <c r="K88" s="11" t="s">
+      <c r="K88" s="12" t="s">
         <v>1065</v>
       </c>
-      <c r="L88" s="11" t="s">
+      <c r="L88" s="12" t="s">
         <v>1066</v>
       </c>
-      <c r="M88" s="11" t="s">
+      <c r="M88" s="12" t="s">
         <v>1067</v>
       </c>
-      <c r="N88" s="11" t="s">
+      <c r="N88" s="12" t="s">
         <v>1068</v>
       </c>
-      <c r="O88" s="11" t="s">
+      <c r="O88" s="12" t="s">
         <v>1069</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="2:15">
-      <c r="B89" s="10">
+      <c r="B89" s="11">
         <v>10084</v>
       </c>
-      <c r="C89" s="11" t="s">
+      <c r="C89" s="12" t="s">
         <v>1070</v>
       </c>
-      <c r="D89" s="12" t="s">
+      <c r="D89" s="13" t="s">
         <v>1071</v>
       </c>
-      <c r="E89" s="11" t="s">
+      <c r="E89" s="12" t="s">
         <v>1072</v>
       </c>
-      <c r="F89" s="11" t="s">
+      <c r="F89" s="12" t="s">
         <v>1073</v>
       </c>
-      <c r="G89" s="11" t="s">
+      <c r="G89" s="12" t="s">
         <v>1074</v>
       </c>
-      <c r="H89" s="11" t="s">
+      <c r="H89" s="12" t="s">
         <v>1075</v>
       </c>
-      <c r="I89" s="11" t="s">
+      <c r="I89" s="12" t="s">
         <v>1074</v>
       </c>
-      <c r="J89" s="11" t="s">
+      <c r="J89" s="12" t="s">
         <v>1076</v>
       </c>
-      <c r="K89" s="11" t="s">
+      <c r="K89" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="L89" s="11" t="s">
+      <c r="L89" s="12" t="s">
         <v>1078</v>
       </c>
-      <c r="M89" s="11" t="s">
+      <c r="M89" s="12" t="s">
         <v>1079</v>
       </c>
-      <c r="N89" s="11" t="s">
+      <c r="N89" s="12" t="s">
         <v>1080</v>
       </c>
-      <c r="O89" s="11" t="s">
+      <c r="O89" s="12" t="s">
         <v>1081</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="2:15">
-      <c r="B90" s="10">
+      <c r="B90" s="11">
         <v>10085</v>
       </c>
-      <c r="C90" s="11" t="s">
+      <c r="C90" s="12" t="s">
         <v>1082</v>
       </c>
-      <c r="D90" s="12" t="s">
+      <c r="D90" s="13" t="s">
         <v>1083</v>
       </c>
-      <c r="E90" s="11" t="s">
+      <c r="E90" s="12" t="s">
         <v>1084</v>
       </c>
-      <c r="F90" s="11" t="s">
+      <c r="F90" s="12" t="s">
         <v>1085</v>
       </c>
-      <c r="G90" s="11" t="s">
+      <c r="G90" s="12" t="s">
         <v>1086</v>
       </c>
-      <c r="H90" s="11" t="s">
+      <c r="H90" s="12" t="s">
         <v>1087</v>
       </c>
-      <c r="I90" s="11" t="s">
+      <c r="I90" s="12" t="s">
         <v>1088</v>
       </c>
-      <c r="J90" s="11" t="s">
+      <c r="J90" s="12" t="s">
         <v>1089</v>
       </c>
-      <c r="K90" s="11" t="s">
+      <c r="K90" s="12" t="s">
         <v>1090</v>
       </c>
-      <c r="L90" s="11" t="s">
+      <c r="L90" s="12" t="s">
         <v>1091</v>
       </c>
-      <c r="M90" s="11" t="s">
+      <c r="M90" s="12" t="s">
         <v>1092</v>
       </c>
-      <c r="N90" s="11" t="s">
+      <c r="N90" s="12" t="s">
         <v>1093</v>
       </c>
-      <c r="O90" s="11" t="s">
+      <c r="O90" s="12" t="s">
         <v>1094</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="2:15">
-      <c r="B91" s="10">
+      <c r="B91" s="11">
         <v>10086</v>
       </c>
-      <c r="C91" s="11" t="s">
+      <c r="C91" s="12" t="s">
         <v>1095</v>
       </c>
-      <c r="D91" s="12" t="s">
+      <c r="D91" s="13" t="s">
         <v>1096</v>
       </c>
-      <c r="E91" s="11" t="s">
+      <c r="E91" s="12" t="s">
         <v>1097</v>
       </c>
-      <c r="F91" s="11" t="s">
+      <c r="F91" s="12" t="s">
         <v>1098</v>
       </c>
-      <c r="G91" s="11" t="s">
+      <c r="G91" s="12" t="s">
         <v>1099</v>
       </c>
-      <c r="H91" s="11" t="s">
+      <c r="H91" s="12" t="s">
         <v>1100</v>
       </c>
-      <c r="I91" s="11" t="s">
+      <c r="I91" s="12" t="s">
         <v>1101</v>
       </c>
-      <c r="J91" s="11" t="s">
+      <c r="J91" s="12" t="s">
         <v>1102</v>
       </c>
-      <c r="K91" s="11" t="s">
+      <c r="K91" s="12" t="s">
         <v>1103</v>
       </c>
-      <c r="L91" s="11" t="s">
+      <c r="L91" s="12" t="s">
         <v>1104</v>
       </c>
-      <c r="M91" s="11" t="s">
+      <c r="M91" s="12" t="s">
         <v>1105</v>
       </c>
-      <c r="N91" s="11" t="s">
+      <c r="N91" s="12" t="s">
         <v>1106</v>
       </c>
-      <c r="O91" s="11" t="s">
+      <c r="O91" s="12" t="s">
         <v>1107</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="2:15">
-      <c r="B92" s="10">
+      <c r="B92" s="11">
         <v>10087</v>
       </c>
-      <c r="C92" s="11" t="s">
+      <c r="C92" s="12" t="s">
         <v>1108</v>
       </c>
-      <c r="D92" s="11" t="s">
+      <c r="D92" s="12" t="s">
         <v>1109</v>
       </c>
-      <c r="E92" s="11" t="s">
+      <c r="E92" s="12" t="s">
         <v>1110</v>
       </c>
-      <c r="F92" s="11" t="s">
+      <c r="F92" s="12" t="s">
         <v>1111</v>
       </c>
-      <c r="G92" s="11" t="s">
+      <c r="G92" s="12" t="s">
         <v>1112</v>
       </c>
-      <c r="H92" s="11" t="s">
+      <c r="H92" s="12" t="s">
         <v>1113</v>
       </c>
-      <c r="I92" s="11" t="s">
+      <c r="I92" s="12" t="s">
         <v>1114</v>
       </c>
-      <c r="J92" s="11" t="s">
+      <c r="J92" s="12" t="s">
         <v>1115</v>
       </c>
-      <c r="K92" s="11" t="s">
+      <c r="K92" s="12" t="s">
         <v>1116</v>
       </c>
-      <c r="L92" s="11" t="s">
+      <c r="L92" s="12" t="s">
         <v>1117</v>
       </c>
-      <c r="M92" s="11" t="s">
+      <c r="M92" s="12" t="s">
         <v>1118</v>
       </c>
-      <c r="N92" s="11" t="s">
+      <c r="N92" s="12" t="s">
         <v>1119</v>
       </c>
-      <c r="O92" s="11" t="s">
+      <c r="O92" s="12" t="s">
         <v>1120</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="2:15">
-      <c r="B93" s="10">
+      <c r="B93" s="11">
         <v>10088</v>
       </c>
-      <c r="C93" s="11" t="s">
+      <c r="C93" s="12" t="s">
         <v>1121</v>
       </c>
-      <c r="D93" s="11" t="s">
+      <c r="D93" s="12" t="s">
         <v>1122</v>
       </c>
-      <c r="E93" s="11" t="s">
+      <c r="E93" s="12" t="s">
         <v>1123</v>
       </c>
-      <c r="F93" s="11" t="s">
+      <c r="F93" s="12" t="s">
         <v>1124</v>
       </c>
-      <c r="G93" s="11" t="s">
+      <c r="G93" s="12" t="s">
         <v>1125</v>
       </c>
-      <c r="H93" s="11" t="s">
+      <c r="H93" s="12" t="s">
         <v>1126</v>
       </c>
-      <c r="I93" s="11" t="s">
+      <c r="I93" s="12" t="s">
         <v>1127</v>
       </c>
-      <c r="J93" s="11" t="s">
+      <c r="J93" s="12" t="s">
         <v>1128</v>
       </c>
-      <c r="K93" s="11" t="s">
+      <c r="K93" s="12" t="s">
         <v>1129</v>
       </c>
-      <c r="L93" s="11" t="s">
+      <c r="L93" s="12" t="s">
         <v>1130</v>
       </c>
-      <c r="M93" s="11" t="s">
+      <c r="M93" s="12" t="s">
         <v>1131</v>
       </c>
-      <c r="N93" s="11" t="s">
+      <c r="N93" s="12" t="s">
         <v>1132</v>
       </c>
-      <c r="O93" s="11" t="s">
+      <c r="O93" s="12" t="s">
         <v>1133</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="2:15">
-      <c r="B94" s="10">
+      <c r="B94" s="11">
         <v>10089</v>
       </c>
-      <c r="C94" s="11" t="s">
+      <c r="C94" s="12" t="s">
         <v>1134</v>
       </c>
-      <c r="D94" s="11" t="s">
+      <c r="D94" s="12" t="s">
         <v>1135</v>
       </c>
-      <c r="E94" s="11" t="s">
+      <c r="E94" s="12" t="s">
         <v>1136</v>
       </c>
-      <c r="F94" s="11" t="s">
+      <c r="F94" s="12" t="s">
         <v>1137</v>
       </c>
-      <c r="G94" s="11" t="s">
+      <c r="G94" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="H94" s="11" t="s">
+      <c r="H94" s="12" t="s">
         <v>1139</v>
       </c>
-      <c r="I94" s="11" t="s">
+      <c r="I94" s="12" t="s">
         <v>1140</v>
       </c>
-      <c r="J94" s="11" t="s">
+      <c r="J94" s="12" t="s">
         <v>1141</v>
       </c>
-      <c r="K94" s="11" t="s">
+      <c r="K94" s="12" t="s">
         <v>1142</v>
       </c>
-      <c r="L94" s="11" t="s">
+      <c r="L94" s="12" t="s">
         <v>1143</v>
       </c>
-      <c r="M94" s="11" t="s">
+      <c r="M94" s="12" t="s">
         <v>1144</v>
       </c>
-      <c r="N94" s="11" t="s">
+      <c r="N94" s="12" t="s">
         <v>1145</v>
       </c>
-      <c r="O94" s="11" t="s">
+      <c r="O94" s="12" t="s">
         <v>1146</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="2:15">
-      <c r="B95" s="10">
+      <c r="B95" s="11">
         <v>10090</v>
       </c>
-      <c r="C95" s="11" t="s">
+      <c r="C95" s="12" t="s">
         <v>1147</v>
       </c>
-      <c r="D95" s="12" t="s">
+      <c r="D95" s="13" t="s">
         <v>1148</v>
       </c>
-      <c r="E95" s="11" t="s">
+      <c r="E95" s="12" t="s">
         <v>1149</v>
       </c>
-      <c r="F95" s="11" t="s">
+      <c r="F95" s="12" t="s">
         <v>1150</v>
       </c>
-      <c r="G95" s="11" t="s">
+      <c r="G95" s="12" t="s">
         <v>1151</v>
       </c>
-      <c r="H95" s="11" t="s">
+      <c r="H95" s="12" t="s">
         <v>1152</v>
       </c>
-      <c r="I95" s="11" t="s">
+      <c r="I95" s="12" t="s">
         <v>1153</v>
       </c>
-      <c r="J95" s="11" t="s">
+      <c r="J95" s="12" t="s">
         <v>1154</v>
       </c>
-      <c r="K95" s="11" t="s">
+      <c r="K95" s="12" t="s">
         <v>1155</v>
       </c>
-      <c r="L95" s="11" t="s">
+      <c r="L95" s="12" t="s">
         <v>1156</v>
       </c>
-      <c r="M95" s="11" t="s">
+      <c r="M95" s="12" t="s">
         <v>1157</v>
       </c>
-      <c r="N95" s="11" t="s">
+      <c r="N95" s="12" t="s">
         <v>1158</v>
       </c>
-      <c r="O95" s="11" t="s">
+      <c r="O95" s="12" t="s">
         <v>1159</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="2:15">
-      <c r="B96" s="10">
+      <c r="B96" s="11">
         <v>10091</v>
       </c>
       <c r="C96" t="s">
@@ -11216,7 +11588,7 @@
       </c>
     </row>
     <row r="97" customHeight="1" spans="1:16">
-      <c r="B97" s="10">
+      <c r="B97" s="11">
         <v>10092</v>
       </c>
       <c r="C97" t="s">
@@ -11260,7 +11632,7 @@
       </c>
     </row>
     <row r="98" customHeight="1" spans="1:16">
-      <c r="B98" s="3">
+      <c r="B98" s="4">
         <v>10093</v>
       </c>
       <c r="C98" t="s">
@@ -11272,28 +11644,28 @@
       <c r="E98" t="s">
         <v>1188</v>
       </c>
-      <c r="F98" s="17" t="s">
+      <c r="F98" s="18" t="s">
         <v>1189</v>
       </c>
-      <c r="G98" s="17" t="s">
+      <c r="G98" s="18" t="s">
         <v>1190</v>
       </c>
       <c r="H98" t="s">
         <v>1191</v>
       </c>
-      <c r="I98" s="17" t="s">
+      <c r="I98" s="18" t="s">
         <v>1192</v>
       </c>
-      <c r="J98" s="17" t="s">
+      <c r="J98" s="18" t="s">
         <v>1193</v>
       </c>
-      <c r="K98" s="17" t="s">
+      <c r="K98" s="18" t="s">
         <v>1194</v>
       </c>
       <c r="L98" t="s">
         <v>1195</v>
       </c>
-      <c r="M98" s="17" t="s">
+      <c r="M98" s="18" t="s">
         <v>1196</v>
       </c>
       <c r="N98" t="s">
@@ -11304,7 +11676,7 @@
       </c>
     </row>
     <row r="99" customHeight="1" spans="1:16">
-      <c r="B99" s="3">
+      <c r="B99" s="4">
         <v>10094</v>
       </c>
       <c r="C99" t="s">
@@ -11325,10 +11697,10 @@
       <c r="H99" t="s">
         <v>1204</v>
       </c>
-      <c r="I99" s="17" t="s">
+      <c r="I99" s="18" t="s">
         <v>1205</v>
       </c>
-      <c r="J99" s="17" t="s">
+      <c r="J99" s="18" t="s">
         <v>1206</v>
       </c>
       <c r="K99" t="s">
@@ -11337,18 +11709,18 @@
       <c r="L99" t="s">
         <v>1208</v>
       </c>
-      <c r="M99" s="17" t="s">
+      <c r="M99" s="18" t="s">
         <v>1209</v>
       </c>
-      <c r="N99" s="17" t="s">
+      <c r="N99" s="18" t="s">
         <v>1210</v>
       </c>
-      <c r="O99" s="17" t="s">
+      <c r="O99" s="18" t="s">
         <v>1211</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="1:16">
-      <c r="B100" s="3">
+      <c r="B100" s="4">
         <v>10095</v>
       </c>
       <c r="C100" t="s">
@@ -11381,18 +11753,18 @@
       <c r="L100" t="s">
         <v>1221</v>
       </c>
-      <c r="M100" s="17" t="s">
+      <c r="M100" s="18" t="s">
         <v>1222</v>
       </c>
-      <c r="N100" s="17" t="s">
+      <c r="N100" s="18" t="s">
         <v>1223</v>
       </c>
-      <c r="O100" s="17" t="s">
+      <c r="O100" s="18" t="s">
         <v>1224</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="1:16">
-      <c r="B101" s="3">
+      <c r="B101" s="4">
         <v>10096</v>
       </c>
       <c r="C101" t="s">
@@ -11404,31 +11776,31 @@
       <c r="E101" t="s">
         <v>1227</v>
       </c>
-      <c r="F101" s="17" t="s">
+      <c r="F101" s="18" t="s">
         <v>1228</v>
       </c>
-      <c r="G101" s="17" t="s">
+      <c r="G101" s="18" t="s">
         <v>1229</v>
       </c>
       <c r="H101" t="s">
         <v>1230</v>
       </c>
-      <c r="I101" s="17" t="s">
+      <c r="I101" s="18" t="s">
         <v>1231</v>
       </c>
-      <c r="J101" s="17" t="s">
+      <c r="J101" s="18" t="s">
         <v>1232</v>
       </c>
-      <c r="K101" s="17" t="s">
+      <c r="K101" s="18" t="s">
         <v>1233</v>
       </c>
-      <c r="L101" s="17" t="s">
+      <c r="L101" s="18" t="s">
         <v>1234</v>
       </c>
-      <c r="M101" s="17" t="s">
+      <c r="M101" s="18" t="s">
         <v>1235</v>
       </c>
-      <c r="N101" s="17" t="s">
+      <c r="N101" s="18" t="s">
         <v>1236</v>
       </c>
       <c r="O101" t="s">
@@ -11436,7 +11808,7 @@
       </c>
     </row>
     <row r="102" customHeight="1" spans="1:16">
-      <c r="B102" s="3">
+      <c r="B102" s="4">
         <v>10097</v>
       </c>
       <c r="C102" t="s">
@@ -11448,28 +11820,28 @@
       <c r="E102" t="s">
         <v>1240</v>
       </c>
-      <c r="F102" s="18" t="s">
+      <c r="F102" s="19" t="s">
         <v>1241</v>
       </c>
-      <c r="G102" s="18" t="s">
+      <c r="G102" s="19" t="s">
         <v>1242</v>
       </c>
       <c r="H102" t="s">
         <v>1243</v>
       </c>
-      <c r="I102" s="17" t="s">
+      <c r="I102" s="18" t="s">
         <v>1244</v>
       </c>
-      <c r="J102" s="17" t="s">
+      <c r="J102" s="18" t="s">
         <v>1245</v>
       </c>
-      <c r="K102" s="17" t="s">
+      <c r="K102" s="18" t="s">
         <v>1246</v>
       </c>
       <c r="L102" t="s">
         <v>1247</v>
       </c>
-      <c r="M102" s="17" t="s">
+      <c r="M102" s="18" t="s">
         <v>1248</v>
       </c>
       <c r="N102" t="s">
@@ -11483,7 +11855,7 @@
       <c r="A103" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B103" s="3">
+      <c r="B103" s="4">
         <v>10098</v>
       </c>
       <c r="C103" s="2" t="s">
@@ -11530,57 +11902,57 @@
       </c>
     </row>
     <row r="104" customFormat="1" customHeight="1" spans="1:16">
-      <c r="B104" s="3">
+      <c r="B104" s="4">
         <v>10099</v>
       </c>
-      <c r="C104" s="11" t="s">
+      <c r="C104" s="12" t="s">
         <v>1265</v>
       </c>
-      <c r="D104" s="12" t="s">
+      <c r="D104" s="13" t="s">
         <v>1266</v>
       </c>
-      <c r="E104" s="11" t="s">
+      <c r="E104" s="12" t="s">
         <v>1267</v>
       </c>
-      <c r="F104" s="11" t="s">
+      <c r="F104" s="12" t="s">
         <v>1268</v>
       </c>
-      <c r="G104" s="11" t="s">
+      <c r="G104" s="12" t="s">
         <v>1269</v>
       </c>
-      <c r="H104" s="11" t="s">
+      <c r="H104" s="12" t="s">
         <v>1270</v>
       </c>
-      <c r="I104" s="11" t="s">
+      <c r="I104" s="12" t="s">
         <v>1271</v>
       </c>
-      <c r="J104" s="11" t="s">
+      <c r="J104" s="12" t="s">
         <v>1272</v>
       </c>
-      <c r="K104" s="11" t="s">
+      <c r="K104" s="12" t="s">
         <v>1273</v>
       </c>
-      <c r="L104" s="11" t="s">
+      <c r="L104" s="12" t="s">
         <v>1274</v>
       </c>
-      <c r="M104" s="11" t="s">
+      <c r="M104" s="12" t="s">
         <v>1275</v>
       </c>
-      <c r="N104" s="14" t="s">
+      <c r="N104" s="15" t="s">
         <v>1276</v>
       </c>
-      <c r="O104" s="11" t="s">
+      <c r="O104" s="12" t="s">
         <v>1277</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="B105" s="3">
+      <c r="B105" s="4">
         <v>10100</v>
       </c>
       <c r="C105" t="s">
         <v>1278</v>
       </c>
-      <c r="D105" s="16" t="s">
+      <c r="D105" s="17" t="s">
         <v>153</v>
       </c>
       <c r="E105" t="s">
@@ -11589,7 +11961,7 @@
       <c r="F105" t="s">
         <v>1280</v>
       </c>
-      <c r="G105" s="16" t="s">
+      <c r="G105" s="17" t="s">
         <v>1281</v>
       </c>
       <c r="H105" t="s">
@@ -11601,25 +11973,25 @@
       <c r="J105" t="s">
         <v>1284</v>
       </c>
-      <c r="K105" s="16" t="s">
+      <c r="K105" s="17" t="s">
         <v>1285</v>
       </c>
       <c r="L105" t="s">
         <v>1286</v>
       </c>
-      <c r="M105" s="17" t="s">
+      <c r="M105" s="18" t="s">
         <v>1287</v>
       </c>
-      <c r="N105" s="18" t="s">
+      <c r="N105" s="19" t="s">
         <v>1288</v>
       </c>
-      <c r="O105" s="17" t="s">
+      <c r="O105" s="18" t="s">
         <v>1289</v>
       </c>
       <c r="P105"/>
     </row>
     <row r="106" customHeight="1" spans="1:16">
-      <c r="B106" s="3">
+      <c r="B106" s="4">
         <v>10101</v>
       </c>
       <c r="C106" s="2" t="s">
@@ -11663,43 +12035,43 @@
       </c>
     </row>
     <row r="107" customHeight="1" spans="1:16">
-      <c r="B107" s="3">
+      <c r="B107" s="4">
         <v>10102</v>
       </c>
       <c r="C107" t="s">
         <v>1303</v>
       </c>
-      <c r="D107" s="16" t="s">
+      <c r="D107" s="17" t="s">
         <v>1304</v>
       </c>
       <c r="E107" t="s">
         <v>1305</v>
       </c>
-      <c r="F107" s="17" t="s">
+      <c r="F107" s="18" t="s">
         <v>1306</v>
       </c>
-      <c r="G107" s="17" t="s">
+      <c r="G107" s="18" t="s">
         <v>1307</v>
       </c>
-      <c r="H107" s="17" t="s">
+      <c r="H107" s="18" t="s">
         <v>1308</v>
       </c>
-      <c r="I107" s="17" t="s">
+      <c r="I107" s="18" t="s">
         <v>1309</v>
       </c>
-      <c r="J107" s="17" t="s">
+      <c r="J107" s="18" t="s">
         <v>1310</v>
       </c>
-      <c r="K107" s="17" t="s">
+      <c r="K107" s="18" t="s">
         <v>1311</v>
       </c>
-      <c r="L107" s="17" t="s">
+      <c r="L107" s="18" t="s">
         <v>1312</v>
       </c>
-      <c r="M107" s="17" t="s">
+      <c r="M107" s="18" t="s">
         <v>1313</v>
       </c>
-      <c r="N107" s="17" t="s">
+      <c r="N107" s="18" t="s">
         <v>1314</v>
       </c>
       <c r="O107" t="s">
@@ -11707,13 +12079,13 @@
       </c>
     </row>
     <row r="108" customHeight="1" spans="1:16">
-      <c r="B108" s="3">
+      <c r="B108" s="4">
         <v>10103</v>
       </c>
       <c r="C108" t="s">
         <v>1316</v>
       </c>
-      <c r="D108" s="16" t="s">
+      <c r="D108" s="17" t="s">
         <v>1317</v>
       </c>
       <c r="E108" t="s">
@@ -11722,7 +12094,7 @@
       <c r="F108" t="s">
         <v>1319</v>
       </c>
-      <c r="G108" s="16" t="s">
+      <c r="G108" s="17" t="s">
         <v>1320</v>
       </c>
       <c r="H108" t="s">
@@ -11734,13 +12106,13 @@
       <c r="J108" t="s">
         <v>1323</v>
       </c>
-      <c r="K108" s="17" t="s">
+      <c r="K108" s="18" t="s">
         <v>1324</v>
       </c>
-      <c r="L108" s="17" t="s">
+      <c r="L108" s="18" t="s">
         <v>1325</v>
       </c>
-      <c r="M108" s="17" t="s">
+      <c r="M108" s="18" t="s">
         <v>1326</v>
       </c>
       <c r="N108" t="s">
@@ -11751,13 +12123,13 @@
       </c>
     </row>
     <row r="109" customHeight="1" spans="1:16">
-      <c r="B109" s="3">
+      <c r="B109" s="4">
         <v>10104</v>
       </c>
       <c r="C109" t="s">
         <v>1329</v>
       </c>
-      <c r="D109" s="16" t="s">
+      <c r="D109" s="17" t="s">
         <v>1330</v>
       </c>
       <c r="E109" t="s">
@@ -11766,7 +12138,7 @@
       <c r="F109" t="s">
         <v>1332</v>
       </c>
-      <c r="G109" s="16" t="s">
+      <c r="G109" s="17" t="s">
         <v>1333</v>
       </c>
       <c r="H109" t="s">
@@ -11778,24 +12150,24 @@
       <c r="J109" t="s">
         <v>1336</v>
       </c>
-      <c r="K109" s="17" t="s">
+      <c r="K109" s="18" t="s">
         <v>1337</v>
       </c>
-      <c r="L109" s="17" t="s">
+      <c r="L109" s="18" t="s">
         <v>1338</v>
       </c>
-      <c r="M109" s="17" t="s">
+      <c r="M109" s="18" t="s">
         <v>1339</v>
       </c>
-      <c r="N109" s="17" t="s">
+      <c r="N109" s="18" t="s">
         <v>1340</v>
       </c>
-      <c r="O109" s="17" t="s">
+      <c r="O109" s="18" t="s">
         <v>1341</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="1:16">
-      <c r="B110" s="3">
+      <c r="B110" s="4">
         <v>10105</v>
       </c>
       <c r="C110" t="s">
@@ -11807,75 +12179,75 @@
       <c r="E110" t="s">
         <v>1344</v>
       </c>
-      <c r="F110" s="17" t="s">
+      <c r="F110" s="18" t="s">
         <v>1345</v>
       </c>
-      <c r="G110" s="17" t="s">
+      <c r="G110" s="18" t="s">
         <v>1346</v>
       </c>
-      <c r="H110" s="17" t="s">
+      <c r="H110" s="18" t="s">
         <v>1347</v>
       </c>
-      <c r="I110" s="17" t="s">
+      <c r="I110" s="18" t="s">
         <v>1348</v>
       </c>
-      <c r="J110" s="17" t="s">
+      <c r="J110" s="18" t="s">
         <v>1349</v>
       </c>
-      <c r="K110" s="17" t="s">
+      <c r="K110" s="18" t="s">
         <v>1350</v>
       </c>
       <c r="L110" t="s">
         <v>1351</v>
       </c>
-      <c r="M110" s="18" t="s">
+      <c r="M110" s="19" t="s">
         <v>1352</v>
       </c>
-      <c r="N110" s="18" t="s">
+      <c r="N110" s="19" t="s">
         <v>1353</v>
       </c>
-      <c r="O110" s="18" t="s">
+      <c r="O110" s="19" t="s">
         <v>1354</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="1:16">
-      <c r="B111" s="3">
+      <c r="B111" s="4">
         <v>10106</v>
       </c>
-      <c r="C111" s="19" t="s">
+      <c r="C111" s="20" t="s">
         <v>1355</v>
       </c>
-      <c r="D111" s="16" t="s">
+      <c r="D111" s="17" t="s">
         <v>1356</v>
       </c>
       <c r="E111" t="s">
         <v>1357</v>
       </c>
-      <c r="F111" s="17" t="s">
+      <c r="F111" s="18" t="s">
         <v>1358</v>
       </c>
-      <c r="G111" s="16" t="s">
+      <c r="G111" s="17" t="s">
         <v>1359</v>
       </c>
-      <c r="H111" s="17" t="s">
+      <c r="H111" s="18" t="s">
         <v>1360</v>
       </c>
-      <c r="I111" s="17" t="s">
+      <c r="I111" s="18" t="s">
         <v>1361</v>
       </c>
-      <c r="J111" s="17" t="s">
+      <c r="J111" s="18" t="s">
         <v>1362</v>
       </c>
-      <c r="K111" s="17" t="s">
+      <c r="K111" s="18" t="s">
         <v>1363</v>
       </c>
       <c r="L111" t="s">
         <v>1364</v>
       </c>
-      <c r="M111" s="17" t="s">
+      <c r="M111" s="18" t="s">
         <v>1365</v>
       </c>
-      <c r="N111" s="17" t="s">
+      <c r="N111" s="18" t="s">
         <v>1366</v>
       </c>
       <c r="O111" t="s">
@@ -11883,7 +12255,7 @@
       </c>
     </row>
     <row r="112" customHeight="1" spans="1:16">
-      <c r="B112" s="3">
+      <c r="B112" s="4">
         <v>10107</v>
       </c>
       <c r="C112" t="s">
@@ -11895,7 +12267,7 @@
       <c r="E112" t="s">
         <v>1370</v>
       </c>
-      <c r="F112" s="17" t="s">
+      <c r="F112" s="18" t="s">
         <v>1371</v>
       </c>
       <c r="G112" t="s">
@@ -11904,19 +12276,19 @@
       <c r="H112" t="s">
         <v>1373</v>
       </c>
-      <c r="I112" s="17" t="s">
+      <c r="I112" s="18" t="s">
         <v>1374</v>
       </c>
-      <c r="J112" s="17" t="s">
+      <c r="J112" s="18" t="s">
         <v>1375</v>
       </c>
-      <c r="K112" s="17" t="s">
+      <c r="K112" s="18" t="s">
         <v>1376</v>
       </c>
       <c r="L112" t="s">
         <v>1377</v>
       </c>
-      <c r="M112" s="17" t="s">
+      <c r="M112" s="18" t="s">
         <v>1378</v>
       </c>
       <c r="N112" t="s">
@@ -11930,7 +12302,7 @@
       <c r="A113" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B113" s="3">
+      <c r="B113" s="4">
         <v>10108</v>
       </c>
       <c r="C113" s="2" t="s">
@@ -11980,7 +12352,7 @@
       <c r="A114" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B114" s="3">
+      <c r="B114" s="4">
         <v>10109</v>
       </c>
       <c r="C114" s="2" t="s">
@@ -12030,7 +12402,7 @@
       <c r="A115" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B115" s="3">
+      <c r="B115" s="4">
         <v>10110</v>
       </c>
       <c r="C115" s="2" t="s">
@@ -12080,7 +12452,7 @@
       <c r="A116" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B116" s="3">
+      <c r="B116" s="4">
         <v>10111</v>
       </c>
       <c r="C116" s="2" t="s">
@@ -12130,7 +12502,7 @@
       <c r="A117" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B117" s="3">
+      <c r="B117" s="4">
         <v>10112</v>
       </c>
       <c r="C117" s="2" t="s">
@@ -12180,7 +12552,7 @@
       <c r="A118" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B118" s="3">
+      <c r="B118" s="4">
         <v>10113</v>
       </c>
       <c r="C118" s="2" t="s">
@@ -12230,7 +12602,7 @@
       <c r="A119" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B119" s="3">
+      <c r="B119" s="4">
         <v>10114</v>
       </c>
       <c r="C119" s="2" t="s">
@@ -12280,7 +12652,7 @@
       <c r="A120" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B120" s="3">
+      <c r="B120" s="4">
         <v>10115</v>
       </c>
       <c r="C120" s="2" t="s">
@@ -12330,7 +12702,7 @@
       <c r="A121" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B121" s="3">
+      <c r="B121" s="4">
         <v>10116</v>
       </c>
       <c r="C121" s="2" t="s">
@@ -12380,7 +12752,7 @@
       <c r="A122" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B122" s="3">
+      <c r="B122" s="4">
         <v>10117</v>
       </c>
       <c r="C122" s="2" t="s">
@@ -12430,7 +12802,7 @@
       <c r="A123" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B123" s="3">
+      <c r="B123" s="4">
         <v>10118</v>
       </c>
       <c r="C123" s="2" t="s">
@@ -12480,7 +12852,7 @@
       <c r="A124" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B124" s="3">
+      <c r="B124" s="4">
         <v>10119</v>
       </c>
       <c r="C124" s="2" t="s">
@@ -12530,10 +12902,10 @@
       <c r="A125" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B125" s="3">
+      <c r="B125" s="4">
         <v>10120</v>
       </c>
-      <c r="C125" s="20" t="s">
+      <c r="C125" s="21" t="s">
         <v>1534</v>
       </c>
       <c r="D125" s="2" t="s">
@@ -12577,230 +12949,230 @@
       </c>
     </row>
     <row r="126" customHeight="1" spans="1:16">
-      <c r="B126" s="3">
+      <c r="B126" s="4">
         <v>10121</v>
       </c>
       <c r="C126" t="s">
         <v>1545</v>
       </c>
-      <c r="D126" s="12" t="s">
+      <c r="D126" s="13" t="s">
         <v>1546</v>
       </c>
-      <c r="E126" s="11" t="s">
+      <c r="E126" s="12" t="s">
         <v>1547</v>
       </c>
-      <c r="F126" s="11" t="s">
+      <c r="F126" s="12" t="s">
         <v>1548</v>
       </c>
-      <c r="G126" s="11" t="s">
+      <c r="G126" s="12" t="s">
         <v>1549</v>
       </c>
-      <c r="H126" s="11" t="s">
+      <c r="H126" s="12" t="s">
         <v>1550</v>
       </c>
-      <c r="I126" s="11" t="s">
+      <c r="I126" s="12" t="s">
         <v>1551</v>
       </c>
-      <c r="J126" s="11" t="s">
+      <c r="J126" s="12" t="s">
         <v>1552</v>
       </c>
-      <c r="K126" s="11" t="s">
+      <c r="K126" s="12" t="s">
         <v>1553</v>
       </c>
-      <c r="L126" s="11" t="s">
+      <c r="L126" s="12" t="s">
         <v>1554</v>
       </c>
-      <c r="M126" s="11" t="s">
+      <c r="M126" s="12" t="s">
         <v>1555</v>
       </c>
-      <c r="N126" s="11" t="s">
+      <c r="N126" s="12" t="s">
         <v>1556</v>
       </c>
-      <c r="O126" s="11" t="s">
+      <c r="O126" s="12" t="s">
         <v>1557</v>
       </c>
     </row>
     <row r="127" customHeight="1" spans="1:16">
-      <c r="B127" s="3">
+      <c r="B127" s="4">
         <v>10122</v>
       </c>
       <c r="C127" t="s">
         <v>1558</v>
       </c>
-      <c r="D127" s="21" t="s">
+      <c r="D127" s="22" t="s">
         <v>1559</v>
       </c>
-      <c r="E127" s="21" t="s">
+      <c r="E127" s="22" t="s">
         <v>1560</v>
       </c>
-      <c r="F127" s="21" t="s">
+      <c r="F127" s="22" t="s">
         <v>1561</v>
       </c>
-      <c r="G127" s="21" t="s">
+      <c r="G127" s="22" t="s">
         <v>1562</v>
       </c>
-      <c r="H127" s="21" t="s">
+      <c r="H127" s="22" t="s">
         <v>1563</v>
       </c>
-      <c r="I127" s="21" t="s">
+      <c r="I127" s="22" t="s">
         <v>1564</v>
       </c>
-      <c r="J127" s="21" t="s">
+      <c r="J127" s="22" t="s">
         <v>1565</v>
       </c>
-      <c r="K127" s="21" t="s">
+      <c r="K127" s="22" t="s">
         <v>1566</v>
       </c>
-      <c r="L127" s="21" t="s">
+      <c r="L127" s="22" t="s">
         <v>1567</v>
       </c>
-      <c r="M127" s="21" t="s">
+      <c r="M127" s="22" t="s">
         <v>1568</v>
       </c>
-      <c r="N127" s="21" t="s">
+      <c r="N127" s="22" t="s">
         <v>1569</v>
       </c>
-      <c r="O127" s="21" t="s">
+      <c r="O127" s="22" t="s">
         <v>1570</v>
       </c>
-      <c r="P127" s="21" t="s">
+      <c r="P127" s="22" t="s">
         <v>1570</v>
       </c>
     </row>
     <row r="128" customHeight="1" spans="1:16">
-      <c r="B128" s="3">
+      <c r="B128" s="4">
         <v>10123</v>
       </c>
       <c r="C128" t="s">
         <v>1571</v>
       </c>
-      <c r="D128" s="12" t="s">
+      <c r="D128" s="13" t="s">
         <v>1572</v>
       </c>
-      <c r="E128" s="11" t="s">
+      <c r="E128" s="12" t="s">
         <v>1573</v>
       </c>
-      <c r="F128" s="11" t="s">
+      <c r="F128" s="12" t="s">
         <v>1574</v>
       </c>
-      <c r="G128" s="11" t="s">
+      <c r="G128" s="12" t="s">
         <v>1575</v>
       </c>
-      <c r="H128" s="11" t="s">
+      <c r="H128" s="12" t="s">
         <v>1576</v>
       </c>
-      <c r="I128" s="11" t="s">
+      <c r="I128" s="12" t="s">
         <v>1577</v>
       </c>
-      <c r="J128" s="11" t="s">
+      <c r="J128" s="12" t="s">
         <v>1578</v>
       </c>
-      <c r="K128" s="11" t="s">
+      <c r="K128" s="12" t="s">
         <v>1579</v>
       </c>
-      <c r="L128" s="11" t="s">
+      <c r="L128" s="12" t="s">
         <v>1580</v>
       </c>
-      <c r="M128" s="11" t="s">
+      <c r="M128" s="12" t="s">
         <v>1581</v>
       </c>
-      <c r="N128" s="11" t="s">
+      <c r="N128" s="12" t="s">
         <v>1582</v>
       </c>
-      <c r="O128" s="11" t="s">
+      <c r="O128" s="12" t="s">
         <v>1583</v>
       </c>
     </row>
     <row r="129" customHeight="1" spans="1:16">
-      <c r="B129" s="3">
+      <c r="B129" s="4">
         <v>10124</v>
       </c>
       <c r="C129" t="s">
         <v>1584</v>
       </c>
-      <c r="D129" s="12" t="s">
+      <c r="D129" s="13" t="s">
         <v>1585</v>
       </c>
-      <c r="E129" s="11" t="s">
+      <c r="E129" s="12" t="s">
         <v>1586</v>
       </c>
-      <c r="F129" s="11" t="s">
+      <c r="F129" s="12" t="s">
         <v>1587</v>
       </c>
-      <c r="G129" s="11" t="s">
+      <c r="G129" s="12" t="s">
         <v>1588</v>
       </c>
-      <c r="H129" s="11" t="s">
+      <c r="H129" s="12" t="s">
         <v>1589</v>
       </c>
-      <c r="I129" s="11" t="s">
+      <c r="I129" s="12" t="s">
         <v>1590</v>
       </c>
-      <c r="J129" s="11" t="s">
+      <c r="J129" s="12" t="s">
         <v>1591</v>
       </c>
-      <c r="K129" s="11" t="s">
+      <c r="K129" s="12" t="s">
         <v>1592</v>
       </c>
-      <c r="L129" s="11" t="s">
+      <c r="L129" s="12" t="s">
         <v>1593</v>
       </c>
-      <c r="M129" s="11" t="s">
+      <c r="M129" s="12" t="s">
         <v>1594</v>
       </c>
-      <c r="N129" s="11" t="s">
+      <c r="N129" s="12" t="s">
         <v>1595</v>
       </c>
-      <c r="O129" s="11" t="s">
+      <c r="O129" s="12" t="s">
         <v>1596</v>
       </c>
     </row>
     <row r="130" customHeight="1" spans="1:16">
-      <c r="B130" s="3">
+      <c r="B130" s="4">
         <v>10125</v>
       </c>
       <c r="C130" t="s">
         <v>1597</v>
       </c>
-      <c r="D130" s="12" t="s">
+      <c r="D130" s="13" t="s">
         <v>1598</v>
       </c>
-      <c r="E130" s="11" t="s">
+      <c r="E130" s="12" t="s">
         <v>1599</v>
       </c>
-      <c r="F130" s="11" t="s">
+      <c r="F130" s="12" t="s">
         <v>1600</v>
       </c>
-      <c r="G130" s="11" t="s">
+      <c r="G130" s="12" t="s">
         <v>1601</v>
       </c>
-      <c r="H130" s="11" t="s">
+      <c r="H130" s="12" t="s">
         <v>1602</v>
       </c>
-      <c r="I130" s="11" t="s">
+      <c r="I130" s="12" t="s">
         <v>1603</v>
       </c>
-      <c r="J130" s="11" t="s">
+      <c r="J130" s="12" t="s">
         <v>1604</v>
       </c>
-      <c r="K130" s="11" t="s">
+      <c r="K130" s="12" t="s">
         <v>1605</v>
       </c>
-      <c r="L130" s="11" t="s">
+      <c r="L130" s="12" t="s">
         <v>1606</v>
       </c>
-      <c r="M130" s="11" t="s">
+      <c r="M130" s="12" t="s">
         <v>1607</v>
       </c>
-      <c r="N130" s="14" t="s">
+      <c r="N130" s="15" t="s">
         <v>1608</v>
       </c>
-      <c r="O130" s="11" t="s">
+      <c r="O130" s="12" t="s">
         <v>1609</v>
       </c>
     </row>
     <row r="131" customHeight="1" spans="1:16">
-      <c r="B131" s="3">
+      <c r="B131" s="4">
         <v>10126</v>
       </c>
       <c r="C131" t="s">
@@ -12844,96 +13216,500 @@
       </c>
     </row>
     <row r="132" customFormat="1" customHeight="1" spans="1:16">
-      <c r="B132" s="3">
+      <c r="B132" s="4">
         <v>10127</v>
       </c>
       <c r="C132" t="s">
         <v>1621</v>
       </c>
-      <c r="D132" s="12" t="s">
+      <c r="D132" s="13" t="s">
         <v>1622</v>
       </c>
-      <c r="E132" s="21" t="s">
+      <c r="E132" s="22" t="s">
         <v>1623</v>
       </c>
-      <c r="F132" s="21" t="s">
+      <c r="F132" s="22" t="s">
         <v>1624</v>
       </c>
-      <c r="G132" s="21" t="s">
+      <c r="G132" s="22" t="s">
         <v>1625</v>
       </c>
-      <c r="H132" s="21" t="s">
+      <c r="H132" s="22" t="s">
         <v>1626</v>
       </c>
-      <c r="I132" s="21" t="s">
+      <c r="I132" s="22" t="s">
         <v>1627</v>
       </c>
-      <c r="J132" s="21" t="s">
+      <c r="J132" s="22" t="s">
         <v>1628</v>
       </c>
-      <c r="K132" s="21" t="s">
+      <c r="K132" s="22" t="s">
         <v>1629</v>
       </c>
-      <c r="L132" s="21" t="s">
+      <c r="L132" s="22" t="s">
         <v>1630</v>
       </c>
-      <c r="M132" s="21" t="s">
+      <c r="M132" s="22" t="s">
         <v>1631</v>
       </c>
-      <c r="N132" s="21" t="s">
+      <c r="N132" s="22" t="s">
         <v>1632</v>
       </c>
-      <c r="O132" s="21" t="s">
+      <c r="O132" s="22" t="s">
         <v>1633</v>
       </c>
     </row>
-    <row r="133" s="2" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A133" s="2" t="s">
+    <row r="133" customFormat="1" customHeight="1" spans="1:16">
+      <c r="B133" s="4">
+        <v>10128</v>
+      </c>
+      <c r="C133" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E133" t="s">
+        <v>1636</v>
+      </c>
+      <c r="F133" t="s">
+        <v>1637</v>
+      </c>
+      <c r="G133" t="s">
+        <v>1638</v>
+      </c>
+      <c r="H133" t="s">
+        <v>1639</v>
+      </c>
+      <c r="I133" t="s">
+        <v>1640</v>
+      </c>
+      <c r="J133" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K133" t="s">
+        <v>1642</v>
+      </c>
+      <c r="L133" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M133" t="s">
+        <v>1644</v>
+      </c>
+      <c r="N133" t="s">
+        <v>1645</v>
+      </c>
+      <c r="O133" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="134" s="3" customFormat="1" ht="16" customHeight="1" spans="1:16">
+      <c r="A134" s="23"/>
+      <c r="B134" s="4">
+        <v>10129</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>1647</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>1648</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>1649</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>1650</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>1651</v>
+      </c>
+      <c r="H134" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="I134" s="3" t="s">
+        <v>1653</v>
+      </c>
+      <c r="J134" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="K134" s="3" t="s">
+        <v>1654</v>
+      </c>
+      <c r="L134" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="M134" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="N134" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="O134" s="3" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="135" s="3" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A135" s="23"/>
+      <c r="B135" s="4">
+        <v>10130</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>1660</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="H135" s="3" t="s">
+        <v>1662</v>
+      </c>
+      <c r="I135" s="3" t="s">
+        <v>1663</v>
+      </c>
+      <c r="J135" s="3" t="s">
+        <v>1664</v>
+      </c>
+      <c r="K135" s="3" t="s">
+        <v>1665</v>
+      </c>
+      <c r="L135" s="3" t="s">
+        <v>1666</v>
+      </c>
+      <c r="M135" s="3" t="s">
+        <v>1667</v>
+      </c>
+      <c r="N135" s="3" t="s">
+        <v>1668</v>
+      </c>
+      <c r="O135" s="3" t="s">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="136" s="3" customFormat="1" ht="25" customHeight="1" spans="1:16">
+      <c r="A136" s="23"/>
+      <c r="B136" s="4">
+        <v>10131</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>1670</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>1672</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>1673</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>1674</v>
+      </c>
+      <c r="H136" s="3" t="s">
+        <v>1675</v>
+      </c>
+      <c r="I136" s="3" t="s">
+        <v>1676</v>
+      </c>
+      <c r="J136" s="3" t="s">
+        <v>1677</v>
+      </c>
+      <c r="K136" s="3" t="s">
+        <v>1678</v>
+      </c>
+      <c r="L136" s="3" t="s">
+        <v>1679</v>
+      </c>
+      <c r="M136" s="3" t="s">
+        <v>1680</v>
+      </c>
+      <c r="N136" s="3" t="s">
+        <v>1681</v>
+      </c>
+      <c r="O136" s="3" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="137" s="3" customFormat="1" ht="70" customHeight="1" spans="1:16">
+      <c r="A137" s="23"/>
+      <c r="B137" s="4">
+        <v>10132</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>1683</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>1684</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>1685</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>1686</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>1687</v>
+      </c>
+      <c r="H137" s="1" t="s">
+        <v>1688</v>
+      </c>
+      <c r="I137" s="3" t="s">
+        <v>1689</v>
+      </c>
+      <c r="J137" s="3" t="s">
+        <v>1690</v>
+      </c>
+      <c r="K137" s="3" t="s">
+        <v>1691</v>
+      </c>
+      <c r="L137" s="3" t="s">
+        <v>1692</v>
+      </c>
+      <c r="M137" s="3" t="s">
+        <v>1693</v>
+      </c>
+      <c r="N137" s="3" t="s">
+        <v>1694</v>
+      </c>
+      <c r="O137" s="3" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="138" s="3" customFormat="1" ht="19" customHeight="1" spans="1:16">
+      <c r="A138" s="23"/>
+      <c r="B138" s="4">
+        <v>10133</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>1696</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>1697</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>1698</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>1699</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>1700</v>
+      </c>
+      <c r="H138" s="3" t="s">
+        <v>1701</v>
+      </c>
+      <c r="I138" s="3" t="s">
+        <v>1702</v>
+      </c>
+      <c r="J138" s="3" t="s">
+        <v>1703</v>
+      </c>
+      <c r="K138" s="3" t="s">
+        <v>1704</v>
+      </c>
+      <c r="L138" s="3" t="s">
+        <v>1705</v>
+      </c>
+      <c r="M138" s="3" t="s">
+        <v>1706</v>
+      </c>
+      <c r="N138" s="3" t="s">
+        <v>1707</v>
+      </c>
+      <c r="O138" s="3" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="139" s="3" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A139" s="23"/>
+      <c r="B139" s="4">
+        <v>10134</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>1709</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>1710</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>1711</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>1712</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>1713</v>
+      </c>
+      <c r="H139" s="3" t="s">
+        <v>1714</v>
+      </c>
+      <c r="I139" s="3" t="s">
+        <v>1715</v>
+      </c>
+      <c r="J139" s="3" t="s">
+        <v>1716</v>
+      </c>
+      <c r="K139" s="3" t="s">
+        <v>1717</v>
+      </c>
+      <c r="L139" s="3" t="s">
+        <v>1718</v>
+      </c>
+      <c r="M139" s="3" t="s">
+        <v>1719</v>
+      </c>
+      <c r="N139" s="3" t="s">
+        <v>1720</v>
+      </c>
+      <c r="O139" s="3" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="140" s="3" customFormat="1" ht="13.5" spans="1:16">
+      <c r="A140" s="23"/>
+      <c r="B140" s="4">
+        <v>10135</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>1722</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>1723</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>1724</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>1726</v>
+      </c>
+      <c r="H140" s="3" t="s">
+        <v>1727</v>
+      </c>
+      <c r="I140" s="3" t="s">
+        <v>1728</v>
+      </c>
+      <c r="J140" s="3" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K140" s="3" t="s">
+        <v>1730</v>
+      </c>
+      <c r="L140" s="3" t="s">
+        <v>1731</v>
+      </c>
+      <c r="M140" s="3" t="s">
+        <v>1732</v>
+      </c>
+      <c r="N140" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="O140" s="3" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="141" s="3" customFormat="1" ht="31" customHeight="1" spans="1:16">
+      <c r="A141" s="23"/>
+      <c r="B141" s="4">
+        <v>10136</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>1735</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>1736</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>1737</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>1738</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>1739</v>
+      </c>
+      <c r="H141" s="3" t="s">
+        <v>1740</v>
+      </c>
+      <c r="I141" s="3" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J141" s="3" t="s">
+        <v>1742</v>
+      </c>
+      <c r="K141" s="3" t="s">
+        <v>1743</v>
+      </c>
+      <c r="L141" s="3" t="s">
+        <v>1744</v>
+      </c>
+      <c r="M141" s="3" t="s">
+        <v>1745</v>
+      </c>
+      <c r="N141" s="3" t="s">
+        <v>1746</v>
+      </c>
+      <c r="O141" s="3" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="142" s="2" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A142" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B133" s="3">
-        <v>10128</v>
-      </c>
-      <c r="C133" s="20" t="s">
-        <v>1634</v>
-      </c>
-      <c r="D133" s="20" t="s">
-        <v>1635</v>
-      </c>
-      <c r="E133" s="20" t="s">
-        <v>1636</v>
-      </c>
-      <c r="F133" s="20" t="s">
-        <v>1637</v>
-      </c>
-      <c r="G133" s="20" t="s">
-        <v>1638</v>
-      </c>
-      <c r="H133" s="20" t="s">
-        <v>1639</v>
-      </c>
-      <c r="I133" s="20" t="s">
-        <v>1640</v>
-      </c>
-      <c r="J133" s="20" t="s">
-        <v>1641</v>
-      </c>
-      <c r="K133" s="20" t="s">
-        <v>1642</v>
-      </c>
-      <c r="L133" s="2" t="s">
-        <v>1643</v>
-      </c>
-      <c r="M133" s="20" t="s">
-        <v>1644</v>
-      </c>
-      <c r="N133" s="20" t="s">
-        <v>1645</v>
-      </c>
-      <c r="O133" s="20" t="s">
-        <v>1646</v>
-      </c>
-      <c r="P133" s="2" t="s">
+      <c r="B142" s="4">
+        <v>10137</v>
+      </c>
+      <c r="C142" s="21" t="s">
+        <v>1748</v>
+      </c>
+      <c r="D142" s="21" t="s">
+        <v>1749</v>
+      </c>
+      <c r="E142" s="21" t="s">
+        <v>1750</v>
+      </c>
+      <c r="F142" s="21" t="s">
+        <v>1751</v>
+      </c>
+      <c r="G142" s="21" t="s">
+        <v>1752</v>
+      </c>
+      <c r="H142" s="21" t="s">
+        <v>1753</v>
+      </c>
+      <c r="I142" s="21" t="s">
+        <v>1754</v>
+      </c>
+      <c r="J142" s="21" t="s">
+        <v>1755</v>
+      </c>
+      <c r="K142" s="21" t="s">
+        <v>1756</v>
+      </c>
+      <c r="L142" s="2" t="s">
+        <v>1757</v>
+      </c>
+      <c r="M142" s="21" t="s">
+        <v>1758</v>
+      </c>
+      <c r="N142" s="21" t="s">
+        <v>1759</v>
+      </c>
+      <c r="O142" s="21" t="s">
+        <v>1760</v>
+      </c>
+      <c r="P142" s="2" t="s">
         <v>1251</v>
       </c>
     </row>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1864" uniqueCount="1752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1955" uniqueCount="1817">
   <si>
     <t>##var</t>
   </si>
@@ -5932,6 +5932,201 @@
   </si>
   <si>
     <t>Şu anda çok sayıda çekim talebi var. Bankalar gönderim sırasına göre toplu işliyor. Hesabı aktif tutun ve bugünkü check-in için &lt;color=#EA2111&gt;{0}&lt;/color&gt; seviye daha tamamlayın, sıra konumunuzu korumanıza yardımcı olur. Lütfen sabırla bekleyin.</t>
+  </si>
+  <si>
+    <t>CONGRATULATIONS</t>
+  </si>
+  <si>
+    <t>HERZLICHEN GLÜCKWUNSCH</t>
+  </si>
+  <si>
+    <t>PARABÉNS</t>
+  </si>
+  <si>
+    <t>FÉLICITATIONS</t>
+  </si>
+  <si>
+    <t>FELICIDADES</t>
+  </si>
+  <si>
+    <t>SELAMAT</t>
+  </si>
+  <si>
+    <t>ПОЗДРАВЛЯЕМ</t>
+  </si>
+  <si>
+    <t>TEBRİKLER</t>
+  </si>
+  <si>
+    <t>您现在可以提现！</t>
+  </si>
+  <si>
+    <t>You can cash Now!</t>
+  </si>
+  <si>
+    <t>Sie können jetzt auszahlen!</t>
+  </si>
+  <si>
+    <t>今すぐ出金できます！</t>
+  </si>
+  <si>
+    <t>Você pode sacar agora!</t>
+  </si>
+  <si>
+    <t>Vous pouvez retirer maintenant!</t>
+  </si>
+  <si>
+    <t>¡Puedes retirar ahora!</t>
+  </si>
+  <si>
+    <t>지금 출금할 수 있습니다!</t>
+  </si>
+  <si>
+    <t>Anda bisa menarik sekarang!</t>
+  </si>
+  <si>
+    <t>Вы можете вывести средства сейчас!</t>
+  </si>
+  <si>
+    <t>आप अब निकाल सकते हैं!</t>
+  </si>
+  <si>
+    <t>คุณสามารถถอนเงินได้แล้ว!</t>
+  </si>
+  <si>
+    <t>Şimdi para çekebilirsiniz!</t>
+  </si>
+  <si>
+    <t>提现</t>
+  </si>
+  <si>
+    <t>Cash Out</t>
+  </si>
+  <si>
+    <t>Tarik Tunai</t>
+  </si>
+  <si>
+    <t>Вывод средств</t>
+  </si>
+  <si>
+    <t>ถอนเงิน</t>
+  </si>
+  <si>
+    <t>Para Çekme</t>
+  </si>
+  <si>
+    <t>Redeem</t>
+  </si>
+  <si>
+    <t>換金</t>
+  </si>
+  <si>
+    <t>Racheter</t>
+  </si>
+  <si>
+    <t>교환</t>
+  </si>
+  <si>
+    <t>Tukar</t>
+  </si>
+  <si>
+    <t>Погасить</t>
+  </si>
+  <si>
+    <t>रिडीम करें</t>
+  </si>
+  <si>
+    <t>แลก</t>
+  </si>
+  <si>
+    <t>Kullanmak</t>
+  </si>
+  <si>
+    <t>总余额</t>
+  </si>
+  <si>
+    <t>Total balance</t>
+  </si>
+  <si>
+    <t>Gesamtsaldo</t>
+  </si>
+  <si>
+    <t>総残高</t>
+  </si>
+  <si>
+    <t>Saldo Total</t>
+  </si>
+  <si>
+    <t>Solde total</t>
+  </si>
+  <si>
+    <t>Saldo total</t>
+  </si>
+  <si>
+    <t>총 잔액</t>
+  </si>
+  <si>
+    <t>Общий баланс</t>
+  </si>
+  <si>
+    <t>कुल शेष</t>
+  </si>
+  <si>
+    <t>ยอดคงเหลือทั้งหมด</t>
+  </si>
+  <si>
+    <t>Toplam Bakiye</t>
+  </si>
+  <si>
+    <t>再挣&lt;color=#EA2111&gt;{0}&lt;/color&gt;以提现&lt;color=#EA2111&gt;{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Earn &lt;color=#EA2111&gt;{0}&lt;/color&gt; more to withdraw  &lt;color=#EA2111&gt;{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Verdiene &lt;color=#EA2111&gt;{0}&lt;/color&gt; mehr, um &lt;color=#EA2111&gt;{1}&lt;/color&gt; auszuzahlen</t>
+  </si>
+  <si>
+    <t>&lt;color=#EA2111&gt;{0}&lt;/color&gt;稼いで&lt;color=#EA2111&gt;{1}&lt;/color&gt;を出金</t>
+  </si>
+  <si>
+    <t>Ganhe &lt;color=#EA2111&gt;{0}&lt;/color&gt; mais para sacar &lt;color=#EA2111&gt;{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Gagnez &lt;color=#EA2111&gt;{0}&lt;/color&gt; de plus pour retirer &lt;color=#EA2111&gt;{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Gana &lt;color=#EA2111&gt;{0}&lt;/color&gt; más para retirar &lt;color=#EA2111&gt;{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=#EA2111&gt;{0}&lt;/color&gt; 더 벌어서 &lt;color=#EA2111&gt;{1}&lt;/color&gt; 출금</t>
+  </si>
+  <si>
+    <t>Dapatkan &lt;color=#EA2111&gt;{0}&lt;/color&gt; lagi untuk menarik &lt;color=#EA2111&gt;{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Заработайте &lt;color=#EA2111&gt;{0}&lt;/color&gt; больше, чтобы вывести &lt;color=#EA2111&gt;{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=#EA2111&gt;{0}&lt;/color&gt; और कमाएं ताकि &lt;color=#EA2111&gt;{1}&lt;/color&gt; निकाल सकें</t>
+  </si>
+  <si>
+    <t>หา&lt;color=#EA2111&gt;{0}&lt;/color&gt;เพิ่มเพื่อถอน&lt;color=#EA2111&gt;{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=#EA2111&gt;{0}&lt;/color&gt; daha kazanarak &lt;color=#EA2111&gt;{1}&lt;/color&gt; çekin</t>
+  </si>
+  <si>
+    <t>Progressing</t>
+  </si>
+  <si>
+    <t>Sedang Diproses</t>
+  </si>
+  <si>
+    <t>प्रगति पर है</t>
+  </si>
+  <si>
+    <t>İşleniyor</t>
   </si>
 </sst>
 </file>
@@ -6625,7 +6820,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6690,6 +6885,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -7223,7 +7421,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W141"/>
+  <dimension ref="A1:W148"/>
   <sheetFormatPr defaultColWidth="9.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.875" customWidth="1"/>
@@ -13043,7 +13241,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="129" customHeight="1" spans="1:15">
+    <row r="129" customHeight="1" spans="1:16">
       <c r="B129" s="4">
         <v>10124</v>
       </c>
@@ -13087,7 +13285,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="130" customHeight="1" spans="1:15">
+    <row r="130" customHeight="1" spans="1:16">
       <c r="B130" s="4">
         <v>10125</v>
       </c>
@@ -13131,7 +13329,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="131" customHeight="1" spans="1:15">
+    <row r="131" customHeight="1" spans="1:16">
       <c r="B131" s="4">
         <v>10126</v>
       </c>
@@ -13175,7 +13373,7 @@
         <v>1624</v>
       </c>
     </row>
-    <row r="132" customFormat="1" customHeight="1" spans="1:15">
+    <row r="132" customFormat="1" customHeight="1" spans="1:16">
       <c r="B132" s="4">
         <v>10127</v>
       </c>
@@ -13219,7 +13417,7 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="133" customHeight="1" spans="1:15">
+    <row r="133" customHeight="1" spans="1:16">
       <c r="B133" s="4">
         <v>10128</v>
       </c>
@@ -13263,7 +13461,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="134" s="3" customFormat="1" ht="16" customHeight="1" spans="1:15">
+    <row r="134" s="3" customFormat="1" ht="16" customHeight="1" spans="1:16">
       <c r="A134" s="23"/>
       <c r="B134" s="4">
         <v>10129</v>
@@ -13308,7 +13506,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="135" s="3" customFormat="1" customHeight="1" spans="1:15">
+    <row r="135" s="3" customFormat="1" customHeight="1" spans="1:16">
       <c r="A135" s="23"/>
       <c r="B135" s="4">
         <v>10130</v>
@@ -13353,7 +13551,7 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="136" s="3" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="136" s="3" customFormat="1" ht="25" customHeight="1" spans="1:16">
       <c r="A136" s="23"/>
       <c r="B136" s="4">
         <v>10131</v>
@@ -13398,7 +13596,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="137" s="3" customFormat="1" ht="70" customHeight="1" spans="1:15">
+    <row r="137" s="3" customFormat="1" ht="70" customHeight="1" spans="1:16">
       <c r="A137" s="23"/>
       <c r="B137" s="4">
         <v>10132</v>
@@ -13443,7 +13641,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="138" s="3" customFormat="1" ht="19" customHeight="1" spans="1:15">
+    <row r="138" s="3" customFormat="1" ht="19" customHeight="1" spans="1:16">
       <c r="A138" s="23"/>
       <c r="B138" s="4">
         <v>10133</v>
@@ -13488,7 +13686,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="139" s="3" customFormat="1" ht="13.5" spans="1:15">
+    <row r="139" s="3" customFormat="1" ht="13.5" spans="1:16">
       <c r="A139" s="23"/>
       <c r="B139" s="4">
         <v>10134</v>
@@ -13533,7 +13731,7 @@
         <v>1725</v>
       </c>
     </row>
-    <row r="140" s="3" customFormat="1" ht="13.5" spans="1:15">
+    <row r="140" s="3" customFormat="1" ht="13.5" spans="1:16">
       <c r="A140" s="23"/>
       <c r="B140" s="4">
         <v>10135</v>
@@ -13578,7 +13776,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="141" s="3" customFormat="1" ht="31" customHeight="1" spans="1:15">
+    <row r="141" s="3" customFormat="1" ht="31" customHeight="1" spans="1:16">
       <c r="A141" s="23"/>
       <c r="B141" s="4">
         <v>10136</v>
@@ -13621,6 +13819,315 @@
       </c>
       <c r="O141" s="3" t="s">
         <v>1751</v>
+      </c>
+    </row>
+    <row r="142" s="1" customFormat="1" ht="13.5" spans="1:16">
+      <c r="B142" s="4">
+        <v>10137</v>
+      </c>
+      <c r="C142" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D142" s="12" t="s">
+        <v>1752</v>
+      </c>
+      <c r="E142" s="24" t="s">
+        <v>1753</v>
+      </c>
+      <c r="F142" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G142" s="24" t="s">
+        <v>1754</v>
+      </c>
+      <c r="H142" s="24" t="s">
+        <v>1755</v>
+      </c>
+      <c r="I142" s="24" t="s">
+        <v>1756</v>
+      </c>
+      <c r="J142" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="K142" s="24" t="s">
+        <v>1757</v>
+      </c>
+      <c r="L142" s="24" t="s">
+        <v>1758</v>
+      </c>
+      <c r="M142" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="N142" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="O142" s="24" t="s">
+        <v>1759</v>
+      </c>
+      <c r="P142"/>
+    </row>
+    <row r="143" customHeight="1" spans="1:16">
+      <c r="B143" s="4">
+        <v>10138</v>
+      </c>
+      <c r="C143" t="s">
+        <v>1760</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>1761</v>
+      </c>
+      <c r="E143" s="24" t="s">
+        <v>1762</v>
+      </c>
+      <c r="F143" s="24" t="s">
+        <v>1763</v>
+      </c>
+      <c r="G143" s="24" t="s">
+        <v>1764</v>
+      </c>
+      <c r="H143" s="24" t="s">
+        <v>1765</v>
+      </c>
+      <c r="I143" s="24" t="s">
+        <v>1766</v>
+      </c>
+      <c r="J143" s="24" t="s">
+        <v>1767</v>
+      </c>
+      <c r="K143" s="24" t="s">
+        <v>1768</v>
+      </c>
+      <c r="L143" s="24" t="s">
+        <v>1769</v>
+      </c>
+      <c r="M143" s="24" t="s">
+        <v>1770</v>
+      </c>
+      <c r="N143" s="24" t="s">
+        <v>1771</v>
+      </c>
+      <c r="O143" s="24" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="144" customHeight="1" spans="1:16">
+      <c r="B144" s="4">
+        <v>10139</v>
+      </c>
+      <c r="C144" t="s">
+        <v>1773</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>1774</v>
+      </c>
+      <c r="E144" s="24" t="s">
+        <v>1387</v>
+      </c>
+      <c r="F144" s="24" t="s">
+        <v>344</v>
+      </c>
+      <c r="G144" s="24" t="s">
+        <v>1388</v>
+      </c>
+      <c r="H144" s="24" t="s">
+        <v>1389</v>
+      </c>
+      <c r="I144" s="24" t="s">
+        <v>1390</v>
+      </c>
+      <c r="J144" s="24" t="s">
+        <v>348</v>
+      </c>
+      <c r="K144" s="24" t="s">
+        <v>1775</v>
+      </c>
+      <c r="L144" s="24" t="s">
+        <v>1776</v>
+      </c>
+      <c r="M144" s="24" t="s">
+        <v>1393</v>
+      </c>
+      <c r="N144" s="24" t="s">
+        <v>1777</v>
+      </c>
+      <c r="O144" s="24" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="145" customHeight="1" spans="2:15">
+      <c r="B145" s="4">
+        <v>10140</v>
+      </c>
+      <c r="C145" t="s">
+        <v>152</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>1779</v>
+      </c>
+      <c r="E145" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="F145" s="24" t="s">
+        <v>1780</v>
+      </c>
+      <c r="G145" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="H145" s="24" t="s">
+        <v>1781</v>
+      </c>
+      <c r="I145" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="J145" s="24" t="s">
+        <v>1782</v>
+      </c>
+      <c r="K145" s="24" t="s">
+        <v>1783</v>
+      </c>
+      <c r="L145" s="24" t="s">
+        <v>1784</v>
+      </c>
+      <c r="M145" s="24" t="s">
+        <v>1785</v>
+      </c>
+      <c r="N145" s="24" t="s">
+        <v>1786</v>
+      </c>
+      <c r="O145" s="24" t="s">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="146" customHeight="1" spans="2:15">
+      <c r="B146" s="4">
+        <v>10141</v>
+      </c>
+      <c r="C146" t="s">
+        <v>1788</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>1789</v>
+      </c>
+      <c r="E146" s="24" t="s">
+        <v>1790</v>
+      </c>
+      <c r="F146" s="24" t="s">
+        <v>1791</v>
+      </c>
+      <c r="G146" s="24" t="s">
+        <v>1792</v>
+      </c>
+      <c r="H146" s="24" t="s">
+        <v>1793</v>
+      </c>
+      <c r="I146" s="24" t="s">
+        <v>1794</v>
+      </c>
+      <c r="J146" s="24" t="s">
+        <v>1795</v>
+      </c>
+      <c r="K146" s="24" t="s">
+        <v>1792</v>
+      </c>
+      <c r="L146" s="24" t="s">
+        <v>1796</v>
+      </c>
+      <c r="M146" s="24" t="s">
+        <v>1797</v>
+      </c>
+      <c r="N146" s="24" t="s">
+        <v>1798</v>
+      </c>
+      <c r="O146" s="24" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" spans="2:15">
+      <c r="B147" s="4">
+        <v>10142</v>
+      </c>
+      <c r="C147" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>1801</v>
+      </c>
+      <c r="E147" s="24" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F147" s="24" t="s">
+        <v>1803</v>
+      </c>
+      <c r="G147" s="24" t="s">
+        <v>1804</v>
+      </c>
+      <c r="H147" s="24" t="s">
+        <v>1805</v>
+      </c>
+      <c r="I147" s="24" t="s">
+        <v>1806</v>
+      </c>
+      <c r="J147" s="24" t="s">
+        <v>1807</v>
+      </c>
+      <c r="K147" s="24" t="s">
+        <v>1808</v>
+      </c>
+      <c r="L147" s="24" t="s">
+        <v>1809</v>
+      </c>
+      <c r="M147" s="24" t="s">
+        <v>1810</v>
+      </c>
+      <c r="N147" s="24" t="s">
+        <v>1811</v>
+      </c>
+      <c r="O147" s="24" t="s">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="148" customHeight="1" spans="2:15">
+      <c r="B148" s="4">
+        <v>10143</v>
+      </c>
+      <c r="C148" t="s">
+        <v>586</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>1813</v>
+      </c>
+      <c r="E148" s="24" t="s">
+        <v>588</v>
+      </c>
+      <c r="F148" s="24" t="s">
+        <v>589</v>
+      </c>
+      <c r="G148" s="24" t="s">
+        <v>590</v>
+      </c>
+      <c r="H148" s="24" t="s">
+        <v>591</v>
+      </c>
+      <c r="I148" s="24" t="s">
+        <v>592</v>
+      </c>
+      <c r="J148" s="24" t="s">
+        <v>593</v>
+      </c>
+      <c r="K148" s="24" t="s">
+        <v>1814</v>
+      </c>
+      <c r="L148" s="24" t="s">
+        <v>595</v>
+      </c>
+      <c r="M148" s="24" t="s">
+        <v>1815</v>
+      </c>
+      <c r="N148" s="24" t="s">
+        <v>597</v>
+      </c>
+      <c r="O148" s="24" t="s">
+        <v>1816</v>
       </c>
     </row>
   </sheetData>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1955" uniqueCount="1817">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1957" uniqueCount="1819">
   <si>
     <t>##var</t>
   </si>
@@ -6127,6 +6127,12 @@
   </si>
   <si>
     <t>İşleniyor</t>
+  </si>
+  <si>
+    <t>您的帐户成功保存</t>
+  </si>
+  <si>
+    <t>Your account success saved</t>
   </si>
 </sst>
 </file>
@@ -6820,7 +6826,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6885,9 +6891,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -7421,7 +7424,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W148"/>
+  <dimension ref="A1:W149"/>
   <sheetFormatPr defaultColWidth="9.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.875" customWidth="1"/>
@@ -13831,37 +13834,37 @@
       <c r="D142" s="12" t="s">
         <v>1752</v>
       </c>
-      <c r="E142" s="24" t="s">
+      <c r="E142" s="22" t="s">
         <v>1753</v>
       </c>
-      <c r="F142" s="24" t="s">
+      <c r="F142" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="G142" s="24" t="s">
+      <c r="G142" s="22" t="s">
         <v>1754</v>
       </c>
-      <c r="H142" s="24" t="s">
+      <c r="H142" s="22" t="s">
         <v>1755</v>
       </c>
-      <c r="I142" s="24" t="s">
+      <c r="I142" s="22" t="s">
         <v>1756</v>
       </c>
-      <c r="J142" s="24" t="s">
+      <c r="J142" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="K142" s="24" t="s">
+      <c r="K142" s="22" t="s">
         <v>1757</v>
       </c>
-      <c r="L142" s="24" t="s">
+      <c r="L142" s="22" t="s">
         <v>1758</v>
       </c>
-      <c r="M142" s="24" t="s">
+      <c r="M142" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="N142" s="24" t="s">
+      <c r="N142" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="O142" s="24" t="s">
+      <c r="O142" s="22" t="s">
         <v>1759</v>
       </c>
       <c r="P142"/>
@@ -13876,37 +13879,37 @@
       <c r="D143" s="1" t="s">
         <v>1761</v>
       </c>
-      <c r="E143" s="24" t="s">
+      <c r="E143" s="22" t="s">
         <v>1762</v>
       </c>
-      <c r="F143" s="24" t="s">
+      <c r="F143" s="22" t="s">
         <v>1763</v>
       </c>
-      <c r="G143" s="24" t="s">
+      <c r="G143" s="22" t="s">
         <v>1764</v>
       </c>
-      <c r="H143" s="24" t="s">
+      <c r="H143" s="22" t="s">
         <v>1765</v>
       </c>
-      <c r="I143" s="24" t="s">
+      <c r="I143" s="22" t="s">
         <v>1766</v>
       </c>
-      <c r="J143" s="24" t="s">
+      <c r="J143" s="22" t="s">
         <v>1767</v>
       </c>
-      <c r="K143" s="24" t="s">
+      <c r="K143" s="22" t="s">
         <v>1768</v>
       </c>
-      <c r="L143" s="24" t="s">
+      <c r="L143" s="22" t="s">
         <v>1769</v>
       </c>
-      <c r="M143" s="24" t="s">
+      <c r="M143" s="22" t="s">
         <v>1770</v>
       </c>
-      <c r="N143" s="24" t="s">
+      <c r="N143" s="22" t="s">
         <v>1771</v>
       </c>
-      <c r="O143" s="24" t="s">
+      <c r="O143" s="22" t="s">
         <v>1772</v>
       </c>
     </row>
@@ -13920,37 +13923,37 @@
       <c r="D144" s="1" t="s">
         <v>1774</v>
       </c>
-      <c r="E144" s="24" t="s">
+      <c r="E144" s="22" t="s">
         <v>1387</v>
       </c>
-      <c r="F144" s="24" t="s">
+      <c r="F144" s="22" t="s">
         <v>344</v>
       </c>
-      <c r="G144" s="24" t="s">
+      <c r="G144" s="22" t="s">
         <v>1388</v>
       </c>
-      <c r="H144" s="24" t="s">
+      <c r="H144" s="22" t="s">
         <v>1389</v>
       </c>
-      <c r="I144" s="24" t="s">
+      <c r="I144" s="22" t="s">
         <v>1390</v>
       </c>
-      <c r="J144" s="24" t="s">
+      <c r="J144" s="22" t="s">
         <v>348</v>
       </c>
-      <c r="K144" s="24" t="s">
+      <c r="K144" s="22" t="s">
         <v>1775</v>
       </c>
-      <c r="L144" s="24" t="s">
+      <c r="L144" s="22" t="s">
         <v>1776</v>
       </c>
-      <c r="M144" s="24" t="s">
+      <c r="M144" s="22" t="s">
         <v>1393</v>
       </c>
-      <c r="N144" s="24" t="s">
+      <c r="N144" s="22" t="s">
         <v>1777</v>
       </c>
-      <c r="O144" s="24" t="s">
+      <c r="O144" s="22" t="s">
         <v>1778</v>
       </c>
     </row>
@@ -13964,37 +13967,37 @@
       <c r="D145" s="1" t="s">
         <v>1779</v>
       </c>
-      <c r="E145" s="24" t="s">
+      <c r="E145" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="F145" s="24" t="s">
+      <c r="F145" s="22" t="s">
         <v>1780</v>
       </c>
-      <c r="G145" s="24" t="s">
+      <c r="G145" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="H145" s="24" t="s">
+      <c r="H145" s="22" t="s">
         <v>1781</v>
       </c>
-      <c r="I145" s="24" t="s">
+      <c r="I145" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="J145" s="24" t="s">
+      <c r="J145" s="22" t="s">
         <v>1782</v>
       </c>
-      <c r="K145" s="24" t="s">
+      <c r="K145" s="22" t="s">
         <v>1783</v>
       </c>
-      <c r="L145" s="24" t="s">
+      <c r="L145" s="22" t="s">
         <v>1784</v>
       </c>
-      <c r="M145" s="24" t="s">
+      <c r="M145" s="22" t="s">
         <v>1785</v>
       </c>
-      <c r="N145" s="24" t="s">
+      <c r="N145" s="22" t="s">
         <v>1786</v>
       </c>
-      <c r="O145" s="24" t="s">
+      <c r="O145" s="22" t="s">
         <v>1787</v>
       </c>
     </row>
@@ -14008,37 +14011,37 @@
       <c r="D146" s="1" t="s">
         <v>1789</v>
       </c>
-      <c r="E146" s="24" t="s">
+      <c r="E146" s="22" t="s">
         <v>1790</v>
       </c>
-      <c r="F146" s="24" t="s">
+      <c r="F146" s="22" t="s">
         <v>1791</v>
       </c>
-      <c r="G146" s="24" t="s">
+      <c r="G146" s="22" t="s">
         <v>1792</v>
       </c>
-      <c r="H146" s="24" t="s">
+      <c r="H146" s="22" t="s">
         <v>1793</v>
       </c>
-      <c r="I146" s="24" t="s">
+      <c r="I146" s="22" t="s">
         <v>1794</v>
       </c>
-      <c r="J146" s="24" t="s">
+      <c r="J146" s="22" t="s">
         <v>1795</v>
       </c>
-      <c r="K146" s="24" t="s">
+      <c r="K146" s="22" t="s">
         <v>1792</v>
       </c>
-      <c r="L146" s="24" t="s">
+      <c r="L146" s="22" t="s">
         <v>1796</v>
       </c>
-      <c r="M146" s="24" t="s">
+      <c r="M146" s="22" t="s">
         <v>1797</v>
       </c>
-      <c r="N146" s="24" t="s">
+      <c r="N146" s="22" t="s">
         <v>1798</v>
       </c>
-      <c r="O146" s="24" t="s">
+      <c r="O146" s="22" t="s">
         <v>1799</v>
       </c>
     </row>
@@ -14052,37 +14055,37 @@
       <c r="D147" s="1" t="s">
         <v>1801</v>
       </c>
-      <c r="E147" s="24" t="s">
+      <c r="E147" s="22" t="s">
         <v>1802</v>
       </c>
-      <c r="F147" s="24" t="s">
+      <c r="F147" s="22" t="s">
         <v>1803</v>
       </c>
-      <c r="G147" s="24" t="s">
+      <c r="G147" s="22" t="s">
         <v>1804</v>
       </c>
-      <c r="H147" s="24" t="s">
+      <c r="H147" s="22" t="s">
         <v>1805</v>
       </c>
-      <c r="I147" s="24" t="s">
+      <c r="I147" s="22" t="s">
         <v>1806</v>
       </c>
-      <c r="J147" s="24" t="s">
+      <c r="J147" s="22" t="s">
         <v>1807</v>
       </c>
-      <c r="K147" s="24" t="s">
+      <c r="K147" s="22" t="s">
         <v>1808</v>
       </c>
-      <c r="L147" s="24" t="s">
+      <c r="L147" s="22" t="s">
         <v>1809</v>
       </c>
-      <c r="M147" s="24" t="s">
+      <c r="M147" s="22" t="s">
         <v>1810</v>
       </c>
-      <c r="N147" s="24" t="s">
+      <c r="N147" s="22" t="s">
         <v>1811</v>
       </c>
-      <c r="O147" s="24" t="s">
+      <c r="O147" s="22" t="s">
         <v>1812</v>
       </c>
     </row>
@@ -14096,38 +14099,49 @@
       <c r="D148" s="1" t="s">
         <v>1813</v>
       </c>
-      <c r="E148" s="24" t="s">
+      <c r="E148" s="22" t="s">
         <v>588</v>
       </c>
-      <c r="F148" s="24" t="s">
+      <c r="F148" s="22" t="s">
         <v>589</v>
       </c>
-      <c r="G148" s="24" t="s">
+      <c r="G148" s="22" t="s">
         <v>590</v>
       </c>
-      <c r="H148" s="24" t="s">
+      <c r="H148" s="22" t="s">
         <v>591</v>
       </c>
-      <c r="I148" s="24" t="s">
+      <c r="I148" s="22" t="s">
         <v>592</v>
       </c>
-      <c r="J148" s="24" t="s">
+      <c r="J148" s="22" t="s">
         <v>593</v>
       </c>
-      <c r="K148" s="24" t="s">
+      <c r="K148" s="22" t="s">
         <v>1814</v>
       </c>
-      <c r="L148" s="24" t="s">
+      <c r="L148" s="22" t="s">
         <v>595</v>
       </c>
-      <c r="M148" s="24" t="s">
+      <c r="M148" s="22" t="s">
         <v>1815</v>
       </c>
-      <c r="N148" s="24" t="s">
+      <c r="N148" s="22" t="s">
         <v>597</v>
       </c>
-      <c r="O148" s="24" t="s">
+      <c r="O148" s="22" t="s">
         <v>1816</v>
+      </c>
+    </row>
+    <row r="149" customHeight="1" spans="2:15">
+      <c r="B149" s="4">
+        <v>10144</v>
+      </c>
+      <c r="C149" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>1818</v>
       </c>
     </row>
   </sheetData>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1957" uniqueCount="1819">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2072" uniqueCount="1933">
   <si>
     <t>##var</t>
   </si>
@@ -6133,6 +6133,348 @@
   </si>
   <si>
     <t>Your account success saved</t>
+  </si>
+  <si>
+    <t>Ihr Konto wurde erfolgreich gespeichert</t>
+  </si>
+  <si>
+    <t>あなたのアカウントは正常に保存されました</t>
+  </si>
+  <si>
+    <t>Sua conta foi salva com sucesso</t>
+  </si>
+  <si>
+    <t>Votre compte a été enregistré avec succès</t>
+  </si>
+  <si>
+    <t>Su cuenta ha sido guardada con éxito</t>
+  </si>
+  <si>
+    <t>귀하의 계정이 성공적으로 저장되었습니다</t>
+  </si>
+  <si>
+    <t>Akun Anda berhasil disimpan</t>
+  </si>
+  <si>
+    <t>Ваш аккаунт успешно сохранен</t>
+  </si>
+  <si>
+    <t>आपका खाता सफलतापूर्वक सहेजा गया</t>
+  </si>
+  <si>
+    <t>บัญชีของคุณถูกบันทึกสำเร็จ</t>
+  </si>
+  <si>
+    <t>Hesabınız başarıyla kaydedildi</t>
+  </si>
+  <si>
+    <t>账户</t>
+  </si>
+  <si>
+    <t>Account</t>
+  </si>
+  <si>
+    <t>Konto</t>
+  </si>
+  <si>
+    <t>アカウント</t>
+  </si>
+  <si>
+    <t>Conta</t>
+  </si>
+  <si>
+    <t>Compte</t>
+  </si>
+  <si>
+    <t>Cuenta</t>
+  </si>
+  <si>
+    <t>계정</t>
+  </si>
+  <si>
+    <t>Akun</t>
+  </si>
+  <si>
+    <t>Аккаунт</t>
+  </si>
+  <si>
+    <t>खाता</t>
+  </si>
+  <si>
+    <t>บัญชี</t>
+  </si>
+  <si>
+    <t>Hesap</t>
+  </si>
+  <si>
+    <t>输入账户</t>
+  </si>
+  <si>
+    <t>Enter account</t>
+  </si>
+  <si>
+    <t>Konto eingeben</t>
+  </si>
+  <si>
+    <t>アカウントを入力</t>
+  </si>
+  <si>
+    <t>Digite a conta</t>
+  </si>
+  <si>
+    <t>Saisissez le compte</t>
+  </si>
+  <si>
+    <t>Ingrese la cuenta</t>
+  </si>
+  <si>
+    <t>계정 입력</t>
+  </si>
+  <si>
+    <t>Masukkan akun</t>
+  </si>
+  <si>
+    <t>Введите аккаунт</t>
+  </si>
+  <si>
+    <t>खाता दर्ज करें</t>
+  </si>
+  <si>
+    <t>ป้อนบัญชี</t>
+  </si>
+  <si>
+    <t>Hesap girin</t>
+  </si>
+  <si>
+    <t>账户信息</t>
+  </si>
+  <si>
+    <t>Account number</t>
+  </si>
+  <si>
+    <t>Kontonummer</t>
+  </si>
+  <si>
+    <t>アカウント番号</t>
+  </si>
+  <si>
+    <t>Número da conta</t>
+  </si>
+  <si>
+    <t>Numéro de compte</t>
+  </si>
+  <si>
+    <t>Número de cuenta</t>
+  </si>
+  <si>
+    <t>계정 번호</t>
+  </si>
+  <si>
+    <t>Nomor akun</t>
+  </si>
+  <si>
+    <t>Номер аккаунта</t>
+  </si>
+  <si>
+    <t>खाता संख्या</t>
+  </si>
+  <si>
+    <t>หมายเลขบัญชี</t>
+  </si>
+  <si>
+    <t>Hesap numarası</t>
+  </si>
+  <si>
+    <t>确认提款</t>
+  </si>
+  <si>
+    <t>Confirm Withdrawal</t>
+  </si>
+  <si>
+    <t>Auszahlung bestätigen</t>
+  </si>
+  <si>
+    <t>出金を確認</t>
+  </si>
+  <si>
+    <t>Confirmar saque</t>
+  </si>
+  <si>
+    <t>Confirmer le retrait</t>
+  </si>
+  <si>
+    <t>Confirmar el retiro</t>
+  </si>
+  <si>
+    <t>출금 확인</t>
+  </si>
+  <si>
+    <t>Konfirmasi Penarikan</t>
+  </si>
+  <si>
+    <t>Подтвердить вывод средств</t>
+  </si>
+  <si>
+    <t>निकासी की पुष्टि करें</t>
+  </si>
+  <si>
+    <t>ยืนยันการถอนเงิน</t>
+  </si>
+  <si>
+    <t>Çekmeyi onayla</t>
+  </si>
+  <si>
+    <t>账户：</t>
+  </si>
+  <si>
+    <t>Account:</t>
+  </si>
+  <si>
+    <t>Konto:</t>
+  </si>
+  <si>
+    <t>アカウント：</t>
+  </si>
+  <si>
+    <t>Conta:</t>
+  </si>
+  <si>
+    <t>Compte:</t>
+  </si>
+  <si>
+    <t>Cuenta:</t>
+  </si>
+  <si>
+    <t>계정:</t>
+  </si>
+  <si>
+    <t>Akun:</t>
+  </si>
+  <si>
+    <t>Аккаунт:</t>
+  </si>
+  <si>
+    <t>खाता:</t>
+  </si>
+  <si>
+    <t>บัญชี:</t>
+  </si>
+  <si>
+    <t>Hesap:</t>
+  </si>
+  <si>
+    <t>收入：</t>
+  </si>
+  <si>
+    <t>Received:</t>
+  </si>
+  <si>
+    <t>Erhalten:</t>
+  </si>
+  <si>
+    <t>受取：</t>
+  </si>
+  <si>
+    <t>Recebido:</t>
+  </si>
+  <si>
+    <t>Reçu:</t>
+  </si>
+  <si>
+    <t>Recibido:</t>
+  </si>
+  <si>
+    <t>수령:</t>
+  </si>
+  <si>
+    <t>Diterima:</t>
+  </si>
+  <si>
+    <t>Получено:</t>
+  </si>
+  <si>
+    <t>प्राप्त:</t>
+  </si>
+  <si>
+    <t>ได้รับ:</t>
+  </si>
+  <si>
+    <t>Alındı:</t>
+  </si>
+  <si>
+    <t>手续费：</t>
+  </si>
+  <si>
+    <t>Handling fee:</t>
+  </si>
+  <si>
+    <t>Bearbeitungsgebühr:</t>
+  </si>
+  <si>
+    <t>手数料：</t>
+  </si>
+  <si>
+    <t>Taxa de serviço:</t>
+  </si>
+  <si>
+    <t>Frais de traitement:</t>
+  </si>
+  <si>
+    <t>Tarifa de gestión:</t>
+  </si>
+  <si>
+    <t>수수료:</t>
+  </si>
+  <si>
+    <t>Biaya penanganan:</t>
+  </si>
+  <si>
+    <t>Комиссия:</t>
+  </si>
+  <si>
+    <t>हैंडलिंग शुल्क:</t>
+  </si>
+  <si>
+    <t>ค่าธรรมเนียม:</t>
+  </si>
+  <si>
+    <t>İşlem ücreti:</t>
+  </si>
+  <si>
+    <t>日期：</t>
+  </si>
+  <si>
+    <t>Time:</t>
+  </si>
+  <si>
+    <t>Zeit:</t>
+  </si>
+  <si>
+    <t>日時：</t>
+  </si>
+  <si>
+    <t>Hora:</t>
+  </si>
+  <si>
+    <t>Heure:</t>
+  </si>
+  <si>
+    <t>시간:</t>
+  </si>
+  <si>
+    <t>Waktu:</t>
+  </si>
+  <si>
+    <t>Время:</t>
+  </si>
+  <si>
+    <t>समय:</t>
+  </si>
+  <si>
+    <t>เวลา:</t>
+  </si>
+  <si>
+    <t>Zaman:</t>
   </si>
 </sst>
 </file>
@@ -7424,7 +7766,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W149"/>
+  <dimension ref="A1:W157"/>
   <sheetFormatPr defaultColWidth="9.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.875" customWidth="1"/>
@@ -14143,6 +14485,391 @@
       <c r="D149" s="1" t="s">
         <v>1818</v>
       </c>
+      <c r="E149" t="s">
+        <v>1819</v>
+      </c>
+      <c r="F149" t="s">
+        <v>1820</v>
+      </c>
+      <c r="G149" t="s">
+        <v>1821</v>
+      </c>
+      <c r="H149" t="s">
+        <v>1822</v>
+      </c>
+      <c r="I149" t="s">
+        <v>1823</v>
+      </c>
+      <c r="J149" t="s">
+        <v>1824</v>
+      </c>
+      <c r="K149" t="s">
+        <v>1825</v>
+      </c>
+      <c r="L149" t="s">
+        <v>1826</v>
+      </c>
+      <c r="M149" t="s">
+        <v>1827</v>
+      </c>
+      <c r="N149" t="s">
+        <v>1828</v>
+      </c>
+      <c r="O149" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="150" customHeight="1" spans="2:15">
+      <c r="B150" s="4">
+        <v>10145</v>
+      </c>
+      <c r="C150" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E150" t="s">
+        <v>1832</v>
+      </c>
+      <c r="F150" t="s">
+        <v>1833</v>
+      </c>
+      <c r="G150" t="s">
+        <v>1834</v>
+      </c>
+      <c r="H150" t="s">
+        <v>1835</v>
+      </c>
+      <c r="I150" t="s">
+        <v>1836</v>
+      </c>
+      <c r="J150" t="s">
+        <v>1837</v>
+      </c>
+      <c r="K150" t="s">
+        <v>1838</v>
+      </c>
+      <c r="L150" t="s">
+        <v>1839</v>
+      </c>
+      <c r="M150" t="s">
+        <v>1840</v>
+      </c>
+      <c r="N150" t="s">
+        <v>1841</v>
+      </c>
+      <c r="O150" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="151" customHeight="1" spans="2:15">
+      <c r="B151" s="4">
+        <v>10146</v>
+      </c>
+      <c r="C151" t="s">
+        <v>1843</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="E151" t="s">
+        <v>1845</v>
+      </c>
+      <c r="F151" t="s">
+        <v>1846</v>
+      </c>
+      <c r="G151" t="s">
+        <v>1847</v>
+      </c>
+      <c r="H151" t="s">
+        <v>1848</v>
+      </c>
+      <c r="I151" t="s">
+        <v>1849</v>
+      </c>
+      <c r="J151" t="s">
+        <v>1850</v>
+      </c>
+      <c r="K151" t="s">
+        <v>1851</v>
+      </c>
+      <c r="L151" t="s">
+        <v>1852</v>
+      </c>
+      <c r="M151" t="s">
+        <v>1853</v>
+      </c>
+      <c r="N151" t="s">
+        <v>1854</v>
+      </c>
+      <c r="O151" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="152" customHeight="1" spans="2:15">
+      <c r="B152" s="4">
+        <v>10147</v>
+      </c>
+      <c r="C152" t="s">
+        <v>1856</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>1857</v>
+      </c>
+      <c r="E152" t="s">
+        <v>1858</v>
+      </c>
+      <c r="F152" t="s">
+        <v>1859</v>
+      </c>
+      <c r="G152" t="s">
+        <v>1860</v>
+      </c>
+      <c r="H152" t="s">
+        <v>1861</v>
+      </c>
+      <c r="I152" t="s">
+        <v>1862</v>
+      </c>
+      <c r="J152" t="s">
+        <v>1863</v>
+      </c>
+      <c r="K152" t="s">
+        <v>1864</v>
+      </c>
+      <c r="L152" t="s">
+        <v>1865</v>
+      </c>
+      <c r="M152" t="s">
+        <v>1866</v>
+      </c>
+      <c r="N152" t="s">
+        <v>1867</v>
+      </c>
+      <c r="O152" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="153" customHeight="1" spans="2:15">
+      <c r="B153" s="4">
+        <v>10148</v>
+      </c>
+      <c r="C153" t="s">
+        <v>1869</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>1870</v>
+      </c>
+      <c r="E153" t="s">
+        <v>1871</v>
+      </c>
+      <c r="F153" t="s">
+        <v>1872</v>
+      </c>
+      <c r="G153" t="s">
+        <v>1873</v>
+      </c>
+      <c r="H153" t="s">
+        <v>1874</v>
+      </c>
+      <c r="I153" t="s">
+        <v>1875</v>
+      </c>
+      <c r="J153" t="s">
+        <v>1876</v>
+      </c>
+      <c r="K153" t="s">
+        <v>1877</v>
+      </c>
+      <c r="L153" t="s">
+        <v>1878</v>
+      </c>
+      <c r="M153" t="s">
+        <v>1879</v>
+      </c>
+      <c r="N153" t="s">
+        <v>1880</v>
+      </c>
+      <c r="O153" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="154" customHeight="1" spans="2:15">
+      <c r="B154" s="4">
+        <v>10149</v>
+      </c>
+      <c r="C154" t="s">
+        <v>1882</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>1883</v>
+      </c>
+      <c r="E154" t="s">
+        <v>1884</v>
+      </c>
+      <c r="F154" t="s">
+        <v>1885</v>
+      </c>
+      <c r="G154" t="s">
+        <v>1886</v>
+      </c>
+      <c r="H154" t="s">
+        <v>1887</v>
+      </c>
+      <c r="I154" t="s">
+        <v>1888</v>
+      </c>
+      <c r="J154" t="s">
+        <v>1889</v>
+      </c>
+      <c r="K154" t="s">
+        <v>1890</v>
+      </c>
+      <c r="L154" t="s">
+        <v>1891</v>
+      </c>
+      <c r="M154" t="s">
+        <v>1892</v>
+      </c>
+      <c r="N154" t="s">
+        <v>1893</v>
+      </c>
+      <c r="O154" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="155" customHeight="1" spans="2:15">
+      <c r="B155" s="4">
+        <v>10150</v>
+      </c>
+      <c r="C155" t="s">
+        <v>1895</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>1896</v>
+      </c>
+      <c r="E155" t="s">
+        <v>1897</v>
+      </c>
+      <c r="F155" t="s">
+        <v>1898</v>
+      </c>
+      <c r="G155" t="s">
+        <v>1899</v>
+      </c>
+      <c r="H155" t="s">
+        <v>1900</v>
+      </c>
+      <c r="I155" t="s">
+        <v>1901</v>
+      </c>
+      <c r="J155" t="s">
+        <v>1902</v>
+      </c>
+      <c r="K155" t="s">
+        <v>1903</v>
+      </c>
+      <c r="L155" t="s">
+        <v>1904</v>
+      </c>
+      <c r="M155" t="s">
+        <v>1905</v>
+      </c>
+      <c r="N155" t="s">
+        <v>1906</v>
+      </c>
+      <c r="O155" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="156" customHeight="1" spans="2:15">
+      <c r="B156" s="4">
+        <v>10151</v>
+      </c>
+      <c r="C156" t="s">
+        <v>1908</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E156" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F156" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G156" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H156" t="s">
+        <v>1913</v>
+      </c>
+      <c r="I156" t="s">
+        <v>1914</v>
+      </c>
+      <c r="J156" t="s">
+        <v>1915</v>
+      </c>
+      <c r="K156" t="s">
+        <v>1916</v>
+      </c>
+      <c r="L156" t="s">
+        <v>1917</v>
+      </c>
+      <c r="M156" t="s">
+        <v>1918</v>
+      </c>
+      <c r="N156" t="s">
+        <v>1919</v>
+      </c>
+      <c r="O156" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="157" customHeight="1" spans="2:15">
+      <c r="B157" s="4">
+        <v>10152</v>
+      </c>
+      <c r="C157" t="s">
+        <v>1921</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>1922</v>
+      </c>
+      <c r="E157" t="s">
+        <v>1923</v>
+      </c>
+      <c r="F157" t="s">
+        <v>1924</v>
+      </c>
+      <c r="G157" t="s">
+        <v>1925</v>
+      </c>
+      <c r="H157" t="s">
+        <v>1926</v>
+      </c>
+      <c r="I157" t="s">
+        <v>1925</v>
+      </c>
+      <c r="J157" t="s">
+        <v>1927</v>
+      </c>
+      <c r="K157" t="s">
+        <v>1928</v>
+      </c>
+      <c r="L157" t="s">
+        <v>1929</v>
+      </c>
+      <c r="M157" t="s">
+        <v>1930</v>
+      </c>
+      <c r="N157" t="s">
+        <v>1931</v>
+      </c>
+      <c r="O157" t="s">
+        <v>1932</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2528" uniqueCount="1990">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2541" uniqueCount="1998">
   <si>
     <t>##var</t>
   </si>
@@ -6064,6 +6064,30 @@
   </si>
   <si>
     <t>Complete today's tasks and wait for the countdown</t>
+  </si>
+  <si>
+    <t>再挣&lt;color=#EA2111&gt;{0}&lt;/color&gt;即可提现&lt;color=#EA2111&gt;{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Earn &lt;color=#EA2111&gt;{0}&lt;/color&gt; more to withdraw &lt;color=#EA2111&gt;{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Verdiene &lt;color=#EA2111&gt;{0}&lt;/color&gt; mehr, um &lt;color=#EA2111&gt;{1}&lt;/color&gt; abzuheben</t>
+  </si>
+  <si>
+    <t>あと&lt;color=#EA2111&gt;{0}&lt;/color&gt;稼ぐと&lt;color=#EA2111&gt;{1}&lt;/color&gt;を出金できます</t>
+  </si>
+  <si>
+    <t>&lt;color=#EA2111&gt;{0}&lt;/color&gt; 더 벌면 &lt;color=#EA2111&gt;{1}&lt;/color&gt;을 출금할 수 있습니다</t>
+  </si>
+  <si>
+    <t>&lt;color=#EA2111&gt;{0}&lt;/color&gt; और कमाएं ताकि &lt;color=#EA2111&gt;{1}&lt;/color&gt; को निकाल सकें</t>
+  </si>
+  <si>
+    <t>รับ &lt;color=#EA2111&gt;{0}&lt;/color&gt; เพิ่มเติมเพื่อถอน &lt;color=#EA2111&gt;{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=#EA2111&gt;{0}&lt;/color&gt; daha kazanarak &lt;color=#EA2111&gt;{1}&lt;/color&gt; çekebilirsiniz</t>
   </si>
 </sst>
 </file>
@@ -6757,7 +6781,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -6812,6 +6836,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -7345,7 +7373,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W198"/>
+  <dimension ref="A1:W199"/>
   <sheetFormatPr defaultColWidth="9.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.875" style="3" customWidth="1"/>
@@ -10832,7 +10860,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="78" spans="2:15">
+    <row r="78" ht="13.5" spans="2:15">
       <c r="B78" s="10">
         <v>10073</v>
       </c>
@@ -14474,7 +14502,7 @@
         <v>1933</v>
       </c>
     </row>
-    <row r="164" spans="2:15">
+    <row r="164" ht="13.5" spans="2:15">
       <c r="B164">
         <v>10201</v>
       </c>
@@ -15750,7 +15778,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="193" ht="13.5" spans="2:15">
+    <row r="193" ht="13.5" spans="2:17">
       <c r="B193">
         <v>10230</v>
       </c>
@@ -15794,7 +15822,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="194" ht="13.5" spans="2:15">
+    <row r="194" ht="13.5" spans="2:17">
       <c r="B194">
         <v>10231</v>
       </c>
@@ -15838,7 +15866,7 @@
         <v>1983</v>
       </c>
     </row>
-    <row r="195" ht="13.5" spans="2:15">
+    <row r="195" ht="13.5" spans="2:17">
       <c r="B195">
         <v>10232</v>
       </c>
@@ -15882,7 +15910,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="196" ht="13.5" spans="2:15">
+    <row r="196" ht="13.5" spans="2:17">
       <c r="B196">
         <v>10233</v>
       </c>
@@ -15926,7 +15954,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="197" ht="13.5" spans="2:15">
+    <row r="197" ht="13.5" spans="2:17">
       <c r="B197">
         <v>10234</v>
       </c>
@@ -15970,7 +15998,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="198" ht="13.5" spans="2:15">
+    <row r="198" ht="13.5" spans="2:17">
       <c r="B198">
         <v>10235</v>
       </c>
@@ -16013,6 +16041,52 @@
       <c r="O198" t="s">
         <v>1075</v>
       </c>
+    </row>
+    <row r="199" customHeight="1" spans="2:17">
+      <c r="B199">
+        <v>10236</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>1991</v>
+      </c>
+      <c r="E199" s="20" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F199" s="20" t="s">
+        <v>1993</v>
+      </c>
+      <c r="G199" s="20" t="s">
+        <v>1804</v>
+      </c>
+      <c r="H199" s="20" t="s">
+        <v>1805</v>
+      </c>
+      <c r="I199" s="20" t="s">
+        <v>1806</v>
+      </c>
+      <c r="J199" s="20" t="s">
+        <v>1994</v>
+      </c>
+      <c r="K199" s="20" t="s">
+        <v>1808</v>
+      </c>
+      <c r="L199" s="20" t="s">
+        <v>1809</v>
+      </c>
+      <c r="M199" s="20" t="s">
+        <v>1995</v>
+      </c>
+      <c r="N199" s="20" t="s">
+        <v>1996</v>
+      </c>
+      <c r="O199" s="20" t="s">
+        <v>1997</v>
+      </c>
+      <c r="P199" s="21"/>
+      <c r="Q199" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Language" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2541" uniqueCount="1998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2554" uniqueCount="2000">
   <si>
     <t>##var</t>
   </si>
@@ -6088,6 +6088,12 @@
   </si>
   <si>
     <t>&lt;color=#EA2111&gt;{0}&lt;/color&gt; daha kazanarak &lt;color=#EA2111&gt;{1}&lt;/color&gt; çekebilirsiniz</t>
+  </si>
+  <si>
+    <t>完成上一步骤</t>
+  </si>
+  <si>
+    <t>Finish Previous Step</t>
   </si>
 </sst>
 </file>
@@ -7373,7 +7379,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W199"/>
+  <dimension ref="A1:W200"/>
   <sheetFormatPr defaultColWidth="9.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.875" style="3" customWidth="1"/>
@@ -7384,6 +7390,7 @@
     <col min="7" max="7" width="59.875" style="3" customWidth="1"/>
     <col min="8" max="9" width="22.625" style="3" customWidth="1"/>
     <col min="11" max="11" width="60.75" style="3" customWidth="1"/>
+    <col min="12" max="12" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="13.5" spans="1:16">
@@ -16088,6 +16095,50 @@
       <c r="P199" s="21"/>
       <c r="Q199" s="21"/>
     </row>
+    <row r="200" customHeight="1" spans="2:17">
+      <c r="B200">
+        <v>10237</v>
+      </c>
+      <c r="C200" t="s">
+        <v>1998</v>
+      </c>
+      <c r="D200" t="s">
+        <v>1999</v>
+      </c>
+      <c r="E200" t="s">
+        <v>1999</v>
+      </c>
+      <c r="F200" t="s">
+        <v>1999</v>
+      </c>
+      <c r="G200" t="s">
+        <v>1999</v>
+      </c>
+      <c r="H200" t="s">
+        <v>1999</v>
+      </c>
+      <c r="I200" t="s">
+        <v>1999</v>
+      </c>
+      <c r="J200" t="s">
+        <v>1999</v>
+      </c>
+      <c r="K200" t="s">
+        <v>1999</v>
+      </c>
+      <c r="L200" t="s">
+        <v>1999</v>
+      </c>
+      <c r="M200" t="s">
+        <v>1999</v>
+      </c>
+      <c r="N200" t="s">
+        <v>1999</v>
+      </c>
+      <c r="O200" t="s">
+        <v>1999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Language" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2554" uniqueCount="2000">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2570" uniqueCount="2016">
   <si>
     <t>##var</t>
   </si>
@@ -6094,6 +6094,54 @@
   </si>
   <si>
     <t>Finish Previous Step</t>
+  </si>
+  <si>
+    <t>步骤1完成动画标题</t>
+  </si>
+  <si>
+    <t>Step1 finish text</t>
+  </si>
+  <si>
+    <t>步骤2完成动画标题</t>
+  </si>
+  <si>
+    <t>Step2 finish text</t>
+  </si>
+  <si>
+    <t>步骤3完成动画标题</t>
+  </si>
+  <si>
+    <t>Step3 finish text</t>
+  </si>
+  <si>
+    <t>步骤4完成动画标题</t>
+  </si>
+  <si>
+    <t>Step4 finish text</t>
+  </si>
+  <si>
+    <t>步骤5完成动画标题</t>
+  </si>
+  <si>
+    <t>Step5 finish text</t>
+  </si>
+  <si>
+    <t>步骤6完成动画标题</t>
+  </si>
+  <si>
+    <t>Step6 finish text</t>
+  </si>
+  <si>
+    <t>步骤7完成动画标题</t>
+  </si>
+  <si>
+    <t>Step7 finish text</t>
+  </si>
+  <si>
+    <t>步骤8完成动画标题</t>
+  </si>
+  <si>
+    <t>Step8 finish text</t>
   </si>
 </sst>
 </file>
@@ -7379,7 +7427,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W200"/>
+  <dimension ref="A1:W208"/>
   <sheetFormatPr defaultColWidth="9.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.875" style="3" customWidth="1"/>
@@ -11351,7 +11399,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="89" ht="13.5" spans="2:15">
+    <row r="89" spans="2:15">
       <c r="B89" s="10">
         <v>10084</v>
       </c>
@@ -16137,6 +16185,94 @@
       </c>
       <c r="O200" t="s">
         <v>1999</v>
+      </c>
+    </row>
+    <row r="201" customHeight="1" spans="2:17">
+      <c r="B201" s="4">
+        <v>10238</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>2000</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="202" customHeight="1" spans="2:17">
+      <c r="B202" s="4">
+        <v>10239</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>2002</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="203" customHeight="1" spans="2:17">
+      <c r="B203" s="4">
+        <v>10240</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>2004</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="204" customHeight="1" spans="2:17">
+      <c r="B204" s="4">
+        <v>10241</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>2006</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="205" customHeight="1" spans="2:17">
+      <c r="B205" s="4">
+        <v>10242</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>2008</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="206" customHeight="1" spans="2:17">
+      <c r="B206" s="4">
+        <v>10243</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="207" customHeight="1" spans="2:17">
+      <c r="B207" s="4">
+        <v>10244</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>2012</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="208" customHeight="1" spans="2:17">
+      <c r="B208" s="4">
+        <v>10245</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>2014</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>2015</v>
       </c>
     </row>
   </sheetData>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2570" uniqueCount="2016">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2570" uniqueCount="2015">
   <si>
     <t>##var</t>
   </si>
@@ -5904,16 +5904,16 @@
     <t>Withdrawal Eligibility</t>
   </si>
   <si>
-    <t>达成提现金额 {0}/{1}</t>
-  </si>
-  <si>
-    <t>Reached payout goal {0}/{1}</t>
-  </si>
-  <si>
-    <t>观看广告 {0}/{1} 次</t>
-  </si>
-  <si>
-    <t>Watch video {0}/{1} times</t>
+    <t>达成提现金额 &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Reached payout goal &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>观看广告 &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; 次</t>
+  </si>
+  <si>
+    <t>Watch video &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; times</t>
   </si>
   <si>
     <t>为确保提现请求由真实玩家发起，需完成身份核验。请观看 &lt;color=#EA2111&gt;{0}&lt;/color&gt; 次视频广告以激活提现资格，有助于保障账户与打款安全。</t>
@@ -5928,10 +5928,10 @@
     <t>Payout Channel Confirmation</t>
   </si>
   <si>
-    <t>完成关卡 {0}/{1} 关</t>
-  </si>
-  <si>
-    <t>Complete {0}/{1} levels</t>
+    <t>完成关卡 &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; 关</t>
+  </si>
+  <si>
+    <t>Complete &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; levels</t>
   </si>
   <si>
     <t>需确认您的收款渠道处于可用状态且与账户信息一致。请保持在线并完成 &lt;color=#EA2111&gt;{0}&lt;/color&gt; 关，有助于减少打款失败并顺利处理提现。</t>
@@ -5946,10 +5946,10 @@
     <t>Account Activity Check</t>
   </si>
   <si>
-    <t>活跃签到 {0}/{1} 天</t>
-  </si>
-  <si>
-    <t>Active check-in {0}/{1} days</t>
+    <t>活跃签到 &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; 天</t>
+  </si>
+  <si>
+    <t>Active check-in &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; days</t>
   </si>
   <si>
     <t>为确认账户已启用且您为真实玩家，请保持连续活跃。今日还需 &lt;color=#EA2111&gt;{0}&lt;/color&gt; 关完成签到，不活跃可能导致审核延后。</t>
@@ -5982,10 +5982,7 @@
     <t>Risk review submitted</t>
   </si>
   <si>
-    <t>银行审核 {0}/{1} 天</t>
-  </si>
-  <si>
-    <t>Bank review {0}/{1} days</t>
+    <t>Bank review &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; days</t>
   </si>
   <si>
     <t>银行审核约需 &lt;color=#EA2111&gt;{0}&lt;/color&gt; 天，请保持账号活跃。不活跃账号可能被插队，导致审核进度延迟。今日还需 &lt;color=#EA2111&gt;{1}&lt;/color&gt; 关完成签到。</t>
@@ -6018,10 +6015,10 @@
     <t>Fee compliance confirmed</t>
   </si>
   <si>
-    <t>排队进度 {0}/{1}</t>
-  </si>
-  <si>
-    <t>Queue progress {0}/{1}</t>
+    <t>排队进度 &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Queue progress &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt;</t>
   </si>
   <si>
     <t>当前提现申请较多，将按提交顺序分批处理。请保持账号活跃并完成今日 &lt;color=#EA2111&gt;{0}&lt;/color&gt; 关，有助于维持审核顺位。较大金额申请将优先处理，请耐心等待。</t>
@@ -6042,10 +6039,10 @@
     <t>Final queue step completed</t>
   </si>
   <si>
-    <t>保持活跃 {0}/{1} 关</t>
-  </si>
-  <si>
-    <t>Stay active {0}/{1} levels</t>
+    <t>保持活跃 &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; 关</t>
+  </si>
+  <si>
+    <t>Stay active &lt;color=#EA2111&gt;{0}/{1}&lt;/color&gt; levels</t>
   </si>
   <si>
     <t>当前支付通道较为繁忙，您的申请正在排队处理中。请保持账号活跃并完成每日 &lt;color=#EA2111&gt;{0}&lt;/color&gt; 关，以免排队顺位被延后。请耐心等待，无需额外操作。</t>
@@ -6054,10 +6051,10 @@
     <t>The payout channel is busy and your request is queued. Stay active and complete &lt;color=#EA2111&gt;{0}&lt;/color&gt; levels daily to maintain your queue position. Please wait patiently.</t>
   </si>
   <si>
-    <t>剩余 {0} 可继续</t>
-  </si>
-  <si>
-    <t>Available in {0}</t>
+    <t>剩余 &lt;color=#EA2111&gt;{0}&lt;/color&gt; 可继续</t>
+  </si>
+  <si>
+    <t>Available in &lt;color=#EA2111&gt;{0}&lt;/color&gt;</t>
   </si>
   <si>
     <t>请完成今日任务并等待倒计时结束</t>
@@ -11399,7 +11396,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="89" spans="2:15">
+    <row r="89" ht="13.5" spans="2:15">
       <c r="B89" s="10">
         <v>10084</v>
       </c>
@@ -14601,7 +14598,7 @@
         <v>1935</v>
       </c>
     </row>
-    <row r="165" ht="13.5" spans="2:15">
+    <row r="165" spans="2:15">
       <c r="B165">
         <v>10202</v>
       </c>
@@ -14645,7 +14642,7 @@
         <v>1937</v>
       </c>
     </row>
-    <row r="166" ht="13.5" spans="2:15">
+    <row r="166" spans="2:15">
       <c r="B166">
         <v>10203</v>
       </c>
@@ -14777,7 +14774,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="169" ht="13.5" spans="2:15">
+    <row r="169" spans="2:15">
       <c r="B169">
         <v>10206</v>
       </c>
@@ -14821,7 +14818,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="170" ht="13.5" spans="2:15">
+    <row r="170" spans="2:15">
       <c r="B170">
         <v>10207</v>
       </c>
@@ -14953,7 +14950,7 @@
         <v>1949</v>
       </c>
     </row>
-    <row r="173" ht="13.5" spans="2:15">
+    <row r="173" spans="2:15">
       <c r="B173">
         <v>10210</v>
       </c>
@@ -14997,7 +14994,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="174" ht="13.5" spans="2:15">
+    <row r="174" spans="2:15">
       <c r="B174">
         <v>10211</v>
       </c>
@@ -15041,7 +15038,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="175" ht="13.5" spans="2:15">
+    <row r="175" spans="2:15">
       <c r="B175">
         <v>10212</v>
       </c>
@@ -15129,7 +15126,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="177" ht="13.5" spans="2:15">
+    <row r="177" spans="2:15">
       <c r="B177">
         <v>10214</v>
       </c>
@@ -15173,7 +15170,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="178" ht="13.5" spans="2:15">
+    <row r="178" spans="2:15">
       <c r="B178">
         <v>10215</v>
       </c>
@@ -15349,48 +15346,48 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="182" ht="13.5" spans="2:15">
+    <row r="182" spans="2:15">
       <c r="B182">
         <v>10219</v>
       </c>
       <c r="C182" t="s">
+        <v>1713</v>
+      </c>
+      <c r="D182" t="s">
         <v>1962</v>
       </c>
-      <c r="D182" t="s">
-        <v>1963</v>
-      </c>
       <c r="E182" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="F182" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="G182" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H182" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="I182" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="J182" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="K182" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="L182" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="M182" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="N182" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="O182" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="183" ht="13.5" spans="2:15">
@@ -15398,43 +15395,43 @@
         <v>10220</v>
       </c>
       <c r="C183" t="s">
+        <v>1963</v>
+      </c>
+      <c r="D183" t="s">
         <v>1964</v>
       </c>
-      <c r="D183" t="s">
-        <v>1965</v>
-      </c>
       <c r="E183" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="F183" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="G183" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H183" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="I183" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="J183" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="K183" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="L183" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="M183" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="N183" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="O183" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="184" ht="13.5" spans="2:15">
@@ -15442,90 +15439,90 @@
         <v>10221</v>
       </c>
       <c r="C184" t="s">
+        <v>1965</v>
+      </c>
+      <c r="D184" t="s">
         <v>1966</v>
       </c>
-      <c r="D184" t="s">
-        <v>1967</v>
-      </c>
       <c r="E184" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="F184" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="G184" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H184" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="I184" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="J184" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="K184" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="L184" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="M184" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="N184" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="O184" t="s">
-        <v>1967</v>
-      </c>
-    </row>
-    <row r="185" ht="13.5" spans="2:15">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="185" spans="2:15">
       <c r="B185">
         <v>10222</v>
       </c>
       <c r="C185" t="s">
+        <v>1713</v>
+      </c>
+      <c r="D185" t="s">
         <v>1962</v>
       </c>
-      <c r="D185" t="s">
-        <v>1963</v>
-      </c>
       <c r="E185" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="F185" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="G185" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H185" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="I185" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="J185" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="K185" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="L185" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="M185" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="N185" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="O185" t="s">
-        <v>1963</v>
-      </c>
-    </row>
-    <row r="186" ht="13.5" spans="2:15">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="186" spans="2:15">
       <c r="B186">
         <v>10223</v>
       </c>
@@ -15574,43 +15571,43 @@
         <v>10224</v>
       </c>
       <c r="C187" t="s">
+        <v>1967</v>
+      </c>
+      <c r="D187" t="s">
         <v>1968</v>
       </c>
-      <c r="D187" t="s">
-        <v>1969</v>
-      </c>
       <c r="E187" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="F187" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="G187" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H187" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="I187" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="J187" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="K187" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="L187" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="M187" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="N187" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="O187" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="188" ht="13.5" spans="2:15">
@@ -15618,43 +15615,43 @@
         <v>10225</v>
       </c>
       <c r="C188" t="s">
+        <v>1969</v>
+      </c>
+      <c r="D188" t="s">
         <v>1970</v>
       </c>
-      <c r="D188" t="s">
-        <v>1971</v>
-      </c>
       <c r="E188" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="F188" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="G188" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H188" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="I188" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="J188" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="K188" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="L188" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="M188" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="N188" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="O188" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="189" ht="13.5" spans="2:15">
@@ -15662,87 +15659,87 @@
         <v>10226</v>
       </c>
       <c r="C189" t="s">
+        <v>1971</v>
+      </c>
+      <c r="D189" t="s">
         <v>1972</v>
       </c>
-      <c r="D189" t="s">
-        <v>1973</v>
-      </c>
       <c r="E189" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="F189" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="G189" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H189" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="I189" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="J189" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="K189" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="L189" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="M189" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="N189" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="O189" t="s">
-        <v>1973</v>
-      </c>
-    </row>
-    <row r="190" ht="13.5" spans="2:15">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="190" spans="2:15">
       <c r="B190">
         <v>10227</v>
       </c>
       <c r="C190" t="s">
+        <v>1973</v>
+      </c>
+      <c r="D190" t="s">
         <v>1974</v>
       </c>
-      <c r="D190" t="s">
-        <v>1975</v>
-      </c>
       <c r="E190" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="F190" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="G190" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H190" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="I190" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="J190" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="K190" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="L190" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="M190" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="N190" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="O190" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="191" ht="13.5" spans="2:15">
@@ -15750,43 +15747,43 @@
         <v>10228</v>
       </c>
       <c r="C191" t="s">
+        <v>1975</v>
+      </c>
+      <c r="D191" t="s">
         <v>1976</v>
       </c>
-      <c r="D191" t="s">
-        <v>1977</v>
-      </c>
       <c r="E191" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="F191" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="G191" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H191" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="I191" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="J191" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="K191" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="L191" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="M191" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="N191" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="O191" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="192" ht="13.5" spans="2:15">
@@ -15794,43 +15791,43 @@
         <v>10229</v>
       </c>
       <c r="C192" t="s">
+        <v>1977</v>
+      </c>
+      <c r="D192" t="s">
         <v>1978</v>
       </c>
-      <c r="D192" t="s">
-        <v>1979</v>
-      </c>
       <c r="E192" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="F192" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="G192" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H192" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="I192" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="J192" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="K192" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="L192" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="M192" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="N192" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="O192" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="193" ht="13.5" spans="2:17">
@@ -15838,87 +15835,87 @@
         <v>10230</v>
       </c>
       <c r="C193" t="s">
+        <v>1979</v>
+      </c>
+      <c r="D193" t="s">
         <v>1980</v>
       </c>
-      <c r="D193" t="s">
-        <v>1981</v>
-      </c>
       <c r="E193" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="F193" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="G193" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H193" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="I193" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="J193" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="K193" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="L193" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="M193" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="N193" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="O193" t="s">
-        <v>1981</v>
-      </c>
-    </row>
-    <row r="194" ht="13.5" spans="2:17">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="194" spans="2:17">
       <c r="B194">
         <v>10231</v>
       </c>
       <c r="C194" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D194" t="s">
         <v>1982</v>
       </c>
-      <c r="D194" t="s">
-        <v>1983</v>
-      </c>
       <c r="E194" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="F194" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="G194" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H194" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="I194" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="J194" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="K194" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="L194" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="M194" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="N194" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="O194" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="195" ht="13.5" spans="2:17">
@@ -15926,87 +15923,87 @@
         <v>10232</v>
       </c>
       <c r="C195" t="s">
+        <v>1983</v>
+      </c>
+      <c r="D195" t="s">
         <v>1984</v>
       </c>
-      <c r="D195" t="s">
-        <v>1985</v>
-      </c>
       <c r="E195" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="F195" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="G195" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H195" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="I195" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="J195" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="K195" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="L195" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="M195" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="N195" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="O195" t="s">
-        <v>1985</v>
-      </c>
-    </row>
-    <row r="196" ht="13.5" spans="2:17">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="196" spans="2:17">
       <c r="B196">
         <v>10233</v>
       </c>
       <c r="C196" t="s">
+        <v>1985</v>
+      </c>
+      <c r="D196" t="s">
         <v>1986</v>
       </c>
-      <c r="D196" t="s">
-        <v>1987</v>
-      </c>
       <c r="E196" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="F196" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="G196" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H196" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="I196" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="J196" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="K196" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="L196" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="M196" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="N196" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="O196" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="197" ht="13.5" spans="2:17">
@@ -16014,43 +16011,43 @@
         <v>10234</v>
       </c>
       <c r="C197" t="s">
+        <v>1987</v>
+      </c>
+      <c r="D197" t="s">
         <v>1988</v>
       </c>
-      <c r="D197" t="s">
-        <v>1989</v>
-      </c>
       <c r="E197" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="F197" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="G197" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H197" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="I197" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="J197" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="K197" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="L197" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="M197" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="N197" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="O197" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="198" ht="13.5" spans="2:17">
@@ -16102,16 +16099,16 @@
         <v>10236</v>
       </c>
       <c r="C199" s="3" t="s">
+        <v>1989</v>
+      </c>
+      <c r="D199" s="1" t="s">
         <v>1990</v>
       </c>
-      <c r="D199" s="1" t="s">
+      <c r="E199" s="20" t="s">
         <v>1991</v>
       </c>
-      <c r="E199" s="20" t="s">
+      <c r="F199" s="20" t="s">
         <v>1992</v>
-      </c>
-      <c r="F199" s="20" t="s">
-        <v>1993</v>
       </c>
       <c r="G199" s="20" t="s">
         <v>1804</v>
@@ -16123,7 +16120,7 @@
         <v>1806</v>
       </c>
       <c r="J199" s="20" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="K199" s="20" t="s">
         <v>1808</v>
@@ -16132,13 +16129,13 @@
         <v>1809</v>
       </c>
       <c r="M199" s="20" t="s">
+        <v>1994</v>
+      </c>
+      <c r="N199" s="20" t="s">
         <v>1995</v>
       </c>
-      <c r="N199" s="20" t="s">
+      <c r="O199" s="20" t="s">
         <v>1996</v>
-      </c>
-      <c r="O199" s="20" t="s">
-        <v>1997</v>
       </c>
       <c r="P199" s="21"/>
       <c r="Q199" s="21"/>
@@ -16148,43 +16145,43 @@
         <v>10237</v>
       </c>
       <c r="C200" t="s">
+        <v>1997</v>
+      </c>
+      <c r="D200" t="s">
         <v>1998</v>
       </c>
-      <c r="D200" t="s">
-        <v>1999</v>
-      </c>
       <c r="E200" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="F200" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="G200" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H200" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="I200" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="J200" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="K200" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="L200" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="M200" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="N200" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="O200" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="201" customHeight="1" spans="2:17">
@@ -16192,10 +16189,10 @@
         <v>10238</v>
       </c>
       <c r="C201" s="3" t="s">
+        <v>1999</v>
+      </c>
+      <c r="D201" s="1" t="s">
         <v>2000</v>
-      </c>
-      <c r="D201" s="1" t="s">
-        <v>2001</v>
       </c>
     </row>
     <row r="202" customHeight="1" spans="2:17">
@@ -16203,10 +16200,10 @@
         <v>10239</v>
       </c>
       <c r="C202" s="3" t="s">
+        <v>2001</v>
+      </c>
+      <c r="D202" s="1" t="s">
         <v>2002</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>2003</v>
       </c>
     </row>
     <row r="203" customHeight="1" spans="2:17">
@@ -16214,10 +16211,10 @@
         <v>10240</v>
       </c>
       <c r="C203" s="3" t="s">
+        <v>2003</v>
+      </c>
+      <c r="D203" s="1" t="s">
         <v>2004</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>2005</v>
       </c>
     </row>
     <row r="204" customHeight="1" spans="2:17">
@@ -16225,10 +16222,10 @@
         <v>10241</v>
       </c>
       <c r="C204" s="3" t="s">
+        <v>2005</v>
+      </c>
+      <c r="D204" s="1" t="s">
         <v>2006</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>2007</v>
       </c>
     </row>
     <row r="205" customHeight="1" spans="2:17">
@@ -16236,10 +16233,10 @@
         <v>10242</v>
       </c>
       <c r="C205" s="3" t="s">
+        <v>2007</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>2008</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>2009</v>
       </c>
     </row>
     <row r="206" customHeight="1" spans="2:17">
@@ -16247,10 +16244,10 @@
         <v>10243</v>
       </c>
       <c r="C206" s="3" t="s">
+        <v>2009</v>
+      </c>
+      <c r="D206" s="1" t="s">
         <v>2010</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>2011</v>
       </c>
     </row>
     <row r="207" customHeight="1" spans="2:17">
@@ -16258,10 +16255,10 @@
         <v>10244</v>
       </c>
       <c r="C207" s="3" t="s">
+        <v>2011</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>2012</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>2013</v>
       </c>
     </row>
     <row r="208" customHeight="1" spans="2:17">
@@ -16269,10 +16266,10 @@
         <v>10245</v>
       </c>
       <c r="C208" s="3" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>2014</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>2015</v>
       </c>
     </row>
   </sheetData>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Language" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2516" uniqueCount="1978">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2528" uniqueCount="1990">
   <si>
     <t>##var</t>
   </si>
@@ -5856,6 +5856,46 @@
   </si>
   <si>
     <t>Zaman:</t>
+  </si>
+  <si>
+    <t>累计奖励</t>
+  </si>
+  <si>
+    <t>Total Reward1</t>
+  </si>
+  <si>
+    <t>累积通过{0}次关卡将便能获得抽奖资格</t>
+  </si>
+  <si>
+    <t>Accumulating {0} passes will grant you the qualification for the lottery</t>
+  </si>
+  <si>
+    <t>累计奖励2</t>
+  </si>
+  <si>
+    <t>Total Reward2</t>
+  </si>
+  <si>
+    <t>参与成功，请等待开奖时间
+（剩余约{0}天）</t>
+  </si>
+  <si>
+    <t>Participation successful, please wait for the lottery draw time
+ (approximately {0} days remaining)</t>
+  </si>
+  <si>
+    <t>累计奖励3</t>
+  </si>
+  <si>
+    <t>Total Reward3</t>
+  </si>
+  <si>
+    <t>抱歉，你没有赢得大奖。
+但我们还是为你准备了一份奖励</t>
+  </si>
+  <si>
+    <t>Sorry, you didn't win the grand prize.
+But we still have prepared a reward for you</t>
   </si>
   <si>
     <t>提现资格审核</t>
@@ -7305,7 +7345,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W192"/>
+  <dimension ref="A1:W198"/>
   <sheetFormatPr defaultColWidth="9.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.875" style="3" customWidth="1"/>
@@ -10792,7 +10832,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="78" ht="13.5" spans="2:15">
+    <row r="78" spans="2:15">
       <c r="B78" s="10">
         <v>10073</v>
       </c>
@@ -14368,669 +14408,471 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="158" spans="2:15">
-      <c r="B158">
+    <row r="158" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="B158" s="4">
+        <v>10153</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>1922</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="159" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="B159" s="4">
+        <v>10154</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>1924</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="160" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="B160" s="4">
+        <v>10155</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>1926</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="161" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="B161" s="4">
+        <v>10156</v>
+      </c>
+      <c r="C161" s="18" t="s">
+        <v>1928</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="162" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="B162" s="4">
+        <v>10157</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>1930</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="163" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="B163" s="4">
+        <v>10158</v>
+      </c>
+      <c r="C163" s="18" t="s">
+        <v>1932</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="164" spans="2:15">
+      <c r="B164">
         <v>10201</v>
       </c>
-      <c r="C158" t="s">
-        <v>1922</v>
-      </c>
-      <c r="D158" t="s">
-        <v>1923</v>
-      </c>
-      <c r="E158" t="s">
-        <v>1923</v>
-      </c>
-      <c r="F158" t="s">
-        <v>1923</v>
-      </c>
-      <c r="G158" t="s">
-        <v>1923</v>
-      </c>
-      <c r="H158" t="s">
-        <v>1923</v>
-      </c>
-      <c r="I158" t="s">
-        <v>1923</v>
-      </c>
-      <c r="J158" t="s">
-        <v>1923</v>
-      </c>
-      <c r="K158" t="s">
-        <v>1923</v>
-      </c>
-      <c r="L158" t="s">
-        <v>1923</v>
-      </c>
-      <c r="M158" t="s">
-        <v>1923</v>
-      </c>
-      <c r="N158" t="s">
-        <v>1923</v>
-      </c>
-      <c r="O158" t="s">
-        <v>1923</v>
-      </c>
-    </row>
-    <row r="159" spans="2:15">
-      <c r="B159">
-        <v>10202</v>
-      </c>
-      <c r="C159" t="s">
-        <v>1924</v>
-      </c>
-      <c r="D159" t="s">
-        <v>1925</v>
-      </c>
-      <c r="E159" t="s">
-        <v>1925</v>
-      </c>
-      <c r="F159" t="s">
-        <v>1925</v>
-      </c>
-      <c r="G159" t="s">
-        <v>1925</v>
-      </c>
-      <c r="H159" t="s">
-        <v>1925</v>
-      </c>
-      <c r="I159" t="s">
-        <v>1925</v>
-      </c>
-      <c r="J159" t="s">
-        <v>1925</v>
-      </c>
-      <c r="K159" t="s">
-        <v>1925</v>
-      </c>
-      <c r="L159" t="s">
-        <v>1925</v>
-      </c>
-      <c r="M159" t="s">
-        <v>1925</v>
-      </c>
-      <c r="N159" t="s">
-        <v>1925</v>
-      </c>
-      <c r="O159" t="s">
-        <v>1925</v>
-      </c>
-    </row>
-    <row r="160" spans="2:15">
-      <c r="B160">
-        <v>10203</v>
-      </c>
-      <c r="C160" t="s">
-        <v>1926</v>
-      </c>
-      <c r="D160" t="s">
-        <v>1927</v>
-      </c>
-      <c r="E160" t="s">
-        <v>1927</v>
-      </c>
-      <c r="F160" t="s">
-        <v>1927</v>
-      </c>
-      <c r="G160" t="s">
-        <v>1927</v>
-      </c>
-      <c r="H160" t="s">
-        <v>1927</v>
-      </c>
-      <c r="I160" t="s">
-        <v>1927</v>
-      </c>
-      <c r="J160" t="s">
-        <v>1927</v>
-      </c>
-      <c r="K160" t="s">
-        <v>1927</v>
-      </c>
-      <c r="L160" t="s">
-        <v>1927</v>
-      </c>
-      <c r="M160" t="s">
-        <v>1927</v>
-      </c>
-      <c r="N160" t="s">
-        <v>1927</v>
-      </c>
-      <c r="O160" t="s">
-        <v>1927</v>
-      </c>
-    </row>
-    <row r="161" spans="2:15">
-      <c r="B161">
-        <v>10204</v>
-      </c>
-      <c r="C161" t="s">
-        <v>1928</v>
-      </c>
-      <c r="D161" t="s">
-        <v>1929</v>
-      </c>
-      <c r="E161" t="s">
-        <v>1929</v>
-      </c>
-      <c r="F161" t="s">
-        <v>1929</v>
-      </c>
-      <c r="G161" t="s">
-        <v>1929</v>
-      </c>
-      <c r="H161" t="s">
-        <v>1929</v>
-      </c>
-      <c r="I161" t="s">
-        <v>1929</v>
-      </c>
-      <c r="J161" t="s">
-        <v>1929</v>
-      </c>
-      <c r="K161" t="s">
-        <v>1929</v>
-      </c>
-      <c r="L161" t="s">
-        <v>1929</v>
-      </c>
-      <c r="M161" t="s">
-        <v>1929</v>
-      </c>
-      <c r="N161" t="s">
-        <v>1929</v>
-      </c>
-      <c r="O161" t="s">
-        <v>1929</v>
-      </c>
-    </row>
-    <row r="162" spans="2:15">
-      <c r="B162">
-        <v>10205</v>
-      </c>
-      <c r="C162" t="s">
-        <v>1930</v>
-      </c>
-      <c r="D162" t="s">
-        <v>1931</v>
-      </c>
-      <c r="E162" t="s">
-        <v>1931</v>
-      </c>
-      <c r="F162" t="s">
-        <v>1931</v>
-      </c>
-      <c r="G162" t="s">
-        <v>1931</v>
-      </c>
-      <c r="H162" t="s">
-        <v>1931</v>
-      </c>
-      <c r="I162" t="s">
-        <v>1931</v>
-      </c>
-      <c r="J162" t="s">
-        <v>1931</v>
-      </c>
-      <c r="K162" t="s">
-        <v>1931</v>
-      </c>
-      <c r="L162" t="s">
-        <v>1931</v>
-      </c>
-      <c r="M162" t="s">
-        <v>1931</v>
-      </c>
-      <c r="N162" t="s">
-        <v>1931</v>
-      </c>
-      <c r="O162" t="s">
-        <v>1931</v>
-      </c>
-    </row>
-    <row r="163" ht="13.5" spans="2:15">
-      <c r="B163">
-        <v>10206</v>
-      </c>
-      <c r="C163" t="s">
-        <v>1926</v>
-      </c>
-      <c r="D163" t="s">
-        <v>1927</v>
-      </c>
-      <c r="E163" t="s">
-        <v>1927</v>
-      </c>
-      <c r="F163" t="s">
-        <v>1927</v>
-      </c>
-      <c r="G163" t="s">
-        <v>1927</v>
-      </c>
-      <c r="H163" t="s">
-        <v>1927</v>
-      </c>
-      <c r="I163" t="s">
-        <v>1927</v>
-      </c>
-      <c r="J163" t="s">
-        <v>1927</v>
-      </c>
-      <c r="K163" t="s">
-        <v>1927</v>
-      </c>
-      <c r="L163" t="s">
-        <v>1927</v>
-      </c>
-      <c r="M163" t="s">
-        <v>1927</v>
-      </c>
-      <c r="N163" t="s">
-        <v>1927</v>
-      </c>
-      <c r="O163" t="s">
-        <v>1927</v>
-      </c>
-    </row>
-    <row r="164" ht="13.5" spans="2:15">
-      <c r="B164">
-        <v>10207</v>
-      </c>
       <c r="C164" t="s">
-        <v>1932</v>
+        <v>1934</v>
       </c>
       <c r="D164" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="E164" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="F164" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="G164" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="H164" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="I164" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="J164" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="K164" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="L164" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="M164" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="N164" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="O164" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="165" ht="13.5" spans="2:15">
       <c r="B165">
-        <v>10208</v>
+        <v>10202</v>
       </c>
       <c r="C165" t="s">
-        <v>1934</v>
+        <v>1936</v>
       </c>
       <c r="D165" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="E165" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="F165" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="G165" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="H165" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="I165" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="J165" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="K165" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="L165" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="M165" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="N165" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="O165" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="166" ht="13.5" spans="2:15">
       <c r="B166">
-        <v>10209</v>
+        <v>10203</v>
       </c>
       <c r="C166" t="s">
-        <v>1936</v>
+        <v>1938</v>
       </c>
       <c r="D166" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="E166" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="F166" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="G166" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="H166" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="I166" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="J166" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="K166" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="L166" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="M166" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="N166" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="O166" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="167" ht="13.5" spans="2:15">
       <c r="B167">
-        <v>10210</v>
+        <v>10204</v>
       </c>
       <c r="C167" t="s">
-        <v>1932</v>
+        <v>1940</v>
       </c>
       <c r="D167" t="s">
-        <v>1933</v>
+        <v>1941</v>
       </c>
       <c r="E167" t="s">
-        <v>1933</v>
+        <v>1941</v>
       </c>
       <c r="F167" t="s">
-        <v>1933</v>
+        <v>1941</v>
       </c>
       <c r="G167" t="s">
-        <v>1933</v>
+        <v>1941</v>
       </c>
       <c r="H167" t="s">
-        <v>1933</v>
+        <v>1941</v>
       </c>
       <c r="I167" t="s">
-        <v>1933</v>
+        <v>1941</v>
       </c>
       <c r="J167" t="s">
-        <v>1933</v>
+        <v>1941</v>
       </c>
       <c r="K167" t="s">
-        <v>1933</v>
+        <v>1941</v>
       </c>
       <c r="L167" t="s">
-        <v>1933</v>
+        <v>1941</v>
       </c>
       <c r="M167" t="s">
-        <v>1933</v>
+        <v>1941</v>
       </c>
       <c r="N167" t="s">
-        <v>1933</v>
+        <v>1941</v>
       </c>
       <c r="O167" t="s">
-        <v>1933</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="168" ht="13.5" spans="2:15">
       <c r="B168">
-        <v>10211</v>
+        <v>10205</v>
       </c>
       <c r="C168" t="s">
-        <v>1938</v>
+        <v>1942</v>
       </c>
       <c r="D168" t="s">
-        <v>1939</v>
+        <v>1943</v>
       </c>
       <c r="E168" t="s">
-        <v>1939</v>
+        <v>1943</v>
       </c>
       <c r="F168" t="s">
-        <v>1939</v>
+        <v>1943</v>
       </c>
       <c r="G168" t="s">
-        <v>1939</v>
+        <v>1943</v>
       </c>
       <c r="H168" t="s">
-        <v>1939</v>
+        <v>1943</v>
       </c>
       <c r="I168" t="s">
-        <v>1939</v>
+        <v>1943</v>
       </c>
       <c r="J168" t="s">
-        <v>1939</v>
+        <v>1943</v>
       </c>
       <c r="K168" t="s">
-        <v>1939</v>
+        <v>1943</v>
       </c>
       <c r="L168" t="s">
-        <v>1939</v>
+        <v>1943</v>
       </c>
       <c r="M168" t="s">
-        <v>1939</v>
+        <v>1943</v>
       </c>
       <c r="N168" t="s">
-        <v>1939</v>
+        <v>1943</v>
       </c>
       <c r="O168" t="s">
-        <v>1939</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="169" ht="13.5" spans="2:15">
       <c r="B169">
-        <v>10212</v>
+        <v>10206</v>
       </c>
       <c r="C169" t="s">
-        <v>1940</v>
+        <v>1938</v>
       </c>
       <c r="D169" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="E169" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="F169" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="G169" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="H169" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="I169" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="J169" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="K169" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="L169" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="M169" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="N169" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="O169" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="170" ht="13.5" spans="2:15">
       <c r="B170">
-        <v>10213</v>
+        <v>10207</v>
       </c>
       <c r="C170" t="s">
-        <v>1942</v>
+        <v>1944</v>
       </c>
       <c r="D170" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="E170" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="F170" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="G170" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="H170" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="I170" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="J170" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="K170" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="L170" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="M170" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="N170" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="O170" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="171" ht="13.5" spans="2:15">
       <c r="B171">
-        <v>10214</v>
+        <v>10208</v>
       </c>
       <c r="C171" t="s">
-        <v>1938</v>
+        <v>1946</v>
       </c>
       <c r="D171" t="s">
-        <v>1939</v>
+        <v>1947</v>
       </c>
       <c r="E171" t="s">
-        <v>1939</v>
+        <v>1947</v>
       </c>
       <c r="F171" t="s">
-        <v>1939</v>
+        <v>1947</v>
       </c>
       <c r="G171" t="s">
-        <v>1939</v>
+        <v>1947</v>
       </c>
       <c r="H171" t="s">
-        <v>1939</v>
+        <v>1947</v>
       </c>
       <c r="I171" t="s">
-        <v>1939</v>
+        <v>1947</v>
       </c>
       <c r="J171" t="s">
-        <v>1939</v>
+        <v>1947</v>
       </c>
       <c r="K171" t="s">
-        <v>1939</v>
+        <v>1947</v>
       </c>
       <c r="L171" t="s">
-        <v>1939</v>
+        <v>1947</v>
       </c>
       <c r="M171" t="s">
-        <v>1939</v>
+        <v>1947</v>
       </c>
       <c r="N171" t="s">
-        <v>1939</v>
+        <v>1947</v>
       </c>
       <c r="O171" t="s">
-        <v>1939</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="172" ht="13.5" spans="2:15">
       <c r="B172">
-        <v>10215</v>
+        <v>10209</v>
       </c>
       <c r="C172" t="s">
-        <v>1932</v>
+        <v>1948</v>
       </c>
       <c r="D172" t="s">
-        <v>1933</v>
+        <v>1949</v>
       </c>
       <c r="E172" t="s">
-        <v>1933</v>
+        <v>1949</v>
       </c>
       <c r="F172" t="s">
-        <v>1933</v>
+        <v>1949</v>
       </c>
       <c r="G172" t="s">
-        <v>1933</v>
+        <v>1949</v>
       </c>
       <c r="H172" t="s">
-        <v>1933</v>
+        <v>1949</v>
       </c>
       <c r="I172" t="s">
-        <v>1933</v>
+        <v>1949</v>
       </c>
       <c r="J172" t="s">
-        <v>1933</v>
+        <v>1949</v>
       </c>
       <c r="K172" t="s">
-        <v>1933</v>
+        <v>1949</v>
       </c>
       <c r="L172" t="s">
-        <v>1933</v>
+        <v>1949</v>
       </c>
       <c r="M172" t="s">
-        <v>1933</v>
+        <v>1949</v>
       </c>
       <c r="N172" t="s">
-        <v>1933</v>
+        <v>1949</v>
       </c>
       <c r="O172" t="s">
-        <v>1933</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="173" ht="13.5" spans="2:15">
       <c r="B173">
-        <v>10216</v>
+        <v>10210</v>
       </c>
       <c r="C173" t="s">
         <v>1944</v>
@@ -15074,579 +14916,579 @@
     </row>
     <row r="174" ht="13.5" spans="2:15">
       <c r="B174">
-        <v>10217</v>
+        <v>10211</v>
       </c>
       <c r="C174" t="s">
-        <v>1946</v>
+        <v>1950</v>
       </c>
       <c r="D174" t="s">
-        <v>1947</v>
+        <v>1951</v>
       </c>
       <c r="E174" t="s">
-        <v>1947</v>
+        <v>1951</v>
       </c>
       <c r="F174" t="s">
-        <v>1947</v>
+        <v>1951</v>
       </c>
       <c r="G174" t="s">
-        <v>1947</v>
+        <v>1951</v>
       </c>
       <c r="H174" t="s">
-        <v>1947</v>
+        <v>1951</v>
       </c>
       <c r="I174" t="s">
-        <v>1947</v>
+        <v>1951</v>
       </c>
       <c r="J174" t="s">
-        <v>1947</v>
+        <v>1951</v>
       </c>
       <c r="K174" t="s">
-        <v>1947</v>
+        <v>1951</v>
       </c>
       <c r="L174" t="s">
-        <v>1947</v>
+        <v>1951</v>
       </c>
       <c r="M174" t="s">
-        <v>1947</v>
+        <v>1951</v>
       </c>
       <c r="N174" t="s">
-        <v>1947</v>
+        <v>1951</v>
       </c>
       <c r="O174" t="s">
-        <v>1947</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="175" ht="13.5" spans="2:15">
       <c r="B175">
-        <v>10218</v>
+        <v>10212</v>
       </c>
       <c r="C175" t="s">
-        <v>1948</v>
+        <v>1952</v>
       </c>
       <c r="D175" t="s">
-        <v>1949</v>
+        <v>1953</v>
       </c>
       <c r="E175" t="s">
-        <v>1949</v>
+        <v>1953</v>
       </c>
       <c r="F175" t="s">
-        <v>1949</v>
+        <v>1953</v>
       </c>
       <c r="G175" t="s">
-        <v>1949</v>
+        <v>1953</v>
       </c>
       <c r="H175" t="s">
-        <v>1949</v>
+        <v>1953</v>
       </c>
       <c r="I175" t="s">
-        <v>1949</v>
+        <v>1953</v>
       </c>
       <c r="J175" t="s">
-        <v>1949</v>
+        <v>1953</v>
       </c>
       <c r="K175" t="s">
-        <v>1949</v>
+        <v>1953</v>
       </c>
       <c r="L175" t="s">
-        <v>1949</v>
+        <v>1953</v>
       </c>
       <c r="M175" t="s">
-        <v>1949</v>
+        <v>1953</v>
       </c>
       <c r="N175" t="s">
-        <v>1949</v>
+        <v>1953</v>
       </c>
       <c r="O175" t="s">
-        <v>1949</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="176" ht="13.5" spans="2:15">
       <c r="B176">
-        <v>10219</v>
+        <v>10213</v>
       </c>
       <c r="C176" t="s">
-        <v>1950</v>
+        <v>1954</v>
       </c>
       <c r="D176" t="s">
-        <v>1951</v>
+        <v>1955</v>
       </c>
       <c r="E176" t="s">
-        <v>1951</v>
+        <v>1955</v>
       </c>
       <c r="F176" t="s">
-        <v>1951</v>
+        <v>1955</v>
       </c>
       <c r="G176" t="s">
-        <v>1951</v>
+        <v>1955</v>
       </c>
       <c r="H176" t="s">
-        <v>1951</v>
+        <v>1955</v>
       </c>
       <c r="I176" t="s">
-        <v>1951</v>
+        <v>1955</v>
       </c>
       <c r="J176" t="s">
-        <v>1951</v>
+        <v>1955</v>
       </c>
       <c r="K176" t="s">
-        <v>1951</v>
+        <v>1955</v>
       </c>
       <c r="L176" t="s">
-        <v>1951</v>
+        <v>1955</v>
       </c>
       <c r="M176" t="s">
-        <v>1951</v>
+        <v>1955</v>
       </c>
       <c r="N176" t="s">
-        <v>1951</v>
+        <v>1955</v>
       </c>
       <c r="O176" t="s">
-        <v>1951</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="177" ht="13.5" spans="2:15">
       <c r="B177">
-        <v>10220</v>
+        <v>10214</v>
       </c>
       <c r="C177" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="D177" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="E177" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="F177" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="G177" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="H177" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="I177" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="J177" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="K177" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="L177" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="M177" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="N177" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="O177" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="178" ht="13.5" spans="2:15">
       <c r="B178">
-        <v>10221</v>
+        <v>10215</v>
       </c>
       <c r="C178" t="s">
-        <v>1954</v>
+        <v>1944</v>
       </c>
       <c r="D178" t="s">
-        <v>1955</v>
+        <v>1945</v>
       </c>
       <c r="E178" t="s">
-        <v>1955</v>
+        <v>1945</v>
       </c>
       <c r="F178" t="s">
-        <v>1955</v>
+        <v>1945</v>
       </c>
       <c r="G178" t="s">
-        <v>1955</v>
+        <v>1945</v>
       </c>
       <c r="H178" t="s">
-        <v>1955</v>
+        <v>1945</v>
       </c>
       <c r="I178" t="s">
-        <v>1955</v>
+        <v>1945</v>
       </c>
       <c r="J178" t="s">
-        <v>1955</v>
+        <v>1945</v>
       </c>
       <c r="K178" t="s">
-        <v>1955</v>
+        <v>1945</v>
       </c>
       <c r="L178" t="s">
-        <v>1955</v>
+        <v>1945</v>
       </c>
       <c r="M178" t="s">
-        <v>1955</v>
+        <v>1945</v>
       </c>
       <c r="N178" t="s">
-        <v>1955</v>
+        <v>1945</v>
       </c>
       <c r="O178" t="s">
-        <v>1955</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="179" ht="13.5" spans="2:15">
       <c r="B179">
-        <v>10222</v>
+        <v>10216</v>
       </c>
       <c r="C179" t="s">
-        <v>1950</v>
+        <v>1956</v>
       </c>
       <c r="D179" t="s">
-        <v>1951</v>
+        <v>1957</v>
       </c>
       <c r="E179" t="s">
-        <v>1951</v>
+        <v>1957</v>
       </c>
       <c r="F179" t="s">
-        <v>1951</v>
+        <v>1957</v>
       </c>
       <c r="G179" t="s">
-        <v>1951</v>
+        <v>1957</v>
       </c>
       <c r="H179" t="s">
-        <v>1951</v>
+        <v>1957</v>
       </c>
       <c r="I179" t="s">
-        <v>1951</v>
+        <v>1957</v>
       </c>
       <c r="J179" t="s">
-        <v>1951</v>
+        <v>1957</v>
       </c>
       <c r="K179" t="s">
-        <v>1951</v>
+        <v>1957</v>
       </c>
       <c r="L179" t="s">
-        <v>1951</v>
+        <v>1957</v>
       </c>
       <c r="M179" t="s">
-        <v>1951</v>
+        <v>1957</v>
       </c>
       <c r="N179" t="s">
-        <v>1951</v>
+        <v>1957</v>
       </c>
       <c r="O179" t="s">
-        <v>1951</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="180" ht="13.5" spans="2:15">
       <c r="B180">
-        <v>10223</v>
+        <v>10217</v>
       </c>
       <c r="C180" t="s">
-        <v>1932</v>
+        <v>1958</v>
       </c>
       <c r="D180" t="s">
-        <v>1933</v>
+        <v>1959</v>
       </c>
       <c r="E180" t="s">
-        <v>1933</v>
+        <v>1959</v>
       </c>
       <c r="F180" t="s">
-        <v>1933</v>
+        <v>1959</v>
       </c>
       <c r="G180" t="s">
-        <v>1933</v>
+        <v>1959</v>
       </c>
       <c r="H180" t="s">
-        <v>1933</v>
+        <v>1959</v>
       </c>
       <c r="I180" t="s">
-        <v>1933</v>
+        <v>1959</v>
       </c>
       <c r="J180" t="s">
-        <v>1933</v>
+        <v>1959</v>
       </c>
       <c r="K180" t="s">
-        <v>1933</v>
+        <v>1959</v>
       </c>
       <c r="L180" t="s">
-        <v>1933</v>
+        <v>1959</v>
       </c>
       <c r="M180" t="s">
-        <v>1933</v>
+        <v>1959</v>
       </c>
       <c r="N180" t="s">
-        <v>1933</v>
+        <v>1959</v>
       </c>
       <c r="O180" t="s">
-        <v>1933</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="181" ht="13.5" spans="2:15">
       <c r="B181">
-        <v>10224</v>
+        <v>10218</v>
       </c>
       <c r="C181" t="s">
-        <v>1956</v>
+        <v>1960</v>
       </c>
       <c r="D181" t="s">
-        <v>1957</v>
+        <v>1961</v>
       </c>
       <c r="E181" t="s">
-        <v>1957</v>
+        <v>1961</v>
       </c>
       <c r="F181" t="s">
-        <v>1957</v>
+        <v>1961</v>
       </c>
       <c r="G181" t="s">
-        <v>1957</v>
+        <v>1961</v>
       </c>
       <c r="H181" t="s">
-        <v>1957</v>
+        <v>1961</v>
       </c>
       <c r="I181" t="s">
-        <v>1957</v>
+        <v>1961</v>
       </c>
       <c r="J181" t="s">
-        <v>1957</v>
+        <v>1961</v>
       </c>
       <c r="K181" t="s">
-        <v>1957</v>
+        <v>1961</v>
       </c>
       <c r="L181" t="s">
-        <v>1957</v>
+        <v>1961</v>
       </c>
       <c r="M181" t="s">
-        <v>1957</v>
+        <v>1961</v>
       </c>
       <c r="N181" t="s">
-        <v>1957</v>
+        <v>1961</v>
       </c>
       <c r="O181" t="s">
-        <v>1957</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="182" ht="13.5" spans="2:15">
       <c r="B182">
-        <v>10225</v>
+        <v>10219</v>
       </c>
       <c r="C182" t="s">
-        <v>1958</v>
+        <v>1962</v>
       </c>
       <c r="D182" t="s">
-        <v>1959</v>
+        <v>1963</v>
       </c>
       <c r="E182" t="s">
-        <v>1959</v>
+        <v>1963</v>
       </c>
       <c r="F182" t="s">
-        <v>1959</v>
+        <v>1963</v>
       </c>
       <c r="G182" t="s">
-        <v>1959</v>
+        <v>1963</v>
       </c>
       <c r="H182" t="s">
-        <v>1959</v>
+        <v>1963</v>
       </c>
       <c r="I182" t="s">
-        <v>1959</v>
+        <v>1963</v>
       </c>
       <c r="J182" t="s">
-        <v>1959</v>
+        <v>1963</v>
       </c>
       <c r="K182" t="s">
-        <v>1959</v>
+        <v>1963</v>
       </c>
       <c r="L182" t="s">
-        <v>1959</v>
+        <v>1963</v>
       </c>
       <c r="M182" t="s">
-        <v>1959</v>
+        <v>1963</v>
       </c>
       <c r="N182" t="s">
-        <v>1959</v>
+        <v>1963</v>
       </c>
       <c r="O182" t="s">
-        <v>1959</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="183" ht="13.5" spans="2:15">
       <c r="B183">
-        <v>10226</v>
+        <v>10220</v>
       </c>
       <c r="C183" t="s">
-        <v>1960</v>
+        <v>1964</v>
       </c>
       <c r="D183" t="s">
-        <v>1961</v>
+        <v>1965</v>
       </c>
       <c r="E183" t="s">
-        <v>1961</v>
+        <v>1965</v>
       </c>
       <c r="F183" t="s">
-        <v>1961</v>
+        <v>1965</v>
       </c>
       <c r="G183" t="s">
-        <v>1961</v>
+        <v>1965</v>
       </c>
       <c r="H183" t="s">
-        <v>1961</v>
+        <v>1965</v>
       </c>
       <c r="I183" t="s">
-        <v>1961</v>
+        <v>1965</v>
       </c>
       <c r="J183" t="s">
-        <v>1961</v>
+        <v>1965</v>
       </c>
       <c r="K183" t="s">
-        <v>1961</v>
+        <v>1965</v>
       </c>
       <c r="L183" t="s">
-        <v>1961</v>
+        <v>1965</v>
       </c>
       <c r="M183" t="s">
-        <v>1961</v>
+        <v>1965</v>
       </c>
       <c r="N183" t="s">
-        <v>1961</v>
+        <v>1965</v>
       </c>
       <c r="O183" t="s">
-        <v>1961</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="184" ht="13.5" spans="2:15">
       <c r="B184">
-        <v>10227</v>
+        <v>10221</v>
       </c>
       <c r="C184" t="s">
-        <v>1962</v>
+        <v>1966</v>
       </c>
       <c r="D184" t="s">
-        <v>1963</v>
+        <v>1967</v>
       </c>
       <c r="E184" t="s">
-        <v>1963</v>
+        <v>1967</v>
       </c>
       <c r="F184" t="s">
-        <v>1963</v>
+        <v>1967</v>
       </c>
       <c r="G184" t="s">
-        <v>1963</v>
+        <v>1967</v>
       </c>
       <c r="H184" t="s">
-        <v>1963</v>
+        <v>1967</v>
       </c>
       <c r="I184" t="s">
-        <v>1963</v>
+        <v>1967</v>
       </c>
       <c r="J184" t="s">
-        <v>1963</v>
+        <v>1967</v>
       </c>
       <c r="K184" t="s">
-        <v>1963</v>
+        <v>1967</v>
       </c>
       <c r="L184" t="s">
-        <v>1963</v>
+        <v>1967</v>
       </c>
       <c r="M184" t="s">
-        <v>1963</v>
+        <v>1967</v>
       </c>
       <c r="N184" t="s">
-        <v>1963</v>
+        <v>1967</v>
       </c>
       <c r="O184" t="s">
-        <v>1963</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="185" ht="13.5" spans="2:15">
       <c r="B185">
-        <v>10228</v>
+        <v>10222</v>
       </c>
       <c r="C185" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="D185" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="E185" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="F185" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="G185" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="H185" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="I185" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="J185" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="K185" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="L185" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="M185" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="N185" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="O185" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="186" ht="13.5" spans="2:15">
       <c r="B186">
-        <v>10229</v>
+        <v>10223</v>
       </c>
       <c r="C186" t="s">
-        <v>1966</v>
+        <v>1944</v>
       </c>
       <c r="D186" t="s">
-        <v>1967</v>
+        <v>1945</v>
       </c>
       <c r="E186" t="s">
-        <v>1967</v>
+        <v>1945</v>
       </c>
       <c r="F186" t="s">
-        <v>1967</v>
+        <v>1945</v>
       </c>
       <c r="G186" t="s">
-        <v>1967</v>
+        <v>1945</v>
       </c>
       <c r="H186" t="s">
-        <v>1967</v>
+        <v>1945</v>
       </c>
       <c r="I186" t="s">
-        <v>1967</v>
+        <v>1945</v>
       </c>
       <c r="J186" t="s">
-        <v>1967</v>
+        <v>1945</v>
       </c>
       <c r="K186" t="s">
-        <v>1967</v>
+        <v>1945</v>
       </c>
       <c r="L186" t="s">
-        <v>1967</v>
+        <v>1945</v>
       </c>
       <c r="M186" t="s">
-        <v>1967</v>
+        <v>1945</v>
       </c>
       <c r="N186" t="s">
-        <v>1967</v>
+        <v>1945</v>
       </c>
       <c r="O186" t="s">
-        <v>1967</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="187" ht="13.5" spans="2:15">
       <c r="B187">
-        <v>10230</v>
+        <v>10224</v>
       </c>
       <c r="C187" t="s">
         <v>1968</v>
@@ -15690,7 +15532,7 @@
     </row>
     <row r="188" ht="13.5" spans="2:15">
       <c r="B188">
-        <v>10231</v>
+        <v>10225</v>
       </c>
       <c r="C188" t="s">
         <v>1970</v>
@@ -15734,7 +15576,7 @@
     </row>
     <row r="189" ht="13.5" spans="2:15">
       <c r="B189">
-        <v>10232</v>
+        <v>10226</v>
       </c>
       <c r="C189" t="s">
         <v>1972</v>
@@ -15778,7 +15620,7 @@
     </row>
     <row r="190" ht="13.5" spans="2:15">
       <c r="B190">
-        <v>10233</v>
+        <v>10227</v>
       </c>
       <c r="C190" t="s">
         <v>1974</v>
@@ -15822,7 +15664,7 @@
     </row>
     <row r="191" ht="13.5" spans="2:15">
       <c r="B191">
-        <v>10234</v>
+        <v>10228</v>
       </c>
       <c r="C191" t="s">
         <v>1976</v>
@@ -15866,45 +15708,309 @@
     </row>
     <row r="192" ht="13.5" spans="2:15">
       <c r="B192">
+        <v>10229</v>
+      </c>
+      <c r="C192" t="s">
+        <v>1978</v>
+      </c>
+      <c r="D192" t="s">
+        <v>1979</v>
+      </c>
+      <c r="E192" t="s">
+        <v>1979</v>
+      </c>
+      <c r="F192" t="s">
+        <v>1979</v>
+      </c>
+      <c r="G192" t="s">
+        <v>1979</v>
+      </c>
+      <c r="H192" t="s">
+        <v>1979</v>
+      </c>
+      <c r="I192" t="s">
+        <v>1979</v>
+      </c>
+      <c r="J192" t="s">
+        <v>1979</v>
+      </c>
+      <c r="K192" t="s">
+        <v>1979</v>
+      </c>
+      <c r="L192" t="s">
+        <v>1979</v>
+      </c>
+      <c r="M192" t="s">
+        <v>1979</v>
+      </c>
+      <c r="N192" t="s">
+        <v>1979</v>
+      </c>
+      <c r="O192" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="193" ht="13.5" spans="2:15">
+      <c r="B193">
+        <v>10230</v>
+      </c>
+      <c r="C193" t="s">
+        <v>1980</v>
+      </c>
+      <c r="D193" t="s">
+        <v>1981</v>
+      </c>
+      <c r="E193" t="s">
+        <v>1981</v>
+      </c>
+      <c r="F193" t="s">
+        <v>1981</v>
+      </c>
+      <c r="G193" t="s">
+        <v>1981</v>
+      </c>
+      <c r="H193" t="s">
+        <v>1981</v>
+      </c>
+      <c r="I193" t="s">
+        <v>1981</v>
+      </c>
+      <c r="J193" t="s">
+        <v>1981</v>
+      </c>
+      <c r="K193" t="s">
+        <v>1981</v>
+      </c>
+      <c r="L193" t="s">
+        <v>1981</v>
+      </c>
+      <c r="M193" t="s">
+        <v>1981</v>
+      </c>
+      <c r="N193" t="s">
+        <v>1981</v>
+      </c>
+      <c r="O193" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="194" ht="13.5" spans="2:15">
+      <c r="B194">
+        <v>10231</v>
+      </c>
+      <c r="C194" t="s">
+        <v>1982</v>
+      </c>
+      <c r="D194" t="s">
+        <v>1983</v>
+      </c>
+      <c r="E194" t="s">
+        <v>1983</v>
+      </c>
+      <c r="F194" t="s">
+        <v>1983</v>
+      </c>
+      <c r="G194" t="s">
+        <v>1983</v>
+      </c>
+      <c r="H194" t="s">
+        <v>1983</v>
+      </c>
+      <c r="I194" t="s">
+        <v>1983</v>
+      </c>
+      <c r="J194" t="s">
+        <v>1983</v>
+      </c>
+      <c r="K194" t="s">
+        <v>1983</v>
+      </c>
+      <c r="L194" t="s">
+        <v>1983</v>
+      </c>
+      <c r="M194" t="s">
+        <v>1983</v>
+      </c>
+      <c r="N194" t="s">
+        <v>1983</v>
+      </c>
+      <c r="O194" t="s">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="195" ht="13.5" spans="2:15">
+      <c r="B195">
+        <v>10232</v>
+      </c>
+      <c r="C195" t="s">
+        <v>1984</v>
+      </c>
+      <c r="D195" t="s">
+        <v>1985</v>
+      </c>
+      <c r="E195" t="s">
+        <v>1985</v>
+      </c>
+      <c r="F195" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G195" t="s">
+        <v>1985</v>
+      </c>
+      <c r="H195" t="s">
+        <v>1985</v>
+      </c>
+      <c r="I195" t="s">
+        <v>1985</v>
+      </c>
+      <c r="J195" t="s">
+        <v>1985</v>
+      </c>
+      <c r="K195" t="s">
+        <v>1985</v>
+      </c>
+      <c r="L195" t="s">
+        <v>1985</v>
+      </c>
+      <c r="M195" t="s">
+        <v>1985</v>
+      </c>
+      <c r="N195" t="s">
+        <v>1985</v>
+      </c>
+      <c r="O195" t="s">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="196" ht="13.5" spans="2:15">
+      <c r="B196">
+        <v>10233</v>
+      </c>
+      <c r="C196" t="s">
+        <v>1986</v>
+      </c>
+      <c r="D196" t="s">
+        <v>1987</v>
+      </c>
+      <c r="E196" t="s">
+        <v>1987</v>
+      </c>
+      <c r="F196" t="s">
+        <v>1987</v>
+      </c>
+      <c r="G196" t="s">
+        <v>1987</v>
+      </c>
+      <c r="H196" t="s">
+        <v>1987</v>
+      </c>
+      <c r="I196" t="s">
+        <v>1987</v>
+      </c>
+      <c r="J196" t="s">
+        <v>1987</v>
+      </c>
+      <c r="K196" t="s">
+        <v>1987</v>
+      </c>
+      <c r="L196" t="s">
+        <v>1987</v>
+      </c>
+      <c r="M196" t="s">
+        <v>1987</v>
+      </c>
+      <c r="N196" t="s">
+        <v>1987</v>
+      </c>
+      <c r="O196" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="197" ht="13.5" spans="2:15">
+      <c r="B197">
+        <v>10234</v>
+      </c>
+      <c r="C197" t="s">
+        <v>1988</v>
+      </c>
+      <c r="D197" t="s">
+        <v>1989</v>
+      </c>
+      <c r="E197" t="s">
+        <v>1989</v>
+      </c>
+      <c r="F197" t="s">
+        <v>1989</v>
+      </c>
+      <c r="G197" t="s">
+        <v>1989</v>
+      </c>
+      <c r="H197" t="s">
+        <v>1989</v>
+      </c>
+      <c r="I197" t="s">
+        <v>1989</v>
+      </c>
+      <c r="J197" t="s">
+        <v>1989</v>
+      </c>
+      <c r="K197" t="s">
+        <v>1989</v>
+      </c>
+      <c r="L197" t="s">
+        <v>1989</v>
+      </c>
+      <c r="M197" t="s">
+        <v>1989</v>
+      </c>
+      <c r="N197" t="s">
+        <v>1989</v>
+      </c>
+      <c r="O197" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="198" ht="13.5" spans="2:15">
+      <c r="B198">
         <v>10235</v>
       </c>
-      <c r="C192" t="s">
+      <c r="C198" t="s">
         <v>1074</v>
       </c>
-      <c r="D192" t="s">
+      <c r="D198" t="s">
         <v>1075</v>
       </c>
-      <c r="E192" t="s">
+      <c r="E198" t="s">
         <v>1075</v>
       </c>
-      <c r="F192" t="s">
+      <c r="F198" t="s">
         <v>1075</v>
       </c>
-      <c r="G192" t="s">
+      <c r="G198" t="s">
         <v>1075</v>
       </c>
-      <c r="H192" t="s">
+      <c r="H198" t="s">
         <v>1075</v>
       </c>
-      <c r="I192" t="s">
+      <c r="I198" t="s">
         <v>1075</v>
       </c>
-      <c r="J192" t="s">
+      <c r="J198" t="s">
         <v>1075</v>
       </c>
-      <c r="K192" t="s">
+      <c r="K198" t="s">
         <v>1075</v>
       </c>
-      <c r="L192" t="s">
+      <c r="L198" t="s">
         <v>1075</v>
       </c>
-      <c r="M192" t="s">
+      <c r="M198" t="s">
         <v>1075</v>
       </c>
-      <c r="N192" t="s">
+      <c r="N198" t="s">
         <v>1075</v>
       </c>
-      <c r="O192" t="s">
+      <c r="O198" t="s">
         <v>1075</v>
       </c>
     </row>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2614" uniqueCount="2328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2658" uniqueCount="2379">
   <si>
     <t>##var</t>
   </si>
@@ -6921,43 +6921,43 @@
     <t>Finish Previous Step</t>
   </si>
   <si>
-    <t>恭喜您成功提现 ${0}！</t>
-  </si>
-  <si>
-    <t>Congratulations on your successful withdrawal of ${0}!</t>
-  </si>
-  <si>
-    <t>Herzlichen Glückwunsch zu Ihrer Auszahlung von ${0}!</t>
+    <t>恭喜您成功提现{0}！</t>
+  </si>
+  <si>
+    <t>Congratulations on your successful withdrawal of {0}!</t>
+  </si>
+  <si>
+    <t>Herzlichen Glückwunsch zu Ihrer Auszahlung von {0}!</t>
   </si>
   <si>
     <t>おめでとうございます！${0} の出金に成功しました！</t>
   </si>
   <si>
-    <t>Parabéns pelo saque bem-sucedido de ${0}!</t>
-  </si>
-  <si>
-    <t>Félicitations pour votre retrait réussi de ${0} !</t>
-  </si>
-  <si>
-    <t>¡Felicitaciones por su retiro exitoso de ${0}!</t>
-  </si>
-  <si>
-    <t>축하합니다! ${0} 출금에 성공했습니다!</t>
-  </si>
-  <si>
-    <t>Selamat atas penarikan berhasil ${0}!</t>
-  </si>
-  <si>
-    <t>Поздравляем с успешным выводом ${0}!</t>
-  </si>
-  <si>
-    <t>बधाई हो! ${0} की सफल निकासी!</t>
-  </si>
-  <si>
-    <t>ยินดีด้วย! ถอน ${0} สำเร็จแล้ว!</t>
-  </si>
-  <si>
-    <t>Tebrikler! ${0} çekiminiz başarılı!</t>
+    <t>Parabéns pelo saque bem-sucedido de {0}!</t>
+  </si>
+  <si>
+    <t>Félicitations pour votre retrait réussi de {0} !</t>
+  </si>
+  <si>
+    <t>¡Felicitaciones por su retiro exitoso de {0}!</t>
+  </si>
+  <si>
+    <t>축하합니다! {0} 출금에 성공했습니다!</t>
+  </si>
+  <si>
+    <t>Selamat atas penarikan berhasil {0}!</t>
+  </si>
+  <si>
+    <t>Поздравляем с успешным выводом {0}!</t>
+  </si>
+  <si>
+    <t>बधाई हो! {0} की सफल निकासी!</t>
+  </si>
+  <si>
+    <t>ยินดีด้วย! ถอน {0} สำเร็จแล้ว!</t>
+  </si>
+  <si>
+    <t>Tebrikler! {0} çekiminiz başarılı!</t>
   </si>
   <si>
     <t>做得好！身份核验已完成！</t>
@@ -7077,7 +7077,160 @@
     <t>Hazır! Tüm doğrulamalar tamamlandı!</t>
   </si>
   <si>
-    <t>All Set!Every Verification is Complete!</t>
+    <t>太好了！银行通道核验已完成！</t>
+  </si>
+  <si>
+    <t>Great! Bank Channel Verification Complete!</t>
+  </si>
+  <si>
+    <t>Super! Bankkanal-Überprüfung abgeschlossen!</t>
+  </si>
+  <si>
+    <t>素晴らしい！銀行チャネル審査が完了しました！</t>
+  </si>
+  <si>
+    <t>Ótimo! Verificação do canal bancário concluída!</t>
+  </si>
+  <si>
+    <t>Super ! Vérification du canal bancaire terminée !</t>
+  </si>
+  <si>
+    <t>¡Genial! Verificación del canal bancario completada.</t>
+  </si>
+  <si>
+    <t>훌륭합니다! 은행 채널 심사가 완료되었습니다!</t>
+  </si>
+  <si>
+    <t>Bagus! Verifikasi saluran bank selesai!</t>
+  </si>
+  <si>
+    <t>Отлично! Проверка банковского канала завершена!</t>
+  </si>
+  <si>
+    <t>बहुत बढ़िया! बैंक चैनल सत्यापन पूर्ण!</t>
+  </si>
+  <si>
+    <t>เยี่ยมมาก! ตรวจสอบช่องทางธนาคารเสร็จสิ้น!</t>
+  </si>
+  <si>
+    <t>Harika! Banka kanalı doğrulaması tamamlandı!</t>
+  </si>
+  <si>
+    <t>恭喜！到账金额核算已完成！</t>
+  </si>
+  <si>
+    <t>Congratulations! Payout Amount Calculated!</t>
+  </si>
+  <si>
+    <t>Herzlichen Glückwunsch! Auszahlungsbetrag berechnet!</t>
+  </si>
+  <si>
+    <t>おめでとうございます！入金額の算出が完了しました！</t>
+  </si>
+  <si>
+    <t>Parabéns! Valor do saque calculado!</t>
+  </si>
+  <si>
+    <t>Félicitations ! Montant du retrait calculé !</t>
+  </si>
+  <si>
+    <t>¡Felicitaciones! Monto del retiro calculado.</t>
+  </si>
+  <si>
+    <t>축하합니다! 입금액 산출이 완료되었습니다!</t>
+  </si>
+  <si>
+    <t>Selamat! Jumlah penarikan telah dihitung!</t>
+  </si>
+  <si>
+    <t>Поздравляем! Сумма выплаты рассчитана!</t>
+  </si>
+  <si>
+    <t>बधाई हो! निकासी राशि की गणना पूर्ण!</t>
+  </si>
+  <si>
+    <t>ยินดีด้วย! คำนวณยอดรับจริงเสร็จสิ้น!</t>
+  </si>
+  <si>
+    <t>Tebrikler! Ödeme tutarı hesaplandı!</t>
+  </si>
+  <si>
+    <t>很好！您已成功加入打款排队！</t>
+  </si>
+  <si>
+    <t>Excellent! You Have Joined the Payout Queue!</t>
+  </si>
+  <si>
+    <t>Ausgezeichnet! Sie sind in der Auszahlungs-Warteschlange!</t>
+  </si>
+  <si>
+    <t>順調です！出金処理キューに登録されました！</t>
+  </si>
+  <si>
+    <t>Excelente! Você entrou na fila de saque!</t>
+  </si>
+  <si>
+    <t>Excellent ! Vous avez rejoint la file de retrait !</t>
+  </si>
+  <si>
+    <t>¡Excelente! Se ha unido a la cola de retiro.</t>
+  </si>
+  <si>
+    <t>훌륭합니다! 출금 대기열에 등록되었습니다!</t>
+  </si>
+  <si>
+    <t>Luar biasa! Anda telah masuk antrean penarikan!</t>
+  </si>
+  <si>
+    <t>Отлично! Вы в очереди на выплату!</t>
+  </si>
+  <si>
+    <t>शानदार! आप भुगतान कतार में शामिल हो गए!</t>
+  </si>
+  <si>
+    <t>ยอดเยี่ยม! คุณเข้าคิวถอนเงินเรียบร้อยแล้ว!</t>
+  </si>
+  <si>
+    <t>Harika! Ödeme kuyruğuna alındınız!</t>
+  </si>
+  <si>
+    <t>一切就绪！您的提现已进入最终打款处理！</t>
+  </si>
+  <si>
+    <t>All Set! Your Payout Is in Final Processing!</t>
+  </si>
+  <si>
+    <t>Alles bereit! Ihre Auszahlung wird final bearbeitet!</t>
+  </si>
+  <si>
+    <t>準備完了！出金は最終処理に入りました！</t>
+  </si>
+  <si>
+    <t>Tudo pronto! Seu saque está em processamento final!</t>
+  </si>
+  <si>
+    <t>Tout est prêt ! Votre retrait est en traitement final !</t>
+  </si>
+  <si>
+    <t>¡Todo listo! Su retiro está en procesamiento final.</t>
+  </si>
+  <si>
+    <t>모든 준비 완료! 출금이 최종 처리 단계에 들어갔습니다!</t>
+  </si>
+  <si>
+    <t>Siap! Penarikan Anda masuk pemrosesan akhir!</t>
+  </si>
+  <si>
+    <t>Готово! Ваша выплата на финальной обработке!</t>
+  </si>
+  <si>
+    <t>सब तैयार! आपकी निकासी अंतिम प्रसंस्करण में है!</t>
+  </si>
+  <si>
+    <t>พร้อมแล้ว! การถอนของคุณอยู่ในขั้นตอนสุดท้าย!</t>
+  </si>
+  <si>
+    <t>Hazır! Çekiminiz son işleme alındı!</t>
   </si>
 </sst>
 </file>
@@ -8362,7 +8515,7 @@
   <cols>
     <col min="1" max="1" width="9.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="31.625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="44.25" style="2" customWidth="1"/>
     <col min="4" max="4" width="54.25" style="1" customWidth="1"/>
     <col min="5" max="6" width="28.125" style="2" customWidth="1"/>
     <col min="7" max="7" width="59.875" style="2" customWidth="1"/>
@@ -15069,7 +15222,7 @@
         <v>1818</v>
       </c>
     </row>
-    <row r="150" customFormat="1" ht="13.5" spans="2:15">
+    <row r="150" ht="13.5" customHeight="1" spans="2:15">
       <c r="B150" s="3">
         <v>10145</v>
       </c>
@@ -15113,7 +15266,7 @@
         <v>1831</v>
       </c>
     </row>
-    <row r="151" customFormat="1" ht="13.5" spans="2:15">
+    <row r="151" ht="13.5" customHeight="1" spans="2:15">
       <c r="B151" s="3">
         <v>10146</v>
       </c>
@@ -15157,7 +15310,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="152" customFormat="1" ht="13.5" spans="2:15">
+    <row r="152" ht="13.5" customHeight="1" spans="2:15">
       <c r="B152" s="3">
         <v>10147</v>
       </c>
@@ -15201,7 +15354,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="153" customFormat="1" ht="13.5" spans="2:15">
+    <row r="153" ht="13.5" customHeight="1" spans="2:15">
       <c r="B153" s="3">
         <v>10148</v>
       </c>
@@ -15245,7 +15398,7 @@
         <v>1870</v>
       </c>
     </row>
-    <row r="154" customFormat="1" ht="13.5" spans="2:15">
+    <row r="154" ht="13.5" customHeight="1" spans="2:15">
       <c r="B154" s="3">
         <v>10149</v>
       </c>
@@ -15289,7 +15442,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="155" customFormat="1" ht="13.5" spans="2:15">
+    <row r="155" ht="13.5" customHeight="1" spans="2:15">
       <c r="B155" s="3">
         <v>10150</v>
       </c>
@@ -15333,7 +15486,7 @@
         <v>1896</v>
       </c>
     </row>
-    <row r="156" customFormat="1" ht="13.5" spans="2:15">
+    <row r="156" ht="13.5" customHeight="1" spans="2:15">
       <c r="B156" s="3">
         <v>10151</v>
       </c>
@@ -15377,7 +15530,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="157" customFormat="1" ht="13.5" spans="2:15">
+    <row r="157" ht="13.5" customHeight="1" spans="2:15">
       <c r="B157" s="3">
         <v>10152</v>
       </c>
@@ -15421,7 +15574,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="158" customFormat="1" ht="13.5" spans="2:15">
+    <row r="158" ht="13.5" customHeight="1" spans="2:15">
       <c r="B158" s="3">
         <v>10153</v>
       </c>
@@ -15432,7 +15585,7 @@
         <v>1923</v>
       </c>
     </row>
-    <row r="159" customFormat="1" ht="27" spans="2:15">
+    <row r="159" ht="27" customHeight="1" spans="2:15">
       <c r="B159" s="3">
         <v>10154</v>
       </c>
@@ -15443,7 +15596,7 @@
         <v>1925</v>
       </c>
     </row>
-    <row r="160" customFormat="1" ht="13.5" spans="2:15">
+    <row r="160" ht="13.5" customHeight="1" spans="2:15">
       <c r="B160" s="3">
         <v>10155</v>
       </c>
@@ -15454,7 +15607,7 @@
         <v>1927</v>
       </c>
     </row>
-    <row r="161" customFormat="1" ht="40.5" spans="2:15">
+    <row r="161" ht="40.5" customHeight="1" spans="2:15">
       <c r="B161" s="3">
         <v>10156</v>
       </c>
@@ -15465,7 +15618,7 @@
         <v>1929</v>
       </c>
     </row>
-    <row r="162" customFormat="1" ht="13.5" spans="2:15">
+    <row r="162" ht="13.5" customHeight="1" spans="2:15">
       <c r="B162" s="3">
         <v>10157</v>
       </c>
@@ -15476,7 +15629,7 @@
         <v>1931</v>
       </c>
     </row>
-    <row r="163" customFormat="1" ht="27" spans="2:15">
+    <row r="163" ht="27" customHeight="1" spans="2:15">
       <c r="B163" s="3">
         <v>10158</v>
       </c>
@@ -17027,7 +17180,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="199" ht="27" spans="2:17">
+    <row r="199" ht="27" customHeight="1" spans="2:17">
       <c r="B199">
         <v>10236</v>
       </c>
@@ -17073,7 +17226,7 @@
       <c r="P199" s="19"/>
       <c r="Q199" s="19"/>
     </row>
-    <row r="200" ht="13.5" spans="2:17">
+    <row r="200" ht="13.5" customHeight="1" spans="2:17">
       <c r="B200">
         <v>10237</v>
       </c>
@@ -17117,7 +17270,7 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="201" ht="27" spans="2:17">
+    <row r="201" ht="27" customHeight="1" spans="2:17">
       <c r="B201" s="3">
         <v>10238</v>
       </c>
@@ -17161,7 +17314,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="202" ht="13.5" spans="2:17">
+    <row r="202" ht="13.5" customHeight="1" spans="2:17">
       <c r="B202" s="3">
         <v>10239</v>
       </c>
@@ -17205,7 +17358,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="203" ht="13.5" spans="2:17">
+    <row r="203" ht="13.5" customHeight="1" spans="2:17">
       <c r="B203" s="3">
         <v>10240</v>
       </c>
@@ -17249,7 +17402,7 @@
         <v>2313</v>
       </c>
     </row>
-    <row r="204" ht="13.5" spans="2:17">
+    <row r="204" ht="13.5" customHeight="1" spans="2:17">
       <c r="B204" s="3">
         <v>10241</v>
       </c>
@@ -17293,48 +17446,180 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="205" ht="13.5" spans="2:17">
+    <row r="205" ht="13.5" customHeight="1" spans="2:17">
       <c r="B205" s="3">
         <v>10242</v>
       </c>
       <c r="C205" t="s">
-        <v>2314</v>
+        <v>2327</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>2327</v>
-      </c>
-    </row>
-    <row r="206" ht="13.5" spans="2:17">
+        <v>2328</v>
+      </c>
+      <c r="E205" t="s">
+        <v>2329</v>
+      </c>
+      <c r="F205" t="s">
+        <v>2330</v>
+      </c>
+      <c r="G205" t="s">
+        <v>2331</v>
+      </c>
+      <c r="H205" t="s">
+        <v>2332</v>
+      </c>
+      <c r="I205" t="s">
+        <v>2333</v>
+      </c>
+      <c r="J205" t="s">
+        <v>2334</v>
+      </c>
+      <c r="K205" t="s">
+        <v>2335</v>
+      </c>
+      <c r="L205" t="s">
+        <v>2336</v>
+      </c>
+      <c r="M205" t="s">
+        <v>2337</v>
+      </c>
+      <c r="N205" t="s">
+        <v>2338</v>
+      </c>
+      <c r="O205" t="s">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="206" ht="13.5" customHeight="1" spans="2:17">
       <c r="B206" s="3">
         <v>10243</v>
       </c>
       <c r="C206" t="s">
-        <v>2314</v>
+        <v>2340</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>2327</v>
-      </c>
-    </row>
-    <row r="207" ht="13.5" spans="2:17">
+        <v>2341</v>
+      </c>
+      <c r="E206" t="s">
+        <v>2342</v>
+      </c>
+      <c r="F206" t="s">
+        <v>2343</v>
+      </c>
+      <c r="G206" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H206" t="s">
+        <v>2345</v>
+      </c>
+      <c r="I206" t="s">
+        <v>2346</v>
+      </c>
+      <c r="J206" t="s">
+        <v>2347</v>
+      </c>
+      <c r="K206" t="s">
+        <v>2348</v>
+      </c>
+      <c r="L206" t="s">
+        <v>2349</v>
+      </c>
+      <c r="M206" t="s">
+        <v>2350</v>
+      </c>
+      <c r="N206" t="s">
+        <v>2351</v>
+      </c>
+      <c r="O206" t="s">
+        <v>2352</v>
+      </c>
+    </row>
+    <row r="207" ht="13.5" customHeight="1" spans="2:17">
       <c r="B207" s="3">
         <v>10244</v>
       </c>
       <c r="C207" t="s">
-        <v>2314</v>
+        <v>2353</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>2327</v>
-      </c>
-    </row>
-    <row r="208" ht="13.5" spans="2:17">
+        <v>2354</v>
+      </c>
+      <c r="E207" t="s">
+        <v>2355</v>
+      </c>
+      <c r="F207" t="s">
+        <v>2356</v>
+      </c>
+      <c r="G207" t="s">
+        <v>2357</v>
+      </c>
+      <c r="H207" t="s">
+        <v>2358</v>
+      </c>
+      <c r="I207" t="s">
+        <v>2359</v>
+      </c>
+      <c r="J207" t="s">
+        <v>2360</v>
+      </c>
+      <c r="K207" t="s">
+        <v>2361</v>
+      </c>
+      <c r="L207" t="s">
+        <v>2362</v>
+      </c>
+      <c r="M207" t="s">
+        <v>2363</v>
+      </c>
+      <c r="N207" t="s">
+        <v>2364</v>
+      </c>
+      <c r="O207" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="208" ht="13.5" customHeight="1" spans="2:17">
       <c r="B208" s="3">
         <v>10245</v>
       </c>
       <c r="C208" t="s">
-        <v>2314</v>
+        <v>2366</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>2327</v>
+        <v>2367</v>
+      </c>
+      <c r="E208" t="s">
+        <v>2368</v>
+      </c>
+      <c r="F208" t="s">
+        <v>2369</v>
+      </c>
+      <c r="G208" t="s">
+        <v>2370</v>
+      </c>
+      <c r="H208" t="s">
+        <v>2371</v>
+      </c>
+      <c r="I208" t="s">
+        <v>2372</v>
+      </c>
+      <c r="J208" t="s">
+        <v>2373</v>
+      </c>
+      <c r="K208" t="s">
+        <v>2374</v>
+      </c>
+      <c r="L208" t="s">
+        <v>2375</v>
+      </c>
+      <c r="M208" t="s">
+        <v>2376</v>
+      </c>
+      <c r="N208" t="s">
+        <v>2377</v>
+      </c>
+      <c r="O208" t="s">
+        <v>2378</v>
       </c>
     </row>
   </sheetData>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -12708,7 +12708,7 @@
       </c>
       <c r="M165" s="0" t="inlineStr">
         <is>
-          <t>निकासी लक्ष्य पूरा &lt;color=#EA2111&gt;{0}&lt;/color&gt;</t>
+          <t>निकासी लक्ष्य &lt;color=#EA2111&gt;{0}&lt;/color&gt;</t>
         </is>
       </c>
       <c r="N165" s="0" t="inlineStr">
@@ -15180,67 +15180,67 @@
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
-          <t>恭喜您成功提现{0}！</t>
+          <t>恭喜您成功提现&lt;color=#EA2111&gt;{0}&lt;/color&gt;！</t>
         </is>
       </c>
       <c r="D201" s="1" t="inlineStr">
         <is>
-          <t>Congratulations on your successful withdrawal of {0}!</t>
+          <t>Congratulations on your successful withdrawal of &lt;color=#EA2111&gt;{0}&lt;/color&gt;!</t>
         </is>
       </c>
       <c r="E201" s="0" t="inlineStr">
         <is>
-          <t>Herzlichen Glückwunsch zu Ihrer Auszahlung von {0}!</t>
+          <t>Herzlichen Glückwunsch zu Ihrer Auszahlung von &lt;color=#EA2111&gt;{0}&lt;/color&gt;!</t>
         </is>
       </c>
       <c r="F201" s="0" t="inlineStr">
         <is>
-          <t>おめでとうございます！${0} の出金に成功しました！</t>
+          <t>おめでとうございます！&lt;color=#EA2111&gt;{0}&lt;/color&gt; の出金に成功しました！</t>
         </is>
       </c>
       <c r="G201" s="0" t="inlineStr">
         <is>
-          <t>Parabéns pelo saque bem-sucedido de {0}!</t>
+          <t>Parabéns pelo saque bem-sucedido de &lt;color=#EA2111&gt;{0}&lt;/color&gt;!</t>
         </is>
       </c>
       <c r="H201" s="0" t="inlineStr">
         <is>
-          <t>Félicitations pour votre retrait réussi de {0} !</t>
+          <t>Félicitations pour votre retrait réussi de &lt;color=#EA2111&gt;{0}&lt;/color&gt; !</t>
         </is>
       </c>
       <c r="I201" s="0" t="inlineStr">
         <is>
-          <t>¡Felicitaciones por su retiro exitoso de {0}!</t>
+          <t>¡Felicitaciones por su retiro exitoso de &lt;color=#EA2111&gt;{0}&lt;/color&gt;!</t>
         </is>
       </c>
       <c r="J201" s="0" t="inlineStr">
         <is>
-          <t>축하합니다! {0} 출금에 성공했습니다!</t>
+          <t>축하합니다! &lt;color=#EA2111&gt;{0}&lt;/color&gt; 출금에 성공했습니다!</t>
         </is>
       </c>
       <c r="K201" s="0" t="inlineStr">
         <is>
-          <t>Selamat atas penarikan berhasil {0}!</t>
+          <t>Selamat atas penarikan berhasil &lt;color=#EA2111&gt;{0}&lt;/color&gt;!</t>
         </is>
       </c>
       <c r="L201" s="0" t="inlineStr">
         <is>
-          <t>Поздравляем с успешным выводом {0}!</t>
+          <t>Поздравляем с успешным выводом &lt;color=#EA2111&gt;{0}&lt;/color&gt;!</t>
         </is>
       </c>
       <c r="M201" s="0" t="inlineStr">
         <is>
-          <t>बधाई हो! {0} की सफल निकासी!</t>
+          <t>बधाई हो! &lt;color=#EA2111&gt;{0}&lt;/color&gt; की सफल निकासी!</t>
         </is>
       </c>
       <c r="N201" s="0" t="inlineStr">
         <is>
-          <t>ยินดีด้วย! ถอน {0} สำเร็จแล้ว!</t>
+          <t>ยินดีด้วย! ถอน &lt;color=#EA2111&gt;{0}&lt;/color&gt; สำเร็จแล้ว!</t>
         </is>
       </c>
       <c r="O201" s="0" t="inlineStr">
         <is>
-          <t>Tebrikler! {0} çekiminiz başarılı!</t>
+          <t>Tebrikler! &lt;color=#EA2111&gt;{0}&lt;/color&gt; çekiminiz başarılı!</t>
         </is>
       </c>
     </row>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Language" sheetId="1" r:id="rId1"/>
@@ -6921,43 +6921,43 @@
     <t>Finish Previous Step</t>
   </si>
   <si>
-    <t>恭喜您成功提现 ${0}！</t>
-  </si>
-  <si>
-    <t>Congratulations on your successful withdrawal of ${0}!</t>
-  </si>
-  <si>
-    <t>Herzlichen Glückwunsch zu Ihrer Auszahlung von ${0}!</t>
-  </si>
-  <si>
-    <t>おめでとうございます！${0} の出金に成功しました！</t>
-  </si>
-  <si>
-    <t>Parabéns pelo saque bem-sucedido de ${0}!</t>
-  </si>
-  <si>
-    <t>Félicitations pour votre retrait réussi de ${0} !</t>
-  </si>
-  <si>
-    <t>¡Felicitaciones por su retiro exitoso de ${0}!</t>
-  </si>
-  <si>
-    <t>축하합니다! ${0} 출금에 성공했습니다!</t>
-  </si>
-  <si>
-    <t>Selamat atas penarikan berhasil ${0}!</t>
-  </si>
-  <si>
-    <t>Поздравляем с успешным выводом ${0}!</t>
-  </si>
-  <si>
-    <t>बधाई हो! ${0} की सफल निकासी!</t>
-  </si>
-  <si>
-    <t>ยินดีด้วย! ถอน ${0} สำเร็จแล้ว!</t>
-  </si>
-  <si>
-    <t>Tebrikler! ${0} çekiminiz başarılı!</t>
+    <t>恭喜您成功提现 {0}！</t>
+  </si>
+  <si>
+    <t>Congratulations on your successful withdrawal of {0}!</t>
+  </si>
+  <si>
+    <t>Herzlichen Glückwunsch zu Ihrer Auszahlung von {0}!</t>
+  </si>
+  <si>
+    <t>おめでとうございます！{0} の出金に成功しました！</t>
+  </si>
+  <si>
+    <t>Parabéns pelo saque bem-sucedido de {0}!</t>
+  </si>
+  <si>
+    <t>Félicitations pour votre retrait réussi de {0} !</t>
+  </si>
+  <si>
+    <t>¡Felicitaciones por su retiro exitoso de {0}!</t>
+  </si>
+  <si>
+    <t>축하합니다! {0} 출금에 성공했습니다!</t>
+  </si>
+  <si>
+    <t>Selamat atas penarikan berhasil {0}!</t>
+  </si>
+  <si>
+    <t>Поздравляем с успешным выводом {0}!</t>
+  </si>
+  <si>
+    <t>बधाई हो! {0} की सफल निकासी!</t>
+  </si>
+  <si>
+    <t>ยินดีด้วย! ถอน {0} สำเร็จแล้ว!</t>
+  </si>
+  <si>
+    <t>Tebrikler! {0} çekiminiz başarılı!</t>
   </si>
   <si>
     <t>做得好！身份核验已完成！</t>
@@ -17117,7 +17117,7 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="201" ht="27" spans="2:17">
+    <row r="201" ht="13.5" spans="2:17">
       <c r="B201" s="3">
         <v>10238</v>
       </c>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1881" uniqueCount="1764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="1766">
   <si>
     <t>##var</t>
   </si>
@@ -5395,6 +5395,12 @@
   </si>
   <si>
     <t>Earn &lt;color=#EA2111&gt;{0}&lt;/color&gt; more to withdraw &lt;color=#EA2111&gt;{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Ganhe mais &lt;color=#EA2111&gt;{0}&lt;/color&gt; para poder sacar &lt;color=#EA2111&gt;{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Dapatkan lagi &lt;color=#EA2111&gt;{0}&lt;/color&gt; untuk bisa menarik &lt;color=#EA2111&gt;{1}&lt;/color&gt;</t>
   </si>
 </sst>
 </file>
@@ -13124,6 +13130,12 @@
       <c r="D143" s="1" t="s">
         <v>1763</v>
       </c>
+      <c r="G143" s="2" t="s">
+        <v>1764</v>
+      </c>
+      <c r="K143" s="2" t="s">
+        <v>1765</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1879" uniqueCount="1762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="1766">
   <si>
     <t>##var</t>
   </si>
@@ -5389,6 +5389,18 @@
   <si>
     <t>Videoyu sonuna kadar izle
 Nakit ödülü al</t>
+  </si>
+  <si>
+    <t>再挣&lt;color=#EA2111&gt;{0}&lt;/color&gt;即可提现&lt;color=#EA2111&gt;{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Earn &lt;color=#EA2111&gt;{0}&lt;/color&gt; more to withdraw &lt;color=#EA2111&gt;{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Ganhe mais &lt;color=#EA2111&gt;{0}&lt;/color&gt; para poder sacar &lt;color=#EA2111&gt;{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Dapatkan lagi &lt;color=#EA2111&gt;{0}&lt;/color&gt; untuk bisa menarik &lt;color=#EA2111&gt;{1}&lt;/color&gt;</t>
   </si>
 </sst>
 </file>
@@ -6667,7 +6679,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W142"/>
+  <dimension ref="A1:W143"/>
   <sheetFormatPr defaultColWidth="9.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.875" style="2" customWidth="1"/>
@@ -13108,6 +13120,23 @@
         <v>1251</v>
       </c>
     </row>
+    <row r="143" customHeight="1" spans="1:16">
+      <c r="B143" s="3">
+        <v>10138</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>1763</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>1764</v>
+      </c>
+      <c r="K143" s="2" t="s">
+        <v>1765</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/DesignerConfigs/Datas/Language.xlsx
+++ b/DesignerConfigs/Datas/Language.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\_Project\AsWaterGameProj\DesignerConfigs\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1935" uniqueCount="1818">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1987" uniqueCount="1870">
   <si>
     <t>##var</t>
   </si>
@@ -5557,6 +5562,162 @@
   </si>
   <si>
     <t>Gizlilik Politikası</t>
+  </si>
+  <si>
+    <t>请输入您的 Pix 密钥（CPF、CNPJ、手机号、邮箱或随机密钥）</t>
+  </si>
+  <si>
+    <t>Enter your Pix key (CPF, CNPJ, phone, email or random key)</t>
+  </si>
+  <si>
+    <t>Geben Sie Ihren Pix-Schlüssel ein (CPF, CNPJ, Telefon, E-Mail oder Zufallsschlüssel)</t>
+  </si>
+  <si>
+    <t>Pixキーを入力してください（CPF、CNPJ、電話番号、メール、またはランダムキー）</t>
+  </si>
+  <si>
+    <t>Digite sua chave Pix (CPF, CNPJ, telefone, e-mail ou chave aleatória)</t>
+  </si>
+  <si>
+    <t>Saisissez votre clé Pix (CPF, CNPJ, téléphone, e-mail ou clé aléatoire)</t>
+  </si>
+  <si>
+    <t>Introduzca su clave Pix (CPF, CNPJ, teléfono, correo o clave aleatoria)</t>
+  </si>
+  <si>
+    <t>Pix 키를 입력하세요 (CPF, CNPJ, 전화번호, 이메일 또는 랜덤 키)</t>
+  </si>
+  <si>
+    <t>Masukkan kunci Pix Anda (CPF, CNPJ, telepon, email, atau kunci acak)</t>
+  </si>
+  <si>
+    <t>Введите ваш ключ Pix (CPF, CNPJ, телефон, эл. почта или случайный ключ)</t>
+  </si>
+  <si>
+    <t>अपनी Pix कुंजी दर्ज करें (CPF, CNPJ, फ़ोन, ईमेल या रैंडम कुंजी)</t>
+  </si>
+  <si>
+    <t>กรอกคีย์ Pix ของคุณ (CPF, CNPJ, โทรศัพท์, อีเมล หรือคีย์แบบสุ่ม)</t>
+  </si>
+  <si>
+    <t>Pix anahtarınızı girin (CPF, CNPJ, telefon, e-posta veya rastgele anahtar)</t>
+  </si>
+  <si>
+    <t>请输入您的 Pix 密钥</t>
+  </si>
+  <si>
+    <t>Please enter your Pix key</t>
+  </si>
+  <si>
+    <t>Bitte geben Sie Ihren Pix-Schlüssel ein</t>
+  </si>
+  <si>
+    <t>Pixキーを入力してください</t>
+  </si>
+  <si>
+    <t>Por favor, digite sua chave Pix</t>
+  </si>
+  <si>
+    <t>Veuillez saisir votre clé Pix</t>
+  </si>
+  <si>
+    <t>Por favor, introduzca su clave Pix</t>
+  </si>
+  <si>
+    <t>Pix 키를 입력해 주세요</t>
+  </si>
+  <si>
+    <t>Silakan masukkan kunci Pix Anda</t>
+  </si>
+  <si>
+    <t>Пожалуйста, введите ваш ключ Pix</t>
+  </si>
+  <si>
+    <t>कृपया अपनी Pix कुंजी दर्ज करें</t>
+  </si>
+  <si>
+    <t>โปรดกรอกคีย์ Pix ของคุณ</t>
+  </si>
+  <si>
+    <t>Lütfen Pix anahtarınızı girin</t>
+  </si>
+  <si>
+    <t>Pix 密钥格式不正确</t>
+  </si>
+  <si>
+    <t>Invalid Pix key format</t>
+  </si>
+  <si>
+    <t>Ungültiges Pix-Schlüssel-Format</t>
+  </si>
+  <si>
+    <t>Pixキーの形式が正しくありません</t>
+  </si>
+  <si>
+    <t>Formato de chave Pix inválido</t>
+  </si>
+  <si>
+    <t>Format de clé Pix invalide</t>
+  </si>
+  <si>
+    <t>Formato de clave Pix no válido</t>
+  </si>
+  <si>
+    <t>Pix 키 형식이 잘못되었습니다</t>
+  </si>
+  <si>
+    <t>Format kunci Pix tidak valid</t>
+  </si>
+  <si>
+    <t>Неверный формат ключа Pix</t>
+  </si>
+  <si>
+    <t>अमान्य Pix कुंजी प्रारूप</t>
+  </si>
+  <si>
+    <t>รูปแบบคีย์ Pix ไม่ถูกต้อง</t>
+  </si>
+  <si>
+    <t>Geçersiz Pix anahtarı formatı</t>
+  </si>
+  <si>
+    <t>Pix 密钥或个人税号（CPF）格式无效</t>
+  </si>
+  <si>
+    <t>Invalid Pix key or CPF (tax ID) format</t>
+  </si>
+  <si>
+    <t>Ungültiges Pix-Schlüssel- oder CPF-Steuernummer-Format</t>
+  </si>
+  <si>
+    <t>PixキーまたはCPF（個人納税者番号）の形式が無効です</t>
+  </si>
+  <si>
+    <t>Chave Pix ou CPF inválido</t>
+  </si>
+  <si>
+    <t>Format de clé Pix ou CPF invalide</t>
+  </si>
+  <si>
+    <t>Formato de clave Pix o CPF no válido</t>
+  </si>
+  <si>
+    <t>Pix 키 또는 CPF(개인 납세자 번호) 형식이 올바르지 않습니다</t>
+  </si>
+  <si>
+    <t>Format kunci Pix atau CPF tidak valid</t>
+  </si>
+  <si>
+    <t>Неверный формат ключа Pix или CPF</t>
+  </si>
+  <si>
+    <t>अमान्य Pix कुंजी या CPF प्रारूप</t>
+  </si>
+  <si>
+    <t>รูปแบบคีย์ Pix หรือ CPF ไม่ถูกต้อง</t>
+  </si>
+  <si>
+    <t>Geçersiz Pix anahtarı veya CPF formatı</t>
   </si>
 </sst>
 </file>
@@ -6835,7 +6996,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W147"/>
+  <dimension ref="A1:W151"/>
   <sheetFormatPr defaultColWidth="9.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.875" style="2" customWidth="1"/>
@@ -13381,7 +13542,7 @@
         <v>1791</v>
       </c>
     </row>
-    <row r="146" spans="2:15">
+    <row r="146" ht="13.5" spans="2:15">
       <c r="B146" s="3">
         <v>10141</v>
       </c>
@@ -13425,7 +13586,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="147" spans="2:15">
+    <row r="147" ht="13.5" customHeight="1" spans="2:15">
       <c r="B147" s="3">
         <v>10142</v>
       </c>
@@ -13467,6 +13628,182 @@
       </c>
       <c r="O147" t="s">
         <v>1817</v>
+      </c>
+    </row>
+    <row r="148" s="1" customFormat="1" ht="13.5" customHeight="1" spans="2:15">
+      <c r="B148" s="3">
+        <v>10143</v>
+      </c>
+      <c r="C148" t="s">
+        <v>1818</v>
+      </c>
+      <c r="D148" t="s">
+        <v>1819</v>
+      </c>
+      <c r="E148" t="s">
+        <v>1820</v>
+      </c>
+      <c r="F148" t="s">
+        <v>1821</v>
+      </c>
+      <c r="G148" t="s">
+        <v>1822</v>
+      </c>
+      <c r="H148" t="s">
+        <v>1823</v>
+      </c>
+      <c r="I148" t="s">
+        <v>1824</v>
+      </c>
+      <c r="J148" t="s">
+        <v>1825</v>
+      </c>
+      <c r="K148" t="s">
+        <v>1826</v>
+      </c>
+      <c r="L148" t="s">
+        <v>1827</v>
+      </c>
+      <c r="M148" t="s">
+        <v>1828</v>
+      </c>
+      <c r="N148" t="s">
+        <v>1829</v>
+      </c>
+      <c r="O148" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="149" s="1" customFormat="1" ht="13.5" customHeight="1" spans="2:15">
+      <c r="B149" s="3">
+        <v>10144</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D149" t="s">
+        <v>1832</v>
+      </c>
+      <c r="E149" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F149" t="s">
+        <v>1834</v>
+      </c>
+      <c r="G149" t="s">
+        <v>1835</v>
+      </c>
+      <c r="H149" t="s">
+        <v>1836</v>
+      </c>
+      <c r="I149" t="s">
+        <v>1837</v>
+      </c>
+      <c r="J149" t="s">
+        <v>1838</v>
+      </c>
+      <c r="K149" t="s">
+        <v>1839</v>
+      </c>
+      <c r="L149" t="s">
+        <v>1840</v>
+      </c>
+      <c r="M149" t="s">
+        <v>1841</v>
+      </c>
+      <c r="N149" t="s">
+        <v>1842</v>
+      </c>
+      <c r="O149" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="150" s="1" customFormat="1" ht="13.5" customHeight="1" spans="2:15">
+      <c r="B150" s="3">
+        <v>10145</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="D150" t="s">
+        <v>1845</v>
+      </c>
+      <c r="E150" t="s">
+        <v>1846</v>
+      </c>
+      <c r="F150" t="s">
+        <v>1847</v>
+      </c>
+      <c r="G150" t="s">
+        <v>1848</v>
+      </c>
+      <c r="H150" t="s">
+        <v>1849</v>
+      </c>
+      <c r="I150" t="s">
+        <v>1850</v>
+      </c>
+      <c r="J150" t="s">
+        <v>1851</v>
+      </c>
+      <c r="K150" t="s">
+        <v>1852</v>
+      </c>
+      <c r="L150" t="s">
+        <v>1853</v>
+      </c>
+      <c r="M150" t="s">
+        <v>1854</v>
+      </c>
+      <c r="N150" t="s">
+        <v>1855</v>
+      </c>
+      <c r="O150" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="151" ht="13.5" spans="2:15">
+      <c r="B151" s="3">
+        <v>10146</v>
+      </c>
+      <c r="C151" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D151" t="s">
+        <v>1858</v>
+      </c>
+      <c r="E151" t="s">
+        <v>1859</v>
+      </c>
+      <c r="F151" t="s">
+        <v>1860</v>
+      </c>
+      <c r="G151" t="s">
+        <v>1861</v>
+      </c>
+      <c r="H151" t="s">
+        <v>1862</v>
+      </c>
+      <c r="I151" t="s">
+        <v>1863</v>
+      </c>
+      <c r="J151" t="s">
+        <v>1864</v>
+      </c>
+      <c r="K151" t="s">
+        <v>1865</v>
+      </c>
+      <c r="L151" t="s">
+        <v>1866</v>
+      </c>
+      <c r="M151" t="s">
+        <v>1867</v>
+      </c>
+      <c r="N151" t="s">
+        <v>1868</v>
+      </c>
+      <c r="O151" t="s">
+        <v>1869</v>
       </c>
     </row>
   </sheetData>
